--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77A88FAA-C236-C240-8D51-3405750F5112}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53EF775A-CC36-6949-B0ED-DF57D71D3FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7440" yWindow="-34040" windowWidth="43180" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7820" yWindow="-34040" windowWidth="45120" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -63,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="334" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="149">
   <si>
     <t>Trade ID</t>
   </si>
@@ -2800,7 +2800,7 @@
         <v>1</v>
       </c>
       <c r="S25" s="36">
-        <f t="shared" ref="S25:S34" si="4">IF(R25=1, ABS(N25-M25)/M25, 0)</f>
+        <f t="shared" ref="S25:S35" si="4">IF(R25=1, ABS(N25-M25)/M25, 0)</f>
         <v>3.9539800653504951E-3</v>
       </c>
       <c r="T25" s="29">
@@ -3219,11 +3219,11 @@
         <v>46266</v>
       </c>
       <c r="C32" s="51">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="D32" s="31">
         <f t="shared" si="5"/>
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E32" s="43" t="s">
         <v>101</v>
@@ -3247,22 +3247,22 @@
         <v>101</v>
       </c>
       <c r="L32" s="43">
-        <v>-3000</v>
+        <v>-4000</v>
       </c>
       <c r="M32" s="43">
-        <v>50.25</v>
+        <v>50.493000000000002</v>
       </c>
       <c r="N32" s="43" t="s">
         <v>72</v>
       </c>
       <c r="O32" s="43">
-        <v>50.59</v>
+        <v>51.29</v>
       </c>
       <c r="P32" s="45">
-        <v>149745</v>
+        <v>204960</v>
       </c>
       <c r="Q32" s="43">
-        <v>1.21</v>
+        <v>7.88</v>
       </c>
       <c r="R32" s="43" t="s">
         <v>72</v>
@@ -3277,7 +3277,7 @@
         <v>72</v>
       </c>
       <c r="V32" s="29">
-        <v>-994</v>
+        <v>-2508</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
@@ -3421,66 +3421,64 @@
       <c r="B35" s="30">
         <v>46275</v>
       </c>
-      <c r="C35" s="51">
-        <v>46276</v>
+      <c r="C35" s="30">
+        <v>46279</v>
       </c>
       <c r="D35" s="31">
         <f t="shared" si="5"/>
+        <v>4</v>
+      </c>
+      <c r="E35" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="F35" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="G35" s="29" t="s">
+        <v>23</v>
+      </c>
+      <c r="H35" s="32" t="s">
+        <v>24</v>
+      </c>
+      <c r="I35" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="J35" s="29" t="s">
+        <v>133</v>
+      </c>
+      <c r="K35" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="L35" s="29">
         <v>1</v>
       </c>
-      <c r="E35" s="43" t="s">
+      <c r="M35" s="29">
+        <v>52061.3</v>
+      </c>
+      <c r="N35" s="29">
+        <v>52341</v>
+      </c>
+      <c r="O35" s="29">
+        <v>52341</v>
+      </c>
+      <c r="P35" s="35">
+        <v>26031</v>
+      </c>
+      <c r="Q35" s="29">
+        <v>3.11</v>
+      </c>
+      <c r="R35" s="29">
+        <v>1</v>
+      </c>
+      <c r="S35" s="36">
+        <f t="shared" si="4"/>
+        <v>5.3725127878096988E-3</v>
+      </c>
+      <c r="T35" s="29">
         <v>141</v>
       </c>
-      <c r="F35" s="44" t="s">
-        <v>142</v>
-      </c>
-      <c r="G35" s="43" t="s">
-        <v>23</v>
-      </c>
-      <c r="H35" s="44" t="s">
-        <v>24</v>
-      </c>
-      <c r="I35" s="43" t="s">
-        <v>32</v>
-      </c>
-      <c r="J35" s="43" t="s">
-        <v>133</v>
-      </c>
-      <c r="K35" s="43" t="s">
+      <c r="U35" s="37">
         <v>141</v>
-      </c>
-      <c r="L35" s="43">
-        <v>1</v>
-      </c>
-      <c r="M35" s="43">
-        <v>52061.3</v>
-      </c>
-      <c r="N35" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="O35" s="43">
-        <v>52575</v>
-      </c>
-      <c r="P35" s="45">
-        <v>26031</v>
-      </c>
-      <c r="Q35" s="43">
-        <v>3.11</v>
-      </c>
-      <c r="R35" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="S35" s="46" t="s">
-        <v>72</v>
-      </c>
-      <c r="T35" s="43" t="s">
-        <v>72</v>
-      </c>
-      <c r="U35" s="45" t="s">
-        <v>72</v>
-      </c>
-      <c r="V35" s="29">
-        <v>256</v>
       </c>
     </row>
     <row r="36" spans="1:22" x14ac:dyDescent="0.25">
@@ -3491,11 +3489,11 @@
         <v>46275</v>
       </c>
       <c r="C36" s="51">
-        <v>46276</v>
+        <v>46280</v>
       </c>
       <c r="D36" s="31">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E36" s="43" t="s">
         <v>56</v>
@@ -3519,22 +3517,22 @@
         <v>56</v>
       </c>
       <c r="L36" s="43">
-        <v>-100</v>
+        <v>-150</v>
       </c>
       <c r="M36" s="43">
-        <v>653.82000000000005</v>
+        <v>656.93</v>
       </c>
       <c r="N36" s="43" t="s">
         <v>72</v>
       </c>
       <c r="O36" s="43">
-        <v>647.32000000000005</v>
+        <v>665.6</v>
       </c>
       <c r="P36" s="45">
-        <v>64709</v>
+        <v>99615</v>
       </c>
       <c r="Q36" s="43">
-        <v>2.1</v>
+        <v>4.5</v>
       </c>
       <c r="R36" s="43" t="s">
         <v>72</v>
@@ -3549,7 +3547,7 @@
         <v>72</v>
       </c>
       <c r="V36" s="29">
-        <v>646</v>
+        <v>-678</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
@@ -3702,11 +3700,11 @@
       <c r="H40" s="32"/>
       <c r="U40" s="35">
         <f>SUM(U2:U38)</f>
-        <v>72040.47</v>
+        <v>72181.47</v>
       </c>
       <c r="V40" s="35">
         <f>SUM(V2:V38)</f>
-        <v>-92</v>
+        <v>-3186</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
@@ -3735,7 +3733,7 @@
       <c r="F43" s="32"/>
       <c r="U43" s="35">
         <f>U40+V40</f>
-        <v>71948.47</v>
+        <v>68995.47</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
@@ -3761,7 +3759,7 @@
     <row r="49" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U49" s="50">
         <f>U43/U46</f>
-        <v>0.21606147147147148</v>
+        <v>0.20719360360360362</v>
       </c>
     </row>
   </sheetData>
@@ -3840,11 +3838,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" ref="C4:C68" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C69" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="19">
-        <f t="shared" ref="D4:D68" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D69" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -4867,8 +4865,8 @@
         <v>114</v>
       </c>
       <c r="G65" s="23">
-        <f>AVERAGE(C3:C68)</f>
-        <v>1196.1983333333328</v>
+        <f>AVERAGE(C3:C69)</f>
+        <v>1120.5983582089548</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -4891,8 +4889,8 @@
         <v>115</v>
       </c>
       <c r="G66" s="23">
-        <f>_xlfn.STDEV.S(C3:C68)</f>
-        <v>4328.013952603199</v>
+        <f>_xlfn.STDEV.S(C3:C69)</f>
+        <v>4339.449266120314</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -4916,7 +4914,7 @@
       </c>
       <c r="G67" s="24">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.3874765793761332</v>
+        <v>4.0993560153667232</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -4939,17 +4937,32 @@
         <v>117</v>
       </c>
       <c r="G68" s="25">
-        <f>_xlfn.STDEV.S(D2:D68)*SQRT(252)</f>
-        <v>0.18836225122995642</v>
+        <f>_xlfn.STDEV.S(D2:D69)*SQRT(252)</f>
+        <v>0.18852491501012922</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A69" s="22">
+        <v>46279</v>
+      </c>
+      <c r="B69" s="1">
+        <f>B68-1737-2132</f>
+        <v>408536</v>
+      </c>
+      <c r="C69" s="1">
+        <f t="shared" si="0"/>
+        <v>-3869</v>
+      </c>
+      <c r="D69" s="19">
+        <f t="shared" si="1"/>
+        <v>-9.3815545398334161E-3</v>
+      </c>
       <c r="F69" s="21" t="s">
         <v>118</v>
       </c>
       <c r="G69" s="25" cm="1">
-        <f t="array" ref="G69">PRODUCT(1+D2:D68)-1</f>
-        <v>0.23676039705392182</v>
+        <f t="array" ref="G69">PRODUCT(1+D2:D69)-1</f>
+        <v>0.22515766193625431</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -4957,8 +4970,8 @@
         <v>119</v>
       </c>
       <c r="G70" s="25" cm="1">
-        <f t="array" ref="G70">PRODUCT(1+D2:D68)^(252/COUNT(D2:D68))-1</f>
-        <v>1.223842035187003</v>
+        <f t="array" ref="G70">PRODUCT(1+D2:D69)^(252/COUNT(D2:D68))-1</f>
+        <v>1.1463826547279097</v>
       </c>
     </row>
   </sheetData>
@@ -9501,7 +9514,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="10">
-        <f t="shared" ref="L69:L75" si="0">SUM(C69:K69)</f>
+        <f t="shared" ref="L69:L76" si="0">SUM(C69:K69)</f>
         <v>407651</v>
       </c>
       <c r="M69" s="11">
@@ -9947,6 +9960,77 @@
         <v>0</v>
       </c>
       <c r="U75" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A76" s="6">
+        <v>46279</v>
+      </c>
+      <c r="B76" s="7">
+        <v>408536</v>
+      </c>
+      <c r="C76" s="15">
+        <v>304575</v>
+      </c>
+      <c r="D76" s="9">
+        <f>B76-C76-I76</f>
+        <v>103961</v>
+      </c>
+      <c r="E76" s="9">
+        <v>0</v>
+      </c>
+      <c r="F76" s="9">
+        <v>0</v>
+      </c>
+      <c r="G76" s="9">
+        <v>0</v>
+      </c>
+      <c r="H76" s="9">
+        <v>0</v>
+      </c>
+      <c r="I76" s="9">
+        <v>0</v>
+      </c>
+      <c r="J76" s="9">
+        <v>0</v>
+      </c>
+      <c r="K76" s="14">
+        <v>0</v>
+      </c>
+      <c r="L76" s="10">
+        <f t="shared" si="0"/>
+        <v>408536</v>
+      </c>
+      <c r="M76" s="11">
+        <f t="shared" ref="M76" si="3">C76/L76</f>
+        <v>0.74552793389077099</v>
+      </c>
+      <c r="N76" s="11">
+        <f t="shared" ref="N76" si="4">D76/L76</f>
+        <v>0.25447206610922907</v>
+      </c>
+      <c r="O76" s="12">
+        <v>0</v>
+      </c>
+      <c r="P76" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q76" s="12">
+        <v>0</v>
+      </c>
+      <c r="R76" s="12">
+        <v>0</v>
+      </c>
+      <c r="S76" s="12">
+        <f>I76/L76</f>
+        <v>0</v>
+      </c>
+      <c r="T76" s="12">
+        <f>K76/L76</f>
+        <v>0</v>
+      </c>
+      <c r="U76" s="11">
         <v>0</v>
       </c>
     </row>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53EF775A-CC36-6949-B0ED-DF57D71D3FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F763E2-9B5D-774A-9DDA-B42EB486BCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7820" yWindow="-34040" windowWidth="45120" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7440" yWindow="-34040" windowWidth="45120" windowHeight="25040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,7 @@
     <sheet name="exposure" sheetId="7" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -3247,19 +3248,19 @@
         <v>101</v>
       </c>
       <c r="L32" s="43">
-        <v>-4000</v>
+        <v>-5000</v>
       </c>
       <c r="M32" s="43">
-        <v>50.493000000000002</v>
+        <v>50.685000000000002</v>
       </c>
       <c r="N32" s="43" t="s">
         <v>72</v>
       </c>
       <c r="O32" s="43">
-        <v>51.29</v>
+        <v>51.45</v>
       </c>
       <c r="P32" s="45">
-        <v>204960</v>
+        <v>256630</v>
       </c>
       <c r="Q32" s="43">
         <v>7.88</v>
@@ -3277,7 +3278,7 @@
         <v>72</v>
       </c>
       <c r="V32" s="29">
-        <v>-2508</v>
+        <v>-3205</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
@@ -3517,19 +3518,19 @@
         <v>56</v>
       </c>
       <c r="L36" s="43">
-        <v>-150</v>
+        <v>-200</v>
       </c>
       <c r="M36" s="43">
-        <v>656.93</v>
+        <v>672.34</v>
       </c>
       <c r="N36" s="43" t="s">
         <v>72</v>
       </c>
       <c r="O36" s="43">
-        <v>665.6</v>
+        <v>674.51</v>
       </c>
       <c r="P36" s="45">
-        <v>99615</v>
+        <v>134902</v>
       </c>
       <c r="Q36" s="43">
         <v>4.5</v>
@@ -3547,7 +3548,7 @@
         <v>72</v>
       </c>
       <c r="V36" s="29">
-        <v>-678</v>
+        <v>-432</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
@@ -3704,7 +3705,7 @@
       </c>
       <c r="V40" s="35">
         <f>SUM(V2:V38)</f>
-        <v>-3186</v>
+        <v>-3637</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
@@ -3733,7 +3734,7 @@
       <c r="F43" s="32"/>
       <c r="U43" s="35">
         <f>U40+V40</f>
-        <v>68995.47</v>
+        <v>68544.47</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
@@ -3759,7 +3760,7 @@
     <row r="49" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U49" s="50">
         <f>U43/U46</f>
-        <v>0.20719360360360362</v>
+        <v>0.20583924924924926</v>
       </c>
     </row>
   </sheetData>
@@ -3838,11 +3839,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" ref="C4:C69" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C70" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="19">
-        <f t="shared" ref="D4:D69" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D70" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -4865,8 +4866,8 @@
         <v>114</v>
       </c>
       <c r="G65" s="23">
-        <f>AVERAGE(C3:C69)</f>
-        <v>1120.5983582089548</v>
+        <f>AVERAGE(C3:C70)</f>
+        <v>1068.4277941176465</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -4889,8 +4890,8 @@
         <v>115</v>
       </c>
       <c r="G66" s="23">
-        <f>_xlfn.STDEV.S(C3:C69)</f>
-        <v>4339.449266120314</v>
+        <f>_xlfn.STDEV.S(C3:C70)</f>
+        <v>4328.3765001233951</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -4914,7 +4915,7 @@
       </c>
       <c r="G67" s="24">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.0993560153667232</v>
+        <v>3.9185051073778232</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -4937,8 +4938,8 @@
         <v>117</v>
       </c>
       <c r="G68" s="25">
-        <f>_xlfn.STDEV.S(D2:D69)*SQRT(252)</f>
-        <v>0.18852491501012922</v>
+        <f>_xlfn.STDEV.S(D2:D70)*SQRT(252)</f>
+        <v>0.18792239134347269</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -4961,17 +4962,32 @@
         <v>118</v>
       </c>
       <c r="G69" s="25" cm="1">
-        <f t="array" ref="G69">PRODUCT(1+D2:D69)-1</f>
-        <v>0.22515766193625431</v>
+        <f t="array" ref="G69">PRODUCT(1+D2:D70)-1</f>
+        <v>0.21787933727081654</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A70" s="22">
+        <v>46280</v>
+      </c>
+      <c r="B70" s="1">
+        <f>B69-1790-637</f>
+        <v>406109</v>
+      </c>
+      <c r="C70" s="1">
+        <f t="shared" si="0"/>
+        <v>-2427</v>
+      </c>
+      <c r="D70" s="19">
+        <f t="shared" si="1"/>
+        <v>-5.9407249299939296E-3</v>
+      </c>
       <c r="F70" s="21" t="s">
         <v>119</v>
       </c>
       <c r="G70" s="25" cm="1">
-        <f t="array" ref="G70">PRODUCT(1+D2:D69)^(252/COUNT(D2:D68))-1</f>
-        <v>1.1463826547279097</v>
+        <f t="array" ref="G70">PRODUCT(1+D2:D70)^(252/COUNT(D2:D70))-1</f>
+        <v>1.0541949316854442</v>
       </c>
     </row>
   </sheetData>
@@ -9514,7 +9530,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="10">
-        <f t="shared" ref="L69:L76" si="0">SUM(C69:K69)</f>
+        <f t="shared" ref="L69:L77" si="0">SUM(C69:K69)</f>
         <v>407651</v>
       </c>
       <c r="M69" s="11">
@@ -10031,6 +10047,77 @@
         <v>0</v>
       </c>
       <c r="U76" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A77" s="6">
+        <v>46280</v>
+      </c>
+      <c r="B77" s="7">
+        <v>406109</v>
+      </c>
+      <c r="C77" s="15">
+        <v>391532</v>
+      </c>
+      <c r="D77" s="9">
+        <f>B77-C77-I77</f>
+        <v>14577</v>
+      </c>
+      <c r="E77" s="9">
+        <v>0</v>
+      </c>
+      <c r="F77" s="9">
+        <v>0</v>
+      </c>
+      <c r="G77" s="9">
+        <v>0</v>
+      </c>
+      <c r="H77" s="9">
+        <v>0</v>
+      </c>
+      <c r="I77" s="9">
+        <v>0</v>
+      </c>
+      <c r="J77" s="9">
+        <v>0</v>
+      </c>
+      <c r="K77" s="14">
+        <v>0</v>
+      </c>
+      <c r="L77" s="10">
+        <f t="shared" si="0"/>
+        <v>406109</v>
+      </c>
+      <c r="M77" s="11">
+        <f t="shared" ref="M77" si="5">C77/L77</f>
+        <v>0.96410569576148275</v>
+      </c>
+      <c r="N77" s="11">
+        <f t="shared" ref="N77" si="6">D77/L77</f>
+        <v>3.5894304238517243E-2</v>
+      </c>
+      <c r="O77" s="12">
+        <v>0</v>
+      </c>
+      <c r="P77" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="12">
+        <v>0</v>
+      </c>
+      <c r="R77" s="12">
+        <v>0</v>
+      </c>
+      <c r="S77" s="12">
+        <f>I77/L77</f>
+        <v>0</v>
+      </c>
+      <c r="T77" s="12">
+        <f>K77/L77</f>
+        <v>0</v>
+      </c>
+      <c r="U77" s="11">
         <v>0</v>
       </c>
     </row>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15F763E2-9B5D-774A-9DDA-B42EB486BCE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A558ADE0-B97D-3E47-8448-55B897DDB3D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7440" yWindow="-34040" windowWidth="45120" windowHeight="25040" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7440" yWindow="-34040" windowWidth="45120" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,6 @@
     <sheet name="exposure" sheetId="7" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -64,7 +63,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="329" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="341" uniqueCount="151">
   <si>
     <t>Trade ID</t>
   </si>
@@ -511,6 +510,12 @@
   </si>
   <si>
     <t>Rates_Exposure</t>
+  </si>
+  <si>
+    <t>TAN</t>
+  </si>
+  <si>
+    <t>Invesco Solar ETF</t>
   </si>
 </sst>
 </file>
@@ -1107,7 +1112,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V49"/>
+  <dimension ref="A1:V50"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.1640625" style="29" bestFit="1" customWidth="1"/>
@@ -2822,7 +2827,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="31">
-        <f t="shared" ref="D26:D38" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D39" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="29" t="s">
@@ -3220,11 +3225,11 @@
         <v>46266</v>
       </c>
       <c r="C32" s="51">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D32" s="31">
         <f t="shared" si="5"/>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E32" s="43" t="s">
         <v>101</v>
@@ -3248,7 +3253,7 @@
         <v>101</v>
       </c>
       <c r="L32" s="43">
-        <v>-5000</v>
+        <v>-2000</v>
       </c>
       <c r="M32" s="43">
         <v>50.685000000000002</v>
@@ -3257,10 +3262,10 @@
         <v>72</v>
       </c>
       <c r="O32" s="43">
-        <v>51.45</v>
+        <v>49.76</v>
       </c>
       <c r="P32" s="45">
-        <v>256630</v>
+        <v>99520</v>
       </c>
       <c r="Q32" s="43">
         <v>7.88</v>
@@ -3278,7 +3283,7 @@
         <v>72</v>
       </c>
       <c r="V32" s="29">
-        <v>-3205</v>
+        <v>3600</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
@@ -3490,11 +3495,11 @@
         <v>46275</v>
       </c>
       <c r="C36" s="51">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="D36" s="31">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E36" s="43" t="s">
         <v>56</v>
@@ -3518,19 +3523,19 @@
         <v>56</v>
       </c>
       <c r="L36" s="43">
-        <v>-200</v>
+        <v>-280</v>
       </c>
       <c r="M36" s="43">
-        <v>672.34</v>
+        <v>674.59</v>
       </c>
       <c r="N36" s="43" t="s">
         <v>72</v>
       </c>
       <c r="O36" s="43">
-        <v>674.51</v>
+        <v>673.31</v>
       </c>
       <c r="P36" s="45">
-        <v>134902</v>
+        <v>188496</v>
       </c>
       <c r="Q36" s="43">
         <v>4.5</v>
@@ -3548,7 +3553,7 @@
         <v>72</v>
       </c>
       <c r="V36" s="29">
-        <v>-432</v>
+        <v>389</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
@@ -3686,81 +3691,150 @@
       </c>
     </row>
     <row r="39" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F39" s="32"/>
-      <c r="H39" s="32"/>
+      <c r="A39" s="29">
+        <v>34</v>
+      </c>
+      <c r="B39" s="30">
+        <v>46281</v>
+      </c>
+      <c r="C39" s="51">
+        <v>46281</v>
+      </c>
+      <c r="D39" s="31">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E39" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="F39" s="44" t="s">
+        <v>150</v>
+      </c>
+      <c r="G39" s="43" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" s="44" t="s">
+        <v>24</v>
+      </c>
+      <c r="I39" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="J39" s="43" t="s">
+        <v>48</v>
+      </c>
+      <c r="K39" s="43" t="s">
+        <v>149</v>
+      </c>
+      <c r="L39" s="43">
+        <v>2000</v>
+      </c>
+      <c r="M39" s="43">
+        <v>45.21</v>
+      </c>
+      <c r="N39" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="O39" s="43">
+        <v>44.64</v>
+      </c>
+      <c r="P39" s="45">
+        <v>88000</v>
+      </c>
+      <c r="Q39" s="43">
+        <v>5.3</v>
+      </c>
+      <c r="R39" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="S39" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="T39" s="43" t="s">
+        <v>72</v>
+      </c>
+      <c r="U39" s="45" t="s">
+        <v>72</v>
+      </c>
+      <c r="V39" s="29">
+        <v>-1100</v>
+      </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D40" s="48" t="s">
+      <c r="F40" s="32"/>
+      <c r="H40" s="32"/>
+    </row>
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D41" s="48" t="s">
         <v>103</v>
       </c>
-      <c r="E40" s="42">
+      <c r="E41" s="42">
         <f>AVERAGE(D2:D31)</f>
         <v>8.5333333333333332</v>
       </c>
-      <c r="F40" s="32"/>
-      <c r="H40" s="32"/>
-      <c r="U40" s="35">
-        <f>SUM(U2:U38)</f>
+      <c r="F41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="U41" s="35">
+        <f>SUM(U2:U39)</f>
         <v>72181.47</v>
       </c>
-      <c r="V40" s="35">
-        <f>SUM(V2:V38)</f>
-        <v>-3637</v>
-      </c>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D41" s="48" t="s">
+      <c r="V41" s="35">
+        <f>SUM(V2:V39)</f>
+        <v>2889</v>
+      </c>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D42" s="48" t="s">
         <v>104</v>
       </c>
-      <c r="E41" s="42">
+      <c r="E42" s="42">
         <f>AVERAGE(D2:D11,D13,D15:D31)</f>
         <v>5</v>
       </c>
-      <c r="F41" s="32"/>
-      <c r="U41" s="49" t="s">
+      <c r="F42" s="32"/>
+      <c r="U42" s="49" t="s">
         <v>105</v>
       </c>
-      <c r="V41" s="32" t="s">
+      <c r="V42" s="32" t="s">
         <v>106</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F42" s="32"/>
-      <c r="U42" s="29" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F43" s="32"/>
-      <c r="U43" s="35">
-        <f>U40+V40</f>
-        <v>68544.47</v>
+      <c r="U43" s="29" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F44" s="32"/>
+      <c r="U44" s="35">
+        <f>U41+V41</f>
+        <v>75070.47</v>
+      </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F45" s="32"/>
-      <c r="U45" s="32" t="s">
-        <v>108</v>
-      </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F46" s="32"/>
-      <c r="U46" s="35">
+      <c r="U46" s="32" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F47" s="32"/>
+      <c r="U47" s="35">
         <v>333000</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="U48" s="29" t="s">
+    <row r="49" spans="21:21" x14ac:dyDescent="0.25">
+      <c r="U49" s="29" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="49" spans="21:21" x14ac:dyDescent="0.25">
-      <c r="U49" s="50">
-        <f>U43/U46</f>
-        <v>0.20583924924924926</v>
+    <row r="50" spans="21:21" x14ac:dyDescent="0.25">
+      <c r="U50" s="50">
+        <f>U44/U47</f>
+        <v>0.22543684684684684</v>
       </c>
     </row>
   </sheetData>
@@ -3773,7 +3847,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:G70"/>
+  <dimension ref="A1:G71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="20" bestFit="1" customWidth="1"/>
@@ -3839,11 +3913,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="1">
-        <f t="shared" ref="C4:C70" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C71" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="19">
-        <f t="shared" ref="D4:D70" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D71" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -4866,8 +4940,8 @@
         <v>114</v>
       </c>
       <c r="G65" s="23">
-        <f>AVERAGE(C3:C70)</f>
-        <v>1068.4277941176465</v>
+        <f>AVERAGE(C3:C71)</f>
+        <v>1137.0013043478257</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -4890,8 +4964,8 @@
         <v>115</v>
       </c>
       <c r="G66" s="23">
-        <f>_xlfn.STDEV.S(C3:C70)</f>
-        <v>4328.3765001233951</v>
+        <f>_xlfn.STDEV.S(C3:C71)</f>
+        <v>4334.0271391583974</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -4915,7 +4989,7 @@
       </c>
       <c r="G67" s="24">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>3.9185051073778232</v>
+        <v>4.1645646347907652</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -4938,8 +5012,8 @@
         <v>117</v>
       </c>
       <c r="G68" s="25">
-        <f>_xlfn.STDEV.S(D2:D70)*SQRT(252)</f>
-        <v>0.18792239134347269</v>
+        <f>_xlfn.STDEV.S(D2:D71)*SQRT(252)</f>
+        <v>0.18779508191267738</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -4962,8 +5036,8 @@
         <v>118</v>
       </c>
       <c r="G69" s="25" cm="1">
-        <f t="array" ref="G69">PRODUCT(1+D2:D70)-1</f>
-        <v>0.21787933727081654</v>
+        <f t="array" ref="G69">PRODUCT(1+D2:D71)-1</f>
+        <v>0.23527294380544328</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -4986,8 +5060,25 @@
         <v>119</v>
       </c>
       <c r="G70" s="25" cm="1">
-        <f t="array" ref="G70">PRODUCT(1+D2:D70)^(252/COUNT(D2:D70))-1</f>
-        <v>1.0541949316854442</v>
+        <f t="array" ref="G70">PRODUCT(1+D2:D71)^(252/COUNT(D2:D71))-1</f>
+        <v>1.1396687558113086</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A71" s="22">
+        <v>46281</v>
+      </c>
+      <c r="B71" s="1">
+        <f>B70+5800</f>
+        <v>411909</v>
+      </c>
+      <c r="C71" s="1">
+        <f t="shared" si="0"/>
+        <v>5800</v>
+      </c>
+      <c r="D71" s="19">
+        <f t="shared" si="1"/>
+        <v>1.4281879987885026E-2</v>
       </c>
     </row>
   </sheetData>
@@ -9530,7 +9621,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="10">
-        <f t="shared" ref="L69:L77" si="0">SUM(C69:K69)</f>
+        <f t="shared" ref="L69:L78" si="0">SUM(C69:K69)</f>
         <v>407651</v>
       </c>
       <c r="M69" s="11">
@@ -10118,6 +10209,78 @@
         <v>0</v>
       </c>
       <c r="U77" s="11">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A78" s="6">
+        <v>46281</v>
+      </c>
+      <c r="B78" s="7">
+        <f>B77+5870</f>
+        <v>411979</v>
+      </c>
+      <c r="C78" s="15">
+        <v>288016</v>
+      </c>
+      <c r="D78" s="9">
+        <f>B78-C78-K78</f>
+        <v>35963</v>
+      </c>
+      <c r="E78" s="9">
+        <v>0</v>
+      </c>
+      <c r="F78" s="9">
+        <v>0</v>
+      </c>
+      <c r="G78" s="9">
+        <v>0</v>
+      </c>
+      <c r="H78" s="9">
+        <v>0</v>
+      </c>
+      <c r="I78" s="9">
+        <v>0</v>
+      </c>
+      <c r="J78" s="9">
+        <v>0</v>
+      </c>
+      <c r="K78" s="14">
+        <v>88000</v>
+      </c>
+      <c r="L78" s="10">
+        <f t="shared" si="0"/>
+        <v>411979</v>
+      </c>
+      <c r="M78" s="11">
+        <f t="shared" ref="M78" si="7">C78/L78</f>
+        <v>0.69910359508615727</v>
+      </c>
+      <c r="N78" s="11">
+        <f t="shared" ref="N78" si="8">D78/L78</f>
+        <v>8.7293284366436158E-2</v>
+      </c>
+      <c r="O78" s="12">
+        <v>0</v>
+      </c>
+      <c r="P78" s="12">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="12">
+        <v>0</v>
+      </c>
+      <c r="R78" s="12">
+        <v>0</v>
+      </c>
+      <c r="S78" s="12">
+        <f>I78/L78</f>
+        <v>0</v>
+      </c>
+      <c r="T78" s="12">
+        <f>K78/L78</f>
+        <v>0.21360312054740654</v>
+      </c>
+      <c r="U78" s="11">
         <v>0</v>
       </c>
     </row>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{ABFCB2F3-A276-A642-8446-4D9500EE333D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A084FA98-8620-BB4F-B969-6D5155643DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7440" yWindow="-34040" windowWidth="45120" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4584,11 +4584,11 @@
         <v>46266</v>
       </c>
       <c r="C32" s="55">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D32" s="35">
         <f t="shared" si="5"/>
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E32" s="47" t="s">
         <v>101</v>
@@ -4854,11 +4854,11 @@
         <v>46275</v>
       </c>
       <c r="C36" s="55">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D36" s="35">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E36" s="47" t="s">
         <v>56</v>
@@ -5057,11 +5057,11 @@
         <v>46281</v>
       </c>
       <c r="C39" s="55">
-        <v>46281</v>
+        <v>46282</v>
       </c>
       <c r="D39" s="35">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E39" s="47" t="s">
         <v>591</v>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="G65" s="27">
         <f>AVERAGE(C3:C71)</f>
-        <v>1137.0013043478257</v>
+        <v>1139.5810144927532</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="G66" s="27">
         <f>_xlfn.STDEV.S(C3:C71)</f>
-        <v>4334.0271391583974</v>
+        <v>4336.8955026619287</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G67" s="28">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.1645646347907652</v>
+        <v>4.1712528622945912</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="G68" s="29">
         <f>_xlfn.STDEV.S(D2:D71)*SQRT(252)</f>
-        <v>0.18779508191267738</v>
+        <v>0.1878922858618334</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="G69" s="29" cm="1">
         <f t="array" ref="G69">PRODUCT(1+D2:D71)-1</f>
-        <v>0.23527294380544328</v>
+        <v>0.23580674759219566</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="G70" s="29" cm="1">
         <f t="array" ref="G70">PRODUCT(1+D2:D71)^(252/COUNT(D2:D71))-1</f>
-        <v>1.1396687558113086</v>
+        <v>1.1429992733897483</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -6428,16 +6428,16 @@
         <v>46281</v>
       </c>
       <c r="B71" s="5">
-        <f>B70+5800</f>
-        <v>411909</v>
+        <f>B70-63-1183+7224</f>
+        <v>412087</v>
       </c>
       <c r="C71" s="5">
         <f t="shared" si="0"/>
-        <v>5800</v>
+        <v>5978</v>
       </c>
       <c r="D71" s="23">
         <f t="shared" si="1"/>
-        <v>1.4281879987885026E-2</v>
+        <v>1.4720185959927015E-2</v>
       </c>
     </row>
   </sheetData>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A084FA98-8620-BB4F-B969-6D5155643DD7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{734055B3-754D-F447-86F8-3E06AFD309FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7440" yWindow="-34040" windowWidth="45120" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4612,19 +4612,19 @@
         <v>101</v>
       </c>
       <c r="L32" s="47">
-        <v>-2000</v>
+        <v>-1000</v>
       </c>
       <c r="M32" s="47">
-        <v>50.685000000000002</v>
+        <v>51.32</v>
       </c>
       <c r="N32" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O32" s="47">
-        <v>49.76</v>
+        <v>48.4</v>
       </c>
       <c r="P32" s="49">
-        <v>99520</v>
+        <v>46640</v>
       </c>
       <c r="Q32" s="47">
         <v>7.88</v>
@@ -4642,7 +4642,7 @@
         <v>72</v>
       </c>
       <c r="V32" s="33">
-        <v>3600</v>
+        <v>5800</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
@@ -4891,7 +4891,7 @@
         <v>72</v>
       </c>
       <c r="O36" s="47">
-        <v>673.31</v>
+        <v>681</v>
       </c>
       <c r="P36" s="49">
         <v>188496</v>
@@ -4912,7 +4912,7 @@
         <v>72</v>
       </c>
       <c r="V36" s="33">
-        <v>389</v>
+        <v>-1901</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
@@ -5085,7 +5085,7 @@
         <v>591</v>
       </c>
       <c r="L39" s="47">
-        <v>2000</v>
+        <v>1000</v>
       </c>
       <c r="M39" s="47">
         <v>45.21</v>
@@ -5094,10 +5094,10 @@
         <v>72</v>
       </c>
       <c r="O39" s="47">
-        <v>44.64</v>
+        <v>46.64</v>
       </c>
       <c r="P39" s="49">
-        <v>88000</v>
+        <v>44000</v>
       </c>
       <c r="Q39" s="47">
         <v>5.3</v>
@@ -5115,7 +5115,7 @@
         <v>72</v>
       </c>
       <c r="V39" s="33">
-        <v>-1100</v>
+        <v>3100</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="V41" s="39">
         <f>SUM(V2:V39)</f>
-        <v>2889</v>
+        <v>6999</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
@@ -5167,7 +5167,7 @@
       <c r="F44" s="36"/>
       <c r="U44" s="39">
         <f>U41+V41</f>
-        <v>75070.47</v>
+        <v>79180.47</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
@@ -5193,7 +5193,7 @@
     <row r="50" spans="21:21" x14ac:dyDescent="0.25">
       <c r="U50" s="54">
         <f>U44/U47</f>
-        <v>0.22543684684684684</v>
+        <v>0.23777918918918919</v>
       </c>
     </row>
   </sheetData>
@@ -5206,7 +5206,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:G71"/>
+  <dimension ref="A1:G72"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -5272,11 +5272,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C71" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C72" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D71" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D72" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -6299,8 +6299,8 @@
         <v>114</v>
       </c>
       <c r="G65" s="27">
-        <f>AVERAGE(C3:C71)</f>
-        <v>1139.5810144927532</v>
+        <f>AVERAGE(C3:C72)</f>
+        <v>1182.4441428571424</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -6323,8 +6323,8 @@
         <v>115</v>
       </c>
       <c r="G66" s="27">
-        <f>_xlfn.STDEV.S(C3:C71)</f>
-        <v>4336.8955026619287</v>
+        <f>_xlfn.STDEV.S(C3:C72)</f>
+        <v>4320.2639539817364</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G67" s="28">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.1712528622945912</v>
+        <v>4.3448083374743121</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -6371,8 +6371,8 @@
         <v>117</v>
       </c>
       <c r="G68" s="29">
-        <f>_xlfn.STDEV.S(D2:D71)*SQRT(252)</f>
-        <v>0.1878922858618334</v>
+        <f>_xlfn.STDEV.S(D2:D72)*SQRT(252)</f>
+        <v>0.18700415202536144</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -6395,8 +6395,8 @@
         <v>118</v>
       </c>
       <c r="G69" s="29" cm="1">
-        <f t="array" ref="G69">PRODUCT(1+D2:D71)-1</f>
-        <v>0.23580674759219566</v>
+        <f t="array" ref="G69">PRODUCT(1+D2:D72)-1</f>
+        <v>0.24822218398070506</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -6419,8 +6419,8 @@
         <v>119</v>
       </c>
       <c r="G70" s="29" cm="1">
-        <f t="array" ref="G70">PRODUCT(1+D2:D71)^(252/COUNT(D2:D71))-1</f>
-        <v>1.1429992733897483</v>
+        <f t="array" ref="G70">PRODUCT(1+D2:D72)^(252/COUNT(D2:D72))-1</f>
+        <v>1.1966882268236239</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -6438,6 +6438,23 @@
       <c r="D71" s="23">
         <f t="shared" si="1"/>
         <v>1.4720185959927015E-2</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A72" s="26">
+        <v>46282</v>
+      </c>
+      <c r="B72" s="5">
+        <f>B71+4140</f>
+        <v>416227</v>
+      </c>
+      <c r="C72" s="5">
+        <f t="shared" si="0"/>
+        <v>4140</v>
+      </c>
+      <c r="D72" s="23">
+        <f t="shared" si="1"/>
+        <v>1.0046422236081216E-2</v>
       </c>
     </row>
   </sheetData>
@@ -10980,7 +10997,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="14">
-        <f t="shared" ref="L69:L78" si="0">SUM(C69:K69)</f>
+        <f t="shared" ref="L69:L79" si="0">SUM(C69:K69)</f>
         <v>407651</v>
       </c>
       <c r="M69" s="15">
@@ -11641,6 +11658,77 @@
       <c r="U78" s="16">
         <f>K78/L78</f>
         <v>0.21360312054740654</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A79" s="10">
+        <v>46282</v>
+      </c>
+      <c r="B79" s="11">
+        <v>416227</v>
+      </c>
+      <c r="C79" s="19">
+        <v>235136</v>
+      </c>
+      <c r="D79" s="13">
+        <f>B79-C79-K79</f>
+        <v>137091</v>
+      </c>
+      <c r="E79" s="13">
+        <v>0</v>
+      </c>
+      <c r="F79" s="13">
+        <v>0</v>
+      </c>
+      <c r="G79" s="13">
+        <v>0</v>
+      </c>
+      <c r="H79" s="13">
+        <v>0</v>
+      </c>
+      <c r="I79" s="13">
+        <v>0</v>
+      </c>
+      <c r="J79" s="13">
+        <v>0</v>
+      </c>
+      <c r="K79" s="18">
+        <v>44000</v>
+      </c>
+      <c r="L79" s="14">
+        <f t="shared" si="0"/>
+        <v>416227</v>
+      </c>
+      <c r="M79" s="15">
+        <f t="shared" ref="M79" si="9">C79/L79</f>
+        <v>0.56492250622857243</v>
+      </c>
+      <c r="N79" s="15">
+        <f t="shared" ref="N79" si="10">D79/L79</f>
+        <v>0.32936594694721871</v>
+      </c>
+      <c r="O79" s="16">
+        <v>0</v>
+      </c>
+      <c r="P79" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q79" s="16">
+        <v>0</v>
+      </c>
+      <c r="R79" s="16">
+        <v>0</v>
+      </c>
+      <c r="S79" s="16">
+        <f>I79/L79</f>
+        <v>0</v>
+      </c>
+      <c r="T79" s="16">
+        <v>0</v>
+      </c>
+      <c r="U79" s="16">
+        <f>K79/L79</f>
+        <v>0.1057115468242089</v>
       </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.25">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{734055B3-754D-F447-86F8-3E06AFD309FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5851586C-A91D-7F42-AD85-6C2EA625B49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7440" yWindow="-34040" windowWidth="45120" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6300,7 +6300,7 @@
       </c>
       <c r="G65" s="27">
         <f>AVERAGE(C3:C72)</f>
-        <v>1182.4441428571424</v>
+        <v>1174.3869999999995</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -6324,7 +6324,7 @@
       </c>
       <c r="G66" s="27">
         <f>_xlfn.STDEV.S(C3:C72)</f>
-        <v>4320.2639539817364</v>
+        <v>4315.1912184572193</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -6348,7 +6348,7 @@
       </c>
       <c r="G67" s="28">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.3448083374743121</v>
+        <v>4.3202756786172039</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -6372,7 +6372,7 @@
       </c>
       <c r="G68" s="29">
         <f>_xlfn.STDEV.S(D2:D72)*SQRT(252)</f>
-        <v>0.18700415202536144</v>
+        <v>0.18684135333077373</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -6396,7 +6396,7 @@
       </c>
       <c r="G69" s="29" cm="1">
         <f t="array" ref="G69">PRODUCT(1+D2:D72)-1</f>
-        <v>0.24822218398070506</v>
+        <v>0.24653080569009655</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="G70" s="29" cm="1">
         <f t="array" ref="G70">PRODUCT(1+D2:D72)^(252/COUNT(D2:D72))-1</f>
-        <v>1.1966882268236239</v>
+        <v>1.1861417053912677</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -6445,16 +6445,16 @@
         <v>46282</v>
       </c>
       <c r="B72" s="5">
-        <f>B71+4140</f>
-        <v>416227</v>
+        <f>B71-2520+3672+2424</f>
+        <v>415663</v>
       </c>
       <c r="C72" s="5">
         <f t="shared" si="0"/>
-        <v>4140</v>
+        <v>3576</v>
       </c>
       <c r="D72" s="23">
         <f t="shared" si="1"/>
-        <v>1.0046422236081216E-2</v>
+        <v>8.6777792068179777E-3</v>
       </c>
     </row>
   </sheetData>
@@ -11363,7 +11363,7 @@
         <v>0</v>
       </c>
       <c r="S74" s="16">
-        <f>I74/L74</f>
+        <f t="shared" ref="S74:S79" si="3">I74/L74</f>
         <v>4.6226874132058518E-2</v>
       </c>
       <c r="T74" s="16">
@@ -11435,7 +11435,7 @@
         <v>0</v>
       </c>
       <c r="S75" s="16">
-        <f>I75/L75</f>
+        <f t="shared" si="3"/>
         <v>6.3119991270716894E-2</v>
       </c>
       <c r="T75" s="16">
@@ -11486,11 +11486,11 @@
         <v>408536</v>
       </c>
       <c r="M76" s="15">
-        <f t="shared" ref="M76" si="3">C76/L76</f>
+        <f t="shared" ref="M76" si="4">C76/L76</f>
         <v>0.74552793389077099</v>
       </c>
       <c r="N76" s="15">
-        <f t="shared" ref="N76" si="4">D76/L76</f>
+        <f t="shared" ref="N76" si="5">D76/L76</f>
         <v>0.25447206610922907</v>
       </c>
       <c r="O76" s="16">
@@ -11506,7 +11506,7 @@
         <v>0</v>
       </c>
       <c r="S76" s="16">
-        <f>I76/L76</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T76" s="16">
@@ -11557,11 +11557,11 @@
         <v>406109</v>
       </c>
       <c r="M77" s="15">
-        <f t="shared" ref="M77" si="5">C77/L77</f>
+        <f t="shared" ref="M77" si="6">C77/L77</f>
         <v>0.96410569576148275</v>
       </c>
       <c r="N77" s="15">
-        <f t="shared" ref="N77" si="6">D77/L77</f>
+        <f t="shared" ref="N77" si="7">D77/L77</f>
         <v>3.5894304238517243E-2</v>
       </c>
       <c r="O77" s="16">
@@ -11577,7 +11577,7 @@
         <v>0</v>
       </c>
       <c r="S77" s="16">
-        <f>I77/L77</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T77" s="16">
@@ -11629,11 +11629,11 @@
         <v>411979</v>
       </c>
       <c r="M78" s="15">
-        <f t="shared" ref="M78" si="7">C78/L78</f>
+        <f t="shared" ref="M78" si="8">C78/L78</f>
         <v>0.69910359508615727</v>
       </c>
       <c r="N78" s="15">
-        <f t="shared" ref="N78" si="8">D78/L78</f>
+        <f t="shared" ref="N78" si="9">D78/L78</f>
         <v>8.7293284366436158E-2</v>
       </c>
       <c r="O78" s="16">
@@ -11649,7 +11649,7 @@
         <v>0</v>
       </c>
       <c r="S78" s="16">
-        <f>I78/L78</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T78" s="16">
@@ -11700,11 +11700,11 @@
         <v>416227</v>
       </c>
       <c r="M79" s="15">
-        <f t="shared" ref="M79" si="9">C79/L79</f>
+        <f t="shared" ref="M79" si="10">C79/L79</f>
         <v>0.56492250622857243</v>
       </c>
       <c r="N79" s="15">
-        <f t="shared" ref="N79" si="10">D79/L79</f>
+        <f t="shared" ref="N79" si="11">D79/L79</f>
         <v>0.32936594694721871</v>
       </c>
       <c r="O79" s="16">
@@ -11720,7 +11720,7 @@
         <v>0</v>
       </c>
       <c r="S79" s="16">
-        <f>I79/L79</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="T79" s="16">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5851586C-A91D-7F42-AD85-6C2EA625B49E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C30F9D55-F279-7D48-BE02-D4CDD77C66B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7440" yWindow="-34040" windowWidth="45120" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7060" yWindow="-34040" windowWidth="45120" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="795" uniqueCount="593">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="595">
   <si>
     <t>Trade ID</t>
   </si>
@@ -1843,6 +1843,12 @@
   </si>
   <si>
     <t>Invesco Solar ETF</t>
+  </si>
+  <si>
+    <t>HGV</t>
+  </si>
+  <si>
+    <t>Hilton Grand Vacations</t>
   </si>
 </sst>
 </file>
@@ -2471,7 +2477,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V50"/>
+  <dimension ref="A1:V51"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.1640625" style="33" bestFit="1" customWidth="1"/>
@@ -3577,7 +3583,7 @@
         <v>4149.45</v>
       </c>
     </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A17" s="33">
         <v>13</v>
       </c>
@@ -3642,7 +3648,7 @@
         <v>11150</v>
       </c>
     </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A18" s="33">
         <v>14</v>
       </c>
@@ -3707,7 +3713,7 @@
         <v>2033</v>
       </c>
     </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A19" s="33">
         <v>15</v>
       </c>
@@ -3774,7 +3780,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A20" s="33">
         <v>16</v>
       </c>
@@ -3841,7 +3847,7 @@
         <v>4060</v>
       </c>
     </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A21" s="33">
         <v>17</v>
       </c>
@@ -3908,7 +3914,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A22" s="33">
         <v>17</v>
       </c>
@@ -3975,7 +3981,7 @@
         <v>2838</v>
       </c>
     </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A23" s="33">
         <v>18</v>
       </c>
@@ -4042,7 +4048,7 @@
         <v>6742</v>
       </c>
     </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A24" s="33">
         <v>19</v>
       </c>
@@ -4108,7 +4114,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A25" s="33">
         <v>20</v>
       </c>
@@ -4165,7 +4171,7 @@
         <v>1</v>
       </c>
       <c r="S25" s="40">
-        <f t="shared" ref="S25:S35" si="4">IF(R25=1, ABS(N25-M25)/M25, 0)</f>
+        <f t="shared" ref="S25:S36" si="4">IF(R25=1, ABS(N25-M25)/M25, 0)</f>
         <v>3.9539800653504951E-3</v>
       </c>
       <c r="T25" s="33">
@@ -4175,7 +4181,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A26" s="33">
         <v>21</v>
       </c>
@@ -4186,7 +4192,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D39" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D40" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
@@ -4242,7 +4248,7 @@
         <v>715</v>
       </c>
     </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A27" s="33">
         <v>22</v>
       </c>
@@ -4308,7 +4314,7 @@
         <v>3498</v>
       </c>
     </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A28" s="33">
         <v>23</v>
       </c>
@@ -4375,7 +4381,7 @@
         <v>1809</v>
       </c>
     </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A29" s="33">
         <v>24</v>
       </c>
@@ -4442,7 +4448,7 @@
         <v>2891</v>
       </c>
     </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A30" s="33">
         <v>25</v>
       </c>
@@ -4509,7 +4515,7 @@
         <v>-642</v>
       </c>
     </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A31" s="33">
         <v>26</v>
       </c>
@@ -4576,73 +4582,71 @@
         <v>4108</v>
       </c>
     </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A32" s="33">
         <v>27</v>
       </c>
       <c r="B32" s="34">
         <v>46266</v>
       </c>
-      <c r="C32" s="55">
-        <v>46282</v>
+      <c r="C32" s="34">
+        <v>46283</v>
       </c>
       <c r="D32" s="35">
         <f t="shared" si="5"/>
-        <v>16</v>
-      </c>
-      <c r="E32" s="47" t="s">
+        <v>17</v>
+      </c>
+      <c r="E32" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="F32" s="48" t="s">
+      <c r="F32" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="G32" s="47" t="s">
+      <c r="G32" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H32" s="48" t="s">
+      <c r="H32" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I32" s="47" t="s">
+      <c r="I32" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="J32" s="47" t="s">
+      <c r="J32" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="K32" s="47" t="s">
+      <c r="K32" s="33" t="s">
         <v>101</v>
       </c>
-      <c r="L32" s="47">
-        <v>-1000</v>
-      </c>
-      <c r="M32" s="47">
-        <v>51.32</v>
-      </c>
-      <c r="N32" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O32" s="47">
-        <v>48.4</v>
-      </c>
-      <c r="P32" s="49">
-        <v>46640</v>
-      </c>
-      <c r="Q32" s="47">
-        <v>7.88</v>
-      </c>
-      <c r="R32" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S32" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T32" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="U32" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V32" s="33">
-        <v>5800</v>
+      <c r="L32" s="33">
+        <v>-8000</v>
+      </c>
+      <c r="M32" s="33">
+        <v>50.59</v>
+      </c>
+      <c r="N32" s="33">
+        <v>49.67</v>
+      </c>
+      <c r="O32" s="33">
+        <v>49.67</v>
+      </c>
+      <c r="P32" s="39">
+        <v>397331</v>
+      </c>
+      <c r="Q32" s="33">
+        <v>45.99</v>
+      </c>
+      <c r="R32" s="33">
+        <v>1</v>
+      </c>
+      <c r="S32" s="40">
+        <f t="shared" si="4"/>
+        <v>1.8185412136785959E-2</v>
+      </c>
+      <c r="T32" s="33">
+        <v>7389</v>
+      </c>
+      <c r="U32" s="41">
+        <v>7389</v>
       </c>
     </row>
     <row r="33" spans="1:22" x14ac:dyDescent="0.25">
@@ -4853,66 +4857,64 @@
       <c r="B36" s="34">
         <v>46275</v>
       </c>
-      <c r="C36" s="55">
-        <v>46282</v>
+      <c r="C36" s="34">
+        <v>46283</v>
       </c>
       <c r="D36" s="35">
         <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="E36" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="E36" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="F36" s="48" t="s">
+      <c r="F36" s="36" t="s">
         <v>585</v>
       </c>
-      <c r="G36" s="47" t="s">
+      <c r="G36" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H36" s="48" t="s">
+      <c r="H36" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I36" s="47" t="s">
+      <c r="I36" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="J36" s="47" t="s">
+      <c r="J36" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="K36" s="47" t="s">
+      <c r="K36" s="33" t="s">
         <v>56</v>
       </c>
-      <c r="L36" s="47">
+      <c r="L36" s="33">
         <v>-280</v>
       </c>
-      <c r="M36" s="47">
+      <c r="M36" s="33">
         <v>674.59</v>
       </c>
-      <c r="N36" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O36" s="47">
-        <v>681</v>
-      </c>
-      <c r="P36" s="49">
+      <c r="N36" s="33">
+        <v>688</v>
+      </c>
+      <c r="O36" s="33">
+        <v>688</v>
+      </c>
+      <c r="P36" s="39">
         <v>188496</v>
       </c>
-      <c r="Q36" s="47">
+      <c r="Q36" s="33">
         <v>4.5</v>
       </c>
-      <c r="R36" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S36" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T36" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="U36" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V36" s="33">
-        <v>-1901</v>
+      <c r="R36" s="33">
+        <v>0</v>
+      </c>
+      <c r="S36" s="40">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="T36" s="33">
+        <v>-3825</v>
+      </c>
+      <c r="U36" s="45">
+        <v>-3825</v>
       </c>
     </row>
     <row r="37" spans="1:22" x14ac:dyDescent="0.25">
@@ -5088,13 +5090,13 @@
         <v>1000</v>
       </c>
       <c r="M39" s="47">
-        <v>45.21</v>
+        <v>44.8</v>
       </c>
       <c r="N39" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O39" s="47">
-        <v>46.64</v>
+        <v>45.66</v>
       </c>
       <c r="P39" s="49">
         <v>44000</v>
@@ -5115,85 +5117,154 @@
         <v>72</v>
       </c>
       <c r="V39" s="33">
-        <v>3100</v>
+        <v>885</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F40" s="36"/>
-      <c r="H40" s="36"/>
+      <c r="A40" s="33">
+        <v>35</v>
+      </c>
+      <c r="B40" s="34">
+        <v>46283</v>
+      </c>
+      <c r="C40" s="55">
+        <v>46283</v>
+      </c>
+      <c r="D40" s="35">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E40" s="47" t="s">
+        <v>593</v>
+      </c>
+      <c r="F40" s="48" t="s">
+        <v>594</v>
+      </c>
+      <c r="G40" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H40" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I40" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J40" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K40" s="47" t="s">
+        <v>593</v>
+      </c>
+      <c r="L40" s="47">
+        <v>500</v>
+      </c>
+      <c r="M40" s="47">
+        <v>36.01</v>
+      </c>
+      <c r="N40" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O40" s="47">
+        <v>35.590000000000003</v>
+      </c>
+      <c r="P40" s="49">
+        <v>17795</v>
+      </c>
+      <c r="Q40" s="47">
+        <v>1.25</v>
+      </c>
+      <c r="R40" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S40" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T40" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U40" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V40" s="33">
+        <v>-211</v>
+      </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D41" s="52" t="s">
+      <c r="F41" s="36"/>
+      <c r="H41" s="36"/>
+    </row>
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D42" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="E41" s="46">
+      <c r="E42" s="46">
         <f>AVERAGE(D2:D31)</f>
         <v>8.5333333333333332</v>
       </c>
-      <c r="F41" s="36"/>
-      <c r="H41" s="36"/>
-      <c r="U41" s="39">
-        <f>SUM(U2:U39)</f>
-        <v>72181.47</v>
-      </c>
-      <c r="V41" s="39">
-        <f>SUM(V2:V39)</f>
-        <v>6999</v>
-      </c>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D42" s="52" t="s">
+      <c r="F42" s="36"/>
+      <c r="H42" s="36"/>
+      <c r="U42" s="39">
+        <f>SUM(U2:U40)</f>
+        <v>75745.47</v>
+      </c>
+      <c r="V42" s="39">
+        <f>SUM(V2:V40)</f>
+        <v>674</v>
+      </c>
+    </row>
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D43" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="E42" s="46">
+      <c r="E43" s="46">
         <f>AVERAGE(D2:D11,D13,D15:D31)</f>
         <v>5</v>
       </c>
-      <c r="F42" s="36"/>
-      <c r="U42" s="53" t="s">
+      <c r="F43" s="36"/>
+      <c r="U43" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="V42" s="36" t="s">
+      <c r="V43" s="36" t="s">
         <v>106</v>
-      </c>
-    </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F43" s="36"/>
-      <c r="U43" s="33" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F44" s="36"/>
-      <c r="U44" s="39">
-        <f>U41+V41</f>
-        <v>79180.47</v>
+      <c r="U44" s="33" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F45" s="36"/>
+      <c r="U45" s="39">
+        <f>U42+V42</f>
+        <v>76419.47</v>
+      </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F46" s="36"/>
-      <c r="U46" s="36" t="s">
-        <v>108</v>
-      </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F47" s="36"/>
-      <c r="U47" s="39">
+      <c r="U47" s="36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F48" s="36"/>
+      <c r="U48" s="39">
         <v>333000</v>
       </c>
     </row>
-    <row r="49" spans="21:21" x14ac:dyDescent="0.25">
-      <c r="U49" s="33" t="s">
+    <row r="50" spans="21:21" x14ac:dyDescent="0.25">
+      <c r="U50" s="33" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="50" spans="21:21" x14ac:dyDescent="0.25">
-      <c r="U50" s="54">
-        <f>U44/U47</f>
-        <v>0.23777918918918919</v>
+    <row r="51" spans="21:21" x14ac:dyDescent="0.25">
+      <c r="U51" s="54">
+        <f>U45/U48</f>
+        <v>0.22948789789789789</v>
       </c>
     </row>
   </sheetData>
@@ -5206,7 +5277,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:G72"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -5272,11 +5343,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C72" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C73" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D72" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D73" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -6299,8 +6370,8 @@
         <v>114</v>
       </c>
       <c r="G65" s="27">
-        <f>AVERAGE(C3:C72)</f>
-        <v>1174.3869999999995</v>
+        <f>AVERAGE(C3:C73)</f>
+        <v>1132.6632394366193</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -6323,8 +6394,8 @@
         <v>115</v>
       </c>
       <c r="G66" s="27">
-        <f>_xlfn.STDEV.S(C3:C72)</f>
-        <v>4315.1912184572193</v>
+        <f>_xlfn.STDEV.S(C3:C73)</f>
+        <v>4298.6584737725461</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -6348,7 +6419,7 @@
       </c>
       <c r="G67" s="28">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.3202756786172039</v>
+        <v>4.1828099659717246</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -6371,8 +6442,8 @@
         <v>117</v>
       </c>
       <c r="G68" s="29">
-        <f>_xlfn.STDEV.S(D2:D72)*SQRT(252)</f>
-        <v>0.18684135333077373</v>
+        <f>_xlfn.STDEV.S(D2:D73)*SQRT(252)</f>
+        <v>0.18604762485289389</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -6395,8 +6466,8 @@
         <v>118</v>
       </c>
       <c r="G69" s="29" cm="1">
-        <f t="array" ref="G69">PRODUCT(1+D2:D72)-1</f>
-        <v>0.24653080569009655</v>
+        <f t="array" ref="G69">PRODUCT(1+D2:D73)-1</f>
+        <v>0.24116877664114611</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -6419,8 +6490,8 @@
         <v>119</v>
       </c>
       <c r="G70" s="29" cm="1">
-        <f t="array" ref="G70">PRODUCT(1+D2:D72)^(252/COUNT(D2:D72))-1</f>
-        <v>1.1861417053912677</v>
+        <f t="array" ref="G70">PRODUCT(1+D2:D73)^(252/COUNT(D2:D73))-1</f>
+        <v>1.1301390115314884</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -6455,6 +6526,23 @@
       <c r="D72" s="23">
         <f t="shared" si="1"/>
         <v>8.6777792068179777E-3</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A73" s="26">
+        <v>46283</v>
+      </c>
+      <c r="B73" s="5">
+        <f>B72-211-700+634-1511</f>
+        <v>413875</v>
+      </c>
+      <c r="C73" s="5">
+        <f t="shared" si="0"/>
+        <v>-1788</v>
+      </c>
+      <c r="D73" s="23">
+        <f t="shared" si="1"/>
+        <v>-4.3015616015858998E-3</v>
       </c>
     </row>
   </sheetData>
@@ -10997,7 +11085,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="14">
-        <f t="shared" ref="L69:L79" si="0">SUM(C69:K69)</f>
+        <f t="shared" ref="L69:L80" si="0">SUM(C69:K69)</f>
         <v>407651</v>
       </c>
       <c r="M69" s="15">
@@ -11665,14 +11753,14 @@
         <v>46282</v>
       </c>
       <c r="B79" s="11">
-        <v>416227</v>
+        <v>415663</v>
       </c>
       <c r="C79" s="19">
         <v>235136</v>
       </c>
       <c r="D79" s="13">
         <f>B79-C79-K79</f>
-        <v>137091</v>
+        <v>136527</v>
       </c>
       <c r="E79" s="13">
         <v>0</v>
@@ -11697,15 +11785,15 @@
       </c>
       <c r="L79" s="14">
         <f t="shared" si="0"/>
-        <v>416227</v>
+        <v>415663</v>
       </c>
       <c r="M79" s="15">
         <f t="shared" ref="M79" si="10">C79/L79</f>
-        <v>0.56492250622857243</v>
+        <v>0.56568903173965446</v>
       </c>
       <c r="N79" s="15">
         <f t="shared" ref="N79" si="11">D79/L79</f>
-        <v>0.32936594694721871</v>
+        <v>0.32845598477612875</v>
       </c>
       <c r="O79" s="16">
         <v>0</v>
@@ -11728,7 +11816,78 @@
       </c>
       <c r="U79" s="16">
         <f>K79/L79</f>
-        <v>0.1057115468242089</v>
+        <v>0.10585498348421678</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A80" s="10">
+        <v>46282</v>
+      </c>
+      <c r="B80" s="11">
+        <v>413875</v>
+      </c>
+      <c r="C80" s="19">
+        <v>17795</v>
+      </c>
+      <c r="D80" s="13">
+        <f>B80-C80-K80</f>
+        <v>352080</v>
+      </c>
+      <c r="E80" s="13">
+        <v>0</v>
+      </c>
+      <c r="F80" s="13">
+        <v>0</v>
+      </c>
+      <c r="G80" s="13">
+        <v>0</v>
+      </c>
+      <c r="H80" s="13">
+        <v>0</v>
+      </c>
+      <c r="I80" s="13">
+        <v>0</v>
+      </c>
+      <c r="J80" s="13">
+        <v>0</v>
+      </c>
+      <c r="K80" s="18">
+        <v>44000</v>
+      </c>
+      <c r="L80" s="14">
+        <f t="shared" si="0"/>
+        <v>413875</v>
+      </c>
+      <c r="M80" s="15">
+        <f t="shared" ref="M80" si="12">C80/L80</f>
+        <v>4.299607369374811E-2</v>
+      </c>
+      <c r="N80" s="15">
+        <f t="shared" ref="N80" si="13">D80/L80</f>
+        <v>0.85069163394744796</v>
+      </c>
+      <c r="O80" s="16">
+        <v>0</v>
+      </c>
+      <c r="P80" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q80" s="16">
+        <v>0</v>
+      </c>
+      <c r="R80" s="16">
+        <v>0</v>
+      </c>
+      <c r="S80" s="16">
+        <f t="shared" ref="S80" si="14">I80/L80</f>
+        <v>0</v>
+      </c>
+      <c r="T80" s="16">
+        <v>0</v>
+      </c>
+      <c r="U80" s="16">
+        <f>K80/L80</f>
+        <v>0.10631229235880399</v>
       </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.25">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C30F9D55-F279-7D48-BE02-D4CDD77C66B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C034F674-A1C6-4B48-A1BB-AE2243962848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7060" yWindow="-34040" windowWidth="45120" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7440" yWindow="-34040" windowWidth="45120" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="797" uniqueCount="595">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="604">
   <si>
     <t>Trade ID</t>
   </si>
@@ -1849,6 +1849,33 @@
   </si>
   <si>
     <t>Hilton Grand Vacations</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>Deckers Outdoor Corp</t>
+  </si>
+  <si>
+    <t>HD</t>
+  </si>
+  <si>
+    <t>Home Depot</t>
+  </si>
+  <si>
+    <t>DAC</t>
+  </si>
+  <si>
+    <t>Danaos Corporation</t>
+  </si>
+  <si>
+    <t>NSC</t>
+  </si>
+  <si>
+    <t>Norfolk Southern Corporation</t>
+  </si>
+  <si>
+    <t>S&amp;P Micro Futures</t>
   </si>
 </sst>
 </file>
@@ -2477,7 +2504,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V51"/>
+  <dimension ref="A1:V56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.1640625" style="33" bestFit="1" customWidth="1"/>
@@ -4192,7 +4219,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D40" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D45" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
@@ -5059,11 +5086,11 @@
         <v>46281</v>
       </c>
       <c r="C39" s="55">
-        <v>46282</v>
+        <v>46286</v>
       </c>
       <c r="D39" s="35">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E39" s="47" t="s">
         <v>591</v>
@@ -5117,7 +5144,7 @@
         <v>72</v>
       </c>
       <c r="V39" s="33">
-        <v>885</v>
+        <v>2180</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
@@ -5128,11 +5155,11 @@
         <v>46283</v>
       </c>
       <c r="C40" s="55">
-        <v>46283</v>
+        <v>46286</v>
       </c>
       <c r="D40" s="35">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E40" s="47" t="s">
         <v>593</v>
@@ -5156,22 +5183,22 @@
         <v>593</v>
       </c>
       <c r="L40" s="47">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="M40" s="47">
-        <v>36.01</v>
+        <v>35.6</v>
       </c>
       <c r="N40" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O40" s="47">
-        <v>35.590000000000003</v>
+        <v>35.56</v>
       </c>
       <c r="P40" s="49">
-        <v>17795</v>
+        <v>35270</v>
       </c>
       <c r="Q40" s="47">
-        <v>1.25</v>
+        <v>3.11</v>
       </c>
       <c r="R40" s="47" t="s">
         <v>72</v>
@@ -5186,85 +5213,430 @@
         <v>72</v>
       </c>
       <c r="V40" s="33">
-        <v>-211</v>
+        <v>-335</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F41" s="36"/>
-      <c r="H41" s="36"/>
+      <c r="A41" s="33">
+        <v>36</v>
+      </c>
+      <c r="B41" s="34">
+        <v>46286</v>
+      </c>
+      <c r="C41" s="55">
+        <v>46286</v>
+      </c>
+      <c r="D41" s="35">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E41" s="47" t="s">
+        <v>595</v>
+      </c>
+      <c r="F41" s="48" t="s">
+        <v>596</v>
+      </c>
+      <c r="G41" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H41" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I41" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J41" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K41" s="47" t="s">
+        <v>595</v>
+      </c>
+      <c r="L41" s="47">
+        <v>500</v>
+      </c>
+      <c r="M41" s="47">
+        <v>79.78</v>
+      </c>
+      <c r="N41" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O41" s="47">
+        <v>80.23</v>
+      </c>
+      <c r="P41" s="49">
+        <v>40005</v>
+      </c>
+      <c r="Q41" s="47">
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="R41" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S41" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T41" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U41" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V41" s="33">
+        <v>114</v>
+      </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D42" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="E42" s="46">
-        <f>AVERAGE(D2:D31)</f>
-        <v>8.5333333333333332</v>
-      </c>
-      <c r="F42" s="36"/>
-      <c r="H42" s="36"/>
-      <c r="U42" s="39">
-        <f>SUM(U2:U40)</f>
-        <v>75745.47</v>
-      </c>
-      <c r="V42" s="39">
-        <f>SUM(V2:V40)</f>
-        <v>674</v>
+      <c r="A42" s="33">
+        <v>37</v>
+      </c>
+      <c r="B42" s="34">
+        <v>46286</v>
+      </c>
+      <c r="C42" s="55">
+        <v>46286</v>
+      </c>
+      <c r="D42" s="35">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E42" s="47" t="s">
+        <v>597</v>
+      </c>
+      <c r="F42" s="48" t="s">
+        <v>598</v>
+      </c>
+      <c r="G42" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J42" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K42" s="47" t="s">
+        <v>597</v>
+      </c>
+      <c r="L42" s="47">
+        <v>300</v>
+      </c>
+      <c r="M42" s="47">
+        <v>298.27</v>
+      </c>
+      <c r="N42" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O42" s="47">
+        <v>297.7</v>
+      </c>
+      <c r="P42" s="49">
+        <v>89310</v>
+      </c>
+      <c r="Q42" s="47">
+        <v>3.67</v>
+      </c>
+      <c r="R42" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S42" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T42" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U42" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V42" s="33">
+        <v>-172</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D43" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="E43" s="46">
-        <f>AVERAGE(D2:D11,D13,D15:D31)</f>
-        <v>5</v>
-      </c>
-      <c r="F43" s="36"/>
-      <c r="U43" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="V43" s="36" t="s">
-        <v>106</v>
+      <c r="A43" s="33">
+        <v>38</v>
+      </c>
+      <c r="B43" s="34">
+        <v>46286</v>
+      </c>
+      <c r="C43" s="55">
+        <v>46286</v>
+      </c>
+      <c r="D43" s="35">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E43" s="47" t="s">
+        <v>599</v>
+      </c>
+      <c r="F43" s="48" t="s">
+        <v>600</v>
+      </c>
+      <c r="G43" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H43" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I43" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J43" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K43" s="47" t="s">
+        <v>599</v>
+      </c>
+      <c r="L43" s="47">
+        <v>-100</v>
+      </c>
+      <c r="M43" s="47">
+        <v>159.58000000000001</v>
+      </c>
+      <c r="N43" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O43" s="47">
+        <v>159.61000000000001</v>
+      </c>
+      <c r="P43" s="49">
+        <v>15961</v>
+      </c>
+      <c r="Q43" s="47">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="R43" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S43" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T43" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U43" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V43" s="33">
+        <v>-2</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F44" s="36"/>
-      <c r="U44" s="33" t="s">
-        <v>107</v>
+      <c r="A44" s="33">
+        <v>39</v>
+      </c>
+      <c r="B44" s="34">
+        <v>46286</v>
+      </c>
+      <c r="C44" s="55">
+        <v>46286</v>
+      </c>
+      <c r="D44" s="35">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E44" s="47" t="s">
+        <v>601</v>
+      </c>
+      <c r="F44" s="48" t="s">
+        <v>602</v>
+      </c>
+      <c r="G44" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K44" s="47" t="s">
+        <v>601</v>
+      </c>
+      <c r="L44" s="47">
+        <v>400</v>
+      </c>
+      <c r="M44" s="47">
+        <v>310.77999999999997</v>
+      </c>
+      <c r="N44" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O44" s="47">
+        <v>309.07</v>
+      </c>
+      <c r="P44" s="49">
+        <v>123628</v>
+      </c>
+      <c r="Q44" s="47">
+        <v>5.32</v>
+      </c>
+      <c r="R44" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S44" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T44" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U44" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V44" s="33">
+        <v>-685</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F45" s="36"/>
-      <c r="U45" s="39">
-        <f>U42+V42</f>
-        <v>76419.47</v>
+      <c r="A45" s="33">
+        <v>40</v>
+      </c>
+      <c r="B45" s="34">
+        <v>46286</v>
+      </c>
+      <c r="C45" s="55">
+        <v>46286</v>
+      </c>
+      <c r="D45" s="35">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E45" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="F45" s="48" t="s">
+        <v>603</v>
+      </c>
+      <c r="G45" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H45" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I45" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="J45" s="47" t="s">
+        <v>534</v>
+      </c>
+      <c r="K45" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="L45" s="47">
+        <v>-4</v>
+      </c>
+      <c r="M45" s="47">
+        <v>7840.75</v>
+      </c>
+      <c r="N45" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O45" s="47">
+        <v>7836</v>
+      </c>
+      <c r="P45" s="49">
+        <v>156718</v>
+      </c>
+      <c r="Q45" s="47">
+        <v>8.1199999999999992</v>
+      </c>
+      <c r="R45" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S45" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T45" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U45" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V45" s="33">
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F46" s="36"/>
+      <c r="H46" s="36"/>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D47" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="E47" s="46">
+        <f>AVERAGE(D2:D38)</f>
+        <v>7.8648648648648649</v>
+      </c>
       <c r="F47" s="36"/>
-      <c r="U47" s="36" t="s">
+      <c r="H47" s="36"/>
+      <c r="U47" s="39">
+        <f>SUM(U2:U45)</f>
+        <v>75745.47</v>
+      </c>
+      <c r="V47" s="39">
+        <f>SUM(V2:V45)</f>
+        <v>1197</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D48" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="E48" s="46">
+        <f>AVERAGE(D2:D11,D13,D15:D38)</f>
+        <v>5</v>
+      </c>
+      <c r="F48" s="36"/>
+      <c r="U48" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="V48" s="36" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="49" spans="6:21" x14ac:dyDescent="0.25">
+      <c r="F49" s="36"/>
+      <c r="U49" s="33" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="50" spans="6:21" x14ac:dyDescent="0.25">
+      <c r="F50" s="36"/>
+      <c r="U50" s="39">
+        <f>U47+V47</f>
+        <v>76942.47</v>
+      </c>
+    </row>
+    <row r="51" spans="6:21" x14ac:dyDescent="0.25">
+      <c r="F51" s="36"/>
+    </row>
+    <row r="52" spans="6:21" x14ac:dyDescent="0.25">
+      <c r="F52" s="36"/>
+      <c r="U52" s="36" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F48" s="36"/>
-      <c r="U48" s="39">
+    <row r="53" spans="6:21" x14ac:dyDescent="0.25">
+      <c r="F53" s="36"/>
+      <c r="U53" s="39">
         <v>333000</v>
       </c>
     </row>
-    <row r="50" spans="21:21" x14ac:dyDescent="0.25">
-      <c r="U50" s="33" t="s">
+    <row r="55" spans="6:21" x14ac:dyDescent="0.25">
+      <c r="U55" s="33" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="51" spans="21:21" x14ac:dyDescent="0.25">
-      <c r="U51" s="54">
-        <f>U45/U48</f>
-        <v>0.22948789789789789</v>
+    <row r="56" spans="6:21" x14ac:dyDescent="0.25">
+      <c r="U56" s="54">
+        <f>U50/U53</f>
+        <v>0.23105846846846848</v>
       </c>
     </row>
   </sheetData>
@@ -5277,7 +5649,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:G73"/>
+  <dimension ref="A1:G74"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -5343,11 +5715,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C73" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C74" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D73" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D74" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -6370,8 +6742,8 @@
         <v>114</v>
       </c>
       <c r="G65" s="27">
-        <f>AVERAGE(C3:C73)</f>
-        <v>1132.6632394366193</v>
+        <f>AVERAGE(C3:C74)</f>
+        <v>1128.6540277777774</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -6394,8 +6766,8 @@
         <v>115</v>
       </c>
       <c r="G66" s="27">
-        <f>_xlfn.STDEV.S(C3:C73)</f>
-        <v>4298.6584737725461</v>
+        <f>_xlfn.STDEV.S(C3:C74)</f>
+        <v>4268.4144503935695</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -6419,7 +6791,7 @@
       </c>
       <c r="G67" s="28">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.1828099659717246</v>
+        <v>4.1975369192971153</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -6442,8 +6814,8 @@
         <v>117</v>
       </c>
       <c r="G68" s="29">
-        <f>_xlfn.STDEV.S(D2:D73)*SQRT(252)</f>
-        <v>0.18604762485289389</v>
+        <f>_xlfn.STDEV.S(D2:D74)*SQRT(252)</f>
+        <v>0.18476108185626797</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -6466,8 +6838,8 @@
         <v>118</v>
       </c>
       <c r="G69" s="29" cm="1">
-        <f t="array" ref="G69">PRODUCT(1+D2:D73)-1</f>
-        <v>0.24116877664114611</v>
+        <f t="array" ref="G69">PRODUCT(1+D2:D74)-1</f>
+        <v>0.24369984628170194</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -6490,8 +6862,8 @@
         <v>119</v>
       </c>
       <c r="G70" s="29" cm="1">
-        <f t="array" ref="G70">PRODUCT(1+D2:D73)^(252/COUNT(D2:D73))-1</f>
-        <v>1.1301390115314884</v>
+        <f t="array" ref="G70">PRODUCT(1+D2:D74)^(252/COUNT(D2:D74))-1</f>
+        <v>1.1230654082968465</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -6543,6 +6915,23 @@
       <c r="D73" s="23">
         <f t="shared" si="1"/>
         <v>-4.3015616015858998E-3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A74" s="26">
+        <v>46286</v>
+      </c>
+      <c r="B74" s="5">
+        <f>B73+844</f>
+        <v>414719</v>
+      </c>
+      <c r="C74" s="5">
+        <f t="shared" si="0"/>
+        <v>844</v>
+      </c>
+      <c r="D74" s="23">
+        <f t="shared" si="1"/>
+        <v>2.0392630625188763E-3</v>
       </c>
     </row>
   </sheetData>
@@ -11085,7 +11474,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="14">
-        <f t="shared" ref="L69:L80" si="0">SUM(C69:K69)</f>
+        <f t="shared" ref="L69:L81" si="0">SUM(C69:K69)</f>
         <v>407651</v>
       </c>
       <c r="M69" s="15">
@@ -11821,7 +12210,7 @@
     </row>
     <row r="80" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
-        <v>46282</v>
+        <v>46283</v>
       </c>
       <c r="B80" s="11">
         <v>413875</v>
@@ -11888,6 +12277,76 @@
       <c r="U80" s="16">
         <f>K80/L80</f>
         <v>0.10631229235880399</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A81" s="10">
+        <v>46286</v>
+      </c>
+      <c r="B81" s="11">
+        <v>414719</v>
+      </c>
+      <c r="C81" s="19">
+        <v>304174</v>
+      </c>
+      <c r="D81" s="13">
+        <v>0</v>
+      </c>
+      <c r="E81" s="13">
+        <v>0</v>
+      </c>
+      <c r="F81" s="13">
+        <v>0</v>
+      </c>
+      <c r="G81" s="13">
+        <v>0</v>
+      </c>
+      <c r="H81" s="13">
+        <v>0</v>
+      </c>
+      <c r="I81" s="13">
+        <v>156718</v>
+      </c>
+      <c r="J81" s="13">
+        <v>0</v>
+      </c>
+      <c r="K81" s="18">
+        <v>44000</v>
+      </c>
+      <c r="L81" s="14">
+        <f t="shared" si="0"/>
+        <v>504892</v>
+      </c>
+      <c r="M81" s="15">
+        <f t="shared" ref="M81" si="15">C81/L81</f>
+        <v>0.60245359403595222</v>
+      </c>
+      <c r="N81" s="15">
+        <f t="shared" ref="N81" si="16">D81/L81</f>
+        <v>0</v>
+      </c>
+      <c r="O81" s="16">
+        <v>0</v>
+      </c>
+      <c r="P81" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q81" s="16">
+        <v>0</v>
+      </c>
+      <c r="R81" s="16">
+        <v>0</v>
+      </c>
+      <c r="S81" s="16">
+        <f t="shared" ref="S81" si="17">I81/L81</f>
+        <v>0.31039905563962195</v>
+      </c>
+      <c r="T81" s="16">
+        <v>0</v>
+      </c>
+      <c r="U81" s="16">
+        <f>K81/L81</f>
+        <v>8.7147350324425818E-2</v>
       </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.25">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C034F674-A1C6-4B48-A1BB-AE2243962848}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBFDE89A-7753-9349-B9CA-14A1915417C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7440" yWindow="-34040" windowWidth="45120" windowHeight="25040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8800" yWindow="-37220" windowWidth="50360" windowHeight="29720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="857" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="604">
   <si>
     <t>Trade ID</t>
   </si>
@@ -5086,11 +5086,11 @@
         <v>46281</v>
       </c>
       <c r="C39" s="55">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D39" s="35">
         <f t="shared" si="5"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E39" s="47" t="s">
         <v>591</v>
@@ -5123,7 +5123,7 @@
         <v>72</v>
       </c>
       <c r="O39" s="47">
-        <v>45.66</v>
+        <v>46.47</v>
       </c>
       <c r="P39" s="49">
         <v>44000</v>
@@ -5144,7 +5144,7 @@
         <v>72</v>
       </c>
       <c r="V39" s="33">
-        <v>2180</v>
+        <v>1695</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
@@ -5155,11 +5155,11 @@
         <v>46283</v>
       </c>
       <c r="C40" s="55">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D40" s="35">
         <f t="shared" si="5"/>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E40" s="47" t="s">
         <v>593</v>
@@ -5192,7 +5192,7 @@
         <v>72</v>
       </c>
       <c r="O40" s="47">
-        <v>35.56</v>
+        <v>35.479999999999997</v>
       </c>
       <c r="P40" s="49">
         <v>35270</v>
@@ -5213,7 +5213,7 @@
         <v>72</v>
       </c>
       <c r="V40" s="33">
-        <v>-335</v>
+        <v>-35</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
@@ -5224,11 +5224,11 @@
         <v>46286</v>
       </c>
       <c r="C41" s="55">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D41" s="35">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E41" s="47" t="s">
         <v>595</v>
@@ -5261,10 +5261,10 @@
         <v>72</v>
       </c>
       <c r="O41" s="47">
-        <v>80.23</v>
+        <v>79.86</v>
       </c>
       <c r="P41" s="49">
-        <v>40005</v>
+        <v>55902</v>
       </c>
       <c r="Q41" s="47">
         <v>2.5499999999999998</v>
@@ -5282,7 +5282,7 @@
         <v>72</v>
       </c>
       <c r="V41" s="33">
-        <v>114</v>
+        <v>66</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
@@ -5293,11 +5293,11 @@
         <v>46286</v>
       </c>
       <c r="C42" s="55">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D42" s="35">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E42" s="47" t="s">
         <v>597</v>
@@ -5330,10 +5330,10 @@
         <v>72</v>
       </c>
       <c r="O42" s="47">
-        <v>297.7</v>
+        <v>305.25</v>
       </c>
       <c r="P42" s="49">
-        <v>89310</v>
+        <v>45792</v>
       </c>
       <c r="Q42" s="47">
         <v>3.67</v>
@@ -5351,7 +5351,7 @@
         <v>72</v>
       </c>
       <c r="V42" s="33">
-        <v>-172</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
@@ -5362,11 +5362,11 @@
         <v>46286</v>
       </c>
       <c r="C43" s="55">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D43" s="35">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E43" s="47" t="s">
         <v>599</v>
@@ -5399,7 +5399,7 @@
         <v>72</v>
       </c>
       <c r="O43" s="47">
-        <v>159.61000000000001</v>
+        <v>155.94</v>
       </c>
       <c r="P43" s="49">
         <v>15961</v>
@@ -5420,7 +5420,7 @@
         <v>72</v>
       </c>
       <c r="V43" s="33">
-        <v>-2</v>
+        <v>359</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
@@ -5431,11 +5431,11 @@
         <v>46286</v>
       </c>
       <c r="C44" s="55">
-        <v>46286</v>
+        <v>46287</v>
       </c>
       <c r="D44" s="35">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E44" s="47" t="s">
         <v>601</v>
@@ -5468,10 +5468,10 @@
         <v>72</v>
       </c>
       <c r="O44" s="47">
-        <v>309.07</v>
+        <v>314.01</v>
       </c>
       <c r="P44" s="49">
-        <v>123628</v>
+        <v>102050</v>
       </c>
       <c r="Q44" s="47">
         <v>5.32</v>
@@ -5489,7 +5489,7 @@
         <v>72</v>
       </c>
       <c r="V44" s="33">
-        <v>-685</v>
+        <v>1595</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
@@ -5499,66 +5499,64 @@
       <c r="B45" s="34">
         <v>46286</v>
       </c>
-      <c r="C45" s="55">
+      <c r="C45" s="34">
         <v>46286</v>
       </c>
       <c r="D45" s="35">
         <f t="shared" si="5"/>
         <v>0</v>
       </c>
-      <c r="E45" s="47" t="s">
+      <c r="E45" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="F45" s="48" t="s">
+      <c r="F45" s="36" t="s">
         <v>603</v>
       </c>
-      <c r="G45" s="47" t="s">
+      <c r="G45" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H45" s="48" t="s">
+      <c r="H45" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I45" s="47" t="s">
+      <c r="I45" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="J45" s="47" t="s">
+      <c r="J45" s="33" t="s">
         <v>534</v>
       </c>
-      <c r="K45" s="47" t="s">
+      <c r="K45" s="33" t="s">
         <v>79</v>
       </c>
-      <c r="L45" s="47">
+      <c r="L45" s="33">
         <v>-4</v>
       </c>
-      <c r="M45" s="47">
+      <c r="M45" s="33">
         <v>7840.75</v>
       </c>
-      <c r="N45" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O45" s="47">
-        <v>7836</v>
-      </c>
-      <c r="P45" s="49">
+      <c r="N45" s="33">
+        <v>7835.5</v>
+      </c>
+      <c r="O45" s="33">
+        <v>7835.5</v>
+      </c>
+      <c r="P45" s="39">
         <v>156718</v>
       </c>
-      <c r="Q45" s="47">
-        <v>8.1199999999999992</v>
-      </c>
-      <c r="R45" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S45" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T45" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="U45" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V45" s="33">
-        <v>97</v>
+      <c r="Q45" s="33">
+        <v>4.88</v>
+      </c>
+      <c r="R45" s="33">
+        <v>1</v>
+      </c>
+      <c r="S45" s="40">
+        <f t="shared" ref="S45" si="7">IF(R45=1, ABS(N45-M45)/M45, 0)</f>
+        <v>6.6957880304817775E-4</v>
+      </c>
+      <c r="T45" s="33">
+        <v>108</v>
+      </c>
+      <c r="U45" s="41">
+        <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
@@ -5577,11 +5575,11 @@
       <c r="H47" s="36"/>
       <c r="U47" s="39">
         <f>SUM(U2:U45)</f>
-        <v>75745.47</v>
+        <v>75853.47</v>
       </c>
       <c r="V47" s="39">
         <f>SUM(V2:V45)</f>
-        <v>1197</v>
+        <v>5231</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
@@ -5610,7 +5608,7 @@
       <c r="F50" s="36"/>
       <c r="U50" s="39">
         <f>U47+V47</f>
-        <v>76942.47</v>
+        <v>81084.47</v>
       </c>
     </row>
     <row r="51" spans="6:21" x14ac:dyDescent="0.25">
@@ -5636,7 +5634,7 @@
     <row r="56" spans="6:21" x14ac:dyDescent="0.25">
       <c r="U56" s="54">
         <f>U50/U53</f>
-        <v>0.23105846846846848</v>
+        <v>0.24349690690690692</v>
       </c>
     </row>
   </sheetData>
@@ -5649,7 +5647,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:G74"/>
+  <dimension ref="A1:G75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -5715,11 +5713,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C74" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C75" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D74" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D75" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -6742,8 +6740,8 @@
         <v>114</v>
       </c>
       <c r="G65" s="27">
-        <f>AVERAGE(C3:C74)</f>
-        <v>1128.6540277777774</v>
+        <f>AVERAGE(C3:C75)</f>
+        <v>1176.6587671232871</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -6766,8 +6764,8 @@
         <v>115</v>
       </c>
       <c r="G66" s="27">
-        <f>_xlfn.STDEV.S(C3:C74)</f>
-        <v>4268.4144503935695</v>
+        <f>_xlfn.STDEV.S(C3:C75)</f>
+        <v>4261.9974709006747</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -6791,7 +6789,7 @@
       </c>
       <c r="G67" s="28">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.1975369192971153</v>
+        <v>4.382658362020365</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -6814,8 +6812,8 @@
         <v>117</v>
       </c>
       <c r="G68" s="29">
-        <f>_xlfn.STDEV.S(D2:D74)*SQRT(252)</f>
-        <v>0.18476108185626797</v>
+        <f>_xlfn.STDEV.S(D2:D75)*SQRT(252)</f>
+        <v>0.18422027876165134</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -6838,8 +6836,8 @@
         <v>118</v>
       </c>
       <c r="G69" s="29" cm="1">
-        <f t="array" ref="G69">PRODUCT(1+D2:D74)-1</f>
-        <v>0.24369984628170194</v>
+        <f t="array" ref="G69">PRODUCT(1+D2:D75)-1</f>
+        <v>0.25759373922565487</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -6862,8 +6860,8 @@
         <v>119</v>
       </c>
       <c r="G70" s="29" cm="1">
-        <f t="array" ref="G70">PRODUCT(1+D2:D74)^(252/COUNT(D2:D74))-1</f>
-        <v>1.1230654082968465</v>
+        <f t="array" ref="G70">PRODUCT(1+D2:D75)^(252/COUNT(D2:D75))-1</f>
+        <v>1.1826057878918159</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -6922,16 +6920,33 @@
         <v>46286</v>
       </c>
       <c r="B74" s="5">
-        <f>B73+844</f>
-        <v>414719</v>
+        <f>B73+223-322+166-685+1050+145</f>
+        <v>414452</v>
       </c>
       <c r="C74" s="5">
         <f t="shared" si="0"/>
-        <v>844</v>
+        <v>577</v>
       </c>
       <c r="D74" s="23">
         <f t="shared" si="1"/>
-        <v>2.0392630625188763E-3</v>
+        <v>1.3941407429779523E-3</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A75" s="26">
+        <v>46287</v>
+      </c>
+      <c r="B75" s="5">
+        <f>B74+4900</f>
+        <v>419352</v>
+      </c>
+      <c r="C75" s="5">
+        <f t="shared" si="0"/>
+        <v>4900</v>
+      </c>
+      <c r="D75" s="23">
+        <f t="shared" si="1"/>
+        <v>1.1822840763224691E-2</v>
       </c>
     </row>
   </sheetData>
@@ -11474,7 +11489,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="14">
-        <f t="shared" ref="L69:L81" si="0">SUM(C69:K69)</f>
+        <f t="shared" ref="L69:L82" si="0">SUM(C69:K69)</f>
         <v>407651</v>
       </c>
       <c r="M69" s="15">
@@ -12284,7 +12299,7 @@
         <v>46286</v>
       </c>
       <c r="B81" s="11">
-        <v>414719</v>
+        <v>414452</v>
       </c>
       <c r="C81" s="19">
         <v>304174</v>
@@ -12347,6 +12362,77 @@
       <c r="U81" s="16">
         <f>K81/L81</f>
         <v>8.7147350324425818E-2</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A82" s="10">
+        <v>46287</v>
+      </c>
+      <c r="B82" s="11">
+        <v>419352</v>
+      </c>
+      <c r="C82" s="19">
+        <v>254975</v>
+      </c>
+      <c r="D82" s="13">
+        <f>B82-C82-K82</f>
+        <v>120377</v>
+      </c>
+      <c r="E82" s="13">
+        <v>0</v>
+      </c>
+      <c r="F82" s="13">
+        <v>0</v>
+      </c>
+      <c r="G82" s="13">
+        <v>0</v>
+      </c>
+      <c r="H82" s="13">
+        <v>0</v>
+      </c>
+      <c r="I82" s="13">
+        <v>0</v>
+      </c>
+      <c r="J82" s="13">
+        <v>0</v>
+      </c>
+      <c r="K82" s="18">
+        <v>44000</v>
+      </c>
+      <c r="L82" s="14">
+        <f t="shared" si="0"/>
+        <v>419352</v>
+      </c>
+      <c r="M82" s="15">
+        <f t="shared" ref="M82" si="18">C82/L82</f>
+        <v>0.60802142352963617</v>
+      </c>
+      <c r="N82" s="15">
+        <f t="shared" ref="N82" si="19">D82/L82</f>
+        <v>0.28705478929395828</v>
+      </c>
+      <c r="O82" s="16">
+        <v>0</v>
+      </c>
+      <c r="P82" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q82" s="16">
+        <v>0</v>
+      </c>
+      <c r="R82" s="16">
+        <v>0</v>
+      </c>
+      <c r="S82" s="16">
+        <f t="shared" ref="S82" si="20">I82/L82</f>
+        <v>0</v>
+      </c>
+      <c r="T82" s="16">
+        <v>0</v>
+      </c>
+      <c r="U82" s="16">
+        <f>K82/L82</f>
+        <v>0.10492378717640551</v>
       </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.25">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{CBFDE89A-7753-9349-B9CA-14A1915417C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3ECBACBA-C62A-234C-AF68-31E7F3ED601B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="8800" yWindow="-37220" windowWidth="50360" windowHeight="29720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5252,7 +5252,7 @@
         <v>595</v>
       </c>
       <c r="L41" s="47">
-        <v>500</v>
+        <v>700</v>
       </c>
       <c r="M41" s="47">
         <v>79.78</v>
@@ -5321,7 +5321,7 @@
         <v>597</v>
       </c>
       <c r="L42" s="47">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="M42" s="47">
         <v>298.27</v>
@@ -5459,7 +5459,7 @@
         <v>601</v>
       </c>
       <c r="L44" s="47">
-        <v>400</v>
+        <v>325</v>
       </c>
       <c r="M44" s="47">
         <v>310.77999999999997</v>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3ECBACBA-C62A-234C-AF68-31E7F3ED601B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{5162640A-F810-6C49-BD8A-CFDA3C786B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8800" yWindow="-37220" windowWidth="50360" windowHeight="29720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14040" yWindow="-37100" windowWidth="46400" windowHeight="21940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="852" uniqueCount="604">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="606">
   <si>
     <t>Trade ID</t>
   </si>
@@ -1876,6 +1876,12 @@
   </si>
   <si>
     <t>S&amp;P Micro Futures</t>
+  </si>
+  <si>
+    <t>MDU</t>
+  </si>
+  <si>
+    <t>MDU Resources Group</t>
   </si>
 </sst>
 </file>
@@ -2504,7 +2510,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V56"/>
+  <dimension ref="A1:V57"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.1640625" style="33" bestFit="1" customWidth="1"/>
@@ -4219,7 +4225,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D45" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D46" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
@@ -5560,81 +5566,150 @@
       </c>
     </row>
     <row r="46" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F46" s="36"/>
-      <c r="H46" s="36"/>
+      <c r="A46" s="33">
+        <v>41</v>
+      </c>
+      <c r="B46" s="34">
+        <v>46287</v>
+      </c>
+      <c r="C46" s="55">
+        <v>46287</v>
+      </c>
+      <c r="D46" s="35">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E46" s="47" t="s">
+        <v>604</v>
+      </c>
+      <c r="F46" s="48" t="s">
+        <v>605</v>
+      </c>
+      <c r="G46" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H46" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I46" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J46" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K46" s="47" t="s">
+        <v>604</v>
+      </c>
+      <c r="L46" s="47">
+        <v>2000</v>
+      </c>
+      <c r="M46" s="47">
+        <v>18.71</v>
+      </c>
+      <c r="N46" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O46" s="47">
+        <v>18.559999999999999</v>
+      </c>
+      <c r="P46" s="49">
+        <v>37120</v>
+      </c>
+      <c r="Q46" s="47">
+        <v>2.16</v>
+      </c>
+      <c r="R46" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S46" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T46" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U46" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V46" s="33">
+        <v>-313</v>
+      </c>
     </row>
     <row r="47" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D47" s="52" t="s">
+      <c r="F47" s="36"/>
+      <c r="H47" s="36"/>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D48" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="E47" s="46">
+      <c r="E48" s="46">
         <f>AVERAGE(D2:D38)</f>
         <v>7.8648648648648649</v>
       </c>
-      <c r="F47" s="36"/>
-      <c r="H47" s="36"/>
-      <c r="U47" s="39">
+      <c r="F48" s="36"/>
+      <c r="H48" s="36"/>
+      <c r="U48" s="39">
         <f>SUM(U2:U45)</f>
         <v>75853.47</v>
       </c>
-      <c r="V47" s="39">
-        <f>SUM(V2:V45)</f>
-        <v>5231</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D48" s="52" t="s">
+      <c r="V48" s="39">
+        <f>SUM(V2:V46)</f>
+        <v>4918</v>
+      </c>
+    </row>
+    <row r="49" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="D49" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="E48" s="46">
+      <c r="E49" s="46">
         <f>AVERAGE(D2:D11,D13,D15:D38)</f>
         <v>5</v>
       </c>
-      <c r="F48" s="36"/>
-      <c r="U48" s="53" t="s">
+      <c r="F49" s="36"/>
+      <c r="U49" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="V48" s="36" t="s">
+      <c r="V49" s="36" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="49" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F49" s="36"/>
-      <c r="U49" s="33" t="s">
+    <row r="50" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="F50" s="36"/>
+      <c r="U50" s="33" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="50" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F50" s="36"/>
-      <c r="U50" s="39">
-        <f>U47+V47</f>
-        <v>81084.47</v>
-      </c>
-    </row>
-    <row r="51" spans="6:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:22" x14ac:dyDescent="0.25">
       <c r="F51" s="36"/>
-    </row>
-    <row r="52" spans="6:21" x14ac:dyDescent="0.25">
+      <c r="U51" s="39">
+        <f>U48+V48</f>
+        <v>80771.47</v>
+      </c>
+    </row>
+    <row r="52" spans="4:22" x14ac:dyDescent="0.25">
       <c r="F52" s="36"/>
-      <c r="U52" s="36" t="s">
+    </row>
+    <row r="53" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="F53" s="36"/>
+      <c r="U53" s="36" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="53" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F53" s="36"/>
-      <c r="U53" s="39">
+    <row r="54" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="F54" s="36"/>
+      <c r="U54" s="39">
         <v>333000</v>
       </c>
     </row>
-    <row r="55" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="U55" s="33" t="s">
+    <row r="56" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="U56" s="33" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="56" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="U56" s="54">
-        <f>U50/U53</f>
-        <v>0.24349690690690692</v>
+    <row r="57" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="U57" s="54">
+        <f>U51/U54</f>
+        <v>0.24255696696696696</v>
       </c>
     </row>
   </sheetData>
@@ -6741,7 +6816,7 @@
       </c>
       <c r="G65" s="27">
         <f>AVERAGE(C3:C75)</f>
-        <v>1176.6587671232871</v>
+        <v>1163.4669863013694</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -6765,7 +6840,7 @@
       </c>
       <c r="G66" s="27">
         <f>_xlfn.STDEV.S(C3:C75)</f>
-        <v>4261.9974709006747</v>
+        <v>4251.7910048491103</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -6789,7 +6864,7 @@
       </c>
       <c r="G67" s="28">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.382658362020365</v>
+        <v>4.3439260785064739</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -6813,7 +6888,7 @@
       </c>
       <c r="G68" s="29">
         <f>_xlfn.STDEV.S(D2:D75)*SQRT(252)</f>
-        <v>0.18422027876165134</v>
+        <v>0.18389305300468692</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -6837,7 +6912,7 @@
       </c>
       <c r="G69" s="29" cm="1">
         <f t="array" ref="G69">PRODUCT(1+D2:D75)-1</f>
-        <v>0.25759373922565487</v>
+        <v>0.25470580076137117</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -6861,7 +6936,7 @@
       </c>
       <c r="G70" s="29" cm="1">
         <f t="array" ref="G70">PRODUCT(1+D2:D75)^(252/COUNT(D2:D75))-1</f>
-        <v>1.1826057878918159</v>
+        <v>1.1655845220707413</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -6937,16 +7012,16 @@
         <v>46287</v>
       </c>
       <c r="B75" s="5">
-        <f>B74+4900</f>
-        <v>419352</v>
+        <f>B74+361-310+2391+10-313+2008-210</f>
+        <v>418389</v>
       </c>
       <c r="C75" s="5">
         <f t="shared" si="0"/>
-        <v>4900</v>
+        <v>3937</v>
       </c>
       <c r="D75" s="23">
         <f t="shared" si="1"/>
-        <v>1.1822840763224691E-2</v>
+        <v>9.4992906295542062E-3</v>
       </c>
     </row>
   </sheetData>
@@ -12369,14 +12444,14 @@
         <v>46287</v>
       </c>
       <c r="B82" s="11">
-        <v>419352</v>
+        <v>418389</v>
       </c>
       <c r="C82" s="19">
-        <v>254975</v>
+        <v>292095</v>
       </c>
       <c r="D82" s="13">
         <f>B82-C82-K82</f>
-        <v>120377</v>
+        <v>82294</v>
       </c>
       <c r="E82" s="13">
         <v>0</v>
@@ -12401,15 +12476,15 @@
       </c>
       <c r="L82" s="14">
         <f t="shared" si="0"/>
-        <v>419352</v>
+        <v>418389</v>
       </c>
       <c r="M82" s="15">
         <f t="shared" ref="M82" si="18">C82/L82</f>
-        <v>0.60802142352963617</v>
+        <v>0.69814215956920478</v>
       </c>
       <c r="N82" s="15">
         <f t="shared" ref="N82" si="19">D82/L82</f>
-        <v>0.28705478929395828</v>
+        <v>0.19669255166842339</v>
       </c>
       <c r="O82" s="16">
         <v>0</v>
@@ -12432,7 +12507,7 @@
       </c>
       <c r="U82" s="16">
         <f>K82/L82</f>
-        <v>0.10492378717640551</v>
+        <v>0.10516528876237186</v>
       </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.25">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5162640A-F810-6C49-BD8A-CFDA3C786B19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9C93AB4-26D8-B448-8814-91EE5866F46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14040" yWindow="-37100" windowWidth="46400" windowHeight="21940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5360" yWindow="-37100" windowWidth="46400" windowHeight="21940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="864" uniqueCount="606">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="609">
   <si>
     <t>Trade ID</t>
   </si>
@@ -1882,6 +1882,15 @@
   </si>
   <si>
     <t>MDU Resources Group</t>
+  </si>
+  <si>
+    <t>CRWD</t>
+  </si>
+  <si>
+    <t>CrowdStrike Holdings</t>
+  </si>
+  <si>
+    <t>VXMV6</t>
   </si>
 </sst>
 </file>
@@ -2510,7 +2519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:V59"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.1640625" style="33" bestFit="1" customWidth="1"/>
@@ -4225,7 +4234,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D46" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D48" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
@@ -5007,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="S37" s="40">
-        <f t="shared" ref="S37:S38" si="6">IF(R37=1, ABS(N37-M37)/M37, 0)</f>
+        <f t="shared" ref="S37:S40" si="6">IF(R37=1, ABS(N37-M37)/M37, 0)</f>
         <v>1.2137203166226873E-2</v>
       </c>
       <c r="T37" s="33">
@@ -5091,66 +5100,65 @@
       <c r="B39" s="34">
         <v>46281</v>
       </c>
-      <c r="C39" s="55">
-        <v>46287</v>
+      <c r="C39" s="34">
+        <v>46288</v>
       </c>
       <c r="D39" s="35">
         <f t="shared" si="5"/>
-        <v>6</v>
-      </c>
-      <c r="E39" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="E39" s="33" t="s">
         <v>591</v>
       </c>
-      <c r="F39" s="48" t="s">
+      <c r="F39" s="36" t="s">
         <v>592</v>
       </c>
-      <c r="G39" s="47" t="s">
+      <c r="G39" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H39" s="48" t="s">
+      <c r="H39" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I39" s="47" t="s">
+      <c r="I39" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="J39" s="47" t="s">
+      <c r="J39" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="K39" s="47" t="s">
+      <c r="K39" s="33" t="s">
         <v>591</v>
       </c>
-      <c r="L39" s="47">
-        <v>1000</v>
-      </c>
-      <c r="M39" s="47">
-        <v>44.8</v>
-      </c>
-      <c r="N39" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O39" s="47">
-        <v>46.47</v>
-      </c>
-      <c r="P39" s="49">
-        <v>44000</v>
-      </c>
-      <c r="Q39" s="47">
-        <v>5.3</v>
-      </c>
-      <c r="R39" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S39" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T39" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="U39" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V39" s="33">
-        <v>1695</v>
+      <c r="L39" s="33">
+        <v>2000</v>
+      </c>
+      <c r="M39" s="33">
+        <v>45.205500000000001</v>
+      </c>
+      <c r="N39" s="33">
+        <v>46.289000000000001</v>
+      </c>
+      <c r="O39" s="33">
+        <v>46.289000000000001</v>
+      </c>
+      <c r="P39" s="39">
+        <f>ABS(M39*L39)</f>
+        <v>90411</v>
+      </c>
+      <c r="Q39" s="33">
+        <v>23.76</v>
+      </c>
+      <c r="R39" s="33">
+        <v>1</v>
+      </c>
+      <c r="S39" s="40">
+        <f t="shared" si="6"/>
+        <v>2.3968322438641332E-2</v>
+      </c>
+      <c r="T39" s="33">
+        <v>2167</v>
+      </c>
+      <c r="U39" s="41">
+        <v>2167</v>
       </c>
     </row>
     <row r="40" spans="1:22" x14ac:dyDescent="0.25">
@@ -5160,66 +5168,65 @@
       <c r="B40" s="34">
         <v>46283</v>
       </c>
-      <c r="C40" s="55">
-        <v>46287</v>
+      <c r="C40" s="34">
+        <v>46288</v>
       </c>
       <c r="D40" s="35">
         <f t="shared" si="5"/>
-        <v>4</v>
-      </c>
-      <c r="E40" s="47" t="s">
+        <v>5</v>
+      </c>
+      <c r="E40" s="33" t="s">
         <v>593</v>
       </c>
-      <c r="F40" s="48" t="s">
+      <c r="F40" s="36" t="s">
         <v>594</v>
       </c>
-      <c r="G40" s="47" t="s">
+      <c r="G40" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H40" s="48" t="s">
+      <c r="H40" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I40" s="47" t="s">
+      <c r="I40" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="J40" s="47" t="s">
+      <c r="J40" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="K40" s="47" t="s">
+      <c r="K40" s="33" t="s">
         <v>593</v>
       </c>
-      <c r="L40" s="47">
+      <c r="L40" s="33">
         <v>1000</v>
       </c>
-      <c r="M40" s="47">
-        <v>35.6</v>
-      </c>
-      <c r="N40" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O40" s="47">
-        <v>35.479999999999997</v>
-      </c>
-      <c r="P40" s="49">
-        <v>35270</v>
-      </c>
-      <c r="Q40" s="47">
-        <v>3.11</v>
-      </c>
-      <c r="R40" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S40" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T40" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="U40" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V40" s="33">
-        <v>-35</v>
+      <c r="M40" s="33">
+        <v>35.601500000000001</v>
+      </c>
+      <c r="N40" s="33">
+        <v>35.162700000000001</v>
+      </c>
+      <c r="O40" s="33">
+        <v>35.162700000000001</v>
+      </c>
+      <c r="P40" s="39">
+        <f>ABS(M40*L40)</f>
+        <v>35601.5</v>
+      </c>
+      <c r="Q40" s="33">
+        <v>7.57</v>
+      </c>
+      <c r="R40" s="33">
+        <v>0</v>
+      </c>
+      <c r="S40" s="40">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="T40" s="33">
+        <v>-438</v>
+      </c>
+      <c r="U40" s="45">
+        <v>-438</v>
       </c>
     </row>
     <row r="41" spans="1:22" x14ac:dyDescent="0.25">
@@ -5229,66 +5236,64 @@
       <c r="B41" s="34">
         <v>46286</v>
       </c>
-      <c r="C41" s="55">
-        <v>46287</v>
+      <c r="C41" s="34">
+        <v>46288</v>
       </c>
       <c r="D41" s="35">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E41" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="E41" s="33" t="s">
         <v>595</v>
       </c>
-      <c r="F41" s="48" t="s">
+      <c r="F41" s="36" t="s">
         <v>596</v>
       </c>
-      <c r="G41" s="47" t="s">
+      <c r="G41" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H41" s="48" t="s">
+      <c r="H41" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I41" s="47" t="s">
+      <c r="I41" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="J41" s="47" t="s">
+      <c r="J41" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="K41" s="47" t="s">
+      <c r="K41" s="33" t="s">
         <v>595</v>
       </c>
-      <c r="L41" s="47">
+      <c r="L41" s="33">
         <v>700</v>
       </c>
-      <c r="M41" s="47">
-        <v>79.78</v>
-      </c>
-      <c r="N41" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O41" s="47">
-        <v>79.86</v>
-      </c>
-      <c r="P41" s="49">
+      <c r="M41" s="33">
+        <v>79.950999999999993</v>
+      </c>
+      <c r="N41" s="33">
+        <v>79.498000000000005</v>
+      </c>
+      <c r="O41" s="33">
+        <v>79.498000000000005</v>
+      </c>
+      <c r="P41" s="39">
         <v>55902</v>
       </c>
-      <c r="Q41" s="47">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="R41" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S41" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T41" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="U41" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V41" s="33">
-        <v>66</v>
+      <c r="Q41" s="33">
+        <v>5.63</v>
+      </c>
+      <c r="R41" s="33">
+        <v>0</v>
+      </c>
+      <c r="S41" s="40">
+        <f t="shared" ref="S41:S44" si="7">IF(R41=1, ABS(N41-M41)/M41, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="T41" s="33">
+        <v>-317</v>
+      </c>
+      <c r="U41" s="45">
+        <v>-317</v>
       </c>
     </row>
     <row r="42" spans="1:22" x14ac:dyDescent="0.25">
@@ -5298,66 +5303,65 @@
       <c r="B42" s="34">
         <v>46286</v>
       </c>
-      <c r="C42" s="55">
-        <v>46287</v>
+      <c r="C42" s="34">
+        <v>46288</v>
       </c>
       <c r="D42" s="35">
         <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="E42" s="33" t="s">
+        <v>597</v>
+      </c>
+      <c r="F42" s="36" t="s">
+        <v>598</v>
+      </c>
+      <c r="G42" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H42" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="I42" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="J42" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="K42" s="33" t="s">
+        <v>597</v>
+      </c>
+      <c r="L42" s="33">
+        <v>300</v>
+      </c>
+      <c r="M42" s="33">
+        <v>298.27</v>
+      </c>
+      <c r="N42" s="33">
+        <v>304.00940000000003</v>
+      </c>
+      <c r="O42" s="33">
+        <v>304.00940000000003</v>
+      </c>
+      <c r="P42" s="39">
+        <f>M42*L42</f>
+        <v>89481</v>
+      </c>
+      <c r="Q42" s="33">
+        <v>4.5599999999999996</v>
+      </c>
+      <c r="R42" s="33">
         <v>1</v>
       </c>
-      <c r="E42" s="47" t="s">
-        <v>597</v>
-      </c>
-      <c r="F42" s="48" t="s">
-        <v>598</v>
-      </c>
-      <c r="G42" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="H42" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="I42" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="J42" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="K42" s="47" t="s">
-        <v>597</v>
-      </c>
-      <c r="L42" s="47">
-        <v>150</v>
-      </c>
-      <c r="M42" s="47">
-        <v>298.27</v>
-      </c>
-      <c r="N42" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O42" s="47">
-        <v>305.25</v>
-      </c>
-      <c r="P42" s="49">
-        <v>45792</v>
-      </c>
-      <c r="Q42" s="47">
-        <v>3.67</v>
-      </c>
-      <c r="R42" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S42" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T42" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="U42" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V42" s="33">
-        <v>1551</v>
+      <c r="S42" s="40">
+        <f t="shared" si="7"/>
+        <v>1.9242297247460509E-2</v>
+      </c>
+      <c r="T42" s="33">
+        <v>1721</v>
+      </c>
+      <c r="U42" s="41">
+        <v>1721</v>
       </c>
     </row>
     <row r="43" spans="1:22" x14ac:dyDescent="0.25">
@@ -5405,13 +5409,14 @@
         <v>72</v>
       </c>
       <c r="O43" s="47">
-        <v>155.94</v>
+        <v>154.41999999999999</v>
       </c>
       <c r="P43" s="49">
-        <v>15961</v>
+        <f>ABS(M43*L43)</f>
+        <v>15958.000000000002</v>
       </c>
       <c r="Q43" s="47">
-        <v>1.0900000000000001</v>
+        <v>1.02</v>
       </c>
       <c r="R43" s="47" t="s">
         <v>72</v>
@@ -5426,7 +5431,7 @@
         <v>72</v>
       </c>
       <c r="V43" s="33">
-        <v>359</v>
+        <v>517</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
@@ -5436,66 +5441,65 @@
       <c r="B44" s="34">
         <v>46286</v>
       </c>
-      <c r="C44" s="55">
-        <v>46287</v>
+      <c r="C44" s="34">
+        <v>46288</v>
       </c>
       <c r="D44" s="35">
         <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="E44" s="33" t="s">
+        <v>601</v>
+      </c>
+      <c r="F44" s="36" t="s">
+        <v>602</v>
+      </c>
+      <c r="G44" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H44" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="I44" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="J44" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="K44" s="33" t="s">
+        <v>601</v>
+      </c>
+      <c r="L44" s="33">
+        <v>400</v>
+      </c>
+      <c r="M44" s="33">
+        <v>310.77999999999997</v>
+      </c>
+      <c r="N44" s="33">
+        <v>313.61399999999998</v>
+      </c>
+      <c r="O44" s="33">
+        <v>313.61399999999998</v>
+      </c>
+      <c r="P44" s="39">
+        <f>ABS(M44*L44)</f>
+        <v>124311.99999999999</v>
+      </c>
+      <c r="Q44" s="33">
+        <v>6.5</v>
+      </c>
+      <c r="R44" s="33">
         <v>1</v>
       </c>
-      <c r="E44" s="47" t="s">
-        <v>601</v>
-      </c>
-      <c r="F44" s="48" t="s">
-        <v>602</v>
-      </c>
-      <c r="G44" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="H44" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="I44" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="J44" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="K44" s="47" t="s">
-        <v>601</v>
-      </c>
-      <c r="L44" s="47">
-        <v>325</v>
-      </c>
-      <c r="M44" s="47">
-        <v>310.77999999999997</v>
-      </c>
-      <c r="N44" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O44" s="47">
-        <v>314.01</v>
-      </c>
-      <c r="P44" s="49">
-        <v>102050</v>
-      </c>
-      <c r="Q44" s="47">
-        <v>5.32</v>
-      </c>
-      <c r="R44" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S44" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T44" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="U44" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V44" s="33">
-        <v>1595</v>
+      <c r="S44" s="40">
+        <f t="shared" si="7"/>
+        <v>9.1189909260570284E-3</v>
+      </c>
+      <c r="T44" s="33">
+        <v>1134</v>
+      </c>
+      <c r="U44" s="41">
+        <v>1134</v>
       </c>
     </row>
     <row r="45" spans="1:22" x14ac:dyDescent="0.25">
@@ -5555,7 +5559,7 @@
         <v>1</v>
       </c>
       <c r="S45" s="40">
-        <f t="shared" ref="S45" si="7">IF(R45=1, ABS(N45-M45)/M45, 0)</f>
+        <f t="shared" ref="S45:S46" si="8">IF(R45=1, ABS(N45-M45)/M45, 0)</f>
         <v>6.6957880304817775E-4</v>
       </c>
       <c r="T45" s="33">
@@ -5572,144 +5576,283 @@
       <c r="B46" s="34">
         <v>46287</v>
       </c>
-      <c r="C46" s="55">
-        <v>46287</v>
+      <c r="C46" s="34">
+        <v>46288</v>
       </c>
       <c r="D46" s="35">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E46" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E46" s="33" t="s">
         <v>604</v>
       </c>
-      <c r="F46" s="48" t="s">
+      <c r="F46" s="36" t="s">
         <v>605</v>
       </c>
-      <c r="G46" s="47" t="s">
+      <c r="G46" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H46" s="48" t="s">
+      <c r="H46" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I46" s="47" t="s">
+      <c r="I46" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="J46" s="47" t="s">
+      <c r="J46" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="K46" s="47" t="s">
+      <c r="K46" s="33" t="s">
         <v>604</v>
       </c>
-      <c r="L46" s="47">
+      <c r="L46" s="33">
         <v>2000</v>
       </c>
-      <c r="M46" s="47">
+      <c r="M46" s="33">
         <v>18.71</v>
       </c>
-      <c r="N46" s="47" t="s">
+      <c r="N46" s="33">
+        <v>18.376999999999999</v>
+      </c>
+      <c r="O46" s="33">
+        <v>18.376999999999999</v>
+      </c>
+      <c r="P46" s="39">
+        <f>ABS(M46*L46)</f>
+        <v>37420</v>
+      </c>
+      <c r="Q46" s="33">
+        <v>22.69</v>
+      </c>
+      <c r="R46" s="33">
+        <v>0</v>
+      </c>
+      <c r="S46" s="40">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T46" s="33">
+        <v>-664</v>
+      </c>
+      <c r="U46" s="45">
+        <v>-664</v>
+      </c>
+    </row>
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A47" s="33">
+        <v>42</v>
+      </c>
+      <c r="B47" s="34">
+        <v>46288</v>
+      </c>
+      <c r="C47" s="55">
+        <v>46289</v>
+      </c>
+      <c r="D47" s="35">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="E47" s="47" t="s">
+        <v>606</v>
+      </c>
+      <c r="F47" s="48" t="s">
+        <v>607</v>
+      </c>
+      <c r="G47" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H47" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I47" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J47" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K47" s="47" t="s">
+        <v>606</v>
+      </c>
+      <c r="L47" s="47">
+        <v>-160</v>
+      </c>
+      <c r="M47" s="47">
+        <v>256.4325</v>
+      </c>
+      <c r="N47" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="O46" s="47">
-        <v>18.559999999999999</v>
-      </c>
-      <c r="P46" s="49">
-        <v>37120</v>
-      </c>
-      <c r="Q46" s="47">
-        <v>2.16</v>
-      </c>
-      <c r="R46" s="47" t="s">
+      <c r="O47" s="47">
+        <v>259.3</v>
+      </c>
+      <c r="P47" s="49">
+        <f>ABS(M47*L47)</f>
+        <v>41029.199999999997</v>
+      </c>
+      <c r="Q47" s="47">
+        <v>2.08</v>
+      </c>
+      <c r="R47" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="S46" s="50" t="s">
+      <c r="S47" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="T46" s="47" t="s">
+      <c r="T47" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="U46" s="49" t="s">
+      <c r="U47" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="V46" s="33">
-        <v>-313</v>
-      </c>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F47" s="36"/>
-      <c r="H47" s="36"/>
+      <c r="V47" s="33">
+        <v>-418</v>
+      </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D48" s="52" t="s">
+      <c r="A48" s="33">
+        <v>43</v>
+      </c>
+      <c r="B48" s="34">
+        <v>46288</v>
+      </c>
+      <c r="C48" s="55">
+        <v>46289</v>
+      </c>
+      <c r="D48" s="35">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="E48" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="F48" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="G48" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H48" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I48" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="J48" s="47" t="s">
+        <v>532</v>
+      </c>
+      <c r="K48" s="47" t="s">
+        <v>608</v>
+      </c>
+      <c r="L48" s="47">
+        <v>20</v>
+      </c>
+      <c r="M48" s="47">
+        <v>17.555</v>
+      </c>
+      <c r="N48" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O48" s="47">
+        <v>17.88</v>
+      </c>
+      <c r="P48" s="49">
+        <f>ABS(M48*L48)*100</f>
+        <v>35110</v>
+      </c>
+      <c r="Q48" s="47">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="R48" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S48" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T48" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U48" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V48" s="33">
+        <v>571</v>
+      </c>
+    </row>
+    <row r="49" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="F49" s="36"/>
+      <c r="H49" s="36"/>
+    </row>
+    <row r="50" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="D50" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="E48" s="46">
+      <c r="E50" s="46">
         <f>AVERAGE(D2:D38)</f>
         <v>7.8648648648648649</v>
       </c>
-      <c r="F48" s="36"/>
-      <c r="H48" s="36"/>
-      <c r="U48" s="39">
-        <f>SUM(U2:U45)</f>
-        <v>75853.47</v>
-      </c>
-      <c r="V48" s="39">
-        <f>SUM(V2:V46)</f>
-        <v>4918</v>
-      </c>
-    </row>
-    <row r="49" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="D49" s="52" t="s">
+      <c r="F50" s="36"/>
+      <c r="H50" s="36"/>
+      <c r="U50" s="39">
+        <f>SUM(U2:U48)</f>
+        <v>79456.47</v>
+      </c>
+      <c r="V50" s="39">
+        <f>SUM(V2:V48)</f>
+        <v>670</v>
+      </c>
+    </row>
+    <row r="51" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="D51" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="E49" s="46">
+      <c r="E51" s="46">
         <f>AVERAGE(D2:D11,D13,D15:D38)</f>
         <v>5</v>
       </c>
-      <c r="F49" s="36"/>
-      <c r="U49" s="53" t="s">
+      <c r="F51" s="36"/>
+      <c r="U51" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="V49" s="36" t="s">
+      <c r="V51" s="36" t="s">
         <v>106</v>
-      </c>
-    </row>
-    <row r="50" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="F50" s="36"/>
-      <c r="U50" s="33" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="51" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="F51" s="36"/>
-      <c r="U51" s="39">
-        <f>U48+V48</f>
-        <v>80771.47</v>
       </c>
     </row>
     <row r="52" spans="4:22" x14ac:dyDescent="0.25">
       <c r="F52" s="36"/>
+      <c r="U52" s="33" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="53" spans="4:22" x14ac:dyDescent="0.25">
       <c r="F53" s="36"/>
-      <c r="U53" s="36" t="s">
-        <v>108</v>
+      <c r="U53" s="39">
+        <f>U50+V50</f>
+        <v>80126.47</v>
       </c>
     </row>
     <row r="54" spans="4:22" x14ac:dyDescent="0.25">
       <c r="F54" s="36"/>
-      <c r="U54" s="39">
+    </row>
+    <row r="55" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="F55" s="36"/>
+      <c r="U55" s="36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="F56" s="36"/>
+      <c r="U56" s="39">
         <v>333000</v>
       </c>
     </row>
-    <row r="56" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="U56" s="33" t="s">
+    <row r="58" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="U58" s="33" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="57" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="U57" s="54">
-        <f>U51/U54</f>
-        <v>0.24255696696696696</v>
+    <row r="59" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="U59" s="54">
+        <f>U53/U56</f>
+        <v>0.24062003003003005</v>
       </c>
     </row>
   </sheetData>
@@ -5722,7 +5865,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:G75"/>
+  <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -5788,11 +5931,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C75" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C76" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D75" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D76" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -6815,8 +6958,8 @@
         <v>114</v>
       </c>
       <c r="G65" s="27">
-        <f>AVERAGE(C3:C75)</f>
-        <v>1163.4669863013694</v>
+        <f>AVERAGE(C3:C76)</f>
+        <v>1113.9741891891888</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -6839,8 +6982,8 @@
         <v>115</v>
       </c>
       <c r="G66" s="27">
-        <f>_xlfn.STDEV.S(C3:C75)</f>
-        <v>4251.7910048491103</v>
+        <f>_xlfn.STDEV.S(C3:C76)</f>
+        <v>4243.9783684590075</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -6864,7 +7007,7 @@
       </c>
       <c r="G67" s="28">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.3439260785064739</v>
+        <v>4.1667959857338914</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -6887,8 +7030,8 @@
         <v>117</v>
       </c>
       <c r="G68" s="29">
-        <f>_xlfn.STDEV.S(D2:D75)*SQRT(252)</f>
-        <v>0.18389305300468692</v>
+        <f>_xlfn.STDEV.S(D2:D76)*SQRT(252)</f>
+        <v>0.18340800371925209</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -6911,8 +7054,8 @@
         <v>118</v>
       </c>
       <c r="G69" s="29" cm="1">
-        <f t="array" ref="G69">PRODUCT(1+D2:D75)-1</f>
-        <v>0.25470580076137117</v>
+        <f t="array" ref="G69">PRODUCT(1+D2:D76)-1</f>
+        <v>0.24721155546308982</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -6935,8 +7078,8 @@
         <v>119</v>
       </c>
       <c r="G70" s="29" cm="1">
-        <f t="array" ref="G70">PRODUCT(1+D2:D75)^(252/COUNT(D2:D75))-1</f>
-        <v>1.1655845220707413</v>
+        <f t="array" ref="G70">PRODUCT(1+D2:D76)^(252/COUNT(D2:D76))-1</f>
+        <v>1.1006747883744339</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -7022,6 +7165,23 @@
       <c r="D75" s="23">
         <f t="shared" si="1"/>
         <v>9.4992906295542062E-3</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A76" s="26">
+        <v>46288</v>
+      </c>
+      <c r="B76" s="5">
+        <f>B75-971+158-235-351-411-373-196-485+365</f>
+        <v>415890</v>
+      </c>
+      <c r="C76" s="5">
+        <f t="shared" si="0"/>
+        <v>-2499</v>
+      </c>
+      <c r="D76" s="23">
+        <f t="shared" si="1"/>
+        <v>-5.9729103776628928E-3</v>
       </c>
     </row>
   </sheetData>
@@ -11564,7 +11724,7 @@
         <v>0</v>
       </c>
       <c r="L69" s="14">
-        <f t="shared" ref="L69:L82" si="0">SUM(C69:K69)</f>
+        <f t="shared" ref="L69:L83" si="0">SUM(C69:K69)</f>
         <v>407651</v>
       </c>
       <c r="M69" s="15">
@@ -12479,11 +12639,11 @@
         <v>418389</v>
       </c>
       <c r="M82" s="15">
-        <f t="shared" ref="M82" si="18">C82/L82</f>
+        <f t="shared" ref="M82:M83" si="18">C82/L82</f>
         <v>0.69814215956920478</v>
       </c>
       <c r="N82" s="15">
-        <f t="shared" ref="N82" si="19">D82/L82</f>
+        <f t="shared" ref="N82:N83" si="19">D82/L82</f>
         <v>0.19669255166842339</v>
       </c>
       <c r="O82" s="16">
@@ -12499,7 +12659,7 @@
         <v>0</v>
       </c>
       <c r="S82" s="16">
-        <f t="shared" ref="S82" si="20">I82/L82</f>
+        <f t="shared" ref="S82:S83" si="20">I82/L82</f>
         <v>0</v>
       </c>
       <c r="T82" s="16">
@@ -12508,6 +12668,78 @@
       <c r="U82" s="16">
         <f>K82/L82</f>
         <v>0.10516528876237186</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A83" s="10">
+        <v>46288</v>
+      </c>
+      <c r="B83" s="11">
+        <v>415890</v>
+      </c>
+      <c r="C83" s="19">
+        <v>56987</v>
+      </c>
+      <c r="D83" s="13">
+        <f>B83-C83-H83</f>
+        <v>323203</v>
+      </c>
+      <c r="E83" s="13">
+        <v>0</v>
+      </c>
+      <c r="F83" s="13">
+        <v>0</v>
+      </c>
+      <c r="G83" s="13">
+        <v>0</v>
+      </c>
+      <c r="H83" s="13">
+        <v>35700</v>
+      </c>
+      <c r="I83" s="13">
+        <v>0</v>
+      </c>
+      <c r="J83" s="13">
+        <v>0</v>
+      </c>
+      <c r="K83" s="18">
+        <v>0</v>
+      </c>
+      <c r="L83" s="14">
+        <f t="shared" si="0"/>
+        <v>415890</v>
+      </c>
+      <c r="M83" s="15">
+        <f t="shared" si="18"/>
+        <v>0.13702421313328045</v>
+      </c>
+      <c r="N83" s="15">
+        <f t="shared" si="19"/>
+        <v>0.77713578109596293</v>
+      </c>
+      <c r="O83" s="15">
+        <v>0</v>
+      </c>
+      <c r="P83" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q83" s="15">
+        <v>0</v>
+      </c>
+      <c r="R83" s="15">
+        <f>H83/L83</f>
+        <v>8.5840005770756692E-2</v>
+      </c>
+      <c r="S83" s="15">
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="T83" s="15">
+        <v>0</v>
+      </c>
+      <c r="U83" s="15">
+        <f>K83/L83</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.25">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B9C93AB4-26D8-B448-8814-91EE5866F46E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B51EB213-2CB0-5149-A016-1C6E89C1213F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="5360" yWindow="-37100" windowWidth="46400" windowHeight="21940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="858" uniqueCount="609">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="613">
   <si>
     <t>Trade ID</t>
   </si>
@@ -1891,6 +1891,18 @@
   </si>
   <si>
     <t>VXMV6</t>
+  </si>
+  <si>
+    <t>QG</t>
+  </si>
+  <si>
+    <t>Natural Gas Futures Mini</t>
+  </si>
+  <si>
+    <t>QGX6</t>
+  </si>
+  <si>
+    <t>Energy_Exposure</t>
   </si>
 </sst>
 </file>
@@ -2519,7 +2531,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V59"/>
+  <dimension ref="A1:V60"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.1640625" style="33" bestFit="1" customWidth="1"/>
@@ -4234,7 +4246,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D48" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D49" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
@@ -5372,11 +5384,11 @@
         <v>46286</v>
       </c>
       <c r="C43" s="55">
-        <v>46287</v>
+        <v>46290</v>
       </c>
       <c r="D43" s="35">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E43" s="47" t="s">
         <v>599</v>
@@ -5400,20 +5412,20 @@
         <v>599</v>
       </c>
       <c r="L43" s="47">
-        <v>-100</v>
+        <v>-200</v>
       </c>
       <c r="M43" s="47">
-        <v>159.58000000000001</v>
+        <v>156.29</v>
       </c>
       <c r="N43" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O43" s="47">
-        <v>154.41999999999999</v>
+        <v>154.66</v>
       </c>
       <c r="P43" s="49">
         <f>ABS(M43*L43)</f>
-        <v>15958.000000000002</v>
+        <v>31258</v>
       </c>
       <c r="Q43" s="47">
         <v>1.02</v>
@@ -5431,7 +5443,7 @@
         <v>72</v>
       </c>
       <c r="V43" s="33">
-        <v>517</v>
+        <v>327</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
@@ -5645,11 +5657,11 @@
         <v>46288</v>
       </c>
       <c r="C47" s="55">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D47" s="35">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E47" s="47" t="s">
         <v>606</v>
@@ -5682,7 +5694,7 @@
         <v>72</v>
       </c>
       <c r="O47" s="47">
-        <v>259.3</v>
+        <v>258.86</v>
       </c>
       <c r="P47" s="49">
         <f>ABS(M47*L47)</f>
@@ -5704,7 +5716,7 @@
         <v>72</v>
       </c>
       <c r="V47" s="33">
-        <v>-418</v>
+        <v>-605</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
@@ -5715,11 +5727,11 @@
         <v>46288</v>
       </c>
       <c r="C48" s="55">
-        <v>46289</v>
+        <v>46290</v>
       </c>
       <c r="D48" s="35">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E48" s="47" t="s">
         <v>58</v>
@@ -5752,7 +5764,7 @@
         <v>72</v>
       </c>
       <c r="O48" s="47">
-        <v>17.88</v>
+        <v>17.7</v>
       </c>
       <c r="P48" s="49">
         <f>ABS(M48*L48)*100</f>
@@ -5774,85 +5786,154 @@
         <v>72</v>
       </c>
       <c r="V48" s="33">
-        <v>571</v>
-      </c>
-    </row>
-    <row r="49" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="F49" s="36"/>
-      <c r="H49" s="36"/>
-    </row>
-    <row r="50" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="D50" s="52" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A49" s="33">
+        <v>44</v>
+      </c>
+      <c r="B49" s="34">
+        <v>46289</v>
+      </c>
+      <c r="C49" s="55">
+        <v>46290</v>
+      </c>
+      <c r="D49" s="35">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="E49" s="47" t="s">
+        <v>609</v>
+      </c>
+      <c r="F49" s="48" t="s">
+        <v>610</v>
+      </c>
+      <c r="G49" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H49" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I49" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="J49" s="47" t="s">
+        <v>125</v>
+      </c>
+      <c r="K49" s="47" t="s">
+        <v>611</v>
+      </c>
+      <c r="L49" s="47">
+        <v>-2</v>
+      </c>
+      <c r="M49" s="47">
+        <v>3.327</v>
+      </c>
+      <c r="N49" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O49" s="47">
+        <v>3.24</v>
+      </c>
+      <c r="P49" s="49">
+        <v>16220</v>
+      </c>
+      <c r="Q49" s="47">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="R49" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S49" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T49" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U49" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V49" s="33">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F50" s="36"/>
+      <c r="H50" s="36"/>
+    </row>
+    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D51" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="E50" s="46">
+      <c r="E51" s="46">
         <f>AVERAGE(D2:D38)</f>
         <v>7.8648648648648649</v>
       </c>
-      <c r="F50" s="36"/>
-      <c r="H50" s="36"/>
-      <c r="U50" s="39">
-        <f>SUM(U2:U48)</f>
+      <c r="F51" s="36"/>
+      <c r="H51" s="36"/>
+      <c r="U51" s="39">
+        <f>SUM(U2:U49)</f>
         <v>79456.47</v>
       </c>
-      <c r="V50" s="39">
-        <f>SUM(V2:V48)</f>
-        <v>670</v>
-      </c>
-    </row>
-    <row r="51" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="D51" s="52" t="s">
+      <c r="V51" s="39">
+        <f>SUM(V2:V49)</f>
+        <v>583</v>
+      </c>
+    </row>
+    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D52" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="E51" s="46">
+      <c r="E52" s="46">
         <f>AVERAGE(D2:D11,D13,D15:D38)</f>
         <v>5</v>
       </c>
-      <c r="F51" s="36"/>
-      <c r="U51" s="53" t="s">
+      <c r="F52" s="36"/>
+      <c r="U52" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="V51" s="36" t="s">
+      <c r="V52" s="36" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="52" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="F52" s="36"/>
-      <c r="U52" s="33" t="s">
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F53" s="36"/>
+      <c r="U53" s="33" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="53" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="F53" s="36"/>
-      <c r="U53" s="39">
-        <f>U50+V50</f>
-        <v>80126.47</v>
-      </c>
-    </row>
-    <row r="54" spans="4:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F54" s="36"/>
-    </row>
-    <row r="55" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="U54" s="39">
+        <f>U51+V51</f>
+        <v>80039.47</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F55" s="36"/>
-      <c r="U55" s="36" t="s">
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F56" s="36"/>
+      <c r="U56" s="36" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="56" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="F56" s="36"/>
-      <c r="U56" s="39">
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F57" s="36"/>
+      <c r="U57" s="39">
         <v>333000</v>
       </c>
     </row>
-    <row r="58" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="U58" s="33" t="s">
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U59" s="33" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="59" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="U59" s="54">
-        <f>U53/U56</f>
-        <v>0.24062003003003005</v>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U60" s="54">
+        <f>U54/U57</f>
+        <v>0.24035876876876877</v>
       </c>
     </row>
   </sheetData>
@@ -5865,7 +5946,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:G76"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -5931,11 +6012,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C76" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C77" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D76" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D77" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -6958,8 +7039,8 @@
         <v>114</v>
       </c>
       <c r="G65" s="27">
-        <f>AVERAGE(C3:C76)</f>
-        <v>1113.9741891891888</v>
+        <f>AVERAGE(C3:C77)</f>
+        <v>1101.6145333333329</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -6982,8 +7063,8 @@
         <v>115</v>
       </c>
       <c r="G66" s="27">
-        <f>_xlfn.STDEV.S(C3:C76)</f>
-        <v>4243.9783684590075</v>
+        <f>_xlfn.STDEV.S(C3:C77)</f>
+        <v>4216.5641012521528</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -7007,7 +7088,7 @@
       </c>
       <c r="G67" s="28">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.1667959857338914</v>
+        <v>4.1473550870325235</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -7030,8 +7111,8 @@
         <v>117</v>
       </c>
       <c r="G68" s="29">
-        <f>_xlfn.STDEV.S(D2:D76)*SQRT(252)</f>
-        <v>0.18340800371925209</v>
+        <f>_xlfn.STDEV.S(D2:D77)*SQRT(252)</f>
+        <v>0.18224106616972091</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -7054,8 +7135,8 @@
         <v>118</v>
       </c>
       <c r="G69" s="29" cm="1">
-        <f t="array" ref="G69">PRODUCT(1+D2:D76)-1</f>
-        <v>0.24721155546308982</v>
+        <f t="array" ref="G69">PRODUCT(1+D2:D77)-1</f>
+        <v>0.24777234932894765</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -7078,8 +7159,8 @@
         <v>119</v>
       </c>
       <c r="G70" s="29" cm="1">
-        <f t="array" ref="G70">PRODUCT(1+D2:D76)^(252/COUNT(D2:D76))-1</f>
-        <v>1.1006747883744339</v>
+        <f t="array" ref="G70">PRODUCT(1+D2:D77)^(252/COUNT(D2:D77))-1</f>
+        <v>1.083361365418201</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -7182,6 +7263,23 @@
       <c r="D76" s="23">
         <f t="shared" si="1"/>
         <v>-5.9729103776628928E-3</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A77" s="26">
+        <v>46289</v>
+      </c>
+      <c r="B77" s="5">
+        <f>B76+451-190-215+141</f>
+        <v>416077</v>
+      </c>
+      <c r="C77" s="5">
+        <f t="shared" si="0"/>
+        <v>187</v>
+      </c>
+      <c r="D77" s="23">
+        <f t="shared" si="1"/>
+        <v>4.4963812546586836E-4</v>
       </c>
     </row>
   </sheetData>
@@ -7192,7 +7290,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBFEDD2B-54BB-1449-BCF8-F93ADB145E3A}">
-  <dimension ref="A1:U1048543"/>
+  <dimension ref="A1:W1048543"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="20" bestFit="1" customWidth="1"/>
@@ -7203,22 +7301,22 @@
     <col min="6" max="7" width="9.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.33203125" style="13" customWidth="1"/>
-    <col min="11" max="11" width="9.33203125" style="18" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.83203125" style="21" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18" style="17" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="16.33203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="18.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="20.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="16.6640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="20.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="17.1640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.1640625" style="16" customWidth="1"/>
-    <col min="21" max="21" width="14.83203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="22" max="16384" width="9.1640625" style="18"/>
+    <col min="10" max="11" width="9.33203125" style="13" customWidth="1"/>
+    <col min="12" max="12" width="9.33203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="15.83203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="18" style="17" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="16.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="20.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="16.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="20.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="17.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="17.1640625" style="16" customWidth="1"/>
+    <col min="23" max="23" width="14.83203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.1640625" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>110</v>
       </c>
@@ -7250,40 +7348,46 @@
         <v>121</v>
       </c>
       <c r="K1" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>48</v>
       </c>
-      <c r="L1" s="9" t="s">
+      <c r="M1" s="9" t="s">
         <v>526</v>
       </c>
-      <c r="M1" s="8" t="s">
+      <c r="N1" s="8" t="s">
         <v>527</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>528</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>536</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>537</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>538</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>539</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>540</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>590</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="V1" s="8" t="s">
+        <v>612</v>
+      </c>
+      <c r="W1" s="8" t="s">
         <v>529</v>
       </c>
     </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <v>46175</v>
       </c>
@@ -7317,18 +7421,18 @@
       <c r="K2" s="13">
         <v>0</v>
       </c>
-      <c r="L2" s="14">
+      <c r="L2" s="13">
+        <v>0</v>
+      </c>
+      <c r="M2" s="14">
         <v>300000</v>
       </c>
-      <c r="M2" s="15">
+      <c r="N2" s="15">
         <v>0.35237333333333332</v>
       </c>
-      <c r="N2" s="15">
+      <c r="O2" s="15">
         <v>0.64762666666666668</v>
       </c>
-      <c r="O2" s="16">
-        <v>0</v>
-      </c>
       <c r="P2" s="16">
         <v>0</v>
       </c>
@@ -7344,11 +7448,17 @@
       <c r="T2" s="16">
         <v>0</v>
       </c>
-      <c r="U2" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U2" s="16">
+        <v>0</v>
+      </c>
+      <c r="V2" s="16">
+        <v>0</v>
+      </c>
+      <c r="W2" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <v>46176</v>
       </c>
@@ -7382,18 +7492,18 @@
       <c r="K3" s="13">
         <v>0</v>
       </c>
-      <c r="L3" s="14">
+      <c r="L3" s="13">
+        <v>0</v>
+      </c>
+      <c r="M3" s="14">
         <v>300000</v>
       </c>
-      <c r="M3" s="15">
+      <c r="N3" s="15">
         <v>0.35237333333333332</v>
       </c>
-      <c r="N3" s="15">
+      <c r="O3" s="15">
         <v>0.64762666666666668</v>
       </c>
-      <c r="O3" s="16">
-        <v>0</v>
-      </c>
       <c r="P3" s="16">
         <v>0</v>
       </c>
@@ -7409,11 +7519,17 @@
       <c r="T3" s="16">
         <v>0</v>
       </c>
-      <c r="U3" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U3" s="16">
+        <v>0</v>
+      </c>
+      <c r="V3" s="16">
+        <v>0</v>
+      </c>
+      <c r="W3" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <v>46177</v>
       </c>
@@ -7447,18 +7563,18 @@
       <c r="K4" s="13">
         <v>0</v>
       </c>
-      <c r="L4" s="14">
+      <c r="L4" s="13">
+        <v>0</v>
+      </c>
+      <c r="M4" s="14">
         <v>300000</v>
       </c>
-      <c r="M4" s="15">
+      <c r="N4" s="15">
         <v>0.81459999999999999</v>
       </c>
-      <c r="N4" s="15">
+      <c r="O4" s="15">
         <v>0.18540000000000001</v>
       </c>
-      <c r="O4" s="16">
-        <v>0</v>
-      </c>
       <c r="P4" s="16">
         <v>0</v>
       </c>
@@ -7474,11 +7590,17 @@
       <c r="T4" s="16">
         <v>0</v>
       </c>
-      <c r="U4" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U4" s="16">
+        <v>0</v>
+      </c>
+      <c r="V4" s="16">
+        <v>0</v>
+      </c>
+      <c r="W4" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>46178</v>
       </c>
@@ -7512,21 +7634,21 @@
       <c r="K5" s="13">
         <v>0</v>
       </c>
-      <c r="L5" s="14">
+      <c r="L5" s="13">
+        <v>0</v>
+      </c>
+      <c r="M5" s="14">
         <v>907730</v>
       </c>
-      <c r="M5" s="15">
+      <c r="N5" s="15">
         <v>0.2692210238727375</v>
       </c>
-      <c r="N5" s="15">
-        <v>0</v>
-      </c>
-      <c r="O5" s="16">
+      <c r="O5" s="15">
+        <v>0</v>
+      </c>
+      <c r="P5" s="16">
         <v>0.7307789761272625</v>
       </c>
-      <c r="P5" s="16">
-        <v>0</v>
-      </c>
       <c r="Q5" s="16">
         <v>0</v>
       </c>
@@ -7539,11 +7661,17 @@
       <c r="T5" s="16">
         <v>0</v>
       </c>
-      <c r="U5" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U5" s="16">
+        <v>0</v>
+      </c>
+      <c r="V5" s="16">
+        <v>0</v>
+      </c>
+      <c r="W5" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>46181</v>
       </c>
@@ -7577,24 +7705,24 @@
       <c r="K6" s="13">
         <v>0</v>
       </c>
-      <c r="L6" s="14">
+      <c r="L6" s="13">
+        <v>0</v>
+      </c>
+      <c r="M6" s="14">
         <v>3696918</v>
       </c>
-      <c r="M6" s="15">
+      <c r="N6" s="15">
         <v>3.7509081889292646E-2</v>
       </c>
-      <c r="N6" s="15">
-        <v>0</v>
-      </c>
-      <c r="O6" s="16">
+      <c r="O6" s="15">
+        <v>0</v>
+      </c>
+      <c r="P6" s="16">
         <v>0.17943324682884501</v>
       </c>
-      <c r="P6" s="16">
+      <c r="Q6" s="16">
         <v>0.78305767128186232</v>
       </c>
-      <c r="Q6" s="16">
-        <v>0</v>
-      </c>
       <c r="R6" s="16">
         <v>0</v>
       </c>
@@ -7604,11 +7732,17 @@
       <c r="T6" s="16">
         <v>0</v>
       </c>
-      <c r="U6" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U6" s="16">
+        <v>0</v>
+      </c>
+      <c r="V6" s="16">
+        <v>0</v>
+      </c>
+      <c r="W6" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>46182</v>
       </c>
@@ -7642,21 +7776,21 @@
       <c r="K7" s="13">
         <v>0</v>
       </c>
-      <c r="L7" s="14">
+      <c r="L7" s="13">
+        <v>0</v>
+      </c>
+      <c r="M7" s="14">
         <v>802018</v>
       </c>
-      <c r="M7" s="15">
+      <c r="N7" s="15">
         <v>0.17289886261904347</v>
       </c>
-      <c r="N7" s="15">
-        <v>0</v>
-      </c>
-      <c r="O7" s="16">
+      <c r="O7" s="15">
+        <v>0</v>
+      </c>
+      <c r="P7" s="16">
         <v>0.82710113738095659</v>
       </c>
-      <c r="P7" s="16">
-        <v>0</v>
-      </c>
       <c r="Q7" s="16">
         <v>0</v>
       </c>
@@ -7669,11 +7803,17 @@
       <c r="T7" s="16">
         <v>0</v>
       </c>
-      <c r="U7" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U7" s="16">
+        <v>0</v>
+      </c>
+      <c r="V7" s="16">
+        <v>0</v>
+      </c>
+      <c r="W7" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>46183</v>
       </c>
@@ -7707,21 +7847,21 @@
       <c r="K8" s="13">
         <v>0</v>
       </c>
-      <c r="L8" s="14">
+      <c r="L8" s="13">
+        <v>0</v>
+      </c>
+      <c r="M8" s="14">
         <v>600137</v>
       </c>
-      <c r="M8" s="15">
+      <c r="N8" s="15">
         <v>0.23106057450215534</v>
       </c>
-      <c r="N8" s="15">
-        <v>0</v>
-      </c>
-      <c r="O8" s="16">
+      <c r="O8" s="15">
+        <v>0</v>
+      </c>
+      <c r="P8" s="16">
         <v>0.76893942549784466</v>
       </c>
-      <c r="P8" s="16">
-        <v>0</v>
-      </c>
       <c r="Q8" s="16">
         <v>0</v>
       </c>
@@ -7734,11 +7874,17 @@
       <c r="T8" s="16">
         <v>0</v>
       </c>
-      <c r="U8" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U8" s="16">
+        <v>0</v>
+      </c>
+      <c r="V8" s="16">
+        <v>0</v>
+      </c>
+      <c r="W8" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>46184</v>
       </c>
@@ -7772,21 +7918,21 @@
       <c r="K9" s="13">
         <v>0</v>
       </c>
-      <c r="L9" s="14">
+      <c r="L9" s="13">
+        <v>0</v>
+      </c>
+      <c r="M9" s="14">
         <v>600137</v>
       </c>
-      <c r="M9" s="15">
+      <c r="N9" s="15">
         <v>0.23106057450215534</v>
       </c>
-      <c r="N9" s="15">
-        <v>0</v>
-      </c>
-      <c r="O9" s="16">
+      <c r="O9" s="15">
+        <v>0</v>
+      </c>
+      <c r="P9" s="16">
         <v>0.76893942549784466</v>
       </c>
-      <c r="P9" s="16">
-        <v>0</v>
-      </c>
       <c r="Q9" s="16">
         <v>0</v>
       </c>
@@ -7799,11 +7945,17 @@
       <c r="T9" s="16">
         <v>0</v>
       </c>
-      <c r="U9" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U9" s="16">
+        <v>0</v>
+      </c>
+      <c r="V9" s="16">
+        <v>0</v>
+      </c>
+      <c r="W9" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>46185</v>
       </c>
@@ -7837,21 +7989,21 @@
       <c r="K10" s="13">
         <v>0</v>
       </c>
-      <c r="L10" s="14">
+      <c r="L10" s="13">
+        <v>0</v>
+      </c>
+      <c r="M10" s="14">
         <v>461469</v>
       </c>
-      <c r="M10" s="15">
-        <v>0</v>
-      </c>
       <c r="N10" s="15">
         <v>0</v>
       </c>
-      <c r="O10" s="16">
+      <c r="O10" s="15">
+        <v>0</v>
+      </c>
+      <c r="P10" s="16">
         <v>1</v>
       </c>
-      <c r="P10" s="16">
-        <v>0</v>
-      </c>
       <c r="Q10" s="16">
         <v>0</v>
       </c>
@@ -7864,11 +8016,17 @@
       <c r="T10" s="16">
         <v>0</v>
       </c>
-      <c r="U10" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U10" s="16">
+        <v>0</v>
+      </c>
+      <c r="V10" s="16">
+        <v>0</v>
+      </c>
+      <c r="W10" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>46188</v>
       </c>
@@ -7902,21 +8060,21 @@
       <c r="K11" s="13">
         <v>0</v>
       </c>
-      <c r="L11" s="14">
+      <c r="L11" s="13">
+        <v>0</v>
+      </c>
+      <c r="M11" s="14">
         <v>461469</v>
       </c>
-      <c r="M11" s="15">
-        <v>0</v>
-      </c>
       <c r="N11" s="15">
         <v>0</v>
       </c>
-      <c r="O11" s="16">
+      <c r="O11" s="15">
+        <v>0</v>
+      </c>
+      <c r="P11" s="16">
         <v>1</v>
       </c>
-      <c r="P11" s="16">
-        <v>0</v>
-      </c>
       <c r="Q11" s="16">
         <v>0</v>
       </c>
@@ -7929,11 +8087,17 @@
       <c r="T11" s="16">
         <v>0</v>
       </c>
-      <c r="U11" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U11" s="16">
+        <v>0</v>
+      </c>
+      <c r="V11" s="16">
+        <v>0</v>
+      </c>
+      <c r="W11" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>46189</v>
       </c>
@@ -7967,21 +8131,21 @@
       <c r="K12" s="13">
         <v>0</v>
       </c>
-      <c r="L12" s="14">
+      <c r="L12" s="13">
+        <v>0</v>
+      </c>
+      <c r="M12" s="14">
         <v>461469</v>
       </c>
-      <c r="M12" s="15">
-        <v>0</v>
-      </c>
       <c r="N12" s="15">
         <v>0</v>
       </c>
-      <c r="O12" s="16">
+      <c r="O12" s="15">
+        <v>0</v>
+      </c>
+      <c r="P12" s="16">
         <v>1</v>
       </c>
-      <c r="P12" s="16">
-        <v>0</v>
-      </c>
       <c r="Q12" s="16">
         <v>0</v>
       </c>
@@ -7994,11 +8158,17 @@
       <c r="T12" s="16">
         <v>0</v>
       </c>
-      <c r="U12" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U12" s="16">
+        <v>0</v>
+      </c>
+      <c r="V12" s="16">
+        <v>0</v>
+      </c>
+      <c r="W12" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>46190</v>
       </c>
@@ -8032,38 +8202,44 @@
       <c r="K13" s="13">
         <v>0</v>
       </c>
-      <c r="L13" s="14">
+      <c r="L13" s="13">
+        <v>0</v>
+      </c>
+      <c r="M13" s="14">
         <v>592709</v>
       </c>
-      <c r="M13" s="15">
-        <v>0</v>
-      </c>
       <c r="N13" s="15">
         <v>0</v>
       </c>
-      <c r="O13" s="16">
+      <c r="O13" s="15">
+        <v>0</v>
+      </c>
+      <c r="P13" s="16">
         <v>0.77857599597779015</v>
       </c>
-      <c r="P13" s="16">
-        <v>0</v>
-      </c>
       <c r="Q13" s="16">
+        <v>0</v>
+      </c>
+      <c r="R13" s="16">
         <v>0.22142400402220988</v>
       </c>
-      <c r="R13" s="16">
-        <v>0</v>
-      </c>
       <c r="S13" s="16">
         <v>0</v>
       </c>
       <c r="T13" s="16">
         <v>0</v>
       </c>
-      <c r="U13" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U13" s="16">
+        <v>0</v>
+      </c>
+      <c r="V13" s="16">
+        <v>0</v>
+      </c>
+      <c r="W13" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>46191</v>
       </c>
@@ -8097,38 +8273,44 @@
       <c r="K14" s="13">
         <v>0</v>
       </c>
-      <c r="L14" s="14">
+      <c r="L14" s="13">
+        <v>0</v>
+      </c>
+      <c r="M14" s="14">
         <v>592709</v>
       </c>
-      <c r="M14" s="15">
-        <v>0</v>
-      </c>
       <c r="N14" s="15">
         <v>0</v>
       </c>
-      <c r="O14" s="16">
+      <c r="O14" s="15">
+        <v>0</v>
+      </c>
+      <c r="P14" s="16">
         <v>0.77857599597779015</v>
       </c>
-      <c r="P14" s="16">
-        <v>0</v>
-      </c>
       <c r="Q14" s="16">
+        <v>0</v>
+      </c>
+      <c r="R14" s="16">
         <v>0.22142400402220988</v>
       </c>
-      <c r="R14" s="16">
-        <v>0</v>
-      </c>
       <c r="S14" s="16">
         <v>0</v>
       </c>
       <c r="T14" s="16">
         <v>0</v>
       </c>
-      <c r="U14" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U14" s="16">
+        <v>0</v>
+      </c>
+      <c r="V14" s="16">
+        <v>0</v>
+      </c>
+      <c r="W14" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>46192</v>
       </c>
@@ -8162,38 +8344,44 @@
       <c r="K15" s="13">
         <v>0</v>
       </c>
-      <c r="L15" s="14">
+      <c r="L15" s="13">
+        <v>0</v>
+      </c>
+      <c r="M15" s="14">
         <v>592709</v>
       </c>
-      <c r="M15" s="15">
-        <v>0</v>
-      </c>
       <c r="N15" s="15">
         <v>0</v>
       </c>
-      <c r="O15" s="16">
+      <c r="O15" s="15">
+        <v>0</v>
+      </c>
+      <c r="P15" s="16">
         <v>0.77857599597779015</v>
       </c>
-      <c r="P15" s="16">
-        <v>0</v>
-      </c>
       <c r="Q15" s="16">
+        <v>0</v>
+      </c>
+      <c r="R15" s="16">
         <v>0.22142400402220988</v>
       </c>
-      <c r="R15" s="16">
-        <v>0</v>
-      </c>
       <c r="S15" s="16">
         <v>0</v>
       </c>
       <c r="T15" s="16">
         <v>0</v>
       </c>
-      <c r="U15" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U15" s="16">
+        <v>0</v>
+      </c>
+      <c r="V15" s="16">
+        <v>0</v>
+      </c>
+      <c r="W15" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>46195</v>
       </c>
@@ -8227,24 +8415,24 @@
       <c r="K16" s="13">
         <v>0</v>
       </c>
-      <c r="L16" s="14">
+      <c r="L16" s="13">
+        <v>0</v>
+      </c>
+      <c r="M16" s="14">
         <v>3586250</v>
       </c>
-      <c r="M16" s="15">
-        <v>0</v>
-      </c>
       <c r="N16" s="15">
         <v>0</v>
       </c>
-      <c r="O16" s="16">
+      <c r="O16" s="15">
+        <v>0</v>
+      </c>
+      <c r="P16" s="16">
         <v>0.12867730916695713</v>
       </c>
-      <c r="P16" s="16">
+      <c r="Q16" s="16">
         <v>0.87132269083304292</v>
       </c>
-      <c r="Q16" s="16">
-        <v>0</v>
-      </c>
       <c r="R16" s="16">
         <v>0</v>
       </c>
@@ -8254,11 +8442,17 @@
       <c r="T16" s="16">
         <v>0</v>
       </c>
-      <c r="U16" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U16" s="16">
+        <v>0</v>
+      </c>
+      <c r="V16" s="16">
+        <v>0</v>
+      </c>
+      <c r="W16" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>46196</v>
       </c>
@@ -8292,24 +8486,24 @@
       <c r="K17" s="13">
         <v>0</v>
       </c>
-      <c r="L17" s="14">
+      <c r="L17" s="13">
+        <v>0</v>
+      </c>
+      <c r="M17" s="14">
         <v>3586250</v>
       </c>
-      <c r="M17" s="15">
-        <v>0</v>
-      </c>
       <c r="N17" s="15">
         <v>0</v>
       </c>
-      <c r="O17" s="16">
+      <c r="O17" s="15">
+        <v>0</v>
+      </c>
+      <c r="P17" s="16">
         <v>0.12867730916695713</v>
       </c>
-      <c r="P17" s="16">
+      <c r="Q17" s="16">
         <v>0.87132269083304292</v>
       </c>
-      <c r="Q17" s="16">
-        <v>0</v>
-      </c>
       <c r="R17" s="16">
         <v>0</v>
       </c>
@@ -8319,11 +8513,17 @@
       <c r="T17" s="16">
         <v>0</v>
       </c>
-      <c r="U17" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U17" s="16">
+        <v>0</v>
+      </c>
+      <c r="V17" s="16">
+        <v>0</v>
+      </c>
+      <c r="W17" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>46197</v>
       </c>
@@ -8355,26 +8555,26 @@
         <v>0</v>
       </c>
       <c r="K18" s="13">
+        <v>0</v>
+      </c>
+      <c r="L18" s="13">
         <v>193096</v>
       </c>
-      <c r="L18" s="14">
+      <c r="M18" s="14">
         <v>3779346</v>
       </c>
-      <c r="M18" s="15">
-        <v>0</v>
-      </c>
       <c r="N18" s="15">
         <v>0</v>
       </c>
-      <c r="O18" s="16">
+      <c r="O18" s="15">
+        <v>0</v>
+      </c>
+      <c r="P18" s="16">
         <v>0.12210287176670249</v>
       </c>
-      <c r="P18" s="16">
+      <c r="Q18" s="16">
         <v>0.8268046905469888</v>
       </c>
-      <c r="Q18" s="16">
-        <v>0</v>
-      </c>
       <c r="R18" s="16">
         <v>0</v>
       </c>
@@ -8384,11 +8584,17 @@
       <c r="T18" s="16">
         <v>0</v>
       </c>
-      <c r="U18" s="15">
+      <c r="U18" s="16">
+        <v>0</v>
+      </c>
+      <c r="V18" s="16">
+        <v>0</v>
+      </c>
+      <c r="W18" s="15">
         <v>5.1092437686308688E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>46198</v>
       </c>
@@ -8420,26 +8626,26 @@
         <v>0</v>
       </c>
       <c r="K19" s="13">
+        <v>0</v>
+      </c>
+      <c r="L19" s="13">
         <v>193096</v>
       </c>
-      <c r="L19" s="14">
+      <c r="M19" s="14">
         <v>3981471</v>
       </c>
-      <c r="M19" s="15">
-        <v>0</v>
-      </c>
       <c r="N19" s="15">
         <v>0</v>
       </c>
-      <c r="O19" s="16">
+      <c r="O19" s="15">
+        <v>0</v>
+      </c>
+      <c r="P19" s="16">
         <v>0.16667055970017111</v>
       </c>
-      <c r="P19" s="16">
+      <c r="Q19" s="16">
         <v>0.78483078239173409</v>
       </c>
-      <c r="Q19" s="16">
-        <v>0</v>
-      </c>
       <c r="R19" s="16">
         <v>0</v>
       </c>
@@ -8449,11 +8655,17 @@
       <c r="T19" s="16">
         <v>0</v>
       </c>
-      <c r="U19" s="15">
+      <c r="U19" s="16">
+        <v>0</v>
+      </c>
+      <c r="V19" s="16">
+        <v>0</v>
+      </c>
+      <c r="W19" s="15">
         <v>4.8498657908094774E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>46199</v>
       </c>
@@ -8485,26 +8697,26 @@
         <v>0</v>
       </c>
       <c r="K20" s="13">
+        <v>0</v>
+      </c>
+      <c r="L20" s="13">
         <v>193096</v>
       </c>
-      <c r="L20" s="14">
+      <c r="M20" s="14">
         <v>3981471</v>
       </c>
-      <c r="M20" s="15">
-        <v>0</v>
-      </c>
       <c r="N20" s="15">
         <v>0</v>
       </c>
-      <c r="O20" s="16">
+      <c r="O20" s="15">
+        <v>0</v>
+      </c>
+      <c r="P20" s="16">
         <v>0.16667055970017111</v>
       </c>
-      <c r="P20" s="16">
+      <c r="Q20" s="16">
         <v>0.78483078239173409</v>
       </c>
-      <c r="Q20" s="16">
-        <v>0</v>
-      </c>
       <c r="R20" s="16">
         <v>0</v>
       </c>
@@ -8514,11 +8726,17 @@
       <c r="T20" s="16">
         <v>0</v>
       </c>
-      <c r="U20" s="15">
+      <c r="U20" s="16">
+        <v>0</v>
+      </c>
+      <c r="V20" s="16">
+        <v>0</v>
+      </c>
+      <c r="W20" s="15">
         <v>4.8498657908094774E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>46202</v>
       </c>
@@ -8550,26 +8768,26 @@
         <v>0</v>
       </c>
       <c r="K21" s="13">
+        <v>0</v>
+      </c>
+      <c r="L21" s="13">
         <v>416939</v>
       </c>
-      <c r="L21" s="14">
+      <c r="M21" s="14">
         <v>4260349</v>
       </c>
-      <c r="M21" s="15">
+      <c r="N21" s="15">
         <v>1.2917955782495754E-2</v>
       </c>
-      <c r="N21" s="15">
-        <v>0</v>
-      </c>
-      <c r="O21" s="16">
+      <c r="O21" s="15">
+        <v>0</v>
+      </c>
+      <c r="P21" s="16">
         <v>0.1557604787776776</v>
       </c>
-      <c r="P21" s="16">
+      <c r="Q21" s="16">
         <v>0.73345657832257405</v>
       </c>
-      <c r="Q21" s="16">
-        <v>0</v>
-      </c>
       <c r="R21" s="16">
         <v>0</v>
       </c>
@@ -8579,11 +8797,17 @@
       <c r="T21" s="16">
         <v>0</v>
       </c>
-      <c r="U21" s="15">
+      <c r="U21" s="16">
+        <v>0</v>
+      </c>
+      <c r="V21" s="16">
+        <v>0</v>
+      </c>
+      <c r="W21" s="15">
         <v>9.7864987117252597E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>46203</v>
       </c>
@@ -8615,40 +8839,46 @@
         <v>0</v>
       </c>
       <c r="K22" s="13">
+        <v>0</v>
+      </c>
+      <c r="L22" s="13">
         <v>223843</v>
       </c>
-      <c r="L22" s="14">
+      <c r="M22" s="14">
         <v>3524723</v>
       </c>
-      <c r="M22" s="15">
+      <c r="N22" s="15">
         <v>1.5613992929373457E-2</v>
       </c>
-      <c r="N22" s="15">
-        <v>0</v>
-      </c>
-      <c r="O22" s="16">
+      <c r="O22" s="15">
         <v>0</v>
       </c>
       <c r="P22" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="16">
         <v>0.88653236013156211</v>
       </c>
-      <c r="Q22" s="16">
-        <v>0</v>
-      </c>
       <c r="R22" s="16">
+        <v>0</v>
+      </c>
+      <c r="S22" s="16">
         <v>3.4347096211532084E-2</v>
       </c>
-      <c r="S22" s="16">
-        <v>0</v>
-      </c>
       <c r="T22" s="16">
         <v>0</v>
       </c>
-      <c r="U22" s="15">
+      <c r="U22" s="16">
+        <v>0</v>
+      </c>
+      <c r="V22" s="16">
+        <v>0</v>
+      </c>
+      <c r="W22" s="15">
         <v>6.3506550727532349E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>46204</v>
       </c>
@@ -8680,40 +8910,46 @@
         <v>0</v>
       </c>
       <c r="K23" s="13">
+        <v>0</v>
+      </c>
+      <c r="L23" s="13">
         <v>223843</v>
       </c>
-      <c r="L23" s="14">
+      <c r="M23" s="14">
         <v>3469688</v>
       </c>
-      <c r="M23" s="15">
-        <v>0</v>
-      </c>
       <c r="N23" s="15">
         <v>0</v>
       </c>
-      <c r="O23" s="16">
+      <c r="O23" s="15">
         <v>0</v>
       </c>
       <c r="P23" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q23" s="16">
         <v>0.90059423210386635</v>
       </c>
-      <c r="Q23" s="16">
-        <v>0</v>
-      </c>
       <c r="R23" s="16">
+        <v>0</v>
+      </c>
+      <c r="S23" s="16">
         <v>3.4891898061151318E-2</v>
       </c>
-      <c r="S23" s="16">
-        <v>0</v>
-      </c>
       <c r="T23" s="16">
         <v>0</v>
       </c>
-      <c r="U23" s="15">
+      <c r="U23" s="16">
+        <v>0</v>
+      </c>
+      <c r="V23" s="16">
+        <v>0</v>
+      </c>
+      <c r="W23" s="15">
         <v>6.4513869834982279E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>46205</v>
       </c>
@@ -8745,44 +8981,50 @@
         <v>0</v>
       </c>
       <c r="K24" s="13">
+        <v>0</v>
+      </c>
+      <c r="L24" s="13">
         <v>223843</v>
       </c>
-      <c r="L24" s="14">
-        <f>SUM(C24:K24)</f>
+      <c r="M24" s="14">
+        <f>SUM(C24:L24)</f>
         <v>460932</v>
       </c>
-      <c r="M24" s="15">
-        <v>0</v>
-      </c>
       <c r="N24" s="15">
         <v>0</v>
       </c>
-      <c r="O24" s="16">
+      <c r="O24" s="15">
         <v>0</v>
       </c>
       <c r="P24" s="16">
         <v>0</v>
       </c>
       <c r="Q24" s="16">
-        <f>G24/L24</f>
+        <v>0</v>
+      </c>
+      <c r="R24" s="16">
+        <f>G24/M24</f>
         <v>0.25171825779073703</v>
       </c>
-      <c r="R24" s="16">
-        <f>H24/L24</f>
+      <c r="S24" s="16">
+        <f>H24/M24</f>
         <v>0.2626504560325601</v>
       </c>
-      <c r="S24" s="16">
-        <v>0</v>
-      </c>
       <c r="T24" s="16">
         <v>0</v>
       </c>
-      <c r="U24" s="15">
-        <f>K24/L24</f>
+      <c r="U24" s="16">
+        <v>0</v>
+      </c>
+      <c r="V24" s="16">
+        <v>0</v>
+      </c>
+      <c r="W24" s="15">
+        <f>L24/M24</f>
         <v>0.48563128617670287</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>46206</v>
       </c>
@@ -8814,20 +9056,20 @@
         <v>0</v>
       </c>
       <c r="K25" s="13">
+        <v>0</v>
+      </c>
+      <c r="L25" s="13">
         <v>223843</v>
       </c>
-      <c r="L25" s="14">
+      <c r="M25" s="14">
         <v>374479.39</v>
       </c>
-      <c r="M25" s="15">
-        <v>0</v>
-      </c>
       <c r="N25" s="15">
+        <v>0</v>
+      </c>
+      <c r="O25" s="15">
         <v>7.8969339273918415E-2</v>
       </c>
-      <c r="O25" s="16">
-        <v>0</v>
-      </c>
       <c r="P25" s="16">
         <v>0</v>
       </c>
@@ -8835,19 +9077,25 @@
         <v>0</v>
       </c>
       <c r="R25" s="16">
+        <v>0</v>
+      </c>
+      <c r="S25" s="16">
         <v>0.32328614933921995</v>
       </c>
-      <c r="S25" s="16">
-        <v>0</v>
-      </c>
       <c r="T25" s="16">
         <v>0</v>
       </c>
-      <c r="U25" s="15">
+      <c r="U25" s="16">
+        <v>0</v>
+      </c>
+      <c r="V25" s="16">
+        <v>0</v>
+      </c>
+      <c r="W25" s="15">
         <v>0.59774451138686158</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>46209</v>
       </c>
@@ -8879,20 +9127,20 @@
         <v>0</v>
       </c>
       <c r="K26" s="13">
+        <v>0</v>
+      </c>
+      <c r="L26" s="13">
         <v>223843</v>
       </c>
-      <c r="L26" s="14">
+      <c r="M26" s="14">
         <v>372801.92</v>
       </c>
-      <c r="M26" s="15">
-        <v>0</v>
-      </c>
       <c r="N26" s="15">
+        <v>0</v>
+      </c>
+      <c r="O26" s="15">
         <v>7.4825043819516768E-2</v>
       </c>
-      <c r="O26" s="16">
-        <v>0</v>
-      </c>
       <c r="P26" s="16">
         <v>0</v>
       </c>
@@ -8900,19 +9148,25 @@
         <v>0</v>
       </c>
       <c r="R26" s="16">
+        <v>0</v>
+      </c>
+      <c r="S26" s="16">
         <v>0.32474081678549299</v>
       </c>
-      <c r="S26" s="16">
-        <v>0</v>
-      </c>
       <c r="T26" s="16">
         <v>0</v>
       </c>
-      <c r="U26" s="15">
+      <c r="U26" s="16">
+        <v>0</v>
+      </c>
+      <c r="V26" s="16">
+        <v>0</v>
+      </c>
+      <c r="W26" s="15">
         <v>0.60043413939499024</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>46210</v>
       </c>
@@ -8944,20 +9198,20 @@
         <v>0</v>
       </c>
       <c r="K27" s="13">
+        <v>0</v>
+      </c>
+      <c r="L27" s="13">
         <v>223843</v>
       </c>
-      <c r="L27" s="14">
+      <c r="M27" s="14">
         <v>375246.11</v>
       </c>
-      <c r="M27" s="15">
-        <v>0</v>
-      </c>
       <c r="N27" s="15">
+        <v>0</v>
+      </c>
+      <c r="O27" s="15">
         <v>8.0851231209298838E-2</v>
       </c>
-      <c r="O27" s="16">
-        <v>0</v>
-      </c>
       <c r="P27" s="16">
         <v>0</v>
       </c>
@@ -8965,19 +9219,25 @@
         <v>0</v>
       </c>
       <c r="R27" s="16">
+        <v>0</v>
+      </c>
+      <c r="S27" s="16">
         <v>0.32262559630531545</v>
       </c>
-      <c r="S27" s="16">
-        <v>0</v>
-      </c>
       <c r="T27" s="16">
         <v>0</v>
       </c>
-      <c r="U27" s="15">
+      <c r="U27" s="16">
+        <v>0</v>
+      </c>
+      <c r="V27" s="16">
+        <v>0</v>
+      </c>
+      <c r="W27" s="15">
         <v>0.59652317248538567</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>46211</v>
       </c>
@@ -9009,18 +9269,18 @@
         <v>0</v>
       </c>
       <c r="K28" s="13">
+        <v>0</v>
+      </c>
+      <c r="L28" s="13">
         <v>223843</v>
       </c>
-      <c r="L28" s="14">
+      <c r="M28" s="14">
         <v>435718</v>
       </c>
-      <c r="M28" s="15">
+      <c r="N28" s="15">
         <v>0.20841691185583336</v>
       </c>
-      <c r="N28" s="15">
-        <v>0</v>
-      </c>
-      <c r="O28" s="16">
+      <c r="O28" s="15">
         <v>0</v>
       </c>
       <c r="P28" s="16">
@@ -9030,19 +9290,25 @@
         <v>0</v>
       </c>
       <c r="R28" s="16">
+        <v>0</v>
+      </c>
+      <c r="S28" s="16">
         <v>0.27784943472613022</v>
       </c>
-      <c r="S28" s="16">
-        <v>0</v>
-      </c>
       <c r="T28" s="16">
         <v>0</v>
       </c>
-      <c r="U28" s="15">
+      <c r="U28" s="16">
+        <v>0</v>
+      </c>
+      <c r="V28" s="16">
+        <v>0</v>
+      </c>
+      <c r="W28" s="15">
         <v>0.51373365341803645</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>46212</v>
       </c>
@@ -9074,18 +9340,18 @@
         <v>0</v>
       </c>
       <c r="K29" s="13">
+        <v>0</v>
+      </c>
+      <c r="L29" s="13">
         <v>223843</v>
       </c>
-      <c r="L29" s="14">
+      <c r="M29" s="14">
         <v>435718</v>
       </c>
-      <c r="M29" s="15">
+      <c r="N29" s="15">
         <v>0.20841691185583336</v>
       </c>
-      <c r="N29" s="15">
-        <v>0</v>
-      </c>
-      <c r="O29" s="16">
+      <c r="O29" s="15">
         <v>0</v>
       </c>
       <c r="P29" s="16">
@@ -9095,19 +9361,25 @@
         <v>0</v>
       </c>
       <c r="R29" s="16">
+        <v>0</v>
+      </c>
+      <c r="S29" s="16">
         <v>0.27784943472613022</v>
       </c>
-      <c r="S29" s="16">
-        <v>0</v>
-      </c>
       <c r="T29" s="16">
         <v>0</v>
       </c>
-      <c r="U29" s="15">
+      <c r="U29" s="16">
+        <v>0</v>
+      </c>
+      <c r="V29" s="16">
+        <v>0</v>
+      </c>
+      <c r="W29" s="15">
         <v>0.51373365341803645</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>46213</v>
       </c>
@@ -9139,18 +9411,18 @@
         <v>0</v>
       </c>
       <c r="K30" s="13">
+        <v>0</v>
+      </c>
+      <c r="L30" s="13">
         <v>223843</v>
       </c>
-      <c r="L30" s="14">
+      <c r="M30" s="14">
         <v>435718</v>
       </c>
-      <c r="M30" s="15">
+      <c r="N30" s="15">
         <v>0.20841691185583336</v>
       </c>
-      <c r="N30" s="15">
-        <v>0</v>
-      </c>
-      <c r="O30" s="16">
+      <c r="O30" s="15">
         <v>0</v>
       </c>
       <c r="P30" s="16">
@@ -9160,19 +9432,25 @@
         <v>0</v>
       </c>
       <c r="R30" s="16">
+        <v>0</v>
+      </c>
+      <c r="S30" s="16">
         <v>0.27784943472613022</v>
       </c>
-      <c r="S30" s="16">
-        <v>0</v>
-      </c>
       <c r="T30" s="16">
         <v>0</v>
       </c>
-      <c r="U30" s="15">
+      <c r="U30" s="16">
+        <v>0</v>
+      </c>
+      <c r="V30" s="16">
+        <v>0</v>
+      </c>
+      <c r="W30" s="15">
         <v>0.51373365341803645</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>46216</v>
       </c>
@@ -9204,18 +9482,18 @@
         <v>0</v>
       </c>
       <c r="K31" s="13">
+        <v>0</v>
+      </c>
+      <c r="L31" s="13">
         <v>223843</v>
       </c>
-      <c r="L31" s="14">
+      <c r="M31" s="14">
         <v>435718</v>
       </c>
-      <c r="M31" s="15">
+      <c r="N31" s="15">
         <v>0.20841691185583336</v>
       </c>
-      <c r="N31" s="15">
-        <v>0</v>
-      </c>
-      <c r="O31" s="16">
+      <c r="O31" s="15">
         <v>0</v>
       </c>
       <c r="P31" s="16">
@@ -9225,19 +9503,25 @@
         <v>0</v>
       </c>
       <c r="R31" s="16">
+        <v>0</v>
+      </c>
+      <c r="S31" s="16">
         <v>0.27784943472613022</v>
       </c>
-      <c r="S31" s="16">
-        <v>0</v>
-      </c>
       <c r="T31" s="16">
         <v>0</v>
       </c>
-      <c r="U31" s="15">
+      <c r="U31" s="16">
+        <v>0</v>
+      </c>
+      <c r="V31" s="16">
+        <v>0</v>
+      </c>
+      <c r="W31" s="15">
         <v>0.51373365341803645</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>46217</v>
       </c>
@@ -9269,20 +9553,20 @@
         <v>0</v>
       </c>
       <c r="K32" s="13">
+        <v>0</v>
+      </c>
+      <c r="L32" s="13">
         <v>223843</v>
       </c>
-      <c r="L32" s="14">
+      <c r="M32" s="14">
         <v>378852.03</v>
       </c>
-      <c r="M32" s="15">
-        <v>0</v>
-      </c>
       <c r="N32" s="15">
+        <v>0</v>
+      </c>
+      <c r="O32" s="15">
         <v>8.9599704665697652E-2</v>
       </c>
-      <c r="O32" s="16">
-        <v>0</v>
-      </c>
       <c r="P32" s="16">
         <v>0</v>
       </c>
@@ -9290,19 +9574,25 @@
         <v>0</v>
       </c>
       <c r="R32" s="16">
+        <v>0</v>
+      </c>
+      <c r="S32" s="16">
         <v>0.31955484044786558</v>
       </c>
-      <c r="S32" s="16">
-        <v>0</v>
-      </c>
       <c r="T32" s="16">
         <v>0</v>
       </c>
-      <c r="U32" s="15">
+      <c r="U32" s="16">
+        <v>0</v>
+      </c>
+      <c r="V32" s="16">
+        <v>0</v>
+      </c>
+      <c r="W32" s="15">
         <v>0.5908454548864368</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>46218</v>
       </c>
@@ -9334,20 +9624,20 @@
         <v>0</v>
       </c>
       <c r="K33" s="13">
+        <v>0</v>
+      </c>
+      <c r="L33" s="13">
         <v>223843</v>
       </c>
-      <c r="L33" s="14">
+      <c r="M33" s="14">
         <v>374437.1</v>
       </c>
-      <c r="M33" s="15">
-        <v>0</v>
-      </c>
       <c r="N33" s="15">
+        <v>0</v>
+      </c>
+      <c r="O33" s="15">
         <v>7.8865315429480623E-2</v>
       </c>
-      <c r="O33" s="16">
-        <v>0</v>
-      </c>
       <c r="P33" s="16">
         <v>0</v>
       </c>
@@ -9355,19 +9645,25 @@
         <v>0</v>
       </c>
       <c r="R33" s="16">
+        <v>0</v>
+      </c>
+      <c r="S33" s="16">
         <v>0.32332266220414591</v>
       </c>
-      <c r="S33" s="16">
-        <v>0</v>
-      </c>
       <c r="T33" s="16">
         <v>0</v>
       </c>
-      <c r="U33" s="15">
+      <c r="U33" s="16">
+        <v>0</v>
+      </c>
+      <c r="V33" s="16">
+        <v>0</v>
+      </c>
+      <c r="W33" s="15">
         <v>0.59781202236637343</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>46219</v>
       </c>
@@ -9399,20 +9695,20 @@
         <v>0</v>
       </c>
       <c r="K34" s="13">
+        <v>0</v>
+      </c>
+      <c r="L34" s="13">
         <v>223843</v>
       </c>
-      <c r="L34" s="14">
+      <c r="M34" s="14">
         <v>372248.26</v>
       </c>
-      <c r="M34" s="15">
-        <v>0</v>
-      </c>
       <c r="N34" s="15">
+        <v>0</v>
+      </c>
+      <c r="O34" s="15">
         <v>7.3448993421755704E-2</v>
       </c>
-      <c r="O34" s="16">
-        <v>0</v>
-      </c>
       <c r="P34" s="16">
         <v>0</v>
       </c>
@@ -9420,19 +9716,25 @@
         <v>0</v>
       </c>
       <c r="R34" s="16">
+        <v>0</v>
+      </c>
+      <c r="S34" s="16">
         <v>0.32522381703006481</v>
       </c>
-      <c r="S34" s="16">
-        <v>0</v>
-      </c>
       <c r="T34" s="16">
         <v>0</v>
       </c>
-      <c r="U34" s="15">
+      <c r="U34" s="16">
+        <v>0</v>
+      </c>
+      <c r="V34" s="16">
+        <v>0</v>
+      </c>
+      <c r="W34" s="15">
         <v>0.60132718954817943</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>46220</v>
       </c>
@@ -9464,20 +9766,20 @@
         <v>0</v>
       </c>
       <c r="K35" s="13">
+        <v>0</v>
+      </c>
+      <c r="L35" s="13">
         <v>223843</v>
       </c>
-      <c r="L35" s="14">
+      <c r="M35" s="14">
         <v>376025.4</v>
       </c>
-      <c r="M35" s="15">
-        <v>0</v>
-      </c>
       <c r="N35" s="15">
+        <v>0</v>
+      </c>
+      <c r="O35" s="15">
         <v>8.2756111688199838E-2</v>
       </c>
-      <c r="O35" s="16">
-        <v>0</v>
-      </c>
       <c r="P35" s="16">
         <v>0</v>
       </c>
@@ -9485,19 +9787,25 @@
         <v>0</v>
       </c>
       <c r="R35" s="16">
+        <v>0</v>
+      </c>
+      <c r="S35" s="16">
         <v>0.32195697418312696</v>
       </c>
-      <c r="S35" s="16">
-        <v>0</v>
-      </c>
       <c r="T35" s="16">
         <v>0</v>
       </c>
-      <c r="U35" s="15">
+      <c r="U35" s="16">
+        <v>0</v>
+      </c>
+      <c r="V35" s="16">
+        <v>0</v>
+      </c>
+      <c r="W35" s="15">
         <v>0.59528691412867318</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>46223</v>
       </c>
@@ -9529,20 +9837,20 @@
         <v>0</v>
       </c>
       <c r="K36" s="13">
+        <v>0</v>
+      </c>
+      <c r="L36" s="13">
         <v>223843</v>
       </c>
-      <c r="L36" s="14">
+      <c r="M36" s="14">
         <v>375009.72</v>
       </c>
-      <c r="M36" s="15">
-        <v>0</v>
-      </c>
       <c r="N36" s="15">
+        <v>0</v>
+      </c>
+      <c r="O36" s="15">
         <v>8.0271839353923874E-2</v>
       </c>
-      <c r="O36" s="16">
-        <v>0</v>
-      </c>
       <c r="P36" s="16">
         <v>0</v>
       </c>
@@ -9550,19 +9858,25 @@
         <v>0</v>
       </c>
       <c r="R36" s="16">
+        <v>0</v>
+      </c>
+      <c r="S36" s="16">
         <v>0.32282896560654484</v>
       </c>
-      <c r="S36" s="16">
-        <v>0</v>
-      </c>
       <c r="T36" s="16">
         <v>0</v>
       </c>
-      <c r="U36" s="15">
+      <c r="U36" s="16">
+        <v>0</v>
+      </c>
+      <c r="V36" s="16">
+        <v>0</v>
+      </c>
+      <c r="W36" s="15">
         <v>0.59689919503953126</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>46224</v>
       </c>
@@ -9594,20 +9908,20 @@
         <v>0</v>
       </c>
       <c r="K37" s="13">
+        <v>0</v>
+      </c>
+      <c r="L37" s="13">
         <v>223843</v>
       </c>
-      <c r="L37" s="14">
+      <c r="M37" s="14">
         <v>375731.28</v>
       </c>
-      <c r="M37" s="15">
-        <v>0</v>
-      </c>
       <c r="N37" s="15">
+        <v>0</v>
+      </c>
+      <c r="O37" s="15">
         <v>8.2038099143622076E-2</v>
       </c>
-      <c r="O37" s="16">
-        <v>0</v>
-      </c>
       <c r="P37" s="16">
         <v>0</v>
       </c>
@@ -9615,19 +9929,25 @@
         <v>0</v>
       </c>
       <c r="R37" s="16">
+        <v>0</v>
+      </c>
+      <c r="S37" s="16">
         <v>0.32220900000660047</v>
       </c>
-      <c r="S37" s="16">
-        <v>0</v>
-      </c>
       <c r="T37" s="16">
         <v>0</v>
       </c>
-      <c r="U37" s="15">
+      <c r="U37" s="16">
+        <v>0</v>
+      </c>
+      <c r="V37" s="16">
+        <v>0</v>
+      </c>
+      <c r="W37" s="15">
         <v>0.5957529008497775</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <v>46225</v>
       </c>
@@ -9659,20 +9979,20 @@
         <v>0</v>
       </c>
       <c r="K38" s="13">
+        <v>0</v>
+      </c>
+      <c r="L38" s="13">
         <v>223843</v>
       </c>
-      <c r="L38" s="14">
+      <c r="M38" s="14">
         <v>378174.99</v>
       </c>
-      <c r="M38" s="15">
-        <v>0</v>
-      </c>
       <c r="N38" s="15">
+        <v>0</v>
+      </c>
+      <c r="O38" s="15">
         <v>8.79698311091381E-2</v>
       </c>
-      <c r="O38" s="16">
-        <v>0</v>
-      </c>
       <c r="P38" s="16">
         <v>0</v>
       </c>
@@ -9680,19 +10000,25 @@
         <v>0</v>
       </c>
       <c r="R38" s="16">
+        <v>0</v>
+      </c>
+      <c r="S38" s="16">
         <v>0.32012693383028845</v>
       </c>
-      <c r="S38" s="16">
-        <v>0</v>
-      </c>
       <c r="T38" s="16">
         <v>0</v>
       </c>
-      <c r="U38" s="15">
+      <c r="U38" s="16">
+        <v>0</v>
+      </c>
+      <c r="V38" s="16">
+        <v>0</v>
+      </c>
+      <c r="W38" s="15">
         <v>0.59190323506057341</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <v>46226</v>
       </c>
@@ -9724,20 +10050,20 @@
         <v>0</v>
       </c>
       <c r="K39" s="13">
+        <v>0</v>
+      </c>
+      <c r="L39" s="13">
         <v>223843</v>
       </c>
-      <c r="L39" s="14">
+      <c r="M39" s="14">
         <v>380362.45</v>
       </c>
-      <c r="M39" s="15">
-        <v>0</v>
-      </c>
       <c r="N39" s="15">
+        <v>0</v>
+      </c>
+      <c r="O39" s="15">
         <v>9.3214905940373474E-2</v>
       </c>
-      <c r="O39" s="16">
-        <v>0</v>
-      </c>
       <c r="P39" s="16">
         <v>0</v>
       </c>
@@ -9745,19 +10071,25 @@
         <v>0</v>
       </c>
       <c r="R39" s="16">
+        <v>0</v>
+      </c>
+      <c r="S39" s="16">
         <v>0.31828588757907095</v>
       </c>
-      <c r="S39" s="16">
-        <v>0</v>
-      </c>
       <c r="T39" s="16">
         <v>0</v>
       </c>
-      <c r="U39" s="15">
+      <c r="U39" s="16">
+        <v>0</v>
+      </c>
+      <c r="V39" s="16">
+        <v>0</v>
+      </c>
+      <c r="W39" s="15">
         <v>0.58849920648055554</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <v>46227</v>
       </c>
@@ -9790,20 +10122,20 @@
         <v>0</v>
       </c>
       <c r="K40" s="13">
+        <v>0</v>
+      </c>
+      <c r="L40" s="13">
         <v>223843</v>
       </c>
-      <c r="L40" s="14">
+      <c r="M40" s="14">
         <v>377185.45</v>
       </c>
-      <c r="M40" s="15">
-        <v>0</v>
-      </c>
       <c r="N40" s="15">
+        <v>0</v>
+      </c>
+      <c r="O40" s="15">
         <v>8.5577134536870422E-2</v>
       </c>
-      <c r="O40" s="16">
-        <v>0</v>
-      </c>
       <c r="P40" s="16">
         <v>0</v>
       </c>
@@ -9811,19 +10143,25 @@
         <v>0</v>
       </c>
       <c r="R40" s="16">
+        <v>0</v>
+      </c>
+      <c r="S40" s="16">
         <v>0.32096678172501086</v>
       </c>
-      <c r="S40" s="16">
-        <v>0</v>
-      </c>
       <c r="T40" s="16">
         <v>0</v>
       </c>
-      <c r="U40" s="15">
+      <c r="U40" s="16">
+        <v>0</v>
+      </c>
+      <c r="V40" s="16">
+        <v>0</v>
+      </c>
+      <c r="W40" s="15">
         <v>0.59345608373811876</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <v>46230</v>
       </c>
@@ -9856,20 +10194,20 @@
         <v>0</v>
       </c>
       <c r="K41" s="13">
+        <v>0</v>
+      </c>
+      <c r="L41" s="13">
         <v>223843</v>
       </c>
-      <c r="L41" s="14">
+      <c r="M41" s="14">
         <v>378220.45</v>
       </c>
-      <c r="M41" s="15">
-        <v>0</v>
-      </c>
       <c r="N41" s="15">
+        <v>0</v>
+      </c>
+      <c r="O41" s="15">
         <v>8.807945207616355E-2</v>
       </c>
-      <c r="O41" s="16">
-        <v>0</v>
-      </c>
       <c r="P41" s="16">
         <v>0</v>
       </c>
@@ -9877,19 +10215,25 @@
         <v>0</v>
       </c>
       <c r="R41" s="16">
+        <v>0</v>
+      </c>
+      <c r="S41" s="16">
         <v>0.32008845634867178</v>
       </c>
-      <c r="S41" s="16">
-        <v>0</v>
-      </c>
       <c r="T41" s="16">
         <v>0</v>
       </c>
-      <c r="U41" s="15">
+      <c r="U41" s="16">
+        <v>0</v>
+      </c>
+      <c r="V41" s="16">
+        <v>0</v>
+      </c>
+      <c r="W41" s="15">
         <v>0.5918320915751647</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <v>46231</v>
       </c>
@@ -9922,18 +10266,18 @@
         <v>0</v>
       </c>
       <c r="K42" s="13">
+        <v>0</v>
+      </c>
+      <c r="L42" s="13">
         <v>223843</v>
       </c>
-      <c r="L42" s="14">
+      <c r="M42" s="14">
         <v>679531</v>
       </c>
-      <c r="M42" s="15">
+      <c r="N42" s="15">
         <v>0.49243375210255308</v>
       </c>
-      <c r="N42" s="15">
-        <v>0</v>
-      </c>
-      <c r="O42" s="16">
+      <c r="O42" s="15">
         <v>0</v>
       </c>
       <c r="P42" s="16">
@@ -9943,19 +10287,25 @@
         <v>0</v>
       </c>
       <c r="R42" s="16">
+        <v>0</v>
+      </c>
+      <c r="S42" s="16">
         <v>0.17815817085607574</v>
       </c>
-      <c r="S42" s="16">
-        <v>0</v>
-      </c>
       <c r="T42" s="16">
         <v>0</v>
       </c>
-      <c r="U42" s="15">
+      <c r="U42" s="16">
+        <v>0</v>
+      </c>
+      <c r="V42" s="16">
+        <v>0</v>
+      </c>
+      <c r="W42" s="15">
         <v>0.32940807704137121</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
         <v>46232</v>
       </c>
@@ -9988,18 +10338,18 @@
         <v>0</v>
       </c>
       <c r="K43" s="13">
+        <v>0</v>
+      </c>
+      <c r="L43" s="13">
         <v>223843</v>
       </c>
-      <c r="L43" s="14">
+      <c r="M43" s="14">
         <v>679531</v>
       </c>
-      <c r="M43" s="15">
+      <c r="N43" s="15">
         <v>0.49243375210255308</v>
       </c>
-      <c r="N43" s="15">
-        <v>0</v>
-      </c>
-      <c r="O43" s="16">
+      <c r="O43" s="15">
         <v>0</v>
       </c>
       <c r="P43" s="16">
@@ -10009,19 +10359,25 @@
         <v>0</v>
       </c>
       <c r="R43" s="16">
+        <v>0</v>
+      </c>
+      <c r="S43" s="16">
         <v>0.17815817085607574</v>
       </c>
-      <c r="S43" s="16">
-        <v>0</v>
-      </c>
       <c r="T43" s="16">
         <v>0</v>
       </c>
-      <c r="U43" s="15">
+      <c r="U43" s="16">
+        <v>0</v>
+      </c>
+      <c r="V43" s="16">
+        <v>0</v>
+      </c>
+      <c r="W43" s="15">
         <v>0.32940807704137121</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <v>46233</v>
       </c>
@@ -10054,20 +10410,20 @@
         <v>0</v>
       </c>
       <c r="K44" s="13">
+        <v>0</v>
+      </c>
+      <c r="L44" s="13">
         <v>223843</v>
       </c>
-      <c r="L44" s="14">
+      <c r="M44" s="14">
         <v>391793.7</v>
       </c>
-      <c r="M44" s="15">
-        <v>0</v>
-      </c>
       <c r="N44" s="15">
+        <v>0</v>
+      </c>
+      <c r="O44" s="15">
         <v>0.11967190896637697</v>
       </c>
-      <c r="O44" s="16">
-        <v>0</v>
-      </c>
       <c r="P44" s="16">
         <v>0</v>
       </c>
@@ -10075,19 +10431,25 @@
         <v>0</v>
       </c>
       <c r="R44" s="16">
+        <v>0</v>
+      </c>
+      <c r="S44" s="16">
         <v>0.30899935348628627</v>
       </c>
-      <c r="S44" s="16">
-        <v>0</v>
-      </c>
       <c r="T44" s="16">
         <v>0</v>
       </c>
-      <c r="U44" s="15">
+      <c r="U44" s="16">
+        <v>0</v>
+      </c>
+      <c r="V44" s="16">
+        <v>0</v>
+      </c>
+      <c r="W44" s="15">
         <v>0.57132873754733671</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
         <v>46234</v>
       </c>
@@ -10120,20 +10482,20 @@
         <v>0</v>
       </c>
       <c r="K45" s="13">
+        <v>0</v>
+      </c>
+      <c r="L45" s="13">
         <v>223843</v>
       </c>
-      <c r="L45" s="14">
+      <c r="M45" s="14">
         <v>388741.7</v>
       </c>
-      <c r="M45" s="15">
-        <v>0</v>
-      </c>
       <c r="N45" s="15">
+        <v>0</v>
+      </c>
+      <c r="O45" s="15">
         <v>0.11276047823014616</v>
       </c>
-      <c r="O45" s="16">
-        <v>0</v>
-      </c>
       <c r="P45" s="16">
         <v>0</v>
       </c>
@@ -10141,19 +10503,25 @@
         <v>0</v>
       </c>
       <c r="R45" s="16">
+        <v>0</v>
+      </c>
+      <c r="S45" s="16">
         <v>0.3114252985980151</v>
       </c>
-      <c r="S45" s="16">
-        <v>0</v>
-      </c>
       <c r="T45" s="16">
         <v>0</v>
       </c>
-      <c r="U45" s="15">
+      <c r="U45" s="16">
+        <v>0</v>
+      </c>
+      <c r="V45" s="16">
+        <v>0</v>
+      </c>
+      <c r="W45" s="15">
         <v>0.57581422317183872</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A46" s="10">
         <v>46237</v>
       </c>
@@ -10186,20 +10554,20 @@
         <v>0</v>
       </c>
       <c r="K46" s="13">
+        <v>0</v>
+      </c>
+      <c r="L46" s="13">
         <v>223843</v>
       </c>
-      <c r="L46" s="14">
+      <c r="M46" s="14">
         <v>385314.7</v>
       </c>
-      <c r="M46" s="15">
-        <v>0</v>
-      </c>
       <c r="N46" s="15">
+        <v>0</v>
+      </c>
+      <c r="O46" s="15">
         <v>0.10486934446051503</v>
       </c>
-      <c r="O46" s="16">
-        <v>0</v>
-      </c>
       <c r="P46" s="16">
         <v>0</v>
       </c>
@@ -10207,19 +10575,25 @@
         <v>0</v>
       </c>
       <c r="R46" s="16">
+        <v>0</v>
+      </c>
+      <c r="S46" s="16">
         <v>0.31419512414138362</v>
       </c>
-      <c r="S46" s="16">
-        <v>0</v>
-      </c>
       <c r="T46" s="16">
         <v>0</v>
       </c>
-      <c r="U46" s="15">
+      <c r="U46" s="16">
+        <v>0</v>
+      </c>
+      <c r="V46" s="16">
+        <v>0</v>
+      </c>
+      <c r="W46" s="15">
         <v>0.58093553139810128</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A47" s="10">
         <v>46238</v>
       </c>
@@ -10252,20 +10626,20 @@
         <v>0</v>
       </c>
       <c r="K47" s="13">
+        <v>0</v>
+      </c>
+      <c r="L47" s="13">
         <v>223843</v>
       </c>
-      <c r="L47" s="14">
+      <c r="M47" s="14">
         <v>383427.7</v>
       </c>
-      <c r="M47" s="15">
-        <v>0</v>
-      </c>
       <c r="N47" s="15">
+        <v>0</v>
+      </c>
+      <c r="O47" s="15">
         <v>0.1004640509801457</v>
       </c>
-      <c r="O47" s="16">
-        <v>0</v>
-      </c>
       <c r="P47" s="16">
         <v>0</v>
       </c>
@@ -10273,19 +10647,25 @@
         <v>0</v>
       </c>
       <c r="R47" s="16">
+        <v>0</v>
+      </c>
+      <c r="S47" s="16">
         <v>0.31574140313806226</v>
       </c>
-      <c r="S47" s="16">
-        <v>0</v>
-      </c>
       <c r="T47" s="16">
         <v>0</v>
       </c>
-      <c r="U47" s="15">
+      <c r="U47" s="16">
+        <v>0</v>
+      </c>
+      <c r="V47" s="16">
+        <v>0</v>
+      </c>
+      <c r="W47" s="15">
         <v>0.58379454588179203</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A48" s="10">
         <v>46239</v>
       </c>
@@ -10318,20 +10698,20 @@
         <v>0</v>
       </c>
       <c r="K48" s="13">
+        <v>0</v>
+      </c>
+      <c r="L48" s="13">
         <v>223843</v>
       </c>
-      <c r="L48" s="14">
+      <c r="M48" s="14">
         <v>381652.7</v>
       </c>
-      <c r="M48" s="15">
-        <v>0</v>
-      </c>
       <c r="N48" s="15">
+        <v>0</v>
+      </c>
+      <c r="O48" s="15">
         <v>9.6280466507901064E-2</v>
       </c>
-      <c r="O48" s="16">
-        <v>0</v>
-      </c>
       <c r="P48" s="16">
         <v>0</v>
       </c>
@@ -10339,19 +10719,25 @@
         <v>0</v>
       </c>
       <c r="R48" s="16">
+        <v>0</v>
+      </c>
+      <c r="S48" s="16">
         <v>0.31720986121675543</v>
       </c>
-      <c r="S48" s="16">
-        <v>0</v>
-      </c>
       <c r="T48" s="16">
         <v>0</v>
       </c>
-      <c r="U48" s="15">
+      <c r="U48" s="16">
+        <v>0</v>
+      </c>
+      <c r="V48" s="16">
+        <v>0</v>
+      </c>
+      <c r="W48" s="15">
         <v>0.58650967227534356</v>
       </c>
     </row>
-    <row r="49" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" s="10">
         <v>46240</v>
       </c>
@@ -10384,20 +10770,20 @@
         <v>0</v>
       </c>
       <c r="K49" s="13">
+        <v>0</v>
+      </c>
+      <c r="L49" s="13">
         <v>223843</v>
       </c>
-      <c r="L49" s="14">
+      <c r="M49" s="14">
         <v>383198.7</v>
       </c>
-      <c r="M49" s="15">
-        <v>0</v>
-      </c>
       <c r="N49" s="15">
+        <v>0</v>
+      </c>
+      <c r="O49" s="15">
         <v>9.9926487224513055E-2</v>
       </c>
-      <c r="O49" s="16">
-        <v>0</v>
-      </c>
       <c r="P49" s="16">
         <v>0</v>
       </c>
@@ -10405,19 +10791,25 @@
         <v>0</v>
       </c>
       <c r="R49" s="16">
+        <v>0</v>
+      </c>
+      <c r="S49" s="16">
         <v>0.31593009057702959</v>
       </c>
-      <c r="S49" s="16">
-        <v>0</v>
-      </c>
       <c r="T49" s="16">
         <v>0</v>
       </c>
-      <c r="U49" s="15">
+      <c r="U49" s="16">
+        <v>0</v>
+      </c>
+      <c r="V49" s="16">
+        <v>0</v>
+      </c>
+      <c r="W49" s="15">
         <v>0.58414342219845738</v>
       </c>
     </row>
-    <row r="50" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" s="10">
         <v>46241</v>
       </c>
@@ -10450,20 +10842,20 @@
         <v>0</v>
       </c>
       <c r="K50" s="13">
+        <v>0</v>
+      </c>
+      <c r="L50" s="13">
         <v>223843</v>
       </c>
-      <c r="L50" s="14">
+      <c r="M50" s="14">
         <v>384776.7</v>
       </c>
-      <c r="M50" s="15">
-        <v>0</v>
-      </c>
       <c r="N50" s="15">
+        <v>0</v>
+      </c>
+      <c r="O50" s="15">
         <v>0.10361776063883289</v>
       </c>
-      <c r="O50" s="16">
-        <v>0</v>
-      </c>
       <c r="P50" s="16">
         <v>0</v>
       </c>
@@ -10471,19 +10863,25 @@
         <v>0</v>
       </c>
       <c r="R50" s="16">
+        <v>0</v>
+      </c>
+      <c r="S50" s="16">
         <v>0.31463443602484248</v>
       </c>
-      <c r="S50" s="16">
-        <v>0</v>
-      </c>
       <c r="T50" s="16">
         <v>0</v>
       </c>
-      <c r="U50" s="15">
+      <c r="U50" s="16">
+        <v>0</v>
+      </c>
+      <c r="V50" s="16">
+        <v>0</v>
+      </c>
+      <c r="W50" s="15">
         <v>0.5817478033363247</v>
       </c>
     </row>
-    <row r="51" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>46244</v>
       </c>
@@ -10515,21 +10913,21 @@
       <c r="J51" s="13">
         <v>0</v>
       </c>
-      <c r="K51" s="18">
+      <c r="K51" s="13">
+        <v>0</v>
+      </c>
+      <c r="L51" s="18">
         <v>54051</v>
       </c>
-      <c r="L51" s="14">
+      <c r="M51" s="14">
         <v>384909.7</v>
       </c>
-      <c r="M51" s="15">
-        <v>0</v>
-      </c>
       <c r="N51" s="15">
+        <v>0</v>
+      </c>
+      <c r="O51" s="15">
         <v>6.342448631458239E-2</v>
       </c>
-      <c r="O51" s="16">
-        <v>0</v>
-      </c>
       <c r="P51" s="16">
         <v>0</v>
       </c>
@@ -10537,19 +10935,25 @@
         <v>0</v>
       </c>
       <c r="R51" s="16">
+        <v>0</v>
+      </c>
+      <c r="S51" s="16">
         <v>0.31452571862959028</v>
       </c>
-      <c r="S51" s="16">
+      <c r="T51" s="16">
         <v>0.48162465118442066</v>
       </c>
-      <c r="T51" s="16">
-        <v>0</v>
-      </c>
-      <c r="U51" s="15">
+      <c r="U51" s="16">
+        <v>0</v>
+      </c>
+      <c r="V51" s="16">
+        <v>0</v>
+      </c>
+      <c r="W51" s="15">
         <v>0.14042514387140673</v>
       </c>
     </row>
-    <row r="52" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>46245</v>
       </c>
@@ -10581,21 +10985,21 @@
       <c r="J52" s="13">
         <v>0</v>
       </c>
-      <c r="K52" s="18">
+      <c r="K52" s="13">
+        <v>0</v>
+      </c>
+      <c r="L52" s="18">
         <v>54051</v>
       </c>
-      <c r="L52" s="14">
+      <c r="M52" s="14">
         <v>379686.7</v>
       </c>
-      <c r="M52" s="15">
-        <v>0</v>
-      </c>
       <c r="N52" s="15">
+        <v>0</v>
+      </c>
+      <c r="O52" s="15">
         <v>5.0540880151977961E-2</v>
       </c>
-      <c r="O52" s="16">
-        <v>0</v>
-      </c>
       <c r="P52" s="16">
         <v>0</v>
       </c>
@@ -10603,19 +11007,25 @@
         <v>0</v>
       </c>
       <c r="R52" s="16">
+        <v>0</v>
+      </c>
+      <c r="S52" s="16">
         <v>0.31885235906340675</v>
       </c>
-      <c r="S52" s="16">
+      <c r="T52" s="16">
         <v>0.48824991762945608</v>
       </c>
-      <c r="T52" s="16">
-        <v>0</v>
-      </c>
-      <c r="U52" s="15">
+      <c r="U52" s="16">
+        <v>0</v>
+      </c>
+      <c r="V52" s="16">
+        <v>0</v>
+      </c>
+      <c r="W52" s="15">
         <v>0.14235684315515923</v>
       </c>
     </row>
-    <row r="53" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>46246</v>
       </c>
@@ -10647,46 +11057,52 @@
       <c r="J53" s="13">
         <v>0</v>
       </c>
-      <c r="K53" s="18">
+      <c r="K53" s="13">
+        <v>0</v>
+      </c>
+      <c r="L53" s="18">
         <v>218671</v>
       </c>
-      <c r="L53" s="14">
-        <f>SUM(C53:K53)</f>
+      <c r="M53" s="14">
+        <f>SUM(C53:L53)</f>
         <v>676730</v>
       </c>
-      <c r="M53" s="15">
-        <v>0</v>
-      </c>
       <c r="N53" s="15">
         <v>0</v>
       </c>
-      <c r="O53" s="16">
+      <c r="O53" s="15">
         <v>0</v>
       </c>
       <c r="P53" s="16">
         <v>0</v>
       </c>
       <c r="Q53" s="16">
-        <f>G53/L53</f>
+        <v>0</v>
+      </c>
+      <c r="R53" s="16">
+        <f>G53/M53</f>
         <v>0.2699821199001079</v>
       </c>
-      <c r="R53" s="16">
-        <f>H53/L53</f>
+      <c r="S53" s="16">
+        <f>H53/M53</f>
         <v>0.17889557135046474</v>
       </c>
-      <c r="S53" s="16">
-        <f>I53/L53</f>
+      <c r="T53" s="16">
+        <f>I53/M53</f>
         <v>0.22799343903772554</v>
       </c>
-      <c r="T53" s="16">
-        <v>0</v>
-      </c>
-      <c r="U53" s="15">
-        <f>K53/L53</f>
+      <c r="U53" s="16">
+        <v>0</v>
+      </c>
+      <c r="V53" s="16">
+        <v>0</v>
+      </c>
+      <c r="W53" s="15">
+        <f>L53/M53</f>
         <v>0.32312886971170185</v>
       </c>
     </row>
-    <row r="54" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>46247</v>
       </c>
@@ -10718,19 +11134,19 @@
       <c r="J54" s="13">
         <v>0</v>
       </c>
-      <c r="K54" s="18">
+      <c r="K54" s="13">
+        <v>0</v>
+      </c>
+      <c r="L54" s="18">
         <v>218671</v>
       </c>
-      <c r="L54" s="14">
+      <c r="M54" s="14">
         <v>494025</v>
       </c>
-      <c r="M54" s="15">
-        <v>0</v>
-      </c>
       <c r="N54" s="15">
         <v>0</v>
       </c>
-      <c r="O54" s="16">
+      <c r="O54" s="15">
         <v>0</v>
       </c>
       <c r="P54" s="16">
@@ -10740,19 +11156,25 @@
         <v>0</v>
       </c>
       <c r="R54" s="16">
+        <v>0</v>
+      </c>
+      <c r="S54" s="16">
         <v>0.24505642427002683</v>
       </c>
-      <c r="S54" s="16">
+      <c r="T54" s="16">
         <v>0.31231212995293761</v>
       </c>
-      <c r="T54" s="16">
-        <v>0</v>
-      </c>
-      <c r="U54" s="15">
+      <c r="U54" s="16">
+        <v>0</v>
+      </c>
+      <c r="V54" s="16">
+        <v>0</v>
+      </c>
+      <c r="W54" s="15">
         <v>0.44263144577703556</v>
       </c>
     </row>
-    <row r="55" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>46248</v>
       </c>
@@ -10784,19 +11206,19 @@
       <c r="J55" s="13">
         <v>0</v>
       </c>
-      <c r="K55" s="18">
+      <c r="K55" s="13">
+        <v>0</v>
+      </c>
+      <c r="L55" s="18">
         <v>218671</v>
       </c>
-      <c r="L55" s="14">
+      <c r="M55" s="14">
         <v>494025</v>
       </c>
-      <c r="M55" s="15">
-        <v>0</v>
-      </c>
       <c r="N55" s="15">
         <v>0</v>
       </c>
-      <c r="O55" s="16">
+      <c r="O55" s="15">
         <v>0</v>
       </c>
       <c r="P55" s="16">
@@ -10806,19 +11228,25 @@
         <v>0</v>
       </c>
       <c r="R55" s="16">
+        <v>0</v>
+      </c>
+      <c r="S55" s="16">
         <v>0.24505642427002683</v>
       </c>
-      <c r="S55" s="16">
+      <c r="T55" s="16">
         <v>0.31231212995293761</v>
       </c>
-      <c r="T55" s="16">
-        <v>0</v>
-      </c>
-      <c r="U55" s="15">
+      <c r="U55" s="16">
+        <v>0</v>
+      </c>
+      <c r="V55" s="16">
+        <v>0</v>
+      </c>
+      <c r="W55" s="15">
         <v>0.44263144577703556</v>
       </c>
     </row>
-    <row r="56" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>46251</v>
       </c>
@@ -10850,19 +11278,19 @@
       <c r="J56" s="13">
         <v>0</v>
       </c>
-      <c r="K56" s="18">
+      <c r="K56" s="13">
+        <v>0</v>
+      </c>
+      <c r="L56" s="18">
         <v>218671</v>
       </c>
-      <c r="L56" s="14">
+      <c r="M56" s="14">
         <v>494025</v>
       </c>
-      <c r="M56" s="15">
-        <v>0</v>
-      </c>
       <c r="N56" s="15">
         <v>0</v>
       </c>
-      <c r="O56" s="16">
+      <c r="O56" s="15">
         <v>0</v>
       </c>
       <c r="P56" s="16">
@@ -10872,19 +11300,25 @@
         <v>0</v>
       </c>
       <c r="R56" s="16">
+        <v>0</v>
+      </c>
+      <c r="S56" s="16">
         <v>0.24505642427002683</v>
       </c>
-      <c r="S56" s="16">
+      <c r="T56" s="16">
         <v>0.31231212995293761</v>
       </c>
-      <c r="T56" s="16">
-        <v>0</v>
-      </c>
-      <c r="U56" s="15">
+      <c r="U56" s="16">
+        <v>0</v>
+      </c>
+      <c r="V56" s="16">
+        <v>0</v>
+      </c>
+      <c r="W56" s="15">
         <v>0.44263144577703556</v>
       </c>
     </row>
-    <row r="57" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
         <v>46252</v>
       </c>
@@ -10916,19 +11350,19 @@
       <c r="J57" s="13">
         <v>0</v>
       </c>
-      <c r="K57" s="18">
+      <c r="K57" s="13">
+        <v>0</v>
+      </c>
+      <c r="L57" s="18">
         <v>218671</v>
       </c>
-      <c r="L57" s="14">
+      <c r="M57" s="14">
         <v>494025</v>
       </c>
-      <c r="M57" s="15">
-        <v>0</v>
-      </c>
       <c r="N57" s="15">
         <v>0</v>
       </c>
-      <c r="O57" s="16">
+      <c r="O57" s="15">
         <v>0</v>
       </c>
       <c r="P57" s="16">
@@ -10938,19 +11372,25 @@
         <v>0</v>
       </c>
       <c r="R57" s="16">
+        <v>0</v>
+      </c>
+      <c r="S57" s="16">
         <v>0.24505642427002683</v>
       </c>
-      <c r="S57" s="16">
+      <c r="T57" s="16">
         <v>0.31231212995293761</v>
       </c>
-      <c r="T57" s="16">
-        <v>0</v>
-      </c>
-      <c r="U57" s="15">
+      <c r="U57" s="16">
+        <v>0</v>
+      </c>
+      <c r="V57" s="16">
+        <v>0</v>
+      </c>
+      <c r="W57" s="15">
         <v>0.44263144577703556</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" s="10">
         <v>46253</v>
       </c>
@@ -10982,19 +11422,19 @@
       <c r="J58" s="13">
         <v>0</v>
       </c>
-      <c r="K58" s="18">
+      <c r="K58" s="13">
+        <v>0</v>
+      </c>
+      <c r="L58" s="18">
         <v>218671</v>
       </c>
-      <c r="L58" s="14">
+      <c r="M58" s="14">
         <v>494025</v>
       </c>
-      <c r="M58" s="15">
-        <v>0</v>
-      </c>
       <c r="N58" s="15">
         <v>0</v>
       </c>
-      <c r="O58" s="16">
+      <c r="O58" s="15">
         <v>0</v>
       </c>
       <c r="P58" s="16">
@@ -11004,19 +11444,25 @@
         <v>0</v>
       </c>
       <c r="R58" s="16">
+        <v>0</v>
+      </c>
+      <c r="S58" s="16">
         <v>0.24505642427002683</v>
       </c>
-      <c r="S58" s="16">
+      <c r="T58" s="16">
         <v>0.31231212995293761</v>
       </c>
-      <c r="T58" s="16">
-        <v>0</v>
-      </c>
-      <c r="U58" s="15">
+      <c r="U58" s="16">
+        <v>0</v>
+      </c>
+      <c r="V58" s="16">
+        <v>0</v>
+      </c>
+      <c r="W58" s="15">
         <v>0.44263144577703556</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>46254</v>
       </c>
@@ -11048,46 +11494,52 @@
       <c r="J59" s="13">
         <v>0</v>
       </c>
-      <c r="K59" s="18">
+      <c r="K59" s="13">
+        <v>0</v>
+      </c>
+      <c r="L59" s="18">
         <v>218671</v>
       </c>
-      <c r="L59" s="14">
-        <f>SUM(C59:K59)</f>
+      <c r="M59" s="14">
+        <f>SUM(C59:L59)</f>
         <v>1945025</v>
       </c>
-      <c r="M59" s="15">
-        <v>0</v>
-      </c>
       <c r="N59" s="15">
         <v>0</v>
       </c>
-      <c r="O59" s="16">
+      <c r="O59" s="15">
         <v>0</v>
       </c>
       <c r="P59" s="16">
-        <f>E59/L59</f>
+        <v>0</v>
+      </c>
+      <c r="Q59" s="16">
+        <f>E59/M59</f>
         <v>0.7460058354005733</v>
       </c>
-      <c r="Q59" s="16">
-        <v>0</v>
-      </c>
       <c r="R59" s="16">
-        <f>H59/L59</f>
+        <v>0</v>
+      </c>
+      <c r="S59" s="16">
+        <f>H59/M59</f>
         <v>6.2242901762188149E-2</v>
       </c>
-      <c r="S59" s="16">
-        <f>I59/L59</f>
+      <c r="T59" s="16">
+        <f>I59/M59</f>
         <v>7.9325458541663993E-2</v>
       </c>
-      <c r="T59" s="16">
-        <v>0</v>
-      </c>
-      <c r="U59" s="15">
-        <f>K59/L59</f>
+      <c r="U59" s="16">
+        <v>0</v>
+      </c>
+      <c r="V59" s="16">
+        <v>0</v>
+      </c>
+      <c r="W59" s="15">
+        <f>L59/M59</f>
         <v>0.11242580429557461</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" s="10">
         <v>46255</v>
       </c>
@@ -11119,41 +11571,47 @@
       <c r="J60" s="13">
         <v>0</v>
       </c>
-      <c r="K60" s="18">
+      <c r="K60" s="13">
+        <v>0</v>
+      </c>
+      <c r="L60" s="18">
         <v>218671</v>
       </c>
-      <c r="L60" s="14">
+      <c r="M60" s="14">
         <v>930260</v>
       </c>
-      <c r="M60" s="15">
-        <v>0</v>
-      </c>
       <c r="N60" s="15">
         <v>0</v>
       </c>
-      <c r="O60" s="16">
+      <c r="O60" s="15">
         <v>0</v>
       </c>
       <c r="P60" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="16">
         <v>0.46893879130565647</v>
       </c>
-      <c r="Q60" s="16">
-        <v>0</v>
-      </c>
       <c r="R60" s="16">
+        <v>0</v>
+      </c>
+      <c r="S60" s="16">
         <v>0.13013996087115431</v>
       </c>
-      <c r="S60" s="16">
+      <c r="T60" s="16">
         <v>0.16585685722271193</v>
       </c>
-      <c r="T60" s="16">
-        <v>0</v>
-      </c>
-      <c r="U60" s="15">
+      <c r="U60" s="16">
+        <v>0</v>
+      </c>
+      <c r="V60" s="16">
+        <v>0</v>
+      </c>
+      <c r="W60" s="15">
         <v>0.23506439060047729</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" s="10">
         <v>46258</v>
       </c>
@@ -11185,48 +11643,54 @@
       <c r="J61" s="13">
         <v>0</v>
       </c>
-      <c r="K61" s="18">
+      <c r="K61" s="13">
+        <v>0</v>
+      </c>
+      <c r="L61" s="18">
         <v>218671</v>
       </c>
-      <c r="L61" s="14">
-        <f>SUM(C61:K61)</f>
+      <c r="M61" s="14">
+        <f>SUM(C61:L61)</f>
         <v>1204798</v>
       </c>
-      <c r="M61" s="15">
-        <f>C61/L61</f>
+      <c r="N61" s="15">
+        <f>C61/M61</f>
         <v>0.11067249447625245</v>
       </c>
-      <c r="N61" s="15">
-        <v>0</v>
-      </c>
-      <c r="O61" s="16">
-        <f>F61/L61</f>
+      <c r="O61" s="15">
+        <v>0</v>
+      </c>
+      <c r="P61" s="16">
+        <f>F61/M61</f>
         <v>0.11719806971791122</v>
       </c>
-      <c r="P61" s="16">
-        <f>E61/L61</f>
+      <c r="Q61" s="16">
+        <f>E61/M61</f>
         <v>0.36208144435830736</v>
       </c>
-      <c r="Q61" s="16">
-        <v>0</v>
-      </c>
       <c r="R61" s="16">
-        <f>H61/L61</f>
+        <v>0</v>
+      </c>
+      <c r="S61" s="16">
+        <f>H61/M61</f>
         <v>0.10048489456323799</v>
       </c>
-      <c r="S61" s="16">
-        <f>I61/L61</f>
+      <c r="T61" s="16">
+        <f>I61/M61</f>
         <v>0.12806296159190173</v>
       </c>
-      <c r="T61" s="16">
-        <v>0</v>
-      </c>
-      <c r="U61" s="15">
-        <f>K61/L61</f>
+      <c r="U61" s="16">
+        <v>0</v>
+      </c>
+      <c r="V61" s="16">
+        <v>0</v>
+      </c>
+      <c r="W61" s="15">
+        <f>L61/M61</f>
         <v>0.18150013529238926</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
         <v>46259</v>
       </c>
@@ -11258,21 +11722,21 @@
       <c r="J62" s="13">
         <v>0</v>
       </c>
-      <c r="K62" s="18">
+      <c r="K62" s="13">
+        <v>0</v>
+      </c>
+      <c r="L62" s="18">
         <v>54671</v>
       </c>
-      <c r="L62" s="14">
+      <c r="M62" s="14">
         <v>396282.31</v>
       </c>
-      <c r="M62" s="15">
-        <v>0</v>
-      </c>
       <c r="N62" s="15">
+        <v>0</v>
+      </c>
+      <c r="O62" s="15">
         <v>0.86204027123996529</v>
       </c>
-      <c r="O62" s="16">
-        <v>0</v>
-      </c>
       <c r="P62" s="16">
         <v>0</v>
       </c>
@@ -11288,11 +11752,17 @@
       <c r="T62" s="16">
         <v>0</v>
       </c>
-      <c r="U62" s="15">
+      <c r="U62" s="16">
+        <v>0</v>
+      </c>
+      <c r="V62" s="16">
+        <v>0</v>
+      </c>
+      <c r="W62" s="15">
         <v>0.13795972876003473</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>46260</v>
       </c>
@@ -11324,21 +11794,21 @@
       <c r="J63" s="13">
         <v>0</v>
       </c>
-      <c r="K63" s="18">
+      <c r="K63" s="13">
+        <v>0</v>
+      </c>
+      <c r="L63" s="18">
         <v>54671</v>
       </c>
-      <c r="L63" s="14">
+      <c r="M63" s="14">
         <v>395802.31</v>
       </c>
-      <c r="M63" s="15">
-        <v>0</v>
-      </c>
       <c r="N63" s="15">
+        <v>0</v>
+      </c>
+      <c r="O63" s="15">
         <v>0.86187296380357159</v>
       </c>
-      <c r="O63" s="16">
-        <v>0</v>
-      </c>
       <c r="P63" s="16">
         <v>0</v>
       </c>
@@ -11354,11 +11824,17 @@
       <c r="T63" s="16">
         <v>0</v>
       </c>
-      <c r="U63" s="15">
+      <c r="U63" s="16">
+        <v>0</v>
+      </c>
+      <c r="V63" s="16">
+        <v>0</v>
+      </c>
+      <c r="W63" s="15">
         <v>0.13812703619642847</v>
       </c>
     </row>
-    <row r="64" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>46261</v>
       </c>
@@ -11390,21 +11866,21 @@
       <c r="J64" s="13">
         <v>0</v>
       </c>
-      <c r="K64" s="18">
+      <c r="K64" s="13">
+        <v>0</v>
+      </c>
+      <c r="L64" s="18">
         <v>54671</v>
       </c>
-      <c r="L64" s="14">
+      <c r="M64" s="14">
         <v>396617.31</v>
       </c>
-      <c r="M64" s="15">
-        <v>0</v>
-      </c>
       <c r="N64" s="15">
+        <v>0</v>
+      </c>
+      <c r="O64" s="15">
         <v>0.8621567979471193</v>
       </c>
-      <c r="O64" s="16">
-        <v>0</v>
-      </c>
       <c r="P64" s="16">
         <v>0</v>
       </c>
@@ -11420,11 +11896,17 @@
       <c r="T64" s="16">
         <v>0</v>
       </c>
-      <c r="U64" s="15">
+      <c r="U64" s="16">
+        <v>0</v>
+      </c>
+      <c r="V64" s="16">
+        <v>0</v>
+      </c>
+      <c r="W64" s="15">
         <v>0.13784320205288064</v>
       </c>
     </row>
-    <row r="65" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>46262</v>
       </c>
@@ -11456,21 +11938,21 @@
       <c r="J65" s="13">
         <v>0</v>
       </c>
-      <c r="K65" s="18">
+      <c r="K65" s="13">
+        <v>0</v>
+      </c>
+      <c r="L65" s="18">
         <v>54671</v>
       </c>
-      <c r="L65" s="14">
+      <c r="M65" s="14">
         <v>396917.31</v>
       </c>
-      <c r="M65" s="15">
-        <v>0</v>
-      </c>
       <c r="N65" s="15">
+        <v>0</v>
+      </c>
+      <c r="O65" s="15">
         <v>0.86226098327634038</v>
       </c>
-      <c r="O65" s="16">
-        <v>0</v>
-      </c>
       <c r="P65" s="16">
         <v>0</v>
       </c>
@@ -11486,11 +11968,17 @@
       <c r="T65" s="16">
         <v>0</v>
       </c>
-      <c r="U65" s="15">
+      <c r="U65" s="16">
+        <v>0</v>
+      </c>
+      <c r="V65" s="16">
+        <v>0</v>
+      </c>
+      <c r="W65" s="15">
         <v>0.13773901672365965</v>
       </c>
     </row>
-    <row r="66" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>46265</v>
       </c>
@@ -11522,21 +12010,21 @@
       <c r="J66" s="13">
         <v>0</v>
       </c>
-      <c r="K66" s="18">
+      <c r="K66" s="13">
+        <v>0</v>
+      </c>
+      <c r="L66" s="18">
         <v>54671</v>
       </c>
-      <c r="L66" s="14">
+      <c r="M66" s="14">
         <v>399269.72</v>
       </c>
-      <c r="M66" s="15">
+      <c r="N66" s="15">
         <v>0.14977093679931452</v>
       </c>
-      <c r="N66" s="15">
+      <c r="O66" s="15">
         <v>0.71330157468490218</v>
       </c>
-      <c r="O66" s="16">
-        <v>0</v>
-      </c>
       <c r="P66" s="16">
         <v>0</v>
       </c>
@@ -11552,11 +12040,17 @@
       <c r="T66" s="16">
         <v>0</v>
       </c>
-      <c r="U66" s="15">
+      <c r="U66" s="16">
+        <v>0</v>
+      </c>
+      <c r="V66" s="16">
+        <v>0</v>
+      </c>
+      <c r="W66" s="15">
         <v>0.13692748851578326</v>
       </c>
     </row>
-    <row r="67" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>46266</v>
       </c>
@@ -11588,19 +12082,19 @@
       <c r="J67" s="13">
         <v>0</v>
       </c>
-      <c r="K67" s="18">
+      <c r="K67" s="13">
+        <v>0</v>
+      </c>
+      <c r="L67" s="18">
         <v>54671</v>
       </c>
-      <c r="L67" s="14">
+      <c r="M67" s="14">
         <v>926093</v>
       </c>
-      <c r="M67" s="15">
+      <c r="N67" s="15">
         <v>0.94096597209999433</v>
       </c>
-      <c r="N67" s="15">
-        <v>0</v>
-      </c>
-      <c r="O67" s="16">
+      <c r="O67" s="15">
         <v>0</v>
       </c>
       <c r="P67" s="16">
@@ -11618,11 +12112,17 @@
       <c r="T67" s="16">
         <v>0</v>
       </c>
-      <c r="U67" s="15">
+      <c r="U67" s="16">
+        <v>0</v>
+      </c>
+      <c r="V67" s="16">
+        <v>0</v>
+      </c>
+      <c r="W67" s="15">
         <v>5.9034027900005726E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>46267</v>
       </c>
@@ -11654,19 +12154,19 @@
       <c r="J68" s="13">
         <v>0</v>
       </c>
-      <c r="K68" s="18">
+      <c r="K68" s="13">
+        <v>0</v>
+      </c>
+      <c r="L68" s="18">
         <v>54671</v>
       </c>
-      <c r="L68" s="14">
+      <c r="M68" s="14">
         <v>794093</v>
       </c>
-      <c r="M68" s="15">
+      <c r="N68" s="15">
         <v>0.93115290022705144</v>
       </c>
-      <c r="N68" s="15">
-        <v>0</v>
-      </c>
-      <c r="O68" s="16">
+      <c r="O68" s="15">
         <v>0</v>
       </c>
       <c r="P68" s="16">
@@ -11684,11 +12184,17 @@
       <c r="T68" s="16">
         <v>0</v>
       </c>
-      <c r="U68" s="15">
+      <c r="U68" s="16">
+        <v>0</v>
+      </c>
+      <c r="V68" s="16">
+        <v>0</v>
+      </c>
+      <c r="W68" s="15">
         <v>6.8847099772948506E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>46268</v>
       </c>
@@ -11720,22 +12226,22 @@
       <c r="J69" s="13">
         <v>0</v>
       </c>
-      <c r="K69" s="18">
-        <v>0</v>
-      </c>
-      <c r="L69" s="14">
-        <f t="shared" ref="L69:L83" si="0">SUM(C69:K69)</f>
+      <c r="K69" s="13">
+        <v>0</v>
+      </c>
+      <c r="L69" s="18">
+        <v>0</v>
+      </c>
+      <c r="M69" s="14">
+        <f t="shared" ref="M69:M84" si="0">SUM(C69:L69)</f>
         <v>407651</v>
       </c>
-      <c r="M69" s="15">
+      <c r="N69" s="15">
         <v>0.25051515991027662</v>
       </c>
-      <c r="N69" s="15">
+      <c r="O69" s="15">
         <v>0.74948484008972338</v>
       </c>
-      <c r="O69" s="16">
-        <v>0</v>
-      </c>
       <c r="P69" s="16">
         <v>0</v>
       </c>
@@ -11751,11 +12257,17 @@
       <c r="T69" s="16">
         <v>0</v>
       </c>
-      <c r="U69" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U69" s="16">
+        <v>0</v>
+      </c>
+      <c r="V69" s="16">
+        <v>0</v>
+      </c>
+      <c r="W69" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>46269</v>
       </c>
@@ -11787,24 +12299,24 @@
       <c r="J70" s="13">
         <v>0</v>
       </c>
-      <c r="K70" s="18">
-        <v>0</v>
-      </c>
-      <c r="L70" s="14">
+      <c r="K70" s="13">
+        <v>0</v>
+      </c>
+      <c r="L70" s="18">
+        <v>0</v>
+      </c>
+      <c r="M70" s="14">
         <f t="shared" si="0"/>
         <v>408551</v>
       </c>
-      <c r="M70" s="15">
-        <f t="shared" ref="M70:M75" si="1">C70/L70</f>
+      <c r="N70" s="15">
+        <f t="shared" ref="N70:N75" si="1">C70/M70</f>
         <v>0.24736201845057287</v>
       </c>
-      <c r="N70" s="15">
-        <f t="shared" ref="N70:N75" si="2">D70/L70</f>
+      <c r="O70" s="15">
+        <f t="shared" ref="O70:O75" si="2">D70/M70</f>
         <v>0.75263798154942707</v>
       </c>
-      <c r="O70" s="16">
-        <v>0</v>
-      </c>
       <c r="P70" s="16">
         <v>0</v>
       </c>
@@ -11820,11 +12332,17 @@
       <c r="T70" s="16">
         <v>0</v>
       </c>
-      <c r="U70" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U70" s="16">
+        <v>0</v>
+      </c>
+      <c r="V70" s="16">
+        <v>0</v>
+      </c>
+      <c r="W70" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>46272</v>
       </c>
@@ -11856,24 +12374,24 @@
       <c r="J71" s="13">
         <v>0</v>
       </c>
-      <c r="K71" s="18">
-        <v>0</v>
-      </c>
-      <c r="L71" s="14">
+      <c r="K71" s="13">
+        <v>0</v>
+      </c>
+      <c r="L71" s="18">
+        <v>0</v>
+      </c>
+      <c r="M71" s="14">
         <f t="shared" si="0"/>
         <v>408551</v>
       </c>
-      <c r="M71" s="15">
+      <c r="N71" s="15">
         <f t="shared" si="1"/>
         <v>0.24736201845057287</v>
       </c>
-      <c r="N71" s="15">
+      <c r="O71" s="15">
         <f t="shared" si="2"/>
         <v>0.75263798154942707</v>
       </c>
-      <c r="O71" s="16">
-        <v>0</v>
-      </c>
       <c r="P71" s="16">
         <v>0</v>
       </c>
@@ -11889,11 +12407,17 @@
       <c r="T71" s="16">
         <v>0</v>
       </c>
-      <c r="U71" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U71" s="16">
+        <v>0</v>
+      </c>
+      <c r="V71" s="16">
+        <v>0</v>
+      </c>
+      <c r="W71" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>46273</v>
       </c>
@@ -11925,24 +12449,24 @@
       <c r="J72" s="13">
         <v>0</v>
       </c>
-      <c r="K72" s="18">
-        <v>0</v>
-      </c>
-      <c r="L72" s="14">
+      <c r="K72" s="13">
+        <v>0</v>
+      </c>
+      <c r="L72" s="18">
+        <v>0</v>
+      </c>
+      <c r="M72" s="14">
         <f t="shared" si="0"/>
         <v>408551</v>
       </c>
-      <c r="M72" s="15">
+      <c r="N72" s="15">
         <f t="shared" si="1"/>
         <v>0.24736201845057287</v>
       </c>
-      <c r="N72" s="15">
+      <c r="O72" s="15">
         <f t="shared" si="2"/>
         <v>0.75263798154942707</v>
       </c>
-      <c r="O72" s="16">
-        <v>0</v>
-      </c>
       <c r="P72" s="16">
         <v>0</v>
       </c>
@@ -11958,11 +12482,17 @@
       <c r="T72" s="16">
         <v>0</v>
       </c>
-      <c r="U72" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U72" s="16">
+        <v>0</v>
+      </c>
+      <c r="V72" s="16">
+        <v>0</v>
+      </c>
+      <c r="W72" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>46274</v>
       </c>
@@ -11994,24 +12524,24 @@
       <c r="J73" s="13">
         <v>0</v>
       </c>
-      <c r="K73" s="18">
-        <v>0</v>
-      </c>
-      <c r="L73" s="14">
+      <c r="K73" s="13">
+        <v>0</v>
+      </c>
+      <c r="L73" s="18">
+        <v>0</v>
+      </c>
+      <c r="M73" s="14">
         <f t="shared" si="0"/>
         <v>409358</v>
       </c>
-      <c r="M73" s="15">
+      <c r="N73" s="15">
         <f t="shared" si="1"/>
         <v>0.45189296410476892</v>
       </c>
-      <c r="N73" s="15">
+      <c r="O73" s="15">
         <f t="shared" si="2"/>
         <v>0.54810703589523102</v>
       </c>
-      <c r="O73" s="16">
-        <v>0</v>
-      </c>
       <c r="P73" s="16">
         <v>0</v>
       </c>
@@ -12027,11 +12557,17 @@
       <c r="T73" s="16">
         <v>0</v>
       </c>
-      <c r="U73" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U73" s="16">
+        <v>0</v>
+      </c>
+      <c r="V73" s="16">
+        <v>0</v>
+      </c>
+      <c r="W73" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>46275</v>
       </c>
@@ -12062,24 +12598,24 @@
       <c r="J74" s="13">
         <v>0</v>
       </c>
-      <c r="K74" s="18">
+      <c r="K74" s="13">
+        <v>0</v>
+      </c>
+      <c r="L74" s="18">
         <v>120370</v>
       </c>
-      <c r="L74" s="14">
+      <c r="M74" s="14">
         <f t="shared" si="0"/>
         <v>563114</v>
       </c>
-      <c r="M74" s="15">
+      <c r="N74" s="15">
         <f t="shared" si="1"/>
         <v>0.74001534325198803</v>
       </c>
-      <c r="N74" s="15">
+      <c r="O74" s="15">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="O74" s="16">
-        <v>0</v>
-      </c>
       <c r="P74" s="16">
         <v>0</v>
       </c>
@@ -12090,18 +12626,24 @@
         <v>0</v>
       </c>
       <c r="S74" s="16">
-        <f t="shared" ref="S74:S79" si="3">I74/L74</f>
+        <v>0</v>
+      </c>
+      <c r="T74" s="16">
+        <f t="shared" ref="T74:T79" si="3">I74/M74</f>
         <v>4.6226874132058518E-2</v>
       </c>
-      <c r="T74" s="16">
-        <f>K74/L74</f>
+      <c r="U74" s="16">
+        <f>L74/M74</f>
         <v>0.21375778261595343</v>
       </c>
-      <c r="U74" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V74" s="16">
+        <v>0</v>
+      </c>
+      <c r="W74" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>46276</v>
       </c>
@@ -12137,21 +12679,21 @@
       <c r="K75" s="13">
         <v>0</v>
       </c>
-      <c r="L75" s="14">
+      <c r="L75" s="13">
+        <v>0</v>
+      </c>
+      <c r="M75" s="14">
         <f t="shared" si="0"/>
         <v>412405</v>
       </c>
-      <c r="M75" s="15">
+      <c r="N75" s="15">
         <f t="shared" si="1"/>
         <v>0.52517307016161296</v>
       </c>
-      <c r="N75" s="15">
+      <c r="O75" s="15">
         <f t="shared" si="2"/>
         <v>0.41170693856767016</v>
       </c>
-      <c r="O75" s="16">
-        <v>0</v>
-      </c>
       <c r="P75" s="16">
         <v>0</v>
       </c>
@@ -12162,18 +12704,24 @@
         <v>0</v>
       </c>
       <c r="S75" s="16">
+        <v>0</v>
+      </c>
+      <c r="T75" s="16">
         <f t="shared" si="3"/>
         <v>6.3119991270716894E-2</v>
       </c>
-      <c r="T75" s="16">
-        <f>K75/L75</f>
-        <v>0</v>
-      </c>
-      <c r="U75" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U75" s="16">
+        <f>L75/M75</f>
+        <v>0</v>
+      </c>
+      <c r="V75" s="16">
+        <v>0</v>
+      </c>
+      <c r="W75" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>46279</v>
       </c>
@@ -12205,24 +12753,24 @@
       <c r="J76" s="13">
         <v>0</v>
       </c>
-      <c r="K76" s="18">
-        <v>0</v>
-      </c>
-      <c r="L76" s="14">
+      <c r="K76" s="13">
+        <v>0</v>
+      </c>
+      <c r="L76" s="18">
+        <v>0</v>
+      </c>
+      <c r="M76" s="14">
         <f t="shared" si="0"/>
         <v>408536</v>
       </c>
-      <c r="M76" s="15">
-        <f t="shared" ref="M76" si="4">C76/L76</f>
+      <c r="N76" s="15">
+        <f t="shared" ref="N76" si="4">C76/M76</f>
         <v>0.74552793389077099</v>
       </c>
-      <c r="N76" s="15">
-        <f t="shared" ref="N76" si="5">D76/L76</f>
+      <c r="O76" s="15">
+        <f t="shared" ref="O76" si="5">D76/M76</f>
         <v>0.25447206610922907</v>
       </c>
-      <c r="O76" s="16">
-        <v>0</v>
-      </c>
       <c r="P76" s="16">
         <v>0</v>
       </c>
@@ -12233,18 +12781,24 @@
         <v>0</v>
       </c>
       <c r="S76" s="16">
+        <v>0</v>
+      </c>
+      <c r="T76" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T76" s="16">
-        <f>K76/L76</f>
-        <v>0</v>
-      </c>
-      <c r="U76" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U76" s="16">
+        <f>L76/M76</f>
+        <v>0</v>
+      </c>
+      <c r="V76" s="16">
+        <v>0</v>
+      </c>
+      <c r="W76" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>46280</v>
       </c>
@@ -12276,24 +12830,24 @@
       <c r="J77" s="13">
         <v>0</v>
       </c>
-      <c r="K77" s="18">
-        <v>0</v>
-      </c>
-      <c r="L77" s="14">
+      <c r="K77" s="13">
+        <v>0</v>
+      </c>
+      <c r="L77" s="18">
+        <v>0</v>
+      </c>
+      <c r="M77" s="14">
         <f t="shared" si="0"/>
         <v>406109</v>
       </c>
-      <c r="M77" s="15">
-        <f t="shared" ref="M77" si="6">C77/L77</f>
+      <c r="N77" s="15">
+        <f t="shared" ref="N77" si="6">C77/M77</f>
         <v>0.96410569576148275</v>
       </c>
-      <c r="N77" s="15">
-        <f t="shared" ref="N77" si="7">D77/L77</f>
+      <c r="O77" s="15">
+        <f t="shared" ref="O77" si="7">D77/M77</f>
         <v>3.5894304238517243E-2</v>
       </c>
-      <c r="O77" s="16">
-        <v>0</v>
-      </c>
       <c r="P77" s="16">
         <v>0</v>
       </c>
@@ -12304,18 +12858,24 @@
         <v>0</v>
       </c>
       <c r="S77" s="16">
+        <v>0</v>
+      </c>
+      <c r="T77" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T77" s="16">
-        <f>K77/L77</f>
-        <v>0</v>
-      </c>
-      <c r="U77" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="U77" s="16">
+        <f>L77/M77</f>
+        <v>0</v>
+      </c>
+      <c r="V77" s="16">
+        <v>0</v>
+      </c>
+      <c r="W77" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>46281</v>
       </c>
@@ -12327,7 +12887,7 @@
         <v>288016</v>
       </c>
       <c r="D78" s="13">
-        <f>B78-C78-K78</f>
+        <f>B78-C78-L78</f>
         <v>35963</v>
       </c>
       <c r="E78" s="13">
@@ -12348,24 +12908,24 @@
       <c r="J78" s="13">
         <v>0</v>
       </c>
-      <c r="K78" s="18">
+      <c r="K78" s="13">
+        <v>0</v>
+      </c>
+      <c r="L78" s="18">
         <v>88000</v>
       </c>
-      <c r="L78" s="14">
+      <c r="M78" s="14">
         <f t="shared" si="0"/>
         <v>411979</v>
       </c>
-      <c r="M78" s="15">
-        <f t="shared" ref="M78" si="8">C78/L78</f>
+      <c r="N78" s="15">
+        <f t="shared" ref="N78" si="8">C78/M78</f>
         <v>0.69910359508615727</v>
       </c>
-      <c r="N78" s="15">
-        <f t="shared" ref="N78" si="9">D78/L78</f>
+      <c r="O78" s="15">
+        <f t="shared" ref="O78" si="9">D78/M78</f>
         <v>8.7293284366436158E-2</v>
       </c>
-      <c r="O78" s="16">
-        <v>0</v>
-      </c>
       <c r="P78" s="16">
         <v>0</v>
       </c>
@@ -12376,18 +12936,24 @@
         <v>0</v>
       </c>
       <c r="S78" s="16">
+        <v>0</v>
+      </c>
+      <c r="T78" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T78" s="16">
-        <v>0</v>
-      </c>
       <c r="U78" s="16">
-        <f>K78/L78</f>
+        <v>0</v>
+      </c>
+      <c r="V78" s="16">
+        <v>0</v>
+      </c>
+      <c r="W78" s="16">
+        <f t="shared" ref="W78:W83" si="10">L78/M78</f>
         <v>0.21360312054740654</v>
       </c>
     </row>
-    <row r="79" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>46282</v>
       </c>
@@ -12398,7 +12964,7 @@
         <v>235136</v>
       </c>
       <c r="D79" s="13">
-        <f>B79-C79-K79</f>
+        <f>B79-C79-L79</f>
         <v>136527</v>
       </c>
       <c r="E79" s="13">
@@ -12419,24 +12985,24 @@
       <c r="J79" s="13">
         <v>0</v>
       </c>
-      <c r="K79" s="18">
+      <c r="K79" s="13">
+        <v>0</v>
+      </c>
+      <c r="L79" s="18">
         <v>44000</v>
       </c>
-      <c r="L79" s="14">
+      <c r="M79" s="14">
         <f t="shared" si="0"/>
         <v>415663</v>
       </c>
-      <c r="M79" s="15">
-        <f t="shared" ref="M79" si="10">C79/L79</f>
+      <c r="N79" s="15">
+        <f t="shared" ref="N79" si="11">C79/M79</f>
         <v>0.56568903173965446</v>
       </c>
-      <c r="N79" s="15">
-        <f t="shared" ref="N79" si="11">D79/L79</f>
+      <c r="O79" s="15">
+        <f t="shared" ref="O79" si="12">D79/M79</f>
         <v>0.32845598477612875</v>
       </c>
-      <c r="O79" s="16">
-        <v>0</v>
-      </c>
       <c r="P79" s="16">
         <v>0</v>
       </c>
@@ -12447,18 +13013,24 @@
         <v>0</v>
       </c>
       <c r="S79" s="16">
+        <v>0</v>
+      </c>
+      <c r="T79" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T79" s="16">
-        <v>0</v>
-      </c>
       <c r="U79" s="16">
-        <f>K79/L79</f>
+        <v>0</v>
+      </c>
+      <c r="V79" s="16">
+        <v>0</v>
+      </c>
+      <c r="W79" s="16">
+        <f t="shared" si="10"/>
         <v>0.10585498348421678</v>
       </c>
     </row>
-    <row r="80" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>46283</v>
       </c>
@@ -12469,7 +13041,7 @@
         <v>17795</v>
       </c>
       <c r="D80" s="13">
-        <f>B80-C80-K80</f>
+        <f>B80-C80-L80</f>
         <v>352080</v>
       </c>
       <c r="E80" s="13">
@@ -12490,24 +13062,24 @@
       <c r="J80" s="13">
         <v>0</v>
       </c>
-      <c r="K80" s="18">
+      <c r="K80" s="13">
+        <v>0</v>
+      </c>
+      <c r="L80" s="18">
         <v>44000</v>
       </c>
-      <c r="L80" s="14">
+      <c r="M80" s="14">
         <f t="shared" si="0"/>
         <v>413875</v>
       </c>
-      <c r="M80" s="15">
-        <f t="shared" ref="M80" si="12">C80/L80</f>
+      <c r="N80" s="15">
+        <f t="shared" ref="N80" si="13">C80/M80</f>
         <v>4.299607369374811E-2</v>
       </c>
-      <c r="N80" s="15">
-        <f t="shared" ref="N80" si="13">D80/L80</f>
+      <c r="O80" s="15">
+        <f t="shared" ref="O80" si="14">D80/M80</f>
         <v>0.85069163394744796</v>
       </c>
-      <c r="O80" s="16">
-        <v>0</v>
-      </c>
       <c r="P80" s="16">
         <v>0</v>
       </c>
@@ -12518,18 +13090,24 @@
         <v>0</v>
       </c>
       <c r="S80" s="16">
-        <f t="shared" ref="S80" si="14">I80/L80</f>
         <v>0</v>
       </c>
       <c r="T80" s="16">
+        <f t="shared" ref="T80" si="15">I80/M80</f>
         <v>0</v>
       </c>
       <c r="U80" s="16">
-        <f>K80/L80</f>
+        <v>0</v>
+      </c>
+      <c r="V80" s="16">
+        <v>0</v>
+      </c>
+      <c r="W80" s="16">
+        <f t="shared" si="10"/>
         <v>0.10631229235880399</v>
       </c>
     </row>
-    <row r="81" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>46286</v>
       </c>
@@ -12560,22 +13138,22 @@
       <c r="J81" s="13">
         <v>0</v>
       </c>
-      <c r="K81" s="18">
+      <c r="K81" s="13">
+        <v>0</v>
+      </c>
+      <c r="L81" s="18">
         <v>44000</v>
       </c>
-      <c r="L81" s="14">
+      <c r="M81" s="14">
         <f t="shared" si="0"/>
         <v>504892</v>
       </c>
-      <c r="M81" s="15">
-        <f t="shared" ref="M81" si="15">C81/L81</f>
+      <c r="N81" s="15">
+        <f t="shared" ref="N81" si="16">C81/M81</f>
         <v>0.60245359403595222</v>
       </c>
-      <c r="N81" s="15">
-        <f t="shared" ref="N81" si="16">D81/L81</f>
-        <v>0</v>
-      </c>
-      <c r="O81" s="16">
+      <c r="O81" s="15">
+        <f t="shared" ref="O81" si="17">D81/M81</f>
         <v>0</v>
       </c>
       <c r="P81" s="16">
@@ -12588,18 +13166,24 @@
         <v>0</v>
       </c>
       <c r="S81" s="16">
-        <f t="shared" ref="S81" si="17">I81/L81</f>
+        <v>0</v>
+      </c>
+      <c r="T81" s="16">
+        <f t="shared" ref="T81" si="18">I81/M81</f>
         <v>0.31039905563962195</v>
       </c>
-      <c r="T81" s="16">
-        <v>0</v>
-      </c>
       <c r="U81" s="16">
-        <f>K81/L81</f>
+        <v>0</v>
+      </c>
+      <c r="V81" s="16">
+        <v>0</v>
+      </c>
+      <c r="W81" s="16">
+        <f t="shared" si="10"/>
         <v>8.7147350324425818E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>46287</v>
       </c>
@@ -12610,7 +13194,7 @@
         <v>292095</v>
       </c>
       <c r="D82" s="13">
-        <f>B82-C82-K82</f>
+        <f>B82-C82-L82</f>
         <v>82294</v>
       </c>
       <c r="E82" s="13">
@@ -12631,24 +13215,24 @@
       <c r="J82" s="13">
         <v>0</v>
       </c>
-      <c r="K82" s="18">
+      <c r="K82" s="13">
+        <v>0</v>
+      </c>
+      <c r="L82" s="18">
         <v>44000</v>
       </c>
-      <c r="L82" s="14">
+      <c r="M82" s="14">
         <f t="shared" si="0"/>
         <v>418389</v>
       </c>
-      <c r="M82" s="15">
-        <f t="shared" ref="M82:M83" si="18">C82/L82</f>
+      <c r="N82" s="15">
+        <f t="shared" ref="N82:N83" si="19">C82/M82</f>
         <v>0.69814215956920478</v>
       </c>
-      <c r="N82" s="15">
-        <f t="shared" ref="N82:N83" si="19">D82/L82</f>
+      <c r="O82" s="15">
+        <f t="shared" ref="O82:O83" si="20">D82/M82</f>
         <v>0.19669255166842339</v>
       </c>
-      <c r="O82" s="16">
-        <v>0</v>
-      </c>
       <c r="P82" s="16">
         <v>0</v>
       </c>
@@ -12659,18 +13243,24 @@
         <v>0</v>
       </c>
       <c r="S82" s="16">
-        <f t="shared" ref="S82:S83" si="20">I82/L82</f>
         <v>0</v>
       </c>
       <c r="T82" s="16">
+        <f t="shared" ref="T82:T83" si="21">I82/M82</f>
         <v>0</v>
       </c>
       <c r="U82" s="16">
-        <f>K82/L82</f>
+        <v>0</v>
+      </c>
+      <c r="V82" s="16">
+        <v>0</v>
+      </c>
+      <c r="W82" s="16">
+        <f t="shared" si="10"/>
         <v>0.10516528876237186</v>
       </c>
     </row>
-    <row r="83" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>46288</v>
       </c>
@@ -12702,24 +13292,24 @@
       <c r="J83" s="13">
         <v>0</v>
       </c>
-      <c r="K83" s="18">
-        <v>0</v>
-      </c>
-      <c r="L83" s="14">
+      <c r="K83" s="13">
+        <v>0</v>
+      </c>
+      <c r="L83" s="18">
+        <v>0</v>
+      </c>
+      <c r="M83" s="14">
         <f t="shared" si="0"/>
         <v>415890</v>
       </c>
-      <c r="M83" s="15">
-        <f t="shared" si="18"/>
-        <v>0.13702421313328045</v>
-      </c>
       <c r="N83" s="15">
         <f t="shared" si="19"/>
+        <v>0.13702421313328045</v>
+      </c>
+      <c r="O83" s="15">
+        <f t="shared" si="20"/>
         <v>0.77713578109596293</v>
       </c>
-      <c r="O83" s="15">
-        <v>0</v>
-      </c>
       <c r="P83" s="15">
         <v>0</v>
       </c>
@@ -12727,18 +13317,103 @@
         <v>0</v>
       </c>
       <c r="R83" s="15">
-        <f>H83/L83</f>
+        <v>0</v>
+      </c>
+      <c r="S83" s="15">
+        <f>H83/M83</f>
         <v>8.5840005770756692E-2</v>
       </c>
-      <c r="S83" s="15">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
       <c r="T83" s="15">
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
       <c r="U83" s="15">
-        <f>K83/L83</f>
+        <v>0</v>
+      </c>
+      <c r="V83" s="16">
+        <v>0</v>
+      </c>
+      <c r="W83" s="15">
+        <f t="shared" si="10"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A84" s="10">
+        <v>46289</v>
+      </c>
+      <c r="B84" s="11">
+        <v>416077</v>
+      </c>
+      <c r="C84" s="19">
+        <v>72287</v>
+      </c>
+      <c r="D84" s="13">
+        <f>B84-C84-H84-K84</f>
+        <v>291870</v>
+      </c>
+      <c r="E84" s="13">
+        <v>0</v>
+      </c>
+      <c r="F84" s="13">
+        <v>0</v>
+      </c>
+      <c r="G84" s="13">
+        <v>0</v>
+      </c>
+      <c r="H84" s="13">
+        <v>35700</v>
+      </c>
+      <c r="I84" s="13">
+        <v>0</v>
+      </c>
+      <c r="J84" s="13">
+        <v>0</v>
+      </c>
+      <c r="K84" s="13">
+        <v>16220</v>
+      </c>
+      <c r="L84" s="18">
+        <v>0</v>
+      </c>
+      <c r="M84" s="14">
+        <f t="shared" si="0"/>
+        <v>416077</v>
+      </c>
+      <c r="N84" s="15">
+        <f t="shared" ref="N84" si="22">C84/M84</f>
+        <v>0.17373466930399903</v>
+      </c>
+      <c r="O84" s="15">
+        <f t="shared" ref="O84" si="23">D84/M84</f>
+        <v>0.70148073553693191</v>
+      </c>
+      <c r="P84" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q84" s="15">
+        <v>0</v>
+      </c>
+      <c r="R84" s="15">
+        <v>0</v>
+      </c>
+      <c r="S84" s="15">
+        <f>H84/M84</f>
+        <v>8.5801426178327575E-2</v>
+      </c>
+      <c r="T84" s="15">
+        <f t="shared" ref="T84" si="24">I84/M84</f>
+        <v>0</v>
+      </c>
+      <c r="U84" s="15">
+        <v>0</v>
+      </c>
+      <c r="V84" s="16">
+        <f>K84/M84</f>
+        <v>3.8983168980741542E-2</v>
+      </c>
+      <c r="W84" s="15">
+        <f t="shared" ref="W84" si="25">L84/M84</f>
         <v>0</v>
       </c>
     </row>
@@ -12746,7 +13421,7 @@
       <c r="A1048543" s="10"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="M2:U1048576">
+  <conditionalFormatting sqref="N2:W1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B51EB213-2CB0-5149-A016-1C6E89C1213F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97D62673-B86E-4D4E-B910-41A6DC0A101C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5360" yWindow="-37100" windowWidth="46400" windowHeight="21940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="872" uniqueCount="613">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="615">
   <si>
     <t>Trade ID</t>
   </si>
@@ -1903,6 +1903,12 @@
   </si>
   <si>
     <t>Energy_Exposure</t>
+  </si>
+  <si>
+    <t>DDOG</t>
+  </si>
+  <si>
+    <t>Datadog</t>
   </si>
 </sst>
 </file>
@@ -2531,7 +2537,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V60"/>
+  <dimension ref="A1:V61"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.1640625" style="33" bestFit="1" customWidth="1"/>
@@ -4246,7 +4252,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D49" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D50" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
@@ -5443,7 +5449,7 @@
         <v>72</v>
       </c>
       <c r="V43" s="33">
-        <v>327</v>
+        <v>431</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
@@ -5716,7 +5722,7 @@
         <v>72</v>
       </c>
       <c r="V47" s="33">
-        <v>-605</v>
+        <v>686</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
@@ -5786,7 +5792,7 @@
         <v>72</v>
       </c>
       <c r="V48" s="33">
-        <v>271</v>
+        <v>-9</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -5796,144 +5802,209 @@
       <c r="B49" s="34">
         <v>46289</v>
       </c>
-      <c r="C49" s="55">
+      <c r="C49" s="34">
         <v>46290</v>
       </c>
       <c r="D49" s="35">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="E49" s="47" t="s">
+      <c r="E49" s="33" t="s">
         <v>609</v>
       </c>
-      <c r="F49" s="48" t="s">
+      <c r="F49" s="36" t="s">
         <v>610</v>
       </c>
-      <c r="G49" s="47" t="s">
+      <c r="G49" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H49" s="48" t="s">
+      <c r="H49" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I49" s="47" t="s">
+      <c r="I49" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="J49" s="47" t="s">
+      <c r="J49" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="K49" s="47" t="s">
+      <c r="K49" s="33" t="s">
         <v>611</v>
       </c>
-      <c r="L49" s="47">
+      <c r="L49" s="33">
         <v>-2</v>
       </c>
-      <c r="M49" s="47">
+      <c r="M49" s="33">
         <v>3.327</v>
       </c>
-      <c r="N49" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O49" s="47">
-        <v>3.24</v>
-      </c>
-      <c r="P49" s="49">
+      <c r="N49" s="33">
+        <v>3.26</v>
+      </c>
+      <c r="O49" s="33">
+        <v>3.26</v>
+      </c>
+      <c r="P49" s="39">
         <v>16220</v>
       </c>
-      <c r="Q49" s="47">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="R49" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S49" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T49" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="U49" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V49" s="33">
-        <v>590</v>
+      <c r="Q49" s="33">
+        <v>5.44</v>
+      </c>
+      <c r="R49" s="33">
+        <v>1</v>
+      </c>
+      <c r="S49" s="40">
+        <f t="shared" ref="S49:S50" si="9">IF(R49=1, ABS(N49-M49)/M49, 0)</f>
+        <v>2.0138262699128395E-2</v>
+      </c>
+      <c r="T49" s="33">
+        <v>338</v>
+      </c>
+      <c r="U49" s="41">
+        <v>338</v>
       </c>
     </row>
     <row r="50" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F50" s="36"/>
-      <c r="H50" s="36"/>
+      <c r="A50" s="33">
+        <v>45</v>
+      </c>
+      <c r="B50" s="34">
+        <v>46290</v>
+      </c>
+      <c r="C50" s="34">
+        <v>46290</v>
+      </c>
+      <c r="D50" s="35">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E50" s="33" t="s">
+        <v>613</v>
+      </c>
+      <c r="F50" s="36" t="s">
+        <v>614</v>
+      </c>
+      <c r="G50" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H50" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="I50" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="J50" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="K50" s="33" t="s">
+        <v>613</v>
+      </c>
+      <c r="L50" s="33">
+        <v>-750</v>
+      </c>
+      <c r="M50" s="33">
+        <v>274.52</v>
+      </c>
+      <c r="N50" s="33">
+        <v>271.52999999999997</v>
+      </c>
+      <c r="O50" s="33">
+        <v>271.52999999999997</v>
+      </c>
+      <c r="P50" s="39">
+        <v>205889</v>
+      </c>
+      <c r="Q50" s="33">
+        <v>10.91</v>
+      </c>
+      <c r="R50" s="33">
+        <v>1</v>
+      </c>
+      <c r="S50" s="40">
+        <f t="shared" si="9"/>
+        <v>1.0891738306862922E-2</v>
+      </c>
+      <c r="T50" s="33">
+        <v>2245</v>
+      </c>
+      <c r="U50" s="41">
+        <v>2245</v>
+      </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D51" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="E51" s="46">
-        <f>AVERAGE(D2:D38)</f>
-        <v>7.8648648648648649</v>
-      </c>
       <c r="F51" s="36"/>
       <c r="H51" s="36"/>
-      <c r="U51" s="39">
-        <f>SUM(U2:U49)</f>
-        <v>79456.47</v>
-      </c>
-      <c r="V51" s="39">
-        <f>SUM(V2:V49)</f>
-        <v>583</v>
-      </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
       <c r="D52" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="E52" s="46">
+        <f>AVERAGE(D2:D50)</f>
+        <v>6.5102040816326534</v>
+      </c>
+      <c r="F52" s="36"/>
+      <c r="H52" s="36"/>
+      <c r="U52" s="39">
+        <f>SUM(U2:U50)</f>
+        <v>82039.47</v>
+      </c>
+      <c r="V52" s="39">
+        <f>SUM(V2:V49)</f>
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D53" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="E52" s="46">
-        <f>AVERAGE(D2:D11,D13,D15:D38)</f>
-        <v>5</v>
-      </c>
-      <c r="F52" s="36"/>
-      <c r="U52" s="53" t="s">
+      <c r="E53" s="46">
+        <f>AVERAGE(D2:D11,D13,D15:D50)</f>
+        <v>4.3191489361702127</v>
+      </c>
+      <c r="F53" s="36"/>
+      <c r="U53" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="V52" s="36" t="s">
+      <c r="V53" s="36" t="s">
         <v>106</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F53" s="36"/>
-      <c r="U53" s="33" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F54" s="36"/>
-      <c r="U54" s="39">
-        <f>U51+V51</f>
-        <v>80039.47</v>
+      <c r="U54" s="33" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F55" s="36"/>
+      <c r="U55" s="39">
+        <f>U52+V52</f>
+        <v>83147.47</v>
+      </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F56" s="36"/>
-      <c r="U56" s="36" t="s">
-        <v>108</v>
-      </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F57" s="36"/>
-      <c r="U57" s="39">
+      <c r="U57" s="36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F58" s="36"/>
+      <c r="U58" s="39">
         <v>333000</v>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="U59" s="33" t="s">
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U60" s="33" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="U60" s="54">
-        <f>U54/U57</f>
-        <v>0.24035876876876877</v>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U61" s="54">
+        <f>U55/U58</f>
+        <v>0.2496921021021021</v>
       </c>
     </row>
   </sheetData>
@@ -5946,7 +6017,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -6012,11 +6083,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C77" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C78" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D77" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D78" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -7039,8 +7110,8 @@
         <v>114</v>
       </c>
       <c r="G65" s="27">
-        <f>AVERAGE(C3:C77)</f>
-        <v>1101.6145333333329</v>
+        <f>AVERAGE(C3:C78)</f>
+        <v>1132.9617105263153</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
@@ -7063,8 +7134,8 @@
         <v>115</v>
       </c>
       <c r="G66" s="27">
-        <f>_xlfn.STDEV.S(C3:C77)</f>
-        <v>4216.5641012521528</v>
+        <f>_xlfn.STDEV.S(C3:C78)</f>
+        <v>4197.2651860151009</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
@@ -7088,7 +7159,7 @@
       </c>
       <c r="G67" s="28">
         <f>(G65/G66)*SQRT(252)</f>
-        <v>4.1473550870325235</v>
+        <v>4.2849829088690736</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
@@ -7111,8 +7182,8 @@
         <v>117</v>
       </c>
       <c r="G68" s="29">
-        <f>_xlfn.STDEV.S(D2:D77)*SQRT(252)</f>
-        <v>0.18224106616972091</v>
+        <f>_xlfn.STDEV.S(D2:D78)*SQRT(252)</f>
+        <v>0.18130074935190868</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
@@ -7135,8 +7206,8 @@
         <v>118</v>
       </c>
       <c r="G69" s="29" cm="1">
-        <f t="array" ref="G69">PRODUCT(1+D2:D77)-1</f>
-        <v>0.24777234932894765</v>
+        <f t="array" ref="G69">PRODUCT(1+D2:D78)-1</f>
+        <v>0.25822050884043724</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
@@ -7159,8 +7230,8 @@
         <v>119</v>
       </c>
       <c r="G70" s="29" cm="1">
-        <f t="array" ref="G70">PRODUCT(1+D2:D77)^(252/COUNT(D2:D77))-1</f>
-        <v>1.083361365418201</v>
+        <f t="array" ref="G70">PRODUCT(1+D2:D78)^(252/COUNT(D2:D78))-1</f>
+        <v>1.120687461383878</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
@@ -7280,6 +7351,23 @@
       <c r="D77" s="23">
         <f t="shared" si="1"/>
         <v>4.4963812546586836E-4</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A78" s="26">
+        <v>46290</v>
+      </c>
+      <c r="B78" s="5">
+        <f>B77+1206+104+2234+547-607</f>
+        <v>419561</v>
+      </c>
+      <c r="C78" s="5">
+        <f t="shared" si="0"/>
+        <v>3484</v>
+      </c>
+      <c r="D78" s="23">
+        <f t="shared" si="1"/>
+        <v>8.3734501065908466E-3</v>
       </c>
     </row>
   </sheetData>
@@ -12233,7 +12321,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="14">
-        <f t="shared" ref="M69:M84" si="0">SUM(C69:L69)</f>
+        <f t="shared" ref="M69:M85" si="0">SUM(C69:L69)</f>
         <v>407651</v>
       </c>
       <c r="N69" s="15">
@@ -13414,6 +13502,85 @@
       </c>
       <c r="W84" s="15">
         <f t="shared" ref="W84" si="25">L84/M84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A85" s="10">
+        <v>46290</v>
+      </c>
+      <c r="B85" s="11">
+        <v>419561</v>
+      </c>
+      <c r="C85" s="19">
+        <v>72287</v>
+      </c>
+      <c r="D85" s="13">
+        <f>B85-C85-H85-K85</f>
+        <v>311574</v>
+      </c>
+      <c r="E85" s="13">
+        <v>0</v>
+      </c>
+      <c r="F85" s="13">
+        <v>0</v>
+      </c>
+      <c r="G85" s="13">
+        <v>0</v>
+      </c>
+      <c r="H85" s="13">
+        <v>35700</v>
+      </c>
+      <c r="I85" s="13">
+        <v>0</v>
+      </c>
+      <c r="J85" s="13">
+        <v>0</v>
+      </c>
+      <c r="K85" s="13">
+        <v>0</v>
+      </c>
+      <c r="L85" s="18">
+        <v>0</v>
+      </c>
+      <c r="M85" s="14">
+        <f t="shared" si="0"/>
+        <v>419561</v>
+      </c>
+      <c r="N85" s="15">
+        <f t="shared" ref="N85" si="26">C85/M85</f>
+        <v>0.17229199091431283</v>
+      </c>
+      <c r="O85" s="15">
+        <f t="shared" ref="O85" si="27">D85/M85</f>
+        <v>0.74261907088599755</v>
+      </c>
+      <c r="P85" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q85" s="15">
+        <v>0</v>
+      </c>
+      <c r="R85" s="15">
+        <v>0</v>
+      </c>
+      <c r="S85" s="15">
+        <f>H85/M85</f>
+        <v>8.508893819968967E-2</v>
+      </c>
+      <c r="T85" s="15">
+        <f t="shared" ref="T85" si="28">I85/M85</f>
+        <v>0</v>
+      </c>
+      <c r="U85" s="15">
+        <v>0</v>
+      </c>
+      <c r="V85" s="16">
+        <f>K85/M85</f>
+        <v>0</v>
+      </c>
+      <c r="W85" s="15">
+        <f t="shared" ref="W85" si="29">L85/M85</f>
         <v>0</v>
       </c>
     </row>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97D62673-B86E-4D4E-B910-41A6DC0A101C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FB0B704-A772-BC4A-B670-59423321B624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="20740" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="23940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="874" uniqueCount="615">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="635">
   <si>
     <t>Trade ID</t>
   </si>
@@ -1909,6 +1909,66 @@
   </si>
   <si>
     <t>Datadog</t>
+  </si>
+  <si>
+    <t>LCII</t>
+  </si>
+  <si>
+    <t>LCI Industries</t>
+  </si>
+  <si>
+    <t>TIP</t>
+  </si>
+  <si>
+    <t>iShares TIPS Bond ETF</t>
+  </si>
+  <si>
+    <t>TSM</t>
+  </si>
+  <si>
+    <t>Taiwan Semiconductor</t>
+  </si>
+  <si>
+    <t>ACAD</t>
+  </si>
+  <si>
+    <t>Acadia Pharmaceuticals</t>
+  </si>
+  <si>
+    <t>FDX</t>
+  </si>
+  <si>
+    <t>Fedex</t>
+  </si>
+  <si>
+    <t>Pairs Trading</t>
+  </si>
+  <si>
+    <t>UPS</t>
+  </si>
+  <si>
+    <t>United Parcel Service</t>
+  </si>
+  <si>
+    <t>IWM</t>
+  </si>
+  <si>
+    <t>iShares Russell 2000 ETF</t>
+  </si>
+  <si>
+    <t>Long Small Cap vs Broad Mkt</t>
+  </si>
+  <si>
+    <t>SPY</t>
+  </si>
+  <si>
+    <t>S&amp;P500 ETF</t>
+  </si>
+  <si>
+    <t>VMBS</t>
+  </si>
+  <si>
+    <t>Vanguard Mortgage Backed Securities ETF</t>
   </si>
 </sst>
 </file>
@@ -2537,7 +2597,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V61"/>
+  <dimension ref="A1:V71"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.1640625" style="33" bestFit="1" customWidth="1"/>
@@ -4252,7 +4312,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D50" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D53" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
@@ -5390,11 +5450,11 @@
         <v>46286</v>
       </c>
       <c r="C43" s="55">
-        <v>46290</v>
+        <v>46294</v>
       </c>
       <c r="D43" s="35">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E43" s="47" t="s">
         <v>599</v>
@@ -5427,7 +5487,7 @@
         <v>72</v>
       </c>
       <c r="O43" s="47">
-        <v>154.66</v>
+        <v>154.4</v>
       </c>
       <c r="P43" s="49">
         <f>ABS(M43*L43)</f>
@@ -5449,7 +5509,7 @@
         <v>72</v>
       </c>
       <c r="V43" s="33">
-        <v>431</v>
+        <v>363</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
@@ -5663,11 +5723,11 @@
         <v>46288</v>
       </c>
       <c r="C47" s="55">
-        <v>46290</v>
+        <v>46294</v>
       </c>
       <c r="D47" s="35">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E47" s="47" t="s">
         <v>606</v>
@@ -5700,7 +5760,7 @@
         <v>72</v>
       </c>
       <c r="O47" s="47">
-        <v>258.86</v>
+        <v>262.75</v>
       </c>
       <c r="P47" s="49">
         <f>ABS(M47*L47)</f>
@@ -5722,7 +5782,7 @@
         <v>72</v>
       </c>
       <c r="V47" s="33">
-        <v>686</v>
+        <v>-988</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
@@ -5733,11 +5793,11 @@
         <v>46288</v>
       </c>
       <c r="C48" s="55">
-        <v>46290</v>
+        <v>46294</v>
       </c>
       <c r="D48" s="35">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E48" s="47" t="s">
         <v>58</v>
@@ -5761,20 +5821,20 @@
         <v>608</v>
       </c>
       <c r="L48" s="47">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="M48" s="47">
-        <v>17.555</v>
+        <v>17.652000000000001</v>
       </c>
       <c r="N48" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O48" s="47">
-        <v>17.7</v>
+        <v>17.649999999999999</v>
       </c>
       <c r="P48" s="49">
         <f>ABS(M48*L48)*100</f>
-        <v>35110</v>
+        <v>52956.000000000007</v>
       </c>
       <c r="Q48" s="47">
         <v>9.1999999999999993</v>
@@ -5792,7 +5852,7 @@
         <v>72</v>
       </c>
       <c r="V48" s="33">
-        <v>-9</v>
+        <v>26</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -5930,81 +5990,715 @@
       </c>
     </row>
     <row r="51" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F51" s="36"/>
-      <c r="H51" s="36"/>
+      <c r="A51" s="33">
+        <v>46</v>
+      </c>
+      <c r="B51" s="34">
+        <v>46293</v>
+      </c>
+      <c r="C51" s="55">
+        <v>46294</v>
+      </c>
+      <c r="D51" s="35">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="E51" s="47" t="s">
+        <v>615</v>
+      </c>
+      <c r="F51" s="48" t="s">
+        <v>616</v>
+      </c>
+      <c r="G51" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H51" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I51" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J51" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K51" s="47" t="s">
+        <v>615</v>
+      </c>
+      <c r="L51" s="47">
+        <v>600</v>
+      </c>
+      <c r="M51" s="47">
+        <v>84.65</v>
+      </c>
+      <c r="N51" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O51" s="47">
+        <v>85.39</v>
+      </c>
+      <c r="P51" s="49">
+        <f>ABS(M51*L51)</f>
+        <v>50790</v>
+      </c>
+      <c r="Q51" s="47">
+        <v>2.44</v>
+      </c>
+      <c r="R51" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S51" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T51" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U51" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V51" s="33">
+        <v>438</v>
+      </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D52" s="52" t="s">
+      <c r="A52" s="33">
+        <v>47</v>
+      </c>
+      <c r="B52" s="34">
+        <v>46293</v>
+      </c>
+      <c r="C52" s="55">
+        <v>46294</v>
+      </c>
+      <c r="D52" s="35">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="E52" s="47" t="s">
+        <v>617</v>
+      </c>
+      <c r="F52" s="48" t="s">
+        <v>618</v>
+      </c>
+      <c r="G52" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H52" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I52" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="J52" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="K52" s="47" t="s">
+        <v>617</v>
+      </c>
+      <c r="L52" s="47">
+        <v>400</v>
+      </c>
+      <c r="M52" s="47">
+        <v>104.14</v>
+      </c>
+      <c r="N52" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O52" s="47">
+        <v>104.02</v>
+      </c>
+      <c r="P52" s="49">
+        <f>ABS(M52*L52)</f>
+        <v>41656</v>
+      </c>
+      <c r="Q52" s="47">
+        <v>1.56</v>
+      </c>
+      <c r="R52" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S52" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T52" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U52" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V52" s="33">
+        <v>-44</v>
+      </c>
+    </row>
+    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A53" s="33">
+        <v>48</v>
+      </c>
+      <c r="B53" s="34">
+        <v>46293</v>
+      </c>
+      <c r="C53" s="55">
+        <v>46294</v>
+      </c>
+      <c r="D53" s="35">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="E53" s="47" t="s">
+        <v>619</v>
+      </c>
+      <c r="F53" s="48" t="s">
+        <v>620</v>
+      </c>
+      <c r="G53" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H53" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I53" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J53" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K53" s="47" t="s">
+        <v>619</v>
+      </c>
+      <c r="L53" s="47">
+        <v>-100</v>
+      </c>
+      <c r="M53" s="47">
+        <v>446.67</v>
+      </c>
+      <c r="N53" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O53" s="47">
+        <v>457.08</v>
+      </c>
+      <c r="P53" s="49">
+        <f>ABS(M53*L53)</f>
+        <v>44667</v>
+      </c>
+      <c r="Q53" s="47">
+        <v>2.33</v>
+      </c>
+      <c r="R53" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S53" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T53" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U53" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V53" s="33">
+        <v>-933</v>
+      </c>
+    </row>
+    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A54" s="33">
+        <v>49</v>
+      </c>
+      <c r="B54" s="34">
+        <v>46293</v>
+      </c>
+      <c r="C54" s="55">
+        <v>46294</v>
+      </c>
+      <c r="D54" s="35">
+        <v>0</v>
+      </c>
+      <c r="E54" s="47" t="s">
+        <v>621</v>
+      </c>
+      <c r="F54" s="48" t="s">
+        <v>622</v>
+      </c>
+      <c r="G54" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H54" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I54" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J54" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K54" s="47" t="s">
+        <v>621</v>
+      </c>
+      <c r="L54" s="47">
+        <v>4000</v>
+      </c>
+      <c r="M54" s="47">
+        <v>20.27</v>
+      </c>
+      <c r="N54" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O54" s="47">
+        <v>20.21</v>
+      </c>
+      <c r="P54" s="49">
+        <f>ABS(M54*L54)</f>
+        <v>81080</v>
+      </c>
+      <c r="Q54" s="47">
+        <v>5.4</v>
+      </c>
+      <c r="R54" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S54" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T54" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U54" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V54" s="33">
+        <v>-198</v>
+      </c>
+    </row>
+    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A55" s="33">
+        <v>50</v>
+      </c>
+      <c r="B55" s="34">
+        <v>46293</v>
+      </c>
+      <c r="C55" s="55">
+        <v>46294</v>
+      </c>
+      <c r="D55" s="35">
+        <v>0</v>
+      </c>
+      <c r="E55" s="47" t="s">
+        <v>623</v>
+      </c>
+      <c r="F55" s="48" t="s">
+        <v>624</v>
+      </c>
+      <c r="G55" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="H55" s="48" t="s">
+        <v>625</v>
+      </c>
+      <c r="I55" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J55" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K55" s="47" t="s">
+        <v>623</v>
+      </c>
+      <c r="L55" s="47">
+        <v>175</v>
+      </c>
+      <c r="M55" s="47">
+        <v>287.99</v>
+      </c>
+      <c r="N55" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O55" s="47">
+        <v>287.52</v>
+      </c>
+      <c r="P55" s="49">
+        <f>ABS(M55*L55)</f>
+        <v>50398.25</v>
+      </c>
+      <c r="Q55" s="47">
+        <v>1.49</v>
+      </c>
+      <c r="R55" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S55" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T55" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U55" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V55" s="33">
+        <v>-92</v>
+      </c>
+    </row>
+    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A56" s="33">
+        <v>51</v>
+      </c>
+      <c r="B56" s="34">
+        <v>46293</v>
+      </c>
+      <c r="C56" s="55">
+        <v>46294</v>
+      </c>
+      <c r="D56" s="35">
+        <v>0</v>
+      </c>
+      <c r="E56" s="47" t="s">
+        <v>626</v>
+      </c>
+      <c r="F56" s="48" t="s">
+        <v>627</v>
+      </c>
+      <c r="G56" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="H56" s="48" t="s">
+        <v>625</v>
+      </c>
+      <c r="I56" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J56" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K56" s="47" t="s">
+        <v>626</v>
+      </c>
+      <c r="L56" s="47">
+        <v>-520</v>
+      </c>
+      <c r="M56" s="47">
+        <v>93.92</v>
+      </c>
+      <c r="N56" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O56" s="47">
+        <v>93.94</v>
+      </c>
+      <c r="P56" s="49">
+        <f>ABS(M56*L56)</f>
+        <v>48838.400000000001</v>
+      </c>
+      <c r="Q56" s="47">
+        <v>1.55</v>
+      </c>
+      <c r="R56" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S56" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T56" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U56" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V56" s="33">
+        <v>-5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A57" s="33">
+        <v>52</v>
+      </c>
+      <c r="B57" s="34">
+        <v>46294</v>
+      </c>
+      <c r="C57" s="55">
+        <v>46294</v>
+      </c>
+      <c r="D57" s="35">
+        <v>0</v>
+      </c>
+      <c r="E57" s="47" t="s">
+        <v>628</v>
+      </c>
+      <c r="F57" s="48" t="s">
+        <v>629</v>
+      </c>
+      <c r="G57" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="H57" s="48" t="s">
+        <v>630</v>
+      </c>
+      <c r="I57" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="J57" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="K57" s="47" t="s">
+        <v>628</v>
+      </c>
+      <c r="L57" s="47">
+        <v>200</v>
+      </c>
+      <c r="M57" s="47">
+        <v>280.43</v>
+      </c>
+      <c r="N57" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O57" s="47">
+        <v>279.16000000000003</v>
+      </c>
+      <c r="P57" s="49">
+        <f>ABS(M57*L57)</f>
+        <v>56086</v>
+      </c>
+      <c r="Q57" s="47">
+        <v>3.11</v>
+      </c>
+      <c r="R57" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S57" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T57" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U57" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V57" s="33">
+        <v>-265</v>
+      </c>
+    </row>
+    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A58" s="33">
+        <v>53</v>
+      </c>
+      <c r="B58" s="34">
+        <v>46294</v>
+      </c>
+      <c r="C58" s="55">
+        <v>46294</v>
+      </c>
+      <c r="D58" s="35">
+        <v>0</v>
+      </c>
+      <c r="E58" s="47" t="s">
+        <v>631</v>
+      </c>
+      <c r="F58" s="48" t="s">
+        <v>632</v>
+      </c>
+      <c r="G58" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="H58" s="48" t="s">
+        <v>630</v>
+      </c>
+      <c r="I58" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="J58" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="K58" s="47" t="s">
+        <v>631</v>
+      </c>
+      <c r="L58" s="47">
+        <v>-70</v>
+      </c>
+      <c r="M58" s="47">
+        <v>765.18</v>
+      </c>
+      <c r="N58" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O58" s="47">
+        <v>764.59</v>
+      </c>
+      <c r="P58" s="49">
+        <f>ABS(M58*L58)</f>
+        <v>53562.6</v>
+      </c>
+      <c r="Q58" s="47">
+        <v>3.11</v>
+      </c>
+      <c r="R58" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S58" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T58" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U58" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V58" s="33">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A59" s="33">
+        <v>43</v>
+      </c>
+      <c r="B59" s="34">
+        <v>46294</v>
+      </c>
+      <c r="C59" s="55">
+        <v>46294</v>
+      </c>
+      <c r="D59" s="35">
+        <v>0</v>
+      </c>
+      <c r="E59" s="47" t="s">
+        <v>633</v>
+      </c>
+      <c r="F59" s="48" t="s">
+        <v>634</v>
+      </c>
+      <c r="G59" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H59" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I59" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="J59" s="47" t="s">
+        <v>48</v>
+      </c>
+      <c r="K59" s="47" t="s">
+        <v>633</v>
+      </c>
+      <c r="L59" s="47">
+        <v>1300</v>
+      </c>
+      <c r="M59" s="47">
+        <v>44.37</v>
+      </c>
+      <c r="N59" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O59" s="47">
+        <v>44.45</v>
+      </c>
+      <c r="P59" s="49">
+        <f>ABS(M59*L59)</f>
+        <v>57681</v>
+      </c>
+      <c r="Q59" s="47">
+        <v>3.11</v>
+      </c>
+      <c r="R59" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S59" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T59" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U59" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V59" s="33">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B60" s="34"/>
+      <c r="C60" s="34"/>
+      <c r="D60" s="35"/>
+      <c r="F60" s="36"/>
+      <c r="H60" s="36"/>
+      <c r="P60" s="39"/>
+      <c r="S60" s="40"/>
+      <c r="U60" s="41"/>
+    </row>
+    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F61" s="36"/>
+      <c r="H61" s="36"/>
+    </row>
+    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D62" s="52" t="s">
         <v>103</v>
       </c>
-      <c r="E52" s="46">
+      <c r="E62" s="46">
         <f>AVERAGE(D2:D50)</f>
-        <v>6.5102040816326534</v>
-      </c>
-      <c r="F52" s="36"/>
-      <c r="H52" s="36"/>
-      <c r="U52" s="39">
+        <v>6.7551020408163263</v>
+      </c>
+      <c r="F62" s="36"/>
+      <c r="H62" s="36"/>
+      <c r="U62" s="39">
         <f>SUM(U2:U50)</f>
         <v>82039.47</v>
       </c>
-      <c r="V52" s="39">
-        <f>SUM(V2:V49)</f>
-        <v>1108</v>
-      </c>
-    </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D53" s="52" t="s">
+      <c r="V62" s="39">
+        <f>SUM(V2:V59)</f>
+        <v>-1562</v>
+      </c>
+    </row>
+    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D63" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="E53" s="46">
+      <c r="E63" s="46">
         <f>AVERAGE(D2:D11,D13,D15:D50)</f>
-        <v>4.3191489361702127</v>
-      </c>
-      <c r="F53" s="36"/>
-      <c r="U53" s="53" t="s">
+        <v>4.5744680851063828</v>
+      </c>
+      <c r="F63" s="36"/>
+      <c r="U63" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="V53" s="36" t="s">
+      <c r="V63" s="36" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F54" s="36"/>
-      <c r="U54" s="33" t="s">
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F64" s="36"/>
+      <c r="U64" s="33" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F55" s="36"/>
-      <c r="U55" s="39">
-        <f>U52+V52</f>
-        <v>83147.47</v>
-      </c>
-    </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F56" s="36"/>
-    </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F57" s="36"/>
-      <c r="U57" s="36" t="s">
+    <row r="65" spans="6:21" x14ac:dyDescent="0.25">
+      <c r="F65" s="36"/>
+      <c r="U65" s="39">
+        <f>U62+V62</f>
+        <v>80477.47</v>
+      </c>
+    </row>
+    <row r="66" spans="6:21" x14ac:dyDescent="0.25">
+      <c r="F66" s="36"/>
+    </row>
+    <row r="67" spans="6:21" x14ac:dyDescent="0.25">
+      <c r="F67" s="36"/>
+      <c r="U67" s="36" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F58" s="36"/>
-      <c r="U58" s="39">
+    <row r="68" spans="6:21" x14ac:dyDescent="0.25">
+      <c r="F68" s="36"/>
+      <c r="U68" s="39">
         <v>333000</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="U60" s="33" t="s">
+    <row r="70" spans="6:21" x14ac:dyDescent="0.25">
+      <c r="U70" s="33" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="U61" s="54">
-        <f>U55/U58</f>
-        <v>0.2496921021021021</v>
+    <row r="71" spans="6:21" x14ac:dyDescent="0.25">
+      <c r="U71" s="54">
+        <f>U65/U68</f>
+        <v>0.24167408408408408</v>
       </c>
     </row>
   </sheetData>
@@ -6017,7 +6711,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -6083,11 +6777,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C78" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C80" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D78" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D80" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -7106,13 +7800,6 @@
         <f t="shared" si="1"/>
         <v>-1.3217444088987665E-3</v>
       </c>
-      <c r="F65" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="G65" s="27">
-        <f>AVERAGE(C3:C78)</f>
-        <v>1132.9617105263153</v>
-      </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" s="26">
@@ -7130,13 +7817,6 @@
         <f t="shared" si="1"/>
         <v>3.3013815803985677E-3</v>
       </c>
-      <c r="F66" s="25" t="s">
-        <v>115</v>
-      </c>
-      <c r="G66" s="27">
-        <f>_xlfn.STDEV.S(C3:C78)</f>
-        <v>4197.2651860151009</v>
-      </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" s="26">
@@ -7154,13 +7834,6 @@
         <f t="shared" si="1"/>
         <v>5.9947527591985503E-3</v>
       </c>
-      <c r="F67" s="25" t="s">
-        <v>116</v>
-      </c>
-      <c r="G67" s="28">
-        <f>(G65/G66)*SQRT(252)</f>
-        <v>4.2849829088690736</v>
-      </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" s="26">
@@ -7178,13 +7851,6 @@
         <f t="shared" si="1"/>
         <v>1.4399774654453973E-3</v>
       </c>
-      <c r="F68" s="25" t="s">
-        <v>117</v>
-      </c>
-      <c r="G68" s="29">
-        <f>_xlfn.STDEV.S(D2:D78)*SQRT(252)</f>
-        <v>0.18130074935190868</v>
-      </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" s="26">
@@ -7202,13 +7868,6 @@
         <f t="shared" si="1"/>
         <v>-9.3815545398334161E-3</v>
       </c>
-      <c r="F69" s="25" t="s">
-        <v>118</v>
-      </c>
-      <c r="G69" s="29" cm="1">
-        <f t="array" ref="G69">PRODUCT(1+D2:D78)-1</f>
-        <v>0.25822050884043724</v>
-      </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" s="26">
@@ -7226,13 +7885,6 @@
         <f t="shared" si="1"/>
         <v>-5.9407249299939296E-3</v>
       </c>
-      <c r="F70" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="G70" s="29" cm="1">
-        <f t="array" ref="G70">PRODUCT(1+D2:D78)^(252/COUNT(D2:D78))-1</f>
-        <v>1.120687461383878</v>
-      </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" s="26">
@@ -7301,6 +7953,13 @@
         <f t="shared" si="1"/>
         <v>1.3941407429779523E-3</v>
       </c>
+      <c r="F74" s="25" t="s">
+        <v>114</v>
+      </c>
+      <c r="G74" s="27">
+        <f>AVERAGE(C3:C80)</f>
+        <v>1071.1678205128201</v>
+      </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" s="26">
@@ -7318,6 +7977,13 @@
         <f t="shared" si="1"/>
         <v>9.4992906295542062E-3</v>
       </c>
+      <c r="F75" s="25" t="s">
+        <v>115</v>
+      </c>
+      <c r="G75" s="27">
+        <f>_xlfn.STDEV.S(C3:C80)</f>
+        <v>4168.9231616011057</v>
+      </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" s="26">
@@ -7335,6 +8001,13 @@
         <f t="shared" si="1"/>
         <v>-5.9729103776628928E-3</v>
       </c>
+      <c r="F76" s="25" t="s">
+        <v>116</v>
+      </c>
+      <c r="G76" s="28">
+        <f>(G74/G75)*SQRT(252)</f>
+        <v>4.0788139607786267</v>
+      </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" s="26">
@@ -7352,6 +8025,13 @@
         <f t="shared" si="1"/>
         <v>4.4963812546586836E-4</v>
       </c>
+      <c r="F77" s="25" t="s">
+        <v>117</v>
+      </c>
+      <c r="G77" s="29">
+        <f>_xlfn.STDEV.S(D2:D80)*SQRT(252)</f>
+        <v>0.17990141779373467</v>
+      </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" s="26">
@@ -7368,6 +8048,54 @@
       <c r="D78" s="23">
         <f t="shared" si="1"/>
         <v>8.3734501065908466E-3</v>
+      </c>
+      <c r="F78" s="25" t="s">
+        <v>118</v>
+      </c>
+      <c r="G78" s="29" cm="1">
+        <f t="array" ref="G78">PRODUCT(1+D2:D80)-1</f>
+        <v>0.25056132416984456</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A79" s="26">
+        <v>46293</v>
+      </c>
+      <c r="B79" s="5">
+        <f>B78+1042-1139+172+289+523-20-620-249+407</f>
+        <v>419966</v>
+      </c>
+      <c r="C79" s="5">
+        <f t="shared" si="0"/>
+        <v>405</v>
+      </c>
+      <c r="D79" s="23">
+        <f t="shared" si="1"/>
+        <v>9.6529467705530299E-4</v>
+      </c>
+      <c r="F79" s="25" t="s">
+        <v>119</v>
+      </c>
+      <c r="G79" s="29" cm="1">
+        <f t="array" ref="G79">PRODUCT(1+D2:D80)^(252/COUNT(D2:D80))-1</f>
+        <v>1.0405753524006216</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A80" s="26">
+        <v>46294</v>
+      </c>
+      <c r="B80" s="5">
+        <f>B79-1240-558-240-381-285--84+69-32-406+166+95-231</f>
+        <v>417007</v>
+      </c>
+      <c r="C80" s="5">
+        <f t="shared" si="0"/>
+        <v>-2959</v>
+      </c>
+      <c r="D80" s="23">
+        <f t="shared" si="1"/>
+        <v>-7.0458084702094935E-3</v>
       </c>
     </row>
   </sheetData>
@@ -12321,7 +13049,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="14">
-        <f t="shared" ref="M69:M85" si="0">SUM(C69:L69)</f>
+        <f t="shared" ref="M69:M87" si="0">SUM(C69:L69)</f>
         <v>407651</v>
       </c>
       <c r="N69" s="15">
@@ -13552,7 +14280,7 @@
         <v>0.17229199091431283</v>
       </c>
       <c r="O85" s="15">
-        <f t="shared" ref="O85" si="27">D85/M85</f>
+        <f t="shared" ref="O85:O86" si="27">D85/M85</f>
         <v>0.74261907088599755</v>
       </c>
       <c r="P85" s="15">
@@ -13582,6 +14310,162 @@
       <c r="W85" s="15">
         <f t="shared" ref="W85" si="29">L85/M85</f>
         <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A86" s="10">
+        <v>46293</v>
+      </c>
+      <c r="B86" s="11">
+        <v>420061</v>
+      </c>
+      <c r="C86" s="19">
+        <v>350539</v>
+      </c>
+      <c r="D86" s="13">
+        <v>0</v>
+      </c>
+      <c r="E86" s="13">
+        <v>0</v>
+      </c>
+      <c r="F86" s="13">
+        <v>0</v>
+      </c>
+      <c r="G86" s="13">
+        <v>0</v>
+      </c>
+      <c r="H86" s="13">
+        <v>35700</v>
+      </c>
+      <c r="I86" s="13">
+        <v>0</v>
+      </c>
+      <c r="J86" s="13">
+        <v>0</v>
+      </c>
+      <c r="K86" s="13">
+        <v>0</v>
+      </c>
+      <c r="L86" s="18">
+        <v>41648</v>
+      </c>
+      <c r="M86" s="14">
+        <f t="shared" si="0"/>
+        <v>427887</v>
+      </c>
+      <c r="N86" s="15">
+        <f t="shared" ref="N86" si="30">C86/M86</f>
+        <v>0.81923264787198491</v>
+      </c>
+      <c r="O86" s="15">
+        <f t="shared" si="27"/>
+        <v>0</v>
+      </c>
+      <c r="P86" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q86" s="15">
+        <v>0</v>
+      </c>
+      <c r="R86" s="15">
+        <v>0</v>
+      </c>
+      <c r="S86" s="15">
+        <f>H86/M86</f>
+        <v>8.3433242888893561E-2</v>
+      </c>
+      <c r="T86" s="15">
+        <f t="shared" ref="T86" si="31">I86/M86</f>
+        <v>0</v>
+      </c>
+      <c r="U86" s="15">
+        <v>0</v>
+      </c>
+      <c r="V86" s="16">
+        <f>K86/M86</f>
+        <v>0</v>
+      </c>
+      <c r="W86" s="15">
+        <f t="shared" ref="W86" si="32">L86/M86</f>
+        <v>9.7334109239121544E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A87" s="10">
+        <v>46294</v>
+      </c>
+      <c r="B87" s="11">
+        <v>417007</v>
+      </c>
+      <c r="C87" s="19">
+        <v>348061</v>
+      </c>
+      <c r="D87" s="13">
+        <v>0</v>
+      </c>
+      <c r="E87" s="13">
+        <v>0</v>
+      </c>
+      <c r="F87" s="13">
+        <v>0</v>
+      </c>
+      <c r="G87" s="13">
+        <v>0</v>
+      </c>
+      <c r="H87" s="13">
+        <v>52956</v>
+      </c>
+      <c r="I87" s="13">
+        <v>0</v>
+      </c>
+      <c r="J87" s="13">
+        <v>0</v>
+      </c>
+      <c r="K87" s="13">
+        <v>0</v>
+      </c>
+      <c r="L87" s="18">
+        <v>208986</v>
+      </c>
+      <c r="M87" s="14">
+        <f t="shared" si="0"/>
+        <v>610003</v>
+      </c>
+      <c r="N87" s="15">
+        <f t="shared" ref="N87" si="33">C87/M87</f>
+        <v>0.57058899710329292</v>
+      </c>
+      <c r="O87" s="15">
+        <f t="shared" ref="O87" si="34">D87/M87</f>
+        <v>0</v>
+      </c>
+      <c r="P87" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q87" s="15">
+        <v>0</v>
+      </c>
+      <c r="R87" s="15">
+        <v>0</v>
+      </c>
+      <c r="S87" s="15">
+        <f>H87/M87</f>
+        <v>8.6812687806453417E-2</v>
+      </c>
+      <c r="T87" s="15">
+        <f t="shared" ref="T87" si="35">I87/M87</f>
+        <v>0</v>
+      </c>
+      <c r="U87" s="15">
+        <v>0</v>
+      </c>
+      <c r="V87" s="16">
+        <f>K87/M87</f>
+        <v>0</v>
+      </c>
+      <c r="W87" s="15">
+        <f t="shared" ref="W87" si="36">L87/M87</f>
+        <v>0.34259831509025368</v>
       </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.25">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4FB0B704-A772-BC4A-B670-59423321B624}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E297F384-C279-0B49-B3C9-E27F92B49953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="23940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="982" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="634">
   <si>
     <t>Trade ID</t>
   </si>
@@ -1935,21 +1935,6 @@
     <t>Acadia Pharmaceuticals</t>
   </si>
   <si>
-    <t>FDX</t>
-  </si>
-  <si>
-    <t>Fedex</t>
-  </si>
-  <si>
-    <t>Pairs Trading</t>
-  </si>
-  <si>
-    <t>UPS</t>
-  </si>
-  <si>
-    <t>United Parcel Service</t>
-  </si>
-  <si>
     <t>IWM</t>
   </si>
   <si>
@@ -1969,6 +1954,18 @@
   </si>
   <si>
     <t>Vanguard Mortgage Backed Securities ETF</t>
+  </si>
+  <si>
+    <t>WAT</t>
+  </si>
+  <si>
+    <t>Waters Corporation</t>
+  </si>
+  <si>
+    <t>TMO</t>
+  </si>
+  <si>
+    <t>Thermo Fisher Scientific</t>
   </si>
 </sst>
 </file>
@@ -4312,7 +4309,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D53" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D59" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
@@ -5450,11 +5447,11 @@
         <v>46286</v>
       </c>
       <c r="C43" s="55">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D43" s="35">
         <f t="shared" si="5"/>
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E43" s="47" t="s">
         <v>599</v>
@@ -5487,7 +5484,7 @@
         <v>72</v>
       </c>
       <c r="O43" s="47">
-        <v>154.4</v>
+        <v>154.01</v>
       </c>
       <c r="P43" s="49">
         <f>ABS(M43*L43)</f>
@@ -5509,7 +5506,7 @@
         <v>72</v>
       </c>
       <c r="V43" s="33">
-        <v>363</v>
+        <v>397</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
@@ -5723,11 +5720,11 @@
         <v>46288</v>
       </c>
       <c r="C47" s="55">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D47" s="35">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E47" s="47" t="s">
         <v>606</v>
@@ -5751,20 +5748,20 @@
         <v>606</v>
       </c>
       <c r="L47" s="47">
-        <v>-160</v>
+        <v>-200</v>
       </c>
       <c r="M47" s="47">
-        <v>256.4325</v>
+        <v>258.43</v>
       </c>
       <c r="N47" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O47" s="47">
-        <v>262.75</v>
+        <v>264.33999999999997</v>
       </c>
       <c r="P47" s="49">
         <f>ABS(M47*L47)</f>
-        <v>41029.199999999997</v>
+        <v>51686</v>
       </c>
       <c r="Q47" s="47">
         <v>2.08</v>
@@ -5782,7 +5779,7 @@
         <v>72</v>
       </c>
       <c r="V47" s="33">
-        <v>-988</v>
+        <v>-1200</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
@@ -5793,11 +5790,11 @@
         <v>46288</v>
       </c>
       <c r="C48" s="55">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D48" s="35">
         <f t="shared" si="5"/>
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E48" s="47" t="s">
         <v>58</v>
@@ -5852,7 +5849,7 @@
         <v>72</v>
       </c>
       <c r="V48" s="33">
-        <v>26</v>
+        <v>926</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -5997,11 +5994,11 @@
         <v>46293</v>
       </c>
       <c r="C51" s="55">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D51" s="35">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E51" s="47" t="s">
         <v>615</v>
@@ -6025,20 +6022,20 @@
         <v>615</v>
       </c>
       <c r="L51" s="47">
-        <v>600</v>
+        <v>700</v>
       </c>
       <c r="M51" s="47">
-        <v>84.65</v>
+        <v>84.41</v>
       </c>
       <c r="N51" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O51" s="47">
-        <v>85.39</v>
+        <v>83.71</v>
       </c>
       <c r="P51" s="49">
-        <f>ABS(M51*L51)</f>
-        <v>50790</v>
+        <f t="shared" ref="P51:P59" si="10">ABS(M51*L51)</f>
+        <v>59087</v>
       </c>
       <c r="Q51" s="47">
         <v>2.44</v>
@@ -6056,7 +6053,7 @@
         <v>72</v>
       </c>
       <c r="V51" s="33">
-        <v>438</v>
+        <v>-522</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -6067,11 +6064,11 @@
         <v>46293</v>
       </c>
       <c r="C52" s="55">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D52" s="35">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E52" s="47" t="s">
         <v>617</v>
@@ -6107,7 +6104,7 @@
         <v>104.02</v>
       </c>
       <c r="P52" s="49">
-        <f>ABS(M52*L52)</f>
+        <f t="shared" si="10"/>
         <v>41656</v>
       </c>
       <c r="Q52" s="47">
@@ -6126,7 +6123,7 @@
         <v>72</v>
       </c>
       <c r="V52" s="33">
-        <v>-44</v>
+        <v>-52</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
@@ -6137,11 +6134,11 @@
         <v>46293</v>
       </c>
       <c r="C53" s="55">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D53" s="35">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E53" s="47" t="s">
         <v>619</v>
@@ -6165,10 +6162,10 @@
         <v>619</v>
       </c>
       <c r="L53" s="47">
-        <v>-100</v>
+        <v>-110</v>
       </c>
       <c r="M53" s="47">
-        <v>446.67</v>
+        <v>446.98</v>
       </c>
       <c r="N53" s="47" t="s">
         <v>72</v>
@@ -6177,8 +6174,8 @@
         <v>457.08</v>
       </c>
       <c r="P53" s="49">
-        <f>ABS(M53*L53)</f>
-        <v>44667</v>
+        <f t="shared" si="10"/>
+        <v>49167.8</v>
       </c>
       <c r="Q53" s="47">
         <v>2.33</v>
@@ -6196,7 +6193,7 @@
         <v>72</v>
       </c>
       <c r="V53" s="33">
-        <v>-933</v>
+        <v>-990</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -6206,66 +6203,68 @@
       <c r="B54" s="34">
         <v>46293</v>
       </c>
-      <c r="C54" s="55">
-        <v>46294</v>
+      <c r="C54" s="34">
+        <v>46295</v>
       </c>
       <c r="D54" s="35">
-        <v>0</v>
-      </c>
-      <c r="E54" s="47" t="s">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="E54" s="33" t="s">
         <v>621</v>
       </c>
-      <c r="F54" s="48" t="s">
+      <c r="F54" s="36" t="s">
         <v>622</v>
       </c>
-      <c r="G54" s="47" t="s">
+      <c r="G54" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H54" s="48" t="s">
+      <c r="H54" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I54" s="47" t="s">
+      <c r="I54" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="J54" s="47" t="s">
+      <c r="J54" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="K54" s="47" t="s">
+      <c r="K54" s="33" t="s">
         <v>621</v>
       </c>
-      <c r="L54" s="47">
+      <c r="L54" s="33">
         <v>4000</v>
       </c>
-      <c r="M54" s="47">
+      <c r="M54" s="33">
         <v>20.27</v>
       </c>
-      <c r="N54" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O54" s="47">
+      <c r="N54" s="33">
         <v>20.21</v>
       </c>
-      <c r="P54" s="49">
-        <f>ABS(M54*L54)</f>
+      <c r="O54" s="33">
+        <v>20.21</v>
+      </c>
+      <c r="P54" s="39">
+        <f t="shared" si="10"/>
         <v>81080</v>
       </c>
-      <c r="Q54" s="47">
+      <c r="Q54" s="33">
         <v>5.4</v>
       </c>
-      <c r="R54" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S54" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T54" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="U54" s="49" t="s">
-        <v>72</v>
+      <c r="R54" s="33">
+        <v>0</v>
+      </c>
+      <c r="S54" s="40">
+        <f t="shared" ref="S54" si="11">IF(R54=1, ABS(N54-M54)/M54, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="T54" s="33">
+        <v>-214</v>
+      </c>
+      <c r="U54" s="45">
+        <v>-214</v>
       </c>
       <c r="V54" s="33">
-        <v>-198</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.25">
@@ -6273,13 +6272,14 @@
         <v>50</v>
       </c>
       <c r="B55" s="34">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C55" s="55">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D55" s="35">
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E55" s="47" t="s">
         <v>623</v>
@@ -6294,32 +6294,32 @@
         <v>625</v>
       </c>
       <c r="I55" s="47" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="J55" s="47" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="K55" s="47" t="s">
         <v>623</v>
       </c>
       <c r="L55" s="47">
-        <v>175</v>
+        <v>200</v>
       </c>
       <c r="M55" s="47">
-        <v>287.99</v>
+        <v>280.43</v>
       </c>
       <c r="N55" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O55" s="47">
-        <v>287.52</v>
+        <v>278</v>
       </c>
       <c r="P55" s="49">
-        <f>ABS(M55*L55)</f>
-        <v>50398.25</v>
+        <f t="shared" si="10"/>
+        <v>56086</v>
       </c>
       <c r="Q55" s="47">
-        <v>1.49</v>
+        <v>3.11</v>
       </c>
       <c r="R55" s="47" t="s">
         <v>72</v>
@@ -6334,21 +6334,22 @@
         <v>72</v>
       </c>
       <c r="V55" s="33">
-        <v>-92</v>
+        <v>-477</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A56" s="33">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B56" s="34">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C56" s="55">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D56" s="35">
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E56" s="47" t="s">
         <v>626</v>
@@ -6363,32 +6364,32 @@
         <v>625</v>
       </c>
       <c r="I56" s="47" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="J56" s="47" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="K56" s="47" t="s">
         <v>626</v>
       </c>
       <c r="L56" s="47">
-        <v>-520</v>
+        <v>-70</v>
       </c>
       <c r="M56" s="47">
-        <v>93.92</v>
+        <v>765.18</v>
       </c>
       <c r="N56" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O56" s="47">
-        <v>93.94</v>
+        <v>764.59</v>
       </c>
       <c r="P56" s="49">
-        <f>ABS(M56*L56)</f>
-        <v>48838.400000000001</v>
+        <f t="shared" si="10"/>
+        <v>53562.6</v>
       </c>
       <c r="Q56" s="47">
-        <v>1.55</v>
+        <v>3.11</v>
       </c>
       <c r="R56" s="47" t="s">
         <v>72</v>
@@ -6403,21 +6404,22 @@
         <v>72</v>
       </c>
       <c r="V56" s="33">
-        <v>-5</v>
+        <v>198</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A57" s="33">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B57" s="34">
         <v>46294</v>
       </c>
       <c r="C57" s="55">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D57" s="35">
-        <v>0</v>
+        <f t="shared" si="5"/>
+        <v>1</v>
       </c>
       <c r="E57" s="47" t="s">
         <v>628</v>
@@ -6426,10 +6428,10 @@
         <v>629</v>
       </c>
       <c r="G57" s="47" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H57" s="48" t="s">
-        <v>630</v>
+        <v>24</v>
       </c>
       <c r="I57" s="47" t="s">
         <v>48</v>
@@ -6441,20 +6443,20 @@
         <v>628</v>
       </c>
       <c r="L57" s="47">
-        <v>200</v>
+        <v>2000</v>
       </c>
       <c r="M57" s="47">
-        <v>280.43</v>
+        <v>44.366999999999997</v>
       </c>
       <c r="N57" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O57" s="47">
-        <v>279.16000000000003</v>
+        <v>44.48</v>
       </c>
       <c r="P57" s="49">
-        <f>ABS(M57*L57)</f>
-        <v>56086</v>
+        <f t="shared" si="10"/>
+        <v>88734</v>
       </c>
       <c r="Q57" s="47">
         <v>3.11</v>
@@ -6472,61 +6474,62 @@
         <v>72</v>
       </c>
       <c r="V57" s="33">
-        <v>-265</v>
+        <v>87</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A58" s="33">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B58" s="34">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C58" s="55">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D58" s="35">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E58" s="47" t="s">
+        <v>630</v>
+      </c>
+      <c r="F58" s="48" t="s">
         <v>631</v>
       </c>
-      <c r="F58" s="48" t="s">
-        <v>632</v>
-      </c>
       <c r="G58" s="47" t="s">
-        <v>30</v>
+        <v>23</v>
       </c>
       <c r="H58" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I58" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J58" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K58" s="47" t="s">
         <v>630</v>
       </c>
-      <c r="I58" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="J58" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="K58" s="47" t="s">
-        <v>631</v>
-      </c>
       <c r="L58" s="47">
-        <v>-70</v>
+        <v>-100</v>
       </c>
       <c r="M58" s="47">
-        <v>765.18</v>
+        <v>446.99</v>
       </c>
       <c r="N58" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O58" s="47">
-        <v>764.59</v>
+        <v>445.2</v>
       </c>
       <c r="P58" s="49">
-        <f>ABS(M58*L58)</f>
-        <v>53562.6</v>
+        <f t="shared" si="10"/>
+        <v>44699</v>
       </c>
       <c r="Q58" s="47">
-        <v>3.11</v>
+        <v>2.4700000000000002</v>
       </c>
       <c r="R58" s="47" t="s">
         <v>72</v>
@@ -6541,27 +6544,28 @@
         <v>72</v>
       </c>
       <c r="V58" s="33">
-        <v>41</v>
+        <v>760</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A59" s="33">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B59" s="34">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="C59" s="55">
-        <v>46294</v>
+        <v>46295</v>
       </c>
       <c r="D59" s="35">
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="E59" s="47" t="s">
+        <v>632</v>
+      </c>
+      <c r="F59" s="48" t="s">
         <v>633</v>
-      </c>
-      <c r="F59" s="48" t="s">
-        <v>634</v>
       </c>
       <c r="G59" s="47" t="s">
         <v>23</v>
@@ -6570,32 +6574,32 @@
         <v>24</v>
       </c>
       <c r="I59" s="47" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="J59" s="47" t="s">
-        <v>48</v>
+        <v>25</v>
       </c>
       <c r="K59" s="47" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="L59" s="47">
-        <v>1300</v>
+        <v>-100</v>
       </c>
       <c r="M59" s="47">
-        <v>44.37</v>
+        <v>672.45</v>
       </c>
       <c r="N59" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O59" s="47">
-        <v>44.45</v>
+        <v>680.77</v>
       </c>
       <c r="P59" s="49">
-        <f>ABS(M59*L59)</f>
-        <v>57681</v>
+        <f t="shared" si="10"/>
+        <v>67245</v>
       </c>
       <c r="Q59" s="47">
-        <v>3.11</v>
+        <v>3.45</v>
       </c>
       <c r="R59" s="47" t="s">
         <v>72</v>
@@ -6610,7 +6614,7 @@
         <v>72</v>
       </c>
       <c r="V59" s="33">
-        <v>95</v>
+        <v>-108</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
@@ -6621,7 +6625,7 @@
       <c r="H60" s="36"/>
       <c r="P60" s="39"/>
       <c r="S60" s="40"/>
-      <c r="U60" s="41"/>
+      <c r="U60" s="39"/>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F61" s="36"/>
@@ -6632,8 +6636,8 @@
         <v>103</v>
       </c>
       <c r="E62" s="46">
-        <f>AVERAGE(D2:D50)</f>
-        <v>6.7551020408163263</v>
+        <f>AVERAGE(D2:D59)</f>
+        <v>5.9482758620689653</v>
       </c>
       <c r="F62" s="36"/>
       <c r="H62" s="36"/>
@@ -6643,7 +6647,7 @@
       </c>
       <c r="V62" s="39">
         <f>SUM(V2:V59)</f>
-        <v>-1562</v>
+        <v>-981</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
@@ -6651,8 +6655,8 @@
         <v>104</v>
       </c>
       <c r="E63" s="46">
-        <f>AVERAGE(D2:D11,D13,D15:D50)</f>
-        <v>4.5744680851063828</v>
+        <f>AVERAGE(D2:D11,D13,D15:D59)</f>
+        <v>4.0892857142857144</v>
       </c>
       <c r="F63" s="36"/>
       <c r="U63" s="53" t="s">
@@ -6672,7 +6676,7 @@
       <c r="F65" s="36"/>
       <c r="U65" s="39">
         <f>U62+V62</f>
-        <v>80477.47</v>
+        <v>81058.47</v>
       </c>
     </row>
     <row r="66" spans="6:21" x14ac:dyDescent="0.25">
@@ -6698,7 +6702,7 @@
     <row r="71" spans="6:21" x14ac:dyDescent="0.25">
       <c r="U71" s="54">
         <f>U65/U68</f>
-        <v>0.24167408408408408</v>
+        <v>0.24341882882882884</v>
       </c>
     </row>
   </sheetData>
@@ -6711,7 +6715,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:G80"/>
+  <dimension ref="A1:I81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -6777,11 +6781,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C80" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C81" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D80" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D81" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -7784,7 +7788,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="26">
         <v>46273</v>
       </c>
@@ -7801,7 +7805,7 @@
         <v>-1.3217444088987665E-3</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="26">
         <v>46274</v>
       </c>
@@ -7818,7 +7822,7 @@
         <v>3.3013815803985677E-3</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="26">
         <v>46275</v>
       </c>
@@ -7835,7 +7839,7 @@
         <v>5.9947527591985503E-3</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="26">
         <v>46276</v>
       </c>
@@ -7852,7 +7856,7 @@
         <v>1.4399774654453973E-3</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="26">
         <v>46279</v>
       </c>
@@ -7869,7 +7873,7 @@
         <v>-9.3815545398334161E-3</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="26">
         <v>46280</v>
       </c>
@@ -7886,7 +7890,7 @@
         <v>-5.9407249299939296E-3</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="26">
         <v>46281</v>
       </c>
@@ -7903,7 +7907,7 @@
         <v>1.4720185959927015E-2</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="26">
         <v>46282</v>
       </c>
@@ -7920,7 +7924,7 @@
         <v>8.6777792068179777E-3</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="26">
         <v>46283</v>
       </c>
@@ -7937,7 +7941,7 @@
         <v>-4.3015616015858998E-3</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="26">
         <v>46286</v>
       </c>
@@ -7957,11 +7961,12 @@
         <v>114</v>
       </c>
       <c r="G74" s="27">
-        <f>AVERAGE(C3:C80)</f>
-        <v>1071.1678205128201</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.2">
+        <f>AVERAGE(C3:C81)</f>
+        <v>1059.2289873417717</v>
+      </c>
+      <c r="I74" s="27"/>
+    </row>
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="26">
         <v>46287</v>
       </c>
@@ -7981,11 +7986,12 @@
         <v>115</v>
       </c>
       <c r="G75" s="27">
-        <f>_xlfn.STDEV.S(C3:C80)</f>
-        <v>4168.9231616011057</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.2">
+        <f>_xlfn.STDEV.S(C3:C81)</f>
+        <v>4143.4721139666781</v>
+      </c>
+      <c r="I75" s="27"/>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="26">
         <v>46288</v>
       </c>
@@ -8006,10 +8012,11 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
-        <v>4.0788139607786267</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.2">
+        <v>4.0581276835879025</v>
+      </c>
+      <c r="I76" s="28"/>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="26">
         <v>46289</v>
       </c>
@@ -8029,11 +8036,12 @@
         <v>117</v>
       </c>
       <c r="G77" s="29">
-        <f>_xlfn.STDEV.S(D2:D80)*SQRT(252)</f>
-        <v>0.17990141779373467</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.2">
+        <f>_xlfn.STDEV.S(D2:D81)*SQRT(252)</f>
+        <v>0.17881827902957989</v>
+      </c>
+      <c r="I77" s="29"/>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="26">
         <v>46290</v>
       </c>
@@ -8053,11 +8061,12 @@
         <v>118</v>
       </c>
       <c r="G78" s="29" cm="1">
-        <f t="array" ref="G78">PRODUCT(1+D2:D80)-1</f>
-        <v>0.25056132416984456</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="array" ref="G78">PRODUCT(1+D2:D81)-1</f>
+        <v>0.25094518307267766</v>
+      </c>
+      <c r="I78" s="29"/>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="26">
         <v>46293</v>
       </c>
@@ -8077,11 +8086,12 @@
         <v>119</v>
       </c>
       <c r="G79" s="29" cm="1">
-        <f t="array" ref="G79">PRODUCT(1+D2:D80)^(252/COUNT(D2:D80))-1</f>
-        <v>1.0405753524006216</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.2">
+        <f t="array" ref="G79">PRODUCT(1+D2:D81)^(252/COUNT(D2:D81))-1</f>
+        <v>1.0244198140350593</v>
+      </c>
+      <c r="I79" s="29"/>
+    </row>
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="26">
         <v>46294</v>
       </c>
@@ -8096,6 +8106,23 @@
       <c r="D80" s="23">
         <f t="shared" si="1"/>
         <v>-7.0458084702094935E-3</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A81" s="26">
+        <v>46295</v>
+      </c>
+      <c r="B81" s="5">
+        <f>B80+128</f>
+        <v>417135</v>
+      </c>
+      <c r="C81" s="5">
+        <f t="shared" si="0"/>
+        <v>128</v>
+      </c>
+      <c r="D81" s="23">
+        <f t="shared" si="1"/>
+        <v>3.0694928382497176E-4</v>
       </c>
     </row>
   </sheetData>
@@ -13049,7 +13076,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="14">
-        <f t="shared" ref="M69:M87" si="0">SUM(C69:L69)</f>
+        <f t="shared" ref="M69:M88" si="0">SUM(C69:L69)</f>
         <v>407651</v>
       </c>
       <c r="N69" s="15">
@@ -14466,6 +14493,84 @@
       <c r="W87" s="15">
         <f t="shared" ref="W87" si="36">L87/M87</f>
         <v>0.34259831509025368</v>
+      </c>
+    </row>
+    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A88" s="10">
+        <v>46295</v>
+      </c>
+      <c r="B88" s="11">
+        <v>417135</v>
+      </c>
+      <c r="C88" s="19">
+        <v>279688</v>
+      </c>
+      <c r="D88" s="13">
+        <v>0</v>
+      </c>
+      <c r="E88" s="13">
+        <v>0</v>
+      </c>
+      <c r="F88" s="13">
+        <v>0</v>
+      </c>
+      <c r="G88" s="13">
+        <v>0</v>
+      </c>
+      <c r="H88" s="13">
+        <v>52956</v>
+      </c>
+      <c r="I88" s="13">
+        <v>0</v>
+      </c>
+      <c r="J88" s="13">
+        <v>0</v>
+      </c>
+      <c r="K88" s="13">
+        <v>0</v>
+      </c>
+      <c r="L88" s="18">
+        <v>240039</v>
+      </c>
+      <c r="M88" s="14">
+        <f t="shared" si="0"/>
+        <v>572683</v>
+      </c>
+      <c r="N88" s="15">
+        <f t="shared" ref="N88" si="37">C88/M88</f>
+        <v>0.4883818796786355</v>
+      </c>
+      <c r="O88" s="15">
+        <f t="shared" ref="O88" si="38">D88/M88</f>
+        <v>0</v>
+      </c>
+      <c r="P88" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q88" s="15">
+        <v>0</v>
+      </c>
+      <c r="R88" s="15">
+        <v>0</v>
+      </c>
+      <c r="S88" s="15">
+        <f>H88/M88</f>
+        <v>9.2470005221038515E-2</v>
+      </c>
+      <c r="T88" s="15">
+        <f t="shared" ref="T88" si="39">I88/M88</f>
+        <v>0</v>
+      </c>
+      <c r="U88" s="15">
+        <v>0</v>
+      </c>
+      <c r="V88" s="16">
+        <f>K88/M88</f>
+        <v>0</v>
+      </c>
+      <c r="W88" s="15">
+        <f t="shared" ref="W88" si="40">L88/M88</f>
+        <v>0.41914811510032601</v>
       </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.25">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E297F384-C279-0B49-B3C9-E27F92B49953}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{872267F4-2152-A64D-808C-3A788BCCAB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="23940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="977" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="634">
   <si>
     <t>Trade ID</t>
   </si>
@@ -4309,7 +4309,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D59" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D60" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
@@ -5475,20 +5475,20 @@
         <v>599</v>
       </c>
       <c r="L43" s="47">
-        <v>-200</v>
+        <v>-300</v>
       </c>
       <c r="M43" s="47">
-        <v>156.29</v>
+        <v>157.56</v>
       </c>
       <c r="N43" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O43" s="47">
-        <v>154.01</v>
+        <v>163</v>
       </c>
       <c r="P43" s="49">
         <f>ABS(M43*L43)</f>
-        <v>31258</v>
+        <v>47268</v>
       </c>
       <c r="Q43" s="47">
         <v>1.02</v>
@@ -5506,7 +5506,7 @@
         <v>72</v>
       </c>
       <c r="V43" s="33">
-        <v>397</v>
+        <v>-1050</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
@@ -5634,7 +5634,7 @@
         <v>1</v>
       </c>
       <c r="S45" s="40">
-        <f t="shared" ref="S45:S46" si="8">IF(R45=1, ABS(N45-M45)/M45, 0)</f>
+        <f t="shared" ref="S45:S48" si="8">IF(R45=1, ABS(N45-M45)/M45, 0)</f>
         <v>6.6957880304817775E-4</v>
       </c>
       <c r="T45" s="33">
@@ -5748,20 +5748,20 @@
         <v>606</v>
       </c>
       <c r="L47" s="47">
-        <v>-200</v>
+        <v>-260</v>
       </c>
       <c r="M47" s="47">
-        <v>258.43</v>
+        <v>261.35000000000002</v>
       </c>
       <c r="N47" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O47" s="47">
-        <v>264.33999999999997</v>
+        <v>271</v>
       </c>
       <c r="P47" s="49">
         <f>ABS(M47*L47)</f>
-        <v>51686</v>
+        <v>67951</v>
       </c>
       <c r="Q47" s="47">
         <v>2.08</v>
@@ -5779,7 +5779,7 @@
         <v>72</v>
       </c>
       <c r="V47" s="33">
-        <v>-1200</v>
+        <v>-2353</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
@@ -5789,67 +5789,65 @@
       <c r="B48" s="34">
         <v>46288</v>
       </c>
-      <c r="C48" s="55">
-        <v>46295</v>
+      <c r="C48" s="34">
+        <v>46296</v>
       </c>
       <c r="D48" s="35">
         <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="E48" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="E48" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="F48" s="48" t="s">
+      <c r="F48" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="G48" s="47" t="s">
+      <c r="G48" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H48" s="48" t="s">
+      <c r="H48" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I48" s="47" t="s">
+      <c r="I48" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="J48" s="47" t="s">
+      <c r="J48" s="33" t="s">
         <v>532</v>
       </c>
-      <c r="K48" s="47" t="s">
+      <c r="K48" s="33" t="s">
         <v>608</v>
       </c>
-      <c r="L48" s="47">
+      <c r="L48" s="33">
         <v>30</v>
       </c>
-      <c r="M48" s="47">
+      <c r="M48" s="33">
         <v>17.652000000000001</v>
       </c>
-      <c r="N48" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O48" s="47">
-        <v>17.649999999999999</v>
-      </c>
-      <c r="P48" s="49">
+      <c r="N48" s="33">
+        <v>18.277999999999999</v>
+      </c>
+      <c r="O48" s="33">
+        <v>18.277999999999999</v>
+      </c>
+      <c r="P48" s="39">
         <f>ABS(M48*L48)*100</f>
         <v>52956.000000000007</v>
       </c>
-      <c r="Q48" s="47">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="R48" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S48" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T48" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="U48" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V48" s="33">
-        <v>926</v>
+      <c r="Q48" s="33">
+        <v>27.6</v>
+      </c>
+      <c r="R48" s="33">
+        <v>1</v>
+      </c>
+      <c r="S48" s="40">
+        <f t="shared" si="8"/>
+        <v>3.5463403580330705E-2</v>
+      </c>
+      <c r="T48" s="33">
+        <v>1895</v>
+      </c>
+      <c r="U48" s="41">
+        <v>1895</v>
       </c>
     </row>
     <row r="49" spans="1:22" x14ac:dyDescent="0.25">
@@ -5909,7 +5907,7 @@
         <v>1</v>
       </c>
       <c r="S49" s="40">
-        <f t="shared" ref="S49:S50" si="9">IF(R49=1, ABS(N49-M49)/M49, 0)</f>
+        <f t="shared" ref="S49:S51" si="9">IF(R49=1, ABS(N49-M49)/M49, 0)</f>
         <v>2.0138262699128395E-2</v>
       </c>
       <c r="T49" s="33">
@@ -5993,67 +5991,65 @@
       <c r="B51" s="34">
         <v>46293</v>
       </c>
-      <c r="C51" s="55">
-        <v>46295</v>
+      <c r="C51" s="34">
+        <v>46296</v>
       </c>
       <c r="D51" s="35">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="E51" s="47" t="s">
+        <v>3</v>
+      </c>
+      <c r="E51" s="33" t="s">
         <v>615</v>
       </c>
-      <c r="F51" s="48" t="s">
+      <c r="F51" s="36" t="s">
         <v>616</v>
       </c>
-      <c r="G51" s="47" t="s">
+      <c r="G51" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H51" s="48" t="s">
+      <c r="H51" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I51" s="47" t="s">
+      <c r="I51" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="J51" s="47" t="s">
+      <c r="J51" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="K51" s="47" t="s">
+      <c r="K51" s="33" t="s">
         <v>615</v>
       </c>
-      <c r="L51" s="47">
+      <c r="L51" s="33">
         <v>700</v>
       </c>
-      <c r="M51" s="47">
+      <c r="M51" s="33">
         <v>84.41</v>
       </c>
-      <c r="N51" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O51" s="47">
-        <v>83.71</v>
-      </c>
-      <c r="P51" s="49">
-        <f t="shared" ref="P51:P59" si="10">ABS(M51*L51)</f>
+      <c r="N51" s="33">
+        <v>82.27</v>
+      </c>
+      <c r="O51" s="33">
+        <v>82.27</v>
+      </c>
+      <c r="P51" s="39">
+        <f t="shared" ref="P51:P60" si="10">ABS(M51*L51)</f>
         <v>59087</v>
       </c>
-      <c r="Q51" s="47">
-        <v>2.44</v>
-      </c>
-      <c r="R51" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S51" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T51" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="U51" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V51" s="33">
-        <v>-522</v>
+      <c r="Q51" s="33">
+        <v>9.65</v>
+      </c>
+      <c r="R51" s="33">
+        <v>0</v>
+      </c>
+      <c r="S51" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="T51" s="33">
+        <v>-1498</v>
+      </c>
+      <c r="U51" s="45">
+        <v>-1498</v>
       </c>
     </row>
     <row r="52" spans="1:22" x14ac:dyDescent="0.25">
@@ -6123,7 +6119,7 @@
         <v>72</v>
       </c>
       <c r="V52" s="33">
-        <v>-52</v>
+        <v>132</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
@@ -6193,7 +6189,7 @@
         <v>72</v>
       </c>
       <c r="V53" s="33">
-        <v>-990</v>
+        <v>-1925</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -6263,9 +6259,6 @@
       <c r="U54" s="45">
         <v>-214</v>
       </c>
-      <c r="V54" s="33">
-        <v>0</v>
-      </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" s="33">
@@ -6334,7 +6327,7 @@
         <v>72</v>
       </c>
       <c r="V55" s="33">
-        <v>-477</v>
+        <v>390</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.25">
@@ -6404,7 +6397,7 @@
         <v>72</v>
       </c>
       <c r="V56" s="33">
-        <v>198</v>
+        <v>-375</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.25">
@@ -6474,7 +6467,7 @@
         <v>72</v>
       </c>
       <c r="V57" s="33">
-        <v>87</v>
+        <v>277</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.25">
@@ -6484,67 +6477,65 @@
       <c r="B58" s="34">
         <v>46295</v>
       </c>
-      <c r="C58" s="55">
-        <v>46295</v>
+      <c r="C58" s="34">
+        <v>46296</v>
       </c>
       <c r="D58" s="35">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E58" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E58" s="33" t="s">
         <v>630</v>
       </c>
-      <c r="F58" s="48" t="s">
+      <c r="F58" s="36" t="s">
         <v>631</v>
       </c>
-      <c r="G58" s="47" t="s">
+      <c r="G58" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H58" s="48" t="s">
+      <c r="H58" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I58" s="47" t="s">
+      <c r="I58" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="J58" s="47" t="s">
+      <c r="J58" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="K58" s="47" t="s">
+      <c r="K58" s="33" t="s">
         <v>630</v>
       </c>
-      <c r="L58" s="47">
+      <c r="L58" s="33">
         <v>-100</v>
       </c>
-      <c r="M58" s="47">
-        <v>446.99</v>
-      </c>
-      <c r="N58" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O58" s="47">
-        <v>445.2</v>
-      </c>
-      <c r="P58" s="49">
+      <c r="M58" s="33">
+        <v>447</v>
+      </c>
+      <c r="N58" s="33">
+        <v>434.77</v>
+      </c>
+      <c r="O58" s="33">
+        <v>434.77</v>
+      </c>
+      <c r="P58" s="39">
         <f t="shared" si="10"/>
-        <v>44699</v>
-      </c>
-      <c r="Q58" s="47">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="R58" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S58" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T58" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="U58" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V58" s="33">
-        <v>760</v>
+        <v>44700</v>
+      </c>
+      <c r="Q58" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="R58" s="33">
+        <v>1</v>
+      </c>
+      <c r="S58" s="40">
+        <f t="shared" ref="S58:S60" si="12">IF(R58=1, ABS(N58-M58)/M58, 0)</f>
+        <v>2.7360178970917266E-2</v>
+      </c>
+      <c r="T58" s="33">
+        <v>1222</v>
+      </c>
+      <c r="U58" s="41">
+        <v>1222</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.25">
@@ -6554,78 +6545,134 @@
       <c r="B59" s="34">
         <v>46295</v>
       </c>
-      <c r="C59" s="55">
-        <v>46295</v>
+      <c r="C59" s="34">
+        <v>46296</v>
       </c>
       <c r="D59" s="35">
         <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E59" s="47" t="s">
+        <v>1</v>
+      </c>
+      <c r="E59" s="33" t="s">
         <v>632</v>
       </c>
-      <c r="F59" s="48" t="s">
+      <c r="F59" s="36" t="s">
         <v>633</v>
       </c>
-      <c r="G59" s="47" t="s">
+      <c r="G59" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H59" s="48" t="s">
+      <c r="H59" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I59" s="47" t="s">
+      <c r="I59" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="J59" s="47" t="s">
+      <c r="J59" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="K59" s="47" t="s">
+      <c r="K59" s="33" t="s">
         <v>632</v>
       </c>
-      <c r="L59" s="47">
+      <c r="L59" s="33">
         <v>-100</v>
       </c>
-      <c r="M59" s="47">
-        <v>672.45</v>
-      </c>
-      <c r="N59" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O59" s="47">
-        <v>680.77</v>
-      </c>
-      <c r="P59" s="49">
+      <c r="M59" s="33">
+        <v>674.15</v>
+      </c>
+      <c r="N59" s="33">
+        <v>666.83</v>
+      </c>
+      <c r="O59" s="33">
+        <v>666.83</v>
+      </c>
+      <c r="P59" s="39">
         <f t="shared" si="10"/>
-        <v>67245</v>
-      </c>
-      <c r="Q59" s="47">
-        <v>3.45</v>
-      </c>
-      <c r="R59" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S59" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T59" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="U59" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V59" s="33">
-        <v>-108</v>
+        <v>67415</v>
+      </c>
+      <c r="Q59" s="33">
+        <v>3.25</v>
+      </c>
+      <c r="R59" s="33">
+        <v>1</v>
+      </c>
+      <c r="S59" s="40">
+        <f t="shared" si="12"/>
+        <v>1.0858117629607559E-2</v>
+      </c>
+      <c r="T59" s="33">
+        <v>880</v>
+      </c>
+      <c r="U59" s="41">
+        <v>880</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B60" s="34"/>
-      <c r="C60" s="34"/>
-      <c r="D60" s="35"/>
-      <c r="F60" s="36"/>
-      <c r="H60" s="36"/>
-      <c r="P60" s="39"/>
-      <c r="S60" s="40"/>
-      <c r="U60" s="39"/>
+      <c r="A60" s="33">
+        <v>54</v>
+      </c>
+      <c r="B60" s="34">
+        <v>46296</v>
+      </c>
+      <c r="C60" s="34">
+        <v>46296</v>
+      </c>
+      <c r="D60" s="35">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E60" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="F60" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="G60" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H60" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="I60" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="J60" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="K60" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="L60" s="33">
+        <v>200</v>
+      </c>
+      <c r="M60" s="33">
+        <v>326.27999999999997</v>
+      </c>
+      <c r="N60" s="33">
+        <v>332.03</v>
+      </c>
+      <c r="O60" s="33">
+        <v>332.03</v>
+      </c>
+      <c r="P60" s="39">
+        <f t="shared" si="10"/>
+        <v>65255.999999999993</v>
+      </c>
+      <c r="Q60" s="33">
+        <v>2.59</v>
+      </c>
+      <c r="R60" s="33">
+        <v>1</v>
+      </c>
+      <c r="S60" s="40">
+        <f t="shared" si="12"/>
+        <v>1.762290057619223E-2</v>
+      </c>
+      <c r="T60" s="33">
+        <v>1058</v>
+      </c>
+      <c r="U60" s="41">
+        <v>1058</v>
+      </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.25">
       <c r="F61" s="36"/>
@@ -6636,18 +6683,18 @@
         <v>103</v>
       </c>
       <c r="E62" s="46">
-        <f>AVERAGE(D2:D59)</f>
-        <v>5.9482758620689653</v>
+        <f>AVERAGE(D2:D60)</f>
+        <v>5.9152542372881358</v>
       </c>
       <c r="F62" s="36"/>
       <c r="H62" s="36"/>
       <c r="U62" s="39">
-        <f>SUM(U2:U50)</f>
-        <v>82039.47</v>
+        <f>SUM(U2:U60)</f>
+        <v>85382.47</v>
       </c>
       <c r="V62" s="39">
-        <f>SUM(V2:V59)</f>
-        <v>-981</v>
+        <f>SUM(V2:V60)</f>
+        <v>-4904</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
@@ -6655,8 +6702,8 @@
         <v>104</v>
       </c>
       <c r="E63" s="46">
-        <f>AVERAGE(D2:D11,D13,D15:D59)</f>
-        <v>4.0892857142857144</v>
+        <f>AVERAGE(D2:D11,D13,D15:D60)</f>
+        <v>4.0877192982456139</v>
       </c>
       <c r="F63" s="36"/>
       <c r="U63" s="53" t="s">
@@ -6676,7 +6723,7 @@
       <c r="F65" s="36"/>
       <c r="U65" s="39">
         <f>U62+V62</f>
-        <v>81058.47</v>
+        <v>80478.47</v>
       </c>
     </row>
     <row r="66" spans="6:21" x14ac:dyDescent="0.25">
@@ -6702,7 +6749,7 @@
     <row r="71" spans="6:21" x14ac:dyDescent="0.25">
       <c r="U71" s="54">
         <f>U65/U68</f>
-        <v>0.24341882882882884</v>
+        <v>0.2416770870870871</v>
       </c>
     </row>
   </sheetData>
@@ -6715,7 +6762,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:I81"/>
+  <dimension ref="A1:I82"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -6781,11 +6828,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C81" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C82" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D81" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D82" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -7961,10 +8008,12 @@
         <v>114</v>
       </c>
       <c r="G74" s="27">
-        <f>AVERAGE(C3:C81)</f>
-        <v>1059.2289873417717</v>
-      </c>
-      <c r="I74" s="27"/>
+        <f>AVERAGE(C3:C82)</f>
+        <v>1050.6761249999995</v>
+      </c>
+      <c r="I74" s="27">
+        <v>1055.5960759493667</v>
+      </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="26">
@@ -7986,10 +8035,12 @@
         <v>115</v>
       </c>
       <c r="G75" s="27">
-        <f>_xlfn.STDEV.S(C3:C81)</f>
-        <v>4143.4721139666781</v>
-      </c>
-      <c r="I75" s="27"/>
+        <f>_xlfn.STDEV.S(C3:C82)</f>
+        <v>4118.3458084033773</v>
+      </c>
+      <c r="I75" s="27">
+        <v>4144.4247725141895</v>
+      </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="26">
@@ -8012,9 +8063,11 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
-        <v>4.0581276835879025</v>
-      </c>
-      <c r="I76" s="28"/>
+        <v>4.0499188721124577</v>
+      </c>
+      <c r="I76" s="28">
+        <v>4.0432796180832771</v>
+      </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="26">
@@ -8036,10 +8089,12 @@
         <v>117</v>
       </c>
       <c r="G77" s="29">
-        <f>_xlfn.STDEV.S(D2:D81)*SQRT(252)</f>
-        <v>0.17881827902957989</v>
-      </c>
-      <c r="I77" s="29"/>
+        <f>_xlfn.STDEV.S(D2:D82)*SQRT(252)</f>
+        <v>0.17774657247085821</v>
+      </c>
+      <c r="I77" s="29">
+        <v>0.17885385081705873</v>
+      </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="26">
@@ -8061,10 +8116,12 @@
         <v>118</v>
       </c>
       <c r="G78" s="29" cm="1">
-        <f t="array" ref="G78">PRODUCT(1+D2:D81)-1</f>
-        <v>0.25094518307267766</v>
-      </c>
-      <c r="I78" s="29"/>
+        <f t="array" ref="G78">PRODUCT(1+D2:D82)-1</f>
+        <v>0.25206976970207151</v>
+      </c>
+      <c r="I78" s="29">
+        <v>0.25008449943898148</v>
+      </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="26">
@@ -8086,10 +8143,12 @@
         <v>119</v>
       </c>
       <c r="G79" s="29" cm="1">
-        <f t="array" ref="G79">PRODUCT(1+D2:D81)^(252/COUNT(D2:D81))-1</f>
-        <v>1.0244198140350593</v>
-      </c>
-      <c r="I79" s="29"/>
+        <f t="array" ref="G79">PRODUCT(1+D2:D82)^(252/COUNT(D2:D82))-1</f>
+        <v>1.0124875590957805</v>
+      </c>
+      <c r="I79" s="29">
+        <v>1.0200355656772704</v>
+      </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="26">
@@ -8113,16 +8172,33 @@
         <v>46295</v>
       </c>
       <c r="B81" s="5">
-        <f>B80+128</f>
-        <v>417135</v>
+        <f>B80-159</f>
+        <v>416848</v>
       </c>
       <c r="C81" s="5">
         <f t="shared" si="0"/>
-        <v>128</v>
+        <v>-159</v>
       </c>
       <c r="D81" s="23">
         <f t="shared" si="1"/>
-        <v>3.0694928382497176E-4</v>
+        <v>-3.812885635013321E-4</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A82" s="26">
+        <v>46296</v>
+      </c>
+      <c r="B82" s="5">
+        <f>B81+662</f>
+        <v>417510</v>
+      </c>
+      <c r="C82" s="5">
+        <f t="shared" si="0"/>
+        <v>662</v>
+      </c>
+      <c r="D82" s="23">
+        <f t="shared" si="1"/>
+        <v>1.5881088550262926E-3</v>
       </c>
     </row>
   </sheetData>
@@ -13076,7 +13152,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="14">
-        <f t="shared" ref="M69:M88" si="0">SUM(C69:L69)</f>
+        <f t="shared" ref="M69:M89" si="0">SUM(C69:L69)</f>
         <v>407651</v>
       </c>
       <c r="N69" s="15">
@@ -14163,7 +14239,7 @@
         <v>0</v>
       </c>
       <c r="S83" s="15">
-        <f>H83/M83</f>
+        <f t="shared" ref="S83:S88" si="22">H83/M83</f>
         <v>8.5840005770756692E-2</v>
       </c>
       <c r="T83" s="15">
@@ -14224,11 +14300,11 @@
         <v>416077</v>
       </c>
       <c r="N84" s="15">
-        <f t="shared" ref="N84" si="22">C84/M84</f>
+        <f t="shared" ref="N84" si="23">C84/M84</f>
         <v>0.17373466930399903</v>
       </c>
       <c r="O84" s="15">
-        <f t="shared" ref="O84" si="23">D84/M84</f>
+        <f t="shared" ref="O84" si="24">D84/M84</f>
         <v>0.70148073553693191</v>
       </c>
       <c r="P84" s="15">
@@ -14241,11 +14317,11 @@
         <v>0</v>
       </c>
       <c r="S84" s="15">
-        <f>H84/M84</f>
+        <f t="shared" si="22"/>
         <v>8.5801426178327575E-2</v>
       </c>
       <c r="T84" s="15">
-        <f t="shared" ref="T84" si="24">I84/M84</f>
+        <f t="shared" ref="T84" si="25">I84/M84</f>
         <v>0</v>
       </c>
       <c r="U84" s="15">
@@ -14256,7 +14332,7 @@
         <v>3.8983168980741542E-2</v>
       </c>
       <c r="W84" s="15">
-        <f t="shared" ref="W84" si="25">L84/M84</f>
+        <f t="shared" ref="W84" si="26">L84/M84</f>
         <v>0</v>
       </c>
     </row>
@@ -14303,11 +14379,11 @@
         <v>419561</v>
       </c>
       <c r="N85" s="15">
-        <f t="shared" ref="N85" si="26">C85/M85</f>
+        <f t="shared" ref="N85" si="27">C85/M85</f>
         <v>0.17229199091431283</v>
       </c>
       <c r="O85" s="15">
-        <f t="shared" ref="O85:O86" si="27">D85/M85</f>
+        <f t="shared" ref="O85:O86" si="28">D85/M85</f>
         <v>0.74261907088599755</v>
       </c>
       <c r="P85" s="15">
@@ -14320,11 +14396,11 @@
         <v>0</v>
       </c>
       <c r="S85" s="15">
-        <f>H85/M85</f>
+        <f t="shared" si="22"/>
         <v>8.508893819968967E-2</v>
       </c>
       <c r="T85" s="15">
-        <f t="shared" ref="T85" si="28">I85/M85</f>
+        <f t="shared" ref="T85" si="29">I85/M85</f>
         <v>0</v>
       </c>
       <c r="U85" s="15">
@@ -14335,7 +14411,7 @@
         <v>0</v>
       </c>
       <c r="W85" s="15">
-        <f t="shared" ref="W85" si="29">L85/M85</f>
+        <f t="shared" ref="W85" si="30">L85/M85</f>
         <v>0</v>
       </c>
     </row>
@@ -14381,11 +14457,11 @@
         <v>427887</v>
       </c>
       <c r="N86" s="15">
-        <f t="shared" ref="N86" si="30">C86/M86</f>
+        <f t="shared" ref="N86" si="31">C86/M86</f>
         <v>0.81923264787198491</v>
       </c>
       <c r="O86" s="15">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>0</v>
       </c>
       <c r="P86" s="15">
@@ -14398,11 +14474,11 @@
         <v>0</v>
       </c>
       <c r="S86" s="15">
-        <f>H86/M86</f>
+        <f t="shared" si="22"/>
         <v>8.3433242888893561E-2</v>
       </c>
       <c r="T86" s="15">
-        <f t="shared" ref="T86" si="31">I86/M86</f>
+        <f t="shared" ref="T86" si="32">I86/M86</f>
         <v>0</v>
       </c>
       <c r="U86" s="15">
@@ -14413,7 +14489,7 @@
         <v>0</v>
       </c>
       <c r="W86" s="15">
-        <f t="shared" ref="W86" si="32">L86/M86</f>
+        <f t="shared" ref="W86" si="33">L86/M86</f>
         <v>9.7334109239121544E-2</v>
       </c>
     </row>
@@ -14459,11 +14535,11 @@
         <v>610003</v>
       </c>
       <c r="N87" s="15">
-        <f t="shared" ref="N87" si="33">C87/M87</f>
+        <f t="shared" ref="N87" si="34">C87/M87</f>
         <v>0.57058899710329292</v>
       </c>
       <c r="O87" s="15">
-        <f t="shared" ref="O87" si="34">D87/M87</f>
+        <f t="shared" ref="O87" si="35">D87/M87</f>
         <v>0</v>
       </c>
       <c r="P87" s="15">
@@ -14476,11 +14552,11 @@
         <v>0</v>
       </c>
       <c r="S87" s="15">
-        <f>H87/M87</f>
+        <f t="shared" si="22"/>
         <v>8.6812687806453417E-2</v>
       </c>
       <c r="T87" s="15">
-        <f t="shared" ref="T87" si="35">I87/M87</f>
+        <f t="shared" ref="T87" si="36">I87/M87</f>
         <v>0</v>
       </c>
       <c r="U87" s="15">
@@ -14491,7 +14567,7 @@
         <v>0</v>
       </c>
       <c r="W87" s="15">
-        <f t="shared" ref="W87" si="36">L87/M87</f>
+        <f t="shared" ref="W87" si="37">L87/M87</f>
         <v>0.34259831509025368</v>
       </c>
     </row>
@@ -14537,11 +14613,11 @@
         <v>572683</v>
       </c>
       <c r="N88" s="15">
-        <f t="shared" ref="N88" si="37">C88/M88</f>
+        <f t="shared" ref="N88" si="38">C88/M88</f>
         <v>0.4883818796786355</v>
       </c>
       <c r="O88" s="15">
-        <f t="shared" ref="O88" si="38">D88/M88</f>
+        <f t="shared" ref="O88" si="39">D88/M88</f>
         <v>0</v>
       </c>
       <c r="P88" s="15">
@@ -14554,11 +14630,11 @@
         <v>0</v>
       </c>
       <c r="S88" s="15">
-        <f>H88/M88</f>
+        <f t="shared" si="22"/>
         <v>9.2470005221038515E-2</v>
       </c>
       <c r="T88" s="15">
-        <f t="shared" ref="T88" si="39">I88/M88</f>
+        <f t="shared" ref="T88" si="40">I88/M88</f>
         <v>0</v>
       </c>
       <c r="U88" s="15">
@@ -14569,8 +14645,87 @@
         <v>0</v>
       </c>
       <c r="W88" s="15">
-        <f t="shared" ref="W88" si="40">L88/M88</f>
+        <f t="shared" ref="W88" si="41">L88/M88</f>
         <v>0.41914811510032601</v>
+      </c>
+    </row>
+    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A89" s="10">
+        <v>46296</v>
+      </c>
+      <c r="B89" s="11">
+        <v>417510</v>
+      </c>
+      <c r="C89" s="19">
+        <v>164387</v>
+      </c>
+      <c r="D89" s="13">
+        <f>B89-C89-H89-L89</f>
+        <v>13084</v>
+      </c>
+      <c r="E89" s="13">
+        <v>0</v>
+      </c>
+      <c r="F89" s="13">
+        <v>0</v>
+      </c>
+      <c r="G89" s="13">
+        <v>0</v>
+      </c>
+      <c r="H89" s="13">
+        <v>0</v>
+      </c>
+      <c r="I89" s="13">
+        <v>0</v>
+      </c>
+      <c r="J89" s="13">
+        <v>0</v>
+      </c>
+      <c r="K89" s="13">
+        <v>0</v>
+      </c>
+      <c r="L89" s="18">
+        <v>240039</v>
+      </c>
+      <c r="M89" s="14">
+        <f t="shared" si="0"/>
+        <v>417510</v>
+      </c>
+      <c r="N89" s="15">
+        <f t="shared" ref="N89" si="42">C89/M89</f>
+        <v>0.39373188666139736</v>
+      </c>
+      <c r="O89" s="15">
+        <f t="shared" ref="O89" si="43">D89/M89</f>
+        <v>3.1338171540801416E-2</v>
+      </c>
+      <c r="P89" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="15">
+        <v>0</v>
+      </c>
+      <c r="R89" s="15">
+        <v>0</v>
+      </c>
+      <c r="S89" s="15">
+        <f t="shared" ref="S89" si="44">H89/M89</f>
+        <v>0</v>
+      </c>
+      <c r="T89" s="15">
+        <f t="shared" ref="T89" si="45">I89/M89</f>
+        <v>0</v>
+      </c>
+      <c r="U89" s="15">
+        <v>0</v>
+      </c>
+      <c r="V89" s="16">
+        <f>K89/M89</f>
+        <v>0</v>
+      </c>
+      <c r="W89" s="15">
+        <f t="shared" ref="W89" si="46">L89/M89</f>
+        <v>0.57492994179780121</v>
       </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.25">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{872267F4-2152-A64D-808C-3A788BCCAB32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{18343F33-73CC-AF45-8095-A00F4983201F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="23940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1520" yWindow="-42680" windowWidth="48520" windowHeight="32580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="964" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="634">
   <si>
     <t>Trade ID</t>
   </si>
@@ -2115,7 +2115,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2270,6 +2270,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2594,16 +2597,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V71"/>
+  <dimension ref="A1:V77"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.1640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="14.1640625" style="51" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14" style="51" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5" style="46" customWidth="1"/>
-    <col min="5" max="5" width="7.33203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="43.33203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="31.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9" style="33" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="57.6640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.33203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="43.1640625" style="33" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="13" style="33" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="12.33203125" style="33" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="10.5" style="33" bestFit="1" customWidth="1"/>
@@ -2611,7 +2614,7 @@
     <col min="14" max="16" width="11.83203125" style="33" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="7.5" style="33" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="10.1640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="15.83203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="18.1640625" style="33" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="10" style="33" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" style="33" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.83203125" style="33" bestFit="1" customWidth="1"/>
@@ -2747,7 +2750,7 @@
         <f t="shared" ref="S2:S12" si="2">IF(R2=1, ABS(N2-M2)/M2, 0)</f>
         <v>0.10949561071590727</v>
       </c>
-      <c r="T2" s="33">
+      <c r="T2" s="39">
         <v>11575</v>
       </c>
       <c r="U2" s="41">
@@ -2815,7 +2818,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T3" s="37">
+      <c r="T3" s="42">
         <v>-4105.18</v>
       </c>
       <c r="U3" s="43">
@@ -2882,7 +2885,7 @@
         <f t="shared" si="2"/>
         <v>5.0275118715610072E-2</v>
       </c>
-      <c r="T4" s="33">
+      <c r="T4" s="39">
         <v>-33350</v>
       </c>
       <c r="U4" s="41">
@@ -2950,7 +2953,7 @@
         <f t="shared" si="2"/>
         <v>3.8664932813178418E-3</v>
       </c>
-      <c r="T5" s="33">
+      <c r="T5" s="39">
         <v>11150</v>
       </c>
       <c r="U5" s="41">
@@ -3017,7 +3020,7 @@
         <f t="shared" si="2"/>
         <v>8.761368585972186E-2</v>
       </c>
-      <c r="T6" s="33">
+      <c r="T6" s="39">
         <v>40406.25</v>
       </c>
       <c r="U6" s="41">
@@ -3085,7 +3088,7 @@
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T7" s="33">
+      <c r="T7" s="39">
         <v>-6010</v>
       </c>
       <c r="U7" s="43">
@@ -3153,7 +3156,7 @@
         <f t="shared" si="2"/>
         <v>1.4981048673406688E-3</v>
       </c>
-      <c r="T8" s="33">
+      <c r="T8" s="39">
         <v>4681.25</v>
       </c>
       <c r="U8" s="41">
@@ -3221,7 +3224,7 @@
         <f t="shared" si="2"/>
         <v>5.6477269194499897E-3</v>
       </c>
-      <c r="T9" s="37">
+      <c r="T9" s="42">
         <v>-545</v>
       </c>
       <c r="U9" s="44">
@@ -3288,7 +3291,7 @@
         <f t="shared" si="2"/>
         <v>2.9847779636592513E-2</v>
       </c>
-      <c r="T10" s="37">
+      <c r="T10" s="42">
         <v>2883.2</v>
       </c>
       <c r="U10" s="44">
@@ -3355,7 +3358,7 @@
         <f t="shared" si="2"/>
         <v>3.5250463821892395E-3</v>
       </c>
-      <c r="T11" s="33">
+      <c r="T11" s="39">
         <v>-712.5</v>
       </c>
       <c r="U11" s="41">
@@ -3422,7 +3425,7 @@
         <f t="shared" si="2"/>
         <v>2.0497383883003945E-2</v>
       </c>
-      <c r="T12" s="37">
+      <c r="T12" s="42">
         <v>4588</v>
       </c>
       <c r="U12" s="41">
@@ -3490,7 +3493,7 @@
         <f t="shared" ref="S13:S19" si="3">IF(R13=1, ABS(N13-M13)/M13, 0)</f>
         <v>8.5709094212773618E-2</v>
       </c>
-      <c r="T13" s="37">
+      <c r="T13" s="42">
         <v>4717</v>
       </c>
       <c r="U13" s="44">
@@ -3557,7 +3560,7 @@
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T14" s="33">
+      <c r="T14" s="39">
         <v>-16354</v>
       </c>
       <c r="U14" s="45">
@@ -3625,7 +3628,7 @@
         <f t="shared" si="3"/>
         <v>2.2139625080801483E-2</v>
       </c>
-      <c r="T15" s="33">
+      <c r="T15" s="39">
         <v>2568.75</v>
       </c>
       <c r="U15" s="41">
@@ -3693,7 +3696,7 @@
         <f t="shared" si="3"/>
         <v>4.5693152386489792E-2</v>
       </c>
-      <c r="T16" s="37">
+      <c r="T16" s="42">
         <v>4149.45</v>
       </c>
       <c r="U16" s="44">
@@ -3751,6 +3754,9 @@
       <c r="P17" s="39">
         <v>232660</v>
       </c>
+      <c r="Q17" s="33">
+        <v>4.5999999999999996</v>
+      </c>
       <c r="R17" s="33">
         <v>1</v>
       </c>
@@ -3758,7 +3764,7 @@
         <f t="shared" si="3"/>
         <v>4.9999102817154174E-2</v>
       </c>
-      <c r="T17" s="33">
+      <c r="T17" s="39">
         <v>11150</v>
       </c>
       <c r="U17" s="41">
@@ -3816,6 +3822,9 @@
       <c r="P18" s="39">
         <v>101964</v>
       </c>
+      <c r="Q18" s="33">
+        <v>6.8</v>
+      </c>
       <c r="R18" s="33">
         <v>1</v>
       </c>
@@ -3823,7 +3832,7 @@
         <f t="shared" si="3"/>
         <v>2.0001183501982336E-2</v>
       </c>
-      <c r="T18" s="33">
+      <c r="T18" s="39">
         <v>2033</v>
       </c>
       <c r="U18" s="41">
@@ -3890,7 +3899,7 @@
         <f t="shared" si="3"/>
         <v>3.2654344970491629E-3</v>
       </c>
-      <c r="T19" s="33">
+      <c r="T19" s="39">
         <v>177</v>
       </c>
       <c r="U19" s="41">
@@ -3957,7 +3966,7 @@
         <f>IF(R20=1, ABS(N20-M20)/M20, 0)</f>
         <v>4.3449412469766758E-3</v>
       </c>
-      <c r="T20" s="33">
+      <c r="T20" s="39">
         <v>4060</v>
       </c>
       <c r="U20" s="41">
@@ -4024,7 +4033,7 @@
         <f>IF(R21=1, ABS(N21-M21)/M21, 0)</f>
         <v>8.6259263758959263E-3</v>
       </c>
-      <c r="T21" s="33">
+      <c r="T21" s="39">
         <v>1420</v>
       </c>
       <c r="U21" s="41">
@@ -4091,7 +4100,7 @@
         <f>IF(R22=1, ABS(N22-M22)/M22, 0)</f>
         <v>9.435785134612908E-3</v>
       </c>
-      <c r="T22" s="33">
+      <c r="T22" s="39">
         <v>1418</v>
       </c>
       <c r="U22" s="41">
@@ -4158,7 +4167,7 @@
         <f>IF(R23=1, ABS(N23-M23)/M23, 0)</f>
         <v>3.5589713272243556E-2</v>
       </c>
-      <c r="T23" s="33">
+      <c r="T23" s="39">
         <v>6742</v>
       </c>
       <c r="U23" s="41">
@@ -4224,7 +4233,7 @@
       <c r="S24" s="40">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="T24" s="33">
+      <c r="T24" s="39">
         <v>1245</v>
       </c>
       <c r="U24" s="41">
@@ -4291,7 +4300,7 @@
         <f t="shared" ref="S25:S36" si="4">IF(R25=1, ABS(N25-M25)/M25, 0)</f>
         <v>3.9539800653504951E-3</v>
       </c>
-      <c r="T25" s="33">
+      <c r="T25" s="39">
         <v>1710</v>
       </c>
       <c r="U25" s="41">
@@ -4309,7 +4318,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D60" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D61" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
@@ -4358,7 +4367,7 @@
         <f t="shared" si="4"/>
         <v>8.4025752021974973E-3</v>
       </c>
-      <c r="T26" s="33">
+      <c r="T26" s="39">
         <v>715</v>
       </c>
       <c r="U26" s="41">
@@ -4424,7 +4433,7 @@
         <f t="shared" si="4"/>
         <v>2.623408180713668E-2</v>
       </c>
-      <c r="T27" s="33">
+      <c r="T27" s="39">
         <v>3498</v>
       </c>
       <c r="U27" s="41">
@@ -4491,7 +4500,7 @@
         <f t="shared" si="4"/>
         <v>3.0251341995685504E-2</v>
       </c>
-      <c r="T28" s="33">
+      <c r="T28" s="39">
         <v>1809</v>
       </c>
       <c r="U28" s="41">
@@ -4558,7 +4567,7 @@
         <f t="shared" si="4"/>
         <v>2.7141972539147393E-3</v>
       </c>
-      <c r="T29" s="33">
+      <c r="T29" s="39">
         <v>2891</v>
       </c>
       <c r="U29" s="41">
@@ -4625,7 +4634,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="T30" s="33">
+      <c r="T30" s="39">
         <v>-642</v>
       </c>
       <c r="U30" s="45">
@@ -4692,7 +4701,7 @@
         <f t="shared" si="4"/>
         <v>8.455326735182055E-3</v>
       </c>
-      <c r="T31" s="33">
+      <c r="T31" s="39">
         <v>4108</v>
       </c>
       <c r="U31" s="41">
@@ -4759,7 +4768,7 @@
         <f t="shared" si="4"/>
         <v>1.8185412136785959E-2</v>
       </c>
-      <c r="T32" s="33">
+      <c r="T32" s="39">
         <v>7389</v>
       </c>
       <c r="U32" s="41">
@@ -4826,7 +4835,7 @@
         <f t="shared" si="4"/>
         <v>1.9886363636363667E-2</v>
       </c>
-      <c r="T33" s="33">
+      <c r="T33" s="39">
         <v>2247</v>
       </c>
       <c r="U33" s="41">
@@ -4893,7 +4902,7 @@
         <f t="shared" si="4"/>
         <v>9.8159124408065835E-3</v>
       </c>
-      <c r="T34" s="33">
+      <c r="T34" s="39">
         <v>1253</v>
       </c>
       <c r="U34" s="41">
@@ -4960,7 +4969,7 @@
         <f t="shared" si="4"/>
         <v>5.3725127878096988E-3</v>
       </c>
-      <c r="T35" s="33">
+      <c r="T35" s="39">
         <v>141</v>
       </c>
       <c r="U35" s="41">
@@ -5027,7 +5036,7 @@
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="T36" s="33">
+      <c r="T36" s="39">
         <v>-3825</v>
       </c>
       <c r="U36" s="45">
@@ -5094,7 +5103,7 @@
         <f t="shared" ref="S37:S40" si="6">IF(R37=1, ABS(N37-M37)/M37, 0)</f>
         <v>1.2137203166226873E-2</v>
       </c>
-      <c r="T37" s="33">
+      <c r="T37" s="39">
         <v>345</v>
       </c>
       <c r="U37" s="41">
@@ -5161,7 +5170,7 @@
         <f t="shared" si="6"/>
         <v>1.8280016618196831E-3</v>
       </c>
-      <c r="T38" s="33">
+      <c r="T38" s="39">
         <v>220</v>
       </c>
       <c r="U38" s="41">
@@ -5229,7 +5238,7 @@
         <f t="shared" si="6"/>
         <v>2.3968322438641332E-2</v>
       </c>
-      <c r="T39" s="33">
+      <c r="T39" s="39">
         <v>2167</v>
       </c>
       <c r="U39" s="41">
@@ -5297,7 +5306,7 @@
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T40" s="33">
+      <c r="T40" s="39">
         <v>-438</v>
       </c>
       <c r="U40" s="45">
@@ -5364,7 +5373,7 @@
         <f t="shared" ref="S41:S44" si="7">IF(R41=1, ABS(N41-M41)/M41, 0)</f>
         <v>0</v>
       </c>
-      <c r="T41" s="33">
+      <c r="T41" s="39">
         <v>-317</v>
       </c>
       <c r="U41" s="45">
@@ -5432,7 +5441,7 @@
         <f t="shared" si="7"/>
         <v>1.9242297247460509E-2</v>
       </c>
-      <c r="T42" s="33">
+      <c r="T42" s="39">
         <v>1721</v>
       </c>
       <c r="U42" s="41">
@@ -5449,7 +5458,7 @@
       <c r="C43" s="55">
         <v>46295</v>
       </c>
-      <c r="D43" s="35">
+      <c r="D43" s="56">
         <f t="shared" si="5"/>
         <v>9</v>
       </c>
@@ -5484,7 +5493,7 @@
         <v>72</v>
       </c>
       <c r="O43" s="47">
-        <v>163</v>
+        <v>165.15</v>
       </c>
       <c r="P43" s="49">
         <f>ABS(M43*L43)</f>
@@ -5499,14 +5508,14 @@
       <c r="S43" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="T43" s="47" t="s">
+      <c r="T43" s="49" t="s">
         <v>72</v>
       </c>
       <c r="U43" s="49" t="s">
         <v>72</v>
       </c>
       <c r="V43" s="33">
-        <v>-1050</v>
+        <v>-2427</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
@@ -5570,7 +5579,7 @@
         <f t="shared" si="7"/>
         <v>9.1189909260570284E-3</v>
       </c>
-      <c r="T44" s="33">
+      <c r="T44" s="39">
         <v>1134</v>
       </c>
       <c r="U44" s="41">
@@ -5637,7 +5646,7 @@
         <f t="shared" ref="S45:S48" si="8">IF(R45=1, ABS(N45-M45)/M45, 0)</f>
         <v>6.6957880304817775E-4</v>
       </c>
-      <c r="T45" s="33">
+      <c r="T45" s="39">
         <v>108</v>
       </c>
       <c r="U45" s="41">
@@ -5705,7 +5714,7 @@
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T46" s="33">
+      <c r="T46" s="39">
         <v>-664</v>
       </c>
       <c r="U46" s="45">
@@ -5722,7 +5731,7 @@
       <c r="C47" s="55">
         <v>46295</v>
       </c>
-      <c r="D47" s="35">
+      <c r="D47" s="56">
         <f t="shared" si="5"/>
         <v>7</v>
       </c>
@@ -5757,7 +5766,7 @@
         <v>72</v>
       </c>
       <c r="O47" s="47">
-        <v>271</v>
+        <v>272.49</v>
       </c>
       <c r="P47" s="49">
         <f>ABS(M47*L47)</f>
@@ -5772,14 +5781,14 @@
       <c r="S47" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="T47" s="47" t="s">
+      <c r="T47" s="49" t="s">
         <v>72</v>
       </c>
       <c r="U47" s="49" t="s">
         <v>72</v>
       </c>
       <c r="V47" s="33">
-        <v>-2353</v>
+        <v>-3006</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
@@ -5843,7 +5852,7 @@
         <f t="shared" si="8"/>
         <v>3.5463403580330705E-2</v>
       </c>
-      <c r="T48" s="33">
+      <c r="T48" s="39">
         <v>1895</v>
       </c>
       <c r="U48" s="41">
@@ -5907,10 +5916,10 @@
         <v>1</v>
       </c>
       <c r="S49" s="40">
-        <f t="shared" ref="S49:S51" si="9">IF(R49=1, ABS(N49-M49)/M49, 0)</f>
+        <f t="shared" ref="S49:S53" si="9">IF(R49=1, ABS(N49-M49)/M49, 0)</f>
         <v>2.0138262699128395E-2</v>
       </c>
-      <c r="T49" s="33">
+      <c r="T49" s="39">
         <v>338</v>
       </c>
       <c r="U49" s="41">
@@ -5977,7 +5986,7 @@
         <f t="shared" si="9"/>
         <v>1.0891738306862922E-2</v>
       </c>
-      <c r="T50" s="33">
+      <c r="T50" s="39">
         <v>2245</v>
       </c>
       <c r="U50" s="41">
@@ -6032,7 +6041,7 @@
         <v>82.27</v>
       </c>
       <c r="P51" s="39">
-        <f t="shared" ref="P51:P60" si="10">ABS(M51*L51)</f>
+        <f t="shared" ref="P51:P61" si="10">ABS(M51*L51)</f>
         <v>59087</v>
       </c>
       <c r="Q51" s="33">
@@ -6045,7 +6054,7 @@
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T51" s="33">
+      <c r="T51" s="39">
         <v>-1498</v>
       </c>
       <c r="U51" s="45">
@@ -6062,7 +6071,7 @@
       <c r="C52" s="55">
         <v>46295</v>
       </c>
-      <c r="D52" s="35">
+      <c r="D52" s="56">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
@@ -6097,7 +6106,7 @@
         <v>72</v>
       </c>
       <c r="O52" s="47">
-        <v>104.02</v>
+        <v>104.11</v>
       </c>
       <c r="P52" s="49">
         <f t="shared" si="10"/>
@@ -6112,14 +6121,14 @@
       <c r="S52" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="T52" s="47" t="s">
+      <c r="T52" s="49" t="s">
         <v>72</v>
       </c>
       <c r="U52" s="49" t="s">
         <v>72</v>
       </c>
       <c r="V52" s="33">
-        <v>132</v>
+        <v>-12</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
@@ -6129,67 +6138,65 @@
       <c r="B53" s="34">
         <v>46293</v>
       </c>
-      <c r="C53" s="55">
-        <v>46295</v>
+      <c r="C53" s="34">
+        <v>46297</v>
       </c>
       <c r="D53" s="35">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="E53" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="E53" s="33" t="s">
         <v>619</v>
       </c>
-      <c r="F53" s="48" t="s">
+      <c r="F53" s="36" t="s">
         <v>620</v>
       </c>
-      <c r="G53" s="47" t="s">
+      <c r="G53" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H53" s="48" t="s">
+      <c r="H53" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I53" s="47" t="s">
+      <c r="I53" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="J53" s="47" t="s">
+      <c r="J53" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="K53" s="47" t="s">
+      <c r="K53" s="33" t="s">
         <v>619</v>
       </c>
-      <c r="L53" s="47">
+      <c r="L53" s="33">
         <v>-110</v>
       </c>
-      <c r="M53" s="47">
-        <v>446.98</v>
-      </c>
-      <c r="N53" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O53" s="47">
-        <v>457.08</v>
-      </c>
-      <c r="P53" s="49">
+      <c r="M53" s="33">
+        <v>447.99</v>
+      </c>
+      <c r="N53" s="33">
+        <v>466.29</v>
+      </c>
+      <c r="O53" s="33">
+        <v>466.29</v>
+      </c>
+      <c r="P53" s="39">
         <f t="shared" si="10"/>
-        <v>49167.8</v>
-      </c>
-      <c r="Q53" s="47">
-        <v>2.33</v>
-      </c>
-      <c r="R53" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S53" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T53" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="U53" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V53" s="33">
-        <v>-1925</v>
+        <v>49278.9</v>
+      </c>
+      <c r="Q53" s="33">
+        <v>2.68</v>
+      </c>
+      <c r="R53" s="33">
+        <v>0</v>
+      </c>
+      <c r="S53" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="T53" s="39">
+        <v>-2013</v>
+      </c>
+      <c r="U53" s="45">
+        <v>-2013</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -6253,7 +6260,7 @@
         <f t="shared" ref="S54" si="11">IF(R54=1, ABS(N54-M54)/M54, 0)</f>
         <v>0</v>
       </c>
-      <c r="T54" s="33">
+      <c r="T54" s="39">
         <v>-214</v>
       </c>
       <c r="U54" s="45">
@@ -6270,7 +6277,7 @@
       <c r="C55" s="55">
         <v>46295</v>
       </c>
-      <c r="D55" s="35">
+      <c r="D55" s="56">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -6305,7 +6312,7 @@
         <v>72</v>
       </c>
       <c r="O55" s="47">
-        <v>278</v>
+        <v>282.10000000000002</v>
       </c>
       <c r="P55" s="49">
         <f t="shared" si="10"/>
@@ -6320,7 +6327,7 @@
       <c r="S55" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="T55" s="47" t="s">
+      <c r="T55" s="49" t="s">
         <v>72</v>
       </c>
       <c r="U55" s="49" t="s">
@@ -6340,7 +6347,7 @@
       <c r="C56" s="55">
         <v>46295</v>
       </c>
-      <c r="D56" s="35">
+      <c r="D56" s="56">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -6375,7 +6382,7 @@
         <v>72</v>
       </c>
       <c r="O56" s="47">
-        <v>764.59</v>
+        <v>770.94</v>
       </c>
       <c r="P56" s="49">
         <f t="shared" si="10"/>
@@ -6390,14 +6397,14 @@
       <c r="S56" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="T56" s="47" t="s">
+      <c r="T56" s="49" t="s">
         <v>72</v>
       </c>
       <c r="U56" s="49" t="s">
         <v>72</v>
       </c>
       <c r="V56" s="33">
-        <v>-375</v>
+        <v>-443</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.25">
@@ -6410,7 +6417,7 @@
       <c r="C57" s="55">
         <v>46295</v>
       </c>
-      <c r="D57" s="35">
+      <c r="D57" s="56">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -6460,7 +6467,7 @@
       <c r="S57" s="50" t="s">
         <v>72</v>
       </c>
-      <c r="T57" s="47" t="s">
+      <c r="T57" s="49" t="s">
         <v>72</v>
       </c>
       <c r="U57" s="49" t="s">
@@ -6531,7 +6538,7 @@
         <f t="shared" ref="S58:S60" si="12">IF(R58=1, ABS(N58-M58)/M58, 0)</f>
         <v>2.7360178970917266E-2</v>
       </c>
-      <c r="T58" s="33">
+      <c r="T58" s="39">
         <v>1222</v>
       </c>
       <c r="U58" s="41">
@@ -6599,7 +6606,7 @@
         <f t="shared" si="12"/>
         <v>1.0858117629607559E-2</v>
       </c>
-      <c r="T59" s="33">
+      <c r="T59" s="39">
         <v>880</v>
       </c>
       <c r="U59" s="41">
@@ -6667,7 +6674,7 @@
         <f t="shared" si="12"/>
         <v>1.762290057619223E-2</v>
       </c>
-      <c r="T60" s="33">
+      <c r="T60" s="39">
         <v>1058</v>
       </c>
       <c r="U60" s="41">
@@ -6675,81 +6682,206 @@
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F61" s="36"/>
-      <c r="H61" s="36"/>
+      <c r="A61" s="33">
+        <v>55</v>
+      </c>
+      <c r="B61" s="34">
+        <v>46297</v>
+      </c>
+      <c r="C61" s="55">
+        <v>46297</v>
+      </c>
+      <c r="D61" s="56">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E61" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="F61" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="G61" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H61" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I61" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="J61" s="47" t="s">
+        <v>532</v>
+      </c>
+      <c r="K61" s="47" t="s">
+        <v>608</v>
+      </c>
+      <c r="L61" s="47">
+        <v>10</v>
+      </c>
+      <c r="M61" s="47">
+        <v>17.91</v>
+      </c>
+      <c r="N61" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O61" s="47">
+        <v>17.68</v>
+      </c>
+      <c r="P61" s="49">
+        <f>ABS(M61*L61)*100</f>
+        <v>17910</v>
+      </c>
+      <c r="Q61" s="47">
+        <v>1.88</v>
+      </c>
+      <c r="R61" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S61" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T61" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="U61" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V61" s="33">
+        <v>-250</v>
+      </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D62" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="E62" s="46">
-        <f>AVERAGE(D2:D60)</f>
-        <v>5.9152542372881358</v>
-      </c>
+      <c r="B62" s="34"/>
+      <c r="C62" s="34"/>
+      <c r="D62" s="35"/>
       <c r="F62" s="36"/>
       <c r="H62" s="36"/>
-      <c r="U62" s="39">
-        <f>SUM(U2:U60)</f>
-        <v>85382.47</v>
-      </c>
-      <c r="V62" s="39">
-        <f>SUM(V2:V60)</f>
-        <v>-4904</v>
-      </c>
+      <c r="P62" s="39"/>
+      <c r="S62" s="40"/>
+      <c r="T62" s="39"/>
+      <c r="U62" s="41"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="D63" s="52" t="s">
+      <c r="B63" s="34"/>
+      <c r="C63" s="34"/>
+      <c r="D63" s="35"/>
+      <c r="F63" s="36"/>
+      <c r="H63" s="36"/>
+      <c r="P63" s="39"/>
+      <c r="S63" s="40"/>
+      <c r="T63" s="39"/>
+      <c r="U63" s="41"/>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B64" s="34"/>
+      <c r="C64" s="34"/>
+      <c r="D64" s="35"/>
+      <c r="F64" s="36"/>
+      <c r="H64" s="36"/>
+      <c r="P64" s="39"/>
+      <c r="S64" s="40"/>
+      <c r="T64" s="39"/>
+      <c r="U64" s="41"/>
+    </row>
+    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B65" s="34"/>
+      <c r="C65" s="34"/>
+      <c r="D65" s="35"/>
+      <c r="F65" s="36"/>
+      <c r="H65" s="36"/>
+      <c r="P65" s="39"/>
+      <c r="S65" s="40"/>
+      <c r="T65" s="39"/>
+      <c r="U65" s="41"/>
+    </row>
+    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="B66" s="34"/>
+      <c r="C66" s="34"/>
+      <c r="D66" s="35"/>
+      <c r="F66" s="36"/>
+      <c r="H66" s="36"/>
+      <c r="P66" s="39"/>
+      <c r="S66" s="40"/>
+      <c r="T66" s="39"/>
+      <c r="U66" s="41"/>
+    </row>
+    <row r="67" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="F67" s="36"/>
+      <c r="H67" s="36"/>
+    </row>
+    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="D68" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="E68" s="46">
+        <f>AVERAGE(D2:D60)</f>
+        <v>5.9491525423728815</v>
+      </c>
+      <c r="F68" s="36"/>
+      <c r="H68" s="36"/>
+      <c r="U68" s="39">
+        <f>SUM(U2:U66)</f>
+        <v>83369.47</v>
+      </c>
+      <c r="V68" s="39">
+        <f>SUM(V2:V66)</f>
+        <v>-5471</v>
+      </c>
+    </row>
+    <row r="69" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="D69" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="E63" s="46">
+      <c r="E69" s="46">
         <f>AVERAGE(D2:D11,D13,D15:D60)</f>
-        <v>4.0877192982456139</v>
-      </c>
-      <c r="F63" s="36"/>
-      <c r="U63" s="53" t="s">
+        <v>4.1228070175438596</v>
+      </c>
+      <c r="F69" s="36"/>
+      <c r="U69" s="53" t="s">
         <v>105</v>
       </c>
-      <c r="V63" s="36" t="s">
+      <c r="V69" s="36" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="F64" s="36"/>
-      <c r="U64" s="33" t="s">
+    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="F70" s="36"/>
+      <c r="U70" s="33" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="65" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F65" s="36"/>
-      <c r="U65" s="39">
-        <f>U62+V62</f>
-        <v>80478.47</v>
-      </c>
-    </row>
-    <row r="66" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F66" s="36"/>
-    </row>
-    <row r="67" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F67" s="36"/>
-      <c r="U67" s="36" t="s">
+    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="F71" s="36"/>
+      <c r="U71" s="39">
+        <f>U68+V68</f>
+        <v>77898.47</v>
+      </c>
+    </row>
+    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="F72" s="36"/>
+    </row>
+    <row r="73" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="F73" s="36"/>
+      <c r="U73" s="36" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="68" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="F68" s="36"/>
-      <c r="U68" s="39">
+    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="F74" s="36"/>
+      <c r="U74" s="39">
         <v>333000</v>
       </c>
     </row>
-    <row r="70" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="U70" s="33" t="s">
+    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="U76" s="33" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="71" spans="6:21" x14ac:dyDescent="0.25">
-      <c r="U71" s="54">
-        <f>U65/U68</f>
-        <v>0.2416770870870871</v>
+    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="U77" s="54">
+        <f>U71/U74</f>
+        <v>0.23392933933933935</v>
       </c>
     </row>
   </sheetData>
@@ -6762,7 +6894,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:I82"/>
+  <dimension ref="A1:I83"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -6828,11 +6960,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C82" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C83" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D82" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D83" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -8008,11 +8140,11 @@
         <v>114</v>
       </c>
       <c r="G74" s="27">
-        <f>AVERAGE(C3:C82)</f>
+        <f>AVERAGE(C3:C83)</f>
+        <v>996.54432098765392</v>
+      </c>
+      <c r="I74" s="27">
         <v>1050.6761249999995</v>
-      </c>
-      <c r="I74" s="27">
-        <v>1055.5960759493667</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -8035,11 +8167,11 @@
         <v>115</v>
       </c>
       <c r="G75" s="27">
-        <f>_xlfn.STDEV.S(C3:C82)</f>
+        <f>_xlfn.STDEV.S(C3:C83)</f>
+        <v>4121.4212322668327</v>
+      </c>
+      <c r="I75" s="27">
         <v>4118.3458084033773</v>
-      </c>
-      <c r="I75" s="27">
-        <v>4144.4247725141895</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
@@ -8063,10 +8195,10 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
+        <v>3.8383969439642409</v>
+      </c>
+      <c r="I76" s="28">
         <v>4.0499188721124577</v>
-      </c>
-      <c r="I76" s="28">
-        <v>4.0432796180832771</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
@@ -8089,11 +8221,11 @@
         <v>117</v>
       </c>
       <c r="G77" s="29">
-        <f>_xlfn.STDEV.S(D2:D82)*SQRT(252)</f>
+        <f>_xlfn.STDEV.S(D2:D83)*SQRT(252)</f>
+        <v>0.17766253922781455</v>
+      </c>
+      <c r="I77" s="29">
         <v>0.17774657247085821</v>
-      </c>
-      <c r="I77" s="29">
-        <v>0.17885385081705873</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -8116,11 +8248,11 @@
         <v>118</v>
       </c>
       <c r="G78" s="29" cm="1">
-        <f t="array" ref="G78">PRODUCT(1+D2:D82)-1</f>
+        <f t="array" ref="G78">PRODUCT(1+D3:D83)-1</f>
+        <v>0.24207144484233956</v>
+      </c>
+      <c r="I78" s="29">
         <v>0.25206976970207151</v>
-      </c>
-      <c r="I78" s="29">
-        <v>0.25008449943898148</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -8143,11 +8275,11 @@
         <v>119</v>
       </c>
       <c r="G79" s="29" cm="1">
-        <f t="array" ref="G79">PRODUCT(1+D2:D82)^(252/COUNT(D2:D82))-1</f>
+        <f t="array" ref="G79">PRODUCT(1+D2:D83)^(252/COUNT(D2:D83))-1</f>
+        <v>0.94683213592105586</v>
+      </c>
+      <c r="I79" s="29">
         <v>1.0124875590957805</v>
-      </c>
-      <c r="I79" s="29">
-        <v>1.0200355656772704</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -8199,6 +8331,23 @@
       <c r="D82" s="23">
         <f t="shared" si="1"/>
         <v>1.5881088550262926E-3</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A83" s="26">
+        <v>46297</v>
+      </c>
+      <c r="B83" s="5">
+        <f>B82-3334</f>
+        <v>414176</v>
+      </c>
+      <c r="C83" s="5">
+        <f t="shared" si="0"/>
+        <v>-3334</v>
+      </c>
+      <c r="D83" s="23">
+        <f t="shared" si="1"/>
+        <v>-7.9854374745515072E-3</v>
       </c>
     </row>
   </sheetData>
@@ -13152,7 +13301,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="14">
-        <f t="shared" ref="M69:M89" si="0">SUM(C69:L69)</f>
+        <f t="shared" ref="M69:M90" si="0">SUM(C69:L69)</f>
         <v>407651</v>
       </c>
       <c r="N69" s="15">
@@ -14328,11 +14477,11 @@
         <v>0</v>
       </c>
       <c r="V84" s="16">
-        <f>K84/M84</f>
+        <f t="shared" ref="V84:V89" si="26">K84/M84</f>
         <v>3.8983168980741542E-2</v>
       </c>
       <c r="W84" s="15">
-        <f t="shared" ref="W84" si="26">L84/M84</f>
+        <f t="shared" ref="W84" si="27">L84/M84</f>
         <v>0</v>
       </c>
     </row>
@@ -14379,11 +14528,11 @@
         <v>419561</v>
       </c>
       <c r="N85" s="15">
-        <f t="shared" ref="N85" si="27">C85/M85</f>
+        <f t="shared" ref="N85" si="28">C85/M85</f>
         <v>0.17229199091431283</v>
       </c>
       <c r="O85" s="15">
-        <f t="shared" ref="O85:O86" si="28">D85/M85</f>
+        <f t="shared" ref="O85:O86" si="29">D85/M85</f>
         <v>0.74261907088599755</v>
       </c>
       <c r="P85" s="15">
@@ -14400,18 +14549,18 @@
         <v>8.508893819968967E-2</v>
       </c>
       <c r="T85" s="15">
-        <f t="shared" ref="T85" si="29">I85/M85</f>
+        <f t="shared" ref="T85" si="30">I85/M85</f>
         <v>0</v>
       </c>
       <c r="U85" s="15">
         <v>0</v>
       </c>
       <c r="V85" s="16">
-        <f>K85/M85</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="W85" s="15">
-        <f t="shared" ref="W85" si="30">L85/M85</f>
+        <f t="shared" ref="W85" si="31">L85/M85</f>
         <v>0</v>
       </c>
     </row>
@@ -14457,11 +14606,11 @@
         <v>427887</v>
       </c>
       <c r="N86" s="15">
-        <f t="shared" ref="N86" si="31">C86/M86</f>
+        <f t="shared" ref="N86" si="32">C86/M86</f>
         <v>0.81923264787198491</v>
       </c>
       <c r="O86" s="15">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>0</v>
       </c>
       <c r="P86" s="15">
@@ -14478,18 +14627,18 @@
         <v>8.3433242888893561E-2</v>
       </c>
       <c r="T86" s="15">
-        <f t="shared" ref="T86" si="32">I86/M86</f>
+        <f t="shared" ref="T86" si="33">I86/M86</f>
         <v>0</v>
       </c>
       <c r="U86" s="15">
         <v>0</v>
       </c>
       <c r="V86" s="16">
-        <f>K86/M86</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="W86" s="15">
-        <f t="shared" ref="W86" si="33">L86/M86</f>
+        <f t="shared" ref="W86" si="34">L86/M86</f>
         <v>9.7334109239121544E-2</v>
       </c>
     </row>
@@ -14535,11 +14684,11 @@
         <v>610003</v>
       </c>
       <c r="N87" s="15">
-        <f t="shared" ref="N87" si="34">C87/M87</f>
+        <f t="shared" ref="N87" si="35">C87/M87</f>
         <v>0.57058899710329292</v>
       </c>
       <c r="O87" s="15">
-        <f t="shared" ref="O87" si="35">D87/M87</f>
+        <f t="shared" ref="O87" si="36">D87/M87</f>
         <v>0</v>
       </c>
       <c r="P87" s="15">
@@ -14556,18 +14705,18 @@
         <v>8.6812687806453417E-2</v>
       </c>
       <c r="T87" s="15">
-        <f t="shared" ref="T87" si="36">I87/M87</f>
+        <f t="shared" ref="T87" si="37">I87/M87</f>
         <v>0</v>
       </c>
       <c r="U87" s="15">
         <v>0</v>
       </c>
       <c r="V87" s="16">
-        <f>K87/M87</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="W87" s="15">
-        <f t="shared" ref="W87" si="37">L87/M87</f>
+        <f t="shared" ref="W87" si="38">L87/M87</f>
         <v>0.34259831509025368</v>
       </c>
     </row>
@@ -14613,11 +14762,11 @@
         <v>572683</v>
       </c>
       <c r="N88" s="15">
-        <f t="shared" ref="N88" si="38">C88/M88</f>
+        <f t="shared" ref="N88" si="39">C88/M88</f>
         <v>0.4883818796786355</v>
       </c>
       <c r="O88" s="15">
-        <f t="shared" ref="O88" si="39">D88/M88</f>
+        <f t="shared" ref="O88" si="40">D88/M88</f>
         <v>0</v>
       </c>
       <c r="P88" s="15">
@@ -14634,18 +14783,18 @@
         <v>9.2470005221038515E-2</v>
       </c>
       <c r="T88" s="15">
-        <f t="shared" ref="T88" si="40">I88/M88</f>
+        <f t="shared" ref="T88" si="41">I88/M88</f>
         <v>0</v>
       </c>
       <c r="U88" s="15">
         <v>0</v>
       </c>
       <c r="V88" s="16">
-        <f>K88/M88</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="W88" s="15">
-        <f t="shared" ref="W88" si="41">L88/M88</f>
+        <f t="shared" ref="W88" si="42">L88/M88</f>
         <v>0.41914811510032601</v>
       </c>
     </row>
@@ -14692,11 +14841,11 @@
         <v>417510</v>
       </c>
       <c r="N89" s="15">
-        <f t="shared" ref="N89" si="42">C89/M89</f>
+        <f t="shared" ref="N89" si="43">C89/M89</f>
         <v>0.39373188666139736</v>
       </c>
       <c r="O89" s="15">
-        <f t="shared" ref="O89" si="43">D89/M89</f>
+        <f t="shared" ref="O89" si="44">D89/M89</f>
         <v>3.1338171540801416E-2</v>
       </c>
       <c r="P89" s="15">
@@ -14709,23 +14858,102 @@
         <v>0</v>
       </c>
       <c r="S89" s="15">
-        <f t="shared" ref="S89" si="44">H89/M89</f>
+        <f t="shared" ref="S89" si="45">H89/M89</f>
         <v>0</v>
       </c>
       <c r="T89" s="15">
-        <f t="shared" ref="T89" si="45">I89/M89</f>
+        <f t="shared" ref="T89" si="46">I89/M89</f>
         <v>0</v>
       </c>
       <c r="U89" s="15">
         <v>0</v>
       </c>
       <c r="V89" s="16">
-        <f>K89/M89</f>
+        <f t="shared" si="26"/>
         <v>0</v>
       </c>
       <c r="W89" s="15">
-        <f t="shared" ref="W89" si="46">L89/M89</f>
+        <f t="shared" ref="W89" si="47">L89/M89</f>
         <v>0.57492994179780121</v>
+      </c>
+    </row>
+    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A90" s="10">
+        <v>46297</v>
+      </c>
+      <c r="B90" s="11">
+        <v>414176</v>
+      </c>
+      <c r="C90" s="19">
+        <v>115219</v>
+      </c>
+      <c r="D90" s="13">
+        <f>B90-C90-H90-L90</f>
+        <v>41258</v>
+      </c>
+      <c r="E90" s="13">
+        <v>0</v>
+      </c>
+      <c r="F90" s="13">
+        <v>0</v>
+      </c>
+      <c r="G90" s="13">
+        <v>0</v>
+      </c>
+      <c r="H90" s="13">
+        <v>17660</v>
+      </c>
+      <c r="I90" s="13">
+        <v>0</v>
+      </c>
+      <c r="J90" s="13">
+        <v>0</v>
+      </c>
+      <c r="K90" s="13">
+        <v>0</v>
+      </c>
+      <c r="L90" s="18">
+        <v>240039</v>
+      </c>
+      <c r="M90" s="14">
+        <f t="shared" si="0"/>
+        <v>414176</v>
+      </c>
+      <c r="N90" s="15">
+        <f t="shared" ref="N90" si="48">C90/M90</f>
+        <v>0.27818849957505987</v>
+      </c>
+      <c r="O90" s="15">
+        <f t="shared" ref="O90" si="49">D90/M90</f>
+        <v>9.9614656571119523E-2</v>
+      </c>
+      <c r="P90" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="15">
+        <v>0</v>
+      </c>
+      <c r="R90" s="15">
+        <v>0</v>
+      </c>
+      <c r="S90" s="15">
+        <f t="shared" ref="S90" si="50">H90/M90</f>
+        <v>4.2638878158077723E-2</v>
+      </c>
+      <c r="T90" s="15">
+        <f t="shared" ref="T90" si="51">I90/M90</f>
+        <v>0</v>
+      </c>
+      <c r="U90" s="15">
+        <v>0</v>
+      </c>
+      <c r="V90" s="16">
+        <f t="shared" ref="V90" si="52">K90/M90</f>
+        <v>0</v>
+      </c>
+      <c r="W90" s="15">
+        <f t="shared" ref="W90" si="53">L90/M90</f>
+        <v>0.57955796569574292</v>
       </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.25">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18343F33-73CC-AF45-8095-A00F4983201F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2BD4485-84B9-0648-BF09-29D8A9A021DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1520" yWindow="-42680" windowWidth="48520" windowHeight="32580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1080" yWindow="-42260" windowWidth="48520" windowHeight="32580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="635">
   <si>
     <t>Trade ID</t>
   </si>
@@ -1966,6 +1966,9 @@
   </si>
   <si>
     <t>Thermo Fisher Scientific</t>
+  </si>
+  <si>
+    <t>6EZ6</t>
   </si>
 </sst>
 </file>
@@ -4318,7 +4321,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D61" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D62" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
@@ -5484,23 +5487,23 @@
         <v>599</v>
       </c>
       <c r="L43" s="47">
-        <v>-300</v>
+        <v>-600</v>
       </c>
       <c r="M43" s="47">
-        <v>157.56</v>
+        <v>161.21</v>
       </c>
       <c r="N43" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O43" s="47">
-        <v>165.15</v>
+        <v>165.82</v>
       </c>
       <c r="P43" s="49">
-        <f>ABS(M43*L43)</f>
-        <v>47268</v>
+        <f>ABS(O43*L43)</f>
+        <v>99492</v>
       </c>
       <c r="Q43" s="47">
-        <v>1.02</v>
+        <v>4.88</v>
       </c>
       <c r="R43" s="47" t="s">
         <v>72</v>
@@ -5515,7 +5518,7 @@
         <v>72</v>
       </c>
       <c r="V43" s="33">
-        <v>-2427</v>
+        <v>-3660</v>
       </c>
     </row>
     <row r="44" spans="1:22" x14ac:dyDescent="0.25">
@@ -5757,23 +5760,23 @@
         <v>606</v>
       </c>
       <c r="L47" s="47">
-        <v>-260</v>
+        <v>-450</v>
       </c>
       <c r="M47" s="47">
-        <v>261.35000000000002</v>
+        <v>265.10000000000002</v>
       </c>
       <c r="N47" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O47" s="47">
-        <v>272.49</v>
+        <v>272.67</v>
       </c>
       <c r="P47" s="49">
-        <f>ABS(M47*L47)</f>
-        <v>67951</v>
+        <f>ABS(O47*L47)</f>
+        <v>122701.5</v>
       </c>
       <c r="Q47" s="47">
-        <v>2.08</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="R47" s="47" t="s">
         <v>72</v>
@@ -5788,7 +5791,7 @@
         <v>72</v>
       </c>
       <c r="V47" s="33">
-        <v>-3006</v>
+        <v>-3350</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
@@ -6041,7 +6044,7 @@
         <v>82.27</v>
       </c>
       <c r="P51" s="39">
-        <f t="shared" ref="P51:P61" si="10">ABS(M51*L51)</f>
+        <f t="shared" ref="P51:P60" si="10">ABS(M51*L51)</f>
         <v>59087</v>
       </c>
       <c r="Q51" s="33">
@@ -6128,7 +6131,7 @@
         <v>72</v>
       </c>
       <c r="V52" s="33">
-        <v>-12</v>
+        <v>-64</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
@@ -6334,7 +6337,7 @@
         <v>72</v>
       </c>
       <c r="V55" s="33">
-        <v>390</v>
+        <v>738</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.25">
@@ -6404,7 +6407,7 @@
         <v>72</v>
       </c>
       <c r="V56" s="33">
-        <v>-443</v>
+        <v>-990</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.25">
@@ -6474,7 +6477,7 @@
         <v>72</v>
       </c>
       <c r="V57" s="33">
-        <v>277</v>
+        <v>-413</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.25">
@@ -6748,19 +6751,77 @@
         <v>72</v>
       </c>
       <c r="V61" s="33">
-        <v>-250</v>
+        <v>-490</v>
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B62" s="34"/>
-      <c r="C62" s="34"/>
-      <c r="D62" s="35"/>
-      <c r="F62" s="36"/>
-      <c r="H62" s="36"/>
-      <c r="P62" s="39"/>
-      <c r="S62" s="40"/>
-      <c r="T62" s="39"/>
-      <c r="U62" s="41"/>
+      <c r="A62" s="33">
+        <v>56</v>
+      </c>
+      <c r="B62" s="34">
+        <v>46300</v>
+      </c>
+      <c r="C62" s="55">
+        <v>46300</v>
+      </c>
+      <c r="D62" s="56">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E62" s="47" t="s">
+        <v>34</v>
+      </c>
+      <c r="F62" s="48" t="s">
+        <v>35</v>
+      </c>
+      <c r="G62" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H62" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I62" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="J62" s="47" t="s">
+        <v>530</v>
+      </c>
+      <c r="K62" s="47" t="s">
+        <v>634</v>
+      </c>
+      <c r="L62" s="47">
+        <v>10</v>
+      </c>
+      <c r="M62" s="47">
+        <v>1.1242000000000001</v>
+      </c>
+      <c r="N62" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O62" s="47">
+        <v>1.1255999999999999</v>
+      </c>
+      <c r="P62" s="49">
+        <v>1406000</v>
+      </c>
+      <c r="Q62" s="47">
+        <v>6.44</v>
+      </c>
+      <c r="R62" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S62" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T62" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="U62" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V62" s="33">
+        <v>1702</v>
+      </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B63" s="34"/>
@@ -6826,7 +6887,7 @@
       </c>
       <c r="V68" s="39">
         <f>SUM(V2:V66)</f>
-        <v>-5471</v>
+        <v>-6527</v>
       </c>
     </row>
     <row r="69" spans="2:22" x14ac:dyDescent="0.25">
@@ -6855,7 +6916,7 @@
       <c r="F71" s="36"/>
       <c r="U71" s="39">
         <f>U68+V68</f>
-        <v>77898.47</v>
+        <v>76842.47</v>
       </c>
     </row>
     <row r="72" spans="2:22" x14ac:dyDescent="0.25">
@@ -6881,7 +6942,7 @@
     <row r="77" spans="2:22" x14ac:dyDescent="0.25">
       <c r="U77" s="54">
         <f>U71/U74</f>
-        <v>0.23392933933933935</v>
+        <v>0.23075816816816816</v>
       </c>
     </row>
   </sheetData>
@@ -6894,7 +6955,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:I83"/>
+  <dimension ref="A1:I84"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -6960,11 +7021,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C83" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C84" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D83" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D84" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -8140,11 +8201,11 @@
         <v>114</v>
       </c>
       <c r="G74" s="27">
-        <f>AVERAGE(C3:C83)</f>
+        <f>AVERAGE(C3:C84)</f>
+        <v>962.44012195121911</v>
+      </c>
+      <c r="I74" s="27">
         <v>996.54432098765392</v>
-      </c>
-      <c r="I74" s="27">
-        <v>1050.6761249999995</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -8167,11 +8228,11 @@
         <v>115</v>
       </c>
       <c r="G75" s="27">
-        <f>_xlfn.STDEV.S(C3:C83)</f>
+        <f>_xlfn.STDEV.S(C3:C84)</f>
+        <v>4107.5274532832163</v>
+      </c>
+      <c r="I75" s="27">
         <v>4121.4212322668327</v>
-      </c>
-      <c r="I75" s="27">
-        <v>4118.3458084033773</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
@@ -8195,10 +8256,10 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
+        <v>3.7195766700547406</v>
+      </c>
+      <c r="I76" s="28">
         <v>3.8383969439642409</v>
-      </c>
-      <c r="I76" s="28">
-        <v>4.0499188721124577</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
@@ -8221,11 +8282,11 @@
         <v>117</v>
       </c>
       <c r="G77" s="29">
-        <f>_xlfn.STDEV.S(D2:D83)*SQRT(252)</f>
+        <f>_xlfn.STDEV.S(D2:D84)*SQRT(252)</f>
+        <v>0.17700324244459101</v>
+      </c>
+      <c r="I77" s="29">
         <v>0.17766253922781455</v>
-      </c>
-      <c r="I77" s="29">
-        <v>0.17774657247085821</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -8248,11 +8309,11 @@
         <v>118</v>
       </c>
       <c r="G78" s="29" cm="1">
-        <f t="array" ref="G78">PRODUCT(1+D3:D83)-1</f>
+        <f t="array" ref="G78">PRODUCT(1+D3:D84)-1</f>
+        <v>0.23667342902124866</v>
+      </c>
+      <c r="I78" s="29">
         <v>0.24207144484233956</v>
-      </c>
-      <c r="I78" s="29">
-        <v>0.25206976970207151</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -8275,11 +8336,11 @@
         <v>119</v>
       </c>
       <c r="G79" s="29" cm="1">
-        <f t="array" ref="G79">PRODUCT(1+D2:D83)^(252/COUNT(D2:D83))-1</f>
+        <f t="array" ref="G79">PRODUCT(1+D2:D84)^(252/COUNT(D2:D84))-1</f>
+        <v>0.90589779785154745</v>
+      </c>
+      <c r="I79" s="29">
         <v>0.94683213592105586</v>
-      </c>
-      <c r="I79" s="29">
-        <v>1.0124875590957805</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -8348,6 +8409,23 @@
       <c r="D83" s="23">
         <f t="shared" si="1"/>
         <v>-7.9854374745515072E-3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A84" s="26">
+        <v>46300</v>
+      </c>
+      <c r="B84" s="5">
+        <f>B83-1800</f>
+        <v>412376</v>
+      </c>
+      <c r="C84" s="5">
+        <f t="shared" si="0"/>
+        <v>-1800</v>
+      </c>
+      <c r="D84" s="23">
+        <f t="shared" si="1"/>
+        <v>-4.3459785212083754E-3</v>
       </c>
     </row>
   </sheetData>
@@ -13301,7 +13379,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="14">
-        <f t="shared" ref="M69:M90" si="0">SUM(C69:L69)</f>
+        <f t="shared" ref="M69:M91" si="0">SUM(C69:L69)</f>
         <v>407651</v>
       </c>
       <c r="N69" s="15">
@@ -14954,6 +15032,85 @@
       <c r="W90" s="15">
         <f t="shared" ref="W90" si="53">L90/M90</f>
         <v>0.57955796569574292</v>
+      </c>
+    </row>
+    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A91" s="10">
+        <v>46300</v>
+      </c>
+      <c r="B91" s="11">
+        <v>412376</v>
+      </c>
+      <c r="C91" s="19">
+        <v>222194</v>
+      </c>
+      <c r="D91" s="13">
+        <v>0</v>
+      </c>
+      <c r="E91" s="13">
+        <v>1406000</v>
+      </c>
+      <c r="F91" s="13">
+        <v>0</v>
+      </c>
+      <c r="G91" s="13">
+        <v>0</v>
+      </c>
+      <c r="H91" s="13">
+        <v>17660</v>
+      </c>
+      <c r="I91" s="13">
+        <v>0</v>
+      </c>
+      <c r="J91" s="13">
+        <v>0</v>
+      </c>
+      <c r="K91" s="13">
+        <v>0</v>
+      </c>
+      <c r="L91" s="18">
+        <v>240039</v>
+      </c>
+      <c r="M91" s="14">
+        <f t="shared" si="0"/>
+        <v>1885893</v>
+      </c>
+      <c r="N91" s="15">
+        <f t="shared" ref="N91" si="54">C91/M91</f>
+        <v>0.11781898548857225</v>
+      </c>
+      <c r="O91" s="15">
+        <f t="shared" ref="O91" si="55">D91/M91</f>
+        <v>0</v>
+      </c>
+      <c r="P91" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q91" s="15">
+        <f>E91/M91</f>
+        <v>0.74553540418252784</v>
+      </c>
+      <c r="R91" s="15">
+        <v>0</v>
+      </c>
+      <c r="S91" s="15">
+        <f t="shared" ref="S91" si="56">H91/M91</f>
+        <v>9.3642640383097032E-3</v>
+      </c>
+      <c r="T91" s="15">
+        <f t="shared" ref="T91" si="57">I91/M91</f>
+        <v>0</v>
+      </c>
+      <c r="U91" s="15">
+        <v>0</v>
+      </c>
+      <c r="V91" s="16">
+        <f t="shared" ref="V91" si="58">K91/M91</f>
+        <v>0</v>
+      </c>
+      <c r="W91" s="15">
+        <f t="shared" ref="W91" si="59">L91/M91</f>
+        <v>0.12728134629059018</v>
       </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.25">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D2BD4485-84B9-0648-BF09-29D8A9A021DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAD22314-3E0D-AA4B-9E08-9947E167A0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-1080" yWindow="-42260" windowWidth="48520" windowHeight="32580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="983" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="631">
   <si>
     <t>Trade ID</t>
   </si>
@@ -1917,12 +1917,6 @@
     <t>LCI Industries</t>
   </si>
   <si>
-    <t>TIP</t>
-  </si>
-  <si>
-    <t>iShares TIPS Bond ETF</t>
-  </si>
-  <si>
     <t>TSM</t>
   </si>
   <si>
@@ -1948,12 +1942,6 @@
   </si>
   <si>
     <t>S&amp;P500 ETF</t>
-  </si>
-  <si>
-    <t>VMBS</t>
-  </si>
-  <si>
-    <t>Vanguard Mortgage Backed Securities ETF</t>
   </si>
   <si>
     <t>WAT</t>
@@ -2600,7 +2588,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V77"/>
+  <dimension ref="A1:V75"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5" style="33" bestFit="1" customWidth="1"/>
@@ -4321,7 +4309,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D62" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D60" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
@@ -4778,7 +4766,7 @@
         <v>7389</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="33">
         <v>28</v>
       </c>
@@ -4845,7 +4833,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="33">
         <v>29</v>
       </c>
@@ -4912,7 +4900,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="33">
         <v>30</v>
       </c>
@@ -4979,7 +4967,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="33">
         <v>31</v>
       </c>
@@ -5046,7 +5034,7 @@
         <v>-3825</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="33">
         <v>32</v>
       </c>
@@ -5113,7 +5101,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="33">
         <v>33</v>
       </c>
@@ -5180,7 +5168,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="33">
         <v>34</v>
       </c>
@@ -5248,7 +5236,7 @@
         <v>2167</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="33">
         <v>35</v>
       </c>
@@ -5316,7 +5304,7 @@
         <v>-438</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="33">
         <v>36</v>
       </c>
@@ -5383,7 +5371,7 @@
         <v>-317</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="33">
         <v>37</v>
       </c>
@@ -5451,77 +5439,75 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="33">
         <v>38</v>
       </c>
       <c r="B43" s="34">
         <v>46286</v>
       </c>
-      <c r="C43" s="55">
-        <v>46295</v>
-      </c>
-      <c r="D43" s="56">
+      <c r="C43" s="34">
+        <v>46301</v>
+      </c>
+      <c r="D43" s="35">
         <f t="shared" si="5"/>
-        <v>9</v>
-      </c>
-      <c r="E43" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E43" s="33" t="s">
         <v>599</v>
       </c>
-      <c r="F43" s="48" t="s">
+      <c r="F43" s="36" t="s">
         <v>600</v>
       </c>
-      <c r="G43" s="47" t="s">
+      <c r="G43" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H43" s="48" t="s">
+      <c r="H43" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I43" s="47" t="s">
+      <c r="I43" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="J43" s="47" t="s">
+      <c r="J43" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="K43" s="47" t="s">
+      <c r="K43" s="33" t="s">
         <v>599</v>
       </c>
-      <c r="L43" s="47">
-        <v>-600</v>
-      </c>
-      <c r="M43" s="47">
-        <v>161.21</v>
-      </c>
-      <c r="N43" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O43" s="47">
-        <v>165.82</v>
-      </c>
-      <c r="P43" s="49">
+      <c r="L43" s="33">
+        <v>-700</v>
+      </c>
+      <c r="M43" s="33">
+        <v>162.33920000000001</v>
+      </c>
+      <c r="N43" s="33">
+        <v>166.36</v>
+      </c>
+      <c r="O43" s="33">
+        <v>166.36</v>
+      </c>
+      <c r="P43" s="39">
         <f>ABS(O43*L43)</f>
-        <v>99492</v>
-      </c>
-      <c r="Q43" s="47">
-        <v>4.88</v>
-      </c>
-      <c r="R43" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S43" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T43" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="U43" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V43" s="33">
-        <v>-3660</v>
-      </c>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+        <v>116452.00000000001</v>
+      </c>
+      <c r="Q43" s="33">
+        <v>11.47</v>
+      </c>
+      <c r="R43" s="33">
+        <v>0</v>
+      </c>
+      <c r="S43" s="40">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="T43" s="39">
+        <v>-2814</v>
+      </c>
+      <c r="U43" s="45">
+        <v>-2814</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="33">
         <v>39</v>
       </c>
@@ -5589,7 +5575,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="33">
         <v>40</v>
       </c>
@@ -5656,7 +5642,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="33">
         <v>41</v>
       </c>
@@ -5724,77 +5710,75 @@
         <v>-664</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="33">
         <v>42</v>
       </c>
       <c r="B47" s="34">
         <v>46288</v>
       </c>
-      <c r="C47" s="55">
-        <v>46295</v>
-      </c>
-      <c r="D47" s="56">
+      <c r="C47" s="34">
+        <v>46301</v>
+      </c>
+      <c r="D47" s="35">
         <f t="shared" si="5"/>
-        <v>7</v>
-      </c>
-      <c r="E47" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="E47" s="33" t="s">
         <v>606</v>
       </c>
-      <c r="F47" s="48" t="s">
+      <c r="F47" s="36" t="s">
         <v>607</v>
       </c>
-      <c r="G47" s="47" t="s">
+      <c r="G47" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H47" s="48" t="s">
+      <c r="H47" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I47" s="47" t="s">
+      <c r="I47" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="J47" s="47" t="s">
+      <c r="J47" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="K47" s="47" t="s">
+      <c r="K47" s="33" t="s">
         <v>606</v>
       </c>
-      <c r="L47" s="47">
-        <v>-450</v>
-      </c>
-      <c r="M47" s="47">
-        <v>265.10000000000002</v>
-      </c>
-      <c r="N47" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O47" s="47">
-        <v>272.67</v>
-      </c>
-      <c r="P47" s="49">
+      <c r="L47" s="33">
+        <v>-600</v>
+      </c>
+      <c r="M47" s="33">
+        <v>268.09100000000001</v>
+      </c>
+      <c r="N47" s="33">
+        <v>280.87</v>
+      </c>
+      <c r="O47" s="33">
+        <v>280.87</v>
+      </c>
+      <c r="P47" s="39">
         <f>ABS(O47*L47)</f>
-        <v>122701.5</v>
-      </c>
-      <c r="Q47" s="47">
-        <v>5.1100000000000003</v>
-      </c>
-      <c r="R47" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S47" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T47" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="U47" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V47" s="33">
-        <v>-3350</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+        <v>168522</v>
+      </c>
+      <c r="Q47" s="33">
+        <v>10.1</v>
+      </c>
+      <c r="R47" s="33">
+        <v>0</v>
+      </c>
+      <c r="S47" s="40">
+        <f t="shared" si="8"/>
+        <v>0</v>
+      </c>
+      <c r="T47" s="39">
+        <v>-7667</v>
+      </c>
+      <c r="U47" s="45">
+        <v>-7667</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="33">
         <v>43</v>
       </c>
@@ -5919,7 +5903,7 @@
         <v>1</v>
       </c>
       <c r="S49" s="40">
-        <f t="shared" ref="S49:S53" si="9">IF(R49=1, ABS(N49-M49)/M49, 0)</f>
+        <f t="shared" ref="S49:S52" si="9">IF(R49=1, ABS(N49-M49)/M49, 0)</f>
         <v>2.0138262699128395E-2</v>
       </c>
       <c r="T49" s="39">
@@ -6044,7 +6028,7 @@
         <v>82.27</v>
       </c>
       <c r="P51" s="39">
-        <f t="shared" ref="P51:P60" si="10">ABS(M51*L51)</f>
+        <f t="shared" ref="P51:P58" si="10">ABS(M51*L51)</f>
         <v>59087</v>
       </c>
       <c r="Q51" s="33">
@@ -6071,67 +6055,65 @@
       <c r="B52" s="34">
         <v>46293</v>
       </c>
-      <c r="C52" s="55">
-        <v>46295</v>
-      </c>
-      <c r="D52" s="56">
+      <c r="C52" s="34">
+        <v>46297</v>
+      </c>
+      <c r="D52" s="35">
         <f t="shared" si="5"/>
-        <v>2</v>
-      </c>
-      <c r="E52" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="E52" s="33" t="s">
         <v>617</v>
       </c>
-      <c r="F52" s="48" t="s">
+      <c r="F52" s="36" t="s">
         <v>618</v>
       </c>
-      <c r="G52" s="47" t="s">
+      <c r="G52" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H52" s="48" t="s">
+      <c r="H52" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I52" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="J52" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="K52" s="47" t="s">
+      <c r="I52" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="J52" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="K52" s="33" t="s">
         <v>617</v>
       </c>
-      <c r="L52" s="47">
-        <v>400</v>
-      </c>
-      <c r="M52" s="47">
-        <v>104.14</v>
-      </c>
-      <c r="N52" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O52" s="47">
-        <v>104.11</v>
-      </c>
-      <c r="P52" s="49">
+      <c r="L52" s="33">
+        <v>-110</v>
+      </c>
+      <c r="M52" s="33">
+        <v>447.99</v>
+      </c>
+      <c r="N52" s="33">
+        <v>466.29</v>
+      </c>
+      <c r="O52" s="33">
+        <v>466.29</v>
+      </c>
+      <c r="P52" s="39">
         <f t="shared" si="10"/>
-        <v>41656</v>
-      </c>
-      <c r="Q52" s="47">
-        <v>1.56</v>
-      </c>
-      <c r="R52" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S52" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T52" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="U52" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V52" s="33">
-        <v>-64</v>
+        <v>49278.9</v>
+      </c>
+      <c r="Q52" s="33">
+        <v>2.68</v>
+      </c>
+      <c r="R52" s="33">
+        <v>0</v>
+      </c>
+      <c r="S52" s="40">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="T52" s="39">
+        <v>-2013</v>
+      </c>
+      <c r="U52" s="45">
+        <v>-2013</v>
       </c>
     </row>
     <row r="53" spans="1:22" x14ac:dyDescent="0.25">
@@ -6142,11 +6124,11 @@
         <v>46293</v>
       </c>
       <c r="C53" s="34">
-        <v>46297</v>
+        <v>46295</v>
       </c>
       <c r="D53" s="35">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E53" s="33" t="s">
         <v>619</v>
@@ -6170,36 +6152,36 @@
         <v>619</v>
       </c>
       <c r="L53" s="33">
-        <v>-110</v>
+        <v>4000</v>
       </c>
       <c r="M53" s="33">
-        <v>447.99</v>
+        <v>20.27</v>
       </c>
       <c r="N53" s="33">
-        <v>466.29</v>
+        <v>20.21</v>
       </c>
       <c r="O53" s="33">
-        <v>466.29</v>
+        <v>20.21</v>
       </c>
       <c r="P53" s="39">
         <f t="shared" si="10"/>
-        <v>49278.9</v>
+        <v>81080</v>
       </c>
       <c r="Q53" s="33">
-        <v>2.68</v>
+        <v>5.4</v>
       </c>
       <c r="R53" s="33">
         <v>0</v>
       </c>
       <c r="S53" s="40">
-        <f t="shared" si="9"/>
+        <f t="shared" ref="S53:S55" si="11">IF(R53=1, ABS(N53-M53)/M53, 0)</f>
         <v>0</v>
       </c>
       <c r="T53" s="39">
-        <v>-2013</v>
+        <v>-214</v>
       </c>
       <c r="U53" s="45">
-        <v>-2013</v>
+        <v>-214</v>
       </c>
     </row>
     <row r="54" spans="1:22" x14ac:dyDescent="0.25">
@@ -6207,14 +6189,14 @@
         <v>49</v>
       </c>
       <c r="B54" s="34">
-        <v>46293</v>
+        <v>46294</v>
       </c>
       <c r="C54" s="34">
-        <v>46295</v>
+        <v>46301</v>
       </c>
       <c r="D54" s="35">
         <f t="shared" si="5"/>
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="E54" s="33" t="s">
         <v>621</v>
@@ -6223,121 +6205,119 @@
         <v>622</v>
       </c>
       <c r="G54" s="33" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H54" s="36" t="s">
-        <v>24</v>
+        <v>623</v>
       </c>
       <c r="I54" s="33" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="J54" s="33" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="K54" s="33" t="s">
         <v>621</v>
       </c>
       <c r="L54" s="33">
-        <v>4000</v>
+        <v>400</v>
       </c>
       <c r="M54" s="33">
-        <v>20.27</v>
+        <v>281.4135</v>
       </c>
       <c r="N54" s="33">
-        <v>20.21</v>
+        <v>282.18</v>
       </c>
       <c r="O54" s="33">
-        <v>20.21</v>
+        <v>282.18</v>
       </c>
       <c r="P54" s="39">
         <f t="shared" si="10"/>
-        <v>81080</v>
+        <v>112565.4</v>
       </c>
       <c r="Q54" s="33">
-        <v>5.4</v>
+        <v>7.57</v>
       </c>
       <c r="R54" s="33">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S54" s="40">
-        <f t="shared" ref="S54" si="11">IF(R54=1, ABS(N54-M54)/M54, 0)</f>
-        <v>0</v>
+        <f t="shared" si="11"/>
+        <v>2.7237499267093006E-3</v>
       </c>
       <c r="T54" s="39">
-        <v>-214</v>
-      </c>
-      <c r="U54" s="45">
-        <v>-214</v>
+        <v>307</v>
+      </c>
+      <c r="U54" s="41">
+        <v>307</v>
       </c>
     </row>
     <row r="55" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A55" s="33">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B55" s="34">
         <v>46294</v>
       </c>
-      <c r="C55" s="55">
-        <v>46295</v>
-      </c>
-      <c r="D55" s="56">
+      <c r="C55" s="34">
+        <v>46301</v>
+      </c>
+      <c r="D55" s="35">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E55" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="E55" s="33" t="s">
+        <v>624</v>
+      </c>
+      <c r="F55" s="36" t="s">
+        <v>625</v>
+      </c>
+      <c r="G55" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="H55" s="36" t="s">
         <v>623</v>
       </c>
-      <c r="F55" s="48" t="s">
+      <c r="I55" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="J55" s="33" t="s">
+        <v>48</v>
+      </c>
+      <c r="K55" s="33" t="s">
         <v>624</v>
       </c>
-      <c r="G55" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="H55" s="48" t="s">
-        <v>625</v>
-      </c>
-      <c r="I55" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="J55" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="K55" s="47" t="s">
-        <v>623</v>
-      </c>
-      <c r="L55" s="47">
-        <v>200</v>
-      </c>
-      <c r="M55" s="47">
-        <v>280.43</v>
-      </c>
-      <c r="N55" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O55" s="47">
-        <v>282.10000000000002</v>
-      </c>
-      <c r="P55" s="49">
+      <c r="L55" s="33">
+        <v>-140</v>
+      </c>
+      <c r="M55" s="33">
+        <v>767.82</v>
+      </c>
+      <c r="N55" s="33">
+        <v>779.63</v>
+      </c>
+      <c r="O55" s="33">
+        <v>779.63</v>
+      </c>
+      <c r="P55" s="39">
         <f t="shared" si="10"/>
-        <v>56086</v>
-      </c>
-      <c r="Q55" s="47">
-        <v>3.11</v>
-      </c>
-      <c r="R55" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S55" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T55" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="U55" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V55" s="33">
-        <v>738</v>
+        <v>107494.8</v>
+      </c>
+      <c r="Q55" s="33">
+        <v>4.0199999999999996</v>
+      </c>
+      <c r="R55" s="33">
+        <v>0</v>
+      </c>
+      <c r="S55" s="40">
+        <f t="shared" si="11"/>
+        <v>0</v>
+      </c>
+      <c r="T55" s="39">
+        <v>-1653</v>
+      </c>
+      <c r="U55" s="45">
+        <v>-1653</v>
       </c>
     </row>
     <row r="56" spans="1:22" x14ac:dyDescent="0.25">
@@ -6345,69 +6325,67 @@
         <v>50</v>
       </c>
       <c r="B56" s="34">
-        <v>46294</v>
-      </c>
-      <c r="C56" s="55">
         <v>46295</v>
       </c>
-      <c r="D56" s="56">
+      <c r="C56" s="34">
+        <v>46296</v>
+      </c>
+      <c r="D56" s="35">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="E56" s="47" t="s">
+      <c r="E56" s="33" t="s">
         <v>626</v>
       </c>
-      <c r="F56" s="48" t="s">
+      <c r="F56" s="36" t="s">
         <v>627</v>
       </c>
-      <c r="G56" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="H56" s="48" t="s">
-        <v>625</v>
-      </c>
-      <c r="I56" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="J56" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="K56" s="47" t="s">
+      <c r="G56" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H56" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="I56" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="J56" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="K56" s="33" t="s">
         <v>626</v>
       </c>
-      <c r="L56" s="47">
-        <v>-70</v>
-      </c>
-      <c r="M56" s="47">
-        <v>765.18</v>
-      </c>
-      <c r="N56" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O56" s="47">
-        <v>770.94</v>
-      </c>
-      <c r="P56" s="49">
+      <c r="L56" s="33">
+        <v>-100</v>
+      </c>
+      <c r="M56" s="33">
+        <v>447</v>
+      </c>
+      <c r="N56" s="33">
+        <v>434.77</v>
+      </c>
+      <c r="O56" s="33">
+        <v>434.77</v>
+      </c>
+      <c r="P56" s="39">
         <f t="shared" si="10"/>
-        <v>53562.6</v>
-      </c>
-      <c r="Q56" s="47">
-        <v>3.11</v>
-      </c>
-      <c r="R56" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S56" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T56" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="U56" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V56" s="33">
-        <v>-990</v>
+        <v>44700</v>
+      </c>
+      <c r="Q56" s="33">
+        <v>1.9</v>
+      </c>
+      <c r="R56" s="33">
+        <v>1</v>
+      </c>
+      <c r="S56" s="40">
+        <f t="shared" ref="S56:S60" si="12">IF(R56=1, ABS(N56-M56)/M56, 0)</f>
+        <v>2.7360178970917266E-2</v>
+      </c>
+      <c r="T56" s="39">
+        <v>1222</v>
+      </c>
+      <c r="U56" s="41">
+        <v>1222</v>
       </c>
     </row>
     <row r="57" spans="1:22" x14ac:dyDescent="0.25">
@@ -6415,69 +6393,67 @@
         <v>51</v>
       </c>
       <c r="B57" s="34">
-        <v>46294</v>
-      </c>
-      <c r="C57" s="55">
         <v>46295</v>
       </c>
-      <c r="D57" s="56">
+      <c r="C57" s="34">
+        <v>46296</v>
+      </c>
+      <c r="D57" s="35">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="E57" s="47" t="s">
+      <c r="E57" s="33" t="s">
         <v>628</v>
       </c>
-      <c r="F57" s="48" t="s">
+      <c r="F57" s="36" t="s">
         <v>629</v>
       </c>
-      <c r="G57" s="47" t="s">
+      <c r="G57" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H57" s="48" t="s">
+      <c r="H57" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I57" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="J57" s="47" t="s">
-        <v>48</v>
-      </c>
-      <c r="K57" s="47" t="s">
+      <c r="I57" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="J57" s="33" t="s">
+        <v>25</v>
+      </c>
+      <c r="K57" s="33" t="s">
         <v>628</v>
       </c>
-      <c r="L57" s="47">
-        <v>2000</v>
-      </c>
-      <c r="M57" s="47">
-        <v>44.366999999999997</v>
-      </c>
-      <c r="N57" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O57" s="47">
-        <v>44.48</v>
-      </c>
-      <c r="P57" s="49">
+      <c r="L57" s="33">
+        <v>-100</v>
+      </c>
+      <c r="M57" s="33">
+        <v>674.15</v>
+      </c>
+      <c r="N57" s="33">
+        <v>666.83</v>
+      </c>
+      <c r="O57" s="33">
+        <v>666.83</v>
+      </c>
+      <c r="P57" s="39">
         <f t="shared" si="10"/>
-        <v>88734</v>
-      </c>
-      <c r="Q57" s="47">
-        <v>3.11</v>
-      </c>
-      <c r="R57" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S57" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T57" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="U57" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V57" s="33">
-        <v>-413</v>
+        <v>67415</v>
+      </c>
+      <c r="Q57" s="33">
+        <v>3.25</v>
+      </c>
+      <c r="R57" s="33">
+        <v>1</v>
+      </c>
+      <c r="S57" s="40">
+        <f t="shared" si="12"/>
+        <v>1.0858117629607559E-2</v>
+      </c>
+      <c r="T57" s="39">
+        <v>880</v>
+      </c>
+      <c r="U57" s="41">
+        <v>880</v>
       </c>
     </row>
     <row r="58" spans="1:22" x14ac:dyDescent="0.25">
@@ -6485,20 +6461,20 @@
         <v>52</v>
       </c>
       <c r="B58" s="34">
-        <v>46295</v>
+        <v>46296</v>
       </c>
       <c r="C58" s="34">
         <v>46296</v>
       </c>
       <c r="D58" s="35">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E58" s="33" t="s">
-        <v>630</v>
+        <v>26</v>
       </c>
       <c r="F58" s="36" t="s">
-        <v>631</v>
+        <v>27</v>
       </c>
       <c r="G58" s="33" t="s">
         <v>23</v>
@@ -6513,39 +6489,39 @@
         <v>25</v>
       </c>
       <c r="K58" s="33" t="s">
-        <v>630</v>
+        <v>26</v>
       </c>
       <c r="L58" s="33">
-        <v>-100</v>
+        <v>200</v>
       </c>
       <c r="M58" s="33">
-        <v>447</v>
+        <v>326.27999999999997</v>
       </c>
       <c r="N58" s="33">
-        <v>434.77</v>
+        <v>332.03</v>
       </c>
       <c r="O58" s="33">
-        <v>434.77</v>
+        <v>332.03</v>
       </c>
       <c r="P58" s="39">
         <f t="shared" si="10"/>
-        <v>44700</v>
+        <v>65255.999999999993</v>
       </c>
       <c r="Q58" s="33">
-        <v>1.9</v>
+        <v>2.59</v>
       </c>
       <c r="R58" s="33">
         <v>1</v>
       </c>
       <c r="S58" s="40">
-        <f t="shared" ref="S58:S60" si="12">IF(R58=1, ABS(N58-M58)/M58, 0)</f>
-        <v>2.7360178970917266E-2</v>
+        <f t="shared" si="12"/>
+        <v>1.762290057619223E-2</v>
       </c>
       <c r="T58" s="39">
-        <v>1222</v>
+        <v>1058</v>
       </c>
       <c r="U58" s="41">
-        <v>1222</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="59" spans="1:22" x14ac:dyDescent="0.25">
@@ -6553,67 +6529,69 @@
         <v>53</v>
       </c>
       <c r="B59" s="34">
-        <v>46295</v>
-      </c>
-      <c r="C59" s="34">
-        <v>46296</v>
-      </c>
-      <c r="D59" s="35">
+        <v>46297</v>
+      </c>
+      <c r="C59" s="55">
+        <v>46301</v>
+      </c>
+      <c r="D59" s="56">
         <f t="shared" si="5"/>
-        <v>1</v>
-      </c>
-      <c r="E59" s="33" t="s">
-        <v>632</v>
-      </c>
-      <c r="F59" s="36" t="s">
-        <v>633</v>
-      </c>
-      <c r="G59" s="33" t="s">
+        <v>4</v>
+      </c>
+      <c r="E59" s="47" t="s">
+        <v>58</v>
+      </c>
+      <c r="F59" s="48" t="s">
+        <v>59</v>
+      </c>
+      <c r="G59" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="H59" s="36" t="s">
+      <c r="H59" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="I59" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J59" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="K59" s="33" t="s">
-        <v>632</v>
-      </c>
-      <c r="L59" s="33">
-        <v>-100</v>
-      </c>
-      <c r="M59" s="33">
-        <v>674.15</v>
-      </c>
-      <c r="N59" s="33">
-        <v>666.83</v>
-      </c>
-      <c r="O59" s="33">
-        <v>666.83</v>
-      </c>
-      <c r="P59" s="39">
-        <f t="shared" si="10"/>
-        <v>67415</v>
-      </c>
-      <c r="Q59" s="33">
-        <v>3.25</v>
-      </c>
-      <c r="R59" s="33">
-        <v>1</v>
-      </c>
-      <c r="S59" s="40">
-        <f t="shared" si="12"/>
-        <v>1.0858117629607559E-2</v>
-      </c>
-      <c r="T59" s="39">
-        <v>880</v>
-      </c>
-      <c r="U59" s="41">
-        <v>880</v>
+      <c r="I59" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="J59" s="47" t="s">
+        <v>532</v>
+      </c>
+      <c r="K59" s="47" t="s">
+        <v>608</v>
+      </c>
+      <c r="L59" s="47">
+        <v>10</v>
+      </c>
+      <c r="M59" s="47">
+        <v>17.91</v>
+      </c>
+      <c r="N59" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O59" s="47">
+        <v>17.68</v>
+      </c>
+      <c r="P59" s="49">
+        <f>ABS(M59*L59)*100</f>
+        <v>17910</v>
+      </c>
+      <c r="Q59" s="47">
+        <v>1.88</v>
+      </c>
+      <c r="R59" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S59" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T59" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="U59" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V59" s="33">
+        <v>-490</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
@@ -6621,20 +6599,20 @@
         <v>54</v>
       </c>
       <c r="B60" s="34">
-        <v>46296</v>
+        <v>46299</v>
       </c>
       <c r="C60" s="34">
-        <v>46296</v>
+        <v>46300</v>
       </c>
       <c r="D60" s="35">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E60" s="33" t="s">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="F60" s="36" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G60" s="33" t="s">
         <v>23</v>
@@ -6643,185 +6621,67 @@
         <v>24</v>
       </c>
       <c r="I60" s="33" t="s">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="J60" s="33" t="s">
-        <v>25</v>
+        <v>530</v>
       </c>
       <c r="K60" s="33" t="s">
-        <v>26</v>
+        <v>630</v>
       </c>
       <c r="L60" s="33">
-        <v>200</v>
+        <v>10</v>
       </c>
       <c r="M60" s="33">
-        <v>326.27999999999997</v>
+        <v>1.1225000000000001</v>
       </c>
       <c r="N60" s="33">
-        <v>332.03</v>
+        <v>1.1251</v>
       </c>
       <c r="O60" s="33">
-        <v>332.03</v>
+        <v>1.1251</v>
       </c>
       <c r="P60" s="39">
-        <f t="shared" si="10"/>
-        <v>65255.999999999993</v>
+        <v>1406000</v>
       </c>
       <c r="Q60" s="33">
-        <v>2.59</v>
+        <v>42.5</v>
       </c>
       <c r="R60" s="33">
         <v>1</v>
       </c>
       <c r="S60" s="40">
         <f t="shared" si="12"/>
-        <v>1.762290057619223E-2</v>
+        <v>2.3162583518930384E-3</v>
       </c>
       <c r="T60" s="39">
-        <v>1058</v>
+        <v>925</v>
       </c>
       <c r="U60" s="41">
-        <v>1058</v>
+        <v>925</v>
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A61" s="33">
-        <v>55</v>
-      </c>
-      <c r="B61" s="34">
-        <v>46297</v>
-      </c>
-      <c r="C61" s="55">
-        <v>46297</v>
-      </c>
-      <c r="D61" s="56">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E61" s="47" t="s">
-        <v>58</v>
-      </c>
-      <c r="F61" s="48" t="s">
-        <v>59</v>
-      </c>
-      <c r="G61" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="H61" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="I61" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="J61" s="47" t="s">
-        <v>532</v>
-      </c>
-      <c r="K61" s="47" t="s">
-        <v>608</v>
-      </c>
-      <c r="L61" s="47">
-        <v>10</v>
-      </c>
-      <c r="M61" s="47">
-        <v>17.91</v>
-      </c>
-      <c r="N61" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O61" s="47">
-        <v>17.68</v>
-      </c>
-      <c r="P61" s="49">
-        <f>ABS(M61*L61)*100</f>
-        <v>17910</v>
-      </c>
-      <c r="Q61" s="47">
-        <v>1.88</v>
-      </c>
-      <c r="R61" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S61" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T61" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="U61" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V61" s="33">
-        <v>-490</v>
-      </c>
+      <c r="B61" s="34"/>
+      <c r="C61" s="34"/>
+      <c r="D61" s="35"/>
+      <c r="F61" s="36"/>
+      <c r="H61" s="36"/>
+      <c r="P61" s="39"/>
+      <c r="S61" s="40"/>
+      <c r="T61" s="39"/>
+      <c r="U61" s="41"/>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A62" s="33">
-        <v>56</v>
-      </c>
-      <c r="B62" s="34">
-        <v>46300</v>
-      </c>
-      <c r="C62" s="55">
-        <v>46300</v>
-      </c>
-      <c r="D62" s="56">
-        <f t="shared" si="5"/>
-        <v>0</v>
-      </c>
-      <c r="E62" s="47" t="s">
-        <v>34</v>
-      </c>
-      <c r="F62" s="48" t="s">
-        <v>35</v>
-      </c>
-      <c r="G62" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="H62" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="I62" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="J62" s="47" t="s">
-        <v>530</v>
-      </c>
-      <c r="K62" s="47" t="s">
-        <v>634</v>
-      </c>
-      <c r="L62" s="47">
-        <v>10</v>
-      </c>
-      <c r="M62" s="47">
-        <v>1.1242000000000001</v>
-      </c>
-      <c r="N62" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O62" s="47">
-        <v>1.1255999999999999</v>
-      </c>
-      <c r="P62" s="49">
-        <v>1406000</v>
-      </c>
-      <c r="Q62" s="47">
-        <v>6.44</v>
-      </c>
-      <c r="R62" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S62" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T62" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="U62" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V62" s="33">
-        <v>1702</v>
-      </c>
+      <c r="B62" s="34"/>
+      <c r="C62" s="34"/>
+      <c r="D62" s="35"/>
+      <c r="F62" s="36"/>
+      <c r="H62" s="36"/>
+      <c r="P62" s="39"/>
+      <c r="S62" s="40"/>
+      <c r="T62" s="39"/>
+      <c r="U62" s="41"/>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B63" s="34"/>
@@ -6845,104 +6705,82 @@
       <c r="T64" s="39"/>
       <c r="U64" s="41"/>
     </row>
-    <row r="65" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B65" s="34"/>
-      <c r="C65" s="34"/>
-      <c r="D65" s="35"/>
+    <row r="65" spans="4:22" x14ac:dyDescent="0.25">
       <c r="F65" s="36"/>
       <c r="H65" s="36"/>
-      <c r="P65" s="39"/>
-      <c r="S65" s="40"/>
-      <c r="T65" s="39"/>
-      <c r="U65" s="41"/>
-    </row>
-    <row r="66" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="B66" s="34"/>
-      <c r="C66" s="34"/>
-      <c r="D66" s="35"/>
+    </row>
+    <row r="66" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="D66" s="52" t="s">
+        <v>103</v>
+      </c>
+      <c r="E66" s="46">
+        <f>AVERAGE(D2:D58)</f>
+        <v>6.5263157894736841</v>
+      </c>
       <c r="F66" s="36"/>
       <c r="H66" s="36"/>
-      <c r="P66" s="39"/>
-      <c r="S66" s="40"/>
-      <c r="T66" s="39"/>
-      <c r="U66" s="41"/>
-    </row>
-    <row r="67" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="U66" s="39">
+        <f>SUM(U2:U64)</f>
+        <v>72467.47</v>
+      </c>
+      <c r="V66" s="39">
+        <f>SUM(V2:V64)</f>
+        <v>-490</v>
+      </c>
+    </row>
+    <row r="67" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="D67" s="52" t="s">
+        <v>104</v>
+      </c>
+      <c r="E67" s="46">
+        <f>AVERAGE(D2:D11,D13,D15:D58)</f>
+        <v>4.6545454545454543</v>
+      </c>
       <c r="F67" s="36"/>
-      <c r="H67" s="36"/>
-    </row>
-    <row r="68" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="D68" s="52" t="s">
-        <v>103</v>
-      </c>
-      <c r="E68" s="46">
-        <f>AVERAGE(D2:D60)</f>
-        <v>5.9491525423728815</v>
-      </c>
+      <c r="U67" s="53" t="s">
+        <v>105</v>
+      </c>
+      <c r="V67" s="36" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="68" spans="4:22" x14ac:dyDescent="0.25">
       <c r="F68" s="36"/>
-      <c r="H68" s="36"/>
-      <c r="U68" s="39">
-        <f>SUM(U2:U66)</f>
-        <v>83369.47</v>
-      </c>
-      <c r="V68" s="39">
-        <f>SUM(V2:V66)</f>
-        <v>-6527</v>
-      </c>
-    </row>
-    <row r="69" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="D69" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="E69" s="46">
-        <f>AVERAGE(D2:D11,D13,D15:D60)</f>
-        <v>4.1228070175438596</v>
-      </c>
+      <c r="U68" s="33" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="69" spans="4:22" x14ac:dyDescent="0.25">
       <c r="F69" s="36"/>
-      <c r="U69" s="53" t="s">
-        <v>105</v>
-      </c>
-      <c r="V69" s="36" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="70" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="U69" s="39">
+        <f>U66+V66</f>
+        <v>71977.47</v>
+      </c>
+    </row>
+    <row r="70" spans="4:22" x14ac:dyDescent="0.25">
       <c r="F70" s="36"/>
-      <c r="U70" s="33" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="71" spans="2:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="4:22" x14ac:dyDescent="0.25">
       <c r="F71" s="36"/>
-      <c r="U71" s="39">
-        <f>U68+V68</f>
-        <v>76842.47</v>
-      </c>
-    </row>
-    <row r="72" spans="2:22" x14ac:dyDescent="0.25">
+      <c r="U71" s="36" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="72" spans="4:22" x14ac:dyDescent="0.25">
       <c r="F72" s="36"/>
-    </row>
-    <row r="73" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="F73" s="36"/>
-      <c r="U73" s="36" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="74" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="F74" s="36"/>
-      <c r="U74" s="39">
+      <c r="U72" s="39">
         <v>333000</v>
       </c>
     </row>
-    <row r="76" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="U76" s="33" t="s">
+    <row r="74" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="U74" s="33" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="77" spans="2:22" x14ac:dyDescent="0.25">
-      <c r="U77" s="54">
-        <f>U71/U74</f>
-        <v>0.23075816816816816</v>
+    <row r="75" spans="4:22" x14ac:dyDescent="0.25">
+      <c r="U75" s="54">
+        <f>U69/U72</f>
+        <v>0.21614855855855855</v>
       </c>
     </row>
   </sheetData>
@@ -6955,7 +6793,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:I84"/>
+  <dimension ref="A1:I85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -7021,11 +6859,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C84" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C85" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D84" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D85" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -8201,11 +8039,11 @@
         <v>114</v>
       </c>
       <c r="G74" s="27">
-        <f>AVERAGE(C3:C84)</f>
-        <v>962.44012195121911</v>
+        <f>AVERAGE(C3:C85)</f>
+        <v>901.32638554216828</v>
       </c>
       <c r="I74" s="27">
-        <v>996.54432098765392</v>
+        <v>962.08646341463373</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -8228,11 +8066,11 @@
         <v>115</v>
       </c>
       <c r="G75" s="27">
-        <f>_xlfn.STDEV.S(C3:C84)</f>
-        <v>4107.5274532832163</v>
+        <f>_xlfn.STDEV.S(C3:C85)</f>
+        <v>4120.0013011478477</v>
       </c>
       <c r="I75" s="27">
-        <v>4121.4212322668327</v>
+        <v>4107.7694773583607</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
@@ -8256,10 +8094,10 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
-        <v>3.7195766700547406</v>
+        <v>3.4728418152405705</v>
       </c>
       <c r="I76" s="28">
-        <v>3.8383969439642409</v>
+        <v>3.717990801529147</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
@@ -8282,11 +8120,11 @@
         <v>117</v>
       </c>
       <c r="G77" s="29">
-        <f>_xlfn.STDEV.S(D2:D84)*SQRT(252)</f>
-        <v>0.17700324244459101</v>
+        <f>_xlfn.STDEV.S(D2:D85)*SQRT(252)</f>
+        <v>0.17727346578207545</v>
       </c>
       <c r="I77" s="29">
-        <v>0.17766253922781455</v>
+        <v>0.17701175695806795</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -8309,11 +8147,11 @@
         <v>118</v>
       </c>
       <c r="G78" s="29" cm="1">
-        <f t="array" ref="G78">PRODUCT(1+D3:D84)-1</f>
-        <v>0.23667342902124866</v>
+        <f t="array" ref="G78">PRODUCT(1+D3:D85)-1</f>
+        <v>0.22434795956309039</v>
       </c>
       <c r="I78" s="29">
-        <v>0.24207144484233956</v>
+        <v>0.23658646098857528</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -8336,11 +8174,11 @@
         <v>119</v>
       </c>
       <c r="G79" s="29" cm="1">
-        <f t="array" ref="G79">PRODUCT(1+D2:D84)^(252/COUNT(D2:D84))-1</f>
-        <v>0.90589779785154745</v>
+        <f t="array" ref="G79">PRODUCT(1+D2:D85)^(252/COUNT(D2:D85))-1</f>
+        <v>0.83533178263185603</v>
       </c>
       <c r="I79" s="29">
-        <v>0.94683213592105586</v>
+        <v>0.90549089045983155</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -8416,16 +8254,33 @@
         <v>46300</v>
       </c>
       <c r="B84" s="5">
-        <f>B83-1800</f>
-        <v>412376</v>
+        <f>B83-1829</f>
+        <v>412347</v>
       </c>
       <c r="C84" s="5">
         <f t="shared" si="0"/>
-        <v>-1800</v>
+        <v>-1829</v>
       </c>
       <c r="D84" s="23">
         <f t="shared" si="1"/>
-        <v>-4.3459785212083754E-3</v>
+        <v>-4.4159970640500661E-3</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A85" s="26">
+        <v>46301</v>
+      </c>
+      <c r="B85" s="5">
+        <f>B84-4274-65+631-373</f>
+        <v>408266</v>
+      </c>
+      <c r="C85" s="5">
+        <f t="shared" si="0"/>
+        <v>-4081</v>
+      </c>
+      <c r="D85" s="23">
+        <f t="shared" si="1"/>
+        <v>-9.8970042221721028E-3</v>
       </c>
     </row>
   </sheetData>
@@ -13379,7 +13234,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="14">
-        <f t="shared" ref="M69:M91" si="0">SUM(C69:L69)</f>
+        <f t="shared" ref="M69:M92" si="0">SUM(C69:L69)</f>
         <v>407651</v>
       </c>
       <c r="N69" s="15">
@@ -15111,6 +14966,86 @@
       <c r="W91" s="15">
         <f t="shared" ref="W91" si="59">L91/M91</f>
         <v>0.12728134629059018</v>
+      </c>
+    </row>
+    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A92" s="10">
+        <v>46301</v>
+      </c>
+      <c r="B92" s="11">
+        <v>408266</v>
+      </c>
+      <c r="C92" s="19">
+        <v>0</v>
+      </c>
+      <c r="D92" s="13">
+        <f>B92-C92-H92-L92</f>
+        <v>390606</v>
+      </c>
+      <c r="E92" s="13">
+        <v>0</v>
+      </c>
+      <c r="F92" s="13">
+        <v>0</v>
+      </c>
+      <c r="G92" s="13">
+        <v>0</v>
+      </c>
+      <c r="H92" s="13">
+        <v>17660</v>
+      </c>
+      <c r="I92" s="13">
+        <v>0</v>
+      </c>
+      <c r="J92" s="13">
+        <v>0</v>
+      </c>
+      <c r="K92" s="13">
+        <v>0</v>
+      </c>
+      <c r="L92" s="18">
+        <v>0</v>
+      </c>
+      <c r="M92" s="14">
+        <f t="shared" si="0"/>
+        <v>408266</v>
+      </c>
+      <c r="N92" s="15">
+        <f t="shared" ref="N92" si="60">C92/M92</f>
+        <v>0</v>
+      </c>
+      <c r="O92" s="15">
+        <f t="shared" ref="O92" si="61">D92/M92</f>
+        <v>0.95674388756350026</v>
+      </c>
+      <c r="P92" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q92" s="15">
+        <f>E92/M92</f>
+        <v>0</v>
+      </c>
+      <c r="R92" s="15">
+        <v>0</v>
+      </c>
+      <c r="S92" s="15">
+        <f t="shared" ref="S92" si="62">H92/M92</f>
+        <v>4.3256112436499732E-2</v>
+      </c>
+      <c r="T92" s="15">
+        <f t="shared" ref="T92" si="63">I92/M92</f>
+        <v>0</v>
+      </c>
+      <c r="U92" s="15">
+        <v>0</v>
+      </c>
+      <c r="V92" s="16">
+        <f t="shared" ref="V92" si="64">K92/M92</f>
+        <v>0</v>
+      </c>
+      <c r="W92" s="15">
+        <f t="shared" ref="W92" si="65">L92/M92</f>
+        <v>0</v>
       </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.25">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{FAD22314-3E0D-AA4B-9E08-9947E167A0D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{28FB3A79-3769-8C46-A059-EF6AEC52268D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-1080" yWindow="-42260" windowWidth="48520" windowHeight="32580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="934" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="631">
   <si>
     <t>Trade ID</t>
   </si>
@@ -4766,7 +4766,7 @@
         <v>7389</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="33">
         <v>28</v>
       </c>
@@ -4833,7 +4833,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="33">
         <v>29</v>
       </c>
@@ -4900,7 +4900,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="33">
         <v>30</v>
       </c>
@@ -4967,7 +4967,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="33">
         <v>31</v>
       </c>
@@ -5034,7 +5034,7 @@
         <v>-3825</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="33">
         <v>32</v>
       </c>
@@ -5101,7 +5101,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="33">
         <v>33</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="33">
         <v>34</v>
       </c>
@@ -5236,7 +5236,7 @@
         <v>2167</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="33">
         <v>35</v>
       </c>
@@ -5304,7 +5304,7 @@
         <v>-438</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="33">
         <v>36</v>
       </c>
@@ -5371,7 +5371,7 @@
         <v>-317</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="33">
         <v>37</v>
       </c>
@@ -5439,7 +5439,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="33">
         <v>38</v>
       </c>
@@ -5507,7 +5507,7 @@
         <v>-2814</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="33">
         <v>39</v>
       </c>
@@ -5575,7 +5575,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="33">
         <v>40</v>
       </c>
@@ -5642,7 +5642,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="33">
         <v>41</v>
       </c>
@@ -5710,75 +5710,78 @@
         <v>-664</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="33">
         <v>42</v>
       </c>
       <c r="B47" s="34">
         <v>46288</v>
       </c>
-      <c r="C47" s="34">
-        <v>46301</v>
-      </c>
-      <c r="D47" s="35">
+      <c r="C47" s="55">
+        <v>46302</v>
+      </c>
+      <c r="D47" s="56">
         <f t="shared" si="5"/>
-        <v>13</v>
-      </c>
-      <c r="E47" s="33" t="s">
+        <v>14</v>
+      </c>
+      <c r="E47" s="47" t="s">
         <v>606</v>
       </c>
-      <c r="F47" s="36" t="s">
+      <c r="F47" s="48" t="s">
         <v>607</v>
       </c>
-      <c r="G47" s="33" t="s">
+      <c r="G47" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="H47" s="36" t="s">
+      <c r="H47" s="48" t="s">
         <v>24</v>
       </c>
-      <c r="I47" s="33" t="s">
+      <c r="I47" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="J47" s="33" t="s">
+      <c r="J47" s="47" t="s">
         <v>25</v>
       </c>
-      <c r="K47" s="33" t="s">
+      <c r="K47" s="47" t="s">
         <v>606</v>
       </c>
-      <c r="L47" s="33">
+      <c r="L47" s="47">
         <v>-600</v>
       </c>
-      <c r="M47" s="33">
+      <c r="M47" s="47">
         <v>268.09100000000001</v>
       </c>
-      <c r="N47" s="33">
-        <v>280.87</v>
-      </c>
-      <c r="O47" s="33">
-        <v>280.87</v>
-      </c>
-      <c r="P47" s="39">
+      <c r="N47" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O47" s="47">
+        <v>267.39999999999998</v>
+      </c>
+      <c r="P47" s="49">
         <f>ABS(O47*L47)</f>
-        <v>168522</v>
-      </c>
-      <c r="Q47" s="33">
+        <v>160440</v>
+      </c>
+      <c r="Q47" s="47">
         <v>10.1</v>
       </c>
-      <c r="R47" s="33">
-        <v>0</v>
-      </c>
-      <c r="S47" s="40">
-        <f t="shared" si="8"/>
-        <v>0</v>
-      </c>
-      <c r="T47" s="39">
-        <v>-7667</v>
-      </c>
-      <c r="U47" s="45">
-        <v>-7667</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="R47" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S47" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T47" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="U47" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V47" s="33">
+        <f>(M47-O47)*600</f>
+        <v>414.60000000001855</v>
+      </c>
+    </row>
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="33">
         <v>43</v>
       </c>
@@ -6715,17 +6718,17 @@
       </c>
       <c r="E66" s="46">
         <f>AVERAGE(D2:D58)</f>
-        <v>6.5263157894736841</v>
+        <v>6.5438596491228074</v>
       </c>
       <c r="F66" s="36"/>
       <c r="H66" s="36"/>
       <c r="U66" s="39">
         <f>SUM(U2:U64)</f>
-        <v>72467.47</v>
+        <v>80134.47</v>
       </c>
       <c r="V66" s="39">
         <f>SUM(V2:V64)</f>
-        <v>-490</v>
+        <v>-75.399999999981446</v>
       </c>
     </row>
     <row r="67" spans="4:22" x14ac:dyDescent="0.25">
@@ -6734,7 +6737,7 @@
       </c>
       <c r="E67" s="46">
         <f>AVERAGE(D2:D11,D13,D15:D58)</f>
-        <v>4.6545454545454543</v>
+        <v>4.6727272727272728</v>
       </c>
       <c r="F67" s="36"/>
       <c r="U67" s="53" t="s">
@@ -6754,7 +6757,7 @@
       <c r="F69" s="36"/>
       <c r="U69" s="39">
         <f>U66+V66</f>
-        <v>71977.47</v>
+        <v>80059.070000000022</v>
       </c>
     </row>
     <row r="70" spans="4:22" x14ac:dyDescent="0.25">
@@ -6780,7 +6783,7 @@
     <row r="75" spans="4:22" x14ac:dyDescent="0.25">
       <c r="U75" s="54">
         <f>U69/U72</f>
-        <v>0.21614855855855855</v>
+        <v>0.24041762762762769</v>
       </c>
     </row>
   </sheetData>
@@ -8040,7 +8043,7 @@
       </c>
       <c r="G74" s="27">
         <f>AVERAGE(C3:C85)</f>
-        <v>901.32638554216828</v>
+        <v>952.82036144578274</v>
       </c>
       <c r="I74" s="27">
         <v>962.08646341463373</v>
@@ -8067,7 +8070,7 @@
       </c>
       <c r="G75" s="27">
         <f>_xlfn.STDEV.S(C3:C85)</f>
-        <v>4120.0013011478477</v>
+        <v>4083.5179476547146</v>
       </c>
       <c r="I75" s="27">
         <v>4107.7694773583607</v>
@@ -8094,7 +8097,7 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
-        <v>3.4728418152405705</v>
+        <v>3.7040499189460783</v>
       </c>
       <c r="I76" s="28">
         <v>3.717990801529147</v>
@@ -8121,7 +8124,7 @@
       </c>
       <c r="G77" s="29">
         <f>_xlfn.STDEV.S(D2:D85)*SQRT(252)</f>
-        <v>0.17727346578207545</v>
+        <v>0.17598176438533644</v>
       </c>
       <c r="I77" s="29">
         <v>0.17701175695806795</v>
@@ -8148,7 +8151,7 @@
       </c>
       <c r="G78" s="29" cm="1">
         <f t="array" ref="G78">PRODUCT(1+D3:D85)-1</f>
-        <v>0.22434795956309039</v>
+        <v>0.23716524824050333</v>
       </c>
       <c r="I78" s="29">
         <v>0.23658646098857528</v>
@@ -8175,7 +8178,7 @@
       </c>
       <c r="G79" s="29" cm="1">
         <f t="array" ref="G79">PRODUCT(1+D2:D85)^(252/COUNT(D2:D85))-1</f>
-        <v>0.83533178263185603</v>
+        <v>0.89357772754548725</v>
       </c>
       <c r="I79" s="29">
         <v>0.90549089045983155</v>
@@ -8271,16 +8274,16 @@
         <v>46301</v>
       </c>
       <c r="B85" s="5">
-        <f>B84-4274-65+631-373</f>
-        <v>408266</v>
+        <f>B84-65+631-373</f>
+        <v>412540</v>
       </c>
       <c r="C85" s="5">
         <f t="shared" si="0"/>
-        <v>-4081</v>
+        <v>193</v>
       </c>
       <c r="D85" s="23">
         <f t="shared" si="1"/>
-        <v>-9.8970042221721028E-3</v>
+        <v>4.6805239276628667E-4</v>
       </c>
     </row>
   </sheetData>
@@ -14976,11 +14979,11 @@
         <v>408266</v>
       </c>
       <c r="C92" s="19">
-        <v>0</v>
+        <v>160440</v>
       </c>
       <c r="D92" s="13">
         <f>B92-C92-H92-L92</f>
-        <v>390606</v>
+        <v>230166</v>
       </c>
       <c r="E92" s="13">
         <v>0</v>
@@ -15012,11 +15015,11 @@
       </c>
       <c r="N92" s="15">
         <f t="shared" ref="N92" si="60">C92/M92</f>
-        <v>0</v>
+        <v>0.3929790871637609</v>
       </c>
       <c r="O92" s="15">
         <f t="shared" ref="O92" si="61">D92/M92</f>
-        <v>0.95674388756350026</v>
+        <v>0.56376480039973942</v>
       </c>
       <c r="P92" s="15">
         <v>0</v>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{28FB3A79-3769-8C46-A059-EF6AEC52268D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E5297EC-2336-E94D-8697-98EF4B0B1F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-1080" yWindow="-42260" windowWidth="48520" windowHeight="32580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -5755,11 +5755,11 @@
         <v>72</v>
       </c>
       <c r="O47" s="47">
-        <v>267.39999999999998</v>
+        <v>278.26</v>
       </c>
       <c r="P47" s="49">
         <f>ABS(O47*L47)</f>
-        <v>160440</v>
+        <v>166956</v>
       </c>
       <c r="Q47" s="47">
         <v>10.1</v>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="V47" s="33">
         <f>(M47-O47)*600</f>
-        <v>414.60000000001855</v>
+        <v>-6101.3999999999896</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
@@ -6728,7 +6728,7 @@
       </c>
       <c r="V66" s="39">
         <f>SUM(V2:V64)</f>
-        <v>-75.399999999981446</v>
+        <v>-6591.3999999999896</v>
       </c>
     </row>
     <row r="67" spans="4:22" x14ac:dyDescent="0.25">
@@ -6757,7 +6757,7 @@
       <c r="F69" s="36"/>
       <c r="U69" s="39">
         <f>U66+V66</f>
-        <v>80059.070000000022</v>
+        <v>73543.070000000007</v>
       </c>
     </row>
     <row r="70" spans="4:22" x14ac:dyDescent="0.25">
@@ -6783,7 +6783,7 @@
     <row r="75" spans="4:22" x14ac:dyDescent="0.25">
       <c r="U75" s="54">
         <f>U69/U72</f>
-        <v>0.24041762762762769</v>
+        <v>0.22085006006006008</v>
       </c>
     </row>
   </sheetData>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="G74" s="27">
         <f>AVERAGE(C3:C85)</f>
-        <v>952.82036144578274</v>
+        <v>902.21795180722847</v>
       </c>
       <c r="I74" s="27">
         <v>962.08646341463373</v>
@@ -8070,7 +8070,7 @@
       </c>
       <c r="G75" s="27">
         <f>_xlfn.STDEV.S(C3:C85)</f>
-        <v>4083.5179476547146</v>
+        <v>4118.9178440263222</v>
       </c>
       <c r="I75" s="27">
         <v>4107.7694773583607</v>
@@ -8097,7 +8097,7 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
-        <v>3.7040499189460783</v>
+        <v>3.4771914652125262</v>
       </c>
       <c r="I76" s="28">
         <v>3.717990801529147</v>
@@ -8124,7 +8124,7 @@
       </c>
       <c r="G77" s="29">
         <f>_xlfn.STDEV.S(D2:D85)*SQRT(252)</f>
-        <v>0.17598176438533644</v>
+        <v>0.17723571184916939</v>
       </c>
       <c r="I77" s="29">
         <v>0.17701175695806795</v>
@@ -8151,7 +8151,7 @@
       </c>
       <c r="G78" s="29" cm="1">
         <f t="array" ref="G78">PRODUCT(1+D3:D85)-1</f>
-        <v>0.23716524824050333</v>
+        <v>0.22456987799129102</v>
       </c>
       <c r="I78" s="29">
         <v>0.23658646098857528</v>
@@ -8178,7 +8178,7 @@
       </c>
       <c r="G79" s="29" cm="1">
         <f t="array" ref="G79">PRODUCT(1+D2:D85)^(252/COUNT(D2:D85))-1</f>
-        <v>0.89357772754548725</v>
+        <v>0.83632994929563176</v>
       </c>
       <c r="I79" s="29">
         <v>0.90549089045983155</v>
@@ -8274,16 +8274,16 @@
         <v>46301</v>
       </c>
       <c r="B85" s="5">
-        <f>B84-65+631-373</f>
-        <v>412540</v>
+        <f>B84-65+631-373-4200</f>
+        <v>408340</v>
       </c>
       <c r="C85" s="5">
         <f t="shared" si="0"/>
-        <v>193</v>
+        <v>-4007</v>
       </c>
       <c r="D85" s="23">
         <f t="shared" si="1"/>
-        <v>4.6805239276628667E-4</v>
+        <v>-9.7175437192461682E-3</v>
       </c>
     </row>
   </sheetData>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8E5297EC-2336-E94D-8697-98EF4B0B1F24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BDF7E76-69FC-9F46-8CA6-200DBCBF344B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1080" yWindow="-42260" windowWidth="48520" windowHeight="32580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-17220" yWindow="-42260" windowWidth="48520" windowHeight="32580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="939" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="631">
   <si>
     <t>Trade ID</t>
   </si>
@@ -4309,7 +4309,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D60" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D61" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
@@ -5755,11 +5755,11 @@
         <v>72</v>
       </c>
       <c r="O47" s="47">
-        <v>278.26</v>
+        <v>265.44</v>
       </c>
       <c r="P47" s="49">
         <f>ABS(O47*L47)</f>
-        <v>166956</v>
+        <v>159264</v>
       </c>
       <c r="Q47" s="47">
         <v>10.1</v>
@@ -5778,7 +5778,7 @@
       </c>
       <c r="V47" s="33">
         <f>(M47-O47)*600</f>
-        <v>-6101.3999999999896</v>
+        <v>1590.6000000000063</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
@@ -6381,7 +6381,7 @@
         <v>1</v>
       </c>
       <c r="S56" s="40">
-        <f t="shared" ref="S56:S60" si="12">IF(R56=1, ABS(N56-M56)/M56, 0)</f>
+        <f t="shared" ref="S56:S61" si="12">IF(R56=1, ABS(N56-M56)/M56, 0)</f>
         <v>2.7360178970917266E-2</v>
       </c>
       <c r="T56" s="39">
@@ -6594,7 +6594,7 @@
         <v>72</v>
       </c>
       <c r="V59" s="33">
-        <v>-490</v>
+        <v>-130</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
@@ -6645,7 +6645,8 @@
         <v>1.1251</v>
       </c>
       <c r="P60" s="39">
-        <v>1406000</v>
+        <f>1406000*1.121</f>
+        <v>1576126</v>
       </c>
       <c r="Q60" s="33">
         <v>42.5</v>
@@ -6665,15 +6666,72 @@
       </c>
     </row>
     <row r="61" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B61" s="34"/>
-      <c r="C61" s="34"/>
-      <c r="D61" s="35"/>
-      <c r="F61" s="36"/>
-      <c r="H61" s="36"/>
-      <c r="P61" s="39"/>
-      <c r="S61" s="40"/>
-      <c r="T61" s="39"/>
-      <c r="U61" s="41"/>
+      <c r="A61" s="33">
+        <v>55</v>
+      </c>
+      <c r="B61" s="34">
+        <v>46302</v>
+      </c>
+      <c r="C61" s="34">
+        <v>46302</v>
+      </c>
+      <c r="D61" s="35">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E61" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="F61" s="36" t="s">
+        <v>35</v>
+      </c>
+      <c r="G61" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="H61" s="36" t="s">
+        <v>24</v>
+      </c>
+      <c r="I61" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="J61" s="33" t="s">
+        <v>530</v>
+      </c>
+      <c r="K61" s="33" t="s">
+        <v>630</v>
+      </c>
+      <c r="L61" s="33">
+        <v>15</v>
+      </c>
+      <c r="M61" s="33">
+        <v>1.1217200000000001</v>
+      </c>
+      <c r="N61" s="33">
+        <v>1.12226</v>
+      </c>
+      <c r="O61" s="33">
+        <v>1.12226</v>
+      </c>
+      <c r="P61" s="39">
+        <f>L61*125000*1.121</f>
+        <v>2101875</v>
+      </c>
+      <c r="Q61" s="33">
+        <v>73.8</v>
+      </c>
+      <c r="R61" s="33">
+        <v>1</v>
+      </c>
+      <c r="S61" s="40">
+        <f t="shared" si="12"/>
+        <v>4.8140355882036952E-4</v>
+      </c>
+      <c r="T61" s="39">
+        <v>1013</v>
+      </c>
+      <c r="U61" s="41">
+        <v>1013</v>
+      </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B62" s="34"/>
@@ -6717,18 +6775,18 @@
         <v>103</v>
       </c>
       <c r="E66" s="46">
-        <f>AVERAGE(D2:D58)</f>
-        <v>6.5438596491228074</v>
+        <f>AVERAGE(D2:D61)</f>
+        <v>6.3</v>
       </c>
       <c r="F66" s="36"/>
       <c r="H66" s="36"/>
       <c r="U66" s="39">
         <f>SUM(U2:U64)</f>
-        <v>80134.47</v>
+        <v>81147.47</v>
       </c>
       <c r="V66" s="39">
         <f>SUM(V2:V64)</f>
-        <v>-6591.3999999999896</v>
+        <v>1460.6000000000063</v>
       </c>
     </row>
     <row r="67" spans="4:22" x14ac:dyDescent="0.25">
@@ -6736,8 +6794,8 @@
         <v>104</v>
       </c>
       <c r="E67" s="46">
-        <f>AVERAGE(D2:D11,D13,D15:D58)</f>
-        <v>4.6727272727272728</v>
+        <f>AVERAGE(D2:D11,D13,D15:D61)</f>
+        <v>4.5172413793103452</v>
       </c>
       <c r="F67" s="36"/>
       <c r="U67" s="53" t="s">
@@ -6757,7 +6815,7 @@
       <c r="F69" s="36"/>
       <c r="U69" s="39">
         <f>U66+V66</f>
-        <v>73543.070000000007</v>
+        <v>82608.070000000007</v>
       </c>
     </row>
     <row r="70" spans="4:22" x14ac:dyDescent="0.25">
@@ -6783,7 +6841,7 @@
     <row r="75" spans="4:22" x14ac:dyDescent="0.25">
       <c r="U75" s="54">
         <f>U69/U72</f>
-        <v>0.22085006006006008</v>
+        <v>0.24807228228228231</v>
       </c>
     </row>
   </sheetData>
@@ -6796,7 +6854,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:I85"/>
+  <dimension ref="A1:I86"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -6862,11 +6920,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C85" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C86" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D85" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D86" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -8042,11 +8100,11 @@
         <v>114</v>
       </c>
       <c r="G74" s="27">
-        <f>AVERAGE(C3:C85)</f>
+        <f>AVERAGE(C3:C86)</f>
+        <v>998.5129761904758</v>
+      </c>
+      <c r="I74" s="27">
         <v>902.21795180722847</v>
-      </c>
-      <c r="I74" s="27">
-        <v>962.08646341463373</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -8069,11 +8127,11 @@
         <v>115</v>
       </c>
       <c r="G75" s="27">
-        <f>_xlfn.STDEV.S(C3:C85)</f>
+        <f>_xlfn.STDEV.S(C3:C86)</f>
+        <v>4188.0771538061736</v>
+      </c>
+      <c r="I75" s="27">
         <v>4118.9178440263222</v>
-      </c>
-      <c r="I75" s="27">
-        <v>4107.7694773583607</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
@@ -8097,10 +8155,10 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
+        <v>3.7847684063843623</v>
+      </c>
+      <c r="I76" s="28">
         <v>3.4771914652125262</v>
-      </c>
-      <c r="I76" s="28">
-        <v>3.717990801529147</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
@@ -8123,11 +8181,11 @@
         <v>117</v>
       </c>
       <c r="G77" s="29">
-        <f>_xlfn.STDEV.S(D2:D85)*SQRT(252)</f>
+        <f>_xlfn.STDEV.S(D2:D86)*SQRT(252)</f>
+        <v>0.17936221602538568</v>
+      </c>
+      <c r="I77" s="29">
         <v>0.17723571184916939</v>
-      </c>
-      <c r="I77" s="29">
-        <v>0.17701175695806795</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -8150,11 +8208,11 @@
         <v>118</v>
       </c>
       <c r="G78" s="29" cm="1">
-        <f t="array" ref="G78">PRODUCT(1+D3:D85)-1</f>
+        <f t="array" ref="G78">PRODUCT(1+D3:D86)-1</f>
+        <v>0.25153296701764072</v>
+      </c>
+      <c r="I78" s="29">
         <v>0.22456987799129102</v>
-      </c>
-      <c r="I78" s="29">
-        <v>0.23658646098857528</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -8177,11 +8235,11 @@
         <v>119</v>
       </c>
       <c r="G79" s="29" cm="1">
-        <f t="array" ref="G79">PRODUCT(1+D2:D85)^(252/COUNT(D2:D85))-1</f>
+        <f t="array" ref="G79">PRODUCT(1+D2:D86)^(252/COUNT(D2:D86))-1</f>
+        <v>0.94485730362176024</v>
+      </c>
+      <c r="I79" s="29">
         <v>0.83632994929563176</v>
-      </c>
-      <c r="I79" s="29">
-        <v>0.90549089045983155</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -8284,6 +8342,23 @@
       <c r="D85" s="23">
         <f t="shared" si="1"/>
         <v>-9.7175437192461682E-3</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A86" s="26">
+        <v>46302</v>
+      </c>
+      <c r="B86" s="5">
+        <f>B85+7800+938+253</f>
+        <v>417331</v>
+      </c>
+      <c r="C86" s="5">
+        <f t="shared" si="0"/>
+        <v>8991</v>
+      </c>
+      <c r="D86" s="23">
+        <f t="shared" si="1"/>
+        <v>2.2018416025860802E-2</v>
       </c>
     </row>
   </sheetData>
@@ -13237,7 +13312,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="14">
-        <f t="shared" ref="M69:M92" si="0">SUM(C69:L69)</f>
+        <f t="shared" ref="M69:M93" si="0">SUM(C69:L69)</f>
         <v>407651</v>
       </c>
       <c r="N69" s="15">
@@ -15048,6 +15123,85 @@
       </c>
       <c r="W92" s="15">
         <f t="shared" ref="W92" si="65">L92/M92</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A93" s="10">
+        <v>46302</v>
+      </c>
+      <c r="B93" s="11">
+        <v>417331</v>
+      </c>
+      <c r="C93" s="19">
+        <v>160440</v>
+      </c>
+      <c r="D93" s="13">
+        <v>0</v>
+      </c>
+      <c r="E93" s="13">
+        <v>2101875</v>
+      </c>
+      <c r="F93" s="13">
+        <v>0</v>
+      </c>
+      <c r="G93" s="13">
+        <v>0</v>
+      </c>
+      <c r="H93" s="13">
+        <v>17660</v>
+      </c>
+      <c r="I93" s="13">
+        <v>0</v>
+      </c>
+      <c r="J93" s="13">
+        <v>0</v>
+      </c>
+      <c r="K93" s="13">
+        <v>0</v>
+      </c>
+      <c r="L93" s="18">
+        <v>0</v>
+      </c>
+      <c r="M93" s="14">
+        <f t="shared" si="0"/>
+        <v>2279975</v>
+      </c>
+      <c r="N93" s="15">
+        <f t="shared" ref="N93" si="66">C93/M93</f>
+        <v>7.0369192644656187E-2</v>
+      </c>
+      <c r="O93" s="15">
+        <f t="shared" ref="O93" si="67">D93/M93</f>
+        <v>0</v>
+      </c>
+      <c r="P93" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q93" s="15">
+        <f>E93/M93</f>
+        <v>0.92188510838934634</v>
+      </c>
+      <c r="R93" s="15">
+        <v>0</v>
+      </c>
+      <c r="S93" s="15">
+        <f t="shared" ref="S93" si="68">H93/M93</f>
+        <v>7.7456989659974345E-3</v>
+      </c>
+      <c r="T93" s="15">
+        <f t="shared" ref="T93" si="69">I93/M93</f>
+        <v>0</v>
+      </c>
+      <c r="U93" s="15">
+        <v>0</v>
+      </c>
+      <c r="V93" s="16">
+        <f t="shared" ref="V93" si="70">K93/M93</f>
+        <v>0</v>
+      </c>
+      <c r="W93" s="15">
+        <f t="shared" ref="W93" si="71">L93/M93</f>
         <v>0</v>
       </c>
     </row>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{6BDF7E76-69FC-9F46-8CA6-200DBCBF344B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{C61EEE90-9FF4-8B41-A169-64B68F6DF631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-17220" yWindow="-42260" windowWidth="48520" windowHeight="32580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="19580" yWindow="-41980" windowWidth="48520" windowHeight="32580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="946" uniqueCount="631">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="634">
   <si>
     <t>Trade ID</t>
   </si>
@@ -333,9 +333,6 @@
     <t>MGC</t>
   </si>
   <si>
-    <t>Gold Micro</t>
-  </si>
-  <si>
     <t>MGCZ6</t>
   </si>
   <si>
@@ -1957,6 +1954,18 @@
   </si>
   <si>
     <t>6EZ6</t>
+  </si>
+  <si>
+    <t>Long Gold vs Short Copper</t>
+  </si>
+  <si>
+    <t>MHG</t>
+  </si>
+  <si>
+    <t>Copper Futures</t>
+  </si>
+  <si>
+    <t>MHGZ6</t>
   </si>
 </sst>
 </file>
@@ -2845,7 +2854,7 @@
         <v>32</v>
       </c>
       <c r="J4" s="33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K4" s="33" t="s">
         <v>33</v>
@@ -2913,7 +2922,7 @@
         <v>32</v>
       </c>
       <c r="J5" s="33" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K5" s="33" t="s">
         <v>34</v>
@@ -2980,7 +2989,7 @@
         <v>32</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K6" s="33" t="s">
         <v>38</v>
@@ -3048,7 +3057,7 @@
         <v>32</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K7" s="33" t="s">
         <v>41</v>
@@ -3116,7 +3125,7 @@
         <v>32</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K8" s="33" t="s">
         <v>44</v>
@@ -3318,7 +3327,7 @@
         <v>32</v>
       </c>
       <c r="J11" s="33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K11" s="33" t="s">
         <v>53</v>
@@ -3521,7 +3530,7 @@
         <v>32</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K14" s="33" t="s">
         <v>60</v>
@@ -3588,7 +3597,7 @@
         <v>32</v>
       </c>
       <c r="J15" s="37" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K15" s="33" t="s">
         <v>63</v>
@@ -3927,7 +3936,7 @@
         <v>32</v>
       </c>
       <c r="J20" s="33" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="K20" s="33" t="s">
         <v>75</v>
@@ -4061,7 +4070,7 @@
         <v>32</v>
       </c>
       <c r="J22" s="33" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K22" s="33" t="s">
         <v>79</v>
@@ -4128,7 +4137,7 @@
         <v>32</v>
       </c>
       <c r="J23" s="33" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="K23" s="33" t="s">
         <v>83</v>
@@ -4195,7 +4204,7 @@
         <v>32</v>
       </c>
       <c r="J24" s="33" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K24" s="33" t="s">
         <v>84</v>
@@ -4261,7 +4270,7 @@
         <v>32</v>
       </c>
       <c r="J25" s="33" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K25" s="33" t="s">
         <v>87</v>
@@ -4309,14 +4318,14 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D61" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D62" si="5">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
         <v>88</v>
       </c>
       <c r="F26" s="36" t="s">
-        <v>89</v>
+        <v>52</v>
       </c>
       <c r="G26" s="33" t="s">
         <v>23</v>
@@ -4328,10 +4337,10 @@
         <v>32</v>
       </c>
       <c r="J26" s="33" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="K26" s="33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="L26" s="33">
         <v>-3</v>
@@ -4379,10 +4388,10 @@
         <v>0</v>
       </c>
       <c r="E27" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="F27" s="36" t="s">
         <v>91</v>
-      </c>
-      <c r="F27" s="36" t="s">
-        <v>92</v>
       </c>
       <c r="G27" s="33" t="s">
         <v>23</v>
@@ -4397,7 +4406,7 @@
         <v>25</v>
       </c>
       <c r="K27" s="33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="L27" s="33">
         <v>-1000</v>
@@ -4446,10 +4455,10 @@
         <v>1</v>
       </c>
       <c r="E28" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="36" t="s">
         <v>93</v>
-      </c>
-      <c r="F28" s="36" t="s">
-        <v>94</v>
       </c>
       <c r="G28" s="33" t="s">
         <v>23</v>
@@ -4464,7 +4473,7 @@
         <v>25</v>
       </c>
       <c r="K28" s="33" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L28" s="33">
         <v>-1000</v>
@@ -4513,10 +4522,10 @@
         <v>2</v>
       </c>
       <c r="E29" s="33" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="36" t="s">
         <v>95</v>
-      </c>
-      <c r="F29" s="36" t="s">
-        <v>96</v>
       </c>
       <c r="G29" s="33" t="s">
         <v>23</v>
@@ -4531,7 +4540,7 @@
         <v>25</v>
       </c>
       <c r="K29" s="33" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="L29" s="33">
         <v>900</v>
@@ -4580,10 +4589,10 @@
         <v>2</v>
       </c>
       <c r="E30" s="33" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" s="36" t="s">
         <v>97</v>
-      </c>
-      <c r="F30" s="36" t="s">
-        <v>98</v>
       </c>
       <c r="G30" s="33" t="s">
         <v>23</v>
@@ -4598,7 +4607,7 @@
         <v>25</v>
       </c>
       <c r="K30" s="33" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="L30" s="33">
         <v>310</v>
@@ -4647,10 +4656,10 @@
         <v>1</v>
       </c>
       <c r="E31" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="F31" s="36" t="s">
         <v>99</v>
-      </c>
-      <c r="F31" s="36" t="s">
-        <v>100</v>
       </c>
       <c r="G31" s="33" t="s">
         <v>23</v>
@@ -4665,7 +4674,7 @@
         <v>25</v>
       </c>
       <c r="K31" s="33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L31" s="33">
         <v>400</v>
@@ -4714,10 +4723,10 @@
         <v>17</v>
       </c>
       <c r="E32" s="33" t="s">
+        <v>100</v>
+      </c>
+      <c r="F32" s="36" t="s">
         <v>101</v>
-      </c>
-      <c r="F32" s="36" t="s">
-        <v>102</v>
       </c>
       <c r="G32" s="33" t="s">
         <v>23</v>
@@ -4732,7 +4741,7 @@
         <v>25</v>
       </c>
       <c r="K32" s="33" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="L32" s="33">
         <v>-8000</v>
@@ -4781,10 +4790,10 @@
         <v>2</v>
       </c>
       <c r="E33" s="33" t="s">
+        <v>580</v>
+      </c>
+      <c r="F33" s="36" t="s">
         <v>581</v>
-      </c>
-      <c r="F33" s="36" t="s">
-        <v>582</v>
       </c>
       <c r="G33" s="33" t="s">
         <v>23</v>
@@ -4799,7 +4808,7 @@
         <v>25</v>
       </c>
       <c r="K33" s="33" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="L33" s="33">
         <v>13000</v>
@@ -4848,10 +4857,10 @@
         <v>2</v>
       </c>
       <c r="E34" s="33" t="s">
+        <v>98</v>
+      </c>
+      <c r="F34" s="36" t="s">
         <v>99</v>
-      </c>
-      <c r="F34" s="36" t="s">
-        <v>100</v>
       </c>
       <c r="G34" s="33" t="s">
         <v>23</v>
@@ -4866,7 +4875,7 @@
         <v>25</v>
       </c>
       <c r="K34" s="33" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L34" s="33">
         <v>400</v>
@@ -4915,10 +4924,10 @@
         <v>4</v>
       </c>
       <c r="E35" s="33" t="s">
+        <v>582</v>
+      </c>
+      <c r="F35" s="36" t="s">
         <v>583</v>
-      </c>
-      <c r="F35" s="36" t="s">
-        <v>584</v>
       </c>
       <c r="G35" s="33" t="s">
         <v>23</v>
@@ -4930,10 +4939,10 @@
         <v>32</v>
       </c>
       <c r="J35" s="33" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K35" s="33" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="L35" s="33">
         <v>1</v>
@@ -4985,7 +4994,7 @@
         <v>56</v>
       </c>
       <c r="F36" s="36" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="G36" s="33" t="s">
         <v>23</v>
@@ -5049,10 +5058,10 @@
         <v>1</v>
       </c>
       <c r="E37" s="33" t="s">
+        <v>585</v>
+      </c>
+      <c r="F37" s="36" t="s">
         <v>586</v>
-      </c>
-      <c r="F37" s="36" t="s">
-        <v>587</v>
       </c>
       <c r="G37" s="33" t="s">
         <v>23</v>
@@ -5067,7 +5076,7 @@
         <v>25</v>
       </c>
       <c r="K37" s="33" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="L37" s="33">
         <v>250</v>
@@ -5116,10 +5125,10 @@
         <v>1</v>
       </c>
       <c r="E38" s="33" t="s">
+        <v>587</v>
+      </c>
+      <c r="F38" s="36" t="s">
         <v>588</v>
-      </c>
-      <c r="F38" s="36" t="s">
-        <v>589</v>
       </c>
       <c r="G38" s="33" t="s">
         <v>23</v>
@@ -5131,10 +5140,10 @@
         <v>32</v>
       </c>
       <c r="J38" s="33" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K38" s="33" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="L38" s="33">
         <v>1</v>
@@ -5183,10 +5192,10 @@
         <v>7</v>
       </c>
       <c r="E39" s="33" t="s">
+        <v>590</v>
+      </c>
+      <c r="F39" s="36" t="s">
         <v>591</v>
-      </c>
-      <c r="F39" s="36" t="s">
-        <v>592</v>
       </c>
       <c r="G39" s="33" t="s">
         <v>23</v>
@@ -5201,7 +5210,7 @@
         <v>48</v>
       </c>
       <c r="K39" s="33" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="L39" s="33">
         <v>2000</v>
@@ -5251,10 +5260,10 @@
         <v>5</v>
       </c>
       <c r="E40" s="33" t="s">
+        <v>592</v>
+      </c>
+      <c r="F40" s="36" t="s">
         <v>593</v>
-      </c>
-      <c r="F40" s="36" t="s">
-        <v>594</v>
       </c>
       <c r="G40" s="33" t="s">
         <v>23</v>
@@ -5269,7 +5278,7 @@
         <v>25</v>
       </c>
       <c r="K40" s="33" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="L40" s="33">
         <v>1000</v>
@@ -5319,10 +5328,10 @@
         <v>2</v>
       </c>
       <c r="E41" s="33" t="s">
+        <v>594</v>
+      </c>
+      <c r="F41" s="36" t="s">
         <v>595</v>
-      </c>
-      <c r="F41" s="36" t="s">
-        <v>596</v>
       </c>
       <c r="G41" s="33" t="s">
         <v>23</v>
@@ -5337,7 +5346,7 @@
         <v>25</v>
       </c>
       <c r="K41" s="33" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="L41" s="33">
         <v>700</v>
@@ -5386,10 +5395,10 @@
         <v>2</v>
       </c>
       <c r="E42" s="33" t="s">
+        <v>596</v>
+      </c>
+      <c r="F42" s="36" t="s">
         <v>597</v>
-      </c>
-      <c r="F42" s="36" t="s">
-        <v>598</v>
       </c>
       <c r="G42" s="33" t="s">
         <v>23</v>
@@ -5404,7 +5413,7 @@
         <v>25</v>
       </c>
       <c r="K42" s="33" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="L42" s="33">
         <v>300</v>
@@ -5454,10 +5463,10 @@
         <v>15</v>
       </c>
       <c r="E43" s="33" t="s">
+        <v>598</v>
+      </c>
+      <c r="F43" s="36" t="s">
         <v>599</v>
-      </c>
-      <c r="F43" s="36" t="s">
-        <v>600</v>
       </c>
       <c r="G43" s="33" t="s">
         <v>23</v>
@@ -5472,7 +5481,7 @@
         <v>25</v>
       </c>
       <c r="K43" s="33" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="L43" s="33">
         <v>-700</v>
@@ -5522,10 +5531,10 @@
         <v>2</v>
       </c>
       <c r="E44" s="33" t="s">
+        <v>600</v>
+      </c>
+      <c r="F44" s="36" t="s">
         <v>601</v>
-      </c>
-      <c r="F44" s="36" t="s">
-        <v>602</v>
       </c>
       <c r="G44" s="33" t="s">
         <v>23</v>
@@ -5540,7 +5549,7 @@
         <v>25</v>
       </c>
       <c r="K44" s="33" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="L44" s="33">
         <v>400</v>
@@ -5593,7 +5602,7 @@
         <v>79</v>
       </c>
       <c r="F45" s="36" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="G45" s="33" t="s">
         <v>23</v>
@@ -5605,7 +5614,7 @@
         <v>32</v>
       </c>
       <c r="J45" s="33" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="K45" s="33" t="s">
         <v>79</v>
@@ -5657,10 +5666,10 @@
         <v>1</v>
       </c>
       <c r="E46" s="33" t="s">
+        <v>603</v>
+      </c>
+      <c r="F46" s="36" t="s">
         <v>604</v>
-      </c>
-      <c r="F46" s="36" t="s">
-        <v>605</v>
       </c>
       <c r="G46" s="33" t="s">
         <v>23</v>
@@ -5675,7 +5684,7 @@
         <v>25</v>
       </c>
       <c r="K46" s="33" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="L46" s="33">
         <v>2000</v>
@@ -5725,10 +5734,10 @@
         <v>14</v>
       </c>
       <c r="E47" s="47" t="s">
+        <v>605</v>
+      </c>
+      <c r="F47" s="48" t="s">
         <v>606</v>
-      </c>
-      <c r="F47" s="48" t="s">
-        <v>607</v>
       </c>
       <c r="G47" s="47" t="s">
         <v>23</v>
@@ -5743,7 +5752,7 @@
         <v>25</v>
       </c>
       <c r="K47" s="47" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="L47" s="47">
         <v>-600</v>
@@ -5755,11 +5764,11 @@
         <v>72</v>
       </c>
       <c r="O47" s="47">
-        <v>265.44</v>
+        <v>263.01</v>
       </c>
       <c r="P47" s="49">
         <f>ABS(O47*L47)</f>
-        <v>159264</v>
+        <v>157806</v>
       </c>
       <c r="Q47" s="47">
         <v>10.1</v>
@@ -5778,7 +5787,7 @@
       </c>
       <c r="V47" s="33">
         <f>(M47-O47)*600</f>
-        <v>1590.6000000000063</v>
+        <v>3048.6000000000104</v>
       </c>
     </row>
     <row r="48" spans="1:22" x14ac:dyDescent="0.25">
@@ -5811,10 +5820,10 @@
         <v>32</v>
       </c>
       <c r="J48" s="33" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K48" s="33" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="L48" s="33">
         <v>30</v>
@@ -5864,10 +5873,10 @@
         <v>1</v>
       </c>
       <c r="E49" s="33" t="s">
+        <v>608</v>
+      </c>
+      <c r="F49" s="36" t="s">
         <v>609</v>
-      </c>
-      <c r="F49" s="36" t="s">
-        <v>610</v>
       </c>
       <c r="G49" s="33" t="s">
         <v>23</v>
@@ -5879,10 +5888,10 @@
         <v>32</v>
       </c>
       <c r="J49" s="33" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="K49" s="33" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="L49" s="33">
         <v>-2</v>
@@ -5931,10 +5940,10 @@
         <v>0</v>
       </c>
       <c r="E50" s="33" t="s">
+        <v>612</v>
+      </c>
+      <c r="F50" s="36" t="s">
         <v>613</v>
-      </c>
-      <c r="F50" s="36" t="s">
-        <v>614</v>
       </c>
       <c r="G50" s="33" t="s">
         <v>23</v>
@@ -5949,7 +5958,7 @@
         <v>25</v>
       </c>
       <c r="K50" s="33" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="L50" s="33">
         <v>-750</v>
@@ -5998,10 +6007,10 @@
         <v>3</v>
       </c>
       <c r="E51" s="33" t="s">
+        <v>614</v>
+      </c>
+      <c r="F51" s="36" t="s">
         <v>615</v>
-      </c>
-      <c r="F51" s="36" t="s">
-        <v>616</v>
       </c>
       <c r="G51" s="33" t="s">
         <v>23</v>
@@ -6016,7 +6025,7 @@
         <v>25</v>
       </c>
       <c r="K51" s="33" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="L51" s="33">
         <v>700</v>
@@ -6066,10 +6075,10 @@
         <v>4</v>
       </c>
       <c r="E52" s="33" t="s">
+        <v>616</v>
+      </c>
+      <c r="F52" s="36" t="s">
         <v>617</v>
-      </c>
-      <c r="F52" s="36" t="s">
-        <v>618</v>
       </c>
       <c r="G52" s="33" t="s">
         <v>23</v>
@@ -6084,7 +6093,7 @@
         <v>25</v>
       </c>
       <c r="K52" s="33" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="L52" s="33">
         <v>-110</v>
@@ -6134,10 +6143,10 @@
         <v>2</v>
       </c>
       <c r="E53" s="33" t="s">
+        <v>618</v>
+      </c>
+      <c r="F53" s="36" t="s">
         <v>619</v>
-      </c>
-      <c r="F53" s="36" t="s">
-        <v>620</v>
       </c>
       <c r="G53" s="33" t="s">
         <v>23</v>
@@ -6152,7 +6161,7 @@
         <v>25</v>
       </c>
       <c r="K53" s="33" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="L53" s="33">
         <v>4000</v>
@@ -6202,16 +6211,16 @@
         <v>7</v>
       </c>
       <c r="E54" s="33" t="s">
+        <v>620</v>
+      </c>
+      <c r="F54" s="36" t="s">
         <v>621</v>
-      </c>
-      <c r="F54" s="36" t="s">
-        <v>622</v>
       </c>
       <c r="G54" s="33" t="s">
         <v>30</v>
       </c>
       <c r="H54" s="36" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="I54" s="33" t="s">
         <v>48</v>
@@ -6220,7 +6229,7 @@
         <v>48</v>
       </c>
       <c r="K54" s="33" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="L54" s="33">
         <v>400</v>
@@ -6270,16 +6279,16 @@
         <v>7</v>
       </c>
       <c r="E55" s="33" t="s">
+        <v>623</v>
+      </c>
+      <c r="F55" s="36" t="s">
         <v>624</v>
-      </c>
-      <c r="F55" s="36" t="s">
-        <v>625</v>
       </c>
       <c r="G55" s="33" t="s">
         <v>30</v>
       </c>
       <c r="H55" s="36" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="I55" s="33" t="s">
         <v>48</v>
@@ -6288,7 +6297,7 @@
         <v>48</v>
       </c>
       <c r="K55" s="33" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="L55" s="33">
         <v>-140</v>
@@ -6338,10 +6347,10 @@
         <v>1</v>
       </c>
       <c r="E56" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="F56" s="36" t="s">
         <v>626</v>
-      </c>
-      <c r="F56" s="36" t="s">
-        <v>627</v>
       </c>
       <c r="G56" s="33" t="s">
         <v>23</v>
@@ -6356,7 +6365,7 @@
         <v>25</v>
       </c>
       <c r="K56" s="33" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="L56" s="33">
         <v>-100</v>
@@ -6406,10 +6415,10 @@
         <v>1</v>
       </c>
       <c r="E57" s="33" t="s">
+        <v>627</v>
+      </c>
+      <c r="F57" s="36" t="s">
         <v>628</v>
-      </c>
-      <c r="F57" s="36" t="s">
-        <v>629</v>
       </c>
       <c r="G57" s="33" t="s">
         <v>23</v>
@@ -6424,7 +6433,7 @@
         <v>25</v>
       </c>
       <c r="K57" s="33" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="L57" s="33">
         <v>-100</v>
@@ -6557,10 +6566,10 @@
         <v>32</v>
       </c>
       <c r="J59" s="47" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="K59" s="47" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="L59" s="47">
         <v>10</v>
@@ -6594,7 +6603,7 @@
         <v>72</v>
       </c>
       <c r="V59" s="33">
-        <v>-130</v>
+        <v>-350</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
@@ -6627,10 +6636,10 @@
         <v>32</v>
       </c>
       <c r="J60" s="33" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K60" s="33" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="L60" s="33">
         <v>10</v>
@@ -6695,10 +6704,10 @@
         <v>32</v>
       </c>
       <c r="J61" s="33" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="K61" s="33" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="L61" s="33">
         <v>15</v>
@@ -6734,26 +6743,142 @@
       </c>
     </row>
     <row r="62" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B62" s="34"/>
-      <c r="C62" s="34"/>
-      <c r="D62" s="35"/>
-      <c r="F62" s="36"/>
-      <c r="H62" s="36"/>
-      <c r="P62" s="39"/>
-      <c r="S62" s="40"/>
-      <c r="T62" s="39"/>
-      <c r="U62" s="41"/>
+      <c r="A62" s="33">
+        <v>56</v>
+      </c>
+      <c r="B62" s="34">
+        <v>46303</v>
+      </c>
+      <c r="C62" s="55">
+        <v>46303</v>
+      </c>
+      <c r="D62" s="56">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="E62" s="47" t="s">
+        <v>88</v>
+      </c>
+      <c r="F62" s="48" t="s">
+        <v>52</v>
+      </c>
+      <c r="G62" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="H62" s="48" t="s">
+        <v>630</v>
+      </c>
+      <c r="I62" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="J62" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="K62" s="47" t="s">
+        <v>89</v>
+      </c>
+      <c r="L62" s="47">
+        <v>2</v>
+      </c>
+      <c r="M62" s="47">
+        <v>4147.25</v>
+      </c>
+      <c r="N62" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O62" s="47">
+        <v>4160.8</v>
+      </c>
+      <c r="P62" s="49">
+        <v>83214</v>
+      </c>
+      <c r="Q62" s="47">
+        <v>3.2</v>
+      </c>
+      <c r="R62" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S62" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T62" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="U62" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V62" s="33">
+        <v>277</v>
+      </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B63" s="34"/>
-      <c r="C63" s="34"/>
-      <c r="D63" s="35"/>
-      <c r="F63" s="36"/>
-      <c r="H63" s="36"/>
-      <c r="P63" s="39"/>
-      <c r="S63" s="40"/>
-      <c r="T63" s="39"/>
-      <c r="U63" s="41"/>
+      <c r="A63" s="33">
+        <v>56</v>
+      </c>
+      <c r="B63" s="34">
+        <v>46303</v>
+      </c>
+      <c r="C63" s="55">
+        <v>46303</v>
+      </c>
+      <c r="D63" s="56">
+        <f t="shared" ref="D63" si="13">C63-B63</f>
+        <v>0</v>
+      </c>
+      <c r="E63" s="47" t="s">
+        <v>631</v>
+      </c>
+      <c r="F63" s="48" t="s">
+        <v>632</v>
+      </c>
+      <c r="G63" s="47" t="s">
+        <v>30</v>
+      </c>
+      <c r="H63" s="48" t="s">
+        <v>630</v>
+      </c>
+      <c r="I63" s="47" t="s">
+        <v>32</v>
+      </c>
+      <c r="J63" s="47" t="s">
+        <v>122</v>
+      </c>
+      <c r="K63" s="47" t="s">
+        <v>633</v>
+      </c>
+      <c r="L63" s="47">
+        <v>-5</v>
+      </c>
+      <c r="M63" s="47">
+        <v>6.6289999999999996</v>
+      </c>
+      <c r="N63" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O63" s="47">
+        <v>6.5579999999999998</v>
+      </c>
+      <c r="P63" s="49">
+        <v>81975</v>
+      </c>
+      <c r="Q63" s="47">
+        <v>3.2</v>
+      </c>
+      <c r="R63" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S63" s="50" t="s">
+        <v>72</v>
+      </c>
+      <c r="T63" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="U63" s="49" t="s">
+        <v>72</v>
+      </c>
+      <c r="V63" s="33">
+        <v>888</v>
+      </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
       <c r="B64" s="34"/>
@@ -6772,7 +6897,7 @@
     </row>
     <row r="66" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D66" s="52" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="E66" s="46">
         <f>AVERAGE(D2:D61)</f>
@@ -6786,12 +6911,12 @@
       </c>
       <c r="V66" s="39">
         <f>SUM(V2:V64)</f>
-        <v>1460.6000000000063</v>
+        <v>3863.6000000000104</v>
       </c>
     </row>
     <row r="67" spans="4:22" x14ac:dyDescent="0.25">
       <c r="D67" s="52" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="E67" s="46">
         <f>AVERAGE(D2:D11,D13,D15:D61)</f>
@@ -6799,23 +6924,23 @@
       </c>
       <c r="F67" s="36"/>
       <c r="U67" s="53" t="s">
+        <v>104</v>
+      </c>
+      <c r="V67" s="36" t="s">
         <v>105</v>
-      </c>
-      <c r="V67" s="36" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="68" spans="4:22" x14ac:dyDescent="0.25">
       <c r="F68" s="36"/>
       <c r="U68" s="33" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="69" spans="4:22" x14ac:dyDescent="0.25">
       <c r="F69" s="36"/>
       <c r="U69" s="39">
         <f>U66+V66</f>
-        <v>82608.070000000007</v>
+        <v>85011.07</v>
       </c>
     </row>
     <row r="70" spans="4:22" x14ac:dyDescent="0.25">
@@ -6824,7 +6949,7 @@
     <row r="71" spans="4:22" x14ac:dyDescent="0.25">
       <c r="F71" s="36"/>
       <c r="U71" s="36" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="72" spans="4:22" x14ac:dyDescent="0.25">
@@ -6835,13 +6960,13 @@
     </row>
     <row r="74" spans="4:22" x14ac:dyDescent="0.25">
       <c r="U74" s="33" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="75" spans="4:22" x14ac:dyDescent="0.25">
       <c r="U75" s="54">
         <f>U69/U72</f>
-        <v>0.24807228228228231</v>
+        <v>0.2552884984984985</v>
       </c>
     </row>
   </sheetData>
@@ -6854,7 +6979,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:I86"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -6869,16 +6994,16 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="22" t="s">
+        <v>109</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="22" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="D1" s="23" t="s">
         <v>112</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>113</v>
       </c>
       <c r="G1" s="25"/>
     </row>
@@ -6920,11 +7045,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C86" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C87" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D86" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D87" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -8097,14 +8222,14 @@
         <v>1.3941407429779523E-3</v>
       </c>
       <c r="F74" s="25" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="G74" s="27">
-        <f>AVERAGE(C3:C86)</f>
+        <f>AVERAGE(C3:C87)</f>
+        <v>1014.5069411764701</v>
+      </c>
+      <c r="I74" s="27">
         <v>998.5129761904758</v>
-      </c>
-      <c r="I74" s="27">
-        <v>902.21795180722847</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -8124,14 +8249,14 @@
         <v>9.4992906295542062E-3</v>
       </c>
       <c r="F75" s="25" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="G75" s="27">
-        <f>_xlfn.STDEV.S(C3:C86)</f>
+        <f>_xlfn.STDEV.S(C3:C87)</f>
+        <v>4165.6841486600597</v>
+      </c>
+      <c r="I75" s="27">
         <v>4188.0771538061736</v>
-      </c>
-      <c r="I75" s="27">
-        <v>4118.9178440263222</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
@@ -8151,14 +8276,14 @@
         <v>-5.9729103776628928E-3</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
+        <v>3.8660632547935578</v>
+      </c>
+      <c r="I76" s="28">
         <v>3.7847684063843623</v>
-      </c>
-      <c r="I76" s="28">
-        <v>3.4771914652125262</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
@@ -8178,14 +8303,14 @@
         <v>4.4963812546586836E-4</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="G77" s="29">
-        <f>_xlfn.STDEV.S(D2:D86)*SQRT(252)</f>
+        <f>_xlfn.STDEV.S(D2:D87)*SQRT(252)</f>
+        <v>0.17837525027910547</v>
+      </c>
+      <c r="I77" s="29">
         <v>0.17936221602538568</v>
-      </c>
-      <c r="I77" s="29">
-        <v>0.17723571184916939</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -8205,14 +8330,14 @@
         <v>8.3734501065908466E-3</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="G78" s="29" cm="1">
-        <f t="array" ref="G78">PRODUCT(1+D3:D86)-1</f>
+        <f t="array" ref="G78">PRODUCT(1+D3:D87)-1</f>
+        <v>0.25860436774327011</v>
+      </c>
+      <c r="I78" s="29">
         <v>0.25153296701764072</v>
-      </c>
-      <c r="I78" s="29">
-        <v>0.22456987799129102</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -8232,14 +8357,14 @@
         <v>9.6529467705530299E-4</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="G79" s="29" cm="1">
-        <f t="array" ref="G79">PRODUCT(1+D2:D86)^(252/COUNT(D2:D86))-1</f>
+        <f t="array" ref="G79">PRODUCT(1+D2:D87)^(252/COUNT(D2:D87))-1</f>
+        <v>0.96199857349895557</v>
+      </c>
+      <c r="I79" s="29">
         <v>0.94485730362176024</v>
-      </c>
-      <c r="I79" s="29">
-        <v>0.83632994929563176</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -8359,6 +8484,23 @@
       <c r="D86" s="23">
         <f t="shared" si="1"/>
         <v>2.2018416025860802E-2</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A87" s="26">
+        <v>46303</v>
+      </c>
+      <c r="B87" s="5">
+        <f>B86+1458+1100-200</f>
+        <v>419689</v>
+      </c>
+      <c r="C87" s="5">
+        <f t="shared" si="0"/>
+        <v>2358</v>
+      </c>
+      <c r="D87" s="23">
+        <f t="shared" si="1"/>
+        <v>5.650191334935579E-3</v>
       </c>
     </row>
   </sheetData>
@@ -8397,73 +8539,73 @@
   <sheetData>
     <row r="1" spans="1:23" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>522</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>523</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>524</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>525</v>
-      </c>
       <c r="E1" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>122</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>530</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>123</v>
-      </c>
-      <c r="G1" s="8" t="s">
+      <c r="H1" s="8" t="s">
         <v>531</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>532</v>
-      </c>
       <c r="I1" s="8" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="K1" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="L1" s="8" t="s">
         <v>48</v>
       </c>
       <c r="M1" s="9" t="s">
+        <v>525</v>
+      </c>
+      <c r="N1" s="8" t="s">
         <v>526</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>527</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="8" t="s">
+        <v>535</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>536</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>537</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>538</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>539</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>589</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>611</v>
+      </c>
+      <c r="W1" s="8" t="s">
         <v>528</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>536</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>537</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>539</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>540</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>590</v>
-      </c>
-      <c r="V1" s="8" t="s">
-        <v>612</v>
-      </c>
-      <c r="W1" s="8" t="s">
-        <v>529</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
@@ -13312,7 +13454,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="14">
-        <f t="shared" ref="M69:M93" si="0">SUM(C69:L69)</f>
+        <f t="shared" ref="M69:M94" si="0">SUM(C69:L69)</f>
         <v>407651</v>
       </c>
       <c r="N69" s="15">
@@ -15202,6 +15344,87 @@
       </c>
       <c r="W93" s="15">
         <f t="shared" ref="W93" si="71">L93/M93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A94" s="10">
+        <v>46303</v>
+      </c>
+      <c r="B94" s="11">
+        <v>419689</v>
+      </c>
+      <c r="C94" s="19">
+        <v>160440</v>
+      </c>
+      <c r="D94" s="13">
+        <f>B94-C94-H94-L94-F94</f>
+        <v>76400</v>
+      </c>
+      <c r="E94" s="13">
+        <v>0</v>
+      </c>
+      <c r="F94" s="13">
+        <v>165189</v>
+      </c>
+      <c r="G94" s="13">
+        <v>0</v>
+      </c>
+      <c r="H94" s="13">
+        <v>17660</v>
+      </c>
+      <c r="I94" s="13">
+        <v>0</v>
+      </c>
+      <c r="J94" s="13">
+        <v>0</v>
+      </c>
+      <c r="K94" s="13">
+        <v>0</v>
+      </c>
+      <c r="L94" s="18">
+        <v>0</v>
+      </c>
+      <c r="M94" s="14">
+        <f t="shared" si="0"/>
+        <v>419689</v>
+      </c>
+      <c r="N94" s="15">
+        <f t="shared" ref="N94" si="72">C94/M94</f>
+        <v>0.38228307151247709</v>
+      </c>
+      <c r="O94" s="15">
+        <f t="shared" ref="O94" si="73">D94/M94</f>
+        <v>0.18203955786308434</v>
+      </c>
+      <c r="P94" s="15">
+        <f>F94/M94</f>
+        <v>0.393598593244045</v>
+      </c>
+      <c r="Q94" s="15">
+        <f>E94/M94</f>
+        <v>0</v>
+      </c>
+      <c r="R94" s="15">
+        <v>0</v>
+      </c>
+      <c r="S94" s="15">
+        <f t="shared" ref="S94" si="74">H94/M94</f>
+        <v>4.2078777380393576E-2</v>
+      </c>
+      <c r="T94" s="15">
+        <f t="shared" ref="T94" si="75">I94/M94</f>
+        <v>0</v>
+      </c>
+      <c r="U94" s="15">
+        <v>0</v>
+      </c>
+      <c r="V94" s="16">
+        <f t="shared" ref="V94" si="76">K94/M94</f>
+        <v>0</v>
+      </c>
+      <c r="W94" s="15">
+        <f t="shared" ref="W94" si="77">L94/M94</f>
         <v>0</v>
       </c>
     </row>
@@ -15240,386 +15463,386 @@
   <sheetData>
     <row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>125</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>129</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>130</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>142</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>143</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>146</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>154</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>155</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>159</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>160</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>165</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>176</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>177</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>181</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>182</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="L6" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>195</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>198</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>199</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="3" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>208</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="L9" s="3" t="s">
         <v>217</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>220</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="L10" s="3" t="s">
         <v>225</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>226</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>227</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>228</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>230</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>233</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -15630,22 +15853,22 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="3" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>238</v>
-      </c>
       <c r="K12" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -15656,20 +15879,20 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="3" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>243</v>
-      </c>
       <c r="K13" s="3" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -15680,20 +15903,20 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="3" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>247</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>248</v>
-      </c>
       <c r="K14" s="3" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -15704,20 +15927,20 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>253</v>
-      </c>
       <c r="K15" s="3" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -15728,25 +15951,25 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>258</v>
-      </c>
       <c r="K16" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="B17" s="3">
         <v>7</v>
@@ -15756,25 +15979,25 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>264</v>
-      </c>
       <c r="K17" s="3" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B18" s="3">
         <v>10</v>
@@ -15784,25 +16007,25 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>268</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>269</v>
-      </c>
       <c r="K18" s="3" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B19" s="3">
         <v>10</v>
@@ -15812,25 +16035,25 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3" t="s">
+        <v>272</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>273</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>274</v>
-      </c>
       <c r="K19" s="3" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B20" s="3">
         <v>6</v>
@@ -15840,25 +16063,25 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3" t="s">
+        <v>277</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>278</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>279</v>
-      </c>
       <c r="K20" s="3" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B21" s="3">
         <v>8</v>
@@ -15868,25 +16091,25 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>283</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>284</v>
-      </c>
       <c r="K21" s="3" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B22" s="3">
         <v>2</v>
@@ -15896,25 +16119,25 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>288</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>289</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>285</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>290</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B23" s="3">
         <v>149</v>
@@ -15924,23 +16147,23 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3" t="s">
+        <v>291</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>292</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>293</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="B24" s="3">
         <v>11</v>
@@ -15950,21 +16173,21 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>298</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B25" s="3">
         <v>97</v>
@@ -15974,21 +16197,21 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B26" s="3">
         <v>32</v>
@@ -15998,14 +16221,14 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3" t="s">
+        <v>302</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>303</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>304</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
@@ -16022,21 +16245,21 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3" t="s">
+        <v>305</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>306</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>307</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
     </row>
     <row r="28" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B28" s="3">
         <v>22</v>
@@ -16046,21 +16269,21 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="3" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3" t="s">
+        <v>308</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>309</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>310</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
     </row>
     <row r="29" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B29" s="3">
         <f>SUM(B17:B28)</f>
@@ -16071,14 +16294,14 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>313</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>314</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
@@ -16091,14 +16314,14 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>317</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="2"/>
@@ -16111,14 +16334,14 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3" t="s">
+        <v>318</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>319</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>320</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="2"/>
@@ -16131,14 +16354,14 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3" t="s">
+        <v>321</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>322</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>323</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="2"/>
@@ -16151,14 +16374,14 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="3" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3" t="s">
+        <v>324</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>325</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>326</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="2"/>
@@ -16171,11 +16394,11 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="2"/>
@@ -16189,11 +16412,11 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="3" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="2"/>
@@ -16201,1037 +16424,1037 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G36" s="3" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G37" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G38" s="3" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G39" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G40" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G41" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G42" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G43" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G44" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G45" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G46" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G47" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G48" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="49" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G49" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
     </row>
     <row r="50" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G50" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="51" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G51" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="52" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G52" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="53" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G53" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="54" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G54" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="55" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G55" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="56" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G56" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="57" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G57" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="58" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G58" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
     </row>
     <row r="59" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G59" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
     </row>
     <row r="60" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G60" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
     </row>
     <row r="61" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G61" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
     </row>
     <row r="62" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G62" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
     </row>
     <row r="63" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G63" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
     </row>
     <row r="64" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G64" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
     </row>
     <row r="65" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G65" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
     </row>
     <row r="66" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G66" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="67" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G67" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
     </row>
     <row r="68" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G68" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
     </row>
     <row r="69" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G69" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
     </row>
     <row r="70" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G70" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
     </row>
     <row r="71" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G71" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="72" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G72" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="73" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G73" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="74" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G74" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="75" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G75" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
     </row>
     <row r="76" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G76" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
     </row>
     <row r="77" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G77" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
     </row>
     <row r="78" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G78" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="79" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G79" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="80" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G80" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="81" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G81" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="82" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G82" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="83" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G83" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="84" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G84" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="85" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G85" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="86" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G86" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="87" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G87" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="88" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G88" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="89" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G89" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="90" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G90" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="91" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G91" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="92" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G92" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="93" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G93" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="94" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G94" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="95" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G95" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="96" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G96" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="97" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G97" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="98" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G98" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="99" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G99" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="100" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G100" s="3" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="101" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G101" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="102" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G102" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="103" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G103" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="104" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G104" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="105" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G105" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="106" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G106" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="107" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G107" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="108" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G108" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="109" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G109" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="110" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G110" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="111" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G111" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="112" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G112" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="113" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G113" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="114" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G114" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="115" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G115" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="116" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G116" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
     </row>
     <row r="117" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G117" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="118" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G118" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="119" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G119" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="120" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G120" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="121" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G121" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="122" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G122" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="123" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G123" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="124" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G124" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="125" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G125" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="126" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G126" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="127" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G127" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="128" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G128" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="129" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G129" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="130" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G130" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="131" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G131" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="132" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G132" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="133" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G133" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="134" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G134" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="135" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G135" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="136" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G136" s="3" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="137" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G137" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="138" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G138" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="139" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G139" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="140" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G140" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="141" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G141" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="142" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G142" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="143" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G143" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
     </row>
     <row r="144" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G144" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="145" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G145" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="146" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G146" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="147" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G147" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="148" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G148" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="149" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G149" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="150" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G150" s="3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
     </row>
     <row r="151" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G151" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="152" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G152" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="153" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G153" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="154" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G154" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="155" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G155" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="156" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G156" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="157" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G157" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="158" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G158" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="159" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G159" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="160" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G160" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="161" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G161" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="162" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G162" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="163" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G163" s="3" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
     </row>
     <row r="164" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G164" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
     </row>
     <row r="165" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G165" s="3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="166" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G166" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="167" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G167" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="168" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G168" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="169" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G169" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="170" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G170" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="171" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G171" s="3" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="172" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G172" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="173" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G173" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="174" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G174" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
     </row>
     <row r="175" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G175" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="176" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G176" s="3" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="177" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G177" s="3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="178" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G178" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="179" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G179" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="180" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G180" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
     </row>
     <row r="181" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G181" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="182" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G182" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="183" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G183" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="184" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G184" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="185" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G185" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="186" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G186" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="187" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G187" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="188" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G188" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="189" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G189" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="190" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G190" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="191" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G191" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="192" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G192" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
     <row r="193" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G193" s="3" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="194" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G194" s="3" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
     </row>
     <row r="195" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G195" s="3" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
     </row>
     <row r="196" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G196" s="3" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="197" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G197" s="3" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="198" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G198" s="3" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="199" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G199" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="200" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G200" s="3" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="201" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G201" s="3" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="202" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G202" s="3" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="203" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G203" s="3" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="204" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G204" s="3" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
   </sheetData>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C61EEE90-9FF4-8B41-A169-64B68F6DF631}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9CF8DAC-8401-7644-B21F-28D21E6E6015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19580" yWindow="-41980" windowWidth="48520" windowHeight="32580" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="280" yWindow="520" windowWidth="40660" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -6390,7 +6390,7 @@
         <v>1</v>
       </c>
       <c r="S56" s="40">
-        <f t="shared" ref="S56:S61" si="12">IF(R56=1, ABS(N56-M56)/M56, 0)</f>
+        <f t="shared" ref="S56:S63" si="12">IF(R56=1, ABS(N56-M56)/M56, 0)</f>
         <v>2.7360178970917266E-2</v>
       </c>
       <c r="T56" s="39">
@@ -6750,11 +6750,11 @@
         <v>46303</v>
       </c>
       <c r="C62" s="55">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D62" s="56">
         <f t="shared" si="5"/>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E62" s="47" t="s">
         <v>88</v>
@@ -6778,22 +6778,22 @@
         <v>89</v>
       </c>
       <c r="L62" s="47">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M62" s="47">
-        <v>4147.25</v>
+        <v>4209.1099999999997</v>
       </c>
       <c r="N62" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O62" s="47">
-        <v>4160.8</v>
+        <v>4206.3999999999996</v>
       </c>
       <c r="P62" s="49">
-        <v>83214</v>
+        <v>42070</v>
       </c>
       <c r="Q62" s="47">
-        <v>3.2</v>
+        <v>3.84</v>
       </c>
       <c r="R62" s="47" t="s">
         <v>72</v>
@@ -6804,11 +6804,11 @@
       <c r="T62" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="U62" s="49" t="s">
+      <c r="U62" s="41" t="s">
         <v>72</v>
       </c>
       <c r="V62" s="33">
-        <v>277</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
@@ -6819,11 +6819,11 @@
         <v>46303</v>
       </c>
       <c r="C63" s="55">
-        <v>46303</v>
+        <v>46304</v>
       </c>
       <c r="D63" s="56">
         <f t="shared" ref="D63" si="13">C63-B63</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E63" s="47" t="s">
         <v>631</v>
@@ -6847,22 +6847,22 @@
         <v>633</v>
       </c>
       <c r="L63" s="47">
-        <v>-5</v>
+        <v>-3</v>
       </c>
       <c r="M63" s="47">
-        <v>6.6289999999999996</v>
+        <v>6.6917</v>
       </c>
       <c r="N63" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O63" s="47">
-        <v>6.5579999999999998</v>
+        <v>6.6870000000000003</v>
       </c>
       <c r="P63" s="49">
-        <v>81975</v>
+        <v>50164</v>
       </c>
       <c r="Q63" s="47">
-        <v>3.2</v>
+        <v>11.52</v>
       </c>
       <c r="R63" s="47" t="s">
         <v>72</v>
@@ -6873,11 +6873,8 @@
       <c r="T63" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="U63" s="49" t="s">
+      <c r="U63" s="41" t="s">
         <v>72</v>
-      </c>
-      <c r="V63" s="33">
-        <v>888</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
@@ -6911,7 +6908,7 @@
       </c>
       <c r="V66" s="39">
         <f>SUM(V2:V64)</f>
-        <v>3863.6000000000104</v>
+        <v>3719.6000000000104</v>
       </c>
     </row>
     <row r="67" spans="4:22" x14ac:dyDescent="0.25">
@@ -6940,7 +6937,7 @@
       <c r="F69" s="36"/>
       <c r="U69" s="39">
         <f>U66+V66</f>
-        <v>85011.07</v>
+        <v>84867.07</v>
       </c>
     </row>
     <row r="70" spans="4:22" x14ac:dyDescent="0.25">
@@ -6966,7 +6963,7 @@
     <row r="75" spans="4:22" x14ac:dyDescent="0.25">
       <c r="U75" s="54">
         <f>U69/U72</f>
-        <v>0.2552884984984985</v>
+        <v>0.25485606606606609</v>
       </c>
     </row>
   </sheetData>
@@ -8226,7 +8223,7 @@
       </c>
       <c r="G74" s="27">
         <f>AVERAGE(C3:C87)</f>
-        <v>1014.5069411764701</v>
+        <v>1018.4598823529408</v>
       </c>
       <c r="I74" s="27">
         <v>998.5129761904758</v>
@@ -8253,7 +8250,7 @@
       </c>
       <c r="G75" s="27">
         <f>_xlfn.STDEV.S(C3:C87)</f>
-        <v>4165.6841486600597</v>
+        <v>4167.1333742878405</v>
       </c>
       <c r="I75" s="27">
         <v>4188.0771538061736</v>
@@ -8280,7 +8277,7 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
-        <v>3.8660632547935578</v>
+        <v>3.8797772861721547</v>
       </c>
       <c r="I76" s="28">
         <v>3.7847684063843623</v>
@@ -8307,7 +8304,7 @@
       </c>
       <c r="G77" s="29">
         <f>_xlfn.STDEV.S(D2:D87)*SQRT(252)</f>
-        <v>0.17837525027910547</v>
+        <v>0.17841951279339599</v>
       </c>
       <c r="I77" s="29">
         <v>0.17936221602538568</v>
@@ -8334,7 +8331,7 @@
       </c>
       <c r="G78" s="29" cm="1">
         <f t="array" ref="G78">PRODUCT(1+D3:D87)-1</f>
-        <v>0.25860436774327011</v>
+        <v>0.25961199736320695</v>
       </c>
       <c r="I78" s="29">
         <v>0.25153296701764072</v>
@@ -8361,7 +8358,7 @@
       </c>
       <c r="G79" s="29" cm="1">
         <f t="array" ref="G79">PRODUCT(1+D2:D87)^(252/COUNT(D2:D87))-1</f>
-        <v>0.96199857349895557</v>
+        <v>0.96660482859354491</v>
       </c>
       <c r="I79" s="29">
         <v>0.94485730362176024</v>
@@ -8491,16 +8488,16 @@
         <v>46303</v>
       </c>
       <c r="B87" s="5">
-        <f>B86+1458+1100-200</f>
-        <v>419689</v>
+        <f>B86+1458+1236</f>
+        <v>420025</v>
       </c>
       <c r="C87" s="5">
         <f t="shared" si="0"/>
-        <v>2358</v>
+        <v>2694</v>
       </c>
       <c r="D87" s="23">
         <f t="shared" si="1"/>
-        <v>5.650191334935579E-3</v>
+        <v>6.4553076574709279E-3</v>
       </c>
     </row>
   </sheetData>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A9CF8DAC-8401-7644-B21F-28D21E6E6015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B61513C-D494-424E-A12A-4FCFBA21286F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="520" windowWidth="40660" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6390,7 +6390,7 @@
         <v>1</v>
       </c>
       <c r="S56" s="40">
-        <f t="shared" ref="S56:S63" si="12">IF(R56=1, ABS(N56-M56)/M56, 0)</f>
+        <f t="shared" ref="S56:S61" si="12">IF(R56=1, ABS(N56-M56)/M56, 0)</f>
         <v>2.7360178970917266E-2</v>
       </c>
       <c r="T56" s="39">
@@ -6875,6 +6875,9 @@
       </c>
       <c r="U63" s="41" t="s">
         <v>72</v>
+      </c>
+      <c r="V63" s="33">
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7B61513C-D494-424E-A12A-4FCFBA21286F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{21646DDD-A52D-5F4C-B615-40B7C1F08423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="520" windowWidth="40660" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="970" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="634">
   <si>
     <t>Trade ID</t>
   </si>
@@ -4775,7 +4775,7 @@
         <v>7389</v>
       </c>
     </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A33" s="33">
         <v>28</v>
       </c>
@@ -4842,7 +4842,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A34" s="33">
         <v>29</v>
       </c>
@@ -4909,7 +4909,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A35" s="33">
         <v>30</v>
       </c>
@@ -4976,7 +4976,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A36" s="33">
         <v>31</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>-3825</v>
       </c>
     </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A37" s="33">
         <v>32</v>
       </c>
@@ -5110,7 +5110,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A38" s="33">
         <v>33</v>
       </c>
@@ -5177,7 +5177,7 @@
         <v>220</v>
       </c>
     </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A39" s="33">
         <v>34</v>
       </c>
@@ -5245,7 +5245,7 @@
         <v>2167</v>
       </c>
     </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A40" s="33">
         <v>35</v>
       </c>
@@ -5313,7 +5313,7 @@
         <v>-438</v>
       </c>
     </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A41" s="33">
         <v>36</v>
       </c>
@@ -5380,7 +5380,7 @@
         <v>-317</v>
       </c>
     </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A42" s="33">
         <v>37</v>
       </c>
@@ -5448,7 +5448,7 @@
         <v>1721</v>
       </c>
     </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A43" s="33">
         <v>38</v>
       </c>
@@ -5516,7 +5516,7 @@
         <v>-2814</v>
       </c>
     </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A44" s="33">
         <v>39</v>
       </c>
@@ -5584,7 +5584,7 @@
         <v>1134</v>
       </c>
     </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A45" s="33">
         <v>40</v>
       </c>
@@ -5651,7 +5651,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A46" s="33">
         <v>41</v>
       </c>
@@ -5719,78 +5719,75 @@
         <v>-664</v>
       </c>
     </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A47" s="33">
         <v>42</v>
       </c>
       <c r="B47" s="34">
         <v>46288</v>
       </c>
-      <c r="C47" s="55">
-        <v>46302</v>
-      </c>
-      <c r="D47" s="56">
+      <c r="C47" s="34">
+        <v>46303</v>
+      </c>
+      <c r="D47" s="35">
         <f t="shared" si="5"/>
-        <v>14</v>
-      </c>
-      <c r="E47" s="47" t="s">
+        <v>15</v>
+      </c>
+      <c r="E47" s="33" t="s">
         <v>605</v>
       </c>
-      <c r="F47" s="48" t="s">
+      <c r="F47" s="36" t="s">
         <v>606</v>
       </c>
-      <c r="G47" s="47" t="s">
+      <c r="G47" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H47" s="48" t="s">
+      <c r="H47" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I47" s="47" t="s">
+      <c r="I47" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="J47" s="47" t="s">
+      <c r="J47" s="33" t="s">
         <v>25</v>
       </c>
-      <c r="K47" s="47" t="s">
+      <c r="K47" s="33" t="s">
         <v>605</v>
       </c>
-      <c r="L47" s="47">
+      <c r="L47" s="33">
         <v>-600</v>
       </c>
-      <c r="M47" s="47">
+      <c r="M47" s="33">
         <v>268.09100000000001</v>
       </c>
-      <c r="N47" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O47" s="47">
-        <v>263.01</v>
-      </c>
-      <c r="P47" s="49">
+      <c r="N47" s="33">
+        <v>262.3</v>
+      </c>
+      <c r="O47" s="33">
+        <v>262.3</v>
+      </c>
+      <c r="P47" s="39">
         <f>ABS(O47*L47)</f>
-        <v>157806</v>
-      </c>
-      <c r="Q47" s="47">
+        <v>157380</v>
+      </c>
+      <c r="Q47" s="33">
         <v>10.1</v>
       </c>
-      <c r="R47" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S47" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T47" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="U47" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V47" s="33">
-        <f>(M47-O47)*600</f>
-        <v>3048.6000000000104</v>
-      </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="R47" s="33">
+        <v>1</v>
+      </c>
+      <c r="S47" s="40">
+        <f t="shared" si="8"/>
+        <v>2.1600874329984955E-2</v>
+      </c>
+      <c r="T47" s="39">
+        <v>3476</v>
+      </c>
+      <c r="U47" s="41">
+        <v>3476</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A48" s="33">
         <v>43</v>
       </c>
@@ -6544,11 +6541,11 @@
         <v>46297</v>
       </c>
       <c r="C59" s="55">
-        <v>46301</v>
+        <v>46308</v>
       </c>
       <c r="D59" s="56">
         <f t="shared" si="5"/>
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="E59" s="47" t="s">
         <v>58</v>
@@ -6572,20 +6569,20 @@
         <v>607</v>
       </c>
       <c r="L59" s="47">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="M59" s="47">
-        <v>17.91</v>
+        <v>17.53</v>
       </c>
       <c r="N59" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O59" s="47">
-        <v>17.68</v>
+        <v>16.72</v>
       </c>
       <c r="P59" s="49">
         <f>ABS(M59*L59)*100</f>
-        <v>17910</v>
+        <v>26295.000000000004</v>
       </c>
       <c r="Q59" s="47">
         <v>1.88</v>
@@ -6603,7 +6600,7 @@
         <v>72</v>
       </c>
       <c r="V59" s="33">
-        <v>-350</v>
+        <v>-1213</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
@@ -6750,11 +6747,11 @@
         <v>46303</v>
       </c>
       <c r="C62" s="55">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="D62" s="56">
         <f t="shared" si="5"/>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E62" s="47" t="s">
         <v>88</v>
@@ -6787,7 +6784,7 @@
         <v>72</v>
       </c>
       <c r="O62" s="47">
-        <v>4206.3999999999996</v>
+        <v>4188</v>
       </c>
       <c r="P62" s="49">
         <v>42070</v>
@@ -6804,11 +6801,11 @@
       <c r="T62" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="U62" s="41" t="s">
+      <c r="U62" s="49" t="s">
         <v>72</v>
       </c>
       <c r="V62" s="33">
-        <v>1021</v>
+        <v>-219</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
@@ -6819,11 +6816,11 @@
         <v>46303</v>
       </c>
       <c r="C63" s="55">
-        <v>46304</v>
+        <v>46308</v>
       </c>
       <c r="D63" s="56">
         <f t="shared" ref="D63" si="13">C63-B63</f>
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="E63" s="47" t="s">
         <v>631</v>
@@ -6856,7 +6853,7 @@
         <v>72</v>
       </c>
       <c r="O63" s="47">
-        <v>6.6870000000000003</v>
+        <v>6.7714999999999996</v>
       </c>
       <c r="P63" s="49">
         <v>50164</v>
@@ -6873,11 +6870,11 @@
       <c r="T63" s="49" t="s">
         <v>72</v>
       </c>
-      <c r="U63" s="41" t="s">
+      <c r="U63" s="49" t="s">
         <v>72</v>
       </c>
       <c r="V63" s="33">
-        <v>0</v>
+        <v>-594</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
@@ -6901,17 +6898,17 @@
       </c>
       <c r="E66" s="46">
         <f>AVERAGE(D2:D61)</f>
-        <v>6.3</v>
+        <v>6.4333333333333336</v>
       </c>
       <c r="F66" s="36"/>
       <c r="H66" s="36"/>
       <c r="U66" s="39">
         <f>SUM(U2:U64)</f>
-        <v>81147.47</v>
+        <v>84623.47</v>
       </c>
       <c r="V66" s="39">
         <f>SUM(V2:V64)</f>
-        <v>3719.6000000000104</v>
+        <v>-2026</v>
       </c>
     </row>
     <row r="67" spans="4:22" x14ac:dyDescent="0.25">
@@ -6920,7 +6917,7 @@
       </c>
       <c r="E67" s="46">
         <f>AVERAGE(D2:D11,D13,D15:D61)</f>
-        <v>4.5172413793103452</v>
+        <v>4.6551724137931032</v>
       </c>
       <c r="F67" s="36"/>
       <c r="U67" s="53" t="s">
@@ -6940,7 +6937,7 @@
       <c r="F69" s="36"/>
       <c r="U69" s="39">
         <f>U66+V66</f>
-        <v>84867.07</v>
+        <v>82597.47</v>
       </c>
     </row>
     <row r="70" spans="4:22" x14ac:dyDescent="0.25">
@@ -6966,7 +6963,7 @@
     <row r="75" spans="4:22" x14ac:dyDescent="0.25">
       <c r="U75" s="54">
         <f>U69/U72</f>
-        <v>0.25485606606606609</v>
+        <v>0.24804045045045045</v>
       </c>
     </row>
   </sheetData>
@@ -6979,7 +6976,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:I87"/>
+  <dimension ref="A1:I89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -7045,11 +7042,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C87" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C89" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D87" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D89" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -8225,11 +8222,11 @@
         <v>113</v>
       </c>
       <c r="G74" s="27">
-        <f>AVERAGE(C3:C87)</f>
-        <v>1018.4598823529408</v>
+        <f>AVERAGE(C3:C89)</f>
+        <v>978.78264367816053</v>
       </c>
       <c r="I74" s="27">
-        <v>998.5129761904758</v>
+        <v>918.40802325581353</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -8252,11 +8249,11 @@
         <v>114</v>
       </c>
       <c r="G75" s="27">
-        <f>_xlfn.STDEV.S(C3:C87)</f>
-        <v>4167.1333742878405</v>
+        <f>_xlfn.STDEV.S(C3:C89)</f>
+        <v>4126.8937638138605</v>
       </c>
       <c r="I75" s="27">
-        <v>4188.0771538061736</v>
+        <v>4245.185348442973</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
@@ -8280,10 +8277,10 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
-        <v>3.8797772861721547</v>
+        <v>3.7649849174196888</v>
       </c>
       <c r="I76" s="28">
-        <v>3.7847684063843623</v>
+        <v>3.4343083265080891</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
@@ -8306,11 +8303,11 @@
         <v>116</v>
       </c>
       <c r="G77" s="29">
-        <f>_xlfn.STDEV.S(D2:D87)*SQRT(252)</f>
-        <v>0.17841951279339599</v>
+        <f>_xlfn.STDEV.S(D2:D89)*SQRT(252)</f>
+        <v>0.17668183134849275</v>
       </c>
       <c r="I77" s="29">
-        <v>0.17936221602538568</v>
+        <v>0.18088048205045065</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -8333,11 +8330,11 @@
         <v>117</v>
       </c>
       <c r="G78" s="29" cm="1">
-        <f t="array" ref="G78">PRODUCT(1+D3:D87)-1</f>
-        <v>0.25961199736320695</v>
+        <f t="array" ref="G78">PRODUCT(1+D3:D89)-1</f>
+        <v>0.25536855714829354</v>
       </c>
       <c r="I78" s="29">
-        <v>0.25153296701764072</v>
+        <v>0.23686235957498658</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -8360,11 +8357,11 @@
         <v>118</v>
       </c>
       <c r="G79" s="29" cm="1">
-        <f t="array" ref="G79">PRODUCT(1+D2:D87)^(252/COUNT(D2:D87))-1</f>
-        <v>0.96660482859354491</v>
+        <f t="array" ref="G79">PRODUCT(1+D2:D89)^(252/COUNT(D2:D89))-1</f>
+        <v>0.91798379730044988</v>
       </c>
       <c r="I79" s="29">
-        <v>0.94485730362176024</v>
+        <v>0.85103074668335488</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -8501,6 +8498,40 @@
       <c r="D87" s="23">
         <f t="shared" si="1"/>
         <v>6.4553076574709279E-3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A88" s="26">
+        <v>46304</v>
+      </c>
+      <c r="B88" s="5">
+        <f>B87-386</f>
+        <v>419639</v>
+      </c>
+      <c r="C88" s="5">
+        <f t="shared" si="0"/>
+        <v>-386</v>
+      </c>
+      <c r="D88" s="23">
+        <f t="shared" si="1"/>
+        <v>-9.1899291708826859E-4</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A89" s="26">
+        <v>46307</v>
+      </c>
+      <c r="B89" s="5">
+        <f>B88-1029</f>
+        <v>418610</v>
+      </c>
+      <c r="C89" s="5">
+        <f t="shared" si="0"/>
+        <v>-1029</v>
+      </c>
+      <c r="D89" s="23">
+        <f t="shared" si="1"/>
+        <v>-2.4521076449043108E-3</v>
       </c>
     </row>
   </sheetData>
@@ -13454,7 +13485,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="14">
-        <f t="shared" ref="M69:M94" si="0">SUM(C69:L69)</f>
+        <f t="shared" ref="M69:M96" si="0">SUM(C69:L69)</f>
         <v>407651</v>
       </c>
       <c r="N69" s="15">
@@ -15352,14 +15383,14 @@
         <v>46303</v>
       </c>
       <c r="B94" s="11">
-        <v>419689</v>
+        <v>420025</v>
       </c>
       <c r="C94" s="19">
         <v>160440</v>
       </c>
       <c r="D94" s="13">
         <f>B94-C94-H94-L94-F94</f>
-        <v>76400</v>
+        <v>76736</v>
       </c>
       <c r="E94" s="13">
         <v>0</v>
@@ -15387,19 +15418,19 @@
       </c>
       <c r="M94" s="14">
         <f t="shared" si="0"/>
-        <v>419689</v>
+        <v>420025</v>
       </c>
       <c r="N94" s="15">
         <f t="shared" ref="N94" si="72">C94/M94</f>
-        <v>0.38228307151247709</v>
+        <v>0.38197726325813941</v>
       </c>
       <c r="O94" s="15">
         <f t="shared" ref="O94" si="73">D94/M94</f>
-        <v>0.18203955786308434</v>
+        <v>0.18269388726861496</v>
       </c>
       <c r="P94" s="15">
         <f>F94/M94</f>
-        <v>0.393598593244045</v>
+        <v>0.39328373311112436</v>
       </c>
       <c r="Q94" s="15">
         <f>E94/M94</f>
@@ -15410,7 +15441,7 @@
       </c>
       <c r="S94" s="15">
         <f t="shared" ref="S94" si="74">H94/M94</f>
-        <v>4.2078777380393576E-2</v>
+        <v>4.2045116362121306E-2</v>
       </c>
       <c r="T94" s="15">
         <f t="shared" ref="T94" si="75">I94/M94</f>
@@ -15425,6 +15456,168 @@
       </c>
       <c r="W94" s="15">
         <f t="shared" ref="W94" si="77">L94/M94</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A95" s="10">
+        <v>46304</v>
+      </c>
+      <c r="B95" s="11">
+        <v>419639</v>
+      </c>
+      <c r="C95" s="19">
+        <v>0</v>
+      </c>
+      <c r="D95" s="13">
+        <f>B95-C95-H95-L95-F95</f>
+        <v>236790</v>
+      </c>
+      <c r="E95" s="13">
+        <v>0</v>
+      </c>
+      <c r="F95" s="13">
+        <v>165189</v>
+      </c>
+      <c r="G95" s="13">
+        <v>0</v>
+      </c>
+      <c r="H95" s="13">
+        <v>17660</v>
+      </c>
+      <c r="I95" s="13">
+        <v>0</v>
+      </c>
+      <c r="J95" s="13">
+        <v>0</v>
+      </c>
+      <c r="K95" s="13">
+        <v>0</v>
+      </c>
+      <c r="L95" s="18">
+        <v>0</v>
+      </c>
+      <c r="M95" s="14">
+        <f t="shared" si="0"/>
+        <v>419639</v>
+      </c>
+      <c r="N95" s="15">
+        <f t="shared" ref="N95" si="78">C95/M95</f>
+        <v>0</v>
+      </c>
+      <c r="O95" s="15">
+        <f t="shared" ref="O95" si="79">D95/M95</f>
+        <v>0.56427071840319898</v>
+      </c>
+      <c r="P95" s="15">
+        <f>F95/M95</f>
+        <v>0.39364549052876402</v>
+      </c>
+      <c r="Q95" s="15">
+        <f>E95/M95</f>
+        <v>0</v>
+      </c>
+      <c r="R95" s="15">
+        <v>0</v>
+      </c>
+      <c r="S95" s="15">
+        <f t="shared" ref="S95" si="80">H95/M95</f>
+        <v>4.2083791068037051E-2</v>
+      </c>
+      <c r="T95" s="15">
+        <f t="shared" ref="T95" si="81">I95/M95</f>
+        <v>0</v>
+      </c>
+      <c r="U95" s="15">
+        <v>0</v>
+      </c>
+      <c r="V95" s="16">
+        <f t="shared" ref="V95" si="82">K95/M95</f>
+        <v>0</v>
+      </c>
+      <c r="W95" s="15">
+        <f t="shared" ref="W95" si="83">L95/M95</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A96" s="10">
+        <v>46307</v>
+      </c>
+      <c r="B96" s="11">
+        <v>418610</v>
+      </c>
+      <c r="C96" s="19">
+        <v>0</v>
+      </c>
+      <c r="D96" s="13">
+        <f>B96-C96-H96-L96-F96</f>
+        <v>227126</v>
+      </c>
+      <c r="E96" s="13">
+        <v>0</v>
+      </c>
+      <c r="F96" s="13">
+        <v>165189</v>
+      </c>
+      <c r="G96" s="13">
+        <v>0</v>
+      </c>
+      <c r="H96" s="13">
+        <v>26295</v>
+      </c>
+      <c r="I96" s="13">
+        <v>0</v>
+      </c>
+      <c r="J96" s="13">
+        <v>0</v>
+      </c>
+      <c r="K96" s="13">
+        <v>0</v>
+      </c>
+      <c r="L96" s="18">
+        <v>0</v>
+      </c>
+      <c r="M96" s="14">
+        <f t="shared" si="0"/>
+        <v>418610</v>
+      </c>
+      <c r="N96" s="15">
+        <f t="shared" ref="N96" si="84">C96/M96</f>
+        <v>0</v>
+      </c>
+      <c r="O96" s="15">
+        <f t="shared" ref="O96" si="85">D96/M96</f>
+        <v>0.54257184491531496</v>
+      </c>
+      <c r="P96" s="15">
+        <f>F96/M96</f>
+        <v>0.39461312438785506</v>
+      </c>
+      <c r="Q96" s="15">
+        <f>E96/M96</f>
+        <v>0</v>
+      </c>
+      <c r="R96" s="15">
+        <v>0</v>
+      </c>
+      <c r="S96" s="15">
+        <f t="shared" ref="S96" si="86">H96/M96</f>
+        <v>6.281503069682999E-2</v>
+      </c>
+      <c r="T96" s="15">
+        <f t="shared" ref="T96" si="87">I96/M96</f>
+        <v>0</v>
+      </c>
+      <c r="U96" s="15">
+        <v>0</v>
+      </c>
+      <c r="V96" s="16">
+        <f t="shared" ref="V96" si="88">K96/M96</f>
+        <v>0</v>
+      </c>
+      <c r="W96" s="15">
+        <f t="shared" ref="W96" si="89">L96/M96</f>
         <v>0</v>
       </c>
     </row>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{21646DDD-A52D-5F4C-B615-40B7C1F08423}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FFD45C-BEA5-4246-8662-BDA36FC01C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="280" yWindow="520" windowWidth="40660" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -6578,7 +6578,7 @@
         <v>72</v>
       </c>
       <c r="O59" s="47">
-        <v>16.72</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="P59" s="49">
         <f>ABS(M59*L59)*100</f>
@@ -6600,7 +6600,7 @@
         <v>72</v>
       </c>
       <c r="V59" s="33">
-        <v>-1213</v>
+        <v>602</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
@@ -6775,22 +6775,23 @@
         <v>89</v>
       </c>
       <c r="L62" s="47">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M62" s="47">
-        <v>4209.1099999999997</v>
+        <v>4161</v>
       </c>
       <c r="N62" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O62" s="47">
-        <v>4188</v>
+        <v>4176</v>
       </c>
       <c r="P62" s="49">
-        <v>42070</v>
+        <f>L62*O62*10</f>
+        <v>125280</v>
       </c>
       <c r="Q62" s="47">
-        <v>3.84</v>
+        <v>8.64</v>
       </c>
       <c r="R62" s="47" t="s">
         <v>72</v>
@@ -6805,7 +6806,7 @@
         <v>72</v>
       </c>
       <c r="V62" s="33">
-        <v>-219</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
@@ -6844,22 +6845,22 @@
         <v>633</v>
       </c>
       <c r="L63" s="47">
-        <v>-3</v>
+        <v>-8</v>
       </c>
       <c r="M63" s="47">
-        <v>6.6917</v>
+        <v>6.6361999999999997</v>
       </c>
       <c r="N63" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O63" s="47">
-        <v>6.7714999999999996</v>
+        <v>6.5605000000000002</v>
       </c>
       <c r="P63" s="49">
-        <v>50164</v>
+        <v>131210</v>
       </c>
       <c r="Q63" s="47">
-        <v>11.52</v>
+        <v>24.01</v>
       </c>
       <c r="R63" s="47" t="s">
         <v>72</v>
@@ -6874,7 +6875,7 @@
         <v>72</v>
       </c>
       <c r="V63" s="33">
-        <v>-594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="64" spans="1:22" x14ac:dyDescent="0.25">
@@ -6908,7 +6909,7 @@
       </c>
       <c r="V66" s="39">
         <f>SUM(V2:V64)</f>
-        <v>-2026</v>
+        <v>1332</v>
       </c>
     </row>
     <row r="67" spans="4:22" x14ac:dyDescent="0.25">
@@ -6937,7 +6938,7 @@
       <c r="F69" s="36"/>
       <c r="U69" s="39">
         <f>U66+V66</f>
-        <v>82597.47</v>
+        <v>85955.47</v>
       </c>
     </row>
     <row r="70" spans="4:22" x14ac:dyDescent="0.25">
@@ -6963,7 +6964,7 @@
     <row r="75" spans="4:22" x14ac:dyDescent="0.25">
       <c r="U75" s="54">
         <f>U69/U72</f>
-        <v>0.24804045045045045</v>
+        <v>0.25812453453453454</v>
       </c>
     </row>
   </sheetData>
@@ -6976,7 +6977,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:I89"/>
+  <dimension ref="A1:I91"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -7042,11 +7043,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C89" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C91" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D89" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D91" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -8222,11 +8223,11 @@
         <v>113</v>
       </c>
       <c r="G74" s="27">
-        <f>AVERAGE(C3:C89)</f>
+        <f>AVERAGE(C3:C91)</f>
+        <v>992.9223595505614</v>
+      </c>
+      <c r="I74" s="27">
         <v>978.78264367816053</v>
-      </c>
-      <c r="I74" s="27">
-        <v>918.40802325581353</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -8249,11 +8250,11 @@
         <v>114</v>
       </c>
       <c r="G75" s="27">
-        <f>_xlfn.STDEV.S(C3:C89)</f>
+        <f>_xlfn.STDEV.S(C3:C91)</f>
+        <v>4086.8840749527426</v>
+      </c>
+      <c r="I75" s="27">
         <v>4126.8937638138605</v>
-      </c>
-      <c r="I75" s="27">
-        <v>4245.185348442973</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
@@ -8277,10 +8278,10 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
+        <v>3.8567655745360794</v>
+      </c>
+      <c r="I76" s="28">
         <v>3.7649849174196888</v>
-      </c>
-      <c r="I76" s="28">
-        <v>3.4343083265080891</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
@@ -8303,11 +8304,11 @@
         <v>116</v>
       </c>
       <c r="G77" s="29">
-        <f>_xlfn.STDEV.S(D2:D89)*SQRT(252)</f>
+        <f>_xlfn.STDEV.S(D2:D91)*SQRT(252)</f>
+        <v>0.1749096544335895</v>
+      </c>
+      <c r="I77" s="29">
         <v>0.17668183134849275</v>
-      </c>
-      <c r="I77" s="29">
-        <v>0.18088048205045065</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -8330,11 +8331,11 @@
         <v>117</v>
       </c>
       <c r="G78" s="29" cm="1">
-        <f t="array" ref="G78">PRODUCT(1+D3:D89)-1</f>
+        <f t="array" ref="G78">PRODUCT(1+D3:D91)-1</f>
+        <v>0.26501301208197625</v>
+      </c>
+      <c r="I78" s="29">
         <v>0.25536855714829354</v>
-      </c>
-      <c r="I78" s="29">
-        <v>0.23686235957498658</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -8357,11 +8358,11 @@
         <v>118</v>
       </c>
       <c r="G79" s="29" cm="1">
-        <f t="array" ref="G79">PRODUCT(1+D2:D89)^(252/COUNT(D2:D89))-1</f>
+        <f t="array" ref="G79">PRODUCT(1+D2:D91)^(252/COUNT(D2:D91))-1</f>
+        <v>0.93137221672115644</v>
+      </c>
+      <c r="I79" s="29">
         <v>0.91798379730044988</v>
-      </c>
-      <c r="I79" s="29">
-        <v>0.85103074668335488</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -8532,6 +8533,40 @@
       <c r="D89" s="23">
         <f t="shared" si="1"/>
         <v>-2.4521076449043108E-3</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A90" s="26">
+        <v>46308</v>
+      </c>
+      <c r="B90" s="5">
+        <f>B89+130</f>
+        <v>418740</v>
+      </c>
+      <c r="C90" s="5">
+        <f t="shared" si="0"/>
+        <v>130</v>
+      </c>
+      <c r="D90" s="23">
+        <f t="shared" si="1"/>
+        <v>3.1055158739638327E-4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A91" s="26">
+        <v>46309</v>
+      </c>
+      <c r="B91" s="5">
+        <f>B90+586+1300+1200</f>
+        <v>421826</v>
+      </c>
+      <c r="C91" s="5">
+        <f t="shared" si="0"/>
+        <v>3086</v>
+      </c>
+      <c r="D91" s="23">
+        <f t="shared" si="1"/>
+        <v>7.3697282323159953E-3</v>
       </c>
     </row>
   </sheetData>
@@ -8542,7 +8577,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBFEDD2B-54BB-1449-BCF8-F93ADB145E3A}">
-  <dimension ref="A1:W1048543"/>
+  <dimension ref="A1:W1048576"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="20" bestFit="1" customWidth="1"/>
@@ -13485,7 +13520,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="14">
-        <f t="shared" ref="M69:M96" si="0">SUM(C69:L69)</f>
+        <f t="shared" ref="M69:M98" si="0">SUM(C69:L69)</f>
         <v>407651</v>
       </c>
       <c r="N69" s="15">
@@ -15193,29 +15228,29 @@
         <v>0</v>
       </c>
       <c r="Q91" s="15">
-        <f>E91/M91</f>
+        <f t="shared" ref="Q91:Q96" si="56">E91/M91</f>
         <v>0.74553540418252784</v>
       </c>
       <c r="R91" s="15">
         <v>0</v>
       </c>
       <c r="S91" s="15">
-        <f t="shared" ref="S91" si="56">H91/M91</f>
+        <f t="shared" ref="S91" si="57">H91/M91</f>
         <v>9.3642640383097032E-3</v>
       </c>
       <c r="T91" s="15">
-        <f t="shared" ref="T91" si="57">I91/M91</f>
+        <f t="shared" ref="T91" si="58">I91/M91</f>
         <v>0</v>
       </c>
       <c r="U91" s="15">
         <v>0</v>
       </c>
       <c r="V91" s="16">
-        <f t="shared" ref="V91" si="58">K91/M91</f>
+        <f t="shared" ref="V91" si="59">K91/M91</f>
         <v>0</v>
       </c>
       <c r="W91" s="15">
-        <f t="shared" ref="W91" si="59">L91/M91</f>
+        <f t="shared" ref="W91" si="60">L91/M91</f>
         <v>0.12728134629059018</v>
       </c>
     </row>
@@ -15262,40 +15297,40 @@
         <v>408266</v>
       </c>
       <c r="N92" s="15">
-        <f t="shared" ref="N92" si="60">C92/M92</f>
+        <f t="shared" ref="N92" si="61">C92/M92</f>
         <v>0.3929790871637609</v>
       </c>
       <c r="O92" s="15">
-        <f t="shared" ref="O92" si="61">D92/M92</f>
+        <f t="shared" ref="O92" si="62">D92/M92</f>
         <v>0.56376480039973942</v>
       </c>
       <c r="P92" s="15">
         <v>0</v>
       </c>
       <c r="Q92" s="15">
-        <f>E92/M92</f>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="R92" s="15">
         <v>0</v>
       </c>
       <c r="S92" s="15">
-        <f t="shared" ref="S92" si="62">H92/M92</f>
+        <f t="shared" ref="S92" si="63">H92/M92</f>
         <v>4.3256112436499732E-2</v>
       </c>
       <c r="T92" s="15">
-        <f t="shared" ref="T92" si="63">I92/M92</f>
+        <f t="shared" ref="T92" si="64">I92/M92</f>
         <v>0</v>
       </c>
       <c r="U92" s="15">
         <v>0</v>
       </c>
       <c r="V92" s="16">
-        <f t="shared" ref="V92" si="64">K92/M92</f>
+        <f t="shared" ref="V92" si="65">K92/M92</f>
         <v>0</v>
       </c>
       <c r="W92" s="15">
-        <f t="shared" ref="W92" si="65">L92/M92</f>
+        <f t="shared" ref="W92" si="66">L92/M92</f>
         <v>0</v>
       </c>
     </row>
@@ -15341,40 +15376,40 @@
         <v>2279975</v>
       </c>
       <c r="N93" s="15">
-        <f t="shared" ref="N93" si="66">C93/M93</f>
+        <f t="shared" ref="N93" si="67">C93/M93</f>
         <v>7.0369192644656187E-2</v>
       </c>
       <c r="O93" s="15">
-        <f t="shared" ref="O93" si="67">D93/M93</f>
+        <f t="shared" ref="O93" si="68">D93/M93</f>
         <v>0</v>
       </c>
       <c r="P93" s="15">
         <v>0</v>
       </c>
       <c r="Q93" s="15">
-        <f>E93/M93</f>
+        <f t="shared" si="56"/>
         <v>0.92188510838934634</v>
       </c>
       <c r="R93" s="15">
         <v>0</v>
       </c>
       <c r="S93" s="15">
-        <f t="shared" ref="S93" si="68">H93/M93</f>
+        <f t="shared" ref="S93" si="69">H93/M93</f>
         <v>7.7456989659974345E-3</v>
       </c>
       <c r="T93" s="15">
-        <f t="shared" ref="T93" si="69">I93/M93</f>
+        <f t="shared" ref="T93" si="70">I93/M93</f>
         <v>0</v>
       </c>
       <c r="U93" s="15">
         <v>0</v>
       </c>
       <c r="V93" s="16">
-        <f t="shared" ref="V93" si="70">K93/M93</f>
+        <f t="shared" ref="V93" si="71">K93/M93</f>
         <v>0</v>
       </c>
       <c r="W93" s="15">
-        <f t="shared" ref="W93" si="71">L93/M93</f>
+        <f t="shared" ref="W93" si="72">L93/M93</f>
         <v>0</v>
       </c>
     </row>
@@ -15421,11 +15456,11 @@
         <v>420025</v>
       </c>
       <c r="N94" s="15">
-        <f t="shared" ref="N94" si="72">C94/M94</f>
+        <f t="shared" ref="N94" si="73">C94/M94</f>
         <v>0.38197726325813941</v>
       </c>
       <c r="O94" s="15">
-        <f t="shared" ref="O94" si="73">D94/M94</f>
+        <f t="shared" ref="O94" si="74">D94/M94</f>
         <v>0.18269388726861496</v>
       </c>
       <c r="P94" s="15">
@@ -15433,29 +15468,29 @@
         <v>0.39328373311112436</v>
       </c>
       <c r="Q94" s="15">
-        <f>E94/M94</f>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="R94" s="15">
         <v>0</v>
       </c>
       <c r="S94" s="15">
-        <f t="shared" ref="S94" si="74">H94/M94</f>
+        <f t="shared" ref="S94" si="75">H94/M94</f>
         <v>4.2045116362121306E-2</v>
       </c>
       <c r="T94" s="15">
-        <f t="shared" ref="T94" si="75">I94/M94</f>
+        <f t="shared" ref="T94" si="76">I94/M94</f>
         <v>0</v>
       </c>
       <c r="U94" s="15">
         <v>0</v>
       </c>
       <c r="V94" s="16">
-        <f t="shared" ref="V94" si="76">K94/M94</f>
+        <f t="shared" ref="V94" si="77">K94/M94</f>
         <v>0</v>
       </c>
       <c r="W94" s="15">
-        <f t="shared" ref="W94" si="77">L94/M94</f>
+        <f t="shared" ref="W94" si="78">L94/M94</f>
         <v>0</v>
       </c>
     </row>
@@ -15502,11 +15537,11 @@
         <v>419639</v>
       </c>
       <c r="N95" s="15">
-        <f t="shared" ref="N95" si="78">C95/M95</f>
+        <f t="shared" ref="N95" si="79">C95/M95</f>
         <v>0</v>
       </c>
       <c r="O95" s="15">
-        <f t="shared" ref="O95" si="79">D95/M95</f>
+        <f t="shared" ref="O95" si="80">D95/M95</f>
         <v>0.56427071840319898</v>
       </c>
       <c r="P95" s="15">
@@ -15514,29 +15549,29 @@
         <v>0.39364549052876402</v>
       </c>
       <c r="Q95" s="15">
-        <f>E95/M95</f>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="R95" s="15">
         <v>0</v>
       </c>
       <c r="S95" s="15">
-        <f t="shared" ref="S95" si="80">H95/M95</f>
+        <f t="shared" ref="S95" si="81">H95/M95</f>
         <v>4.2083791068037051E-2</v>
       </c>
       <c r="T95" s="15">
-        <f t="shared" ref="T95" si="81">I95/M95</f>
+        <f t="shared" ref="T95" si="82">I95/M95</f>
         <v>0</v>
       </c>
       <c r="U95" s="15">
         <v>0</v>
       </c>
       <c r="V95" s="16">
-        <f t="shared" ref="V95" si="82">K95/M95</f>
+        <f t="shared" ref="V95" si="83">K95/M95</f>
         <v>0</v>
       </c>
       <c r="W95" s="15">
-        <f t="shared" ref="W95" si="83">L95/M95</f>
+        <f t="shared" ref="W95" si="84">L95/M95</f>
         <v>0</v>
       </c>
     </row>
@@ -15583,11 +15618,11 @@
         <v>418610</v>
       </c>
       <c r="N96" s="15">
-        <f t="shared" ref="N96" si="84">C96/M96</f>
+        <f t="shared" ref="N96" si="85">C96/M96</f>
         <v>0</v>
       </c>
       <c r="O96" s="15">
-        <f t="shared" ref="O96" si="85">D96/M96</f>
+        <f t="shared" ref="O96" si="86">D96/M96</f>
         <v>0.54257184491531496</v>
       </c>
       <c r="P96" s="15">
@@ -15595,34 +15630,199 @@
         <v>0.39461312438785506</v>
       </c>
       <c r="Q96" s="15">
-        <f>E96/M96</f>
+        <f t="shared" si="56"/>
         <v>0</v>
       </c>
       <c r="R96" s="15">
         <v>0</v>
       </c>
       <c r="S96" s="15">
-        <f t="shared" ref="S96" si="86">H96/M96</f>
+        <f t="shared" ref="S96" si="87">H96/M96</f>
         <v>6.281503069682999E-2</v>
       </c>
       <c r="T96" s="15">
-        <f t="shared" ref="T96" si="87">I96/M96</f>
+        <f t="shared" ref="T96" si="88">I96/M96</f>
         <v>0</v>
       </c>
       <c r="U96" s="15">
         <v>0</v>
       </c>
       <c r="V96" s="16">
-        <f t="shared" ref="V96" si="88">K96/M96</f>
+        <f t="shared" ref="V96" si="89">K96/M96</f>
         <v>0</v>
       </c>
       <c r="W96" s="15">
-        <f t="shared" ref="W96" si="89">L96/M96</f>
+        <f t="shared" ref="W96" si="90">L96/M96</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A97" s="10">
+        <v>46308</v>
+      </c>
+      <c r="B97" s="11">
+        <v>418740</v>
+      </c>
+      <c r="C97" s="19">
+        <v>0</v>
+      </c>
+      <c r="D97" s="13">
+        <f>B97-C97-H97-L97-F97</f>
+        <v>227256</v>
+      </c>
+      <c r="E97" s="13">
+        <v>0</v>
+      </c>
+      <c r="F97" s="13">
+        <v>165189</v>
+      </c>
+      <c r="G97" s="13">
+        <v>0</v>
+      </c>
+      <c r="H97" s="13">
+        <v>26295</v>
+      </c>
+      <c r="I97" s="13">
+        <v>0</v>
+      </c>
+      <c r="J97" s="13">
+        <v>0</v>
+      </c>
+      <c r="K97" s="13">
+        <v>0</v>
+      </c>
+      <c r="L97" s="18">
+        <v>0</v>
+      </c>
+      <c r="M97" s="14">
+        <f t="shared" si="0"/>
+        <v>418740</v>
+      </c>
+      <c r="N97" s="15">
+        <f t="shared" ref="N97" si="91">C97/M97</f>
+        <v>0</v>
+      </c>
+      <c r="O97" s="15">
+        <f t="shared" ref="O97" si="92">D97/M97</f>
+        <v>0.54271385585327414</v>
+      </c>
+      <c r="P97" s="15">
+        <f>F97/M97</f>
+        <v>0.39449061470124658</v>
+      </c>
+      <c r="Q97" s="15">
+        <f t="shared" ref="Q97" si="93">E97/M97</f>
+        <v>0</v>
+      </c>
+      <c r="R97" s="15">
+        <v>0</v>
+      </c>
+      <c r="S97" s="15">
+        <f t="shared" ref="S97" si="94">H97/M97</f>
+        <v>6.2795529445479295E-2</v>
+      </c>
+      <c r="T97" s="15">
+        <f t="shared" ref="T97" si="95">I97/M97</f>
+        <v>0</v>
+      </c>
+      <c r="U97" s="15">
+        <v>0</v>
+      </c>
+      <c r="V97" s="16">
+        <f t="shared" ref="V97" si="96">K97/M97</f>
+        <v>0</v>
+      </c>
+      <c r="W97" s="15">
+        <f t="shared" ref="W97" si="97">L97/M97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A98" s="10">
+        <v>46309</v>
+      </c>
+      <c r="B98" s="11">
+        <v>421826</v>
+      </c>
+      <c r="C98" s="19">
+        <v>0</v>
+      </c>
+      <c r="D98" s="13">
+        <f>B98-C98-H98-L98-F98</f>
+        <v>139041</v>
+      </c>
+      <c r="E98" s="13">
+        <v>0</v>
+      </c>
+      <c r="F98" s="13">
+        <v>256490</v>
+      </c>
+      <c r="G98" s="13">
+        <v>0</v>
+      </c>
+      <c r="H98" s="13">
+        <v>26295</v>
+      </c>
+      <c r="I98" s="13">
+        <v>0</v>
+      </c>
+      <c r="J98" s="13">
+        <v>0</v>
+      </c>
+      <c r="K98" s="13">
+        <v>0</v>
+      </c>
+      <c r="L98" s="18">
+        <v>0</v>
+      </c>
+      <c r="M98" s="14">
+        <f t="shared" si="0"/>
+        <v>421826</v>
+      </c>
+      <c r="N98" s="15">
+        <f t="shared" ref="N98" si="98">C98/M98</f>
+        <v>0</v>
+      </c>
+      <c r="O98" s="15">
+        <f t="shared" ref="O98" si="99">D98/M98</f>
+        <v>0.32961695106513111</v>
+      </c>
+      <c r="P98" s="15">
+        <f>F98/M98</f>
+        <v>0.60804691982002057</v>
+      </c>
+      <c r="Q98" s="15">
+        <f t="shared" ref="Q98" si="100">E98/M98</f>
+        <v>0</v>
+      </c>
+      <c r="R98" s="15">
+        <v>0</v>
+      </c>
+      <c r="S98" s="15">
+        <f t="shared" ref="S98" si="101">H98/M98</f>
+        <v>6.2336129114848302E-2</v>
+      </c>
+      <c r="T98" s="15">
+        <f t="shared" ref="T98" si="102">I98/M98</f>
+        <v>0</v>
+      </c>
+      <c r="U98" s="15">
+        <v>0</v>
+      </c>
+      <c r="V98" s="16">
+        <f t="shared" ref="V98" si="103">K98/M98</f>
+        <v>0</v>
+      </c>
+      <c r="W98" s="15">
+        <f t="shared" ref="W98" si="104">L98/M98</f>
         <v>0</v>
       </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1048543" s="10"/>
+    </row>
+    <row r="1048576" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A1048576" s="10"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="N2:W1048576">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40FFD45C-BEA5-4246-8662-BDA36FC01C05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D213A20-F34F-2241-9834-E487EFC4A429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="280" yWindow="520" windowWidth="40660" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1980" yWindow="-20900" windowWidth="44300" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="965" uniqueCount="634">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="642">
   <si>
     <t>Trade ID</t>
   </si>
@@ -1966,6 +1966,30 @@
   </si>
   <si>
     <t>MHGZ6</t>
+  </si>
+  <si>
+    <t>UEC</t>
+  </si>
+  <si>
+    <t>Uranium Energy Corp</t>
+  </si>
+  <si>
+    <t>TRUP</t>
+  </si>
+  <si>
+    <t>Trupanion Inc</t>
+  </si>
+  <si>
+    <t>BKE</t>
+  </si>
+  <si>
+    <t>Buckle Inc</t>
+  </si>
+  <si>
+    <t>RL</t>
+  </si>
+  <si>
+    <t>Ralph Lauren</t>
   </si>
 </sst>
 </file>
@@ -2115,7 +2139,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="56">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2252,9 +2276,6 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2597,11 +2618,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V75"/>
+  <dimension ref="A1:V79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="14" style="51" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14" style="50" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5" style="46" customWidth="1"/>
     <col min="5" max="5" width="9" style="33" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="57.6640625" style="33" bestFit="1" customWidth="1"/>
@@ -6387,7 +6408,7 @@
         <v>1</v>
       </c>
       <c r="S56" s="40">
-        <f t="shared" ref="S56:S61" si="12">IF(R56=1, ABS(N56-M56)/M56, 0)</f>
+        <f t="shared" ref="S56:S63" si="12">IF(R56=1, ABS(N56-M56)/M56, 0)</f>
         <v>2.7360178970917266E-2</v>
       </c>
       <c r="T56" s="39">
@@ -6540,67 +6561,65 @@
       <c r="B59" s="34">
         <v>46297</v>
       </c>
-      <c r="C59" s="55">
-        <v>46308</v>
-      </c>
-      <c r="D59" s="56">
+      <c r="C59" s="34">
+        <v>46310</v>
+      </c>
+      <c r="D59" s="35">
         <f t="shared" si="5"/>
-        <v>11</v>
-      </c>
-      <c r="E59" s="47" t="s">
+        <v>13</v>
+      </c>
+      <c r="E59" s="33" t="s">
         <v>58</v>
       </c>
-      <c r="F59" s="48" t="s">
+      <c r="F59" s="36" t="s">
         <v>59</v>
       </c>
-      <c r="G59" s="47" t="s">
+      <c r="G59" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H59" s="48" t="s">
+      <c r="H59" s="36" t="s">
         <v>24</v>
       </c>
-      <c r="I59" s="47" t="s">
+      <c r="I59" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="J59" s="47" t="s">
+      <c r="J59" s="33" t="s">
         <v>531</v>
       </c>
-      <c r="K59" s="47" t="s">
+      <c r="K59" s="33" t="s">
         <v>607</v>
       </c>
-      <c r="L59" s="47">
+      <c r="L59" s="33">
         <v>15</v>
       </c>
-      <c r="M59" s="47">
-        <v>17.53</v>
-      </c>
-      <c r="N59" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O59" s="47">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="P59" s="49">
-        <f>ABS(M59*L59)*100</f>
-        <v>26295.000000000004</v>
-      </c>
-      <c r="Q59" s="47">
-        <v>1.88</v>
-      </c>
-      <c r="R59" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S59" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T59" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="U59" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V59" s="33">
-        <v>602</v>
+      <c r="M59" s="33">
+        <v>17.533999999999999</v>
+      </c>
+      <c r="N59" s="33">
+        <v>17.913</v>
+      </c>
+      <c r="O59" s="33">
+        <v>17.913</v>
+      </c>
+      <c r="P59" s="39">
+        <v>26870</v>
+      </c>
+      <c r="Q59" s="33">
+        <v>6.9</v>
+      </c>
+      <c r="R59" s="33">
+        <v>1</v>
+      </c>
+      <c r="S59" s="40">
+        <f t="shared" si="12"/>
+        <v>2.1615147713014791E-2</v>
+      </c>
+      <c r="T59" s="39">
+        <f>(26870-17905-8396)</f>
+        <v>569</v>
+      </c>
+      <c r="U59" s="41">
+        <v>569</v>
       </c>
     </row>
     <row r="60" spans="1:22" x14ac:dyDescent="0.25">
@@ -6746,67 +6765,65 @@
       <c r="B62" s="34">
         <v>46303</v>
       </c>
-      <c r="C62" s="55">
-        <v>46308</v>
-      </c>
-      <c r="D62" s="56">
+      <c r="C62" s="34">
+        <v>46310</v>
+      </c>
+      <c r="D62" s="35">
         <f t="shared" si="5"/>
+        <v>7</v>
+      </c>
+      <c r="E62" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="F62" s="36" t="s">
+        <v>52</v>
+      </c>
+      <c r="G62" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="H62" s="36" t="s">
+        <v>630</v>
+      </c>
+      <c r="I62" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="J62" s="33" t="s">
+        <v>122</v>
+      </c>
+      <c r="K62" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="L62" s="33">
         <v>5</v>
       </c>
-      <c r="E62" s="47" t="s">
-        <v>88</v>
-      </c>
-      <c r="F62" s="48" t="s">
-        <v>52</v>
-      </c>
-      <c r="G62" s="47" t="s">
-        <v>30</v>
-      </c>
-      <c r="H62" s="48" t="s">
-        <v>630</v>
-      </c>
-      <c r="I62" s="47" t="s">
-        <v>32</v>
-      </c>
-      <c r="J62" s="47" t="s">
-        <v>122</v>
-      </c>
-      <c r="K62" s="47" t="s">
-        <v>89</v>
-      </c>
-      <c r="L62" s="47">
-        <v>3</v>
-      </c>
-      <c r="M62" s="47">
-        <v>4161</v>
-      </c>
-      <c r="N62" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O62" s="47">
-        <v>4176</v>
-      </c>
-      <c r="P62" s="49">
+      <c r="M62" s="33">
+        <v>4155.68</v>
+      </c>
+      <c r="N62" s="33">
+        <v>4185.5200000000004</v>
+      </c>
+      <c r="O62" s="33">
+        <v>4185.5200000000004</v>
+      </c>
+      <c r="P62" s="39">
         <f>L62*O62*10</f>
-        <v>125280</v>
-      </c>
-      <c r="Q62" s="47">
-        <v>8.64</v>
-      </c>
-      <c r="R62" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="S62" s="50" t="s">
-        <v>72</v>
-      </c>
-      <c r="T62" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="U62" s="49" t="s">
-        <v>72</v>
-      </c>
-      <c r="V62" s="33">
-        <v>138</v>
+        <v>209276.00000000003</v>
+      </c>
+      <c r="Q62" s="33">
+        <v>9.6</v>
+      </c>
+      <c r="R62" s="33">
+        <v>1</v>
+      </c>
+      <c r="S62" s="40">
+        <f t="shared" si="12"/>
+        <v>7.1805336310784623E-3</v>
+      </c>
+      <c r="T62" s="39">
+        <v>1492</v>
+      </c>
+      <c r="U62" s="41">
+        <v>1492</v>
       </c>
     </row>
     <row r="63" spans="1:22" x14ac:dyDescent="0.25">
@@ -6816,155 +6833,430 @@
       <c r="B63" s="34">
         <v>46303</v>
       </c>
-      <c r="C63" s="55">
-        <v>46308</v>
-      </c>
-      <c r="D63" s="56">
-        <f t="shared" ref="D63" si="13">C63-B63</f>
-        <v>5</v>
-      </c>
-      <c r="E63" s="47" t="s">
+      <c r="C63" s="34">
+        <v>46310</v>
+      </c>
+      <c r="D63" s="35">
+        <f t="shared" ref="D63:D66" si="13">C63-B63</f>
+        <v>7</v>
+      </c>
+      <c r="E63" s="33" t="s">
         <v>631</v>
       </c>
-      <c r="F63" s="48" t="s">
+      <c r="F63" s="36" t="s">
         <v>632</v>
       </c>
-      <c r="G63" s="47" t="s">
+      <c r="G63" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="H63" s="48" t="s">
+      <c r="H63" s="36" t="s">
         <v>630</v>
       </c>
-      <c r="I63" s="47" t="s">
+      <c r="I63" s="33" t="s">
         <v>32</v>
       </c>
-      <c r="J63" s="47" t="s">
+      <c r="J63" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="K63" s="47" t="s">
+      <c r="K63" s="33" t="s">
         <v>633</v>
       </c>
-      <c r="L63" s="47">
-        <v>-8</v>
-      </c>
-      <c r="M63" s="47">
+      <c r="L63" s="33">
+        <v>-14</v>
+      </c>
+      <c r="M63" s="33">
         <v>6.6361999999999997</v>
       </c>
-      <c r="N63" s="47" t="s">
+      <c r="N63" s="33">
+        <v>6.5984999999999996</v>
+      </c>
+      <c r="O63" s="33">
+        <v>6.5984999999999996</v>
+      </c>
+      <c r="P63" s="39">
+        <v>232267</v>
+      </c>
+      <c r="Q63" s="33">
+        <v>26.88</v>
+      </c>
+      <c r="R63" s="33">
+        <v>1</v>
+      </c>
+      <c r="S63" s="40">
+        <f t="shared" si="12"/>
+        <v>5.6809619963232071E-3</v>
+      </c>
+      <c r="T63" s="39">
+        <v>1318</v>
+      </c>
+      <c r="U63" s="41">
+        <v>1318</v>
+      </c>
+    </row>
+    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A64" s="33">
+        <v>57</v>
+      </c>
+      <c r="B64" s="34">
+        <v>46310</v>
+      </c>
+      <c r="C64" s="54">
+        <v>46311</v>
+      </c>
+      <c r="D64" s="55">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="E64" s="47" t="s">
+        <v>634</v>
+      </c>
+      <c r="F64" s="48" t="s">
+        <v>635</v>
+      </c>
+      <c r="G64" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H64" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I64" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J64" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K64" s="47" t="s">
+        <v>634</v>
+      </c>
+      <c r="L64" s="47">
+        <v>610</v>
+      </c>
+      <c r="M64" s="47">
+        <v>7.2960000000000003</v>
+      </c>
+      <c r="N64" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="O63" s="47">
-        <v>6.5605000000000002</v>
-      </c>
-      <c r="P63" s="49">
-        <v>131210</v>
-      </c>
-      <c r="Q63" s="47">
-        <v>24.01</v>
-      </c>
-      <c r="R63" s="47" t="s">
+      <c r="O64" s="47">
+        <v>8.16</v>
+      </c>
+      <c r="P64" s="49">
+        <v>4984</v>
+      </c>
+      <c r="Q64" s="47">
+        <v>1.01</v>
+      </c>
+      <c r="R64" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="S63" s="50" t="s">
+      <c r="S64" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="T63" s="49" t="s">
+      <c r="T64" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="U63" s="49" t="s">
+      <c r="U64" s="47" t="s">
         <v>72</v>
       </c>
-      <c r="V63" s="33">
-        <v>592</v>
-      </c>
-    </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="B64" s="34"/>
-      <c r="C64" s="34"/>
-      <c r="D64" s="35"/>
-      <c r="F64" s="36"/>
-      <c r="H64" s="36"/>
-      <c r="P64" s="39"/>
-      <c r="S64" s="40"/>
-      <c r="T64" s="39"/>
-      <c r="U64" s="41"/>
-    </row>
-    <row r="65" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="F65" s="36"/>
-      <c r="H65" s="36"/>
-    </row>
-    <row r="66" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="D66" s="52" t="s">
+      <c r="V64" s="33">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A65" s="33">
+        <v>58</v>
+      </c>
+      <c r="B65" s="34">
+        <v>46310</v>
+      </c>
+      <c r="C65" s="54">
+        <v>46311</v>
+      </c>
+      <c r="D65" s="55">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="E65" s="47" t="s">
+        <v>636</v>
+      </c>
+      <c r="F65" s="48" t="s">
+        <v>637</v>
+      </c>
+      <c r="G65" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H65" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I65" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J65" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K65" s="47" t="s">
+        <v>636</v>
+      </c>
+      <c r="L65" s="47">
+        <v>-504</v>
+      </c>
+      <c r="M65" s="47">
+        <v>28.216999999999999</v>
+      </c>
+      <c r="N65" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O65" s="47">
+        <v>27.86</v>
+      </c>
+      <c r="P65" s="49">
+        <v>14041</v>
+      </c>
+      <c r="Q65" s="47">
+        <v>2.33</v>
+      </c>
+      <c r="R65" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S65" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="T65" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U65" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="V65" s="33">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A66" s="33">
+        <v>59</v>
+      </c>
+      <c r="B66" s="34">
+        <v>46310</v>
+      </c>
+      <c r="C66" s="54">
+        <v>46311</v>
+      </c>
+      <c r="D66" s="55">
+        <f t="shared" si="13"/>
+        <v>1</v>
+      </c>
+      <c r="E66" s="47" t="s">
+        <v>638</v>
+      </c>
+      <c r="F66" s="48" t="s">
+        <v>639</v>
+      </c>
+      <c r="G66" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H66" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I66" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J66" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K66" s="47" t="s">
+        <v>638</v>
+      </c>
+      <c r="L66" s="47">
+        <v>-1078</v>
+      </c>
+      <c r="M66" s="47">
+        <v>46.56</v>
+      </c>
+      <c r="N66" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O66" s="47">
+        <v>46.57</v>
+      </c>
+      <c r="P66" s="49">
+        <v>50202</v>
+      </c>
+      <c r="Q66" s="47">
+        <v>4.32</v>
+      </c>
+      <c r="R66" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S66" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="T66" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U66" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="V66" s="33">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A67" s="33">
+        <v>60</v>
+      </c>
+      <c r="B67" s="34">
+        <v>46310</v>
+      </c>
+      <c r="C67" s="54">
+        <v>46311</v>
+      </c>
+      <c r="D67" s="55">
+        <f t="shared" ref="D67" si="14">C67-B67</f>
+        <v>1</v>
+      </c>
+      <c r="E67" s="47" t="s">
+        <v>640</v>
+      </c>
+      <c r="F67" s="48" t="s">
+        <v>641</v>
+      </c>
+      <c r="G67" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="H67" s="48" t="s">
+        <v>24</v>
+      </c>
+      <c r="I67" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="J67" s="47" t="s">
+        <v>25</v>
+      </c>
+      <c r="K67" s="47" t="s">
+        <v>640</v>
+      </c>
+      <c r="L67" s="47">
+        <v>-185</v>
+      </c>
+      <c r="M67" s="47">
+        <v>388.43</v>
+      </c>
+      <c r="N67" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="O67" s="47">
+        <v>391.07</v>
+      </c>
+      <c r="P67" s="49">
+        <v>71860</v>
+      </c>
+      <c r="Q67" s="47">
+        <v>3.66</v>
+      </c>
+      <c r="R67" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="S67" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="T67" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="U67" s="47" t="s">
+        <v>72</v>
+      </c>
+      <c r="V67" s="33">
+        <f>(O67-M67)*L67</f>
+        <v>-488.39999999999748</v>
+      </c>
+    </row>
+    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="B68" s="34"/>
+      <c r="C68" s="34"/>
+      <c r="D68" s="35"/>
+      <c r="F68" s="36"/>
+      <c r="H68" s="36"/>
+      <c r="P68" s="39"/>
+      <c r="S68" s="40"/>
+      <c r="T68" s="39"/>
+      <c r="U68" s="41"/>
+    </row>
+    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F69" s="36"/>
+      <c r="H69" s="36"/>
+    </row>
+    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D70" s="51" t="s">
         <v>102</v>
       </c>
-      <c r="E66" s="46">
-        <f>AVERAGE(D2:D61)</f>
-        <v>6.4333333333333336</v>
-      </c>
-      <c r="F66" s="36"/>
-      <c r="H66" s="36"/>
-      <c r="U66" s="39">
-        <f>SUM(U2:U64)</f>
-        <v>84623.47</v>
-      </c>
-      <c r="V66" s="39">
-        <f>SUM(V2:V64)</f>
-        <v>1332</v>
-      </c>
-    </row>
-    <row r="67" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="D67" s="52" t="s">
+      <c r="E70" s="46">
+        <f>AVERAGE(D2:D63)</f>
+        <v>6.4838709677419351</v>
+      </c>
+      <c r="F70" s="36"/>
+      <c r="H70" s="36"/>
+      <c r="U70" s="39">
+        <f>SUM(U2:U68)</f>
+        <v>88002.47</v>
+      </c>
+      <c r="V70" s="39">
+        <f>SUM(V2:V68)</f>
+        <v>215.60000000000252</v>
+      </c>
+    </row>
+    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D71" s="51" t="s">
         <v>103</v>
       </c>
-      <c r="E67" s="46">
-        <f>AVERAGE(D2:D11,D13,D15:D61)</f>
-        <v>4.6551724137931032</v>
-      </c>
-      <c r="F67" s="36"/>
-      <c r="U67" s="53" t="s">
+      <c r="E71" s="46">
+        <f>AVERAGE(D2:D11,D13,D15:D63)</f>
+        <v>4.7666666666666666</v>
+      </c>
+      <c r="F71" s="36"/>
+      <c r="U71" s="52" t="s">
         <v>104</v>
       </c>
-      <c r="V67" s="36" t="s">
+      <c r="V71" s="36" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="68" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="F68" s="36"/>
-      <c r="U68" s="33" t="s">
+    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F72" s="36"/>
+      <c r="U72" s="33" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="69" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="F69" s="36"/>
-      <c r="U69" s="39">
-        <f>U66+V66</f>
-        <v>85955.47</v>
-      </c>
-    </row>
-    <row r="70" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="F70" s="36"/>
-    </row>
-    <row r="71" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="F71" s="36"/>
-      <c r="U71" s="36" t="s">
+    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F73" s="36"/>
+      <c r="U73" s="39">
+        <f>U70+V70</f>
+        <v>88218.07</v>
+      </c>
+    </row>
+    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F74" s="36"/>
+    </row>
+    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F75" s="36"/>
+      <c r="U75" s="36" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="72" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="F72" s="36"/>
-      <c r="U72" s="39">
+    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="F76" s="36"/>
+      <c r="U76" s="39">
         <v>333000</v>
       </c>
     </row>
-    <row r="74" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="U74" s="33" t="s">
+    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U78" s="33" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="75" spans="4:22" x14ac:dyDescent="0.25">
-      <c r="U75" s="54">
-        <f>U69/U72</f>
-        <v>0.25812453453453454</v>
+    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="U79" s="53">
+        <f>U73/U76</f>
+        <v>0.26491912912912913</v>
       </c>
     </row>
   </sheetData>
@@ -6977,7 +7269,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:I91"/>
+  <dimension ref="A1:I92"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -7043,11 +7335,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C91" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C92" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D91" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D92" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -8223,11 +8515,11 @@
         <v>113</v>
       </c>
       <c r="G74" s="27">
-        <f>AVERAGE(C3:C91)</f>
+        <f>AVERAGE(C3:C92)</f>
+        <v>994.70099999999968</v>
+      </c>
+      <c r="I74" s="27">
         <v>992.9223595505614</v>
-      </c>
-      <c r="I74" s="27">
-        <v>978.78264367816053</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -8250,11 +8542,11 @@
         <v>114</v>
       </c>
       <c r="G75" s="27">
-        <f>_xlfn.STDEV.S(C3:C91)</f>
+        <f>_xlfn.STDEV.S(C3:C92)</f>
+        <v>4063.8942233804319</v>
+      </c>
+      <c r="I75" s="27">
         <v>4086.8840749527426</v>
-      </c>
-      <c r="I75" s="27">
-        <v>4126.8937638138605</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
@@ -8278,10 +8570,10 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
+        <v>3.8855314585596612</v>
+      </c>
+      <c r="I76" s="28">
         <v>3.8567655745360794</v>
-      </c>
-      <c r="I76" s="28">
-        <v>3.7649849174196888</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
@@ -8304,11 +8596,11 @@
         <v>116</v>
       </c>
       <c r="G77" s="29">
-        <f>_xlfn.STDEV.S(D2:D91)*SQRT(252)</f>
+        <f>_xlfn.STDEV.S(D2:D92)*SQRT(252)</f>
+        <v>0.17393524693700121</v>
+      </c>
+      <c r="I77" s="29">
         <v>0.1749096544335895</v>
-      </c>
-      <c r="I77" s="29">
-        <v>0.17668183134849275</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -8331,11 +8623,11 @@
         <v>117</v>
       </c>
       <c r="G78" s="29" cm="1">
-        <f t="array" ref="G78">PRODUCT(1+D3:D91)-1</f>
+        <f t="array" ref="G78">PRODUCT(1+D3:D92)-1</f>
+        <v>0.26847074110515279</v>
+      </c>
+      <c r="I78" s="29">
         <v>0.26501301208197625</v>
-      </c>
-      <c r="I78" s="29">
-        <v>0.25536855714829354</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -8358,11 +8650,11 @@
         <v>118</v>
       </c>
       <c r="G79" s="29" cm="1">
-        <f t="array" ref="G79">PRODUCT(1+D2:D91)^(252/COUNT(D2:D91))-1</f>
+        <f t="array" ref="G79">PRODUCT(1+D2:D92)^(252/COUNT(D2:D92))-1</f>
+        <v>0.93200128707868957</v>
+      </c>
+      <c r="I79" s="29">
         <v>0.93137221672115644</v>
-      </c>
-      <c r="I79" s="29">
-        <v>0.91798379730044988</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -8567,6 +8859,23 @@
       <c r="D91" s="23">
         <f t="shared" si="1"/>
         <v>7.3697282323159953E-3</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A92" s="26">
+        <v>46310</v>
+      </c>
+      <c r="B92" s="5">
+        <f>B91-10-480+180+533+548+382</f>
+        <v>422979</v>
+      </c>
+      <c r="C92" s="5">
+        <f t="shared" si="0"/>
+        <v>1153</v>
+      </c>
+      <c r="D92" s="23">
+        <f t="shared" si="1"/>
+        <v>2.7333545111017338E-3</v>
       </c>
     </row>
   </sheetData>
@@ -13520,7 +13829,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="14">
-        <f t="shared" ref="M69:M98" si="0">SUM(C69:L69)</f>
+        <f t="shared" ref="M69:M99" si="0">SUM(C69:L69)</f>
         <v>407651</v>
       </c>
       <c r="N69" s="15">
@@ -15784,7 +16093,7 @@
         <v>0</v>
       </c>
       <c r="O98" s="15">
-        <f t="shared" ref="O98" si="99">D98/M98</f>
+        <f t="shared" ref="O98:O99" si="99">D98/M98</f>
         <v>0.32961695106513111</v>
       </c>
       <c r="P98" s="15">
@@ -15815,6 +16124,86 @@
       </c>
       <c r="W98" s="15">
         <f t="shared" ref="W98" si="104">L98/M98</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A99" s="10">
+        <v>46310</v>
+      </c>
+      <c r="B99" s="11">
+        <v>422979</v>
+      </c>
+      <c r="C99" s="19">
+        <v>141047</v>
+      </c>
+      <c r="D99" s="13">
+        <f>B99-C99-H99-L99-F99</f>
+        <v>281932</v>
+      </c>
+      <c r="E99" s="13">
+        <v>0</v>
+      </c>
+      <c r="F99" s="13">
+        <v>0</v>
+      </c>
+      <c r="G99" s="13">
+        <v>0</v>
+      </c>
+      <c r="H99" s="13">
+        <v>0</v>
+      </c>
+      <c r="I99" s="13">
+        <v>0</v>
+      </c>
+      <c r="J99" s="13">
+        <v>0</v>
+      </c>
+      <c r="K99" s="13">
+        <v>0</v>
+      </c>
+      <c r="L99" s="18">
+        <v>0</v>
+      </c>
+      <c r="M99" s="14">
+        <f t="shared" si="0"/>
+        <v>422979</v>
+      </c>
+      <c r="N99" s="15">
+        <f t="shared" ref="N99:O99" si="105">C99/M99</f>
+        <v>0.33346099924582545</v>
+      </c>
+      <c r="O99" s="15">
+        <f t="shared" si="99"/>
+        <v>0.6665390007541746</v>
+      </c>
+      <c r="P99" s="15">
+        <f t="shared" ref="O99:P99" si="106">E99/N99</f>
+        <v>0</v>
+      </c>
+      <c r="Q99" s="15">
+        <f t="shared" ref="Q99" si="107">E99/M99</f>
+        <v>0</v>
+      </c>
+      <c r="R99" s="15">
+        <v>0</v>
+      </c>
+      <c r="S99" s="15">
+        <v>0</v>
+      </c>
+      <c r="T99" s="15">
+        <f t="shared" ref="T99" si="108">I99/M99</f>
+        <v>0</v>
+      </c>
+      <c r="U99" s="15">
+        <v>0</v>
+      </c>
+      <c r="V99" s="16">
+        <f t="shared" ref="V99" si="109">K99/M99</f>
+        <v>0</v>
+      </c>
+      <c r="W99" s="15">
+        <f t="shared" ref="W99" si="110">L99/M99</f>
         <v>0</v>
       </c>
     </row>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8D213A20-F34F-2241-9834-E487EFC4A429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{771530F0-72D7-BF4E-B20B-DEC5FE203267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1980" yWindow="-20900" windowWidth="44300" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2618,7 +2618,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V79"/>
+  <dimension ref="A1:X79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5" style="33" bestFit="1" customWidth="1"/>
@@ -2639,7 +2639,8 @@
     <col min="20" max="20" width="10" style="33" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="13" style="33" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="14.83203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="23" max="16384" width="9.1640625" style="33"/>
+    <col min="23" max="23" width="6" style="33" bestFit="1" customWidth="1"/>
+    <col min="24" max="16384" width="9.1640625" style="33"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22" s="30" customFormat="1" x14ac:dyDescent="0.25">
@@ -6929,16 +6930,16 @@
         <v>634</v>
       </c>
       <c r="L64" s="47">
-        <v>610</v>
+        <v>1220</v>
       </c>
       <c r="M64" s="47">
-        <v>7.2960000000000003</v>
+        <v>7.74</v>
       </c>
       <c r="N64" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O64" s="47">
-        <v>8.16</v>
+        <v>7.91</v>
       </c>
       <c r="P64" s="49">
         <v>4984</v>
@@ -6959,10 +6960,10 @@
         <v>72</v>
       </c>
       <c r="V64" s="33">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="65" spans="1:22" x14ac:dyDescent="0.25">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A65" s="33">
         <v>58</v>
       </c>
@@ -7007,7 +7008,7 @@
         <v>72</v>
       </c>
       <c r="O65" s="47">
-        <v>27.86</v>
+        <v>28.12</v>
       </c>
       <c r="P65" s="49">
         <v>14041</v>
@@ -7028,10 +7029,10 @@
         <v>72</v>
       </c>
       <c r="V65" s="33">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="66" spans="1:22" x14ac:dyDescent="0.25">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A66" s="33">
         <v>59</v>
       </c>
@@ -7067,19 +7068,19 @@
         <v>638</v>
       </c>
       <c r="L66" s="47">
-        <v>-1078</v>
+        <v>-1956</v>
       </c>
       <c r="M66" s="47">
-        <v>46.56</v>
+        <v>46.65</v>
       </c>
       <c r="N66" s="47" t="s">
         <v>72</v>
       </c>
       <c r="O66" s="47">
-        <v>46.57</v>
+        <v>46.5</v>
       </c>
       <c r="P66" s="49">
-        <v>50202</v>
+        <v>90954</v>
       </c>
       <c r="Q66" s="47">
         <v>4.32</v>
@@ -7097,10 +7098,10 @@
         <v>72</v>
       </c>
       <c r="V66" s="33">
-        <v>-10</v>
-      </c>
-    </row>
-    <row r="67" spans="1:22" x14ac:dyDescent="0.25">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
       <c r="A67" s="33">
         <v>60</v>
       </c>
@@ -7136,7 +7137,7 @@
         <v>640</v>
       </c>
       <c r="L67" s="47">
-        <v>-185</v>
+        <v>-310</v>
       </c>
       <c r="M67" s="47">
         <v>388.43</v>
@@ -7145,10 +7146,10 @@
         <v>72</v>
       </c>
       <c r="O67" s="47">
-        <v>391.07</v>
+        <v>384.22</v>
       </c>
       <c r="P67" s="49">
-        <v>71860</v>
+        <v>115266</v>
       </c>
       <c r="Q67" s="47">
         <v>3.66</v>
@@ -7166,11 +7167,10 @@
         <v>72</v>
       </c>
       <c r="V67" s="33">
-        <f>(O67-M67)*L67</f>
-        <v>-488.39999999999748</v>
-      </c>
-    </row>
-    <row r="68" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1265</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
       <c r="B68" s="34"/>
       <c r="C68" s="34"/>
       <c r="D68" s="35"/>
@@ -7181,11 +7181,11 @@
       <c r="T68" s="39"/>
       <c r="U68" s="41"/>
     </row>
-    <row r="69" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
       <c r="F69" s="36"/>
       <c r="H69" s="36"/>
     </row>
-    <row r="70" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D70" s="51" t="s">
         <v>102</v>
       </c>
@@ -7201,10 +7201,15 @@
       </c>
       <c r="V70" s="39">
         <f>SUM(V2:V68)</f>
-        <v>215.60000000000252</v>
-      </c>
-    </row>
-    <row r="71" spans="1:22" x14ac:dyDescent="0.25">
+        <v>1860</v>
+      </c>
+      <c r="W70" s="39">
+        <f>SUM(W2:W68)</f>
+        <v>0</v>
+      </c>
+      <c r="X70" s="39"/>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
       <c r="D71" s="51" t="s">
         <v>103</v>
       </c>
@@ -7220,43 +7225,43 @@
         <v>105</v>
       </c>
     </row>
-    <row r="72" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
       <c r="F72" s="36"/>
       <c r="U72" s="33" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="73" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
       <c r="F73" s="36"/>
       <c r="U73" s="39">
         <f>U70+V70</f>
-        <v>88218.07</v>
-      </c>
-    </row>
-    <row r="74" spans="1:22" x14ac:dyDescent="0.25">
+        <v>89862.47</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
       <c r="F74" s="36"/>
     </row>
-    <row r="75" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
       <c r="F75" s="36"/>
       <c r="U75" s="36" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="76" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
       <c r="F76" s="36"/>
       <c r="U76" s="39">
         <v>333000</v>
       </c>
     </row>
-    <row r="78" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
       <c r="U78" s="33" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="79" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
       <c r="U79" s="53">
         <f>U73/U76</f>
-        <v>0.26491912912912913</v>
+        <v>0.26985726726726728</v>
       </c>
     </row>
   </sheetData>
@@ -7269,7 +7274,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I93"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -7335,11 +7340,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C92" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C93" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D92" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D93" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -8515,11 +8520,11 @@
         <v>113</v>
       </c>
       <c r="G74" s="27">
-        <f>AVERAGE(C3:C92)</f>
+        <f>AVERAGE(C3:C93)</f>
+        <v>1001.8361538461535</v>
+      </c>
+      <c r="I74" s="27">
         <v>994.70099999999968</v>
-      </c>
-      <c r="I74" s="27">
-        <v>992.9223595505614</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -8542,11 +8547,11 @@
         <v>114</v>
       </c>
       <c r="G75" s="27">
-        <f>_xlfn.STDEV.S(C3:C92)</f>
+        <f>_xlfn.STDEV.S(C3:C93)</f>
+        <v>4041.8271217339247</v>
+      </c>
+      <c r="I75" s="27">
         <v>4063.8942233804319</v>
-      </c>
-      <c r="I75" s="27">
-        <v>4086.8840749527426</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
@@ -8570,10 +8575,10 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
+        <v>3.934768961181994</v>
+      </c>
+      <c r="I76" s="28">
         <v>3.8855314585596612</v>
-      </c>
-      <c r="I76" s="28">
-        <v>3.8567655745360794</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
@@ -8596,11 +8601,11 @@
         <v>116</v>
       </c>
       <c r="G77" s="29">
-        <f>_xlfn.STDEV.S(D2:D92)*SQRT(252)</f>
+        <f>_xlfn.STDEV.S(D2:D93)*SQRT(252)</f>
+        <v>0.17298853160364927</v>
+      </c>
+      <c r="I77" s="29">
         <v>0.17393524693700121</v>
-      </c>
-      <c r="I77" s="29">
-        <v>0.1749096544335895</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -8623,11 +8628,11 @@
         <v>117</v>
       </c>
       <c r="G78" s="29" cm="1">
-        <f t="array" ref="G78">PRODUCT(1+D3:D92)-1</f>
+        <f t="array" ref="G78">PRODUCT(1+D3:D93)-1</f>
+        <v>0.27340092888841583</v>
+      </c>
+      <c r="I78" s="29">
         <v>0.26847074110515279</v>
-      </c>
-      <c r="I78" s="29">
-        <v>0.26501301208197625</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -8650,11 +8655,11 @@
         <v>118</v>
       </c>
       <c r="G79" s="29" cm="1">
-        <f t="array" ref="G79">PRODUCT(1+D2:D92)^(252/COUNT(D2:D92))-1</f>
+        <f t="array" ref="G79">PRODUCT(1+D2:D93)^(252/COUNT(D2:D93))-1</f>
+        <v>0.93871187618965823</v>
+      </c>
+      <c r="I79" s="29">
         <v>0.93200128707868957</v>
-      </c>
-      <c r="I79" s="29">
-        <v>0.93137221672115644</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -8876,6 +8881,23 @@
       <c r="D92" s="23">
         <f t="shared" si="1"/>
         <v>2.7333545111017338E-3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A93" s="26">
+        <v>46311</v>
+      </c>
+      <c r="B93" s="5">
+        <f>B92+1644</f>
+        <v>424623</v>
+      </c>
+      <c r="C93" s="5">
+        <f t="shared" si="0"/>
+        <v>1644</v>
+      </c>
+      <c r="D93" s="23">
+        <f t="shared" si="1"/>
+        <v>3.886717780315335E-3</v>
       </c>
     </row>
   </sheetData>
@@ -13829,7 +13851,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="14">
-        <f t="shared" ref="M69:M99" si="0">SUM(C69:L69)</f>
+        <f t="shared" ref="M69:M100" si="0">SUM(C69:L69)</f>
         <v>407651</v>
       </c>
       <c r="N69" s="15">
@@ -15733,7 +15755,7 @@
         <v>160440</v>
       </c>
       <c r="D94" s="13">
-        <f>B94-C94-H94-L94-F94</f>
+        <f t="shared" ref="D94:D100" si="73">B94-C94-H94-L94-F94</f>
         <v>76736</v>
       </c>
       <c r="E94" s="13">
@@ -15765,11 +15787,11 @@
         <v>420025</v>
       </c>
       <c r="N94" s="15">
-        <f t="shared" ref="N94" si="73">C94/M94</f>
+        <f t="shared" ref="N94" si="74">C94/M94</f>
         <v>0.38197726325813941</v>
       </c>
       <c r="O94" s="15">
-        <f t="shared" ref="O94" si="74">D94/M94</f>
+        <f t="shared" ref="O94" si="75">D94/M94</f>
         <v>0.18269388726861496</v>
       </c>
       <c r="P94" s="15">
@@ -15784,22 +15806,22 @@
         <v>0</v>
       </c>
       <c r="S94" s="15">
-        <f t="shared" ref="S94" si="75">H94/M94</f>
+        <f t="shared" ref="S94" si="76">H94/M94</f>
         <v>4.2045116362121306E-2</v>
       </c>
       <c r="T94" s="15">
-        <f t="shared" ref="T94" si="76">I94/M94</f>
+        <f t="shared" ref="T94" si="77">I94/M94</f>
         <v>0</v>
       </c>
       <c r="U94" s="15">
         <v>0</v>
       </c>
       <c r="V94" s="16">
-        <f t="shared" ref="V94" si="77">K94/M94</f>
+        <f t="shared" ref="V94" si="78">K94/M94</f>
         <v>0</v>
       </c>
       <c r="W94" s="15">
-        <f t="shared" ref="W94" si="78">L94/M94</f>
+        <f t="shared" ref="W94" si="79">L94/M94</f>
         <v>0</v>
       </c>
     </row>
@@ -15814,7 +15836,7 @@
         <v>0</v>
       </c>
       <c r="D95" s="13">
-        <f>B95-C95-H95-L95-F95</f>
+        <f t="shared" si="73"/>
         <v>236790</v>
       </c>
       <c r="E95" s="13">
@@ -15846,11 +15868,11 @@
         <v>419639</v>
       </c>
       <c r="N95" s="15">
-        <f t="shared" ref="N95" si="79">C95/M95</f>
+        <f t="shared" ref="N95" si="80">C95/M95</f>
         <v>0</v>
       </c>
       <c r="O95" s="15">
-        <f t="shared" ref="O95" si="80">D95/M95</f>
+        <f t="shared" ref="O95" si="81">D95/M95</f>
         <v>0.56427071840319898</v>
       </c>
       <c r="P95" s="15">
@@ -15865,22 +15887,22 @@
         <v>0</v>
       </c>
       <c r="S95" s="15">
-        <f t="shared" ref="S95" si="81">H95/M95</f>
+        <f t="shared" ref="S95" si="82">H95/M95</f>
         <v>4.2083791068037051E-2</v>
       </c>
       <c r="T95" s="15">
-        <f t="shared" ref="T95" si="82">I95/M95</f>
+        <f t="shared" ref="T95" si="83">I95/M95</f>
         <v>0</v>
       </c>
       <c r="U95" s="15">
         <v>0</v>
       </c>
       <c r="V95" s="16">
-        <f t="shared" ref="V95" si="83">K95/M95</f>
+        <f t="shared" ref="V95" si="84">K95/M95</f>
         <v>0</v>
       </c>
       <c r="W95" s="15">
-        <f t="shared" ref="W95" si="84">L95/M95</f>
+        <f t="shared" ref="W95" si="85">L95/M95</f>
         <v>0</v>
       </c>
     </row>
@@ -15895,7 +15917,7 @@
         <v>0</v>
       </c>
       <c r="D96" s="13">
-        <f>B96-C96-H96-L96-F96</f>
+        <f t="shared" si="73"/>
         <v>227126</v>
       </c>
       <c r="E96" s="13">
@@ -15927,11 +15949,11 @@
         <v>418610</v>
       </c>
       <c r="N96" s="15">
-        <f t="shared" ref="N96" si="85">C96/M96</f>
+        <f t="shared" ref="N96" si="86">C96/M96</f>
         <v>0</v>
       </c>
       <c r="O96" s="15">
-        <f t="shared" ref="O96" si="86">D96/M96</f>
+        <f t="shared" ref="O96" si="87">D96/M96</f>
         <v>0.54257184491531496</v>
       </c>
       <c r="P96" s="15">
@@ -15946,22 +15968,22 @@
         <v>0</v>
       </c>
       <c r="S96" s="15">
-        <f t="shared" ref="S96" si="87">H96/M96</f>
+        <f t="shared" ref="S96" si="88">H96/M96</f>
         <v>6.281503069682999E-2</v>
       </c>
       <c r="T96" s="15">
-        <f t="shared" ref="T96" si="88">I96/M96</f>
+        <f t="shared" ref="T96" si="89">I96/M96</f>
         <v>0</v>
       </c>
       <c r="U96" s="15">
         <v>0</v>
       </c>
       <c r="V96" s="16">
-        <f t="shared" ref="V96" si="89">K96/M96</f>
+        <f t="shared" ref="V96" si="90">K96/M96</f>
         <v>0</v>
       </c>
       <c r="W96" s="15">
-        <f t="shared" ref="W96" si="90">L96/M96</f>
+        <f t="shared" ref="W96" si="91">L96/M96</f>
         <v>0</v>
       </c>
     </row>
@@ -15976,7 +15998,7 @@
         <v>0</v>
       </c>
       <c r="D97" s="13">
-        <f>B97-C97-H97-L97-F97</f>
+        <f t="shared" si="73"/>
         <v>227256</v>
       </c>
       <c r="E97" s="13">
@@ -16008,11 +16030,11 @@
         <v>418740</v>
       </c>
       <c r="N97" s="15">
-        <f t="shared" ref="N97" si="91">C97/M97</f>
+        <f t="shared" ref="N97" si="92">C97/M97</f>
         <v>0</v>
       </c>
       <c r="O97" s="15">
-        <f t="shared" ref="O97" si="92">D97/M97</f>
+        <f t="shared" ref="O97" si="93">D97/M97</f>
         <v>0.54271385585327414</v>
       </c>
       <c r="P97" s="15">
@@ -16020,29 +16042,29 @@
         <v>0.39449061470124658</v>
       </c>
       <c r="Q97" s="15">
-        <f t="shared" ref="Q97" si="93">E97/M97</f>
+        <f t="shared" ref="Q97" si="94">E97/M97</f>
         <v>0</v>
       </c>
       <c r="R97" s="15">
         <v>0</v>
       </c>
       <c r="S97" s="15">
-        <f t="shared" ref="S97" si="94">H97/M97</f>
+        <f t="shared" ref="S97" si="95">H97/M97</f>
         <v>6.2795529445479295E-2</v>
       </c>
       <c r="T97" s="15">
-        <f t="shared" ref="T97" si="95">I97/M97</f>
+        <f t="shared" ref="T97" si="96">I97/M97</f>
         <v>0</v>
       </c>
       <c r="U97" s="15">
         <v>0</v>
       </c>
       <c r="V97" s="16">
-        <f t="shared" ref="V97" si="96">K97/M97</f>
+        <f t="shared" ref="V97" si="97">K97/M97</f>
         <v>0</v>
       </c>
       <c r="W97" s="15">
-        <f t="shared" ref="W97" si="97">L97/M97</f>
+        <f t="shared" ref="W97" si="98">L97/M97</f>
         <v>0</v>
       </c>
     </row>
@@ -16057,7 +16079,7 @@
         <v>0</v>
       </c>
       <c r="D98" s="13">
-        <f>B98-C98-H98-L98-F98</f>
+        <f t="shared" si="73"/>
         <v>139041</v>
       </c>
       <c r="E98" s="13">
@@ -16089,11 +16111,11 @@
         <v>421826</v>
       </c>
       <c r="N98" s="15">
-        <f t="shared" ref="N98" si="98">C98/M98</f>
+        <f t="shared" ref="N98" si="99">C98/M98</f>
         <v>0</v>
       </c>
       <c r="O98" s="15">
-        <f t="shared" ref="O98:O99" si="99">D98/M98</f>
+        <f t="shared" ref="O98:O99" si="100">D98/M98</f>
         <v>0.32961695106513111</v>
       </c>
       <c r="P98" s="15">
@@ -16101,29 +16123,29 @@
         <v>0.60804691982002057</v>
       </c>
       <c r="Q98" s="15">
-        <f t="shared" ref="Q98" si="100">E98/M98</f>
+        <f t="shared" ref="Q98" si="101">E98/M98</f>
         <v>0</v>
       </c>
       <c r="R98" s="15">
         <v>0</v>
       </c>
       <c r="S98" s="15">
-        <f t="shared" ref="S98" si="101">H98/M98</f>
+        <f t="shared" ref="S98" si="102">H98/M98</f>
         <v>6.2336129114848302E-2</v>
       </c>
       <c r="T98" s="15">
-        <f t="shared" ref="T98" si="102">I98/M98</f>
+        <f t="shared" ref="T98" si="103">I98/M98</f>
         <v>0</v>
       </c>
       <c r="U98" s="15">
         <v>0</v>
       </c>
       <c r="V98" s="16">
-        <f t="shared" ref="V98" si="103">K98/M98</f>
+        <f t="shared" ref="V98" si="104">K98/M98</f>
         <v>0</v>
       </c>
       <c r="W98" s="15">
-        <f t="shared" ref="W98" si="104">L98/M98</f>
+        <f t="shared" ref="W98" si="105">L98/M98</f>
         <v>0</v>
       </c>
     </row>
@@ -16138,7 +16160,7 @@
         <v>141047</v>
       </c>
       <c r="D99" s="13">
-        <f>B99-C99-H99-L99-F99</f>
+        <f t="shared" si="73"/>
         <v>281932</v>
       </c>
       <c r="E99" s="13">
@@ -16170,19 +16192,19 @@
         <v>422979</v>
       </c>
       <c r="N99" s="15">
-        <f t="shared" ref="N99:O99" si="105">C99/M99</f>
+        <f t="shared" ref="N99" si="106">C99/M99</f>
         <v>0.33346099924582545</v>
       </c>
       <c r="O99" s="15">
-        <f t="shared" si="99"/>
+        <f t="shared" si="100"/>
         <v>0.6665390007541746</v>
       </c>
       <c r="P99" s="15">
-        <f t="shared" ref="O99:P99" si="106">E99/N99</f>
+        <f t="shared" ref="P99" si="107">E99/N99</f>
         <v>0</v>
       </c>
       <c r="Q99" s="15">
-        <f t="shared" ref="Q99" si="107">E99/M99</f>
+        <f t="shared" ref="Q99" si="108">E99/M99</f>
         <v>0</v>
       </c>
       <c r="R99" s="15">
@@ -16192,18 +16214,98 @@
         <v>0</v>
       </c>
       <c r="T99" s="15">
-        <f t="shared" ref="T99" si="108">I99/M99</f>
+        <f t="shared" ref="T99" si="109">I99/M99</f>
         <v>0</v>
       </c>
       <c r="U99" s="15">
         <v>0</v>
       </c>
       <c r="V99" s="16">
-        <f t="shared" ref="V99" si="109">K99/M99</f>
+        <f t="shared" ref="V99" si="110">K99/M99</f>
         <v>0</v>
       </c>
       <c r="W99" s="15">
-        <f t="shared" ref="W99" si="110">L99/M99</f>
+        <f t="shared" ref="W99" si="111">L99/M99</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A100" s="10">
+        <v>46311</v>
+      </c>
+      <c r="B100" s="11">
+        <v>424623</v>
+      </c>
+      <c r="C100" s="19">
+        <v>225245</v>
+      </c>
+      <c r="D100" s="13">
+        <f t="shared" si="73"/>
+        <v>199378</v>
+      </c>
+      <c r="E100" s="13">
+        <v>0</v>
+      </c>
+      <c r="F100" s="13">
+        <v>0</v>
+      </c>
+      <c r="G100" s="13">
+        <v>0</v>
+      </c>
+      <c r="H100" s="13">
+        <v>0</v>
+      </c>
+      <c r="I100" s="13">
+        <v>0</v>
+      </c>
+      <c r="J100" s="13">
+        <v>0</v>
+      </c>
+      <c r="K100" s="13">
+        <v>0</v>
+      </c>
+      <c r="L100" s="18">
+        <v>0</v>
+      </c>
+      <c r="M100" s="14">
+        <f t="shared" si="0"/>
+        <v>424623</v>
+      </c>
+      <c r="N100" s="15">
+        <f t="shared" ref="N100" si="112">C100/M100</f>
+        <v>0.5304587834384854</v>
+      </c>
+      <c r="O100" s="15">
+        <f t="shared" ref="O100" si="113">D100/M100</f>
+        <v>0.46954121656151454</v>
+      </c>
+      <c r="P100" s="15">
+        <f t="shared" ref="P100" si="114">E100/N100</f>
+        <v>0</v>
+      </c>
+      <c r="Q100" s="15">
+        <f t="shared" ref="Q100" si="115">E100/M100</f>
+        <v>0</v>
+      </c>
+      <c r="R100" s="15">
+        <v>0</v>
+      </c>
+      <c r="S100" s="15">
+        <v>0</v>
+      </c>
+      <c r="T100" s="15">
+        <f t="shared" ref="T100" si="116">I100/M100</f>
+        <v>0</v>
+      </c>
+      <c r="U100" s="15">
+        <v>0</v>
+      </c>
+      <c r="V100" s="16">
+        <f t="shared" ref="V100" si="117">K100/M100</f>
+        <v>0</v>
+      </c>
+      <c r="W100" s="15">
+        <f t="shared" ref="W100" si="118">L100/M100</f>
         <v>0</v>
       </c>
     </row>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{771530F0-72D7-BF4E-B20B-DEC5FE203267}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8B84A83-C32C-7E47-8DF3-480D3C3BFB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1980" yWindow="-20900" windowWidth="44300" windowHeight="19260" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="23940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="998" uniqueCount="642">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="746">
   <si>
     <t>Trade ID</t>
   </si>
@@ -87,9 +87,6 @@
     <t>Trade Type</t>
   </si>
   <si>
-    <t>RV Theme</t>
-  </si>
-  <si>
     <t>Asset Class</t>
   </si>
   <si>
@@ -138,9 +135,6 @@
     <t>Directional</t>
   </si>
   <si>
-    <t>NA</t>
-  </si>
-  <si>
     <t>Equities</t>
   </si>
   <si>
@@ -159,9 +153,6 @@
     <t>RV</t>
   </si>
   <si>
-    <t>Long Silver / Short Gold</t>
-  </si>
-  <si>
     <t>Futures</t>
   </si>
   <si>
@@ -192,9 +183,6 @@
     <t>CCU6</t>
   </si>
   <si>
-    <t>SF</t>
-  </si>
-  <si>
     <t>Swiss Franc Futures</t>
   </si>
   <si>
@@ -207,9 +195,6 @@
     <t>iShares Russell 1000 Value ETF</t>
   </si>
   <si>
-    <t>Long Value / Short Growth Stocks</t>
-  </si>
-  <si>
     <t>ETFs</t>
   </si>
   <si>
@@ -243,9 +228,6 @@
     <t>VXM</t>
   </si>
   <si>
-    <t>Vix Futures Mini</t>
-  </si>
-  <si>
     <t>VXMU6</t>
   </si>
   <si>
@@ -300,15 +282,9 @@
     <t>iShares 20+ Year Treasury Bond ETF</t>
   </si>
   <si>
-    <t>Long Bonds(Long End) / Short Equities</t>
-  </si>
-  <si>
     <t>MES</t>
   </si>
   <si>
-    <t>Micro S&amp;P Futures</t>
-  </si>
-  <si>
     <t>SB</t>
   </si>
   <si>
@@ -1932,9 +1908,6 @@
     <t>iShares Russell 2000 ETF</t>
   </si>
   <si>
-    <t>Long Small Cap vs Broad Mkt</t>
-  </si>
-  <si>
     <t>SPY</t>
   </si>
   <si>
@@ -1956,9 +1929,6 @@
     <t>6EZ6</t>
   </si>
   <si>
-    <t>Long Gold vs Short Copper</t>
-  </si>
-  <si>
     <t>MHG</t>
   </si>
   <si>
@@ -1990,6 +1960,348 @@
   </si>
   <si>
     <t>Ralph Lauren</t>
+  </si>
+  <si>
+    <t>Vix Futures</t>
+  </si>
+  <si>
+    <t>S&amp;P Futures</t>
+  </si>
+  <si>
+    <t>Theme</t>
+  </si>
+  <si>
+    <t>RL (-)</t>
+  </si>
+  <si>
+    <t>BKE (-)</t>
+  </si>
+  <si>
+    <t>TRUP (-)</t>
+  </si>
+  <si>
+    <t>UEC (+)</t>
+  </si>
+  <si>
+    <t>Gold (+) Copper (-)</t>
+  </si>
+  <si>
+    <t>Euro (+)</t>
+  </si>
+  <si>
+    <t>Vix (+)</t>
+  </si>
+  <si>
+    <t>JPM (+)</t>
+  </si>
+  <si>
+    <t>TMO (-)</t>
+  </si>
+  <si>
+    <t>WAT (-)</t>
+  </si>
+  <si>
+    <t>IWM (+) SPY(-)</t>
+  </si>
+  <si>
+    <t>ACAD (+)</t>
+  </si>
+  <si>
+    <t>TSM (-)</t>
+  </si>
+  <si>
+    <t>LCII (+)</t>
+  </si>
+  <si>
+    <t>DDOG (-)</t>
+  </si>
+  <si>
+    <t>Natgas (-)</t>
+  </si>
+  <si>
+    <t>CRWD (-)</t>
+  </si>
+  <si>
+    <t>MDU (+)</t>
+  </si>
+  <si>
+    <t>S&amp;P500 (-)</t>
+  </si>
+  <si>
+    <t>NSC (+)</t>
+  </si>
+  <si>
+    <t>DAC (-)</t>
+  </si>
+  <si>
+    <t>HD (+)</t>
+  </si>
+  <si>
+    <t>DECK (+)</t>
+  </si>
+  <si>
+    <t>HGV (+)</t>
+  </si>
+  <si>
+    <t>TAN (+)</t>
+  </si>
+  <si>
+    <t>Bund (+)</t>
+  </si>
+  <si>
+    <t>AFL (+)</t>
+  </si>
+  <si>
+    <t>META (-)</t>
+  </si>
+  <si>
+    <t>Dow (+)</t>
+  </si>
+  <si>
+    <t>SHW (+)</t>
+  </si>
+  <si>
+    <t>TRIP (+)</t>
+  </si>
+  <si>
+    <t>VZ (-)</t>
+  </si>
+  <si>
+    <t>PH (+)</t>
+  </si>
+  <si>
+    <t>ITW (+)</t>
+  </si>
+  <si>
+    <t>SLB (-)</t>
+  </si>
+  <si>
+    <t>NEM (-)</t>
+  </si>
+  <si>
+    <t>Gold (-)</t>
+  </si>
+  <si>
+    <t>CAD (-)</t>
+  </si>
+  <si>
+    <t>Euro (-)</t>
+  </si>
+  <si>
+    <t>Sugar (-)</t>
+  </si>
+  <si>
+    <t>Industrials (+)</t>
+  </si>
+  <si>
+    <t>EFA (+)</t>
+  </si>
+  <si>
+    <t>AAPL (-)</t>
+  </si>
+  <si>
+    <t>SPCX (+)</t>
+  </si>
+  <si>
+    <t>LLY (-)</t>
+  </si>
+  <si>
+    <t>Coffee (-)</t>
+  </si>
+  <si>
+    <t>META (+)</t>
+  </si>
+  <si>
+    <t>KRE (-)</t>
+  </si>
+  <si>
+    <t>Silver (+) Gold (-)</t>
+  </si>
+  <si>
+    <t>CHF (+)</t>
+  </si>
+  <si>
+    <t>Cocoa (-)</t>
+  </si>
+  <si>
+    <t>JPM (-)</t>
+  </si>
+  <si>
+    <t>MU (-)</t>
+  </si>
+  <si>
+    <t>identifier</t>
+  </si>
+  <si>
+    <t>mu</t>
+  </si>
+  <si>
+    <t>jpm</t>
+  </si>
+  <si>
+    <t>silver</t>
+  </si>
+  <si>
+    <t>eur</t>
+  </si>
+  <si>
+    <t>cocoa</t>
+  </si>
+  <si>
+    <t>chf</t>
+  </si>
+  <si>
+    <t>iwd</t>
+  </si>
+  <si>
+    <t>iwf</t>
+  </si>
+  <si>
+    <t>gold</t>
+  </si>
+  <si>
+    <t>kre</t>
+  </si>
+  <si>
+    <t>meta</t>
+  </si>
+  <si>
+    <t>vix</t>
+  </si>
+  <si>
+    <t>coffee</t>
+  </si>
+  <si>
+    <t>lly</t>
+  </si>
+  <si>
+    <t>spcx</t>
+  </si>
+  <si>
+    <t>aapl</t>
+  </si>
+  <si>
+    <t>efa</t>
+  </si>
+  <si>
+    <t>xai</t>
+  </si>
+  <si>
+    <t>tlt</t>
+  </si>
+  <si>
+    <t>es</t>
+  </si>
+  <si>
+    <t>sugar</t>
+  </si>
+  <si>
+    <t>cad</t>
+  </si>
+  <si>
+    <t>nem</t>
+  </si>
+  <si>
+    <t>slb</t>
+  </si>
+  <si>
+    <t>itw</t>
+  </si>
+  <si>
+    <t>ph</t>
+  </si>
+  <si>
+    <t>shw</t>
+  </si>
+  <si>
+    <t>vz</t>
+  </si>
+  <si>
+    <t>trip</t>
+  </si>
+  <si>
+    <t>dow</t>
+  </si>
+  <si>
+    <t>afl</t>
+  </si>
+  <si>
+    <t>bund</t>
+  </si>
+  <si>
+    <t>tan</t>
+  </si>
+  <si>
+    <t>hgv</t>
+  </si>
+  <si>
+    <t>deck</t>
+  </si>
+  <si>
+    <t>hd</t>
+  </si>
+  <si>
+    <t>dac</t>
+  </si>
+  <si>
+    <t>nsc</t>
+  </si>
+  <si>
+    <t>mdu</t>
+  </si>
+  <si>
+    <t>crwd</t>
+  </si>
+  <si>
+    <t>natgas</t>
+  </si>
+  <si>
+    <t>ddog</t>
+  </si>
+  <si>
+    <t>lcii</t>
+  </si>
+  <si>
+    <t>tsm</t>
+  </si>
+  <si>
+    <t>acad</t>
+  </si>
+  <si>
+    <t>iwm</t>
+  </si>
+  <si>
+    <t>spy</t>
+  </si>
+  <si>
+    <t>wat</t>
+  </si>
+  <si>
+    <t>tmo</t>
+  </si>
+  <si>
+    <t>copper</t>
+  </si>
+  <si>
+    <t>uec</t>
+  </si>
+  <si>
+    <t>trup</t>
+  </si>
+  <si>
+    <t>bke</t>
+  </si>
+  <si>
+    <t>rl</t>
+  </si>
+  <si>
+    <t>CHF</t>
+  </si>
+  <si>
+    <t>Value-IWD (+) Growth-IWF (-)</t>
+  </si>
+  <si>
+    <t>Bonds-TLT (+) Equities-ES (-)</t>
   </si>
 </sst>
 </file>
@@ -2618,32 +2930,33 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:X79"/>
+  <dimension ref="A1:Y79"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5" style="33" bestFit="1" customWidth="1"/>
     <col min="2" max="3" width="14" style="50" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5" style="46" customWidth="1"/>
     <col min="5" max="5" width="9" style="33" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="57.6640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.33203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="43.1640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="13" style="33" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="10.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.1640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="11.83203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="7.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="10.1640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="18.1640625" style="33" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="10" style="33" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="13" style="33" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.83203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="6" style="33" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.1640625" style="33"/>
+    <col min="6" max="6" width="11.1640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="57.6640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="13.33203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="43.1640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="13" style="33" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.33203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="10.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="13.1640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="11.83203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="7.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="10.1640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="18.1640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="10" style="33" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="13" style="33" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.83203125" style="33" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="6" style="33" bestFit="1" customWidth="1"/>
+    <col min="25" max="16384" width="9.1640625" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
@@ -2660,58 +2973,61 @@
         <v>4</v>
       </c>
       <c r="F1" s="30" t="s">
+        <v>688</v>
+      </c>
+      <c r="G1" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="30" t="s">
+      <c r="H1" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="30" t="s">
+      <c r="I1" s="30" t="s">
+        <v>634</v>
+      </c>
+      <c r="J1" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="30" t="s">
+      <c r="K1" s="30" t="s">
+        <v>7</v>
+      </c>
+      <c r="L1" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="30" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" s="30" t="s">
+      <c r="M1" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="L1" s="30" t="s">
+      <c r="N1" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="M1" s="30" t="s">
+      <c r="O1" s="30" t="s">
         <v>11</v>
       </c>
-      <c r="N1" s="30" t="s">
+      <c r="P1" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="O1" s="30" t="s">
+      <c r="Q1" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="P1" s="30" t="s">
+      <c r="R1" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="Q1" s="30" t="s">
+      <c r="S1" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="R1" s="30" t="s">
+      <c r="T1" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="S1" s="30" t="s">
+      <c r="U1" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="T1" s="30" t="s">
+      <c r="V1" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="U1" s="30" t="s">
+      <c r="W1" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="V1" s="30" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" s="33">
         <v>1</v>
       </c>
@@ -2726,60 +3042,63 @@
         <v>6</v>
       </c>
       <c r="E2" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F2" s="33" t="s">
+        <v>689</v>
+      </c>
+      <c r="G2" s="36" t="s">
         <v>21</v>
       </c>
-      <c r="F2" s="36" t="s">
+      <c r="H2" s="37" t="s">
         <v>22</v>
       </c>
-      <c r="G2" s="37" t="s">
+      <c r="I2" s="38" t="s">
+        <v>687</v>
+      </c>
+      <c r="J2" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="H2" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="J2" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="K2" s="33" t="s">
-        <v>21</v>
-      </c>
-      <c r="L2" s="33">
+      <c r="K2" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="M2" s="33">
         <v>-100</v>
       </c>
-      <c r="M2" s="33">
+      <c r="N2" s="33">
         <v>1057.1199999999999</v>
       </c>
-      <c r="N2" s="33">
+      <c r="O2" s="33">
         <v>941.37</v>
       </c>
-      <c r="O2" s="33">
-        <f t="shared" ref="O2:O11" si="1">N2</f>
+      <c r="P2" s="33">
+        <f t="shared" ref="P2:P11" si="1">O2</f>
         <v>941.37</v>
       </c>
-      <c r="P2" s="39">
+      <c r="Q2" s="39">
         <v>105712</v>
       </c>
-      <c r="Q2" s="33">
+      <c r="R2" s="33">
         <v>2.94</v>
       </c>
-      <c r="R2" s="33">
+      <c r="S2" s="33">
         <v>1</v>
       </c>
-      <c r="S2" s="40">
-        <f t="shared" ref="S2:S12" si="2">IF(R2=1, ABS(N2-M2)/M2, 0)</f>
+      <c r="T2" s="40">
+        <f t="shared" ref="T2:T12" si="2">IF(S2=1, ABS(O2-N2)/N2, 0)</f>
         <v>0.10949561071590727</v>
       </c>
-      <c r="T2" s="39">
+      <c r="U2" s="39">
         <v>11575</v>
       </c>
-      <c r="U2" s="41">
+      <c r="V2" s="41">
         <v>11575</v>
       </c>
     </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" s="37">
         <v>2</v>
       </c>
@@ -2794,60 +3113,63 @@
         <v>8</v>
       </c>
       <c r="E3" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="F3" s="38" t="s">
-        <v>27</v>
-      </c>
-      <c r="G3" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="F3" s="37" t="s">
+        <v>690</v>
+      </c>
+      <c r="G3" s="38" t="s">
+        <v>25</v>
+      </c>
+      <c r="H3" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" s="38" t="s">
+        <v>686</v>
+      </c>
+      <c r="J3" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="H3" s="38" t="s">
+      <c r="K3" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L3" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="I3" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="J3" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="L3" s="37">
+      <c r="M3" s="37">
         <v>-450</v>
       </c>
-      <c r="M3" s="37">
+      <c r="N3" s="37">
         <v>308.14999999999998</v>
       </c>
-      <c r="N3" s="37">
+      <c r="O3" s="37">
         <v>317.27260000000001</v>
       </c>
-      <c r="O3" s="33">
+      <c r="P3" s="33">
         <f t="shared" si="1"/>
         <v>317.27260000000001</v>
       </c>
-      <c r="P3" s="42">
+      <c r="Q3" s="42">
         <v>138667.5</v>
       </c>
-      <c r="Q3" s="37">
+      <c r="R3" s="37">
         <v>-7.92</v>
       </c>
-      <c r="R3" s="37">
-        <v>0</v>
-      </c>
-      <c r="S3" s="40">
+      <c r="S3" s="37">
+        <v>0</v>
+      </c>
+      <c r="T3" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T3" s="42">
+      <c r="U3" s="42">
         <v>-4105.18</v>
       </c>
-      <c r="U3" s="43">
+      <c r="V3" s="43">
         <v>-4105.18</v>
       </c>
     </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" s="33">
         <v>3</v>
       </c>
@@ -2861,60 +3183,63 @@
         <v>20</v>
       </c>
       <c r="E4" s="33" t="s">
+        <v>26</v>
+      </c>
+      <c r="F4" s="33" t="s">
+        <v>691</v>
+      </c>
+      <c r="G4" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="H4" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="F4" s="36" t="s">
+      <c r="I4" s="36" t="s">
+        <v>683</v>
+      </c>
+      <c r="J4" s="33" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="33" t="s">
+      <c r="K4" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="L4" s="33" t="s">
         <v>30</v>
       </c>
-      <c r="H4" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="I4" s="33" t="s">
-        <v>32</v>
-      </c>
-      <c r="J4" s="33" t="s">
-        <v>122</v>
-      </c>
-      <c r="K4" s="33" t="s">
-        <v>33</v>
-      </c>
-      <c r="L4" s="33">
+      <c r="M4" s="33">
         <v>2</v>
       </c>
-      <c r="M4" s="33">
+      <c r="N4" s="33">
         <v>66.334999999999994</v>
       </c>
-      <c r="N4" s="33">
+      <c r="O4" s="33">
         <v>63</v>
       </c>
-      <c r="O4" s="33">
+      <c r="P4" s="33">
         <f t="shared" si="1"/>
         <v>63</v>
       </c>
-      <c r="P4" s="39">
+      <c r="Q4" s="39">
         <v>663350</v>
       </c>
-      <c r="Q4" s="33">
+      <c r="R4" s="33">
         <v>10.08</v>
       </c>
-      <c r="R4" s="33">
+      <c r="S4" s="33">
         <v>1</v>
       </c>
-      <c r="S4" s="40">
+      <c r="T4" s="40">
         <f t="shared" si="2"/>
         <v>5.0275118715610072E-2</v>
       </c>
-      <c r="T4" s="39">
+      <c r="U4" s="39">
         <v>-33350</v>
       </c>
-      <c r="U4" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V4" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" s="33">
         <v>4</v>
       </c>
@@ -2929,60 +3254,63 @@
         <v>1</v>
       </c>
       <c r="E5" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="F5" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="G5" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="H5" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="I5" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>692</v>
+      </c>
+      <c r="G5" s="36" t="s">
         <v>32</v>
       </c>
+      <c r="H5" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="I5" s="38" t="s">
+        <v>640</v>
+      </c>
       <c r="J5" s="33" t="s">
-        <v>529</v>
+        <v>29</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="L5" s="33">
-        <v>10</v>
+        <v>521</v>
+      </c>
+      <c r="L5" s="33" t="s">
+        <v>31</v>
       </c>
       <c r="M5" s="33">
+        <v>20</v>
+      </c>
+      <c r="N5" s="33">
         <v>1.1535</v>
       </c>
-      <c r="N5" s="33">
+      <c r="O5" s="33">
         <v>1.1579600000000001</v>
       </c>
-      <c r="O5" s="33">
+      <c r="P5" s="33">
         <f t="shared" si="1"/>
         <v>1.1579600000000001</v>
       </c>
-      <c r="P5" s="39">
+      <c r="Q5" s="39">
         <v>2894900</v>
       </c>
-      <c r="Q5" s="33">
+      <c r="R5" s="33">
         <v>-98.8</v>
       </c>
-      <c r="R5" s="33">
+      <c r="S5" s="33">
         <v>1</v>
       </c>
-      <c r="S5" s="40">
+      <c r="T5" s="40">
         <f t="shared" si="2"/>
         <v>3.8664932813178418E-3</v>
       </c>
-      <c r="T5" s="39">
+      <c r="U5" s="39">
         <v>11150</v>
       </c>
-      <c r="U5" s="41">
+      <c r="V5" s="41">
         <v>11150</v>
       </c>
     </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" s="33">
         <v>3</v>
       </c>
@@ -2996,60 +3324,63 @@
         <v>0</v>
       </c>
       <c r="E6" s="33" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="36" t="s">
-        <v>37</v>
-      </c>
-      <c r="G6" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="H6" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="I6" s="33" t="s">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="F6" s="33" t="s">
+        <v>691</v>
+      </c>
+      <c r="G6" s="36" t="s">
+        <v>34</v>
+      </c>
+      <c r="H6" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="I6" s="36" t="s">
+        <v>683</v>
       </c>
       <c r="J6" s="33" t="s">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>38</v>
-      </c>
-      <c r="L6" s="33">
+        <v>114</v>
+      </c>
+      <c r="L6" s="33" t="s">
+        <v>35</v>
+      </c>
+      <c r="M6" s="33">
         <v>3</v>
       </c>
-      <c r="M6" s="33">
+      <c r="N6" s="33">
         <v>61.529200000000003</v>
       </c>
-      <c r="N6" s="33">
+      <c r="O6" s="33">
         <v>66.92</v>
       </c>
-      <c r="O6" s="33">
+      <c r="P6" s="33">
         <f t="shared" si="1"/>
         <v>66.92</v>
       </c>
-      <c r="P6" s="39">
+      <c r="Q6" s="39">
         <v>461468.75</v>
       </c>
-      <c r="Q6" s="33">
+      <c r="R6" s="33">
         <v>14.22</v>
       </c>
-      <c r="R6" s="33">
+      <c r="S6" s="33">
         <v>1</v>
       </c>
-      <c r="S6" s="40">
+      <c r="T6" s="40">
         <f t="shared" si="2"/>
         <v>8.761368585972186E-2</v>
       </c>
-      <c r="T6" s="39">
+      <c r="U6" s="39">
         <v>40406.25</v>
       </c>
-      <c r="U6" s="41">
+      <c r="V6" s="41">
         <v>6343</v>
       </c>
     </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" s="33">
         <v>5</v>
       </c>
@@ -3064,60 +3395,63 @@
         <v>5</v>
       </c>
       <c r="E7" s="33" t="s">
-        <v>39</v>
-      </c>
-      <c r="F7" s="36" t="s">
-        <v>40</v>
-      </c>
-      <c r="G7" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="H7" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="I7" s="33" t="s">
-        <v>32</v>
+        <v>36</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>693</v>
+      </c>
+      <c r="G7" s="36" t="s">
+        <v>37</v>
+      </c>
+      <c r="H7" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="I7" s="38" t="s">
+        <v>685</v>
       </c>
       <c r="J7" s="33" t="s">
-        <v>530</v>
+        <v>29</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>41</v>
-      </c>
-      <c r="L7" s="33">
+        <v>522</v>
+      </c>
+      <c r="L7" s="33" t="s">
+        <v>38</v>
+      </c>
+      <c r="M7" s="33">
         <v>-3</v>
       </c>
-      <c r="M7" s="33">
+      <c r="N7" s="33">
         <v>4374.66</v>
       </c>
-      <c r="N7" s="33">
+      <c r="O7" s="33">
         <v>4575</v>
       </c>
-      <c r="O7" s="33">
+      <c r="P7" s="33">
         <f t="shared" si="1"/>
         <v>4575</v>
       </c>
-      <c r="P7" s="39">
+      <c r="Q7" s="39">
         <v>131240</v>
       </c>
-      <c r="Q7" s="33">
+      <c r="R7" s="33">
         <v>17.82</v>
       </c>
-      <c r="R7" s="33">
-        <v>0</v>
-      </c>
-      <c r="S7" s="40">
+      <c r="S7" s="33">
+        <v>0</v>
+      </c>
+      <c r="T7" s="40">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="T7" s="39">
+      <c r="U7" s="39">
         <v>-6010</v>
       </c>
-      <c r="U7" s="43">
+      <c r="V7" s="43">
         <v>-6010</v>
       </c>
     </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" s="33">
         <v>6</v>
       </c>
@@ -3132,60 +3466,63 @@
         <v>11</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>42</v>
-      </c>
-      <c r="F8" s="36" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="I8" s="33" t="s">
-        <v>32</v>
+        <v>743</v>
+      </c>
+      <c r="F8" s="33" t="s">
+        <v>694</v>
+      </c>
+      <c r="G8" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="H8" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="I8" s="38" t="s">
+        <v>684</v>
       </c>
       <c r="J8" s="33" t="s">
-        <v>529</v>
+        <v>29</v>
       </c>
       <c r="K8" s="33" t="s">
-        <v>44</v>
-      </c>
-      <c r="L8" s="33">
+        <v>521</v>
+      </c>
+      <c r="L8" s="33" t="s">
+        <v>40</v>
+      </c>
+      <c r="M8" s="33">
         <v>20</v>
       </c>
-      <c r="M8" s="33">
+      <c r="N8" s="33">
         <v>1.2499125</v>
       </c>
-      <c r="N8" s="33">
+      <c r="O8" s="33">
         <v>1.2517849999999999</v>
       </c>
-      <c r="O8" s="33">
+      <c r="P8" s="33">
         <f t="shared" si="1"/>
         <v>1.2517849999999999</v>
       </c>
-      <c r="P8" s="39">
+      <c r="Q8" s="39">
         <v>3124781</v>
       </c>
-      <c r="Q8" s="33">
+      <c r="R8" s="33">
         <v>98.8</v>
       </c>
-      <c r="R8" s="33">
+      <c r="S8" s="33">
         <v>1</v>
       </c>
-      <c r="S8" s="40">
+      <c r="T8" s="40">
         <f t="shared" si="2"/>
         <v>1.4981048673406688E-3</v>
       </c>
-      <c r="T8" s="39">
+      <c r="U8" s="39">
         <v>4681.25</v>
       </c>
-      <c r="U8" s="41">
+      <c r="V8" s="41">
         <v>4681.25</v>
       </c>
     </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>7</v>
       </c>
@@ -3200,60 +3537,63 @@
         <v>6</v>
       </c>
       <c r="E9" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F9" s="38" t="s">
-        <v>46</v>
-      </c>
-      <c r="G9" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="H9" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="I9" s="37" t="s">
-        <v>48</v>
+        <v>41</v>
+      </c>
+      <c r="F9" s="37" t="s">
+        <v>695</v>
+      </c>
+      <c r="G9" s="38" t="s">
+        <v>42</v>
+      </c>
+      <c r="H9" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="I9" s="38" t="s">
+        <v>744</v>
       </c>
       <c r="J9" s="37" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K9" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="L9" s="37">
-        <v>400</v>
+        <v>43</v>
+      </c>
+      <c r="L9" s="37" t="s">
+        <v>41</v>
       </c>
       <c r="M9" s="37">
+        <v>-400</v>
+      </c>
+      <c r="N9" s="37">
         <v>241.2475</v>
       </c>
-      <c r="N9" s="37">
+      <c r="O9" s="37">
         <v>242.61</v>
       </c>
-      <c r="O9" s="33">
+      <c r="P9" s="33">
         <f t="shared" si="1"/>
         <v>242.61</v>
       </c>
-      <c r="P9" s="42">
+      <c r="Q9" s="42">
         <v>96499</v>
       </c>
-      <c r="Q9" s="37">
+      <c r="R9" s="37">
         <v>7.43</v>
       </c>
-      <c r="R9" s="37">
+      <c r="S9" s="37">
         <v>1</v>
       </c>
-      <c r="S9" s="40">
+      <c r="T9" s="40">
         <f t="shared" si="2"/>
         <v>5.6477269194499897E-3</v>
       </c>
-      <c r="T9" s="42">
+      <c r="U9" s="42">
         <v>-545</v>
       </c>
-      <c r="U9" s="44">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V9" s="44">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" s="37">
         <v>7</v>
       </c>
@@ -3267,60 +3607,63 @@
         <v>0</v>
       </c>
       <c r="E10" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="F10" s="38" t="s">
-        <v>50</v>
-      </c>
-      <c r="G10" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="H10" s="38" t="s">
-        <v>47</v>
-      </c>
-      <c r="I10" s="37" t="s">
-        <v>48</v>
+        <v>44</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>696</v>
+      </c>
+      <c r="G10" s="38" t="s">
+        <v>45</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="I10" s="38" t="s">
+        <v>744</v>
       </c>
       <c r="J10" s="37" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K10" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="L10" s="37">
+        <v>43</v>
+      </c>
+      <c r="L10" s="37" t="s">
+        <v>44</v>
+      </c>
+      <c r="M10" s="37">
         <v>800</v>
       </c>
-      <c r="M10" s="37">
+      <c r="N10" s="37">
         <v>120.746</v>
       </c>
-      <c r="N10" s="37">
+      <c r="O10" s="37">
         <v>124.35</v>
       </c>
-      <c r="O10" s="33">
+      <c r="P10" s="33">
         <f t="shared" si="1"/>
         <v>124.35</v>
       </c>
-      <c r="P10" s="42">
+      <c r="Q10" s="42">
         <v>96596.800000000003</v>
       </c>
-      <c r="Q10" s="37">
+      <c r="R10" s="37">
         <v>12.93</v>
       </c>
-      <c r="R10" s="37">
+      <c r="S10" s="37">
         <v>1</v>
       </c>
-      <c r="S10" s="40">
+      <c r="T10" s="40">
         <f t="shared" si="2"/>
         <v>2.9847779636592513E-2</v>
       </c>
-      <c r="T10" s="42">
+      <c r="U10" s="42">
         <v>2883.2</v>
       </c>
-      <c r="U10" s="44">
+      <c r="V10" s="44">
         <v>2338.1999999999998</v>
       </c>
     </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
         <v>3</v>
       </c>
@@ -3334,60 +3677,63 @@
         <v>0</v>
       </c>
       <c r="E11" s="33" t="s">
-        <v>51</v>
-      </c>
-      <c r="F11" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="G11" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="H11" s="36" t="s">
-        <v>31</v>
-      </c>
-      <c r="I11" s="33" t="s">
-        <v>32</v>
+        <v>46</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>697</v>
+      </c>
+      <c r="G11" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="H11" s="37" t="s">
+        <v>28</v>
+      </c>
+      <c r="I11" s="36" t="s">
+        <v>683</v>
       </c>
       <c r="J11" s="33" t="s">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="K11" s="33" t="s">
-        <v>53</v>
-      </c>
-      <c r="L11" s="33">
-        <v>-1</v>
+        <v>114</v>
+      </c>
+      <c r="L11" s="33" t="s">
+        <v>48</v>
       </c>
       <c r="M11" s="33">
+        <v>1</v>
+      </c>
+      <c r="N11" s="33">
         <v>4042.5</v>
       </c>
-      <c r="N11" s="33">
+      <c r="O11" s="33">
         <v>4028.25</v>
       </c>
-      <c r="O11" s="33">
+      <c r="P11" s="33">
         <f t="shared" si="1"/>
         <v>4028.25</v>
       </c>
-      <c r="P11" s="39">
+      <c r="Q11" s="39">
         <v>202125</v>
       </c>
-      <c r="Q11" s="33">
+      <c r="R11" s="33">
         <v>4.74</v>
       </c>
-      <c r="R11" s="33">
+      <c r="S11" s="33">
         <v>1</v>
       </c>
-      <c r="S11" s="40">
+      <c r="T11" s="40">
         <f t="shared" si="2"/>
         <v>3.5250463821892395E-3</v>
       </c>
-      <c r="T11" s="39">
+      <c r="U11" s="39">
         <v>-712.5</v>
       </c>
-      <c r="U11" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="V11" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>8</v>
       </c>
@@ -3402,59 +3748,62 @@
         <v>64</v>
       </c>
       <c r="E12" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="F12" s="38" t="s">
-        <v>55</v>
-      </c>
-      <c r="G12" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="H12" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="I12" s="37" t="s">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="F12" s="37" t="s">
+        <v>698</v>
+      </c>
+      <c r="G12" s="38" t="s">
+        <v>50</v>
+      </c>
+      <c r="H12" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="I12" s="38" t="s">
+        <v>682</v>
       </c>
       <c r="J12" s="37" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K12" s="37" t="s">
-        <v>54</v>
-      </c>
-      <c r="L12" s="37">
+        <v>43</v>
+      </c>
+      <c r="L12" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="M12" s="37">
         <v>-3000</v>
       </c>
-      <c r="M12" s="37">
+      <c r="N12" s="37">
         <v>74.614400000000003</v>
-      </c>
-      <c r="N12" s="37">
-        <v>73.084999999999994</v>
       </c>
       <c r="O12" s="37">
         <v>73.084999999999994</v>
       </c>
-      <c r="P12" s="42">
+      <c r="P12" s="37">
+        <v>73.084999999999994</v>
+      </c>
+      <c r="Q12" s="42">
         <v>223843.28</v>
       </c>
-      <c r="Q12" s="37">
+      <c r="R12" s="37">
         <v>44.49</v>
       </c>
-      <c r="R12" s="37">
+      <c r="S12" s="37">
         <v>1</v>
       </c>
-      <c r="S12" s="40">
+      <c r="T12" s="40">
         <f t="shared" si="2"/>
         <v>2.0497383883003945E-2</v>
       </c>
-      <c r="T12" s="42">
+      <c r="U12" s="42">
         <v>4588</v>
       </c>
-      <c r="U12" s="41">
+      <c r="V12" s="41">
         <v>4588</v>
       </c>
     </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A13" s="37">
         <v>9</v>
       </c>
@@ -3469,60 +3818,63 @@
         <v>2</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="F13" s="38" t="s">
-        <v>57</v>
-      </c>
-      <c r="G13" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="F13" s="37" t="s">
+        <v>699</v>
+      </c>
+      <c r="G13" s="38" t="s">
+        <v>52</v>
+      </c>
+      <c r="H13" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="I13" s="38" t="s">
+        <v>681</v>
+      </c>
+      <c r="J13" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="H13" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="I13" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="J13" s="37" t="s">
-        <v>25</v>
-      </c>
       <c r="K13" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="L13" s="37">
+        <v>23</v>
+      </c>
+      <c r="L13" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="M13" s="37">
         <v>100</v>
       </c>
-      <c r="M13" s="37">
+      <c r="N13" s="37">
         <v>550.35</v>
       </c>
-      <c r="N13" s="37">
+      <c r="O13" s="37">
         <v>597.52</v>
       </c>
-      <c r="O13" s="33">
-        <f>N13</f>
+      <c r="P13" s="33">
+        <f>O13</f>
         <v>597.52</v>
       </c>
-      <c r="P13" s="42">
+      <c r="Q13" s="42">
         <v>55035</v>
       </c>
-      <c r="Q13" s="37">
+      <c r="R13" s="37">
         <v>2.29</v>
       </c>
-      <c r="R13" s="37">
+      <c r="S13" s="37">
         <v>1</v>
       </c>
-      <c r="S13" s="40">
-        <f t="shared" ref="S13:S19" si="3">IF(R13=1, ABS(N13-M13)/M13, 0)</f>
+      <c r="T13" s="40">
+        <f t="shared" ref="T13:T19" si="3">IF(S13=1, ABS(O13-N13)/N13, 0)</f>
         <v>8.5709094212773618E-2</v>
       </c>
-      <c r="T13" s="42">
+      <c r="U13" s="42">
         <v>4717</v>
       </c>
-      <c r="U13" s="44">
+      <c r="V13" s="44">
         <v>4717</v>
       </c>
     </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A14" s="33">
         <v>10</v>
       </c>
@@ -3537,59 +3889,62 @@
         <v>52</v>
       </c>
       <c r="E14" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="F14" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="G14" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H14" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="I14" s="37" t="s">
-        <v>32</v>
+        <v>53</v>
+      </c>
+      <c r="F14" s="33" t="s">
+        <v>700</v>
+      </c>
+      <c r="G14" s="36" t="s">
+        <v>632</v>
+      </c>
+      <c r="H14" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I14" s="38" t="s">
+        <v>641</v>
       </c>
       <c r="J14" s="37" t="s">
-        <v>531</v>
-      </c>
-      <c r="K14" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="37" t="s">
+        <v>523</v>
+      </c>
+      <c r="L14" s="33" t="s">
+        <v>54</v>
+      </c>
+      <c r="M14" s="33">
         <v>60</v>
       </c>
-      <c r="L14" s="33">
-        <v>60</v>
-      </c>
-      <c r="M14" s="33">
+      <c r="N14" s="33">
         <v>20.177299999999999</v>
-      </c>
-      <c r="N14" s="33">
-        <v>17.451599999999999</v>
       </c>
       <c r="O14" s="33">
         <v>17.451599999999999</v>
       </c>
-      <c r="P14" s="39">
+      <c r="P14" s="33">
+        <v>17.451599999999999</v>
+      </c>
+      <c r="Q14" s="39">
         <v>121064</v>
       </c>
-      <c r="Q14" s="33">
+      <c r="R14" s="33">
         <v>55.5</v>
       </c>
-      <c r="R14" s="33">
-        <v>0</v>
-      </c>
-      <c r="S14" s="40">
+      <c r="S14" s="33">
+        <v>0</v>
+      </c>
+      <c r="T14" s="40">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="T14" s="39">
+      <c r="U14" s="39">
         <v>-16354</v>
       </c>
-      <c r="U14" s="45">
+      <c r="V14" s="45">
         <v>-16354</v>
       </c>
     </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A15" s="33">
         <v>11</v>
       </c>
@@ -3604,60 +3959,63 @@
         <v>0</v>
       </c>
       <c r="E15" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="F15" s="36" t="s">
-        <v>62</v>
-      </c>
-      <c r="G15" s="37" t="s">
-        <v>23</v>
-      </c>
-      <c r="H15" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="I15" s="37" t="s">
-        <v>32</v>
+        <v>55</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>701</v>
+      </c>
+      <c r="G15" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="H15" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="I15" s="38" t="s">
+        <v>680</v>
       </c>
       <c r="J15" s="37" t="s">
-        <v>530</v>
-      </c>
-      <c r="K15" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="L15" s="33">
+        <v>29</v>
+      </c>
+      <c r="K15" s="37" t="s">
+        <v>522</v>
+      </c>
+      <c r="L15" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="M15" s="33">
         <v>-1</v>
       </c>
-      <c r="M15" s="33">
+      <c r="N15" s="33">
         <v>3.0939999999999999</v>
       </c>
-      <c r="N15" s="33">
+      <c r="O15" s="33">
         <v>3.0255000000000001</v>
       </c>
-      <c r="O15" s="33">
-        <f>N15</f>
+      <c r="P15" s="33">
+        <f>O15</f>
         <v>3.0255000000000001</v>
       </c>
-      <c r="P15" s="39">
+      <c r="Q15" s="39">
         <v>116025</v>
       </c>
-      <c r="Q15" s="33">
+      <c r="R15" s="33">
         <v>5.94</v>
       </c>
-      <c r="R15" s="33">
+      <c r="S15" s="33">
         <v>1</v>
       </c>
-      <c r="S15" s="40">
+      <c r="T15" s="40">
         <f t="shared" si="3"/>
         <v>2.2139625080801483E-2</v>
       </c>
-      <c r="T15" s="39">
+      <c r="U15" s="39">
         <v>2568.75</v>
       </c>
-      <c r="U15" s="41">
+      <c r="V15" s="41">
         <v>2568.75</v>
       </c>
     </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>12</v>
       </c>
@@ -3672,60 +4030,63 @@
         <v>6</v>
       </c>
       <c r="E16" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="F16" s="38" t="s">
-        <v>65</v>
-      </c>
-      <c r="G16" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="F16" s="37" t="s">
+        <v>702</v>
+      </c>
+      <c r="G16" s="38" t="s">
+        <v>59</v>
+      </c>
+      <c r="H16" s="37" t="s">
+        <v>22</v>
+      </c>
+      <c r="I16" s="38" t="s">
+        <v>679</v>
+      </c>
+      <c r="J16" s="37" t="s">
         <v>23</v>
       </c>
-      <c r="H16" s="38" t="s">
-        <v>24</v>
-      </c>
-      <c r="I16" s="37" t="s">
-        <v>25</v>
-      </c>
-      <c r="J16" s="37" t="s">
-        <v>25</v>
-      </c>
       <c r="K16" s="37" t="s">
-        <v>64</v>
-      </c>
-      <c r="L16" s="37">
+        <v>23</v>
+      </c>
+      <c r="L16" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="M16" s="37">
         <v>-75</v>
       </c>
-      <c r="M16" s="37">
+      <c r="N16" s="37">
         <v>1210.816</v>
       </c>
-      <c r="N16" s="37">
+      <c r="O16" s="37">
         <v>1155.49</v>
       </c>
-      <c r="O16" s="33">
-        <f>N16</f>
+      <c r="P16" s="33">
+        <f>O16</f>
         <v>1155.49</v>
       </c>
-      <c r="P16" s="42">
+      <c r="Q16" s="42">
         <v>90811.199999999997</v>
       </c>
-      <c r="Q16" s="37">
+      <c r="R16" s="37">
         <v>2.9</v>
       </c>
-      <c r="R16" s="37">
+      <c r="S16" s="37">
         <v>1</v>
       </c>
-      <c r="S16" s="40">
+      <c r="T16" s="40">
         <f t="shared" si="3"/>
         <v>4.5693152386489792E-2</v>
       </c>
-      <c r="T16" s="42">
+      <c r="U16" s="42">
         <v>4149.45</v>
       </c>
-      <c r="U16" s="44">
+      <c r="V16" s="44">
         <v>4149.45</v>
       </c>
     </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A17" s="33">
         <v>13</v>
       </c>
@@ -3740,60 +4101,63 @@
         <v>3</v>
       </c>
       <c r="E17" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="F17" s="36" t="s">
-        <v>67</v>
-      </c>
-      <c r="G17" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>703</v>
+      </c>
+      <c r="G17" s="36" t="s">
+        <v>61</v>
+      </c>
+      <c r="H17" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I17" s="36" t="s">
+        <v>678</v>
+      </c>
+      <c r="J17" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H17" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I17" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J17" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K17" s="33" t="s">
-        <v>66</v>
-      </c>
-      <c r="L17" s="33">
+        <v>23</v>
+      </c>
+      <c r="L17" s="33" t="s">
+        <v>60</v>
+      </c>
+      <c r="M17" s="33">
         <v>2000</v>
       </c>
-      <c r="M17" s="33">
+      <c r="N17" s="33">
         <v>111.46</v>
       </c>
-      <c r="N17" s="33">
+      <c r="O17" s="33">
         <v>117.0329</v>
       </c>
-      <c r="O17" s="33">
-        <f>N17</f>
+      <c r="P17" s="33">
+        <f>O17</f>
         <v>117.0329</v>
       </c>
-      <c r="P17" s="39">
+      <c r="Q17" s="39">
         <v>232660</v>
       </c>
-      <c r="Q17" s="33">
+      <c r="R17" s="33">
         <v>4.5999999999999996</v>
       </c>
-      <c r="R17" s="33">
+      <c r="S17" s="33">
         <v>1</v>
       </c>
-      <c r="S17" s="40">
+      <c r="T17" s="40">
         <f t="shared" si="3"/>
         <v>4.9999102817154174E-2</v>
       </c>
-      <c r="T17" s="39">
+      <c r="U17" s="39">
         <v>11150</v>
       </c>
-      <c r="U17" s="41">
+      <c r="V17" s="41">
         <v>11150</v>
       </c>
     </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A18" s="33">
         <v>14</v>
       </c>
@@ -3808,60 +4172,63 @@
         <v>3</v>
       </c>
       <c r="E18" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="F18" s="36" t="s">
-        <v>69</v>
-      </c>
-      <c r="G18" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="F18" s="33" t="s">
+        <v>704</v>
+      </c>
+      <c r="G18" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="H18" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I18" s="36" t="s">
+        <v>677</v>
+      </c>
+      <c r="J18" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H18" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I18" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J18" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K18" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="L18" s="33">
+        <v>23</v>
+      </c>
+      <c r="L18" s="33" t="s">
+        <v>62</v>
+      </c>
+      <c r="M18" s="33">
         <v>-300</v>
       </c>
-      <c r="M18" s="33">
+      <c r="N18" s="33">
         <v>337.98</v>
       </c>
-      <c r="N18" s="33">
+      <c r="O18" s="33">
         <v>331.22</v>
       </c>
-      <c r="O18" s="33">
-        <f>N18</f>
+      <c r="P18" s="33">
+        <f>O18</f>
         <v>331.22</v>
       </c>
-      <c r="P18" s="39">
+      <c r="Q18" s="39">
         <v>101964</v>
       </c>
-      <c r="Q18" s="33">
+      <c r="R18" s="33">
         <v>6.8</v>
       </c>
-      <c r="R18" s="33">
+      <c r="S18" s="33">
         <v>1</v>
       </c>
-      <c r="S18" s="40">
+      <c r="T18" s="40">
         <f t="shared" si="3"/>
         <v>2.0001183501982336E-2</v>
       </c>
-      <c r="T18" s="39">
+      <c r="U18" s="39">
         <v>2033</v>
       </c>
-      <c r="U18" s="41">
+      <c r="V18" s="41">
         <v>2033</v>
       </c>
     </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A19" s="33">
         <v>15</v>
       </c>
@@ -3876,59 +4243,62 @@
         <v>24</v>
       </c>
       <c r="E19" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="F19" s="36" t="s">
-        <v>71</v>
-      </c>
-      <c r="G19" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H19" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I19" s="33" t="s">
-        <v>48</v>
+        <v>64</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>705</v>
+      </c>
+      <c r="G19" s="36" t="s">
+        <v>65</v>
+      </c>
+      <c r="H19" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I19" s="36" t="s">
+        <v>676</v>
       </c>
       <c r="J19" s="33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K19" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="L19" s="33">
+        <v>43</v>
+      </c>
+      <c r="L19" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="M19" s="33">
         <v>-500</v>
       </c>
-      <c r="M19" s="33">
+      <c r="N19" s="33">
         <v>108.102</v>
-      </c>
-      <c r="N19" s="33">
-        <v>107.749</v>
       </c>
       <c r="O19" s="33">
         <v>107.749</v>
       </c>
-      <c r="P19" s="39">
+      <c r="P19" s="33">
+        <v>107.749</v>
+      </c>
+      <c r="Q19" s="39">
         <v>54051</v>
       </c>
-      <c r="Q19" s="33">
+      <c r="R19" s="33">
         <v>4.5599999999999996</v>
       </c>
-      <c r="R19" s="33">
+      <c r="S19" s="33">
         <v>1</v>
       </c>
-      <c r="S19" s="40">
+      <c r="T19" s="40">
         <f t="shared" si="3"/>
         <v>3.2654344970491629E-3</v>
       </c>
-      <c r="T19" s="39">
+      <c r="U19" s="39">
         <v>177</v>
       </c>
-      <c r="U19" s="41">
+      <c r="V19" s="41">
         <v>177</v>
       </c>
     </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A20" s="33">
         <v>16</v>
       </c>
@@ -3943,59 +4313,62 @@
         <v>10</v>
       </c>
       <c r="E20" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="F20" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="G20" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H20" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I20" s="33" t="s">
-        <v>32</v>
+        <v>67</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>706</v>
+      </c>
+      <c r="G20" s="36" t="s">
+        <v>68</v>
+      </c>
+      <c r="H20" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I20" s="36" t="s">
+        <v>675</v>
       </c>
       <c r="J20" s="33" t="s">
-        <v>532</v>
+        <v>29</v>
       </c>
       <c r="K20" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="L20" s="33">
-        <v>-1</v>
+        <v>524</v>
+      </c>
+      <c r="L20" s="33" t="s">
+        <v>69</v>
       </c>
       <c r="M20" s="33">
+        <v>-5</v>
+      </c>
+      <c r="N20" s="33">
         <v>1868.84</v>
-      </c>
-      <c r="N20" s="33">
-        <v>1860.72</v>
       </c>
       <c r="O20" s="33">
         <v>1860.72</v>
       </c>
-      <c r="P20" s="39">
+      <c r="P20" s="33">
+        <v>1860.72</v>
+      </c>
+      <c r="Q20" s="39">
         <v>185382</v>
       </c>
-      <c r="Q20" s="33">
+      <c r="R20" s="33">
         <v>11.2</v>
       </c>
-      <c r="R20" s="33">
+      <c r="S20" s="33">
         <v>1</v>
       </c>
-      <c r="S20" s="40">
-        <f>IF(R20=1, ABS(N20-M20)/M20, 0)</f>
+      <c r="T20" s="40">
+        <f>IF(S20=1, ABS(O20-N20)/N20, 0)</f>
         <v>4.3449412469766758E-3</v>
       </c>
-      <c r="T20" s="39">
+      <c r="U20" s="39">
         <v>4060</v>
       </c>
-      <c r="U20" s="41">
+      <c r="V20" s="41">
         <v>4060</v>
       </c>
     </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A21" s="33">
         <v>17</v>
       </c>
@@ -4010,59 +4383,62 @@
         <v>13</v>
       </c>
       <c r="E21" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="F21" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="G21" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="H21" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="I21" s="33" t="s">
-        <v>48</v>
+        <v>70</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>707</v>
+      </c>
+      <c r="G21" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="I21" s="36" t="s">
+        <v>745</v>
       </c>
       <c r="J21" s="33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K21" s="33" t="s">
-        <v>76</v>
-      </c>
-      <c r="L21" s="33">
+        <v>43</v>
+      </c>
+      <c r="L21" s="33" t="s">
+        <v>70</v>
+      </c>
+      <c r="M21" s="33">
         <v>2000</v>
       </c>
-      <c r="M21" s="33">
+      <c r="N21" s="33">
         <v>82.31</v>
-      </c>
-      <c r="N21" s="33">
-        <v>83.02</v>
       </c>
       <c r="O21" s="33">
         <v>83.02</v>
       </c>
-      <c r="P21" s="39">
+      <c r="P21" s="33">
+        <v>83.02</v>
+      </c>
+      <c r="Q21" s="39">
         <v>164620</v>
       </c>
-      <c r="Q21" s="33">
+      <c r="R21" s="33">
         <v>23.92</v>
       </c>
-      <c r="R21" s="33">
+      <c r="S21" s="33">
         <v>1</v>
       </c>
-      <c r="S21" s="40">
-        <f>IF(R21=1, ABS(N21-M21)/M21, 0)</f>
+      <c r="T21" s="40">
+        <f>IF(S21=1, ABS(O21-N21)/N21, 0)</f>
         <v>8.6259263758959263E-3</v>
       </c>
-      <c r="T21" s="39">
+      <c r="U21" s="39">
         <v>1420</v>
       </c>
-      <c r="U21" s="41">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V21" s="41">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A22" s="33">
         <v>17</v>
       </c>
@@ -4077,59 +4453,62 @@
         <v>13</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="F22" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="G22" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="H22" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="I22" s="33" t="s">
-        <v>32</v>
+        <v>72</v>
+      </c>
+      <c r="F22" s="33" t="s">
+        <v>708</v>
+      </c>
+      <c r="G22" s="36" t="s">
+        <v>633</v>
+      </c>
+      <c r="H22" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="I22" s="36" t="s">
+        <v>745</v>
       </c>
       <c r="J22" s="33" t="s">
-        <v>533</v>
+        <v>29</v>
       </c>
       <c r="K22" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="L22" s="33">
+        <v>525</v>
+      </c>
+      <c r="L22" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="M22" s="33">
         <v>-4</v>
       </c>
-      <c r="M22" s="33">
+      <c r="N22" s="33">
         <v>7763</v>
-      </c>
-      <c r="N22" s="33">
-        <v>7689.75</v>
       </c>
       <c r="O22" s="33">
         <v>7689.75</v>
       </c>
-      <c r="P22" s="39">
+      <c r="P22" s="33">
+        <v>7689.75</v>
+      </c>
+      <c r="Q22" s="39">
         <v>154290</v>
       </c>
-      <c r="Q22" s="33">
+      <c r="R22" s="33">
         <v>17.079999999999998</v>
       </c>
-      <c r="R22" s="33">
+      <c r="S22" s="33">
         <v>1</v>
       </c>
-      <c r="S22" s="40">
-        <f>IF(R22=1, ABS(N22-M22)/M22, 0)</f>
+      <c r="T22" s="40">
+        <f>IF(S22=1, ABS(O22-N22)/N22, 0)</f>
         <v>9.435785134612908E-3</v>
       </c>
-      <c r="T22" s="39">
+      <c r="U22" s="39">
         <v>1418</v>
       </c>
-      <c r="U22" s="41">
+      <c r="V22" s="41">
         <v>2838</v>
       </c>
     </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A23" s="33">
         <v>18</v>
       </c>
@@ -4144,59 +4523,62 @@
         <v>0</v>
       </c>
       <c r="E23" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="F23" s="36" t="s">
-        <v>82</v>
-      </c>
-      <c r="G23" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H23" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I23" s="33" t="s">
-        <v>32</v>
+        <v>73</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>709</v>
+      </c>
+      <c r="G23" s="36" t="s">
+        <v>74</v>
+      </c>
+      <c r="H23" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I23" s="36" t="s">
+        <v>674</v>
       </c>
       <c r="J23" s="33" t="s">
-        <v>530</v>
+        <v>29</v>
       </c>
       <c r="K23" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="L23" s="33">
+        <v>522</v>
+      </c>
+      <c r="L23" s="33" t="s">
+        <v>75</v>
+      </c>
+      <c r="M23" s="33">
         <v>-10</v>
       </c>
-      <c r="M23" s="33">
+      <c r="N23" s="33">
         <v>0.16914999999999999</v>
-      </c>
-      <c r="N23" s="33">
-        <v>0.16313</v>
       </c>
       <c r="O23" s="33">
         <v>0.16313</v>
       </c>
-      <c r="P23" s="39">
+      <c r="P23" s="33">
+        <v>0.16313</v>
+      </c>
+      <c r="Q23" s="39">
         <v>182705</v>
       </c>
-      <c r="Q23" s="33">
+      <c r="R23" s="33">
         <v>29.6</v>
       </c>
-      <c r="R23" s="33">
+      <c r="S23" s="33">
         <v>1</v>
       </c>
-      <c r="S23" s="40">
-        <f>IF(R23=1, ABS(N23-M23)/M23, 0)</f>
+      <c r="T23" s="40">
+        <f>IF(S23=1, ABS(O23-N23)/N23, 0)</f>
         <v>3.5589713272243556E-2</v>
       </c>
-      <c r="T23" s="39">
+      <c r="U23" s="39">
         <v>6742</v>
       </c>
-      <c r="U23" s="41">
+      <c r="V23" s="41">
         <v>6742</v>
       </c>
     </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A24" s="33">
         <v>19</v>
       </c>
@@ -4211,58 +4593,61 @@
         <v>0</v>
       </c>
       <c r="E24" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="F24" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="G24" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H24" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I24" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="F24" s="33" t="s">
+        <v>692</v>
+      </c>
+      <c r="G24" s="36" t="s">
         <v>32</v>
       </c>
+      <c r="H24" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I24" s="36" t="s">
+        <v>673</v>
+      </c>
       <c r="J24" s="33" t="s">
-        <v>529</v>
+        <v>29</v>
       </c>
       <c r="K24" s="33" t="s">
-        <v>84</v>
-      </c>
-      <c r="L24" s="33">
+        <v>521</v>
+      </c>
+      <c r="L24" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="M24" s="33">
         <v>-10</v>
       </c>
-      <c r="M24" s="33">
+      <c r="N24" s="33">
         <v>1.1704300000000001</v>
-      </c>
-      <c r="N24" s="33">
-        <v>1.1695</v>
       </c>
       <c r="O24" s="33">
         <v>1.1695</v>
       </c>
-      <c r="P24" s="39">
+      <c r="P24" s="33">
+        <v>1.1695</v>
+      </c>
+      <c r="Q24" s="39">
         <v>1451000</v>
       </c>
-      <c r="Q24" s="33">
+      <c r="R24" s="33">
         <v>6.28</v>
       </c>
-      <c r="R24" s="33">
+      <c r="S24" s="33">
         <v>1</v>
       </c>
-      <c r="S24" s="40">
+      <c r="T24" s="40">
         <v>8.0000000000000004E-4</v>
       </c>
-      <c r="T24" s="39">
+      <c r="U24" s="39">
         <v>1245</v>
       </c>
-      <c r="U24" s="41">
+      <c r="V24" s="41">
         <v>1245</v>
       </c>
     </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A25" s="33">
         <v>20</v>
       </c>
@@ -4277,59 +4662,62 @@
         <v>2</v>
       </c>
       <c r="E25" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="F25" s="36" t="s">
-        <v>86</v>
-      </c>
-      <c r="G25" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H25" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I25" s="33" t="s">
-        <v>32</v>
+        <v>77</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>710</v>
+      </c>
+      <c r="G25" s="36" t="s">
+        <v>78</v>
+      </c>
+      <c r="H25" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I25" s="36" t="s">
+        <v>672</v>
       </c>
       <c r="J25" s="33" t="s">
-        <v>529</v>
+        <v>29</v>
       </c>
       <c r="K25" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="L25" s="33">
+        <v>521</v>
+      </c>
+      <c r="L25" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="M25" s="33">
         <v>-6</v>
       </c>
-      <c r="M25" s="33">
+      <c r="N25" s="33">
         <v>0.72838000000000003</v>
-      </c>
-      <c r="N25" s="33">
-        <v>0.72550000000000003</v>
       </c>
       <c r="O25" s="33">
         <v>0.72550000000000003</v>
       </c>
-      <c r="P25" s="39">
+      <c r="P25" s="33">
+        <v>0.72550000000000003</v>
+      </c>
+      <c r="Q25" s="39">
         <v>436235</v>
       </c>
-      <c r="Q25" s="33">
+      <c r="R25" s="33">
         <v>4.5599999999999996</v>
       </c>
-      <c r="R25" s="33">
+      <c r="S25" s="33">
         <v>1</v>
       </c>
-      <c r="S25" s="40">
-        <f t="shared" ref="S25:S36" si="4">IF(R25=1, ABS(N25-M25)/M25, 0)</f>
+      <c r="T25" s="40">
+        <f t="shared" ref="T25:T36" si="4">IF(S25=1, ABS(O25-N25)/N25, 0)</f>
         <v>3.9539800653504951E-3</v>
       </c>
-      <c r="T25" s="39">
+      <c r="U25" s="39">
         <v>1710</v>
       </c>
-      <c r="U25" s="41">
+      <c r="V25" s="41">
         <v>1710</v>
       </c>
     </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A26" s="33">
         <v>21</v>
       </c>
@@ -4344,59 +4732,62 @@
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="F26" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="G26" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H26" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I26" s="33" t="s">
-        <v>32</v>
+        <v>80</v>
+      </c>
+      <c r="F26" s="33" t="s">
+        <v>697</v>
+      </c>
+      <c r="G26" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="H26" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I26" s="36" t="s">
+        <v>671</v>
       </c>
       <c r="J26" s="33" t="s">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="K26" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="L26" s="33">
+        <v>114</v>
+      </c>
+      <c r="L26" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="M26" s="33">
         <v>-3</v>
       </c>
-      <c r="M26" s="33">
+      <c r="N26" s="33">
         <v>4703.32</v>
-      </c>
-      <c r="N26" s="33">
-        <v>4663.8</v>
       </c>
       <c r="O26" s="33">
         <v>4663.8</v>
       </c>
-      <c r="P26" s="39">
+      <c r="P26" s="33">
+        <v>4663.8</v>
+      </c>
+      <c r="Q26" s="39">
         <v>141200</v>
       </c>
-      <c r="Q26" s="33">
+      <c r="R26" s="33">
         <v>9.6</v>
       </c>
-      <c r="R26" s="33">
+      <c r="S26" s="33">
         <v>1</v>
       </c>
-      <c r="S26" s="40">
+      <c r="T26" s="40">
         <f t="shared" si="4"/>
         <v>8.4025752021974973E-3</v>
       </c>
-      <c r="T26" s="39">
+      <c r="U26" s="39">
         <v>715</v>
       </c>
-      <c r="U26" s="41">
+      <c r="V26" s="41">
         <v>715</v>
       </c>
     </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A27" s="33">
         <v>22</v>
       </c>
@@ -4410,59 +4801,62 @@
         <v>0</v>
       </c>
       <c r="E27" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="F27" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="G27" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>711</v>
+      </c>
+      <c r="G27" s="36" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I27" s="36" t="s">
+        <v>670</v>
+      </c>
+      <c r="J27" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H27" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I27" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J27" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K27" s="33" t="s">
-        <v>90</v>
-      </c>
-      <c r="L27" s="33">
+        <v>23</v>
+      </c>
+      <c r="L27" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="M27" s="33">
         <v>-1000</v>
       </c>
-      <c r="M27" s="33">
+      <c r="N27" s="33">
         <v>133.33799999999999</v>
-      </c>
-      <c r="N27" s="33">
-        <v>129.84</v>
       </c>
       <c r="O27" s="33">
         <v>129.84</v>
       </c>
-      <c r="P27" s="39">
+      <c r="P27" s="33">
+        <v>129.84</v>
+      </c>
+      <c r="Q27" s="39">
         <v>133338</v>
       </c>
-      <c r="Q27" s="33">
+      <c r="R27" s="33">
         <v>9.65</v>
       </c>
-      <c r="R27" s="33">
+      <c r="S27" s="33">
         <v>1</v>
       </c>
-      <c r="S27" s="40">
+      <c r="T27" s="40">
         <f t="shared" si="4"/>
         <v>2.623408180713668E-2</v>
       </c>
-      <c r="T27" s="39">
+      <c r="U27" s="39">
         <v>3498</v>
       </c>
-      <c r="U27" s="41">
+      <c r="V27" s="41">
         <v>3498</v>
       </c>
     </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A28" s="33">
         <v>23</v>
       </c>
@@ -4477,59 +4871,62 @@
         <v>1</v>
       </c>
       <c r="E28" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="F28" s="36" t="s">
-        <v>93</v>
-      </c>
-      <c r="G28" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="F28" s="33" t="s">
+        <v>712</v>
+      </c>
+      <c r="G28" s="36" t="s">
+        <v>85</v>
+      </c>
+      <c r="H28" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I28" s="36" t="s">
+        <v>669</v>
+      </c>
+      <c r="J28" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H28" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I28" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J28" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K28" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="L28" s="33">
+        <v>23</v>
+      </c>
+      <c r="L28" s="33" t="s">
+        <v>84</v>
+      </c>
+      <c r="M28" s="33">
         <v>-1000</v>
       </c>
-      <c r="M28" s="33">
+      <c r="N28" s="33">
         <v>59.798999999999999</v>
-      </c>
-      <c r="N28" s="33">
-        <v>57.99</v>
       </c>
       <c r="O28" s="33">
         <v>57.99</v>
       </c>
-      <c r="P28" s="39">
+      <c r="P28" s="33">
+        <v>57.99</v>
+      </c>
+      <c r="Q28" s="39">
         <v>59799</v>
       </c>
-      <c r="Q28" s="33">
+      <c r="R28" s="33">
         <v>11.32</v>
       </c>
-      <c r="R28" s="33">
+      <c r="S28" s="33">
         <v>1</v>
       </c>
-      <c r="S28" s="40">
+      <c r="T28" s="40">
         <f t="shared" si="4"/>
         <v>3.0251341995685504E-2</v>
       </c>
-      <c r="T28" s="39">
+      <c r="U28" s="39">
         <v>1809</v>
       </c>
-      <c r="U28" s="41">
+      <c r="V28" s="41">
         <v>1809</v>
       </c>
     </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A29" s="33">
         <v>24</v>
       </c>
@@ -4544,59 +4941,62 @@
         <v>2</v>
       </c>
       <c r="E29" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="F29" s="36" t="s">
-        <v>95</v>
-      </c>
-      <c r="G29" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>713</v>
+      </c>
+      <c r="G29" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="H29" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I29" s="36" t="s">
+        <v>668</v>
+      </c>
+      <c r="J29" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H29" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I29" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J29" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K29" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="L29" s="33">
+        <v>23</v>
+      </c>
+      <c r="L29" s="33" t="s">
+        <v>86</v>
+      </c>
+      <c r="M29" s="33">
         <v>900</v>
       </c>
-      <c r="M29" s="33">
+      <c r="N29" s="33">
         <v>269.69299999999998</v>
-      </c>
-      <c r="N29" s="33">
-        <v>270.42500000000001</v>
       </c>
       <c r="O29" s="33">
         <v>270.42500000000001</v>
       </c>
-      <c r="P29" s="39">
+      <c r="P29" s="33">
+        <v>270.42500000000001</v>
+      </c>
+      <c r="Q29" s="39">
         <v>242723</v>
       </c>
-      <c r="Q29" s="33">
+      <c r="R29" s="33">
         <v>12.28</v>
       </c>
-      <c r="R29" s="33">
+      <c r="S29" s="33">
         <v>1</v>
       </c>
-      <c r="S29" s="40">
+      <c r="T29" s="40">
         <f t="shared" si="4"/>
         <v>2.7141972539147393E-3</v>
       </c>
-      <c r="T29" s="39">
+      <c r="U29" s="39">
         <v>2891</v>
       </c>
-      <c r="U29" s="41">
+      <c r="V29" s="41">
         <v>2891</v>
       </c>
     </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A30" s="33">
         <v>25</v>
       </c>
@@ -4611,59 +5011,62 @@
         <v>2</v>
       </c>
       <c r="E30" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="F30" s="36" t="s">
-        <v>97</v>
-      </c>
-      <c r="G30" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="F30" s="33" t="s">
+        <v>714</v>
+      </c>
+      <c r="G30" s="36" t="s">
+        <v>89</v>
+      </c>
+      <c r="H30" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I30" s="36" t="s">
+        <v>667</v>
+      </c>
+      <c r="J30" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H30" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I30" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J30" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K30" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="L30" s="33">
+        <v>23</v>
+      </c>
+      <c r="L30" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="M30" s="33">
         <v>310</v>
       </c>
-      <c r="M30" s="33">
+      <c r="N30" s="33">
         <v>951.66</v>
-      </c>
-      <c r="N30" s="33">
-        <v>949.6</v>
       </c>
       <c r="O30" s="33">
         <v>949.6</v>
       </c>
-      <c r="P30" s="39">
+      <c r="P30" s="33">
+        <v>949.6</v>
+      </c>
+      <c r="Q30" s="39">
         <v>295017</v>
       </c>
-      <c r="Q30" s="33">
+      <c r="R30" s="33">
         <v>9.18</v>
       </c>
-      <c r="R30" s="33">
-        <v>0</v>
-      </c>
-      <c r="S30" s="40">
+      <c r="S30" s="33">
+        <v>0</v>
+      </c>
+      <c r="T30" s="40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="T30" s="39">
+      <c r="U30" s="39">
         <v>-642</v>
       </c>
-      <c r="U30" s="45">
+      <c r="V30" s="45">
         <v>-642</v>
       </c>
     </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A31" s="33">
         <v>26</v>
       </c>
@@ -4678,59 +5081,62 @@
         <v>1</v>
       </c>
       <c r="E31" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="F31" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="G31" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>715</v>
+      </c>
+      <c r="G31" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="H31" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I31" s="36" t="s">
+        <v>664</v>
+      </c>
+      <c r="J31" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H31" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I31" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J31" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K31" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="L31" s="33">
+        <v>23</v>
+      </c>
+      <c r="L31" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="M31" s="33">
         <v>400</v>
       </c>
-      <c r="M31" s="33">
+      <c r="N31" s="33">
         <v>331.50700000000001</v>
-      </c>
-      <c r="N31" s="33">
-        <v>334.31</v>
       </c>
       <c r="O31" s="33">
         <v>334.31</v>
       </c>
-      <c r="P31" s="39">
+      <c r="P31" s="33">
+        <v>334.31</v>
+      </c>
+      <c r="Q31" s="39">
         <v>132602</v>
       </c>
-      <c r="Q31" s="33">
+      <c r="R31" s="33">
         <v>6.69</v>
       </c>
-      <c r="R31" s="33">
+      <c r="S31" s="33">
         <v>1</v>
       </c>
-      <c r="S31" s="40">
+      <c r="T31" s="40">
         <f t="shared" si="4"/>
         <v>8.455326735182055E-3</v>
       </c>
-      <c r="T31" s="39">
+      <c r="U31" s="39">
         <v>4108</v>
       </c>
-      <c r="U31" s="41">
+      <c r="V31" s="41">
         <v>4108</v>
       </c>
     </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A32" s="33">
         <v>27</v>
       </c>
@@ -4745,59 +5151,62 @@
         <v>17</v>
       </c>
       <c r="E32" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="F32" s="36" t="s">
-        <v>101</v>
-      </c>
-      <c r="G32" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="F32" s="33" t="s">
+        <v>716</v>
+      </c>
+      <c r="G32" s="36" t="s">
+        <v>93</v>
+      </c>
+      <c r="H32" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I32" s="36" t="s">
+        <v>666</v>
+      </c>
+      <c r="J32" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H32" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I32" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J32" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K32" s="33" t="s">
-        <v>100</v>
-      </c>
-      <c r="L32" s="33">
+        <v>23</v>
+      </c>
+      <c r="L32" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="M32" s="33">
         <v>-8000</v>
       </c>
-      <c r="M32" s="33">
+      <c r="N32" s="33">
         <v>50.59</v>
-      </c>
-      <c r="N32" s="33">
-        <v>49.67</v>
       </c>
       <c r="O32" s="33">
         <v>49.67</v>
       </c>
-      <c r="P32" s="39">
+      <c r="P32" s="33">
+        <v>49.67</v>
+      </c>
+      <c r="Q32" s="39">
         <v>397331</v>
       </c>
-      <c r="Q32" s="33">
+      <c r="R32" s="33">
         <v>45.99</v>
       </c>
-      <c r="R32" s="33">
+      <c r="S32" s="33">
         <v>1</v>
       </c>
-      <c r="S32" s="40">
+      <c r="T32" s="40">
         <f t="shared" si="4"/>
         <v>1.8185412136785959E-2</v>
       </c>
-      <c r="T32" s="39">
+      <c r="U32" s="39">
         <v>7389</v>
       </c>
-      <c r="U32" s="41">
+      <c r="V32" s="41">
         <v>7389</v>
       </c>
     </row>
-    <row r="33" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A33" s="33">
         <v>28</v>
       </c>
@@ -4812,59 +5221,62 @@
         <v>2</v>
       </c>
       <c r="E33" s="33" t="s">
-        <v>580</v>
-      </c>
-      <c r="F33" s="36" t="s">
-        <v>581</v>
-      </c>
-      <c r="G33" s="33" t="s">
+        <v>572</v>
+      </c>
+      <c r="F33" s="33" t="s">
+        <v>717</v>
+      </c>
+      <c r="G33" s="36" t="s">
+        <v>573</v>
+      </c>
+      <c r="H33" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I33" s="36" t="s">
+        <v>665</v>
+      </c>
+      <c r="J33" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H33" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I33" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J33" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K33" s="33" t="s">
-        <v>580</v>
-      </c>
-      <c r="L33" s="33">
+        <v>23</v>
+      </c>
+      <c r="L33" s="33" t="s">
+        <v>572</v>
+      </c>
+      <c r="M33" s="33">
         <v>13000</v>
       </c>
-      <c r="M33" s="33">
+      <c r="N33" s="33">
         <v>8.6943999999999999</v>
-      </c>
-      <c r="N33" s="33">
-        <v>8.8673000000000002</v>
       </c>
       <c r="O33" s="33">
         <v>8.8673000000000002</v>
       </c>
-      <c r="P33" s="39">
+      <c r="P33" s="33">
+        <v>8.8673000000000002</v>
+      </c>
+      <c r="Q33" s="39">
         <v>113028</v>
       </c>
-      <c r="Q33" s="33">
+      <c r="R33" s="33">
         <v>105.64</v>
       </c>
-      <c r="R33" s="33">
+      <c r="S33" s="33">
         <v>1</v>
       </c>
-      <c r="S33" s="40">
+      <c r="T33" s="40">
         <f t="shared" si="4"/>
         <v>1.9886363636363667E-2</v>
       </c>
-      <c r="T33" s="39">
+      <c r="U33" s="39">
         <v>2247</v>
       </c>
-      <c r="U33" s="41">
+      <c r="V33" s="41">
         <v>2247</v>
       </c>
     </row>
-    <row r="34" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A34" s="33">
         <v>29</v>
       </c>
@@ -4879,59 +5291,62 @@
         <v>2</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="F34" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="G34" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="F34" s="33" t="s">
+        <v>715</v>
+      </c>
+      <c r="G34" s="36" t="s">
+        <v>91</v>
+      </c>
+      <c r="H34" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I34" s="36" t="s">
+        <v>664</v>
+      </c>
+      <c r="J34" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H34" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I34" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J34" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K34" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="L34" s="33">
+        <v>23</v>
+      </c>
+      <c r="L34" s="33" t="s">
+        <v>90</v>
+      </c>
+      <c r="M34" s="33">
         <v>400</v>
       </c>
-      <c r="M34" s="33">
+      <c r="N34" s="33">
         <v>318.87</v>
-      </c>
-      <c r="N34" s="33">
-        <v>322</v>
       </c>
       <c r="O34" s="33">
         <v>322</v>
       </c>
-      <c r="P34" s="39">
+      <c r="P34" s="33">
+        <v>322</v>
+      </c>
+      <c r="Q34" s="39">
         <v>127547</v>
       </c>
-      <c r="Q34" s="33">
+      <c r="R34" s="33">
         <v>4.71</v>
       </c>
-      <c r="R34" s="33">
+      <c r="S34" s="33">
         <v>1</v>
       </c>
-      <c r="S34" s="40">
+      <c r="T34" s="40">
         <f t="shared" si="4"/>
         <v>9.8159124408065835E-3</v>
       </c>
-      <c r="T34" s="39">
+      <c r="U34" s="39">
         <v>1253</v>
       </c>
-      <c r="U34" s="41">
+      <c r="V34" s="41">
         <v>1253</v>
       </c>
     </row>
-    <row r="35" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A35" s="33">
         <v>30</v>
       </c>
@@ -4946,59 +5361,62 @@
         <v>4</v>
       </c>
       <c r="E35" s="33" t="s">
-        <v>582</v>
-      </c>
-      <c r="F35" s="36" t="s">
-        <v>583</v>
-      </c>
-      <c r="G35" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H35" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I35" s="33" t="s">
-        <v>32</v>
+        <v>574</v>
+      </c>
+      <c r="F35" s="33" t="s">
+        <v>718</v>
+      </c>
+      <c r="G35" s="36" t="s">
+        <v>575</v>
+      </c>
+      <c r="H35" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I35" s="36" t="s">
+        <v>663</v>
       </c>
       <c r="J35" s="33" t="s">
-        <v>533</v>
+        <v>29</v>
       </c>
       <c r="K35" s="33" t="s">
-        <v>582</v>
-      </c>
-      <c r="L35" s="33">
+        <v>525</v>
+      </c>
+      <c r="L35" s="33" t="s">
+        <v>574</v>
+      </c>
+      <c r="M35" s="33">
         <v>1</v>
       </c>
-      <c r="M35" s="33">
+      <c r="N35" s="33">
         <v>52061.3</v>
-      </c>
-      <c r="N35" s="33">
-        <v>52341</v>
       </c>
       <c r="O35" s="33">
         <v>52341</v>
       </c>
-      <c r="P35" s="39">
+      <c r="P35" s="33">
+        <v>52341</v>
+      </c>
+      <c r="Q35" s="39">
         <v>26031</v>
       </c>
-      <c r="Q35" s="33">
+      <c r="R35" s="33">
         <v>3.11</v>
       </c>
-      <c r="R35" s="33">
+      <c r="S35" s="33">
         <v>1</v>
       </c>
-      <c r="S35" s="40">
+      <c r="T35" s="40">
         <f t="shared" si="4"/>
         <v>5.3725127878096988E-3</v>
       </c>
-      <c r="T35" s="39">
+      <c r="U35" s="39">
         <v>141</v>
       </c>
-      <c r="U35" s="41">
+      <c r="V35" s="41">
         <v>141</v>
       </c>
     </row>
-    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A36" s="33">
         <v>31</v>
       </c>
@@ -5013,59 +5431,62 @@
         <v>8</v>
       </c>
       <c r="E36" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="F36" s="36" t="s">
-        <v>584</v>
-      </c>
-      <c r="G36" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="F36" s="33" t="s">
+        <v>699</v>
+      </c>
+      <c r="G36" s="36" t="s">
+        <v>576</v>
+      </c>
+      <c r="H36" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" s="36" t="s">
+        <v>662</v>
+      </c>
+      <c r="J36" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H36" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I36" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J36" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K36" s="33" t="s">
-        <v>56</v>
-      </c>
-      <c r="L36" s="33">
+        <v>23</v>
+      </c>
+      <c r="L36" s="33" t="s">
+        <v>51</v>
+      </c>
+      <c r="M36" s="33">
         <v>-280</v>
       </c>
-      <c r="M36" s="33">
+      <c r="N36" s="33">
         <v>674.59</v>
-      </c>
-      <c r="N36" s="33">
-        <v>688</v>
       </c>
       <c r="O36" s="33">
         <v>688</v>
       </c>
-      <c r="P36" s="39">
+      <c r="P36" s="33">
+        <v>688</v>
+      </c>
+      <c r="Q36" s="39">
         <v>188496</v>
       </c>
-      <c r="Q36" s="33">
+      <c r="R36" s="33">
         <v>4.5</v>
       </c>
-      <c r="R36" s="33">
-        <v>0</v>
-      </c>
-      <c r="S36" s="40">
+      <c r="S36" s="33">
+        <v>0</v>
+      </c>
+      <c r="T36" s="40">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="T36" s="39">
+      <c r="U36" s="39">
         <v>-3825</v>
       </c>
-      <c r="U36" s="45">
+      <c r="V36" s="45">
         <v>-3825</v>
       </c>
     </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A37" s="33">
         <v>32</v>
       </c>
@@ -5080,59 +5501,62 @@
         <v>1</v>
       </c>
       <c r="E37" s="33" t="s">
-        <v>585</v>
-      </c>
-      <c r="F37" s="36" t="s">
-        <v>586</v>
-      </c>
-      <c r="G37" s="33" t="s">
+        <v>577</v>
+      </c>
+      <c r="F37" s="33" t="s">
+        <v>719</v>
+      </c>
+      <c r="G37" s="36" t="s">
+        <v>578</v>
+      </c>
+      <c r="H37" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I37" s="36" t="s">
+        <v>661</v>
+      </c>
+      <c r="J37" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H37" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I37" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J37" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K37" s="33" t="s">
-        <v>585</v>
-      </c>
-      <c r="L37" s="33">
+        <v>23</v>
+      </c>
+      <c r="L37" s="33" t="s">
+        <v>577</v>
+      </c>
+      <c r="M37" s="33">
         <v>250</v>
       </c>
-      <c r="M37" s="33">
+      <c r="N37" s="33">
         <v>113.7</v>
-      </c>
-      <c r="N37" s="33">
-        <v>115.08</v>
       </c>
       <c r="O37" s="33">
         <v>115.08</v>
       </c>
-      <c r="P37" s="39">
+      <c r="P37" s="33">
+        <v>115.08</v>
+      </c>
+      <c r="Q37" s="39">
         <v>28770</v>
       </c>
-      <c r="Q37" s="33">
+      <c r="R37" s="33">
         <v>2.94</v>
       </c>
-      <c r="R37" s="33">
+      <c r="S37" s="33">
         <v>1</v>
       </c>
-      <c r="S37" s="40">
-        <f t="shared" ref="S37:S40" si="6">IF(R37=1, ABS(N37-M37)/M37, 0)</f>
+      <c r="T37" s="40">
+        <f t="shared" ref="T37:T40" si="6">IF(S37=1, ABS(O37-N37)/N37, 0)</f>
         <v>1.2137203166226873E-2</v>
       </c>
-      <c r="T37" s="39">
+      <c r="U37" s="39">
         <v>345</v>
       </c>
-      <c r="U37" s="41">
+      <c r="V37" s="41">
         <v>345</v>
       </c>
     </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A38" s="33">
         <v>33</v>
       </c>
@@ -5147,59 +5571,62 @@
         <v>1</v>
       </c>
       <c r="E38" s="33" t="s">
-        <v>587</v>
-      </c>
-      <c r="F38" s="36" t="s">
-        <v>588</v>
-      </c>
-      <c r="G38" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H38" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I38" s="33" t="s">
-        <v>32</v>
+        <v>579</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>720</v>
+      </c>
+      <c r="G38" s="36" t="s">
+        <v>580</v>
+      </c>
+      <c r="H38" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I38" s="36" t="s">
+        <v>660</v>
       </c>
       <c r="J38" s="33" t="s">
-        <v>120</v>
+        <v>29</v>
       </c>
       <c r="K38" s="33" t="s">
-        <v>587</v>
-      </c>
-      <c r="L38" s="33">
+        <v>112</v>
+      </c>
+      <c r="L38" s="33" t="s">
+        <v>579</v>
+      </c>
+      <c r="M38" s="33">
         <v>1</v>
       </c>
-      <c r="M38" s="33">
+      <c r="N38" s="33">
         <v>120.35</v>
-      </c>
-      <c r="N38" s="33">
-        <v>120.57</v>
       </c>
       <c r="O38" s="33">
         <v>120.57</v>
       </c>
-      <c r="P38" s="39">
+      <c r="P38" s="33">
+        <v>120.57</v>
+      </c>
+      <c r="Q38" s="39">
         <v>120370</v>
       </c>
-      <c r="Q38" s="33">
+      <c r="R38" s="33">
         <v>2.2999999999999998</v>
       </c>
-      <c r="R38" s="33">
+      <c r="S38" s="33">
         <v>1</v>
       </c>
-      <c r="S38" s="40">
+      <c r="T38" s="40">
         <f t="shared" si="6"/>
         <v>1.8280016618196831E-3</v>
       </c>
-      <c r="T38" s="39">
+      <c r="U38" s="39">
         <v>220</v>
       </c>
-      <c r="U38" s="41">
+      <c r="V38" s="41">
         <v>220</v>
       </c>
     </row>
-    <row r="39" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A39" s="33">
         <v>34</v>
       </c>
@@ -5214,60 +5641,63 @@
         <v>7</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>590</v>
-      </c>
-      <c r="F39" s="36" t="s">
-        <v>591</v>
-      </c>
-      <c r="G39" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H39" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I39" s="33" t="s">
-        <v>48</v>
+        <v>582</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>721</v>
+      </c>
+      <c r="G39" s="36" t="s">
+        <v>583</v>
+      </c>
+      <c r="H39" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I39" s="36" t="s">
+        <v>659</v>
       </c>
       <c r="J39" s="33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K39" s="33" t="s">
-        <v>590</v>
-      </c>
-      <c r="L39" s="33">
+        <v>43</v>
+      </c>
+      <c r="L39" s="33" t="s">
+        <v>582</v>
+      </c>
+      <c r="M39" s="33">
         <v>2000</v>
       </c>
-      <c r="M39" s="33">
+      <c r="N39" s="33">
         <v>45.205500000000001</v>
-      </c>
-      <c r="N39" s="33">
-        <v>46.289000000000001</v>
       </c>
       <c r="O39" s="33">
         <v>46.289000000000001</v>
       </c>
-      <c r="P39" s="39">
-        <f>ABS(M39*L39)</f>
+      <c r="P39" s="33">
+        <v>46.289000000000001</v>
+      </c>
+      <c r="Q39" s="39">
+        <f>ABS(N39*M39)</f>
         <v>90411</v>
       </c>
-      <c r="Q39" s="33">
+      <c r="R39" s="33">
         <v>23.76</v>
       </c>
-      <c r="R39" s="33">
+      <c r="S39" s="33">
         <v>1</v>
       </c>
-      <c r="S39" s="40">
+      <c r="T39" s="40">
         <f t="shared" si="6"/>
         <v>2.3968322438641332E-2</v>
       </c>
-      <c r="T39" s="39">
+      <c r="U39" s="39">
         <v>2167</v>
       </c>
-      <c r="U39" s="41">
+      <c r="V39" s="41">
         <v>2167</v>
       </c>
     </row>
-    <row r="40" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A40" s="33">
         <v>35</v>
       </c>
@@ -5282,60 +5712,63 @@
         <v>5</v>
       </c>
       <c r="E40" s="33" t="s">
-        <v>592</v>
-      </c>
-      <c r="F40" s="36" t="s">
-        <v>593</v>
-      </c>
-      <c r="G40" s="33" t="s">
+        <v>584</v>
+      </c>
+      <c r="F40" s="33" t="s">
+        <v>722</v>
+      </c>
+      <c r="G40" s="36" t="s">
+        <v>585</v>
+      </c>
+      <c r="H40" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I40" s="36" t="s">
+        <v>658</v>
+      </c>
+      <c r="J40" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H40" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I40" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J40" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K40" s="33" t="s">
-        <v>592</v>
-      </c>
-      <c r="L40" s="33">
+        <v>23</v>
+      </c>
+      <c r="L40" s="33" t="s">
+        <v>584</v>
+      </c>
+      <c r="M40" s="33">
         <v>1000</v>
       </c>
-      <c r="M40" s="33">
+      <c r="N40" s="33">
         <v>35.601500000000001</v>
-      </c>
-      <c r="N40" s="33">
-        <v>35.162700000000001</v>
       </c>
       <c r="O40" s="33">
         <v>35.162700000000001</v>
       </c>
-      <c r="P40" s="39">
-        <f>ABS(M40*L40)</f>
+      <c r="P40" s="33">
+        <v>35.162700000000001</v>
+      </c>
+      <c r="Q40" s="39">
+        <f>ABS(N40*M40)</f>
         <v>35601.5</v>
       </c>
-      <c r="Q40" s="33">
+      <c r="R40" s="33">
         <v>7.57</v>
       </c>
-      <c r="R40" s="33">
-        <v>0</v>
-      </c>
-      <c r="S40" s="40">
+      <c r="S40" s="33">
+        <v>0</v>
+      </c>
+      <c r="T40" s="40">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="T40" s="39">
+      <c r="U40" s="39">
         <v>-438</v>
       </c>
-      <c r="U40" s="45">
+      <c r="V40" s="45">
         <v>-438</v>
       </c>
     </row>
-    <row r="41" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A41" s="33">
         <v>36</v>
       </c>
@@ -5350,59 +5783,62 @@
         <v>2</v>
       </c>
       <c r="E41" s="33" t="s">
-        <v>594</v>
-      </c>
-      <c r="F41" s="36" t="s">
-        <v>595</v>
-      </c>
-      <c r="G41" s="33" t="s">
+        <v>586</v>
+      </c>
+      <c r="F41" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="G41" s="36" t="s">
+        <v>587</v>
+      </c>
+      <c r="H41" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I41" s="36" t="s">
+        <v>657</v>
+      </c>
+      <c r="J41" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H41" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I41" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J41" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K41" s="33" t="s">
-        <v>594</v>
-      </c>
-      <c r="L41" s="33">
+        <v>23</v>
+      </c>
+      <c r="L41" s="33" t="s">
+        <v>586</v>
+      </c>
+      <c r="M41" s="33">
         <v>700</v>
       </c>
-      <c r="M41" s="33">
+      <c r="N41" s="33">
         <v>79.950999999999993</v>
-      </c>
-      <c r="N41" s="33">
-        <v>79.498000000000005</v>
       </c>
       <c r="O41" s="33">
         <v>79.498000000000005</v>
       </c>
-      <c r="P41" s="39">
+      <c r="P41" s="33">
+        <v>79.498000000000005</v>
+      </c>
+      <c r="Q41" s="39">
         <v>55902</v>
       </c>
-      <c r="Q41" s="33">
+      <c r="R41" s="33">
         <v>5.63</v>
       </c>
-      <c r="R41" s="33">
-        <v>0</v>
-      </c>
-      <c r="S41" s="40">
-        <f t="shared" ref="S41:S44" si="7">IF(R41=1, ABS(N41-M41)/M41, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="T41" s="39">
+      <c r="S41" s="33">
+        <v>0</v>
+      </c>
+      <c r="T41" s="40">
+        <f t="shared" ref="T41:T44" si="7">IF(S41=1, ABS(O41-N41)/N41, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="U41" s="39">
         <v>-317</v>
       </c>
-      <c r="U41" s="45">
+      <c r="V41" s="45">
         <v>-317</v>
       </c>
     </row>
-    <row r="42" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A42" s="33">
         <v>37</v>
       </c>
@@ -5417,60 +5853,63 @@
         <v>2</v>
       </c>
       <c r="E42" s="33" t="s">
-        <v>596</v>
-      </c>
-      <c r="F42" s="36" t="s">
-        <v>597</v>
-      </c>
-      <c r="G42" s="33" t="s">
+        <v>588</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>724</v>
+      </c>
+      <c r="G42" s="36" t="s">
+        <v>589</v>
+      </c>
+      <c r="H42" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I42" s="36" t="s">
+        <v>656</v>
+      </c>
+      <c r="J42" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H42" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I42" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J42" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K42" s="33" t="s">
-        <v>596</v>
-      </c>
-      <c r="L42" s="33">
+        <v>23</v>
+      </c>
+      <c r="L42" s="33" t="s">
+        <v>588</v>
+      </c>
+      <c r="M42" s="33">
         <v>300</v>
       </c>
-      <c r="M42" s="33">
+      <c r="N42" s="33">
         <v>298.27</v>
-      </c>
-      <c r="N42" s="33">
-        <v>304.00940000000003</v>
       </c>
       <c r="O42" s="33">
         <v>304.00940000000003</v>
       </c>
-      <c r="P42" s="39">
-        <f>M42*L42</f>
+      <c r="P42" s="33">
+        <v>304.00940000000003</v>
+      </c>
+      <c r="Q42" s="39">
+        <f>N42*M42</f>
         <v>89481</v>
       </c>
-      <c r="Q42" s="33">
+      <c r="R42" s="33">
         <v>4.5599999999999996</v>
       </c>
-      <c r="R42" s="33">
+      <c r="S42" s="33">
         <v>1</v>
       </c>
-      <c r="S42" s="40">
+      <c r="T42" s="40">
         <f t="shared" si="7"/>
         <v>1.9242297247460509E-2</v>
       </c>
-      <c r="T42" s="39">
+      <c r="U42" s="39">
         <v>1721</v>
       </c>
-      <c r="U42" s="41">
+      <c r="V42" s="41">
         <v>1721</v>
       </c>
     </row>
-    <row r="43" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A43" s="33">
         <v>38</v>
       </c>
@@ -5485,60 +5924,63 @@
         <v>15</v>
       </c>
       <c r="E43" s="33" t="s">
-        <v>598</v>
-      </c>
-      <c r="F43" s="36" t="s">
-        <v>599</v>
-      </c>
-      <c r="G43" s="33" t="s">
+        <v>590</v>
+      </c>
+      <c r="F43" s="33" t="s">
+        <v>725</v>
+      </c>
+      <c r="G43" s="36" t="s">
+        <v>591</v>
+      </c>
+      <c r="H43" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I43" s="36" t="s">
+        <v>655</v>
+      </c>
+      <c r="J43" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H43" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I43" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J43" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K43" s="33" t="s">
-        <v>598</v>
-      </c>
-      <c r="L43" s="33">
+        <v>23</v>
+      </c>
+      <c r="L43" s="33" t="s">
+        <v>590</v>
+      </c>
+      <c r="M43" s="33">
         <v>-700</v>
       </c>
-      <c r="M43" s="33">
+      <c r="N43" s="33">
         <v>162.33920000000001</v>
-      </c>
-      <c r="N43" s="33">
-        <v>166.36</v>
       </c>
       <c r="O43" s="33">
         <v>166.36</v>
       </c>
-      <c r="P43" s="39">
-        <f>ABS(O43*L43)</f>
+      <c r="P43" s="33">
+        <v>166.36</v>
+      </c>
+      <c r="Q43" s="39">
+        <f>ABS(P43*M43)</f>
         <v>116452.00000000001</v>
       </c>
-      <c r="Q43" s="33">
+      <c r="R43" s="33">
         <v>11.47</v>
       </c>
-      <c r="R43" s="33">
-        <v>0</v>
-      </c>
-      <c r="S43" s="40">
+      <c r="S43" s="33">
+        <v>0</v>
+      </c>
+      <c r="T43" s="40">
         <f t="shared" si="7"/>
         <v>0</v>
       </c>
-      <c r="T43" s="39">
+      <c r="U43" s="39">
         <v>-2814</v>
       </c>
-      <c r="U43" s="45">
+      <c r="V43" s="45">
         <v>-2814</v>
       </c>
     </row>
-    <row r="44" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A44" s="33">
         <v>39</v>
       </c>
@@ -5553,60 +5995,63 @@
         <v>2</v>
       </c>
       <c r="E44" s="33" t="s">
-        <v>600</v>
-      </c>
-      <c r="F44" s="36" t="s">
-        <v>601</v>
-      </c>
-      <c r="G44" s="33" t="s">
+        <v>592</v>
+      </c>
+      <c r="F44" s="33" t="s">
+        <v>726</v>
+      </c>
+      <c r="G44" s="36" t="s">
+        <v>593</v>
+      </c>
+      <c r="H44" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I44" s="36" t="s">
+        <v>654</v>
+      </c>
+      <c r="J44" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H44" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I44" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J44" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K44" s="33" t="s">
-        <v>600</v>
-      </c>
-      <c r="L44" s="33">
+        <v>23</v>
+      </c>
+      <c r="L44" s="33" t="s">
+        <v>592</v>
+      </c>
+      <c r="M44" s="33">
         <v>400</v>
       </c>
-      <c r="M44" s="33">
+      <c r="N44" s="33">
         <v>310.77999999999997</v>
-      </c>
-      <c r="N44" s="33">
-        <v>313.61399999999998</v>
       </c>
       <c r="O44" s="33">
         <v>313.61399999999998</v>
       </c>
-      <c r="P44" s="39">
-        <f>ABS(M44*L44)</f>
+      <c r="P44" s="33">
+        <v>313.61399999999998</v>
+      </c>
+      <c r="Q44" s="39">
+        <f>ABS(N44*M44)</f>
         <v>124311.99999999999</v>
       </c>
-      <c r="Q44" s="33">
+      <c r="R44" s="33">
         <v>6.5</v>
       </c>
-      <c r="R44" s="33">
+      <c r="S44" s="33">
         <v>1</v>
       </c>
-      <c r="S44" s="40">
+      <c r="T44" s="40">
         <f t="shared" si="7"/>
         <v>9.1189909260570284E-3</v>
       </c>
-      <c r="T44" s="39">
+      <c r="U44" s="39">
         <v>1134</v>
       </c>
-      <c r="U44" s="41">
+      <c r="V44" s="41">
         <v>1134</v>
       </c>
     </row>
-    <row r="45" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A45" s="33">
         <v>40</v>
       </c>
@@ -5621,59 +6066,62 @@
         <v>0</v>
       </c>
       <c r="E45" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="F45" s="36" t="s">
-        <v>602</v>
-      </c>
-      <c r="G45" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H45" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I45" s="33" t="s">
-        <v>32</v>
+        <v>72</v>
+      </c>
+      <c r="F45" s="33" t="s">
+        <v>708</v>
+      </c>
+      <c r="G45" s="36" t="s">
+        <v>594</v>
+      </c>
+      <c r="H45" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I45" s="36" t="s">
+        <v>653</v>
       </c>
       <c r="J45" s="33" t="s">
-        <v>533</v>
+        <v>29</v>
       </c>
       <c r="K45" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="L45" s="33">
+        <v>525</v>
+      </c>
+      <c r="L45" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="M45" s="33">
         <v>-4</v>
       </c>
-      <c r="M45" s="33">
+      <c r="N45" s="33">
         <v>7840.75</v>
-      </c>
-      <c r="N45" s="33">
-        <v>7835.5</v>
       </c>
       <c r="O45" s="33">
         <v>7835.5</v>
       </c>
-      <c r="P45" s="39">
+      <c r="P45" s="33">
+        <v>7835.5</v>
+      </c>
+      <c r="Q45" s="39">
         <v>156718</v>
       </c>
-      <c r="Q45" s="33">
+      <c r="R45" s="33">
         <v>4.88</v>
       </c>
-      <c r="R45" s="33">
+      <c r="S45" s="33">
         <v>1</v>
       </c>
-      <c r="S45" s="40">
-        <f t="shared" ref="S45:S48" si="8">IF(R45=1, ABS(N45-M45)/M45, 0)</f>
+      <c r="T45" s="40">
+        <f t="shared" ref="T45:T48" si="8">IF(S45=1, ABS(O45-N45)/N45, 0)</f>
         <v>6.6957880304817775E-4</v>
       </c>
-      <c r="T45" s="39">
+      <c r="U45" s="39">
         <v>108</v>
       </c>
-      <c r="U45" s="41">
+      <c r="V45" s="41">
         <v>108</v>
       </c>
     </row>
-    <row r="46" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A46" s="33">
         <v>41</v>
       </c>
@@ -5688,60 +6136,63 @@
         <v>1</v>
       </c>
       <c r="E46" s="33" t="s">
-        <v>603</v>
-      </c>
-      <c r="F46" s="36" t="s">
-        <v>604</v>
-      </c>
-      <c r="G46" s="33" t="s">
+        <v>595</v>
+      </c>
+      <c r="F46" s="33" t="s">
+        <v>727</v>
+      </c>
+      <c r="G46" s="36" t="s">
+        <v>596</v>
+      </c>
+      <c r="H46" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I46" s="36" t="s">
+        <v>652</v>
+      </c>
+      <c r="J46" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H46" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I46" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J46" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K46" s="33" t="s">
-        <v>603</v>
-      </c>
-      <c r="L46" s="33">
+        <v>23</v>
+      </c>
+      <c r="L46" s="33" t="s">
+        <v>595</v>
+      </c>
+      <c r="M46" s="33">
         <v>2000</v>
       </c>
-      <c r="M46" s="33">
+      <c r="N46" s="33">
         <v>18.71</v>
-      </c>
-      <c r="N46" s="33">
-        <v>18.376999999999999</v>
       </c>
       <c r="O46" s="33">
         <v>18.376999999999999</v>
       </c>
-      <c r="P46" s="39">
-        <f>ABS(M46*L46)</f>
+      <c r="P46" s="33">
+        <v>18.376999999999999</v>
+      </c>
+      <c r="Q46" s="39">
+        <f>ABS(N46*M46)</f>
         <v>37420</v>
       </c>
-      <c r="Q46" s="33">
+      <c r="R46" s="33">
         <v>22.69</v>
       </c>
-      <c r="R46" s="33">
-        <v>0</v>
-      </c>
-      <c r="S46" s="40">
+      <c r="S46" s="33">
+        <v>0</v>
+      </c>
+      <c r="T46" s="40">
         <f t="shared" si="8"/>
         <v>0</v>
       </c>
-      <c r="T46" s="39">
+      <c r="U46" s="39">
         <v>-664</v>
       </c>
-      <c r="U46" s="45">
+      <c r="V46" s="45">
         <v>-664</v>
       </c>
     </row>
-    <row r="47" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A47" s="33">
         <v>42</v>
       </c>
@@ -5756,60 +6207,63 @@
         <v>15</v>
       </c>
       <c r="E47" s="33" t="s">
-        <v>605</v>
-      </c>
-      <c r="F47" s="36" t="s">
-        <v>606</v>
-      </c>
-      <c r="G47" s="33" t="s">
+        <v>597</v>
+      </c>
+      <c r="F47" s="33" t="s">
+        <v>728</v>
+      </c>
+      <c r="G47" s="36" t="s">
+        <v>598</v>
+      </c>
+      <c r="H47" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I47" s="36" t="s">
+        <v>651</v>
+      </c>
+      <c r="J47" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H47" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I47" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J47" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K47" s="33" t="s">
-        <v>605</v>
-      </c>
-      <c r="L47" s="33">
+        <v>23</v>
+      </c>
+      <c r="L47" s="33" t="s">
+        <v>597</v>
+      </c>
+      <c r="M47" s="33">
         <v>-600</v>
       </c>
-      <c r="M47" s="33">
+      <c r="N47" s="33">
         <v>268.09100000000001</v>
-      </c>
-      <c r="N47" s="33">
-        <v>262.3</v>
       </c>
       <c r="O47" s="33">
         <v>262.3</v>
       </c>
-      <c r="P47" s="39">
-        <f>ABS(O47*L47)</f>
+      <c r="P47" s="33">
+        <v>262.3</v>
+      </c>
+      <c r="Q47" s="39">
+        <f>ABS(P47*M47)</f>
         <v>157380</v>
       </c>
-      <c r="Q47" s="33">
+      <c r="R47" s="33">
         <v>10.1</v>
       </c>
-      <c r="R47" s="33">
+      <c r="S47" s="33">
         <v>1</v>
       </c>
-      <c r="S47" s="40">
+      <c r="T47" s="40">
         <f t="shared" si="8"/>
         <v>2.1600874329984955E-2</v>
       </c>
-      <c r="T47" s="39">
+      <c r="U47" s="39">
         <v>3476</v>
       </c>
-      <c r="U47" s="41">
+      <c r="V47" s="41">
         <v>3476</v>
       </c>
     </row>
-    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
       <c r="A48" s="33">
         <v>43</v>
       </c>
@@ -5824,60 +6278,63 @@
         <v>8</v>
       </c>
       <c r="E48" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="F48" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="G48" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H48" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I48" s="33" t="s">
-        <v>32</v>
+        <v>53</v>
+      </c>
+      <c r="F48" s="33" t="s">
+        <v>700</v>
+      </c>
+      <c r="G48" s="36" t="s">
+        <v>632</v>
+      </c>
+      <c r="H48" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I48" s="36" t="s">
+        <v>641</v>
       </c>
       <c r="J48" s="33" t="s">
-        <v>531</v>
+        <v>29</v>
       </c>
       <c r="K48" s="33" t="s">
-        <v>607</v>
-      </c>
-      <c r="L48" s="33">
+        <v>523</v>
+      </c>
+      <c r="L48" s="33" t="s">
+        <v>599</v>
+      </c>
+      <c r="M48" s="33">
         <v>30</v>
       </c>
-      <c r="M48" s="33">
+      <c r="N48" s="33">
         <v>17.652000000000001</v>
-      </c>
-      <c r="N48" s="33">
-        <v>18.277999999999999</v>
       </c>
       <c r="O48" s="33">
         <v>18.277999999999999</v>
       </c>
-      <c r="P48" s="39">
-        <f>ABS(M48*L48)*100</f>
+      <c r="P48" s="33">
+        <v>18.277999999999999</v>
+      </c>
+      <c r="Q48" s="39">
+        <f>ABS(N48*M48)*100</f>
         <v>52956.000000000007</v>
       </c>
-      <c r="Q48" s="33">
+      <c r="R48" s="33">
         <v>27.6</v>
       </c>
-      <c r="R48" s="33">
+      <c r="S48" s="33">
         <v>1</v>
       </c>
-      <c r="S48" s="40">
+      <c r="T48" s="40">
         <f t="shared" si="8"/>
         <v>3.5463403580330705E-2</v>
       </c>
-      <c r="T48" s="39">
+      <c r="U48" s="39">
         <v>1895</v>
       </c>
-      <c r="U48" s="41">
+      <c r="V48" s="41">
         <v>1895</v>
       </c>
     </row>
-    <row r="49" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A49" s="33">
         <v>44</v>
       </c>
@@ -5892,59 +6349,62 @@
         <v>1</v>
       </c>
       <c r="E49" s="33" t="s">
-        <v>608</v>
-      </c>
-      <c r="F49" s="36" t="s">
-        <v>609</v>
-      </c>
-      <c r="G49" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H49" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I49" s="33" t="s">
-        <v>32</v>
+        <v>600</v>
+      </c>
+      <c r="F49" s="33" t="s">
+        <v>729</v>
+      </c>
+      <c r="G49" s="36" t="s">
+        <v>601</v>
+      </c>
+      <c r="H49" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I49" s="36" t="s">
+        <v>650</v>
       </c>
       <c r="J49" s="33" t="s">
-        <v>124</v>
+        <v>29</v>
       </c>
       <c r="K49" s="33" t="s">
-        <v>610</v>
-      </c>
-      <c r="L49" s="33">
+        <v>116</v>
+      </c>
+      <c r="L49" s="33" t="s">
+        <v>602</v>
+      </c>
+      <c r="M49" s="33">
         <v>-2</v>
       </c>
-      <c r="M49" s="33">
+      <c r="N49" s="33">
         <v>3.327</v>
-      </c>
-      <c r="N49" s="33">
-        <v>3.26</v>
       </c>
       <c r="O49" s="33">
         <v>3.26</v>
       </c>
-      <c r="P49" s="39">
+      <c r="P49" s="33">
+        <v>3.26</v>
+      </c>
+      <c r="Q49" s="39">
         <v>16220</v>
       </c>
-      <c r="Q49" s="33">
+      <c r="R49" s="33">
         <v>5.44</v>
       </c>
-      <c r="R49" s="33">
+      <c r="S49" s="33">
         <v>1</v>
       </c>
-      <c r="S49" s="40">
-        <f t="shared" ref="S49:S52" si="9">IF(R49=1, ABS(N49-M49)/M49, 0)</f>
+      <c r="T49" s="40">
+        <f t="shared" ref="T49:T52" si="9">IF(S49=1, ABS(O49-N49)/N49, 0)</f>
         <v>2.0138262699128395E-2</v>
       </c>
-      <c r="T49" s="39">
+      <c r="U49" s="39">
         <v>338</v>
       </c>
-      <c r="U49" s="41">
+      <c r="V49" s="41">
         <v>338</v>
       </c>
     </row>
-    <row r="50" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A50" s="33">
         <v>45</v>
       </c>
@@ -5959,59 +6419,62 @@
         <v>0</v>
       </c>
       <c r="E50" s="33" t="s">
-        <v>612</v>
-      </c>
-      <c r="F50" s="36" t="s">
-        <v>613</v>
-      </c>
-      <c r="G50" s="33" t="s">
+        <v>604</v>
+      </c>
+      <c r="F50" s="33" t="s">
+        <v>730</v>
+      </c>
+      <c r="G50" s="36" t="s">
+        <v>605</v>
+      </c>
+      <c r="H50" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I50" s="36" t="s">
+        <v>649</v>
+      </c>
+      <c r="J50" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H50" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I50" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J50" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K50" s="33" t="s">
-        <v>612</v>
-      </c>
-      <c r="L50" s="33">
+        <v>23</v>
+      </c>
+      <c r="L50" s="33" t="s">
+        <v>604</v>
+      </c>
+      <c r="M50" s="33">
         <v>-750</v>
       </c>
-      <c r="M50" s="33">
+      <c r="N50" s="33">
         <v>274.52</v>
-      </c>
-      <c r="N50" s="33">
-        <v>271.52999999999997</v>
       </c>
       <c r="O50" s="33">
         <v>271.52999999999997</v>
       </c>
-      <c r="P50" s="39">
+      <c r="P50" s="33">
+        <v>271.52999999999997</v>
+      </c>
+      <c r="Q50" s="39">
         <v>205889</v>
       </c>
-      <c r="Q50" s="33">
+      <c r="R50" s="33">
         <v>10.91</v>
       </c>
-      <c r="R50" s="33">
+      <c r="S50" s="33">
         <v>1</v>
       </c>
-      <c r="S50" s="40">
+      <c r="T50" s="40">
         <f t="shared" si="9"/>
         <v>1.0891738306862922E-2</v>
       </c>
-      <c r="T50" s="39">
+      <c r="U50" s="39">
         <v>2245</v>
       </c>
-      <c r="U50" s="41">
+      <c r="V50" s="41">
         <v>2245</v>
       </c>
     </row>
-    <row r="51" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A51" s="33">
         <v>46</v>
       </c>
@@ -6026,60 +6489,63 @@
         <v>3</v>
       </c>
       <c r="E51" s="33" t="s">
-        <v>614</v>
-      </c>
-      <c r="F51" s="36" t="s">
-        <v>615</v>
-      </c>
-      <c r="G51" s="33" t="s">
+        <v>606</v>
+      </c>
+      <c r="F51" s="33" t="s">
+        <v>731</v>
+      </c>
+      <c r="G51" s="36" t="s">
+        <v>607</v>
+      </c>
+      <c r="H51" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I51" s="36" t="s">
+        <v>648</v>
+      </c>
+      <c r="J51" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H51" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I51" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J51" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K51" s="33" t="s">
-        <v>614</v>
-      </c>
-      <c r="L51" s="33">
+        <v>23</v>
+      </c>
+      <c r="L51" s="33" t="s">
+        <v>606</v>
+      </c>
+      <c r="M51" s="33">
         <v>700</v>
       </c>
-      <c r="M51" s="33">
+      <c r="N51" s="33">
         <v>84.41</v>
-      </c>
-      <c r="N51" s="33">
-        <v>82.27</v>
       </c>
       <c r="O51" s="33">
         <v>82.27</v>
       </c>
-      <c r="P51" s="39">
-        <f t="shared" ref="P51:P58" si="10">ABS(M51*L51)</f>
+      <c r="P51" s="33">
+        <v>82.27</v>
+      </c>
+      <c r="Q51" s="39">
+        <f t="shared" ref="Q51:Q58" si="10">ABS(N51*M51)</f>
         <v>59087</v>
       </c>
-      <c r="Q51" s="33">
+      <c r="R51" s="33">
         <v>9.65</v>
       </c>
-      <c r="R51" s="33">
-        <v>0</v>
-      </c>
-      <c r="S51" s="40">
+      <c r="S51" s="33">
+        <v>0</v>
+      </c>
+      <c r="T51" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T51" s="39">
+      <c r="U51" s="39">
         <v>-1498</v>
       </c>
-      <c r="U51" s="45">
+      <c r="V51" s="45">
         <v>-1498</v>
       </c>
     </row>
-    <row r="52" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A52" s="33">
         <v>47</v>
       </c>
@@ -6094,60 +6560,63 @@
         <v>4</v>
       </c>
       <c r="E52" s="33" t="s">
-        <v>616</v>
-      </c>
-      <c r="F52" s="36" t="s">
-        <v>617</v>
-      </c>
-      <c r="G52" s="33" t="s">
+        <v>608</v>
+      </c>
+      <c r="F52" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="G52" s="36" t="s">
+        <v>609</v>
+      </c>
+      <c r="H52" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I52" s="36" t="s">
+        <v>647</v>
+      </c>
+      <c r="J52" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H52" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I52" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J52" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K52" s="33" t="s">
-        <v>616</v>
-      </c>
-      <c r="L52" s="33">
+        <v>23</v>
+      </c>
+      <c r="L52" s="33" t="s">
+        <v>608</v>
+      </c>
+      <c r="M52" s="33">
         <v>-110</v>
       </c>
-      <c r="M52" s="33">
+      <c r="N52" s="33">
         <v>447.99</v>
-      </c>
-      <c r="N52" s="33">
-        <v>466.29</v>
       </c>
       <c r="O52" s="33">
         <v>466.29</v>
       </c>
-      <c r="P52" s="39">
+      <c r="P52" s="33">
+        <v>466.29</v>
+      </c>
+      <c r="Q52" s="39">
         <f t="shared" si="10"/>
         <v>49278.9</v>
       </c>
-      <c r="Q52" s="33">
+      <c r="R52" s="33">
         <v>2.68</v>
       </c>
-      <c r="R52" s="33">
-        <v>0</v>
-      </c>
-      <c r="S52" s="40">
+      <c r="S52" s="33">
+        <v>0</v>
+      </c>
+      <c r="T52" s="40">
         <f t="shared" si="9"/>
         <v>0</v>
       </c>
-      <c r="T52" s="39">
+      <c r="U52" s="39">
         <v>-2013</v>
       </c>
-      <c r="U52" s="45">
+      <c r="V52" s="45">
         <v>-2013</v>
       </c>
     </row>
-    <row r="53" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A53" s="33">
         <v>48</v>
       </c>
@@ -6162,60 +6631,63 @@
         <v>2</v>
       </c>
       <c r="E53" s="33" t="s">
-        <v>618</v>
-      </c>
-      <c r="F53" s="36" t="s">
-        <v>619</v>
-      </c>
-      <c r="G53" s="33" t="s">
+        <v>610</v>
+      </c>
+      <c r="F53" s="33" t="s">
+        <v>733</v>
+      </c>
+      <c r="G53" s="36" t="s">
+        <v>611</v>
+      </c>
+      <c r="H53" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I53" s="36" t="s">
+        <v>646</v>
+      </c>
+      <c r="J53" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H53" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I53" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J53" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K53" s="33" t="s">
-        <v>618</v>
-      </c>
-      <c r="L53" s="33">
+        <v>23</v>
+      </c>
+      <c r="L53" s="33" t="s">
+        <v>610</v>
+      </c>
+      <c r="M53" s="33">
         <v>4000</v>
       </c>
-      <c r="M53" s="33">
+      <c r="N53" s="33">
         <v>20.27</v>
-      </c>
-      <c r="N53" s="33">
-        <v>20.21</v>
       </c>
       <c r="O53" s="33">
         <v>20.21</v>
       </c>
-      <c r="P53" s="39">
+      <c r="P53" s="33">
+        <v>20.21</v>
+      </c>
+      <c r="Q53" s="39">
         <f t="shared" si="10"/>
         <v>81080</v>
       </c>
-      <c r="Q53" s="33">
+      <c r="R53" s="33">
         <v>5.4</v>
       </c>
-      <c r="R53" s="33">
-        <v>0</v>
-      </c>
-      <c r="S53" s="40">
-        <f t="shared" ref="S53:S55" si="11">IF(R53=1, ABS(N53-M53)/M53, 0)</f>
-        <v>0</v>
-      </c>
-      <c r="T53" s="39">
+      <c r="S53" s="33">
+        <v>0</v>
+      </c>
+      <c r="T53" s="40">
+        <f t="shared" ref="T53:T55" si="11">IF(S53=1, ABS(O53-N53)/N53, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="U53" s="39">
         <v>-214</v>
       </c>
-      <c r="U53" s="45">
+      <c r="V53" s="45">
         <v>-214</v>
       </c>
     </row>
-    <row r="54" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A54" s="33">
         <v>49</v>
       </c>
@@ -6230,60 +6702,63 @@
         <v>7</v>
       </c>
       <c r="E54" s="33" t="s">
-        <v>620</v>
-      </c>
-      <c r="F54" s="36" t="s">
-        <v>621</v>
-      </c>
-      <c r="G54" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="H54" s="36" t="s">
-        <v>622</v>
-      </c>
-      <c r="I54" s="33" t="s">
-        <v>48</v>
+        <v>612</v>
+      </c>
+      <c r="F54" s="33" t="s">
+        <v>734</v>
+      </c>
+      <c r="G54" s="36" t="s">
+        <v>613</v>
+      </c>
+      <c r="H54" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="I54" s="36" t="s">
+        <v>645</v>
       </c>
       <c r="J54" s="33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K54" s="33" t="s">
-        <v>620</v>
-      </c>
-      <c r="L54" s="33">
+        <v>43</v>
+      </c>
+      <c r="L54" s="33" t="s">
+        <v>612</v>
+      </c>
+      <c r="M54" s="33">
         <v>400</v>
       </c>
-      <c r="M54" s="33">
+      <c r="N54" s="33">
         <v>281.4135</v>
-      </c>
-      <c r="N54" s="33">
-        <v>282.18</v>
       </c>
       <c r="O54" s="33">
         <v>282.18</v>
       </c>
-      <c r="P54" s="39">
+      <c r="P54" s="33">
+        <v>282.18</v>
+      </c>
+      <c r="Q54" s="39">
         <f t="shared" si="10"/>
         <v>112565.4</v>
       </c>
-      <c r="Q54" s="33">
+      <c r="R54" s="33">
         <v>7.57</v>
       </c>
-      <c r="R54" s="33">
+      <c r="S54" s="33">
         <v>1</v>
       </c>
-      <c r="S54" s="40">
+      <c r="T54" s="40">
         <f t="shared" si="11"/>
         <v>2.7237499267093006E-3</v>
       </c>
-      <c r="T54" s="39">
+      <c r="U54" s="39">
         <v>307</v>
       </c>
-      <c r="U54" s="41">
+      <c r="V54" s="41">
         <v>307</v>
       </c>
     </row>
-    <row r="55" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A55" s="33">
         <v>49</v>
       </c>
@@ -6298,60 +6773,63 @@
         <v>7</v>
       </c>
       <c r="E55" s="33" t="s">
-        <v>623</v>
-      </c>
-      <c r="F55" s="36" t="s">
-        <v>624</v>
-      </c>
-      <c r="G55" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="H55" s="36" t="s">
-        <v>622</v>
-      </c>
-      <c r="I55" s="33" t="s">
-        <v>48</v>
+        <v>614</v>
+      </c>
+      <c r="F55" s="33" t="s">
+        <v>735</v>
+      </c>
+      <c r="G55" s="36" t="s">
+        <v>615</v>
+      </c>
+      <c r="H55" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="I55" s="36" t="s">
+        <v>645</v>
       </c>
       <c r="J55" s="33" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="K55" s="33" t="s">
-        <v>623</v>
-      </c>
-      <c r="L55" s="33">
+        <v>43</v>
+      </c>
+      <c r="L55" s="33" t="s">
+        <v>614</v>
+      </c>
+      <c r="M55" s="33">
         <v>-140</v>
       </c>
-      <c r="M55" s="33">
+      <c r="N55" s="33">
         <v>767.82</v>
-      </c>
-      <c r="N55" s="33">
-        <v>779.63</v>
       </c>
       <c r="O55" s="33">
         <v>779.63</v>
       </c>
-      <c r="P55" s="39">
+      <c r="P55" s="33">
+        <v>779.63</v>
+      </c>
+      <c r="Q55" s="39">
         <f t="shared" si="10"/>
         <v>107494.8</v>
       </c>
-      <c r="Q55" s="33">
+      <c r="R55" s="33">
         <v>4.0199999999999996</v>
       </c>
-      <c r="R55" s="33">
-        <v>0</v>
-      </c>
-      <c r="S55" s="40">
+      <c r="S55" s="33">
+        <v>0</v>
+      </c>
+      <c r="T55" s="40">
         <f t="shared" si="11"/>
         <v>0</v>
       </c>
-      <c r="T55" s="39">
+      <c r="U55" s="39">
         <v>-1653</v>
       </c>
-      <c r="U55" s="45">
+      <c r="V55" s="45">
         <v>-1653</v>
       </c>
     </row>
-    <row r="56" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A56" s="33">
         <v>50</v>
       </c>
@@ -6366,60 +6844,63 @@
         <v>1</v>
       </c>
       <c r="E56" s="33" t="s">
-        <v>625</v>
-      </c>
-      <c r="F56" s="36" t="s">
-        <v>626</v>
-      </c>
-      <c r="G56" s="33" t="s">
+        <v>616</v>
+      </c>
+      <c r="F56" s="33" t="s">
+        <v>736</v>
+      </c>
+      <c r="G56" s="36" t="s">
+        <v>617</v>
+      </c>
+      <c r="H56" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I56" s="36" t="s">
+        <v>644</v>
+      </c>
+      <c r="J56" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H56" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I56" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J56" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K56" s="33" t="s">
-        <v>625</v>
-      </c>
-      <c r="L56" s="33">
+        <v>23</v>
+      </c>
+      <c r="L56" s="33" t="s">
+        <v>616</v>
+      </c>
+      <c r="M56" s="33">
         <v>-100</v>
       </c>
-      <c r="M56" s="33">
+      <c r="N56" s="33">
         <v>447</v>
-      </c>
-      <c r="N56" s="33">
-        <v>434.77</v>
       </c>
       <c r="O56" s="33">
         <v>434.77</v>
       </c>
-      <c r="P56" s="39">
+      <c r="P56" s="33">
+        <v>434.77</v>
+      </c>
+      <c r="Q56" s="39">
         <f t="shared" si="10"/>
         <v>44700</v>
       </c>
-      <c r="Q56" s="33">
+      <c r="R56" s="33">
         <v>1.9</v>
       </c>
-      <c r="R56" s="33">
+      <c r="S56" s="33">
         <v>1</v>
       </c>
-      <c r="S56" s="40">
-        <f t="shared" ref="S56:S63" si="12">IF(R56=1, ABS(N56-M56)/M56, 0)</f>
+      <c r="T56" s="40">
+        <f t="shared" ref="T56:T63" si="12">IF(S56=1, ABS(O56-N56)/N56, 0)</f>
         <v>2.7360178970917266E-2</v>
       </c>
-      <c r="T56" s="39">
+      <c r="U56" s="39">
         <v>1222</v>
       </c>
-      <c r="U56" s="41">
+      <c r="V56" s="41">
         <v>1222</v>
       </c>
     </row>
-    <row r="57" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A57" s="33">
         <v>51</v>
       </c>
@@ -6434,60 +6915,63 @@
         <v>1</v>
       </c>
       <c r="E57" s="33" t="s">
-        <v>627</v>
-      </c>
-      <c r="F57" s="36" t="s">
-        <v>628</v>
-      </c>
-      <c r="G57" s="33" t="s">
+        <v>618</v>
+      </c>
+      <c r="F57" s="33" t="s">
+        <v>737</v>
+      </c>
+      <c r="G57" s="36" t="s">
+        <v>619</v>
+      </c>
+      <c r="H57" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I57" s="36" t="s">
+        <v>643</v>
+      </c>
+      <c r="J57" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H57" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I57" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J57" s="33" t="s">
-        <v>25</v>
-      </c>
       <c r="K57" s="33" t="s">
-        <v>627</v>
-      </c>
-      <c r="L57" s="33">
+        <v>23</v>
+      </c>
+      <c r="L57" s="33" t="s">
+        <v>618</v>
+      </c>
+      <c r="M57" s="33">
         <v>-100</v>
       </c>
-      <c r="M57" s="33">
+      <c r="N57" s="33">
         <v>674.15</v>
-      </c>
-      <c r="N57" s="33">
-        <v>666.83</v>
       </c>
       <c r="O57" s="33">
         <v>666.83</v>
       </c>
-      <c r="P57" s="39">
+      <c r="P57" s="33">
+        <v>666.83</v>
+      </c>
+      <c r="Q57" s="39">
         <f t="shared" si="10"/>
         <v>67415</v>
       </c>
-      <c r="Q57" s="33">
+      <c r="R57" s="33">
         <v>3.25</v>
       </c>
-      <c r="R57" s="33">
+      <c r="S57" s="33">
         <v>1</v>
       </c>
-      <c r="S57" s="40">
+      <c r="T57" s="40">
         <f t="shared" si="12"/>
         <v>1.0858117629607559E-2</v>
       </c>
-      <c r="T57" s="39">
+      <c r="U57" s="39">
         <v>880</v>
       </c>
-      <c r="U57" s="41">
+      <c r="V57" s="41">
         <v>880</v>
       </c>
     </row>
-    <row r="58" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A58" s="33">
         <v>52</v>
       </c>
@@ -6502,60 +6986,63 @@
         <v>0</v>
       </c>
       <c r="E58" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="F58" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="G58" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="F58" s="33" t="s">
+        <v>690</v>
+      </c>
+      <c r="G58" s="36" t="s">
+        <v>25</v>
+      </c>
+      <c r="H58" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I58" s="36" t="s">
+        <v>642</v>
+      </c>
+      <c r="J58" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="H58" s="36" t="s">
+      <c r="K58" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" s="33" t="s">
         <v>24</v>
       </c>
-      <c r="I58" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="J58" s="33" t="s">
-        <v>25</v>
-      </c>
-      <c r="K58" s="33" t="s">
-        <v>26</v>
-      </c>
-      <c r="L58" s="33">
+      <c r="M58" s="33">
         <v>200</v>
       </c>
-      <c r="M58" s="33">
+      <c r="N58" s="33">
         <v>326.27999999999997</v>
-      </c>
-      <c r="N58" s="33">
-        <v>332.03</v>
       </c>
       <c r="O58" s="33">
         <v>332.03</v>
       </c>
-      <c r="P58" s="39">
+      <c r="P58" s="33">
+        <v>332.03</v>
+      </c>
+      <c r="Q58" s="39">
         <f t="shared" si="10"/>
         <v>65255.999999999993</v>
       </c>
-      <c r="Q58" s="33">
+      <c r="R58" s="33">
         <v>2.59</v>
       </c>
-      <c r="R58" s="33">
+      <c r="S58" s="33">
         <v>1</v>
       </c>
-      <c r="S58" s="40">
+      <c r="T58" s="40">
         <f t="shared" si="12"/>
         <v>1.762290057619223E-2</v>
       </c>
-      <c r="T58" s="39">
+      <c r="U58" s="39">
         <v>1058</v>
       </c>
-      <c r="U58" s="41">
+      <c r="V58" s="41">
         <v>1058</v>
       </c>
     </row>
-    <row r="59" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A59" s="33">
         <v>53</v>
       </c>
@@ -6570,60 +7057,63 @@
         <v>13</v>
       </c>
       <c r="E59" s="33" t="s">
-        <v>58</v>
-      </c>
-      <c r="F59" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="G59" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H59" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I59" s="33" t="s">
-        <v>32</v>
+        <v>53</v>
+      </c>
+      <c r="F59" s="33" t="s">
+        <v>700</v>
+      </c>
+      <c r="G59" s="36" t="s">
+        <v>632</v>
+      </c>
+      <c r="H59" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I59" s="36" t="s">
+        <v>641</v>
       </c>
       <c r="J59" s="33" t="s">
-        <v>531</v>
+        <v>29</v>
       </c>
       <c r="K59" s="33" t="s">
-        <v>607</v>
-      </c>
-      <c r="L59" s="33">
+        <v>523</v>
+      </c>
+      <c r="L59" s="33" t="s">
+        <v>599</v>
+      </c>
+      <c r="M59" s="33">
         <v>15</v>
       </c>
-      <c r="M59" s="33">
+      <c r="N59" s="33">
         <v>17.533999999999999</v>
-      </c>
-      <c r="N59" s="33">
-        <v>17.913</v>
       </c>
       <c r="O59" s="33">
         <v>17.913</v>
       </c>
-      <c r="P59" s="39">
+      <c r="P59" s="33">
+        <v>17.913</v>
+      </c>
+      <c r="Q59" s="39">
         <v>26870</v>
       </c>
-      <c r="Q59" s="33">
+      <c r="R59" s="33">
         <v>6.9</v>
       </c>
-      <c r="R59" s="33">
+      <c r="S59" s="33">
         <v>1</v>
       </c>
-      <c r="S59" s="40">
+      <c r="T59" s="40">
         <f t="shared" si="12"/>
         <v>2.1615147713014791E-2</v>
       </c>
-      <c r="T59" s="39">
+      <c r="U59" s="39">
         <f>(26870-17905-8396)</f>
         <v>569</v>
       </c>
-      <c r="U59" s="41">
+      <c r="V59" s="41">
         <v>569</v>
       </c>
     </row>
-    <row r="60" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A60" s="33">
         <v>54</v>
       </c>
@@ -6638,60 +7128,63 @@
         <v>1</v>
       </c>
       <c r="E60" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="F60" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="G60" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H60" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I60" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="F60" s="33" t="s">
+        <v>692</v>
+      </c>
+      <c r="G60" s="36" t="s">
         <v>32</v>
       </c>
+      <c r="H60" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I60" s="36" t="s">
+        <v>640</v>
+      </c>
       <c r="J60" s="33" t="s">
-        <v>529</v>
+        <v>29</v>
       </c>
       <c r="K60" s="33" t="s">
-        <v>629</v>
-      </c>
-      <c r="L60" s="33">
+        <v>521</v>
+      </c>
+      <c r="L60" s="33" t="s">
+        <v>620</v>
+      </c>
+      <c r="M60" s="33">
         <v>10</v>
       </c>
-      <c r="M60" s="33">
+      <c r="N60" s="33">
         <v>1.1225000000000001</v>
-      </c>
-      <c r="N60" s="33">
-        <v>1.1251</v>
       </c>
       <c r="O60" s="33">
         <v>1.1251</v>
       </c>
-      <c r="P60" s="39">
+      <c r="P60" s="33">
+        <v>1.1251</v>
+      </c>
+      <c r="Q60" s="39">
         <f>1406000*1.121</f>
         <v>1576126</v>
       </c>
-      <c r="Q60" s="33">
+      <c r="R60" s="33">
         <v>42.5</v>
       </c>
-      <c r="R60" s="33">
+      <c r="S60" s="33">
         <v>1</v>
       </c>
-      <c r="S60" s="40">
+      <c r="T60" s="40">
         <f t="shared" si="12"/>
         <v>2.3162583518930384E-3</v>
       </c>
-      <c r="T60" s="39">
+      <c r="U60" s="39">
         <v>925</v>
       </c>
-      <c r="U60" s="41">
+      <c r="V60" s="41">
         <v>925</v>
       </c>
     </row>
-    <row r="61" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A61" s="33">
         <v>55</v>
       </c>
@@ -6706,60 +7199,63 @@
         <v>0</v>
       </c>
       <c r="E61" s="33" t="s">
-        <v>34</v>
-      </c>
-      <c r="F61" s="36" t="s">
-        <v>35</v>
-      </c>
-      <c r="G61" s="33" t="s">
-        <v>23</v>
-      </c>
-      <c r="H61" s="36" t="s">
-        <v>24</v>
-      </c>
-      <c r="I61" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="F61" s="33" t="s">
+        <v>692</v>
+      </c>
+      <c r="G61" s="36" t="s">
         <v>32</v>
       </c>
+      <c r="H61" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I61" s="36" t="s">
+        <v>640</v>
+      </c>
       <c r="J61" s="33" t="s">
-        <v>529</v>
+        <v>29</v>
       </c>
       <c r="K61" s="33" t="s">
-        <v>629</v>
-      </c>
-      <c r="L61" s="33">
+        <v>521</v>
+      </c>
+      <c r="L61" s="33" t="s">
+        <v>620</v>
+      </c>
+      <c r="M61" s="33">
         <v>15</v>
       </c>
-      <c r="M61" s="33">
+      <c r="N61" s="33">
         <v>1.1217200000000001</v>
-      </c>
-      <c r="N61" s="33">
-        <v>1.12226</v>
       </c>
       <c r="O61" s="33">
         <v>1.12226</v>
       </c>
-      <c r="P61" s="39">
-        <f>L61*125000*1.121</f>
+      <c r="P61" s="33">
+        <v>1.12226</v>
+      </c>
+      <c r="Q61" s="39">
+        <f>M61*125000*1.121</f>
         <v>2101875</v>
       </c>
-      <c r="Q61" s="33">
+      <c r="R61" s="33">
         <v>73.8</v>
       </c>
-      <c r="R61" s="33">
+      <c r="S61" s="33">
         <v>1</v>
       </c>
-      <c r="S61" s="40">
+      <c r="T61" s="40">
         <f t="shared" si="12"/>
         <v>4.8140355882036952E-4</v>
       </c>
-      <c r="T61" s="39">
+      <c r="U61" s="39">
         <v>1013</v>
       </c>
-      <c r="U61" s="41">
+      <c r="V61" s="41">
         <v>1013</v>
       </c>
     </row>
-    <row r="62" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A62" s="33">
         <v>56</v>
       </c>
@@ -6774,60 +7270,63 @@
         <v>7</v>
       </c>
       <c r="E62" s="33" t="s">
-        <v>88</v>
-      </c>
-      <c r="F62" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="G62" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="H62" s="36" t="s">
-        <v>630</v>
-      </c>
-      <c r="I62" s="33" t="s">
-        <v>32</v>
+        <v>80</v>
+      </c>
+      <c r="F62" s="33" t="s">
+        <v>697</v>
+      </c>
+      <c r="G62" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="H62" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="I62" s="36" t="s">
+        <v>639</v>
       </c>
       <c r="J62" s="33" t="s">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="K62" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="L62" s="33">
+        <v>114</v>
+      </c>
+      <c r="L62" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="M62" s="33">
         <v>5</v>
       </c>
-      <c r="M62" s="33">
+      <c r="N62" s="33">
         <v>4155.68</v>
-      </c>
-      <c r="N62" s="33">
-        <v>4185.5200000000004</v>
       </c>
       <c r="O62" s="33">
         <v>4185.5200000000004</v>
       </c>
-      <c r="P62" s="39">
-        <f>L62*O62*10</f>
+      <c r="P62" s="33">
+        <v>4185.5200000000004</v>
+      </c>
+      <c r="Q62" s="39">
+        <f>M62*P62*10</f>
         <v>209276.00000000003</v>
       </c>
-      <c r="Q62" s="33">
+      <c r="R62" s="33">
         <v>9.6</v>
       </c>
-      <c r="R62" s="33">
+      <c r="S62" s="33">
         <v>1</v>
       </c>
-      <c r="S62" s="40">
+      <c r="T62" s="40">
         <f t="shared" si="12"/>
         <v>7.1805336310784623E-3</v>
       </c>
-      <c r="T62" s="39">
+      <c r="U62" s="39">
         <v>1492</v>
       </c>
-      <c r="U62" s="41">
+      <c r="V62" s="41">
         <v>1492</v>
       </c>
     </row>
-    <row r="63" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A63" s="33">
         <v>56</v>
       </c>
@@ -6842,59 +7341,62 @@
         <v>7</v>
       </c>
       <c r="E63" s="33" t="s">
-        <v>631</v>
-      </c>
-      <c r="F63" s="36" t="s">
-        <v>632</v>
-      </c>
-      <c r="G63" s="33" t="s">
-        <v>30</v>
-      </c>
-      <c r="H63" s="36" t="s">
-        <v>630</v>
-      </c>
-      <c r="I63" s="33" t="s">
-        <v>32</v>
+        <v>621</v>
+      </c>
+      <c r="F63" s="33" t="s">
+        <v>738</v>
+      </c>
+      <c r="G63" s="36" t="s">
+        <v>622</v>
+      </c>
+      <c r="H63" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="I63" s="36" t="s">
+        <v>639</v>
       </c>
       <c r="J63" s="33" t="s">
-        <v>122</v>
+        <v>29</v>
       </c>
       <c r="K63" s="33" t="s">
-        <v>633</v>
-      </c>
-      <c r="L63" s="33">
+        <v>114</v>
+      </c>
+      <c r="L63" s="33" t="s">
+        <v>623</v>
+      </c>
+      <c r="M63" s="33">
         <v>-14</v>
       </c>
-      <c r="M63" s="33">
+      <c r="N63" s="33">
         <v>6.6361999999999997</v>
-      </c>
-      <c r="N63" s="33">
-        <v>6.5984999999999996</v>
       </c>
       <c r="O63" s="33">
         <v>6.5984999999999996</v>
       </c>
-      <c r="P63" s="39">
+      <c r="P63" s="33">
+        <v>6.5984999999999996</v>
+      </c>
+      <c r="Q63" s="39">
         <v>232267</v>
       </c>
-      <c r="Q63" s="33">
+      <c r="R63" s="33">
         <v>26.88</v>
       </c>
-      <c r="R63" s="33">
+      <c r="S63" s="33">
         <v>1</v>
       </c>
-      <c r="S63" s="40">
+      <c r="T63" s="40">
         <f t="shared" si="12"/>
         <v>5.6809619963232071E-3</v>
       </c>
-      <c r="T63" s="39">
+      <c r="U63" s="39">
         <v>1318</v>
       </c>
-      <c r="U63" s="41">
+      <c r="V63" s="41">
         <v>1318</v>
       </c>
     </row>
-    <row r="64" spans="1:22" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A64" s="33">
         <v>57</v>
       </c>
@@ -6909,61 +7411,64 @@
         <v>1</v>
       </c>
       <c r="E64" s="47" t="s">
-        <v>634</v>
-      </c>
-      <c r="F64" s="48" t="s">
-        <v>635</v>
-      </c>
-      <c r="G64" s="47" t="s">
+        <v>624</v>
+      </c>
+      <c r="F64" s="47" t="s">
+        <v>739</v>
+      </c>
+      <c r="G64" s="48" t="s">
+        <v>625</v>
+      </c>
+      <c r="H64" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="I64" s="48" t="s">
+        <v>638</v>
+      </c>
+      <c r="J64" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="H64" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="I64" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="J64" s="47" t="s">
-        <v>25</v>
-      </c>
       <c r="K64" s="47" t="s">
-        <v>634</v>
-      </c>
-      <c r="L64" s="47">
+        <v>23</v>
+      </c>
+      <c r="L64" s="47" t="s">
+        <v>624</v>
+      </c>
+      <c r="M64" s="47">
         <v>1220</v>
       </c>
-      <c r="M64" s="47">
+      <c r="N64" s="47">
         <v>7.74</v>
       </c>
-      <c r="N64" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O64" s="47">
+      <c r="O64" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="P64" s="47">
         <v>7.91</v>
       </c>
-      <c r="P64" s="49">
+      <c r="Q64" s="49">
         <v>4984</v>
       </c>
-      <c r="Q64" s="47">
+      <c r="R64" s="47">
         <v>1.01</v>
       </c>
-      <c r="R64" s="47" t="s">
-        <v>72</v>
-      </c>
       <c r="S64" s="47" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="T64" s="47" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="U64" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="V64" s="33">
+        <v>66</v>
+      </c>
+      <c r="V64" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="W64" s="33">
         <v>243</v>
       </c>
     </row>
-    <row r="65" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" s="33">
         <v>58</v>
       </c>
@@ -6978,61 +7483,64 @@
         <v>1</v>
       </c>
       <c r="E65" s="47" t="s">
-        <v>636</v>
-      </c>
-      <c r="F65" s="48" t="s">
+        <v>626</v>
+      </c>
+      <c r="F65" s="47" t="s">
+        <v>740</v>
+      </c>
+      <c r="G65" s="48" t="s">
+        <v>627</v>
+      </c>
+      <c r="H65" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="I65" s="48" t="s">
         <v>637</v>
       </c>
-      <c r="G65" s="47" t="s">
+      <c r="J65" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="H65" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="I65" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="J65" s="47" t="s">
-        <v>25</v>
-      </c>
       <c r="K65" s="47" t="s">
-        <v>636</v>
-      </c>
-      <c r="L65" s="47">
+        <v>23</v>
+      </c>
+      <c r="L65" s="47" t="s">
+        <v>626</v>
+      </c>
+      <c r="M65" s="47">
         <v>-504</v>
       </c>
-      <c r="M65" s="47">
+      <c r="N65" s="47">
         <v>28.216999999999999</v>
       </c>
-      <c r="N65" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O65" s="47">
+      <c r="O65" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="P65" s="47">
         <v>28.12</v>
       </c>
-      <c r="P65" s="49">
+      <c r="Q65" s="49">
         <v>14041</v>
       </c>
-      <c r="Q65" s="47">
+      <c r="R65" s="47">
         <v>2.33</v>
       </c>
-      <c r="R65" s="47" t="s">
-        <v>72</v>
-      </c>
       <c r="S65" s="47" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="T65" s="47" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="U65" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="V65" s="33">
+        <v>66</v>
+      </c>
+      <c r="V65" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="W65" s="33">
         <v>49</v>
       </c>
     </row>
-    <row r="66" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66" s="33">
         <v>59</v>
       </c>
@@ -7047,61 +7555,64 @@
         <v>1</v>
       </c>
       <c r="E66" s="47" t="s">
-        <v>638</v>
-      </c>
-      <c r="F66" s="48" t="s">
-        <v>639</v>
-      </c>
-      <c r="G66" s="47" t="s">
+        <v>628</v>
+      </c>
+      <c r="F66" s="47" t="s">
+        <v>741</v>
+      </c>
+      <c r="G66" s="48" t="s">
+        <v>629</v>
+      </c>
+      <c r="H66" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="I66" s="48" t="s">
+        <v>636</v>
+      </c>
+      <c r="J66" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="H66" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="I66" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="J66" s="47" t="s">
-        <v>25</v>
-      </c>
       <c r="K66" s="47" t="s">
-        <v>638</v>
-      </c>
-      <c r="L66" s="47">
+        <v>23</v>
+      </c>
+      <c r="L66" s="47" t="s">
+        <v>628</v>
+      </c>
+      <c r="M66" s="47">
         <v>-1956</v>
       </c>
-      <c r="M66" s="47">
+      <c r="N66" s="47">
         <v>46.65</v>
       </c>
-      <c r="N66" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O66" s="47">
+      <c r="O66" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="P66" s="47">
         <v>46.5</v>
       </c>
-      <c r="P66" s="49">
+      <c r="Q66" s="49">
         <v>90954</v>
       </c>
-      <c r="Q66" s="47">
+      <c r="R66" s="47">
         <v>4.32</v>
       </c>
-      <c r="R66" s="47" t="s">
-        <v>72</v>
-      </c>
       <c r="S66" s="47" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="T66" s="47" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="U66" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="V66" s="33">
+        <v>66</v>
+      </c>
+      <c r="V66" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="W66" s="33">
         <v>303</v>
       </c>
     </row>
-    <row r="67" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" s="33">
         <v>60</v>
       </c>
@@ -7116,156 +7627,161 @@
         <v>1</v>
       </c>
       <c r="E67" s="47" t="s">
-        <v>640</v>
-      </c>
-      <c r="F67" s="48" t="s">
-        <v>641</v>
-      </c>
-      <c r="G67" s="47" t="s">
+        <v>630</v>
+      </c>
+      <c r="F67" s="47" t="s">
+        <v>742</v>
+      </c>
+      <c r="G67" s="48" t="s">
+        <v>631</v>
+      </c>
+      <c r="H67" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="I67" s="48" t="s">
+        <v>635</v>
+      </c>
+      <c r="J67" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="H67" s="48" t="s">
-        <v>24</v>
-      </c>
-      <c r="I67" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="J67" s="47" t="s">
-        <v>25</v>
-      </c>
       <c r="K67" s="47" t="s">
-        <v>640</v>
-      </c>
-      <c r="L67" s="47">
+        <v>23</v>
+      </c>
+      <c r="L67" s="47" t="s">
+        <v>630</v>
+      </c>
+      <c r="M67" s="47">
         <v>-310</v>
       </c>
-      <c r="M67" s="47">
+      <c r="N67" s="47">
         <v>388.43</v>
       </c>
-      <c r="N67" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="O67" s="47">
+      <c r="O67" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="P67" s="47">
         <v>384.22</v>
       </c>
-      <c r="P67" s="49">
+      <c r="Q67" s="49">
         <v>115266</v>
       </c>
-      <c r="Q67" s="47">
+      <c r="R67" s="47">
         <v>3.66</v>
       </c>
-      <c r="R67" s="47" t="s">
-        <v>72</v>
-      </c>
       <c r="S67" s="47" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="T67" s="47" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="U67" s="47" t="s">
-        <v>72</v>
-      </c>
-      <c r="V67" s="33">
+        <v>66</v>
+      </c>
+      <c r="V67" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="W67" s="33">
         <v>1265</v>
       </c>
     </row>
-    <row r="68" spans="1:24" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="B68" s="34"/>
       <c r="C68" s="34"/>
       <c r="D68" s="35"/>
-      <c r="F68" s="36"/>
-      <c r="H68" s="36"/>
-      <c r="P68" s="39"/>
-      <c r="S68" s="40"/>
-      <c r="T68" s="39"/>
-      <c r="U68" s="41"/>
-    </row>
-    <row r="69" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="F69" s="36"/>
-      <c r="H69" s="36"/>
-    </row>
-    <row r="70" spans="1:24" x14ac:dyDescent="0.25">
+      <c r="G68" s="36"/>
+      <c r="I68" s="36"/>
+      <c r="Q68" s="39"/>
+      <c r="T68" s="40"/>
+      <c r="U68" s="39"/>
+      <c r="V68" s="41"/>
+    </row>
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="G69" s="36"/>
+      <c r="I69" s="36"/>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D70" s="51" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="E70" s="46">
         <f>AVERAGE(D2:D63)</f>
         <v>6.4838709677419351</v>
       </c>
-      <c r="F70" s="36"/>
-      <c r="H70" s="36"/>
-      <c r="U70" s="39">
-        <f>SUM(U2:U68)</f>
-        <v>88002.47</v>
-      </c>
+      <c r="F70" s="46"/>
+      <c r="G70" s="36"/>
+      <c r="I70" s="36"/>
       <c r="V70" s="39">
         <f>SUM(V2:V68)</f>
-        <v>1860</v>
+        <v>88002.47</v>
       </c>
       <c r="W70" s="39">
         <f>SUM(W2:W68)</f>
-        <v>0</v>
-      </c>
-      <c r="X70" s="39"/>
-    </row>
-    <row r="71" spans="1:24" x14ac:dyDescent="0.25">
+        <v>1860</v>
+      </c>
+      <c r="X70" s="39">
+        <f>SUM(X2:X68)</f>
+        <v>0</v>
+      </c>
+      <c r="Y70" s="39"/>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="D71" s="51" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="E71" s="46">
         <f>AVERAGE(D2:D11,D13,D15:D63)</f>
         <v>4.7666666666666666</v>
       </c>
-      <c r="F71" s="36"/>
-      <c r="U71" s="52" t="s">
-        <v>104</v>
-      </c>
-      <c r="V71" s="36" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="72" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="F72" s="36"/>
-      <c r="U72" s="33" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="73" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="F73" s="36"/>
-      <c r="U73" s="39">
-        <f>U70+V70</f>
+      <c r="F71" s="46"/>
+      <c r="G71" s="36"/>
+      <c r="V71" s="52" t="s">
+        <v>96</v>
+      </c>
+      <c r="W71" s="36" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="G72" s="36"/>
+      <c r="V72" s="33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="G73" s="36"/>
+      <c r="V73" s="39">
+        <f>V70+W70</f>
         <v>89862.47</v>
       </c>
     </row>
-    <row r="74" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="F74" s="36"/>
-    </row>
-    <row r="75" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="F75" s="36"/>
-      <c r="U75" s="36" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="76" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="F76" s="36"/>
-      <c r="U76" s="39">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="G74" s="36"/>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="G75" s="36"/>
+      <c r="V75" s="36" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="G76" s="36"/>
+      <c r="V76" s="39">
         <v>333000</v>
       </c>
     </row>
-    <row r="78" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="U78" s="33" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="79" spans="1:24" x14ac:dyDescent="0.25">
-      <c r="U79" s="53">
-        <f>U73/U76</f>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V78" s="33" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V79" s="53">
+        <f>V73/V76</f>
         <v>0.26985726726726728</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:U16">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B2:V16">
     <sortCondition ref="B2:B16"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7289,16 +7805,16 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="22" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B1" s="5" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="C1" s="22" t="s">
-        <v>111</v>
+        <v>103</v>
       </c>
       <c r="D1" s="23" t="s">
-        <v>112</v>
+        <v>104</v>
       </c>
       <c r="G1" s="25"/>
     </row>
@@ -8517,7 +9033,7 @@
         <v>1.3941407429779523E-3</v>
       </c>
       <c r="F74" s="25" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="G74" s="27">
         <f>AVERAGE(C3:C93)</f>
@@ -8544,7 +9060,7 @@
         <v>9.4992906295542062E-3</v>
       </c>
       <c r="F75" s="25" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G75" s="27">
         <f>_xlfn.STDEV.S(C3:C93)</f>
@@ -8571,7 +9087,7 @@
         <v>-5.9729103776628928E-3</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
@@ -8598,7 +9114,7 @@
         <v>4.4963812546586836E-4</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G77" s="29">
         <f>_xlfn.STDEV.S(D2:D93)*SQRT(252)</f>
@@ -8625,7 +9141,7 @@
         <v>8.3734501065908466E-3</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="G78" s="29" cm="1">
         <f t="array" ref="G78">PRODUCT(1+D3:D93)-1</f>
@@ -8652,7 +9168,7 @@
         <v>9.6529467705530299E-4</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="G79" s="29" cm="1">
         <f t="array" ref="G79">PRODUCT(1+D2:D93)^(252/COUNT(D2:D93))-1</f>
@@ -8936,73 +9452,73 @@
   <sheetData>
     <row r="1" spans="1:23" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>514</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>515</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>521</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>114</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>522</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="H1" s="8" t="s">
         <v>523</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>524</v>
-      </c>
-      <c r="E1" s="8" t="s">
+      <c r="I1" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="J1" s="8" t="s">
+        <v>112</v>
+      </c>
+      <c r="K1" s="8" t="s">
+        <v>116</v>
+      </c>
+      <c r="L1" s="8" t="s">
+        <v>43</v>
+      </c>
+      <c r="M1" s="9" t="s">
+        <v>517</v>
+      </c>
+      <c r="N1" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="O1" s="8" t="s">
+        <v>519</v>
+      </c>
+      <c r="P1" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="Q1" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="R1" s="8" t="s">
         <v>529</v>
       </c>
-      <c r="F1" s="8" t="s">
-        <v>122</v>
-      </c>
-      <c r="G1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>530</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>531</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>533</v>
-      </c>
-      <c r="J1" s="8" t="s">
-        <v>120</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>124</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>48</v>
-      </c>
-      <c r="M1" s="9" t="s">
-        <v>525</v>
-      </c>
-      <c r="N1" s="8" t="s">
-        <v>526</v>
-      </c>
-      <c r="O1" s="8" t="s">
-        <v>527</v>
-      </c>
-      <c r="P1" s="8" t="s">
-        <v>535</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>536</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>537</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>538</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>539</v>
-      </c>
       <c r="U1" s="8" t="s">
-        <v>589</v>
+        <v>581</v>
       </c>
       <c r="V1" s="8" t="s">
-        <v>611</v>
+        <v>603</v>
       </c>
       <c r="W1" s="8" t="s">
-        <v>528</v>
+        <v>520</v>
       </c>
     </row>
     <row r="2" spans="1:23" x14ac:dyDescent="0.25">
@@ -16347,386 +16863,386 @@
   <sheetData>
     <row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>122</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>126</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>533</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>130</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>134</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>541</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>136</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>534</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>145</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>542</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="3" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="K4" s="3" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="3" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>181</v>
+        <v>173</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="3" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>184</v>
+        <v>176</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="K6" s="3" t="s">
-        <v>186</v>
+        <v>178</v>
       </c>
       <c r="L6" s="3" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>188</v>
+        <v>180</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>189</v>
+        <v>181</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>191</v>
+        <v>183</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>192</v>
+        <v>184</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>194</v>
+        <v>186</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>195</v>
+        <v>187</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>196</v>
+        <v>188</v>
       </c>
       <c r="K7" s="3" t="s">
-        <v>197</v>
+        <v>189</v>
       </c>
       <c r="L7" s="3" t="s">
-        <v>198</v>
+        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>199</v>
+        <v>191</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>200</v>
+        <v>192</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>201</v>
+        <v>193</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="3" t="s">
-        <v>202</v>
+        <v>194</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="3" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>204</v>
+        <v>196</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>205</v>
+        <v>197</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>206</v>
+        <v>198</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>207</v>
+        <v>199</v>
       </c>
       <c r="L8" s="3" t="s">
-        <v>208</v>
+        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
-        <v>209</v>
+        <v>201</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>210</v>
+        <v>202</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="3" t="s">
-        <v>211</v>
+        <v>203</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="3" t="s">
-        <v>193</v>
+        <v>185</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>213</v>
+        <v>205</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>214</v>
+        <v>206</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>215</v>
+        <v>207</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>216</v>
+        <v>208</v>
       </c>
       <c r="L9" s="3" t="s">
-        <v>217</v>
+        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
-        <v>218</v>
+        <v>210</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>219</v>
+        <v>211</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="3" t="s">
-        <v>567</v>
+        <v>559</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="3" t="s">
-        <v>203</v>
+        <v>195</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="L11" s="3" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -16737,22 +17253,22 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="3" t="s">
-        <v>212</v>
+        <v>204</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>534</v>
+        <v>526</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -16763,20 +17279,20 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="3" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -16787,20 +17303,20 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="3" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="K14" s="3" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -16811,20 +17327,20 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="3" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="K15" s="3" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>254</v>
+        <v>246</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -16835,25 +17351,25 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="3" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
-        <v>256</v>
+        <v>248</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>257</v>
+        <v>249</v>
       </c>
       <c r="K16" s="3" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>259</v>
+        <v>251</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>260</v>
+        <v>252</v>
       </c>
       <c r="B17" s="3">
         <v>7</v>
@@ -16863,25 +17379,25 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="3" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
-        <v>262</v>
+        <v>254</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>263</v>
+        <v>255</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>265</v>
+        <v>257</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="B18" s="3">
         <v>10</v>
@@ -16891,25 +17407,25 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="3" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3" t="s">
-        <v>267</v>
+        <v>259</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>268</v>
+        <v>260</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>264</v>
+        <v>256</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>270</v>
+        <v>262</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="B19" s="3">
         <v>10</v>
@@ -16919,25 +17435,25 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="3" t="s">
-        <v>255</v>
+        <v>247</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3" t="s">
-        <v>272</v>
+        <v>264</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>273</v>
+        <v>265</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>269</v>
+        <v>261</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>275</v>
+        <v>267</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="B20" s="3">
         <v>6</v>
@@ -16947,25 +17463,25 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="3" t="s">
-        <v>261</v>
+        <v>253</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3" t="s">
-        <v>277</v>
+        <v>269</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>278</v>
+        <v>270</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>274</v>
+        <v>266</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>280</v>
+        <v>272</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="B21" s="3">
         <v>8</v>
@@ -16975,25 +17491,25 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="3" t="s">
-        <v>266</v>
+        <v>258</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3" t="s">
-        <v>282</v>
+        <v>274</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>279</v>
+        <v>271</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>285</v>
+        <v>277</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="B22" s="3">
         <v>2</v>
@@ -17003,25 +17519,25 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="3" t="s">
-        <v>565</v>
+        <v>557</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3" t="s">
-        <v>287</v>
+        <v>279</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>288</v>
+        <v>280</v>
       </c>
       <c r="K22" s="3" t="s">
-        <v>284</v>
+        <v>276</v>
       </c>
       <c r="L22" s="3" t="s">
-        <v>289</v>
+        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="B23" s="3">
         <v>149</v>
@@ -17031,23 +17547,23 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="3" t="s">
-        <v>271</v>
+        <v>263</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3" t="s">
-        <v>291</v>
+        <v>283</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>292</v>
+        <v>284</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3" t="s">
-        <v>293</v>
+        <v>285</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>294</v>
+        <v>286</v>
       </c>
       <c r="B24" s="3">
         <v>11</v>
@@ -17057,21 +17573,21 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="3" t="s">
-        <v>276</v>
+        <v>268</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3" t="s">
-        <v>296</v>
+        <v>288</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>297</v>
+        <v>289</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="B25" s="3">
         <v>97</v>
@@ -17081,21 +17597,21 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="3" t="s">
-        <v>558</v>
+        <v>550</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3" t="s">
-        <v>299</v>
+        <v>291</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>300</v>
+        <v>292</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>128</v>
+        <v>120</v>
       </c>
       <c r="B26" s="3">
         <v>32</v>
@@ -17105,21 +17621,21 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="3" t="s">
-        <v>281</v>
+        <v>273</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3" t="s">
-        <v>302</v>
+        <v>294</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>303</v>
+        <v>295</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
     </row>
     <row r="27" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A27" s="3" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="B27" s="3">
         <v>20</v>
@@ -17129,21 +17645,21 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="3" t="s">
-        <v>286</v>
+        <v>278</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3" t="s">
-        <v>305</v>
+        <v>297</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>306</v>
+        <v>298</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
     </row>
     <row r="28" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="B28" s="3">
         <v>22</v>
@@ -17153,21 +17669,21 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="3" t="s">
-        <v>290</v>
+        <v>282</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3" t="s">
-        <v>308</v>
+        <v>300</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>309</v>
+        <v>301</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
     </row>
     <row r="29" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>310</v>
+        <v>302</v>
       </c>
       <c r="B29" s="3">
         <f>SUM(B17:B28)</f>
@@ -17178,14 +17694,14 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="3" t="s">
-        <v>295</v>
+        <v>287</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3" t="s">
-        <v>312</v>
+        <v>304</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>313</v>
+        <v>305</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
@@ -17198,14 +17714,14 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="3" t="s">
-        <v>298</v>
+        <v>290</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3" t="s">
-        <v>315</v>
+        <v>307</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>316</v>
+        <v>308</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="2"/>
@@ -17218,14 +17734,14 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="3" t="s">
-        <v>560</v>
+        <v>552</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3" t="s">
-        <v>318</v>
+        <v>310</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>319</v>
+        <v>311</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="2"/>
@@ -17238,14 +17754,14 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="3" t="s">
-        <v>546</v>
+        <v>538</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3" t="s">
-        <v>321</v>
+        <v>313</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>322</v>
+        <v>314</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="2"/>
@@ -17258,14 +17774,14 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="3" t="s">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3" t="s">
-        <v>324</v>
+        <v>316</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>325</v>
+        <v>317</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="2"/>
@@ -17278,11 +17794,11 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="3" t="s">
-        <v>301</v>
+        <v>293</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>327</v>
+        <v>319</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="2"/>
@@ -17296,11 +17812,11 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="3" t="s">
-        <v>304</v>
+        <v>296</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3" t="s">
-        <v>329</v>
+        <v>321</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="2"/>
@@ -17308,1037 +17824,1037 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G36" s="3" t="s">
-        <v>307</v>
+        <v>299</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3" t="s">
-        <v>331</v>
+        <v>323</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G37" s="3" t="s">
-        <v>311</v>
+        <v>303</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>333</v>
+        <v>325</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G38" s="3" t="s">
-        <v>573</v>
+        <v>565</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G39" s="3" t="s">
-        <v>549</v>
+        <v>541</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G40" s="3" t="s">
-        <v>314</v>
+        <v>306</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>339</v>
+        <v>331</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G41" s="3" t="s">
-        <v>317</v>
+        <v>309</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>341</v>
+        <v>333</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G42" s="3" t="s">
-        <v>556</v>
+        <v>548</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>343</v>
+        <v>335</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G43" s="3" t="s">
-        <v>320</v>
+        <v>312</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>345</v>
+        <v>337</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G44" s="3" t="s">
-        <v>323</v>
+        <v>315</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>347</v>
+        <v>339</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G45" s="3" t="s">
-        <v>554</v>
+        <v>546</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>349</v>
+        <v>341</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G46" s="3" t="s">
-        <v>326</v>
+        <v>318</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>351</v>
+        <v>343</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G47" s="3" t="s">
-        <v>328</v>
+        <v>320</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>353</v>
+        <v>345</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G48" s="3" t="s">
-        <v>330</v>
+        <v>322</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>355</v>
+        <v>347</v>
       </c>
     </row>
     <row r="49" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G49" s="3" t="s">
-        <v>557</v>
+        <v>549</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>357</v>
+        <v>349</v>
       </c>
     </row>
     <row r="50" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G50" s="3" t="s">
-        <v>332</v>
+        <v>324</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>359</v>
+        <v>351</v>
       </c>
     </row>
     <row r="51" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G51" s="3" t="s">
-        <v>334</v>
+        <v>326</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>361</v>
+        <v>353</v>
       </c>
     </row>
     <row r="52" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G52" s="3" t="s">
-        <v>336</v>
+        <v>328</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>363</v>
+        <v>355</v>
       </c>
     </row>
     <row r="53" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G53" s="3" t="s">
-        <v>338</v>
+        <v>330</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>365</v>
+        <v>357</v>
       </c>
     </row>
     <row r="54" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G54" s="3" t="s">
-        <v>340</v>
+        <v>332</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>367</v>
+        <v>359</v>
       </c>
     </row>
     <row r="55" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G55" s="3" t="s">
-        <v>342</v>
+        <v>334</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>369</v>
+        <v>361</v>
       </c>
     </row>
     <row r="56" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G56" s="3" t="s">
-        <v>344</v>
+        <v>336</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>371</v>
+        <v>363</v>
       </c>
     </row>
     <row r="57" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G57" s="3" t="s">
-        <v>346</v>
+        <v>338</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>373</v>
+        <v>365</v>
       </c>
     </row>
     <row r="58" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G58" s="3" t="s">
-        <v>348</v>
+        <v>340</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
     </row>
     <row r="59" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G59" s="3" t="s">
-        <v>350</v>
+        <v>342</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
     </row>
     <row r="60" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G60" s="3" t="s">
-        <v>352</v>
+        <v>344</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
     </row>
     <row r="61" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G61" s="3" t="s">
-        <v>570</v>
+        <v>562</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
     </row>
     <row r="62" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G62" s="3" t="s">
-        <v>354</v>
+        <v>346</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
     </row>
     <row r="63" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G63" s="3" t="s">
-        <v>356</v>
+        <v>348</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
     </row>
     <row r="64" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G64" s="3" t="s">
-        <v>358</v>
+        <v>350</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
     </row>
     <row r="65" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G65" s="3" t="s">
-        <v>360</v>
+        <v>352</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
     </row>
     <row r="66" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G66" s="3" t="s">
-        <v>362</v>
+        <v>354</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
     </row>
     <row r="67" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G67" s="3" t="s">
-        <v>364</v>
+        <v>356</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
     </row>
     <row r="68" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G68" s="3" t="s">
-        <v>366</v>
+        <v>358</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>395</v>
+        <v>387</v>
       </c>
     </row>
     <row r="69" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G69" s="3" t="s">
-        <v>368</v>
+        <v>360</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>397</v>
+        <v>389</v>
       </c>
     </row>
     <row r="70" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G70" s="3" t="s">
-        <v>370</v>
+        <v>362</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
     </row>
     <row r="71" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G71" s="3" t="s">
-        <v>372</v>
+        <v>364</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
     </row>
     <row r="72" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G72" s="3" t="s">
-        <v>374</v>
+        <v>366</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
     </row>
     <row r="73" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G73" s="3" t="s">
-        <v>376</v>
+        <v>368</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
     </row>
     <row r="74" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G74" s="3" t="s">
-        <v>378</v>
+        <v>370</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
     </row>
     <row r="75" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G75" s="3" t="s">
-        <v>562</v>
+        <v>554</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>409</v>
+        <v>401</v>
       </c>
     </row>
     <row r="76" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G76" s="3" t="s">
-        <v>380</v>
+        <v>372</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>411</v>
+        <v>403</v>
       </c>
     </row>
     <row r="77" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G77" s="3" t="s">
-        <v>382</v>
+        <v>374</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>413</v>
+        <v>405</v>
       </c>
     </row>
     <row r="78" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G78" s="3" t="s">
-        <v>384</v>
+        <v>376</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>415</v>
+        <v>407</v>
       </c>
     </row>
     <row r="79" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G79" s="3" t="s">
-        <v>386</v>
+        <v>378</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>417</v>
+        <v>409</v>
       </c>
     </row>
     <row r="80" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G80" s="3" t="s">
-        <v>388</v>
+        <v>380</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>419</v>
+        <v>411</v>
       </c>
     </row>
     <row r="81" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G81" s="3" t="s">
-        <v>390</v>
+        <v>382</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>421</v>
+        <v>413</v>
       </c>
     </row>
     <row r="82" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G82" s="3" t="s">
-        <v>392</v>
+        <v>384</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>423</v>
+        <v>415</v>
       </c>
     </row>
     <row r="83" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G83" s="3" t="s">
-        <v>394</v>
+        <v>386</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
     </row>
     <row r="84" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G84" s="3" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>427</v>
+        <v>419</v>
       </c>
     </row>
     <row r="85" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G85" s="3" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>429</v>
+        <v>421</v>
       </c>
     </row>
     <row r="86" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G86" s="3" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>431</v>
+        <v>423</v>
       </c>
     </row>
     <row r="87" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G87" s="3" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>433</v>
+        <v>425</v>
       </c>
     </row>
     <row r="88" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G88" s="3" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>435</v>
+        <v>427</v>
       </c>
     </row>
     <row r="89" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G89" s="3" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>437</v>
+        <v>429</v>
       </c>
     </row>
     <row r="90" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G90" s="3" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
     </row>
     <row r="91" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G91" s="3" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>441</v>
+        <v>433</v>
       </c>
     </row>
     <row r="92" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G92" s="3" t="s">
-        <v>412</v>
+        <v>404</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>443</v>
+        <v>435</v>
       </c>
     </row>
     <row r="93" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G93" s="3" t="s">
-        <v>414</v>
+        <v>406</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>445</v>
+        <v>437</v>
       </c>
     </row>
     <row r="94" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G94" s="3" t="s">
-        <v>416</v>
+        <v>408</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>447</v>
+        <v>439</v>
       </c>
     </row>
     <row r="95" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G95" s="3" t="s">
-        <v>418</v>
+        <v>410</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>449</v>
+        <v>441</v>
       </c>
     </row>
     <row r="96" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G96" s="3" t="s">
-        <v>420</v>
+        <v>412</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>451</v>
+        <v>443</v>
       </c>
     </row>
     <row r="97" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G97" s="3" t="s">
-        <v>422</v>
+        <v>414</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>453</v>
+        <v>445</v>
       </c>
     </row>
     <row r="98" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G98" s="3" t="s">
-        <v>555</v>
+        <v>547</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>455</v>
+        <v>447</v>
       </c>
     </row>
     <row r="99" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G99" s="3" t="s">
-        <v>548</v>
+        <v>540</v>
       </c>
     </row>
     <row r="100" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G100" s="3" t="s">
-        <v>574</v>
+        <v>566</v>
       </c>
     </row>
     <row r="101" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G101" s="3" t="s">
-        <v>424</v>
+        <v>416</v>
       </c>
     </row>
     <row r="102" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G102" s="3" t="s">
-        <v>426</v>
+        <v>418</v>
       </c>
     </row>
     <row r="103" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G103" s="3" t="s">
-        <v>428</v>
+        <v>420</v>
       </c>
     </row>
     <row r="104" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G104" s="3" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
     </row>
     <row r="105" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G105" s="3" t="s">
-        <v>432</v>
+        <v>424</v>
       </c>
     </row>
     <row r="106" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G106" s="3" t="s">
-        <v>434</v>
+        <v>426</v>
       </c>
     </row>
     <row r="107" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G107" s="3" t="s">
-        <v>436</v>
+        <v>428</v>
       </c>
     </row>
     <row r="108" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G108" s="3" t="s">
-        <v>552</v>
+        <v>544</v>
       </c>
     </row>
     <row r="109" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G109" s="3" t="s">
-        <v>438</v>
+        <v>430</v>
       </c>
     </row>
     <row r="110" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G110" s="3" t="s">
-        <v>440</v>
+        <v>432</v>
       </c>
     </row>
     <row r="111" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G111" s="3" t="s">
-        <v>442</v>
+        <v>434</v>
       </c>
     </row>
     <row r="112" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G112" s="3" t="s">
-        <v>444</v>
+        <v>436</v>
       </c>
     </row>
     <row r="113" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G113" s="3" t="s">
-        <v>446</v>
+        <v>438</v>
       </c>
     </row>
     <row r="114" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G114" s="3" t="s">
-        <v>448</v>
+        <v>440</v>
       </c>
     </row>
     <row r="115" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G115" s="3" t="s">
-        <v>450</v>
+        <v>442</v>
       </c>
     </row>
     <row r="116" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G116" s="3" t="s">
-        <v>547</v>
+        <v>539</v>
       </c>
     </row>
     <row r="117" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G117" s="3" t="s">
-        <v>452</v>
+        <v>444</v>
       </c>
     </row>
     <row r="118" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G118" s="3" t="s">
-        <v>454</v>
+        <v>446</v>
       </c>
     </row>
     <row r="119" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G119" s="3" t="s">
-        <v>456</v>
+        <v>448</v>
       </c>
     </row>
     <row r="120" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G120" s="3" t="s">
-        <v>457</v>
+        <v>449</v>
       </c>
     </row>
     <row r="121" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G121" s="3" t="s">
-        <v>458</v>
+        <v>450</v>
       </c>
     </row>
     <row r="122" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G122" s="3" t="s">
-        <v>459</v>
+        <v>451</v>
       </c>
     </row>
     <row r="123" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G123" s="3" t="s">
-        <v>460</v>
+        <v>452</v>
       </c>
     </row>
     <row r="124" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G124" s="3" t="s">
-        <v>559</v>
+        <v>551</v>
       </c>
     </row>
     <row r="125" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G125" s="3" t="s">
-        <v>461</v>
+        <v>453</v>
       </c>
     </row>
     <row r="126" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G126" s="3" t="s">
-        <v>462</v>
+        <v>454</v>
       </c>
     </row>
     <row r="127" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G127" s="3" t="s">
-        <v>463</v>
+        <v>455</v>
       </c>
     </row>
     <row r="128" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G128" s="3" t="s">
-        <v>464</v>
+        <v>456</v>
       </c>
     </row>
     <row r="129" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G129" s="3" t="s">
-        <v>465</v>
+        <v>457</v>
       </c>
     </row>
     <row r="130" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G130" s="3" t="s">
-        <v>466</v>
+        <v>458</v>
       </c>
     </row>
     <row r="131" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G131" s="3" t="s">
-        <v>467</v>
+        <v>459</v>
       </c>
     </row>
     <row r="132" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G132" s="3" t="s">
-        <v>468</v>
+        <v>460</v>
       </c>
     </row>
     <row r="133" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G133" s="3" t="s">
-        <v>469</v>
+        <v>461</v>
       </c>
     </row>
     <row r="134" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G134" s="3" t="s">
-        <v>470</v>
+        <v>462</v>
       </c>
     </row>
     <row r="135" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G135" s="3" t="s">
-        <v>471</v>
+        <v>463</v>
       </c>
     </row>
     <row r="136" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G136" s="3" t="s">
-        <v>578</v>
+        <v>570</v>
       </c>
     </row>
     <row r="137" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G137" s="3" t="s">
-        <v>472</v>
+        <v>464</v>
       </c>
     </row>
     <row r="138" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G138" s="3" t="s">
-        <v>473</v>
+        <v>465</v>
       </c>
     </row>
     <row r="139" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G139" s="3" t="s">
-        <v>474</v>
+        <v>466</v>
       </c>
     </row>
     <row r="140" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G140" s="3" t="s">
-        <v>475</v>
+        <v>467</v>
       </c>
     </row>
     <row r="141" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G141" s="3" t="s">
-        <v>544</v>
+        <v>536</v>
       </c>
     </row>
     <row r="142" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G142" s="3" t="s">
-        <v>476</v>
+        <v>468</v>
       </c>
     </row>
     <row r="143" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G143" s="3" t="s">
-        <v>563</v>
+        <v>555</v>
       </c>
     </row>
     <row r="144" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G144" s="3" t="s">
-        <v>477</v>
+        <v>469</v>
       </c>
     </row>
     <row r="145" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G145" s="3" t="s">
-        <v>478</v>
+        <v>470</v>
       </c>
     </row>
     <row r="146" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G146" s="3" t="s">
-        <v>479</v>
+        <v>471</v>
       </c>
     </row>
     <row r="147" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G147" s="3" t="s">
-        <v>480</v>
+        <v>472</v>
       </c>
     </row>
     <row r="148" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G148" s="3" t="s">
-        <v>481</v>
+        <v>473</v>
       </c>
     </row>
     <row r="149" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G149" s="3" t="s">
-        <v>540</v>
+        <v>532</v>
       </c>
     </row>
     <row r="150" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G150" s="3" t="s">
-        <v>545</v>
+        <v>537</v>
       </c>
     </row>
     <row r="151" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G151" s="3" t="s">
-        <v>482</v>
+        <v>474</v>
       </c>
     </row>
     <row r="152" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G152" s="3" t="s">
-        <v>483</v>
+        <v>475</v>
       </c>
     </row>
     <row r="153" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G153" s="3" t="s">
-        <v>484</v>
+        <v>476</v>
       </c>
     </row>
     <row r="154" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G154" s="3" t="s">
-        <v>550</v>
+        <v>542</v>
       </c>
     </row>
     <row r="155" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G155" s="3" t="s">
-        <v>485</v>
+        <v>477</v>
       </c>
     </row>
     <row r="156" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G156" s="3" t="s">
-        <v>486</v>
+        <v>478</v>
       </c>
     </row>
     <row r="157" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G157" s="3" t="s">
-        <v>487</v>
+        <v>479</v>
       </c>
     </row>
     <row r="158" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G158" s="3" t="s">
-        <v>488</v>
+        <v>480</v>
       </c>
     </row>
     <row r="159" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G159" s="3" t="s">
-        <v>489</v>
+        <v>481</v>
       </c>
     </row>
     <row r="160" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G160" s="3" t="s">
-        <v>490</v>
+        <v>482</v>
       </c>
     </row>
     <row r="161" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G161" s="3" t="s">
-        <v>491</v>
+        <v>483</v>
       </c>
     </row>
     <row r="162" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G162" s="3" t="s">
-        <v>492</v>
+        <v>484</v>
       </c>
     </row>
     <row r="163" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G163" s="3" t="s">
-        <v>579</v>
+        <v>571</v>
       </c>
     </row>
     <row r="164" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G164" s="3" t="s">
-        <v>564</v>
+        <v>556</v>
       </c>
     </row>
     <row r="165" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G165" s="3" t="s">
-        <v>493</v>
+        <v>485</v>
       </c>
     </row>
     <row r="166" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G166" s="3" t="s">
-        <v>494</v>
+        <v>486</v>
       </c>
     </row>
     <row r="167" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G167" s="3" t="s">
-        <v>569</v>
+        <v>561</v>
       </c>
     </row>
     <row r="168" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G168" s="3" t="s">
-        <v>495</v>
+        <v>487</v>
       </c>
     </row>
     <row r="169" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G169" s="3" t="s">
-        <v>496</v>
+        <v>488</v>
       </c>
     </row>
     <row r="170" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G170" s="3" t="s">
-        <v>543</v>
+        <v>535</v>
       </c>
     </row>
     <row r="171" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G171" s="3" t="s">
-        <v>575</v>
+        <v>567</v>
       </c>
     </row>
     <row r="172" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G172" s="3" t="s">
-        <v>497</v>
+        <v>489</v>
       </c>
     </row>
     <row r="173" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G173" s="3" t="s">
-        <v>498</v>
+        <v>490</v>
       </c>
     </row>
     <row r="174" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G174" s="3" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
     </row>
     <row r="175" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G175" s="3" t="s">
-        <v>499</v>
+        <v>491</v>
       </c>
     </row>
     <row r="176" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G176" s="3" t="s">
-        <v>576</v>
+        <v>568</v>
       </c>
     </row>
     <row r="177" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G177" s="3" t="s">
-        <v>500</v>
+        <v>492</v>
       </c>
     </row>
     <row r="178" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G178" s="3" t="s">
-        <v>566</v>
+        <v>558</v>
       </c>
     </row>
     <row r="179" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G179" s="3" t="s">
-        <v>561</v>
+        <v>553</v>
       </c>
     </row>
     <row r="180" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G180" s="3" t="s">
-        <v>553</v>
+        <v>545</v>
       </c>
     </row>
     <row r="181" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G181" s="3" t="s">
-        <v>501</v>
+        <v>493</v>
       </c>
     </row>
     <row r="182" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G182" s="3" t="s">
-        <v>502</v>
+        <v>494</v>
       </c>
     </row>
     <row r="183" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G183" s="3" t="s">
-        <v>503</v>
+        <v>495</v>
       </c>
     </row>
     <row r="184" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G184" s="3" t="s">
-        <v>504</v>
+        <v>496</v>
       </c>
     </row>
     <row r="185" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G185" s="3" t="s">
-        <v>505</v>
+        <v>497</v>
       </c>
     </row>
     <row r="186" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G186" s="3" t="s">
-        <v>506</v>
+        <v>498</v>
       </c>
     </row>
     <row r="187" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G187" s="3" t="s">
-        <v>507</v>
+        <v>499</v>
       </c>
     </row>
     <row r="188" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G188" s="3" t="s">
-        <v>508</v>
+        <v>500</v>
       </c>
     </row>
     <row r="189" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G189" s="3" t="s">
-        <v>509</v>
+        <v>501</v>
       </c>
     </row>
     <row r="190" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G190" s="3" t="s">
-        <v>510</v>
+        <v>502</v>
       </c>
     </row>
     <row r="191" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G191" s="3" t="s">
-        <v>511</v>
+        <v>503</v>
       </c>
     </row>
     <row r="192" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G192" s="3" t="s">
-        <v>512</v>
+        <v>504</v>
       </c>
     </row>
     <row r="193" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G193" s="3" t="s">
-        <v>577</v>
+        <v>569</v>
       </c>
     </row>
     <row r="194" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G194" s="3" t="s">
-        <v>571</v>
+        <v>563</v>
       </c>
     </row>
     <row r="195" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G195" s="3" t="s">
-        <v>513</v>
+        <v>505</v>
       </c>
     </row>
     <row r="196" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G196" s="3" t="s">
-        <v>514</v>
+        <v>506</v>
       </c>
     </row>
     <row r="197" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G197" s="3" t="s">
-        <v>515</v>
+        <v>507</v>
       </c>
     </row>
     <row r="198" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G198" s="3" t="s">
-        <v>516</v>
+        <v>508</v>
       </c>
     </row>
     <row r="199" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G199" s="3" t="s">
-        <v>568</v>
+        <v>560</v>
       </c>
     </row>
     <row r="200" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G200" s="3" t="s">
-        <v>517</v>
+        <v>509</v>
       </c>
     </row>
     <row r="201" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G201" s="3" t="s">
-        <v>518</v>
+        <v>510</v>
       </c>
     </row>
     <row r="202" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G202" s="3" t="s">
-        <v>519</v>
+        <v>511</v>
       </c>
     </row>
     <row r="203" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G203" s="3" t="s">
-        <v>520</v>
+        <v>512</v>
       </c>
     </row>
     <row r="204" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G204" s="3" t="s">
-        <v>521</v>
+        <v>513</v>
       </c>
     </row>
   </sheetData>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B8B84A83-C32C-7E47-8DF3-480D3C3BFB7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B195C62-1C32-B74C-8C06-5F13BE7F4FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="23940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1065" uniqueCount="746">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="752">
   <si>
     <t>Trade ID</t>
   </si>
@@ -2302,6 +2302,24 @@
   </si>
   <si>
     <t>Bonds-TLT (+) Equities-ES (-)</t>
+  </si>
+  <si>
+    <t>MNST</t>
+  </si>
+  <si>
+    <t>mnst</t>
+  </si>
+  <si>
+    <t>Monster Beverage</t>
+  </si>
+  <si>
+    <t>MNST (-)</t>
+  </si>
+  <si>
+    <t>Gross_Exposure</t>
+  </si>
+  <si>
+    <t>Gross_Exposure_pct</t>
   </si>
 </sst>
 </file>
@@ -2451,7 +2469,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2606,6 +2624,15 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="1" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2930,7 +2957,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Y79"/>
+  <dimension ref="A1:Z80"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5" style="33" bestFit="1" customWidth="1"/>
@@ -2940,7 +2967,7 @@
     <col min="6" max="6" width="11.1640625" style="33" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="57.6640625" style="33" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="13.33203125" style="33" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="43.1640625" style="33" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="34" style="33" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="13" style="33" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.33203125" style="33" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="10.5" style="33" bestFit="1" customWidth="1"/>
@@ -2953,10 +2980,12 @@
     <col min="22" max="22" width="13" style="33" bestFit="1" customWidth="1"/>
     <col min="23" max="23" width="14.83203125" style="33" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="6" style="33" bestFit="1" customWidth="1"/>
-    <col min="25" max="16384" width="9.1640625" style="33"/>
+    <col min="25" max="25" width="18.5" style="33" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="23.33203125" style="58" bestFit="1" customWidth="1"/>
+    <col min="27" max="16384" width="9.1640625" style="33"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="30" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" s="30" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="30" t="s">
         <v>0</v>
       </c>
@@ -3026,8 +3055,14 @@
       <c r="W1" s="30" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y1" s="30" t="s">
+        <v>750</v>
+      </c>
+      <c r="Z1" s="57" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="33">
         <v>1</v>
       </c>
@@ -3097,8 +3132,12 @@
       <c r="V2" s="41">
         <v>11575</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y2" s="39">
+        <f>Q2</f>
+        <v>105712</v>
+      </c>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="37">
         <v>2</v>
       </c>
@@ -3168,8 +3207,12 @@
       <c r="V3" s="43">
         <v>-4105.18</v>
       </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y3" s="39">
+        <f>Y2+Q3</f>
+        <v>244379.5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="33">
         <v>3</v>
       </c>
@@ -3238,8 +3281,12 @@
       <c r="V4" s="41">
         <v>0</v>
       </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y4" s="39">
+        <f>Y3+Q4</f>
+        <v>907729.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="33">
         <v>4</v>
       </c>
@@ -3309,8 +3356,12 @@
       <c r="V5" s="41">
         <v>11150</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y5" s="39">
+        <f>Y4+Q5</f>
+        <v>3802629.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="33">
         <v>3</v>
       </c>
@@ -3379,8 +3430,12 @@
       <c r="V6" s="41">
         <v>6343</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y6" s="39">
+        <f>Y5+Q6</f>
+        <v>4264098.25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="33">
         <v>5</v>
       </c>
@@ -3450,8 +3505,12 @@
       <c r="V7" s="43">
         <v>-6010</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y7" s="39">
+        <f>Y6+Q7</f>
+        <v>4395338.25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="33">
         <v>6</v>
       </c>
@@ -3521,8 +3580,12 @@
       <c r="V8" s="41">
         <v>4681.25</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y8" s="39">
+        <f>Y7+Q8</f>
+        <v>7520119.25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="37">
         <v>7</v>
       </c>
@@ -3592,8 +3655,12 @@
       <c r="V9" s="44">
         <v>0</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y9" s="39">
+        <f>Y8+Q9</f>
+        <v>7616618.25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="37">
         <v>7</v>
       </c>
@@ -3662,8 +3729,12 @@
       <c r="V10" s="44">
         <v>2338.1999999999998</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y10" s="39">
+        <f>Y9+Q10</f>
+        <v>7713215.0499999998</v>
+      </c>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="33">
         <v>3</v>
       </c>
@@ -3732,8 +3803,12 @@
       <c r="V11" s="41">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y11" s="39">
+        <f>Y10+Q11</f>
+        <v>7915340.0499999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="37">
         <v>8</v>
       </c>
@@ -3802,8 +3877,12 @@
       <c r="V12" s="41">
         <v>4588</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y12" s="39">
+        <f>Y11+Q12</f>
+        <v>8139183.3300000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="37">
         <v>9</v>
       </c>
@@ -3873,8 +3952,12 @@
       <c r="V13" s="44">
         <v>4717</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y13" s="39">
+        <f>Y12+Q13</f>
+        <v>8194218.3300000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="33">
         <v>10</v>
       </c>
@@ -3943,8 +4026,12 @@
       <c r="V14" s="45">
         <v>-16354</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y14" s="39">
+        <f t="shared" ref="Y14:Y69" si="4">Y13+Q14</f>
+        <v>8315282.3300000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="33">
         <v>11</v>
       </c>
@@ -4014,8 +4101,12 @@
       <c r="V15" s="41">
         <v>2568.75</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y15" s="39">
+        <f t="shared" si="4"/>
+        <v>8431307.3300000001</v>
+      </c>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="37">
         <v>12</v>
       </c>
@@ -4085,8 +4176,12 @@
       <c r="V16" s="44">
         <v>4149.45</v>
       </c>
-    </row>
-    <row r="17" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y16" s="39">
+        <f t="shared" si="4"/>
+        <v>8522118.5299999993</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="33">
         <v>13</v>
       </c>
@@ -4156,8 +4251,12 @@
       <c r="V17" s="41">
         <v>11150</v>
       </c>
-    </row>
-    <row r="18" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y17" s="39">
+        <f t="shared" si="4"/>
+        <v>8754778.5299999993</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="33">
         <v>14</v>
       </c>
@@ -4227,8 +4326,12 @@
       <c r="V18" s="41">
         <v>2033</v>
       </c>
-    </row>
-    <row r="19" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y18" s="39">
+        <f t="shared" si="4"/>
+        <v>8856742.5299999993</v>
+      </c>
+    </row>
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="33">
         <v>15</v>
       </c>
@@ -4297,8 +4400,12 @@
       <c r="V19" s="41">
         <v>177</v>
       </c>
-    </row>
-    <row r="20" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y19" s="39">
+        <f t="shared" si="4"/>
+        <v>8910793.5299999993</v>
+      </c>
+    </row>
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="33">
         <v>16</v>
       </c>
@@ -4367,8 +4474,12 @@
       <c r="V20" s="41">
         <v>4060</v>
       </c>
-    </row>
-    <row r="21" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y20" s="39">
+        <f t="shared" si="4"/>
+        <v>9096175.5299999993</v>
+      </c>
+    </row>
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="33">
         <v>17</v>
       </c>
@@ -4437,8 +4548,12 @@
       <c r="V21" s="41">
         <v>0</v>
       </c>
-    </row>
-    <row r="22" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y21" s="39">
+        <f t="shared" si="4"/>
+        <v>9260795.5299999993</v>
+      </c>
+    </row>
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="33">
         <v>17</v>
       </c>
@@ -4507,8 +4622,12 @@
       <c r="V22" s="41">
         <v>2838</v>
       </c>
-    </row>
-    <row r="23" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y22" s="39">
+        <f t="shared" si="4"/>
+        <v>9415085.5299999993</v>
+      </c>
+    </row>
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="33">
         <v>18</v>
       </c>
@@ -4577,8 +4696,12 @@
       <c r="V23" s="41">
         <v>6742</v>
       </c>
-    </row>
-    <row r="24" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y23" s="39">
+        <f t="shared" si="4"/>
+        <v>9597790.5299999993</v>
+      </c>
+    </row>
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="33">
         <v>19</v>
       </c>
@@ -4646,8 +4769,12 @@
       <c r="V24" s="41">
         <v>1245</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y24" s="39">
+        <f t="shared" si="4"/>
+        <v>11048790.529999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="33">
         <v>20</v>
       </c>
@@ -4707,7 +4834,7 @@
         <v>1</v>
       </c>
       <c r="T25" s="40">
-        <f t="shared" ref="T25:T36" si="4">IF(S25=1, ABS(O25-N25)/N25, 0)</f>
+        <f t="shared" ref="T25:T36" si="5">IF(S25=1, ABS(O25-N25)/N25, 0)</f>
         <v>3.9539800653504951E-3</v>
       </c>
       <c r="U25" s="39">
@@ -4716,8 +4843,12 @@
       <c r="V25" s="41">
         <v>1710</v>
       </c>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y25" s="39">
+        <f t="shared" si="4"/>
+        <v>11485025.529999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="33">
         <v>21</v>
       </c>
@@ -4728,7 +4859,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D62" si="5">C26-B26</f>
+        <f t="shared" ref="D26:D62" si="6">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
@@ -4777,7 +4908,7 @@
         <v>1</v>
       </c>
       <c r="T26" s="40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.4025752021974973E-3</v>
       </c>
       <c r="U26" s="39">
@@ -4786,8 +4917,12 @@
       <c r="V26" s="41">
         <v>715</v>
       </c>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y26" s="39">
+        <f t="shared" si="4"/>
+        <v>11626225.529999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="33">
         <v>22</v>
       </c>
@@ -4846,7 +4981,7 @@
         <v>1</v>
       </c>
       <c r="T27" s="40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.623408180713668E-2</v>
       </c>
       <c r="U27" s="39">
@@ -4855,8 +4990,12 @@
       <c r="V27" s="41">
         <v>3498</v>
       </c>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y27" s="39">
+        <f t="shared" si="4"/>
+        <v>11759563.529999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="33">
         <v>23</v>
       </c>
@@ -4867,7 +5006,7 @@
         <v>46266</v>
       </c>
       <c r="D28" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E28" s="33" t="s">
@@ -4916,7 +5055,7 @@
         <v>1</v>
       </c>
       <c r="T28" s="40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.0251341995685504E-2</v>
       </c>
       <c r="U28" s="39">
@@ -4925,8 +5064,12 @@
       <c r="V28" s="41">
         <v>1809</v>
       </c>
-    </row>
-    <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y28" s="39">
+        <f t="shared" si="4"/>
+        <v>11819362.529999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="33">
         <v>24</v>
       </c>
@@ -4937,7 +5080,7 @@
         <v>46268</v>
       </c>
       <c r="D29" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="E29" s="33" t="s">
@@ -4986,7 +5129,7 @@
         <v>1</v>
       </c>
       <c r="T29" s="40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.7141972539147393E-3</v>
       </c>
       <c r="U29" s="39">
@@ -4995,8 +5138,12 @@
       <c r="V29" s="41">
         <v>2891</v>
       </c>
-    </row>
-    <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y29" s="39">
+        <f t="shared" si="4"/>
+        <v>12062085.529999999</v>
+      </c>
+    </row>
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="33">
         <v>25</v>
       </c>
@@ -5007,7 +5154,7 @@
         <v>46268</v>
       </c>
       <c r="D30" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="E30" s="33" t="s">
@@ -5056,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U30" s="39">
@@ -5065,8 +5212,12 @@
       <c r="V30" s="45">
         <v>-642</v>
       </c>
-    </row>
-    <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y30" s="39">
+        <f t="shared" si="4"/>
+        <v>12357102.529999999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="33">
         <v>26</v>
       </c>
@@ -5077,7 +5228,7 @@
         <v>46267</v>
       </c>
       <c r="D31" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E31" s="33" t="s">
@@ -5126,7 +5277,7 @@
         <v>1</v>
       </c>
       <c r="T31" s="40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8.455326735182055E-3</v>
       </c>
       <c r="U31" s="39">
@@ -5135,8 +5286,12 @@
       <c r="V31" s="41">
         <v>4108</v>
       </c>
-    </row>
-    <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y31" s="39">
+        <f t="shared" si="4"/>
+        <v>12489704.529999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="33">
         <v>27</v>
       </c>
@@ -5147,7 +5302,7 @@
         <v>46283</v>
       </c>
       <c r="D32" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>17</v>
       </c>
       <c r="E32" s="33" t="s">
@@ -5196,7 +5351,7 @@
         <v>1</v>
       </c>
       <c r="T32" s="40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.8185412136785959E-2</v>
       </c>
       <c r="U32" s="39">
@@ -5205,8 +5360,12 @@
       <c r="V32" s="41">
         <v>7389</v>
       </c>
-    </row>
-    <row r="33" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y32" s="39">
+        <f t="shared" si="4"/>
+        <v>12887035.529999999</v>
+      </c>
+    </row>
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="33">
         <v>28</v>
       </c>
@@ -5217,7 +5376,7 @@
         <v>46276</v>
       </c>
       <c r="D33" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="E33" s="33" t="s">
@@ -5266,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="T33" s="40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.9886363636363667E-2</v>
       </c>
       <c r="U33" s="39">
@@ -5275,8 +5434,12 @@
       <c r="V33" s="41">
         <v>2247</v>
       </c>
-    </row>
-    <row r="34" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y33" s="39">
+        <f t="shared" si="4"/>
+        <v>13000063.529999999</v>
+      </c>
+    </row>
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="33">
         <v>29</v>
       </c>
@@ -5287,7 +5450,7 @@
         <v>46276</v>
       </c>
       <c r="D34" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="E34" s="33" t="s">
@@ -5336,7 +5499,7 @@
         <v>1</v>
       </c>
       <c r="T34" s="40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9.8159124408065835E-3</v>
       </c>
       <c r="U34" s="39">
@@ -5345,8 +5508,12 @@
       <c r="V34" s="41">
         <v>1253</v>
       </c>
-    </row>
-    <row r="35" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y34" s="39">
+        <f t="shared" si="4"/>
+        <v>13127610.529999999</v>
+      </c>
+    </row>
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="33">
         <v>30</v>
       </c>
@@ -5357,7 +5524,7 @@
         <v>46279</v>
       </c>
       <c r="D35" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="E35" s="33" t="s">
@@ -5406,7 +5573,7 @@
         <v>1</v>
       </c>
       <c r="T35" s="40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>5.3725127878096988E-3</v>
       </c>
       <c r="U35" s="39">
@@ -5415,8 +5582,12 @@
       <c r="V35" s="41">
         <v>141</v>
       </c>
-    </row>
-    <row r="36" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y35" s="39">
+        <f t="shared" si="4"/>
+        <v>13153641.529999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="33">
         <v>31</v>
       </c>
@@ -5427,7 +5598,7 @@
         <v>46283</v>
       </c>
       <c r="D36" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="E36" s="33" t="s">
@@ -5476,7 +5647,7 @@
         <v>0</v>
       </c>
       <c r="T36" s="40">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0</v>
       </c>
       <c r="U36" s="39">
@@ -5485,8 +5656,12 @@
       <c r="V36" s="45">
         <v>-3825</v>
       </c>
-    </row>
-    <row r="37" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y36" s="39">
+        <f t="shared" si="4"/>
+        <v>13342137.529999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="33">
         <v>32</v>
       </c>
@@ -5497,7 +5672,7 @@
         <v>46276</v>
       </c>
       <c r="D37" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E37" s="33" t="s">
@@ -5546,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="T37" s="40">
-        <f t="shared" ref="T37:T40" si="6">IF(S37=1, ABS(O37-N37)/N37, 0)</f>
+        <f t="shared" ref="T37:T40" si="7">IF(S37=1, ABS(O37-N37)/N37, 0)</f>
         <v>1.2137203166226873E-2</v>
       </c>
       <c r="U37" s="39">
@@ -5555,8 +5730,12 @@
       <c r="V37" s="41">
         <v>345</v>
       </c>
-    </row>
-    <row r="38" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y37" s="39">
+        <f t="shared" si="4"/>
+        <v>13370907.529999999</v>
+      </c>
+    </row>
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="33">
         <v>33</v>
       </c>
@@ -5567,7 +5746,7 @@
         <v>46276</v>
       </c>
       <c r="D38" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E38" s="33" t="s">
@@ -5616,7 +5795,7 @@
         <v>1</v>
       </c>
       <c r="T38" s="40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1.8280016618196831E-3</v>
       </c>
       <c r="U38" s="39">
@@ -5625,8 +5804,12 @@
       <c r="V38" s="41">
         <v>220</v>
       </c>
-    </row>
-    <row r="39" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y38" s="39">
+        <f t="shared" si="4"/>
+        <v>13491277.529999999</v>
+      </c>
+    </row>
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="33">
         <v>34</v>
       </c>
@@ -5637,7 +5820,7 @@
         <v>46288</v>
       </c>
       <c r="D39" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="E39" s="33" t="s">
@@ -5687,7 +5870,7 @@
         <v>1</v>
       </c>
       <c r="T39" s="40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2.3968322438641332E-2</v>
       </c>
       <c r="U39" s="39">
@@ -5696,8 +5879,12 @@
       <c r="V39" s="41">
         <v>2167</v>
       </c>
-    </row>
-    <row r="40" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y39" s="39">
+        <f t="shared" si="4"/>
+        <v>13581688.529999999</v>
+      </c>
+    </row>
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="33">
         <v>35</v>
       </c>
@@ -5708,7 +5895,7 @@
         <v>46288</v>
       </c>
       <c r="D40" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5</v>
       </c>
       <c r="E40" s="33" t="s">
@@ -5758,7 +5945,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="40">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="U40" s="39">
@@ -5767,8 +5954,12 @@
       <c r="V40" s="45">
         <v>-438</v>
       </c>
-    </row>
-    <row r="41" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y40" s="39">
+        <f t="shared" si="4"/>
+        <v>13617290.029999999</v>
+      </c>
+    </row>
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="33">
         <v>36</v>
       </c>
@@ -5779,7 +5970,7 @@
         <v>46288</v>
       </c>
       <c r="D41" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="E41" s="33" t="s">
@@ -5828,7 +6019,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="40">
-        <f t="shared" ref="T41:T44" si="7">IF(S41=1, ABS(O41-N41)/N41, 0)</f>
+        <f t="shared" ref="T41:T44" si="8">IF(S41=1, ABS(O41-N41)/N41, 0)</f>
         <v>0</v>
       </c>
       <c r="U41" s="39">
@@ -5837,8 +6028,12 @@
       <c r="V41" s="45">
         <v>-317</v>
       </c>
-    </row>
-    <row r="42" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y41" s="39">
+        <f t="shared" si="4"/>
+        <v>13673192.029999999</v>
+      </c>
+    </row>
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="33">
         <v>37</v>
       </c>
@@ -5849,7 +6044,7 @@
         <v>46288</v>
       </c>
       <c r="D42" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="E42" s="33" t="s">
@@ -5899,7 +6094,7 @@
         <v>1</v>
       </c>
       <c r="T42" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.9242297247460509E-2</v>
       </c>
       <c r="U42" s="39">
@@ -5908,8 +6103,12 @@
       <c r="V42" s="41">
         <v>1721</v>
       </c>
-    </row>
-    <row r="43" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y42" s="39">
+        <f t="shared" si="4"/>
+        <v>13762673.029999999</v>
+      </c>
+    </row>
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="33">
         <v>38</v>
       </c>
@@ -5920,7 +6119,7 @@
         <v>46301</v>
       </c>
       <c r="D43" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="E43" s="33" t="s">
@@ -5970,7 +6169,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U43" s="39">
@@ -5979,8 +6178,12 @@
       <c r="V43" s="45">
         <v>-2814</v>
       </c>
-    </row>
-    <row r="44" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y43" s="39">
+        <f t="shared" si="4"/>
+        <v>13879125.029999999</v>
+      </c>
+    </row>
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="33">
         <v>39</v>
       </c>
@@ -5991,7 +6194,7 @@
         <v>46288</v>
       </c>
       <c r="D44" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="E44" s="33" t="s">
@@ -6041,7 +6244,7 @@
         <v>1</v>
       </c>
       <c r="T44" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>9.1189909260570284E-3</v>
       </c>
       <c r="U44" s="39">
@@ -6050,8 +6253,12 @@
       <c r="V44" s="41">
         <v>1134</v>
       </c>
-    </row>
-    <row r="45" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y44" s="39">
+        <f t="shared" si="4"/>
+        <v>14003437.029999999</v>
+      </c>
+    </row>
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="33">
         <v>40</v>
       </c>
@@ -6062,7 +6269,7 @@
         <v>46286</v>
       </c>
       <c r="D45" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E45" s="33" t="s">
@@ -6111,7 +6318,7 @@
         <v>1</v>
       </c>
       <c r="T45" s="40">
-        <f t="shared" ref="T45:T48" si="8">IF(S45=1, ABS(O45-N45)/N45, 0)</f>
+        <f t="shared" ref="T45:T48" si="9">IF(S45=1, ABS(O45-N45)/N45, 0)</f>
         <v>6.6957880304817775E-4</v>
       </c>
       <c r="U45" s="39">
@@ -6120,8 +6327,12 @@
       <c r="V45" s="41">
         <v>108</v>
       </c>
-    </row>
-    <row r="46" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y45" s="39">
+        <f t="shared" si="4"/>
+        <v>14160155.029999999</v>
+      </c>
+    </row>
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="33">
         <v>41</v>
       </c>
@@ -6132,7 +6343,7 @@
         <v>46288</v>
       </c>
       <c r="D46" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E46" s="33" t="s">
@@ -6182,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="T46" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U46" s="39">
@@ -6191,8 +6402,12 @@
       <c r="V46" s="45">
         <v>-664</v>
       </c>
-    </row>
-    <row r="47" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y46" s="39">
+        <f t="shared" si="4"/>
+        <v>14197575.029999999</v>
+      </c>
+    </row>
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" s="33">
         <v>42</v>
       </c>
@@ -6203,7 +6418,7 @@
         <v>46303</v>
       </c>
       <c r="D47" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>15</v>
       </c>
       <c r="E47" s="33" t="s">
@@ -6253,7 +6468,7 @@
         <v>1</v>
       </c>
       <c r="T47" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>2.1600874329984955E-2</v>
       </c>
       <c r="U47" s="39">
@@ -6262,8 +6477,12 @@
       <c r="V47" s="41">
         <v>3476</v>
       </c>
-    </row>
-    <row r="48" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="Y47" s="39">
+        <f t="shared" si="4"/>
+        <v>14354955.029999999</v>
+      </c>
+    </row>
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" s="33">
         <v>43</v>
       </c>
@@ -6274,7 +6493,7 @@
         <v>46296</v>
       </c>
       <c r="D48" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8</v>
       </c>
       <c r="E48" s="33" t="s">
@@ -6324,7 +6543,7 @@
         <v>1</v>
       </c>
       <c r="T48" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>3.5463403580330705E-2</v>
       </c>
       <c r="U48" s="39">
@@ -6333,8 +6552,12 @@
       <c r="V48" s="41">
         <v>1895</v>
       </c>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y48" s="39">
+        <f t="shared" si="4"/>
+        <v>14407911.029999999</v>
+      </c>
+    </row>
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" s="33">
         <v>44</v>
       </c>
@@ -6345,7 +6568,7 @@
         <v>46290</v>
       </c>
       <c r="D49" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E49" s="33" t="s">
@@ -6394,7 +6617,7 @@
         <v>1</v>
       </c>
       <c r="T49" s="40">
-        <f t="shared" ref="T49:T52" si="9">IF(S49=1, ABS(O49-N49)/N49, 0)</f>
+        <f t="shared" ref="T49:T52" si="10">IF(S49=1, ABS(O49-N49)/N49, 0)</f>
         <v>2.0138262699128395E-2</v>
       </c>
       <c r="U49" s="39">
@@ -6403,8 +6626,12 @@
       <c r="V49" s="41">
         <v>338</v>
       </c>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y49" s="39">
+        <f t="shared" si="4"/>
+        <v>14424131.029999999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="33">
         <v>45</v>
       </c>
@@ -6415,7 +6642,7 @@
         <v>46290</v>
       </c>
       <c r="D50" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E50" s="33" t="s">
@@ -6464,7 +6691,7 @@
         <v>1</v>
       </c>
       <c r="T50" s="40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0891738306862922E-2</v>
       </c>
       <c r="U50" s="39">
@@ -6473,8 +6700,12 @@
       <c r="V50" s="41">
         <v>2245</v>
       </c>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y50" s="39">
+        <f t="shared" si="4"/>
+        <v>14630020.029999999</v>
+      </c>
+    </row>
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" s="33">
         <v>46</v>
       </c>
@@ -6485,7 +6716,7 @@
         <v>46296</v>
       </c>
       <c r="D51" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3</v>
       </c>
       <c r="E51" s="33" t="s">
@@ -6525,7 +6756,7 @@
         <v>82.27</v>
       </c>
       <c r="Q51" s="39">
-        <f t="shared" ref="Q51:Q58" si="10">ABS(N51*M51)</f>
+        <f t="shared" ref="Q51:Q58" si="11">ABS(N51*M51)</f>
         <v>59087</v>
       </c>
       <c r="R51" s="33">
@@ -6535,7 +6766,7 @@
         <v>0</v>
       </c>
       <c r="T51" s="40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U51" s="39">
@@ -6544,8 +6775,12 @@
       <c r="V51" s="45">
         <v>-1498</v>
       </c>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y51" s="39">
+        <f t="shared" si="4"/>
+        <v>14689107.029999999</v>
+      </c>
+    </row>
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="33">
         <v>47</v>
       </c>
@@ -6556,7 +6791,7 @@
         <v>46297</v>
       </c>
       <c r="D52" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>4</v>
       </c>
       <c r="E52" s="33" t="s">
@@ -6596,7 +6831,7 @@
         <v>466.29</v>
       </c>
       <c r="Q52" s="39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>49278.9</v>
       </c>
       <c r="R52" s="33">
@@ -6606,7 +6841,7 @@
         <v>0</v>
       </c>
       <c r="T52" s="40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U52" s="39">
@@ -6615,8 +6850,12 @@
       <c r="V52" s="45">
         <v>-2013</v>
       </c>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y52" s="39">
+        <f t="shared" si="4"/>
+        <v>14738385.93</v>
+      </c>
+    </row>
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" s="33">
         <v>48</v>
       </c>
@@ -6627,7 +6866,7 @@
         <v>46295</v>
       </c>
       <c r="D53" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2</v>
       </c>
       <c r="E53" s="33" t="s">
@@ -6667,7 +6906,7 @@
         <v>20.21</v>
       </c>
       <c r="Q53" s="39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>81080</v>
       </c>
       <c r="R53" s="33">
@@ -6677,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="T53" s="40">
-        <f t="shared" ref="T53:T55" si="11">IF(S53=1, ABS(O53-N53)/N53, 0)</f>
+        <f t="shared" ref="T53:T55" si="12">IF(S53=1, ABS(O53-N53)/N53, 0)</f>
         <v>0</v>
       </c>
       <c r="U53" s="39">
@@ -6686,8 +6925,12 @@
       <c r="V53" s="45">
         <v>-214</v>
       </c>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y53" s="39">
+        <f t="shared" si="4"/>
+        <v>14819465.93</v>
+      </c>
+    </row>
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" s="33">
         <v>49</v>
       </c>
@@ -6698,7 +6941,7 @@
         <v>46301</v>
       </c>
       <c r="D54" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="E54" s="33" t="s">
@@ -6738,7 +6981,7 @@
         <v>282.18</v>
       </c>
       <c r="Q54" s="39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>112565.4</v>
       </c>
       <c r="R54" s="33">
@@ -6748,7 +6991,7 @@
         <v>1</v>
       </c>
       <c r="T54" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>2.7237499267093006E-3</v>
       </c>
       <c r="U54" s="39">
@@ -6757,8 +7000,12 @@
       <c r="V54" s="41">
         <v>307</v>
       </c>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y54" s="39">
+        <f t="shared" si="4"/>
+        <v>14932031.33</v>
+      </c>
+    </row>
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" s="33">
         <v>49</v>
       </c>
@@ -6769,7 +7016,7 @@
         <v>46301</v>
       </c>
       <c r="D55" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="E55" s="33" t="s">
@@ -6809,7 +7056,7 @@
         <v>779.63</v>
       </c>
       <c r="Q55" s="39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>107494.8</v>
       </c>
       <c r="R55" s="33">
@@ -6819,7 +7066,7 @@
         <v>0</v>
       </c>
       <c r="T55" s="40">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>0</v>
       </c>
       <c r="U55" s="39">
@@ -6828,8 +7075,12 @@
       <c r="V55" s="45">
         <v>-1653</v>
       </c>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y55" s="39">
+        <f t="shared" si="4"/>
+        <v>15039526.130000001</v>
+      </c>
+    </row>
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" s="33">
         <v>50</v>
       </c>
@@ -6840,7 +7091,7 @@
         <v>46296</v>
       </c>
       <c r="D56" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E56" s="33" t="s">
@@ -6880,7 +7131,7 @@
         <v>434.77</v>
       </c>
       <c r="Q56" s="39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>44700</v>
       </c>
       <c r="R56" s="33">
@@ -6890,7 +7141,7 @@
         <v>1</v>
       </c>
       <c r="T56" s="40">
-        <f t="shared" ref="T56:T63" si="12">IF(S56=1, ABS(O56-N56)/N56, 0)</f>
+        <f t="shared" ref="T56:T63" si="13">IF(S56=1, ABS(O56-N56)/N56, 0)</f>
         <v>2.7360178970917266E-2</v>
       </c>
       <c r="U56" s="39">
@@ -6899,8 +7150,12 @@
       <c r="V56" s="41">
         <v>1222</v>
       </c>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y56" s="39">
+        <f t="shared" si="4"/>
+        <v>15084226.130000001</v>
+      </c>
+    </row>
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" s="33">
         <v>51</v>
       </c>
@@ -6911,7 +7166,7 @@
         <v>46296</v>
       </c>
       <c r="D57" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E57" s="33" t="s">
@@ -6951,7 +7206,7 @@
         <v>666.83</v>
       </c>
       <c r="Q57" s="39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>67415</v>
       </c>
       <c r="R57" s="33">
@@ -6961,7 +7216,7 @@
         <v>1</v>
       </c>
       <c r="T57" s="40">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.0858117629607559E-2</v>
       </c>
       <c r="U57" s="39">
@@ -6970,8 +7225,12 @@
       <c r="V57" s="41">
         <v>880</v>
       </c>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y57" s="39">
+        <f t="shared" si="4"/>
+        <v>15151641.130000001</v>
+      </c>
+    </row>
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" s="33">
         <v>52</v>
       </c>
@@ -6982,7 +7241,7 @@
         <v>46296</v>
       </c>
       <c r="D58" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E58" s="33" t="s">
@@ -7022,7 +7281,7 @@
         <v>332.03</v>
       </c>
       <c r="Q58" s="39">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>65255.999999999993</v>
       </c>
       <c r="R58" s="33">
@@ -7032,7 +7291,7 @@
         <v>1</v>
       </c>
       <c r="T58" s="40">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>1.762290057619223E-2</v>
       </c>
       <c r="U58" s="39">
@@ -7041,8 +7300,12 @@
       <c r="V58" s="41">
         <v>1058</v>
       </c>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y58" s="39">
+        <f t="shared" si="4"/>
+        <v>15216897.130000001</v>
+      </c>
+    </row>
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" s="33">
         <v>53</v>
       </c>
@@ -7053,7 +7316,7 @@
         <v>46310</v>
       </c>
       <c r="D59" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>13</v>
       </c>
       <c r="E59" s="33" t="s">
@@ -7102,7 +7365,7 @@
         <v>1</v>
       </c>
       <c r="T59" s="40">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.1615147713014791E-2</v>
       </c>
       <c r="U59" s="39">
@@ -7112,8 +7375,12 @@
       <c r="V59" s="41">
         <v>569</v>
       </c>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y59" s="39">
+        <f t="shared" si="4"/>
+        <v>15243767.130000001</v>
+      </c>
+    </row>
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" s="33">
         <v>54</v>
       </c>
@@ -7124,7 +7391,7 @@
         <v>46300</v>
       </c>
       <c r="D60" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1</v>
       </c>
       <c r="E60" s="33" t="s">
@@ -7174,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="T60" s="40">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.3162583518930384E-3</v>
       </c>
       <c r="U60" s="39">
@@ -7183,8 +7450,12 @@
       <c r="V60" s="41">
         <v>925</v>
       </c>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y60" s="39">
+        <f t="shared" si="4"/>
+        <v>16819893.130000003</v>
+      </c>
+    </row>
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" s="33">
         <v>55</v>
       </c>
@@ -7195,7 +7466,7 @@
         <v>46302</v>
       </c>
       <c r="D61" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="E61" s="33" t="s">
@@ -7245,7 +7516,7 @@
         <v>1</v>
       </c>
       <c r="T61" s="40">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>4.8140355882036952E-4</v>
       </c>
       <c r="U61" s="39">
@@ -7254,8 +7525,12 @@
       <c r="V61" s="41">
         <v>1013</v>
       </c>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y61" s="39">
+        <f t="shared" si="4"/>
+        <v>18921768.130000003</v>
+      </c>
+    </row>
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62" s="33">
         <v>56</v>
       </c>
@@ -7266,7 +7541,7 @@
         <v>46310</v>
       </c>
       <c r="D62" s="35">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>7</v>
       </c>
       <c r="E62" s="33" t="s">
@@ -7316,7 +7591,7 @@
         <v>1</v>
       </c>
       <c r="T62" s="40">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>7.1805336310784623E-3</v>
       </c>
       <c r="U62" s="39">
@@ -7325,8 +7600,12 @@
       <c r="V62" s="41">
         <v>1492</v>
       </c>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y62" s="39">
+        <f t="shared" si="4"/>
+        <v>19131044.130000003</v>
+      </c>
+    </row>
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" s="33">
         <v>56</v>
       </c>
@@ -7337,7 +7616,7 @@
         <v>46310</v>
       </c>
       <c r="D63" s="35">
-        <f t="shared" ref="D63:D66" si="13">C63-B63</f>
+        <f t="shared" ref="D63:D66" si="14">C63-B63</f>
         <v>7</v>
       </c>
       <c r="E63" s="33" t="s">
@@ -7386,7 +7665,7 @@
         <v>1</v>
       </c>
       <c r="T63" s="40">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>5.6809619963232071E-3</v>
       </c>
       <c r="U63" s="39">
@@ -7395,8 +7674,12 @@
       <c r="V63" s="41">
         <v>1318</v>
       </c>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y63" s="39">
+        <f t="shared" si="4"/>
+        <v>19363311.130000003</v>
+      </c>
+    </row>
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" s="33">
         <v>57</v>
       </c>
@@ -7404,11 +7687,11 @@
         <v>46310</v>
       </c>
       <c r="C64" s="54">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D64" s="55">
-        <f t="shared" si="13"/>
-        <v>1</v>
+        <f t="shared" si="14"/>
+        <v>4</v>
       </c>
       <c r="E64" s="47" t="s">
         <v>624</v>
@@ -7465,10 +7748,14 @@
         <v>66</v>
       </c>
       <c r="W64" s="33">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
+        <v>206</v>
+      </c>
+      <c r="Y64" s="39">
+        <f t="shared" si="4"/>
+        <v>19368295.130000003</v>
+      </c>
+    </row>
+    <row r="65" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A65" s="33">
         <v>58</v>
       </c>
@@ -7476,11 +7763,11 @@
         <v>46310</v>
       </c>
       <c r="C65" s="54">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="D65" s="55">
-        <f t="shared" si="13"/>
-        <v>1</v>
+        <f t="shared" si="14"/>
+        <v>4</v>
       </c>
       <c r="E65" s="47" t="s">
         <v>626</v>
@@ -7537,247 +7824,336 @@
         <v>66</v>
       </c>
       <c r="W65" s="33">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
+        <v>534</v>
+      </c>
+      <c r="Y65" s="39">
+        <f t="shared" si="4"/>
+        <v>19382336.130000003</v>
+      </c>
+    </row>
+    <row r="66" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A66" s="33">
         <v>59</v>
       </c>
       <c r="B66" s="34">
         <v>46310</v>
       </c>
-      <c r="C66" s="54">
-        <v>46311</v>
-      </c>
-      <c r="D66" s="55">
-        <f t="shared" si="13"/>
+      <c r="C66" s="34">
+        <v>46314</v>
+      </c>
+      <c r="D66" s="35">
+        <f t="shared" si="14"/>
+        <v>4</v>
+      </c>
+      <c r="E66" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="F66" s="33" t="s">
+        <v>741</v>
+      </c>
+      <c r="G66" s="36" t="s">
+        <v>629</v>
+      </c>
+      <c r="H66" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I66" s="36" t="s">
+        <v>636</v>
+      </c>
+      <c r="J66" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="K66" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" s="33" t="s">
+        <v>628</v>
+      </c>
+      <c r="M66" s="33">
+        <v>-1956</v>
+      </c>
+      <c r="N66" s="33">
+        <v>46.65</v>
+      </c>
+      <c r="O66" s="33">
+        <v>46.613</v>
+      </c>
+      <c r="P66" s="33">
+        <v>46.613</v>
+      </c>
+      <c r="Q66" s="39">
+        <v>90954</v>
+      </c>
+      <c r="R66" s="33">
+        <v>23.41</v>
+      </c>
+      <c r="S66" s="33">
         <v>1</v>
       </c>
-      <c r="E66" s="47" t="s">
-        <v>628</v>
-      </c>
-      <c r="F66" s="47" t="s">
-        <v>741</v>
-      </c>
-      <c r="G66" s="48" t="s">
-        <v>629</v>
-      </c>
-      <c r="H66" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="I66" s="48" t="s">
-        <v>636</v>
-      </c>
-      <c r="J66" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="K66" s="47" t="s">
-        <v>23</v>
-      </c>
-      <c r="L66" s="47" t="s">
-        <v>628</v>
-      </c>
-      <c r="M66" s="47">
-        <v>-1956</v>
-      </c>
-      <c r="N66" s="47">
-        <v>46.65</v>
-      </c>
-      <c r="O66" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="P66" s="47">
-        <v>46.5</v>
-      </c>
-      <c r="Q66" s="49">
-        <v>90954</v>
-      </c>
-      <c r="R66" s="47">
-        <v>4.32</v>
-      </c>
-      <c r="S66" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="T66" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="U66" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="V66" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="W66" s="33">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="T66" s="40">
+        <f t="shared" ref="T66" si="15">IF(S66=1, ABS(O66-N66)/N66, 0)</f>
+        <v>7.9314040728829653E-4</v>
+      </c>
+      <c r="U66" s="33">
+        <v>95</v>
+      </c>
+      <c r="V66" s="41">
+        <v>95</v>
+      </c>
+      <c r="Y66" s="39">
+        <f t="shared" si="4"/>
+        <v>19473290.130000003</v>
+      </c>
+    </row>
+    <row r="67" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A67" s="33">
         <v>60</v>
       </c>
       <c r="B67" s="34">
         <v>46310</v>
       </c>
-      <c r="C67" s="54">
-        <v>46311</v>
-      </c>
-      <c r="D67" s="55">
-        <f t="shared" ref="D67" si="14">C67-B67</f>
+      <c r="C67" s="34">
+        <v>46314</v>
+      </c>
+      <c r="D67" s="35">
+        <f t="shared" ref="D67:D68" si="16">C67-B67</f>
+        <v>4</v>
+      </c>
+      <c r="E67" s="33" t="s">
+        <v>630</v>
+      </c>
+      <c r="F67" s="33" t="s">
+        <v>742</v>
+      </c>
+      <c r="G67" s="36" t="s">
+        <v>631</v>
+      </c>
+      <c r="H67" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I67" s="36" t="s">
+        <v>635</v>
+      </c>
+      <c r="J67" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="K67" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" s="33" t="s">
+        <v>630</v>
+      </c>
+      <c r="M67" s="33">
+        <v>-700</v>
+      </c>
+      <c r="N67" s="33">
+        <v>388.43</v>
+      </c>
+      <c r="O67" s="33">
+        <v>386.34</v>
+      </c>
+      <c r="P67" s="33">
+        <v>386.34</v>
+      </c>
+      <c r="Q67" s="39">
+        <v>271913</v>
+      </c>
+      <c r="R67" s="33">
+        <v>10.98</v>
+      </c>
+      <c r="S67" s="33">
         <v>1</v>
       </c>
-      <c r="E67" s="47" t="s">
-        <v>630</v>
-      </c>
-      <c r="F67" s="47" t="s">
-        <v>742</v>
-      </c>
-      <c r="G67" s="48" t="s">
-        <v>631</v>
-      </c>
-      <c r="H67" s="47" t="s">
+      <c r="T67" s="40">
+        <f t="shared" ref="T67" si="17">IF(S67=1, ABS(O67-N67)/N67, 0)</f>
+        <v>5.3806348634246369E-3</v>
+      </c>
+      <c r="U67" s="33">
+        <v>1470</v>
+      </c>
+      <c r="V67" s="41">
+        <v>1470</v>
+      </c>
+      <c r="Y67" s="39">
+        <f t="shared" si="4"/>
+        <v>19745203.130000003</v>
+      </c>
+    </row>
+    <row r="68" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A68" s="33">
+        <v>61</v>
+      </c>
+      <c r="B68" s="34">
+        <v>46314</v>
+      </c>
+      <c r="C68" s="54">
+        <v>46314</v>
+      </c>
+      <c r="D68" s="55">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="E68" s="47" t="s">
+        <v>746</v>
+      </c>
+      <c r="F68" s="47" t="s">
+        <v>747</v>
+      </c>
+      <c r="G68" s="48" t="s">
+        <v>748</v>
+      </c>
+      <c r="H68" s="47" t="s">
         <v>22</v>
       </c>
-      <c r="I67" s="48" t="s">
-        <v>635</v>
-      </c>
-      <c r="J67" s="47" t="s">
+      <c r="I68" s="48" t="s">
+        <v>749</v>
+      </c>
+      <c r="J68" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="K67" s="47" t="s">
+      <c r="K68" s="47" t="s">
         <v>23</v>
       </c>
-      <c r="L67" s="47" t="s">
-        <v>630</v>
-      </c>
-      <c r="M67" s="47">
-        <v>-310</v>
-      </c>
-      <c r="N67" s="47">
-        <v>388.43</v>
-      </c>
-      <c r="O67" s="47" t="s">
+      <c r="L68" s="47" t="s">
+        <v>746</v>
+      </c>
+      <c r="M68" s="47">
+        <v>-330</v>
+      </c>
+      <c r="N68" s="47">
+        <v>47.295999999999999</v>
+      </c>
+      <c r="O68" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="P67" s="47">
-        <v>384.22</v>
-      </c>
-      <c r="Q67" s="49">
-        <v>115266</v>
-      </c>
-      <c r="R67" s="47">
-        <v>3.66</v>
-      </c>
-      <c r="S67" s="47" t="s">
+      <c r="P68" s="47">
+        <v>46.8</v>
+      </c>
+      <c r="Q68" s="49">
+        <v>15431</v>
+      </c>
+      <c r="R68" s="47">
+        <v>2.12</v>
+      </c>
+      <c r="S68" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="T67" s="47" t="s">
+      <c r="T68" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="U67" s="47" t="s">
+      <c r="U68" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="V67" s="47" t="s">
+      <c r="V68" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="W67" s="33">
-        <v>1265</v>
-      </c>
-    </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="B68" s="34"/>
-      <c r="C68" s="34"/>
-      <c r="D68" s="35"/>
-      <c r="G68" s="36"/>
-      <c r="I68" s="36"/>
-      <c r="Q68" s="39"/>
-      <c r="T68" s="40"/>
-      <c r="U68" s="39"/>
-      <c r="V68" s="41"/>
-    </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="W68" s="33">
+        <v>177</v>
+      </c>
+      <c r="Y68" s="39">
+        <f t="shared" si="4"/>
+        <v>19760634.130000003</v>
+      </c>
+      <c r="Z68" s="58">
+        <f>Y68/424000</f>
+        <v>46.60526917452831</v>
+      </c>
+    </row>
+    <row r="69" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B69" s="34"/>
+      <c r="C69" s="34"/>
+      <c r="D69" s="35"/>
       <c r="G69" s="36"/>
       <c r="I69" s="36"/>
-    </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="D70" s="51" t="s">
+      <c r="Q69" s="39"/>
+      <c r="T69" s="40"/>
+      <c r="U69" s="39"/>
+      <c r="V69" s="41"/>
+      <c r="Y69" s="39"/>
+    </row>
+    <row r="70" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="G70" s="36"/>
+      <c r="I70" s="36"/>
+    </row>
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D71" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="E70" s="46">
+      <c r="E71" s="46">
         <f>AVERAGE(D2:D63)</f>
         <v>6.4838709677419351</v>
       </c>
-      <c r="F70" s="46"/>
-      <c r="G70" s="36"/>
-      <c r="I70" s="36"/>
-      <c r="V70" s="39">
-        <f>SUM(V2:V68)</f>
-        <v>88002.47</v>
-      </c>
-      <c r="W70" s="39">
-        <f>SUM(W2:W68)</f>
-        <v>1860</v>
-      </c>
-      <c r="X70" s="39">
-        <f>SUM(X2:X68)</f>
-        <v>0</v>
-      </c>
-      <c r="Y70" s="39"/>
-    </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="D71" s="51" t="s">
+      <c r="F71" s="46"/>
+      <c r="G71" s="36"/>
+      <c r="I71" s="36"/>
+      <c r="V71" s="39">
+        <f>SUM(V2:V69)</f>
+        <v>89567.47</v>
+      </c>
+      <c r="W71" s="39">
+        <f>SUM(W2:W69)</f>
+        <v>917</v>
+      </c>
+      <c r="X71" s="39">
+        <f>SUM(X2:X69)</f>
+        <v>0</v>
+      </c>
+      <c r="Y71" s="39"/>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D72" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="E71" s="46">
+      <c r="E72" s="46">
         <f>AVERAGE(D2:D11,D13,D15:D63)</f>
         <v>4.7666666666666666</v>
       </c>
-      <c r="F71" s="46"/>
-      <c r="G71" s="36"/>
-      <c r="V71" s="52" t="s">
+      <c r="F72" s="46"/>
+      <c r="G72" s="36"/>
+      <c r="V72" s="52" t="s">
         <v>96</v>
       </c>
-      <c r="W71" s="36" t="s">
+      <c r="W72" s="36" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="G72" s="36"/>
-      <c r="V72" s="33" t="s">
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="G73" s="36"/>
+      <c r="V73" s="33" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="G73" s="36"/>
-      <c r="V73" s="39">
-        <f>V70+W70</f>
-        <v>89862.47</v>
-      </c>
-    </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
       <c r="G74" s="36"/>
-    </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="V74" s="39">
+        <f>V71+W71</f>
+        <v>90484.47</v>
+      </c>
+    </row>
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="G75" s="36"/>
-      <c r="V75" s="36" t="s">
+    </row>
+    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="G76" s="36"/>
+      <c r="V76" s="36" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="G76" s="36"/>
-      <c r="V76" s="39">
+    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="G77" s="36"/>
+      <c r="V77" s="39">
         <v>333000</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="V78" s="33" t="s">
+    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="V79" s="33" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="V79" s="53">
-        <f>V73/V76</f>
-        <v>0.26985726726726728</v>
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="V80" s="53">
+        <f>V74/V77</f>
+        <v>0.27172513513513513</v>
       </c>
     </row>
   </sheetData>
@@ -7790,7 +8166,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:I93"/>
+  <dimension ref="A1:I94"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -7856,11 +8232,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C93" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C94" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D93" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D94" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -9036,11 +9412,11 @@
         <v>105</v>
       </c>
       <c r="G74" s="27">
-        <f>AVERAGE(C3:C93)</f>
+        <f>AVERAGE(C3:C94)</f>
+        <v>998.26184782608664</v>
+      </c>
+      <c r="I74" s="27">
         <v>1001.8361538461535</v>
-      </c>
-      <c r="I74" s="27">
-        <v>994.70099999999968</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -9063,11 +9439,11 @@
         <v>106</v>
       </c>
       <c r="G75" s="27">
-        <f>_xlfn.STDEV.S(C3:C93)</f>
+        <f>_xlfn.STDEV.S(C3:C94)</f>
+        <v>4019.7041349130682</v>
+      </c>
+      <c r="I75" s="27">
         <v>4041.8271217339247</v>
-      </c>
-      <c r="I75" s="27">
-        <v>4063.8942233804319</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
@@ -9091,10 +9467,10 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
+        <v>3.9423089421909632</v>
+      </c>
+      <c r="I76" s="28">
         <v>3.934768961181994</v>
-      </c>
-      <c r="I76" s="28">
-        <v>3.8855314585596612</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
@@ -9117,11 +9493,11 @@
         <v>108</v>
       </c>
       <c r="G77" s="29">
-        <f>_xlfn.STDEV.S(D2:D93)*SQRT(252)</f>
+        <f>_xlfn.STDEV.S(D2:D94)*SQRT(252)</f>
+        <v>0.17205540287833648</v>
+      </c>
+      <c r="I77" s="29">
         <v>0.17298853160364927</v>
-      </c>
-      <c r="I77" s="29">
-        <v>0.17393524693700121</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -9144,11 +9520,11 @@
         <v>109</v>
       </c>
       <c r="G78" s="29" cm="1">
-        <f t="array" ref="G78">PRODUCT(1+D3:D93)-1</f>
+        <f t="array" ref="G78">PRODUCT(1+D3:D94)-1</f>
+        <v>0.27541918702596813</v>
+      </c>
+      <c r="I78" s="29">
         <v>0.27340092888841583</v>
-      </c>
-      <c r="I78" s="29">
-        <v>0.26847074110515279</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -9171,11 +9547,11 @@
         <v>110</v>
       </c>
       <c r="G79" s="29" cm="1">
-        <f t="array" ref="G79">PRODUCT(1+D2:D93)^(252/COUNT(D2:D93))-1</f>
+        <f t="array" ref="G79">PRODUCT(1+D2:D94)^(252/COUNT(D2:D94))-1</f>
+        <v>0.93323835265666988</v>
+      </c>
+      <c r="I79" s="29">
         <v>0.93871187618965823</v>
-      </c>
-      <c r="I79" s="29">
-        <v>0.93200128707868957</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -9414,6 +9790,23 @@
       <c r="D93" s="23">
         <f t="shared" si="1"/>
         <v>3.886717780315335E-3</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A94" s="26">
+        <v>46314</v>
+      </c>
+      <c r="B94" s="5">
+        <f>B93-232+145+481+303-24</f>
+        <v>425296</v>
+      </c>
+      <c r="C94" s="5">
+        <f t="shared" si="0"/>
+        <v>673</v>
+      </c>
+      <c r="D94" s="23">
+        <f t="shared" si="1"/>
+        <v>1.5849353426451228E-3</v>
       </c>
     </row>
   </sheetData>
@@ -14367,7 +14760,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="14">
-        <f t="shared" ref="M69:M100" si="0">SUM(C69:L69)</f>
+        <f t="shared" ref="M69:M101" si="0">SUM(C69:L69)</f>
         <v>407651</v>
       </c>
       <c r="N69" s="15">
@@ -16271,7 +16664,7 @@
         <v>160440</v>
       </c>
       <c r="D94" s="13">
-        <f t="shared" ref="D94:D100" si="73">B94-C94-H94-L94-F94</f>
+        <f t="shared" ref="D94:D101" si="73">B94-C94-H94-L94-F94</f>
         <v>76736</v>
       </c>
       <c r="E94" s="13">
@@ -16822,6 +17215,86 @@
       </c>
       <c r="W100" s="15">
         <f t="shared" ref="W100" si="118">L100/M100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A101" s="10">
+        <v>46314</v>
+      </c>
+      <c r="B101" s="11">
+        <v>425296</v>
+      </c>
+      <c r="C101" s="19">
+        <v>34456</v>
+      </c>
+      <c r="D101" s="13">
+        <f t="shared" si="73"/>
+        <v>390840</v>
+      </c>
+      <c r="E101" s="13">
+        <v>0</v>
+      </c>
+      <c r="F101" s="13">
+        <v>0</v>
+      </c>
+      <c r="G101" s="13">
+        <v>0</v>
+      </c>
+      <c r="H101" s="13">
+        <v>0</v>
+      </c>
+      <c r="I101" s="13">
+        <v>0</v>
+      </c>
+      <c r="J101" s="13">
+        <v>0</v>
+      </c>
+      <c r="K101" s="13">
+        <v>0</v>
+      </c>
+      <c r="L101" s="18">
+        <v>0</v>
+      </c>
+      <c r="M101" s="14">
+        <f t="shared" si="0"/>
+        <v>425296</v>
+      </c>
+      <c r="N101" s="15">
+        <f t="shared" ref="N101" si="119">C101/M101</f>
+        <v>8.1016515556224369E-2</v>
+      </c>
+      <c r="O101" s="15">
+        <f t="shared" ref="O101" si="120">D101/M101</f>
+        <v>0.91898348444377564</v>
+      </c>
+      <c r="P101" s="15">
+        <f t="shared" ref="P101" si="121">E101/N101</f>
+        <v>0</v>
+      </c>
+      <c r="Q101" s="15">
+        <f t="shared" ref="Q101" si="122">E101/M101</f>
+        <v>0</v>
+      </c>
+      <c r="R101" s="15">
+        <v>0</v>
+      </c>
+      <c r="S101" s="15">
+        <v>0</v>
+      </c>
+      <c r="T101" s="15">
+        <f t="shared" ref="T101" si="123">I101/M101</f>
+        <v>0</v>
+      </c>
+      <c r="U101" s="15">
+        <v>0</v>
+      </c>
+      <c r="V101" s="16">
+        <f t="shared" ref="V101" si="124">K101/M101</f>
+        <v>0</v>
+      </c>
+      <c r="W101" s="15">
+        <f t="shared" ref="W101" si="125">L101/M101</f>
         <v>0</v>
       </c>
     </row>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B195C62-1C32-B74C-8C06-5F13BE7F4FE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B00E1C5D-4368-6E41-89F5-6F78A5FEB266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="23940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3208,7 +3208,7 @@
         <v>-4105.18</v>
       </c>
       <c r="Y3" s="39">
-        <f>Y2+Q3</f>
+        <f t="shared" ref="Y3:Y13" si="3">Y2+Q3</f>
         <v>244379.5</v>
       </c>
     </row>
@@ -3282,7 +3282,7 @@
         <v>0</v>
       </c>
       <c r="Y4" s="39">
-        <f>Y3+Q4</f>
+        <f t="shared" si="3"/>
         <v>907729.5</v>
       </c>
     </row>
@@ -3357,7 +3357,7 @@
         <v>11150</v>
       </c>
       <c r="Y5" s="39">
-        <f>Y4+Q5</f>
+        <f t="shared" si="3"/>
         <v>3802629.5</v>
       </c>
     </row>
@@ -3431,7 +3431,7 @@
         <v>6343</v>
       </c>
       <c r="Y6" s="39">
-        <f>Y5+Q6</f>
+        <f t="shared" si="3"/>
         <v>4264098.25</v>
       </c>
     </row>
@@ -3506,7 +3506,7 @@
         <v>-6010</v>
       </c>
       <c r="Y7" s="39">
-        <f>Y6+Q7</f>
+        <f t="shared" si="3"/>
         <v>4395338.25</v>
       </c>
     </row>
@@ -3581,7 +3581,7 @@
         <v>4681.25</v>
       </c>
       <c r="Y8" s="39">
-        <f>Y7+Q8</f>
+        <f t="shared" si="3"/>
         <v>7520119.25</v>
       </c>
     </row>
@@ -3656,7 +3656,7 @@
         <v>0</v>
       </c>
       <c r="Y9" s="39">
-        <f>Y8+Q9</f>
+        <f t="shared" si="3"/>
         <v>7616618.25</v>
       </c>
     </row>
@@ -3730,7 +3730,7 @@
         <v>2338.1999999999998</v>
       </c>
       <c r="Y10" s="39">
-        <f>Y9+Q10</f>
+        <f t="shared" si="3"/>
         <v>7713215.0499999998</v>
       </c>
     </row>
@@ -3804,7 +3804,7 @@
         <v>0</v>
       </c>
       <c r="Y11" s="39">
-        <f>Y10+Q11</f>
+        <f t="shared" si="3"/>
         <v>7915340.0499999998</v>
       </c>
     </row>
@@ -3878,7 +3878,7 @@
         <v>4588</v>
       </c>
       <c r="Y12" s="39">
-        <f>Y11+Q12</f>
+        <f t="shared" si="3"/>
         <v>8139183.3300000001</v>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
         <v>1</v>
       </c>
       <c r="T13" s="40">
-        <f t="shared" ref="T13:T19" si="3">IF(S13=1, ABS(O13-N13)/N13, 0)</f>
+        <f t="shared" ref="T13:T19" si="4">IF(S13=1, ABS(O13-N13)/N13, 0)</f>
         <v>8.5709094212773618E-2</v>
       </c>
       <c r="U13" s="42">
@@ -3953,7 +3953,7 @@
         <v>4717</v>
       </c>
       <c r="Y13" s="39">
-        <f>Y12+Q13</f>
+        <f t="shared" si="3"/>
         <v>8194218.3300000001</v>
       </c>
     </row>
@@ -4017,7 +4017,7 @@
         <v>0</v>
       </c>
       <c r="T14" s="40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="U14" s="39">
@@ -4027,7 +4027,7 @@
         <v>-16354</v>
       </c>
       <c r="Y14" s="39">
-        <f t="shared" ref="Y14:Y69" si="4">Y13+Q14</f>
+        <f t="shared" ref="Y14:Y68" si="5">Y13+Q14</f>
         <v>8315282.3300000001</v>
       </c>
     </row>
@@ -4092,7 +4092,7 @@
         <v>1</v>
       </c>
       <c r="T15" s="40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.2139625080801483E-2</v>
       </c>
       <c r="U15" s="39">
@@ -4102,7 +4102,7 @@
         <v>2568.75</v>
       </c>
       <c r="Y15" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8431307.3300000001</v>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
         <v>1</v>
       </c>
       <c r="T16" s="40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.5693152386489792E-2</v>
       </c>
       <c r="U16" s="42">
@@ -4177,7 +4177,7 @@
         <v>4149.45</v>
       </c>
       <c r="Y16" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8522118.5299999993</v>
       </c>
     </row>
@@ -4242,7 +4242,7 @@
         <v>1</v>
       </c>
       <c r="T17" s="40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.9999102817154174E-2</v>
       </c>
       <c r="U17" s="39">
@@ -4252,7 +4252,7 @@
         <v>11150</v>
       </c>
       <c r="Y17" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8754778.5299999993</v>
       </c>
     </row>
@@ -4317,7 +4317,7 @@
         <v>1</v>
       </c>
       <c r="T18" s="40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>2.0001183501982336E-2</v>
       </c>
       <c r="U18" s="39">
@@ -4327,7 +4327,7 @@
         <v>2033</v>
       </c>
       <c r="Y18" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8856742.5299999993</v>
       </c>
     </row>
@@ -4391,7 +4391,7 @@
         <v>1</v>
       </c>
       <c r="T19" s="40">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>3.2654344970491629E-3</v>
       </c>
       <c r="U19" s="39">
@@ -4401,7 +4401,7 @@
         <v>177</v>
       </c>
       <c r="Y19" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>8910793.5299999993</v>
       </c>
     </row>
@@ -4475,7 +4475,7 @@
         <v>4060</v>
       </c>
       <c r="Y20" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9096175.5299999993</v>
       </c>
     </row>
@@ -4549,7 +4549,7 @@
         <v>0</v>
       </c>
       <c r="Y21" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9260795.5299999993</v>
       </c>
     </row>
@@ -4623,7 +4623,7 @@
         <v>2838</v>
       </c>
       <c r="Y22" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9415085.5299999993</v>
       </c>
     </row>
@@ -4697,7 +4697,7 @@
         <v>6742</v>
       </c>
       <c r="Y23" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>9597790.5299999993</v>
       </c>
     </row>
@@ -4770,7 +4770,7 @@
         <v>1245</v>
       </c>
       <c r="Y24" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11048790.529999999</v>
       </c>
     </row>
@@ -4834,7 +4834,7 @@
         <v>1</v>
       </c>
       <c r="T25" s="40">
-        <f t="shared" ref="T25:T36" si="5">IF(S25=1, ABS(O25-N25)/N25, 0)</f>
+        <f t="shared" ref="T25:T36" si="6">IF(S25=1, ABS(O25-N25)/N25, 0)</f>
         <v>3.9539800653504951E-3</v>
       </c>
       <c r="U25" s="39">
@@ -4844,7 +4844,7 @@
         <v>1710</v>
       </c>
       <c r="Y25" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11485025.529999999</v>
       </c>
     </row>
@@ -4859,7 +4859,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D62" si="6">C26-B26</f>
+        <f t="shared" ref="D26:D62" si="7">C26-B26</f>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
@@ -4908,7 +4908,7 @@
         <v>1</v>
       </c>
       <c r="T26" s="40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.4025752021974973E-3</v>
       </c>
       <c r="U26" s="39">
@@ -4918,7 +4918,7 @@
         <v>715</v>
       </c>
       <c r="Y26" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11626225.529999999</v>
       </c>
     </row>
@@ -4981,7 +4981,7 @@
         <v>1</v>
       </c>
       <c r="T27" s="40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.623408180713668E-2</v>
       </c>
       <c r="U27" s="39">
@@ -4991,7 +4991,7 @@
         <v>3498</v>
       </c>
       <c r="Y27" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11759563.529999999</v>
       </c>
     </row>
@@ -5006,7 +5006,7 @@
         <v>46266</v>
       </c>
       <c r="D28" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E28" s="33" t="s">
@@ -5055,7 +5055,7 @@
         <v>1</v>
       </c>
       <c r="T28" s="40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>3.0251341995685504E-2</v>
       </c>
       <c r="U28" s="39">
@@ -5065,7 +5065,7 @@
         <v>1809</v>
       </c>
       <c r="Y28" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>11819362.529999999</v>
       </c>
     </row>
@@ -5080,7 +5080,7 @@
         <v>46268</v>
       </c>
       <c r="D29" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="E29" s="33" t="s">
@@ -5129,7 +5129,7 @@
         <v>1</v>
       </c>
       <c r="T29" s="40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.7141972539147393E-3</v>
       </c>
       <c r="U29" s="39">
@@ -5139,7 +5139,7 @@
         <v>2891</v>
       </c>
       <c r="Y29" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12062085.529999999</v>
       </c>
     </row>
@@ -5154,7 +5154,7 @@
         <v>46268</v>
       </c>
       <c r="D30" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="E30" s="33" t="s">
@@ -5203,7 +5203,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U30" s="39">
@@ -5213,7 +5213,7 @@
         <v>-642</v>
       </c>
       <c r="Y30" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12357102.529999999</v>
       </c>
     </row>
@@ -5228,7 +5228,7 @@
         <v>46267</v>
       </c>
       <c r="D31" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E31" s="33" t="s">
@@ -5277,7 +5277,7 @@
         <v>1</v>
       </c>
       <c r="T31" s="40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>8.455326735182055E-3</v>
       </c>
       <c r="U31" s="39">
@@ -5287,7 +5287,7 @@
         <v>4108</v>
       </c>
       <c r="Y31" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12489704.529999999</v>
       </c>
     </row>
@@ -5302,7 +5302,7 @@
         <v>46283</v>
       </c>
       <c r="D32" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>17</v>
       </c>
       <c r="E32" s="33" t="s">
@@ -5351,7 +5351,7 @@
         <v>1</v>
       </c>
       <c r="T32" s="40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.8185412136785959E-2</v>
       </c>
       <c r="U32" s="39">
@@ -5361,7 +5361,7 @@
         <v>7389</v>
       </c>
       <c r="Y32" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>12887035.529999999</v>
       </c>
     </row>
@@ -5376,7 +5376,7 @@
         <v>46276</v>
       </c>
       <c r="D33" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="E33" s="33" t="s">
@@ -5425,7 +5425,7 @@
         <v>1</v>
       </c>
       <c r="T33" s="40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.9886363636363667E-2</v>
       </c>
       <c r="U33" s="39">
@@ -5435,7 +5435,7 @@
         <v>2247</v>
       </c>
       <c r="Y33" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13000063.529999999</v>
       </c>
     </row>
@@ -5450,7 +5450,7 @@
         <v>46276</v>
       </c>
       <c r="D34" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="E34" s="33" t="s">
@@ -5499,7 +5499,7 @@
         <v>1</v>
       </c>
       <c r="T34" s="40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>9.8159124408065835E-3</v>
       </c>
       <c r="U34" s="39">
@@ -5509,7 +5509,7 @@
         <v>1253</v>
       </c>
       <c r="Y34" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13127610.529999999</v>
       </c>
     </row>
@@ -5524,7 +5524,7 @@
         <v>46279</v>
       </c>
       <c r="D35" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="E35" s="33" t="s">
@@ -5573,7 +5573,7 @@
         <v>1</v>
       </c>
       <c r="T35" s="40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>5.3725127878096988E-3</v>
       </c>
       <c r="U35" s="39">
@@ -5583,7 +5583,7 @@
         <v>141</v>
       </c>
       <c r="Y35" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13153641.529999999</v>
       </c>
     </row>
@@ -5598,7 +5598,7 @@
         <v>46283</v>
       </c>
       <c r="D36" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="E36" s="33" t="s">
@@ -5647,7 +5647,7 @@
         <v>0</v>
       </c>
       <c r="T36" s="40">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0</v>
       </c>
       <c r="U36" s="39">
@@ -5657,7 +5657,7 @@
         <v>-3825</v>
       </c>
       <c r="Y36" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13342137.529999999</v>
       </c>
     </row>
@@ -5672,7 +5672,7 @@
         <v>46276</v>
       </c>
       <c r="D37" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E37" s="33" t="s">
@@ -5721,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="T37" s="40">
-        <f t="shared" ref="T37:T40" si="7">IF(S37=1, ABS(O37-N37)/N37, 0)</f>
+        <f t="shared" ref="T37:T40" si="8">IF(S37=1, ABS(O37-N37)/N37, 0)</f>
         <v>1.2137203166226873E-2</v>
       </c>
       <c r="U37" s="39">
@@ -5731,7 +5731,7 @@
         <v>345</v>
       </c>
       <c r="Y37" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13370907.529999999</v>
       </c>
     </row>
@@ -5746,7 +5746,7 @@
         <v>46276</v>
       </c>
       <c r="D38" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E38" s="33" t="s">
@@ -5795,7 +5795,7 @@
         <v>1</v>
       </c>
       <c r="T38" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>1.8280016618196831E-3</v>
       </c>
       <c r="U38" s="39">
@@ -5805,7 +5805,7 @@
         <v>220</v>
       </c>
       <c r="Y38" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13491277.529999999</v>
       </c>
     </row>
@@ -5820,7 +5820,7 @@
         <v>46288</v>
       </c>
       <c r="D39" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="E39" s="33" t="s">
@@ -5870,7 +5870,7 @@
         <v>1</v>
       </c>
       <c r="T39" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>2.3968322438641332E-2</v>
       </c>
       <c r="U39" s="39">
@@ -5880,7 +5880,7 @@
         <v>2167</v>
       </c>
       <c r="Y39" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13581688.529999999</v>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
         <v>46288</v>
       </c>
       <c r="D40" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5</v>
       </c>
       <c r="E40" s="33" t="s">
@@ -5945,7 +5945,7 @@
         <v>0</v>
       </c>
       <c r="T40" s="40">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0</v>
       </c>
       <c r="U40" s="39">
@@ -5955,7 +5955,7 @@
         <v>-438</v>
       </c>
       <c r="Y40" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13617290.029999999</v>
       </c>
     </row>
@@ -5970,7 +5970,7 @@
         <v>46288</v>
       </c>
       <c r="D41" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="E41" s="33" t="s">
@@ -6019,7 +6019,7 @@
         <v>0</v>
       </c>
       <c r="T41" s="40">
-        <f t="shared" ref="T41:T44" si="8">IF(S41=1, ABS(O41-N41)/N41, 0)</f>
+        <f t="shared" ref="T41:T44" si="9">IF(S41=1, ABS(O41-N41)/N41, 0)</f>
         <v>0</v>
       </c>
       <c r="U41" s="39">
@@ -6029,7 +6029,7 @@
         <v>-317</v>
       </c>
       <c r="Y41" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13673192.029999999</v>
       </c>
     </row>
@@ -6044,7 +6044,7 @@
         <v>46288</v>
       </c>
       <c r="D42" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="E42" s="33" t="s">
@@ -6094,7 +6094,7 @@
         <v>1</v>
       </c>
       <c r="T42" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>1.9242297247460509E-2</v>
       </c>
       <c r="U42" s="39">
@@ -6104,7 +6104,7 @@
         <v>1721</v>
       </c>
       <c r="Y42" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13762673.029999999</v>
       </c>
     </row>
@@ -6119,7 +6119,7 @@
         <v>46301</v>
       </c>
       <c r="D43" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="E43" s="33" t="s">
@@ -6169,7 +6169,7 @@
         <v>0</v>
       </c>
       <c r="T43" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>0</v>
       </c>
       <c r="U43" s="39">
@@ -6179,7 +6179,7 @@
         <v>-2814</v>
       </c>
       <c r="Y43" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>13879125.029999999</v>
       </c>
     </row>
@@ -6194,7 +6194,7 @@
         <v>46288</v>
       </c>
       <c r="D44" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="E44" s="33" t="s">
@@ -6244,7 +6244,7 @@
         <v>1</v>
       </c>
       <c r="T44" s="40">
-        <f t="shared" si="8"/>
+        <f t="shared" si="9"/>
         <v>9.1189909260570284E-3</v>
       </c>
       <c r="U44" s="39">
@@ -6254,7 +6254,7 @@
         <v>1134</v>
       </c>
       <c r="Y44" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14003437.029999999</v>
       </c>
     </row>
@@ -6269,7 +6269,7 @@
         <v>46286</v>
       </c>
       <c r="D45" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E45" s="33" t="s">
@@ -6318,7 +6318,7 @@
         <v>1</v>
       </c>
       <c r="T45" s="40">
-        <f t="shared" ref="T45:T48" si="9">IF(S45=1, ABS(O45-N45)/N45, 0)</f>
+        <f t="shared" ref="T45:T48" si="10">IF(S45=1, ABS(O45-N45)/N45, 0)</f>
         <v>6.6957880304817775E-4</v>
       </c>
       <c r="U45" s="39">
@@ -6328,7 +6328,7 @@
         <v>108</v>
       </c>
       <c r="Y45" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14160155.029999999</v>
       </c>
     </row>
@@ -6343,7 +6343,7 @@
         <v>46288</v>
       </c>
       <c r="D46" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E46" s="33" t="s">
@@ -6393,7 +6393,7 @@
         <v>0</v>
       </c>
       <c r="T46" s="40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0</v>
       </c>
       <c r="U46" s="39">
@@ -6403,7 +6403,7 @@
         <v>-664</v>
       </c>
       <c r="Y46" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14197575.029999999</v>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
         <v>46303</v>
       </c>
       <c r="D47" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>15</v>
       </c>
       <c r="E47" s="33" t="s">
@@ -6468,7 +6468,7 @@
         <v>1</v>
       </c>
       <c r="T47" s="40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.1600874329984955E-2</v>
       </c>
       <c r="U47" s="39">
@@ -6478,7 +6478,7 @@
         <v>3476</v>
       </c>
       <c r="Y47" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14354955.029999999</v>
       </c>
     </row>
@@ -6493,7 +6493,7 @@
         <v>46296</v>
       </c>
       <c r="D48" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8</v>
       </c>
       <c r="E48" s="33" t="s">
@@ -6543,7 +6543,7 @@
         <v>1</v>
       </c>
       <c r="T48" s="40">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.5463403580330705E-2</v>
       </c>
       <c r="U48" s="39">
@@ -6553,7 +6553,7 @@
         <v>1895</v>
       </c>
       <c r="Y48" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14407911.029999999</v>
       </c>
     </row>
@@ -6568,7 +6568,7 @@
         <v>46290</v>
       </c>
       <c r="D49" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E49" s="33" t="s">
@@ -6617,7 +6617,7 @@
         <v>1</v>
       </c>
       <c r="T49" s="40">
-        <f t="shared" ref="T49:T52" si="10">IF(S49=1, ABS(O49-N49)/N49, 0)</f>
+        <f t="shared" ref="T49:T52" si="11">IF(S49=1, ABS(O49-N49)/N49, 0)</f>
         <v>2.0138262699128395E-2</v>
       </c>
       <c r="U49" s="39">
@@ -6627,7 +6627,7 @@
         <v>338</v>
       </c>
       <c r="Y49" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14424131.029999999</v>
       </c>
     </row>
@@ -6642,7 +6642,7 @@
         <v>46290</v>
       </c>
       <c r="D50" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E50" s="33" t="s">
@@ -6691,7 +6691,7 @@
         <v>1</v>
       </c>
       <c r="T50" s="40">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>1.0891738306862922E-2</v>
       </c>
       <c r="U50" s="39">
@@ -6701,7 +6701,7 @@
         <v>2245</v>
       </c>
       <c r="Y50" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14630020.029999999</v>
       </c>
     </row>
@@ -6716,7 +6716,7 @@
         <v>46296</v>
       </c>
       <c r="D51" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3</v>
       </c>
       <c r="E51" s="33" t="s">
@@ -6756,7 +6756,7 @@
         <v>82.27</v>
       </c>
       <c r="Q51" s="39">
-        <f t="shared" ref="Q51:Q58" si="11">ABS(N51*M51)</f>
+        <f t="shared" ref="Q51:Q58" si="12">ABS(N51*M51)</f>
         <v>59087</v>
       </c>
       <c r="R51" s="33">
@@ -6766,7 +6766,7 @@
         <v>0</v>
       </c>
       <c r="T51" s="40">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="U51" s="39">
@@ -6776,7 +6776,7 @@
         <v>-1498</v>
       </c>
       <c r="Y51" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14689107.029999999</v>
       </c>
     </row>
@@ -6791,7 +6791,7 @@
         <v>46297</v>
       </c>
       <c r="D52" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="E52" s="33" t="s">
@@ -6831,7 +6831,7 @@
         <v>466.29</v>
       </c>
       <c r="Q52" s="39">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>49278.9</v>
       </c>
       <c r="R52" s="33">
@@ -6841,7 +6841,7 @@
         <v>0</v>
       </c>
       <c r="T52" s="40">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>0</v>
       </c>
       <c r="U52" s="39">
@@ -6851,7 +6851,7 @@
         <v>-2013</v>
       </c>
       <c r="Y52" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14738385.93</v>
       </c>
     </row>
@@ -6866,7 +6866,7 @@
         <v>46295</v>
       </c>
       <c r="D53" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>2</v>
       </c>
       <c r="E53" s="33" t="s">
@@ -6906,7 +6906,7 @@
         <v>20.21</v>
       </c>
       <c r="Q53" s="39">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>81080</v>
       </c>
       <c r="R53" s="33">
@@ -6916,7 +6916,7 @@
         <v>0</v>
       </c>
       <c r="T53" s="40">
-        <f t="shared" ref="T53:T55" si="12">IF(S53=1, ABS(O53-N53)/N53, 0)</f>
+        <f t="shared" ref="T53:T55" si="13">IF(S53=1, ABS(O53-N53)/N53, 0)</f>
         <v>0</v>
       </c>
       <c r="U53" s="39">
@@ -6926,7 +6926,7 @@
         <v>-214</v>
       </c>
       <c r="Y53" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14819465.93</v>
       </c>
     </row>
@@ -6941,7 +6941,7 @@
         <v>46301</v>
       </c>
       <c r="D54" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="E54" s="33" t="s">
@@ -6981,7 +6981,7 @@
         <v>282.18</v>
       </c>
       <c r="Q54" s="39">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>112565.4</v>
       </c>
       <c r="R54" s="33">
@@ -6991,7 +6991,7 @@
         <v>1</v>
       </c>
       <c r="T54" s="40">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>2.7237499267093006E-3</v>
       </c>
       <c r="U54" s="39">
@@ -7001,7 +7001,7 @@
         <v>307</v>
       </c>
       <c r="Y54" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>14932031.33</v>
       </c>
     </row>
@@ -7016,7 +7016,7 @@
         <v>46301</v>
       </c>
       <c r="D55" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="E55" s="33" t="s">
@@ -7056,7 +7056,7 @@
         <v>779.63</v>
       </c>
       <c r="Q55" s="39">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>107494.8</v>
       </c>
       <c r="R55" s="33">
@@ -7066,7 +7066,7 @@
         <v>0</v>
       </c>
       <c r="T55" s="40">
-        <f t="shared" si="12"/>
+        <f t="shared" si="13"/>
         <v>0</v>
       </c>
       <c r="U55" s="39">
@@ -7076,7 +7076,7 @@
         <v>-1653</v>
       </c>
       <c r="Y55" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>15039526.130000001</v>
       </c>
     </row>
@@ -7091,7 +7091,7 @@
         <v>46296</v>
       </c>
       <c r="D56" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E56" s="33" t="s">
@@ -7131,7 +7131,7 @@
         <v>434.77</v>
       </c>
       <c r="Q56" s="39">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>44700</v>
       </c>
       <c r="R56" s="33">
@@ -7141,7 +7141,7 @@
         <v>1</v>
       </c>
       <c r="T56" s="40">
-        <f t="shared" ref="T56:T63" si="13">IF(S56=1, ABS(O56-N56)/N56, 0)</f>
+        <f t="shared" ref="T56:T63" si="14">IF(S56=1, ABS(O56-N56)/N56, 0)</f>
         <v>2.7360178970917266E-2</v>
       </c>
       <c r="U56" s="39">
@@ -7151,7 +7151,7 @@
         <v>1222</v>
       </c>
       <c r="Y56" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>15084226.130000001</v>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
         <v>46296</v>
       </c>
       <c r="D57" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E57" s="33" t="s">
@@ -7206,7 +7206,7 @@
         <v>666.83</v>
       </c>
       <c r="Q57" s="39">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>67415</v>
       </c>
       <c r="R57" s="33">
@@ -7216,7 +7216,7 @@
         <v>1</v>
       </c>
       <c r="T57" s="40">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.0858117629607559E-2</v>
       </c>
       <c r="U57" s="39">
@@ -7226,7 +7226,7 @@
         <v>880</v>
       </c>
       <c r="Y57" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>15151641.130000001</v>
       </c>
     </row>
@@ -7241,7 +7241,7 @@
         <v>46296</v>
       </c>
       <c r="D58" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E58" s="33" t="s">
@@ -7281,7 +7281,7 @@
         <v>332.03</v>
       </c>
       <c r="Q58" s="39">
-        <f t="shared" si="11"/>
+        <f t="shared" si="12"/>
         <v>65255.999999999993</v>
       </c>
       <c r="R58" s="33">
@@ -7291,7 +7291,7 @@
         <v>1</v>
       </c>
       <c r="T58" s="40">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>1.762290057619223E-2</v>
       </c>
       <c r="U58" s="39">
@@ -7301,7 +7301,7 @@
         <v>1058</v>
       </c>
       <c r="Y58" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>15216897.130000001</v>
       </c>
     </row>
@@ -7316,7 +7316,7 @@
         <v>46310</v>
       </c>
       <c r="D59" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>13</v>
       </c>
       <c r="E59" s="33" t="s">
@@ -7365,7 +7365,7 @@
         <v>1</v>
       </c>
       <c r="T59" s="40">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.1615147713014791E-2</v>
       </c>
       <c r="U59" s="39">
@@ -7376,7 +7376,7 @@
         <v>569</v>
       </c>
       <c r="Y59" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>15243767.130000001</v>
       </c>
     </row>
@@ -7391,7 +7391,7 @@
         <v>46300</v>
       </c>
       <c r="D60" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
       <c r="E60" s="33" t="s">
@@ -7441,7 +7441,7 @@
         <v>1</v>
       </c>
       <c r="T60" s="40">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>2.3162583518930384E-3</v>
       </c>
       <c r="U60" s="39">
@@ -7451,7 +7451,7 @@
         <v>925</v>
       </c>
       <c r="Y60" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>16819893.130000003</v>
       </c>
     </row>
@@ -7466,7 +7466,7 @@
         <v>46302</v>
       </c>
       <c r="D61" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0</v>
       </c>
       <c r="E61" s="33" t="s">
@@ -7516,7 +7516,7 @@
         <v>1</v>
       </c>
       <c r="T61" s="40">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>4.8140355882036952E-4</v>
       </c>
       <c r="U61" s="39">
@@ -7526,7 +7526,7 @@
         <v>1013</v>
       </c>
       <c r="Y61" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>18921768.130000003</v>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
         <v>46310</v>
       </c>
       <c r="D62" s="35">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="E62" s="33" t="s">
@@ -7591,7 +7591,7 @@
         <v>1</v>
       </c>
       <c r="T62" s="40">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>7.1805336310784623E-3</v>
       </c>
       <c r="U62" s="39">
@@ -7601,7 +7601,7 @@
         <v>1492</v>
       </c>
       <c r="Y62" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19131044.130000003</v>
       </c>
     </row>
@@ -7616,7 +7616,7 @@
         <v>46310</v>
       </c>
       <c r="D63" s="35">
-        <f t="shared" ref="D63:D66" si="14">C63-B63</f>
+        <f t="shared" ref="D63:D66" si="15">C63-B63</f>
         <v>7</v>
       </c>
       <c r="E63" s="33" t="s">
@@ -7665,7 +7665,7 @@
         <v>1</v>
       </c>
       <c r="T63" s="40">
-        <f t="shared" si="13"/>
+        <f t="shared" si="14"/>
         <v>5.6809619963232071E-3</v>
       </c>
       <c r="U63" s="39">
@@ -7675,7 +7675,7 @@
         <v>1318</v>
       </c>
       <c r="Y63" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19363311.130000003</v>
       </c>
     </row>
@@ -7690,7 +7690,7 @@
         <v>46314</v>
       </c>
       <c r="D64" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="E64" s="47" t="s">
@@ -7727,7 +7727,7 @@
         <v>66</v>
       </c>
       <c r="P64" s="47">
-        <v>7.91</v>
+        <v>7.89</v>
       </c>
       <c r="Q64" s="49">
         <v>4984</v>
@@ -7751,7 +7751,7 @@
         <v>206</v>
       </c>
       <c r="Y64" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19368295.130000003</v>
       </c>
     </row>
@@ -7766,7 +7766,7 @@
         <v>46314</v>
       </c>
       <c r="D65" s="55">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="E65" s="47" t="s">
@@ -7803,7 +7803,7 @@
         <v>66</v>
       </c>
       <c r="P65" s="47">
-        <v>28.12</v>
+        <v>27.5</v>
       </c>
       <c r="Q65" s="49">
         <v>14041</v>
@@ -7827,7 +7827,7 @@
         <v>534</v>
       </c>
       <c r="Y65" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19382336.130000003</v>
       </c>
     </row>
@@ -7842,7 +7842,7 @@
         <v>46314</v>
       </c>
       <c r="D66" s="35">
-        <f t="shared" si="14"/>
+        <f t="shared" si="15"/>
         <v>4</v>
       </c>
       <c r="E66" s="33" t="s">
@@ -7891,7 +7891,7 @@
         <v>1</v>
       </c>
       <c r="T66" s="40">
-        <f t="shared" ref="T66" si="15">IF(S66=1, ABS(O66-N66)/N66, 0)</f>
+        <f t="shared" ref="T66" si="16">IF(S66=1, ABS(O66-N66)/N66, 0)</f>
         <v>7.9314040728829653E-4</v>
       </c>
       <c r="U66" s="33">
@@ -7901,7 +7901,7 @@
         <v>95</v>
       </c>
       <c r="Y66" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19473290.130000003</v>
       </c>
     </row>
@@ -7916,7 +7916,7 @@
         <v>46314</v>
       </c>
       <c r="D67" s="35">
-        <f t="shared" ref="D67:D68" si="16">C67-B67</f>
+        <f t="shared" ref="D67:D68" si="17">C67-B67</f>
         <v>4</v>
       </c>
       <c r="E67" s="33" t="s">
@@ -7965,7 +7965,7 @@
         <v>1</v>
       </c>
       <c r="T67" s="40">
-        <f t="shared" ref="T67" si="17">IF(S67=1, ABS(O67-N67)/N67, 0)</f>
+        <f t="shared" ref="T67" si="18">IF(S67=1, ABS(O67-N67)/N67, 0)</f>
         <v>5.3806348634246369E-3</v>
       </c>
       <c r="U67" s="33">
@@ -7975,7 +7975,7 @@
         <v>1470</v>
       </c>
       <c r="Y67" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19745203.130000003</v>
       </c>
     </row>
@@ -7990,7 +7990,7 @@
         <v>46314</v>
       </c>
       <c r="D68" s="55">
-        <f t="shared" si="16"/>
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="E68" s="47" t="s">
@@ -8051,7 +8051,7 @@
         <v>177</v>
       </c>
       <c r="Y68" s="39">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>19760634.130000003</v>
       </c>
       <c r="Z68" s="58">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B00E1C5D-4368-6E41-89F5-6F78A5FEB266}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0200605-B21B-5648-A33D-0C9BC0FC375C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="23940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1070" uniqueCount="752">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="759">
   <si>
     <t>Trade ID</t>
   </si>
@@ -2320,6 +2320,27 @@
   </si>
   <si>
     <t>Gross_Exposure_pct</t>
+  </si>
+  <si>
+    <t>RY</t>
+  </si>
+  <si>
+    <t>ry</t>
+  </si>
+  <si>
+    <t>Royal Bank of Canada</t>
+  </si>
+  <si>
+    <t>RY (+) TD (-)</t>
+  </si>
+  <si>
+    <t>TD</t>
+  </si>
+  <si>
+    <t>td</t>
+  </si>
+  <si>
+    <t>Toronto Dominion Bank</t>
   </si>
 </sst>
 </file>
@@ -2957,7 +2978,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z80"/>
+  <dimension ref="A1:Z81"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5" style="33" bestFit="1" customWidth="1"/>
@@ -7687,11 +7708,11 @@
         <v>46310</v>
       </c>
       <c r="C64" s="54">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D64" s="55">
         <f t="shared" si="15"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E64" s="47" t="s">
         <v>624</v>
@@ -7718,22 +7739,22 @@
         <v>624</v>
       </c>
       <c r="M64" s="47">
-        <v>1220</v>
+        <v>1820</v>
       </c>
       <c r="N64" s="47">
-        <v>7.74</v>
+        <v>7.82</v>
       </c>
       <c r="O64" s="47" t="s">
         <v>66</v>
       </c>
       <c r="P64" s="47">
-        <v>7.89</v>
+        <v>7.92</v>
       </c>
       <c r="Q64" s="49">
-        <v>4984</v>
+        <v>14487</v>
       </c>
       <c r="R64" s="47">
-        <v>1.01</v>
+        <v>3.03</v>
       </c>
       <c r="S64" s="47" t="s">
         <v>66</v>
@@ -7748,11 +7769,11 @@
         <v>66</v>
       </c>
       <c r="W64" s="33">
-        <v>206</v>
+        <v>245</v>
       </c>
       <c r="Y64" s="39">
         <f t="shared" si="5"/>
-        <v>19368295.130000003</v>
+        <v>19377798.130000003</v>
       </c>
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.25">
@@ -7763,11 +7784,11 @@
         <v>46310</v>
       </c>
       <c r="C65" s="54">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D65" s="55">
         <f t="shared" si="15"/>
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E65" s="47" t="s">
         <v>626</v>
@@ -7794,19 +7815,19 @@
         <v>626</v>
       </c>
       <c r="M65" s="47">
-        <v>-504</v>
+        <v>-2242</v>
       </c>
       <c r="N65" s="47">
-        <v>28.216999999999999</v>
+        <v>28.315999999999999</v>
       </c>
       <c r="O65" s="47" t="s">
         <v>66</v>
       </c>
       <c r="P65" s="47">
-        <v>27.5</v>
+        <v>28.76</v>
       </c>
       <c r="Q65" s="49">
-        <v>14041</v>
+        <v>64480</v>
       </c>
       <c r="R65" s="47">
         <v>2.33</v>
@@ -7824,11 +7845,11 @@
         <v>66</v>
       </c>
       <c r="W65" s="33">
-        <v>534</v>
+        <v>-995</v>
       </c>
       <c r="Y65" s="39">
         <f t="shared" si="5"/>
-        <v>19382336.130000003</v>
+        <v>19442278.130000003</v>
       </c>
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.25">
@@ -7902,7 +7923,7 @@
       </c>
       <c r="Y66" s="39">
         <f t="shared" si="5"/>
-        <v>19473290.130000003</v>
+        <v>19533232.130000003</v>
       </c>
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.25">
@@ -7916,7 +7937,7 @@
         <v>46314</v>
       </c>
       <c r="D67" s="35">
-        <f t="shared" ref="D67:D68" si="17">C67-B67</f>
+        <f t="shared" ref="D67:D70" si="17">C67-B67</f>
         <v>4</v>
       </c>
       <c r="E67" s="33" t="s">
@@ -7976,7 +7997,7 @@
       </c>
       <c r="Y67" s="39">
         <f t="shared" si="5"/>
-        <v>19745203.130000003</v>
+        <v>19805145.130000003</v>
       </c>
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.25">
@@ -7987,11 +8008,11 @@
         <v>46314</v>
       </c>
       <c r="C68" s="54">
-        <v>46314</v>
+        <v>46316</v>
       </c>
       <c r="D68" s="55">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E68" s="47" t="s">
         <v>746</v>
@@ -8018,19 +8039,19 @@
         <v>746</v>
       </c>
       <c r="M68" s="47">
-        <v>-330</v>
+        <v>-851</v>
       </c>
       <c r="N68" s="47">
-        <v>47.295999999999999</v>
+        <v>47.387999999999998</v>
       </c>
       <c r="O68" s="47" t="s">
         <v>66</v>
       </c>
       <c r="P68" s="47">
-        <v>46.8</v>
+        <v>47</v>
       </c>
       <c r="Q68" s="49">
-        <v>15431</v>
+        <v>39997</v>
       </c>
       <c r="R68" s="47">
         <v>2.12</v>
@@ -8048,112 +8069,246 @@
         <v>66</v>
       </c>
       <c r="W68" s="33">
-        <v>177</v>
+        <v>331</v>
       </c>
       <c r="Y68" s="39">
         <f t="shared" si="5"/>
-        <v>19760634.130000003</v>
+        <v>19845142.130000003</v>
       </c>
       <c r="Z68" s="58">
         <f>Y68/424000</f>
-        <v>46.60526917452831</v>
+        <v>46.804580495283027</v>
       </c>
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B69" s="34"/>
-      <c r="C69" s="34"/>
-      <c r="D69" s="35"/>
-      <c r="G69" s="36"/>
-      <c r="I69" s="36"/>
-      <c r="Q69" s="39"/>
-      <c r="T69" s="40"/>
-      <c r="U69" s="39"/>
-      <c r="V69" s="41"/>
+      <c r="A69" s="33">
+        <v>62</v>
+      </c>
+      <c r="B69" s="34">
+        <v>46315</v>
+      </c>
+      <c r="C69" s="54">
+        <v>46316</v>
+      </c>
+      <c r="D69" s="55">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="E69" s="47" t="s">
+        <v>752</v>
+      </c>
+      <c r="F69" s="47" t="s">
+        <v>753</v>
+      </c>
+      <c r="G69" s="48" t="s">
+        <v>754</v>
+      </c>
+      <c r="H69" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="I69" s="48" t="s">
+        <v>755</v>
+      </c>
+      <c r="J69" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="K69" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" s="47" t="s">
+        <v>752</v>
+      </c>
+      <c r="M69" s="47">
+        <v>242</v>
+      </c>
+      <c r="N69" s="47">
+        <v>198.52</v>
+      </c>
+      <c r="O69" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="P69" s="47">
+        <v>199.05</v>
+      </c>
+      <c r="Q69" s="49">
+        <v>48170</v>
+      </c>
+      <c r="R69" s="47">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="S69" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="T69" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="U69" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="V69" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="W69" s="33">
+        <v>127</v>
+      </c>
       <c r="Y69" s="39"/>
     </row>
     <row r="70" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="G70" s="36"/>
-      <c r="I70" s="36"/>
+      <c r="A70" s="33">
+        <v>62</v>
+      </c>
+      <c r="B70" s="34">
+        <v>46315</v>
+      </c>
+      <c r="C70" s="54">
+        <v>46316</v>
+      </c>
+      <c r="D70" s="55">
+        <f t="shared" si="17"/>
+        <v>1</v>
+      </c>
+      <c r="E70" s="47" t="s">
+        <v>756</v>
+      </c>
+      <c r="F70" s="47" t="s">
+        <v>757</v>
+      </c>
+      <c r="G70" s="48" t="s">
+        <v>758</v>
+      </c>
+      <c r="H70" s="47" t="s">
+        <v>28</v>
+      </c>
+      <c r="I70" s="48" t="s">
+        <v>755</v>
+      </c>
+      <c r="J70" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="K70" s="47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" s="47" t="s">
+        <v>756</v>
+      </c>
+      <c r="M70" s="47">
+        <v>-400</v>
+      </c>
+      <c r="N70" s="47">
+        <v>121.55800000000001</v>
+      </c>
+      <c r="O70" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="P70" s="47">
+        <v>122.13</v>
+      </c>
+      <c r="Q70" s="49">
+        <v>48852</v>
+      </c>
+      <c r="R70" s="47">
+        <v>2.4500000000000002</v>
+      </c>
+      <c r="S70" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="T70" s="56" t="s">
+        <v>66</v>
+      </c>
+      <c r="U70" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="V70" s="47" t="s">
+        <v>66</v>
+      </c>
+      <c r="W70" s="33">
+        <v>-229</v>
+      </c>
+      <c r="Y70" s="39"/>
     </row>
     <row r="71" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D71" s="51" t="s">
+      <c r="G71" s="36"/>
+      <c r="I71" s="36"/>
+    </row>
+    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D72" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="E71" s="46">
+      <c r="E72" s="46">
         <f>AVERAGE(D2:D63)</f>
         <v>6.4838709677419351</v>
       </c>
-      <c r="F71" s="46"/>
-      <c r="G71" s="36"/>
-      <c r="I71" s="36"/>
-      <c r="V71" s="39">
-        <f>SUM(V2:V69)</f>
+      <c r="F72" s="46"/>
+      <c r="G72" s="36"/>
+      <c r="I72" s="36"/>
+      <c r="V72" s="39">
+        <f>SUM(V2:V70)</f>
         <v>89567.47</v>
       </c>
-      <c r="W71" s="39">
-        <f>SUM(W2:W69)</f>
-        <v>917</v>
-      </c>
-      <c r="X71" s="39">
-        <f>SUM(X2:X69)</f>
-        <v>0</v>
-      </c>
-      <c r="Y71" s="39"/>
-    </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D72" s="51" t="s">
+      <c r="W72" s="39">
+        <f>SUM(W2:W70)</f>
+        <v>-521</v>
+      </c>
+      <c r="X72" s="39">
+        <f>SUM(X2:X70)</f>
+        <v>0</v>
+      </c>
+      <c r="Y72" s="39"/>
+    </row>
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D73" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="E72" s="46">
+      <c r="E73" s="46">
         <f>AVERAGE(D2:D11,D13,D15:D63)</f>
         <v>4.7666666666666666</v>
       </c>
-      <c r="F72" s="46"/>
-      <c r="G72" s="36"/>
-      <c r="V72" s="52" t="s">
+      <c r="F73" s="46"/>
+      <c r="G73" s="36"/>
+      <c r="V73" s="52" t="s">
         <v>96</v>
       </c>
-      <c r="W72" s="36" t="s">
+      <c r="W73" s="36" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="G73" s="36"/>
-      <c r="V73" s="33" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="74" spans="1:26" x14ac:dyDescent="0.25">
       <c r="G74" s="36"/>
-      <c r="V74" s="39">
-        <f>V71+W71</f>
-        <v>90484.47</v>
+      <c r="V74" s="33" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="75" spans="1:26" x14ac:dyDescent="0.25">
       <c r="G75" s="36"/>
+      <c r="V75" s="39">
+        <f>V72+W72</f>
+        <v>89046.47</v>
+      </c>
     </row>
     <row r="76" spans="1:26" x14ac:dyDescent="0.25">
       <c r="G76" s="36"/>
-      <c r="V76" s="36" t="s">
-        <v>99</v>
-      </c>
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.25">
       <c r="G77" s="36"/>
-      <c r="V77" s="39">
+      <c r="V77" s="36" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="78" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="G78" s="36"/>
+      <c r="V78" s="39">
         <v>333000</v>
       </c>
     </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="V79" s="33" t="s">
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="V80" s="33" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="V80" s="53">
-        <f>V74/V77</f>
-        <v>0.27172513513513513</v>
+    <row r="81" spans="22:22" x14ac:dyDescent="0.25">
+      <c r="V81" s="53">
+        <f>V75/V78</f>
+        <v>0.26740681681681683</v>
       </c>
     </row>
   </sheetData>
@@ -8166,7 +8321,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:I94"/>
+  <dimension ref="A1:I95"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -8232,11 +8387,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C94" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C95" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D94" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D95" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -9412,11 +9567,11 @@
         <v>105</v>
       </c>
       <c r="G74" s="27">
-        <f>AVERAGE(C3:C94)</f>
+        <f>AVERAGE(C3:C95)</f>
+        <v>971.50634408602116</v>
+      </c>
+      <c r="I74" s="27">
         <v>998.26184782608664</v>
-      </c>
-      <c r="I74" s="27">
-        <v>1001.8361538461535</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -9439,11 +9594,11 @@
         <v>106</v>
       </c>
       <c r="G75" s="27">
-        <f>_xlfn.STDEV.S(C3:C94)</f>
+        <f>_xlfn.STDEV.S(C3:C95)</f>
+        <v>4006.1159949205462</v>
+      </c>
+      <c r="I75" s="27">
         <v>4019.7041349130682</v>
-      </c>
-      <c r="I75" s="27">
-        <v>4041.8271217339247</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
@@ -9467,10 +9622,10 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
+        <v>3.8496601498791141</v>
+      </c>
+      <c r="I76" s="28">
         <v>3.9423089421909632</v>
-      </c>
-      <c r="I76" s="28">
-        <v>3.934768961181994</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
@@ -9493,11 +9648,11 @@
         <v>108</v>
       </c>
       <c r="G77" s="29">
-        <f>_xlfn.STDEV.S(D2:D94)*SQRT(252)</f>
+        <f>_xlfn.STDEV.S(D2:D95)*SQRT(252)</f>
+        <v>0.17142680382144651</v>
+      </c>
+      <c r="I77" s="29">
         <v>0.17205540287833648</v>
-      </c>
-      <c r="I77" s="29">
-        <v>0.17298853160364927</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -9520,11 +9675,11 @@
         <v>109</v>
       </c>
       <c r="G78" s="29" cm="1">
-        <f t="array" ref="G78">PRODUCT(1+D3:D94)-1</f>
+        <f t="array" ref="G78">PRODUCT(1+D3:D95)-1</f>
+        <v>0.27095082948517613</v>
+      </c>
+      <c r="I78" s="29">
         <v>0.27541918702596813</v>
-      </c>
-      <c r="I78" s="29">
-        <v>0.27340092888841583</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -9547,11 +9702,11 @@
         <v>110</v>
       </c>
       <c r="G79" s="29" cm="1">
-        <f t="array" ref="G79">PRODUCT(1+D2:D94)^(252/COUNT(D2:D94))-1</f>
+        <f t="array" ref="G79">PRODUCT(1+D2:D95)^(252/COUNT(D2:D95))-1</f>
+        <v>0.90175106123334814</v>
+      </c>
+      <c r="I79" s="29">
         <v>0.93323835265666988</v>
-      </c>
-      <c r="I79" s="29">
-        <v>0.93871187618965823</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -9807,6 +9962,23 @@
       <c r="D94" s="23">
         <f t="shared" si="1"/>
         <v>1.5849353426451228E-3</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A95" s="26">
+        <v>46315</v>
+      </c>
+      <c r="B95" s="5">
+        <f>B94-1490</f>
+        <v>423806</v>
+      </c>
+      <c r="C95" s="5">
+        <f t="shared" si="0"/>
+        <v>-1490</v>
+      </c>
+      <c r="D95" s="23">
+        <f t="shared" si="1"/>
+        <v>-3.5034423084157858E-3</v>
       </c>
     </row>
   </sheetData>
@@ -14760,7 +14932,7 @@
         <v>0</v>
       </c>
       <c r="M69" s="14">
-        <f t="shared" ref="M69:M101" si="0">SUM(C69:L69)</f>
+        <f t="shared" ref="M69:M102" si="0">SUM(C69:L69)</f>
         <v>407651</v>
       </c>
       <c r="N69" s="15">
@@ -16664,7 +16836,7 @@
         <v>160440</v>
       </c>
       <c r="D94" s="13">
-        <f t="shared" ref="D94:D101" si="73">B94-C94-H94-L94-F94</f>
+        <f t="shared" ref="D94:D102" si="73">B94-C94-H94-L94-F94</f>
         <v>76736</v>
       </c>
       <c r="E94" s="13">
@@ -17298,11 +17470,92 @@
         <v>0</v>
       </c>
     </row>
+    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A102" s="10">
+        <v>46315</v>
+      </c>
+      <c r="B102" s="11">
+        <v>423806</v>
+      </c>
+      <c r="C102" s="19">
+        <v>215986</v>
+      </c>
+      <c r="D102" s="13">
+        <f t="shared" si="73"/>
+        <v>207820</v>
+      </c>
+      <c r="E102" s="13">
+        <v>0</v>
+      </c>
+      <c r="F102" s="13">
+        <v>0</v>
+      </c>
+      <c r="G102" s="13">
+        <v>0</v>
+      </c>
+      <c r="H102" s="13">
+        <v>0</v>
+      </c>
+      <c r="I102" s="13">
+        <v>0</v>
+      </c>
+      <c r="J102" s="13">
+        <v>0</v>
+      </c>
+      <c r="K102" s="13">
+        <v>0</v>
+      </c>
+      <c r="L102" s="18">
+        <v>0</v>
+      </c>
+      <c r="M102" s="14">
+        <f t="shared" si="0"/>
+        <v>423806</v>
+      </c>
+      <c r="N102" s="15">
+        <f t="shared" ref="N102" si="126">C102/M102</f>
+        <v>0.50963412504778127</v>
+      </c>
+      <c r="O102" s="15">
+        <f t="shared" ref="O102" si="127">D102/M102</f>
+        <v>0.49036587495221873</v>
+      </c>
+      <c r="P102" s="15">
+        <f t="shared" ref="P102" si="128">E102/N102</f>
+        <v>0</v>
+      </c>
+      <c r="Q102" s="15">
+        <f t="shared" ref="Q102" si="129">E102/M102</f>
+        <v>0</v>
+      </c>
+      <c r="R102" s="15">
+        <v>0</v>
+      </c>
+      <c r="S102" s="15">
+        <v>0</v>
+      </c>
+      <c r="T102" s="15">
+        <f t="shared" ref="T102" si="130">I102/M102</f>
+        <v>0</v>
+      </c>
+      <c r="U102" s="15">
+        <v>0</v>
+      </c>
+      <c r="V102" s="16">
+        <f t="shared" ref="V102" si="131">K102/M102</f>
+        <v>0</v>
+      </c>
+      <c r="W102" s="15">
+        <f t="shared" ref="W102" si="132">L102/M102</f>
+        <v>0</v>
+      </c>
+    </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1048543" s="10"/>
     </row>
-    <row r="1048576" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1048576" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1048576" s="10"/>
+      <c r="M1048576" s="14"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="N2:W1048576">

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F0200605-B21B-5648-A33D-0C9BC0FC375C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B42079BE-908C-0045-8E16-9DE54A54C089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="40960" windowHeight="23940" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-1720" yWindow="-27160" windowWidth="43440" windowHeight="23120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="759">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="764">
   <si>
     <t>Trade ID</t>
   </si>
@@ -2341,6 +2341,21 @@
   </si>
   <si>
     <t>Toronto Dominion Bank</t>
+  </si>
+  <si>
+    <t>YW</t>
+  </si>
+  <si>
+    <t>wheat</t>
+  </si>
+  <si>
+    <t>Wheat Futures</t>
+  </si>
+  <si>
+    <t>Wheat (+)</t>
+  </si>
+  <si>
+    <t>Agricultural_Exposure</t>
   </si>
 </sst>
 </file>
@@ -2978,7 +2993,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z81"/>
+  <dimension ref="A1:Z85"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5" style="33" bestFit="1" customWidth="1"/>
@@ -3094,7 +3109,7 @@
         <v>46181</v>
       </c>
       <c r="D2" s="35">
-        <f t="shared" ref="D2:D25" si="0">C2-B2</f>
+        <f>C2-B2</f>
         <v>6</v>
       </c>
       <c r="E2" s="33" t="s">
@@ -3131,7 +3146,7 @@
         <v>941.37</v>
       </c>
       <c r="P2" s="33">
-        <f t="shared" ref="P2:P11" si="1">O2</f>
+        <f t="shared" ref="P2:P11" si="0">O2</f>
         <v>941.37</v>
       </c>
       <c r="Q2" s="39">
@@ -3144,7 +3159,7 @@
         <v>1</v>
       </c>
       <c r="T2" s="40">
-        <f t="shared" ref="T2:T12" si="2">IF(S2=1, ABS(O2-N2)/N2, 0)</f>
+        <f t="shared" ref="T2:T12" si="1">IF(S2=1, ABS(O2-N2)/N2, 0)</f>
         <v>0.10949561071590727</v>
       </c>
       <c r="U2" s="39">
@@ -3169,7 +3184,7 @@
         <v>46185</v>
       </c>
       <c r="D3" s="35">
-        <f t="shared" si="0"/>
+        <f>C3-B3</f>
         <v>8</v>
       </c>
       <c r="E3" s="37" t="s">
@@ -3206,7 +3221,7 @@
         <v>317.27260000000001</v>
       </c>
       <c r="P3" s="33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>317.27260000000001</v>
       </c>
       <c r="Q3" s="42">
@@ -3219,7 +3234,7 @@
         <v>0</v>
       </c>
       <c r="T3" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U3" s="42">
@@ -3229,7 +3244,7 @@
         <v>-4105.18</v>
       </c>
       <c r="Y3" s="39">
-        <f t="shared" ref="Y3:Y13" si="3">Y2+Q3</f>
+        <f t="shared" ref="Y3:Y13" si="2">Y2+Q3</f>
         <v>244379.5</v>
       </c>
     </row>
@@ -3280,7 +3295,7 @@
         <v>63</v>
       </c>
       <c r="P4" s="33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>63</v>
       </c>
       <c r="Q4" s="39">
@@ -3293,7 +3308,7 @@
         <v>1</v>
       </c>
       <c r="T4" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5.0275118715610072E-2</v>
       </c>
       <c r="U4" s="39">
@@ -3303,7 +3318,7 @@
         <v>0</v>
       </c>
       <c r="Y4" s="39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>907729.5</v>
       </c>
     </row>
@@ -3318,7 +3333,7 @@
         <v>46182</v>
       </c>
       <c r="D5" s="35">
-        <f t="shared" si="0"/>
+        <f>C5-B5</f>
         <v>1</v>
       </c>
       <c r="E5" s="33" t="s">
@@ -3355,7 +3370,7 @@
         <v>1.1579600000000001</v>
       </c>
       <c r="P5" s="33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.1579600000000001</v>
       </c>
       <c r="Q5" s="39">
@@ -3368,7 +3383,7 @@
         <v>1</v>
       </c>
       <c r="T5" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.8664932813178418E-3</v>
       </c>
       <c r="U5" s="39">
@@ -3378,7 +3393,7 @@
         <v>11150</v>
       </c>
       <c r="Y5" s="39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>3802629.5</v>
       </c>
     </row>
@@ -3429,7 +3444,7 @@
         <v>66.92</v>
       </c>
       <c r="P6" s="33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>66.92</v>
       </c>
       <c r="Q6" s="39">
@@ -3442,7 +3457,7 @@
         <v>1</v>
       </c>
       <c r="T6" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>8.761368585972186E-2</v>
       </c>
       <c r="U6" s="39">
@@ -3452,7 +3467,7 @@
         <v>6343</v>
       </c>
       <c r="Y6" s="39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>4264098.25</v>
       </c>
     </row>
@@ -3467,7 +3482,7 @@
         <v>46195</v>
       </c>
       <c r="D7" s="35">
-        <f t="shared" si="0"/>
+        <f>C7-B7</f>
         <v>5</v>
       </c>
       <c r="E7" s="33" t="s">
@@ -3504,7 +3519,7 @@
         <v>4575</v>
       </c>
       <c r="P7" s="33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4575</v>
       </c>
       <c r="Q7" s="39">
@@ -3517,7 +3532,7 @@
         <v>0</v>
       </c>
       <c r="T7" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U7" s="39">
@@ -3527,7 +3542,7 @@
         <v>-6010</v>
       </c>
       <c r="Y7" s="39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>4395338.25</v>
       </c>
     </row>
@@ -3542,7 +3557,7 @@
         <v>46205</v>
       </c>
       <c r="D8" s="35">
-        <f t="shared" si="0"/>
+        <f>C8-B8</f>
         <v>11</v>
       </c>
       <c r="E8" s="33" t="s">
@@ -3579,7 +3594,7 @@
         <v>1.2517849999999999</v>
       </c>
       <c r="P8" s="33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>1.2517849999999999</v>
       </c>
       <c r="Q8" s="39">
@@ -3592,7 +3607,7 @@
         <v>1</v>
       </c>
       <c r="T8" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>1.4981048673406688E-3</v>
       </c>
       <c r="U8" s="39">
@@ -3602,7 +3617,7 @@
         <v>4681.25</v>
       </c>
       <c r="Y8" s="39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>7520119.25</v>
       </c>
     </row>
@@ -3617,7 +3632,7 @@
         <v>46203</v>
       </c>
       <c r="D9" s="35">
-        <f t="shared" si="0"/>
+        <f>C9-B9</f>
         <v>6</v>
       </c>
       <c r="E9" s="37" t="s">
@@ -3654,7 +3669,7 @@
         <v>242.61</v>
       </c>
       <c r="P9" s="33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>242.61</v>
       </c>
       <c r="Q9" s="42">
@@ -3667,7 +3682,7 @@
         <v>1</v>
       </c>
       <c r="T9" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>5.6477269194499897E-3</v>
       </c>
       <c r="U9" s="42">
@@ -3677,7 +3692,7 @@
         <v>0</v>
       </c>
       <c r="Y9" s="39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>7616618.25</v>
       </c>
     </row>
@@ -3728,7 +3743,7 @@
         <v>124.35</v>
       </c>
       <c r="P10" s="33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>124.35</v>
       </c>
       <c r="Q10" s="42">
@@ -3741,7 +3756,7 @@
         <v>1</v>
       </c>
       <c r="T10" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.9847779636592513E-2</v>
       </c>
       <c r="U10" s="42">
@@ -3751,7 +3766,7 @@
         <v>2338.1999999999998</v>
       </c>
       <c r="Y10" s="39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>7713215.0499999998</v>
       </c>
     </row>
@@ -3802,7 +3817,7 @@
         <v>4028.25</v>
       </c>
       <c r="P11" s="33">
-        <f t="shared" si="1"/>
+        <f t="shared" si="0"/>
         <v>4028.25</v>
       </c>
       <c r="Q11" s="39">
@@ -3815,7 +3830,7 @@
         <v>1</v>
       </c>
       <c r="T11" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>3.5250463821892395E-3</v>
       </c>
       <c r="U11" s="39">
@@ -3825,7 +3840,7 @@
         <v>0</v>
       </c>
       <c r="Y11" s="39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>7915340.0499999998</v>
       </c>
     </row>
@@ -3840,7 +3855,7 @@
         <v>46266</v>
       </c>
       <c r="D12" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="D12:D26" si="3">C12-B12</f>
         <v>64</v>
       </c>
       <c r="E12" s="37" t="s">
@@ -3889,7 +3904,7 @@
         <v>1</v>
       </c>
       <c r="T12" s="40">
-        <f t="shared" si="2"/>
+        <f t="shared" si="1"/>
         <v>2.0497383883003945E-2</v>
       </c>
       <c r="U12" s="42">
@@ -3899,7 +3914,7 @@
         <v>4588</v>
       </c>
       <c r="Y12" s="39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>8139183.3300000001</v>
       </c>
     </row>
@@ -3914,7 +3929,7 @@
         <v>46204</v>
       </c>
       <c r="D13" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="E13" s="37" t="s">
@@ -3974,7 +3989,7 @@
         <v>4717</v>
       </c>
       <c r="Y13" s="39">
-        <f t="shared" si="3"/>
+        <f t="shared" si="2"/>
         <v>8194218.3300000001</v>
       </c>
     </row>
@@ -3989,7 +4004,7 @@
         <v>46255</v>
       </c>
       <c r="D14" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>52</v>
       </c>
       <c r="E14" s="33" t="s">
@@ -4063,7 +4078,7 @@
         <v>46205</v>
       </c>
       <c r="D15" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E15" s="33" t="s">
@@ -4138,7 +4153,7 @@
         <v>46217</v>
       </c>
       <c r="D16" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>6</v>
       </c>
       <c r="E16" s="37" t="s">
@@ -4213,7 +4228,7 @@
         <v>46233</v>
       </c>
       <c r="D17" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="E17" s="33" t="s">
@@ -4288,7 +4303,7 @@
         <v>46233</v>
       </c>
       <c r="D18" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>3</v>
       </c>
       <c r="E18" s="33" t="s">
@@ -4363,7 +4378,7 @@
         <v>46268</v>
       </c>
       <c r="D19" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>24</v>
       </c>
       <c r="E19" s="33" t="s">
@@ -4437,7 +4452,7 @@
         <v>46254</v>
       </c>
       <c r="D20" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>10</v>
       </c>
       <c r="E20" s="33" t="s">
@@ -4511,7 +4526,7 @@
         <v>46259</v>
       </c>
       <c r="D21" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="E21" s="33" t="s">
@@ -4585,7 +4600,7 @@
         <v>46259</v>
       </c>
       <c r="D22" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>13</v>
       </c>
       <c r="E22" s="33" t="s">
@@ -4659,7 +4674,7 @@
         <v>46246</v>
       </c>
       <c r="D23" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E23" s="33" t="s">
@@ -4733,7 +4748,7 @@
         <v>46254</v>
       </c>
       <c r="D24" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="E24" s="33" t="s">
@@ -4806,7 +4821,7 @@
         <v>46257</v>
       </c>
       <c r="D25" s="35">
-        <f t="shared" si="0"/>
+        <f t="shared" si="3"/>
         <v>2</v>
       </c>
       <c r="E25" s="33" t="s">
@@ -4880,7 +4895,7 @@
         <v>46259</v>
       </c>
       <c r="D26" s="35">
-        <f t="shared" ref="D26:D62" si="7">C26-B26</f>
+        <f t="shared" si="3"/>
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
@@ -5027,7 +5042,7 @@
         <v>46266</v>
       </c>
       <c r="D28" s="35">
-        <f t="shared" si="7"/>
+        <f t="shared" ref="D28:D71" si="7">C28-B28</f>
         <v>1</v>
       </c>
       <c r="E28" s="33" t="s">
@@ -7637,7 +7652,7 @@
         <v>46310</v>
       </c>
       <c r="D63" s="35">
-        <f t="shared" ref="D63:D66" si="15">C63-B63</f>
+        <f t="shared" si="7"/>
         <v>7</v>
       </c>
       <c r="E63" s="33" t="s">
@@ -7708,11 +7723,11 @@
         <v>46310</v>
       </c>
       <c r="C64" s="54">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D64" s="55">
-        <f t="shared" si="15"/>
-        <v>6</v>
+        <f t="shared" si="7"/>
+        <v>7</v>
       </c>
       <c r="E64" s="47" t="s">
         <v>624</v>
@@ -7748,7 +7763,7 @@
         <v>66</v>
       </c>
       <c r="P64" s="47">
-        <v>7.92</v>
+        <v>7.9</v>
       </c>
       <c r="Q64" s="49">
         <v>14487</v>
@@ -7769,7 +7784,7 @@
         <v>66</v>
       </c>
       <c r="W64" s="33">
-        <v>245</v>
+        <v>146</v>
       </c>
       <c r="Y64" s="39">
         <f t="shared" si="5"/>
@@ -7784,11 +7799,11 @@
         <v>46310</v>
       </c>
       <c r="C65" s="54">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D65" s="55">
-        <f t="shared" si="15"/>
-        <v>6</v>
+        <f t="shared" si="7"/>
+        <v>7</v>
       </c>
       <c r="E65" s="47" t="s">
         <v>626</v>
@@ -7824,7 +7839,7 @@
         <v>66</v>
       </c>
       <c r="P65" s="47">
-        <v>28.76</v>
+        <v>28.5</v>
       </c>
       <c r="Q65" s="49">
         <v>64480</v>
@@ -7845,7 +7860,7 @@
         <v>66</v>
       </c>
       <c r="W65" s="33">
-        <v>-995</v>
+        <v>-412</v>
       </c>
       <c r="Y65" s="39">
         <f t="shared" si="5"/>
@@ -7863,7 +7878,7 @@
         <v>46314</v>
       </c>
       <c r="D66" s="35">
-        <f t="shared" si="15"/>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="E66" s="33" t="s">
@@ -7912,7 +7927,7 @@
         <v>1</v>
       </c>
       <c r="T66" s="40">
-        <f t="shared" ref="T66" si="16">IF(S66=1, ABS(O66-N66)/N66, 0)</f>
+        <f t="shared" ref="T66" si="15">IF(S66=1, ABS(O66-N66)/N66, 0)</f>
         <v>7.9314040728829653E-4</v>
       </c>
       <c r="U66" s="33">
@@ -7937,7 +7952,7 @@
         <v>46314</v>
       </c>
       <c r="D67" s="35">
-        <f t="shared" ref="D67:D70" si="17">C67-B67</f>
+        <f t="shared" si="7"/>
         <v>4</v>
       </c>
       <c r="E67" s="33" t="s">
@@ -7986,7 +8001,7 @@
         <v>1</v>
       </c>
       <c r="T67" s="40">
-        <f t="shared" ref="T67" si="18">IF(S67=1, ABS(O67-N67)/N67, 0)</f>
+        <f t="shared" ref="T67:T70" si="16">IF(S67=1, ABS(O67-N67)/N67, 0)</f>
         <v>5.3806348634246369E-3</v>
       </c>
       <c r="U67" s="33">
@@ -8008,11 +8023,11 @@
         <v>46314</v>
       </c>
       <c r="C68" s="54">
-        <v>46316</v>
+        <v>46317</v>
       </c>
       <c r="D68" s="55">
-        <f t="shared" si="17"/>
-        <v>2</v>
+        <f t="shared" si="7"/>
+        <v>3</v>
       </c>
       <c r="E68" s="47" t="s">
         <v>746</v>
@@ -8048,7 +8063,7 @@
         <v>66</v>
       </c>
       <c r="P68" s="47">
-        <v>47</v>
+        <v>46.63</v>
       </c>
       <c r="Q68" s="49">
         <v>39997</v>
@@ -8069,7 +8084,7 @@
         <v>66</v>
       </c>
       <c r="W68" s="33">
-        <v>331</v>
+        <v>645</v>
       </c>
       <c r="Y68" s="39">
         <f t="shared" si="5"/>
@@ -8087,69 +8102,67 @@
       <c r="B69" s="34">
         <v>46315</v>
       </c>
-      <c r="C69" s="54">
+      <c r="C69" s="34">
         <v>46316</v>
       </c>
-      <c r="D69" s="55">
-        <f t="shared" si="17"/>
+      <c r="D69" s="35">
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="E69" s="47" t="s">
+      <c r="E69" s="33" t="s">
         <v>752</v>
       </c>
-      <c r="F69" s="47" t="s">
+      <c r="F69" s="33" t="s">
         <v>753</v>
       </c>
-      <c r="G69" s="48" t="s">
+      <c r="G69" s="36" t="s">
         <v>754</v>
       </c>
-      <c r="H69" s="47" t="s">
+      <c r="H69" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="I69" s="48" t="s">
+      <c r="I69" s="36" t="s">
         <v>755</v>
       </c>
-      <c r="J69" s="47" t="s">
+      <c r="J69" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="K69" s="47" t="s">
+      <c r="K69" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="L69" s="47" t="s">
+      <c r="L69" s="33" t="s">
         <v>752</v>
       </c>
-      <c r="M69" s="47">
+      <c r="M69" s="33">
         <v>242</v>
       </c>
-      <c r="N69" s="47">
+      <c r="N69" s="33">
         <v>198.52</v>
       </c>
-      <c r="O69" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="P69" s="47">
-        <v>199.05</v>
-      </c>
-      <c r="Q69" s="49">
+      <c r="O69" s="33">
+        <v>200.75</v>
+      </c>
+      <c r="P69" s="33">
+        <v>200.75</v>
+      </c>
+      <c r="Q69" s="39">
         <v>48170</v>
       </c>
-      <c r="R69" s="47">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="S69" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="T69" s="56" t="s">
-        <v>66</v>
-      </c>
-      <c r="U69" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="V69" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="W69" s="33">
-        <v>127</v>
+      <c r="R69" s="33">
+        <v>3.91</v>
+      </c>
+      <c r="S69" s="33">
+        <v>1</v>
+      </c>
+      <c r="T69" s="40">
+        <f t="shared" si="16"/>
+        <v>1.1233125125931843E-2</v>
+      </c>
+      <c r="U69" s="33">
+        <v>540</v>
+      </c>
+      <c r="V69" s="41">
+        <v>0</v>
       </c>
       <c r="Y69" s="39"/>
     </row>
@@ -8160,155 +8173,256 @@
       <c r="B70" s="34">
         <v>46315</v>
       </c>
-      <c r="C70" s="54">
+      <c r="C70" s="34">
         <v>46316</v>
       </c>
-      <c r="D70" s="55">
-        <f t="shared" si="17"/>
+      <c r="D70" s="35">
+        <f t="shared" si="7"/>
         <v>1</v>
       </c>
-      <c r="E70" s="47" t="s">
+      <c r="E70" s="33" t="s">
         <v>756</v>
       </c>
-      <c r="F70" s="47" t="s">
+      <c r="F70" s="33" t="s">
         <v>757</v>
       </c>
-      <c r="G70" s="48" t="s">
+      <c r="G70" s="36" t="s">
         <v>758</v>
       </c>
-      <c r="H70" s="47" t="s">
+      <c r="H70" s="33" t="s">
         <v>28</v>
       </c>
-      <c r="I70" s="48" t="s">
+      <c r="I70" s="36" t="s">
         <v>755</v>
       </c>
-      <c r="J70" s="47" t="s">
+      <c r="J70" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="K70" s="47" t="s">
+      <c r="K70" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="L70" s="47" t="s">
+      <c r="L70" s="33" t="s">
         <v>756</v>
       </c>
-      <c r="M70" s="47">
+      <c r="M70" s="33">
         <v>-400</v>
       </c>
-      <c r="N70" s="47">
+      <c r="N70" s="33">
         <v>121.55800000000001</v>
       </c>
-      <c r="O70" s="47" t="s">
+      <c r="O70" s="33">
+        <v>123.6</v>
+      </c>
+      <c r="P70" s="33">
+        <v>123.6</v>
+      </c>
+      <c r="Q70" s="39">
+        <v>48852</v>
+      </c>
+      <c r="R70" s="33">
+        <v>6.37</v>
+      </c>
+      <c r="S70" s="33">
+        <v>0</v>
+      </c>
+      <c r="T70" s="40">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="U70" s="33">
+        <v>-813</v>
+      </c>
+      <c r="V70" s="45">
+        <v>-273</v>
+      </c>
+      <c r="Y70" s="39"/>
+    </row>
+    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="A71" s="33">
+        <v>63</v>
+      </c>
+      <c r="B71" s="34">
+        <v>46316</v>
+      </c>
+      <c r="C71" s="54">
+        <v>46317</v>
+      </c>
+      <c r="D71" s="55">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="E71" s="47" t="s">
+        <v>759</v>
+      </c>
+      <c r="F71" s="47" t="s">
+        <v>760</v>
+      </c>
+      <c r="G71" s="48" t="s">
+        <v>761</v>
+      </c>
+      <c r="H71" s="47" t="s">
+        <v>22</v>
+      </c>
+      <c r="I71" s="48" t="s">
+        <v>762</v>
+      </c>
+      <c r="J71" s="47" t="s">
+        <v>29</v>
+      </c>
+      <c r="K71" s="47" t="s">
+        <v>115</v>
+      </c>
+      <c r="L71" s="47" t="s">
+        <v>759</v>
+      </c>
+      <c r="M71" s="47">
+        <v>2</v>
+      </c>
+      <c r="N71" s="47">
+        <v>622.80999999999995</v>
+      </c>
+      <c r="O71" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="P70" s="47">
-        <v>122.13</v>
-      </c>
-      <c r="Q70" s="49">
-        <v>48852</v>
-      </c>
-      <c r="R70" s="47">
-        <v>2.4500000000000002</v>
-      </c>
-      <c r="S70" s="47" t="s">
+      <c r="P71" s="47">
+        <v>628</v>
+      </c>
+      <c r="Q71" s="49">
+        <v>12568</v>
+      </c>
+      <c r="R71" s="47">
+        <v>1.0900000000000001</v>
+      </c>
+      <c r="S71" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="T70" s="56" t="s">
+      <c r="T71" s="56" t="s">
         <v>66</v>
       </c>
-      <c r="U70" s="47" t="s">
+      <c r="U71" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="V70" s="47" t="s">
+      <c r="V71" s="47" t="s">
         <v>66</v>
       </c>
-      <c r="W70" s="33">
-        <v>-229</v>
-      </c>
-      <c r="Y70" s="39"/>
-    </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="G71" s="36"/>
-      <c r="I71" s="36"/>
+      <c r="W71" s="33">
+        <v>111</v>
+      </c>
+      <c r="Y71" s="39"/>
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D72" s="51" t="s">
+      <c r="B72" s="34"/>
+      <c r="C72" s="34"/>
+      <c r="D72" s="35"/>
+      <c r="G72" s="36"/>
+      <c r="I72" s="36"/>
+      <c r="Q72" s="39"/>
+      <c r="T72" s="40"/>
+      <c r="Y72" s="39"/>
+    </row>
+    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B73" s="34"/>
+      <c r="C73" s="34"/>
+      <c r="D73" s="35"/>
+      <c r="G73" s="36"/>
+      <c r="I73" s="36"/>
+      <c r="Q73" s="39"/>
+      <c r="T73" s="40"/>
+      <c r="Y73" s="39"/>
+    </row>
+    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="B74" s="34"/>
+      <c r="C74" s="34"/>
+      <c r="D74" s="35"/>
+      <c r="G74" s="36"/>
+      <c r="I74" s="36"/>
+      <c r="Q74" s="39"/>
+      <c r="T74" s="40"/>
+      <c r="Y74" s="39"/>
+    </row>
+    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="G75" s="36"/>
+      <c r="I75" s="36"/>
+    </row>
+    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D76" s="51" t="s">
         <v>94</v>
       </c>
-      <c r="E72" s="46">
+      <c r="E76" s="46">
         <f>AVERAGE(D2:D63)</f>
         <v>6.4838709677419351</v>
       </c>
-      <c r="F72" s="46"/>
-      <c r="G72" s="36"/>
-      <c r="I72" s="36"/>
-      <c r="V72" s="39">
+      <c r="F76" s="46"/>
+      <c r="G76" s="36"/>
+      <c r="I76" s="36"/>
+      <c r="V76" s="39">
         <f>SUM(V2:V70)</f>
-        <v>89567.47</v>
-      </c>
-      <c r="W72" s="39">
-        <f>SUM(W2:W70)</f>
-        <v>-521</v>
-      </c>
-      <c r="X72" s="39">
+        <v>89294.47</v>
+      </c>
+      <c r="W76" s="39">
+        <f>SUM(W2:W71)</f>
+        <v>490</v>
+      </c>
+      <c r="X76" s="39">
         <f>SUM(X2:X70)</f>
         <v>0</v>
       </c>
-      <c r="Y72" s="39"/>
-    </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D73" s="51" t="s">
+      <c r="Y76" s="39"/>
+    </row>
+    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="D77" s="51" t="s">
         <v>95</v>
       </c>
-      <c r="E73" s="46">
+      <c r="E77" s="46">
         <f>AVERAGE(D2:D11,D13,D15:D63)</f>
         <v>4.7666666666666666</v>
       </c>
-      <c r="F73" s="46"/>
-      <c r="G73" s="36"/>
-      <c r="V73" s="52" t="s">
+      <c r="F77" s="46"/>
+      <c r="G77" s="36"/>
+      <c r="V77" s="52" t="s">
         <v>96</v>
       </c>
-      <c r="W73" s="36" t="s">
+      <c r="W77" s="36" t="s">
         <v>97</v>
-      </c>
-    </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="G74" s="36"/>
-      <c r="V74" s="33" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="G75" s="36"/>
-      <c r="V75" s="39">
-        <f>V72+W72</f>
-        <v>89046.47</v>
-      </c>
-    </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="G76" s="36"/>
-    </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="G77" s="36"/>
-      <c r="V77" s="36" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="G78" s="36"/>
-      <c r="V78" s="39">
+      <c r="V78" s="33" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="79" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="G79" s="36"/>
+      <c r="V79" s="39">
+        <f>V76+W76</f>
+        <v>89784.47</v>
+      </c>
+    </row>
+    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
+      <c r="G80" s="36"/>
+    </row>
+    <row r="81" spans="7:22" x14ac:dyDescent="0.25">
+      <c r="G81" s="36"/>
+      <c r="V81" s="36" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="82" spans="7:22" x14ac:dyDescent="0.25">
+      <c r="G82" s="36"/>
+      <c r="V82" s="39">
         <v>333000</v>
       </c>
     </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="V80" s="33" t="s">
+    <row r="84" spans="7:22" x14ac:dyDescent="0.25">
+      <c r="V84" s="33" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="81" spans="22:22" x14ac:dyDescent="0.25">
-      <c r="V81" s="53">
-        <f>V75/V78</f>
-        <v>0.26740681681681683</v>
+    <row r="85" spans="7:22" x14ac:dyDescent="0.25">
+      <c r="V85" s="53">
+        <f>V79/V82</f>
+        <v>0.26962303303303303</v>
       </c>
     </row>
   </sheetData>
@@ -8321,7 +8435,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:I95"/>
+  <dimension ref="A1:I96"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -8387,11 +8501,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C95" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C96" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D95" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D96" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -9567,11 +9681,11 @@
         <v>105</v>
       </c>
       <c r="G74" s="27">
-        <f>AVERAGE(C3:C95)</f>
+        <f>AVERAGE(C3:C960)</f>
+        <v>971.66053191489323</v>
+      </c>
+      <c r="I74" s="27">
         <v>971.50634408602116</v>
-      </c>
-      <c r="I74" s="27">
-        <v>998.26184782608664</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -9594,11 +9708,11 @@
         <v>106</v>
       </c>
       <c r="G75" s="27">
-        <f>_xlfn.STDEV.S(C3:C95)</f>
+        <f>_xlfn.STDEV.S(C3:C960)</f>
+        <v>3984.5198053783611</v>
+      </c>
+      <c r="I75" s="27">
         <v>4006.1159949205462</v>
-      </c>
-      <c r="I75" s="27">
-        <v>4019.7041349130682</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
@@ -9622,10 +9736,10 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
+        <v>3.871139688280854</v>
+      </c>
+      <c r="I76" s="28">
         <v>3.8496601498791141</v>
-      </c>
-      <c r="I76" s="28">
-        <v>3.9423089421909632</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
@@ -9648,11 +9762,11 @@
         <v>108</v>
       </c>
       <c r="G77" s="29">
-        <f>_xlfn.STDEV.S(D2:D95)*SQRT(252)</f>
+        <f>_xlfn.STDEV.S(D2:D960)*SQRT(252)</f>
+        <v>0.17051315116727933</v>
+      </c>
+      <c r="I77" s="29">
         <v>0.17142680382144651</v>
-      </c>
-      <c r="I77" s="29">
-        <v>0.17205540287833648</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -9675,11 +9789,11 @@
         <v>109</v>
       </c>
       <c r="G78" s="29" cm="1">
-        <f t="array" ref="G78">PRODUCT(1+D3:D95)-1</f>
+        <f t="array" ref="G78">PRODUCT(1+D3:D960)-1</f>
+        <v>0.27390774259606276</v>
+      </c>
+      <c r="I78" s="29">
         <v>0.27095082948517613</v>
-      </c>
-      <c r="I78" s="29">
-        <v>0.27541918702596813</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -9702,11 +9816,11 @@
         <v>110</v>
       </c>
       <c r="G79" s="29" cm="1">
-        <f t="array" ref="G79">PRODUCT(1+D2:D95)^(252/COUNT(D2:D95))-1</f>
+        <f t="array" ref="G79">PRODUCT(1+D2:D960)^(252/COUNT(D2:D960))-1</f>
+        <v>0.90060697367872566</v>
+      </c>
+      <c r="I79" s="29">
         <v>0.90175106123334814</v>
-      </c>
-      <c r="I79" s="29">
-        <v>0.93323835265666988</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -9979,6 +10093,23 @@
       <c r="D95" s="23">
         <f t="shared" si="1"/>
         <v>-3.5034423084157858E-3</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A96" s="26">
+        <v>46316</v>
+      </c>
+      <c r="B96" s="5">
+        <f>B95+349+409-590+583+127+108</f>
+        <v>424792</v>
+      </c>
+      <c r="C96" s="5">
+        <f t="shared" si="0"/>
+        <v>986</v>
+      </c>
+      <c r="D96" s="23">
+        <f t="shared" si="1"/>
+        <v>2.3265361981661421E-3</v>
       </c>
     </row>
   </sheetData>
@@ -9989,7 +10120,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBFEDD2B-54BB-1449-BCF8-F93ADB145E3A}">
-  <dimension ref="A1:W1048576"/>
+  <dimension ref="A1:Y1048576"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12.6640625" style="20" bestFit="1" customWidth="1"/>
@@ -10000,22 +10131,24 @@
     <col min="6" max="7" width="9.33203125" style="13" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="10" style="13" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="9.33203125" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="9.33203125" style="13" customWidth="1"/>
-    <col min="12" max="12" width="9.33203125" style="18" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="15.83203125" style="21" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="18" style="17" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="16.33203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="18.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="20.5" style="16" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="16.6640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="20.33203125" style="16" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="17.1640625" style="16" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="17.1640625" style="16" customWidth="1"/>
-    <col min="23" max="23" width="14.83203125" style="17" bestFit="1" customWidth="1"/>
-    <col min="24" max="16384" width="9.1640625" style="18"/>
+    <col min="10" max="10" width="12.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="9.33203125" style="13" customWidth="1"/>
+    <col min="13" max="13" width="9.33203125" style="18" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="15.83203125" style="21" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="18" style="17" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="16.33203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="18.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="20.5" style="16" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="16.6640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="20.33203125" style="16" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="17.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="23.1640625" style="16" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="17.1640625" style="16" customWidth="1"/>
+    <col min="25" max="25" width="14.83203125" style="17" bestFit="1" customWidth="1"/>
+    <col min="26" max="16384" width="9.1640625" style="18"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" s="8" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
         <v>101</v>
       </c>
@@ -10044,49 +10177,55 @@
         <v>525</v>
       </c>
       <c r="J1" s="8" t="s">
+        <v>115</v>
+      </c>
+      <c r="K1" s="8" t="s">
         <v>112</v>
       </c>
-      <c r="K1" s="8" t="s">
+      <c r="L1" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="L1" s="8" t="s">
+      <c r="M1" s="8" t="s">
         <v>43</v>
       </c>
-      <c r="M1" s="9" t="s">
+      <c r="N1" s="9" t="s">
         <v>517</v>
       </c>
-      <c r="N1" s="8" t="s">
+      <c r="O1" s="8" t="s">
         <v>518</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>519</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
         <v>527</v>
       </c>
-      <c r="Q1" s="8" t="s">
+      <c r="R1" s="8" t="s">
         <v>528</v>
       </c>
-      <c r="R1" s="8" t="s">
+      <c r="S1" s="8" t="s">
         <v>529</v>
       </c>
-      <c r="S1" s="8" t="s">
+      <c r="T1" s="8" t="s">
         <v>530</v>
       </c>
-      <c r="T1" s="8" t="s">
+      <c r="U1" s="8" t="s">
         <v>531</v>
       </c>
-      <c r="U1" s="8" t="s">
+      <c r="V1" s="8" t="s">
+        <v>763</v>
+      </c>
+      <c r="W1" s="8" t="s">
         <v>581</v>
       </c>
-      <c r="V1" s="8" t="s">
+      <c r="X1" s="8" t="s">
         <v>603</v>
       </c>
-      <c r="W1" s="8" t="s">
+      <c r="Y1" s="8" t="s">
         <v>520</v>
       </c>
     </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A2" s="10">
         <v>46175</v>
       </c>
@@ -10123,18 +10262,18 @@
       <c r="L2" s="13">
         <v>0</v>
       </c>
-      <c r="M2" s="14">
+      <c r="M2" s="13">
+        <v>0</v>
+      </c>
+      <c r="N2" s="14">
         <v>300000</v>
       </c>
-      <c r="N2" s="15">
+      <c r="O2" s="15">
         <v>0.35237333333333332</v>
       </c>
-      <c r="O2" s="15">
+      <c r="P2" s="15">
         <v>0.64762666666666668</v>
       </c>
-      <c r="P2" s="16">
-        <v>0</v>
-      </c>
       <c r="Q2" s="16">
         <v>0</v>
       </c>
@@ -10153,11 +10292,17 @@
       <c r="V2" s="16">
         <v>0</v>
       </c>
-      <c r="W2" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W2" s="16">
+        <v>0</v>
+      </c>
+      <c r="X2" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y2" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A3" s="10">
         <v>46176</v>
       </c>
@@ -10194,18 +10339,18 @@
       <c r="L3" s="13">
         <v>0</v>
       </c>
-      <c r="M3" s="14">
+      <c r="M3" s="13">
+        <v>0</v>
+      </c>
+      <c r="N3" s="14">
         <v>300000</v>
       </c>
-      <c r="N3" s="15">
+      <c r="O3" s="15">
         <v>0.35237333333333332</v>
       </c>
-      <c r="O3" s="15">
+      <c r="P3" s="15">
         <v>0.64762666666666668</v>
       </c>
-      <c r="P3" s="16">
-        <v>0</v>
-      </c>
       <c r="Q3" s="16">
         <v>0</v>
       </c>
@@ -10224,11 +10369,17 @@
       <c r="V3" s="16">
         <v>0</v>
       </c>
-      <c r="W3" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W3" s="16">
+        <v>0</v>
+      </c>
+      <c r="X3" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y3" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A4" s="10">
         <v>46177</v>
       </c>
@@ -10265,18 +10416,18 @@
       <c r="L4" s="13">
         <v>0</v>
       </c>
-      <c r="M4" s="14">
+      <c r="M4" s="13">
+        <v>0</v>
+      </c>
+      <c r="N4" s="14">
         <v>300000</v>
       </c>
-      <c r="N4" s="15">
+      <c r="O4" s="15">
         <v>0.81459999999999999</v>
       </c>
-      <c r="O4" s="15">
+      <c r="P4" s="15">
         <v>0.18540000000000001</v>
       </c>
-      <c r="P4" s="16">
-        <v>0</v>
-      </c>
       <c r="Q4" s="16">
         <v>0</v>
       </c>
@@ -10295,11 +10446,17 @@
       <c r="V4" s="16">
         <v>0</v>
       </c>
-      <c r="W4" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W4" s="16">
+        <v>0</v>
+      </c>
+      <c r="X4" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y4" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A5" s="10">
         <v>46178</v>
       </c>
@@ -10336,21 +10493,21 @@
       <c r="L5" s="13">
         <v>0</v>
       </c>
-      <c r="M5" s="14">
+      <c r="M5" s="13">
+        <v>0</v>
+      </c>
+      <c r="N5" s="14">
         <v>907730</v>
       </c>
-      <c r="N5" s="15">
+      <c r="O5" s="15">
         <v>0.2692210238727375</v>
       </c>
-      <c r="O5" s="15">
-        <v>0</v>
-      </c>
-      <c r="P5" s="16">
+      <c r="P5" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q5" s="16">
         <v>0.7307789761272625</v>
       </c>
-      <c r="Q5" s="16">
-        <v>0</v>
-      </c>
       <c r="R5" s="16">
         <v>0</v>
       </c>
@@ -10366,11 +10523,17 @@
       <c r="V5" s="16">
         <v>0</v>
       </c>
-      <c r="W5" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W5" s="16">
+        <v>0</v>
+      </c>
+      <c r="X5" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A6" s="10">
         <v>46181</v>
       </c>
@@ -10407,24 +10570,24 @@
       <c r="L6" s="13">
         <v>0</v>
       </c>
-      <c r="M6" s="14">
+      <c r="M6" s="13">
+        <v>0</v>
+      </c>
+      <c r="N6" s="14">
         <v>3696918</v>
       </c>
-      <c r="N6" s="15">
+      <c r="O6" s="15">
         <v>3.7509081889292646E-2</v>
       </c>
-      <c r="O6" s="15">
-        <v>0</v>
-      </c>
-      <c r="P6" s="16">
+      <c r="P6" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="16">
         <v>0.17943324682884501</v>
       </c>
-      <c r="Q6" s="16">
+      <c r="R6" s="16">
         <v>0.78305767128186232</v>
       </c>
-      <c r="R6" s="16">
-        <v>0</v>
-      </c>
       <c r="S6" s="16">
         <v>0</v>
       </c>
@@ -10437,11 +10600,17 @@
       <c r="V6" s="16">
         <v>0</v>
       </c>
-      <c r="W6" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W6" s="16">
+        <v>0</v>
+      </c>
+      <c r="X6" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A7" s="10">
         <v>46182</v>
       </c>
@@ -10478,21 +10647,21 @@
       <c r="L7" s="13">
         <v>0</v>
       </c>
-      <c r="M7" s="14">
+      <c r="M7" s="13">
+        <v>0</v>
+      </c>
+      <c r="N7" s="14">
         <v>802018</v>
       </c>
-      <c r="N7" s="15">
+      <c r="O7" s="15">
         <v>0.17289886261904347</v>
       </c>
-      <c r="O7" s="15">
-        <v>0</v>
-      </c>
-      <c r="P7" s="16">
+      <c r="P7" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="16">
         <v>0.82710113738095659</v>
       </c>
-      <c r="Q7" s="16">
-        <v>0</v>
-      </c>
       <c r="R7" s="16">
         <v>0</v>
       </c>
@@ -10508,11 +10677,17 @@
       <c r="V7" s="16">
         <v>0</v>
       </c>
-      <c r="W7" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W7" s="16">
+        <v>0</v>
+      </c>
+      <c r="X7" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A8" s="10">
         <v>46183</v>
       </c>
@@ -10549,21 +10724,21 @@
       <c r="L8" s="13">
         <v>0</v>
       </c>
-      <c r="M8" s="14">
+      <c r="M8" s="13">
+        <v>0</v>
+      </c>
+      <c r="N8" s="14">
         <v>600137</v>
       </c>
-      <c r="N8" s="15">
+      <c r="O8" s="15">
         <v>0.23106057450215534</v>
       </c>
-      <c r="O8" s="15">
-        <v>0</v>
-      </c>
-      <c r="P8" s="16">
+      <c r="P8" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="16">
         <v>0.76893942549784466</v>
       </c>
-      <c r="Q8" s="16">
-        <v>0</v>
-      </c>
       <c r="R8" s="16">
         <v>0</v>
       </c>
@@ -10579,11 +10754,17 @@
       <c r="V8" s="16">
         <v>0</v>
       </c>
-      <c r="W8" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W8" s="16">
+        <v>0</v>
+      </c>
+      <c r="X8" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A9" s="10">
         <v>46184</v>
       </c>
@@ -10620,21 +10801,21 @@
       <c r="L9" s="13">
         <v>0</v>
       </c>
-      <c r="M9" s="14">
+      <c r="M9" s="13">
+        <v>0</v>
+      </c>
+      <c r="N9" s="14">
         <v>600137</v>
       </c>
-      <c r="N9" s="15">
+      <c r="O9" s="15">
         <v>0.23106057450215534</v>
       </c>
-      <c r="O9" s="15">
-        <v>0</v>
-      </c>
-      <c r="P9" s="16">
+      <c r="P9" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="16">
         <v>0.76893942549784466</v>
       </c>
-      <c r="Q9" s="16">
-        <v>0</v>
-      </c>
       <c r="R9" s="16">
         <v>0</v>
       </c>
@@ -10650,11 +10831,17 @@
       <c r="V9" s="16">
         <v>0</v>
       </c>
-      <c r="W9" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W9" s="16">
+        <v>0</v>
+      </c>
+      <c r="X9" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A10" s="10">
         <v>46185</v>
       </c>
@@ -10691,21 +10878,21 @@
       <c r="L10" s="13">
         <v>0</v>
       </c>
-      <c r="M10" s="14">
+      <c r="M10" s="13">
+        <v>0</v>
+      </c>
+      <c r="N10" s="14">
         <v>461469</v>
       </c>
-      <c r="N10" s="15">
-        <v>0</v>
-      </c>
       <c r="O10" s="15">
         <v>0</v>
       </c>
-      <c r="P10" s="16">
+      <c r="P10" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="16">
         <v>1</v>
       </c>
-      <c r="Q10" s="16">
-        <v>0</v>
-      </c>
       <c r="R10" s="16">
         <v>0</v>
       </c>
@@ -10721,11 +10908,17 @@
       <c r="V10" s="16">
         <v>0</v>
       </c>
-      <c r="W10" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W10" s="16">
+        <v>0</v>
+      </c>
+      <c r="X10" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A11" s="10">
         <v>46188</v>
       </c>
@@ -10762,21 +10955,21 @@
       <c r="L11" s="13">
         <v>0</v>
       </c>
-      <c r="M11" s="14">
+      <c r="M11" s="13">
+        <v>0</v>
+      </c>
+      <c r="N11" s="14">
         <v>461469</v>
       </c>
-      <c r="N11" s="15">
-        <v>0</v>
-      </c>
       <c r="O11" s="15">
         <v>0</v>
       </c>
-      <c r="P11" s="16">
+      <c r="P11" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="16">
         <v>1</v>
       </c>
-      <c r="Q11" s="16">
-        <v>0</v>
-      </c>
       <c r="R11" s="16">
         <v>0</v>
       </c>
@@ -10792,11 +10985,17 @@
       <c r="V11" s="16">
         <v>0</v>
       </c>
-      <c r="W11" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W11" s="16">
+        <v>0</v>
+      </c>
+      <c r="X11" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A12" s="10">
         <v>46189</v>
       </c>
@@ -10833,21 +11032,21 @@
       <c r="L12" s="13">
         <v>0</v>
       </c>
-      <c r="M12" s="14">
+      <c r="M12" s="13">
+        <v>0</v>
+      </c>
+      <c r="N12" s="14">
         <v>461469</v>
       </c>
-      <c r="N12" s="15">
-        <v>0</v>
-      </c>
       <c r="O12" s="15">
         <v>0</v>
       </c>
-      <c r="P12" s="16">
+      <c r="P12" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="16">
         <v>1</v>
       </c>
-      <c r="Q12" s="16">
-        <v>0</v>
-      </c>
       <c r="R12" s="16">
         <v>0</v>
       </c>
@@ -10863,11 +11062,17 @@
       <c r="V12" s="16">
         <v>0</v>
       </c>
-      <c r="W12" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W12" s="16">
+        <v>0</v>
+      </c>
+      <c r="X12" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A13" s="10">
         <v>46190</v>
       </c>
@@ -10904,27 +11109,27 @@
       <c r="L13" s="13">
         <v>0</v>
       </c>
-      <c r="M13" s="14">
+      <c r="M13" s="13">
+        <v>0</v>
+      </c>
+      <c r="N13" s="14">
         <v>592709</v>
       </c>
-      <c r="N13" s="15">
-        <v>0</v>
-      </c>
       <c r="O13" s="15">
         <v>0</v>
       </c>
-      <c r="P13" s="16">
+      <c r="P13" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q13" s="16">
         <v>0.77857599597779015</v>
       </c>
-      <c r="Q13" s="16">
-        <v>0</v>
-      </c>
       <c r="R13" s="16">
+        <v>0</v>
+      </c>
+      <c r="S13" s="16">
         <v>0.22142400402220988</v>
       </c>
-      <c r="S13" s="16">
-        <v>0</v>
-      </c>
       <c r="T13" s="16">
         <v>0</v>
       </c>
@@ -10934,11 +11139,17 @@
       <c r="V13" s="16">
         <v>0</v>
       </c>
-      <c r="W13" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W13" s="16">
+        <v>0</v>
+      </c>
+      <c r="X13" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A14" s="10">
         <v>46191</v>
       </c>
@@ -10975,27 +11186,27 @@
       <c r="L14" s="13">
         <v>0</v>
       </c>
-      <c r="M14" s="14">
+      <c r="M14" s="13">
+        <v>0</v>
+      </c>
+      <c r="N14" s="14">
         <v>592709</v>
       </c>
-      <c r="N14" s="15">
-        <v>0</v>
-      </c>
       <c r="O14" s="15">
         <v>0</v>
       </c>
-      <c r="P14" s="16">
+      <c r="P14" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="16">
         <v>0.77857599597779015</v>
       </c>
-      <c r="Q14" s="16">
-        <v>0</v>
-      </c>
       <c r="R14" s="16">
+        <v>0</v>
+      </c>
+      <c r="S14" s="16">
         <v>0.22142400402220988</v>
       </c>
-      <c r="S14" s="16">
-        <v>0</v>
-      </c>
       <c r="T14" s="16">
         <v>0</v>
       </c>
@@ -11005,11 +11216,17 @@
       <c r="V14" s="16">
         <v>0</v>
       </c>
-      <c r="W14" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W14" s="16">
+        <v>0</v>
+      </c>
+      <c r="X14" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A15" s="10">
         <v>46192</v>
       </c>
@@ -11046,27 +11263,27 @@
       <c r="L15" s="13">
         <v>0</v>
       </c>
-      <c r="M15" s="14">
+      <c r="M15" s="13">
+        <v>0</v>
+      </c>
+      <c r="N15" s="14">
         <v>592709</v>
       </c>
-      <c r="N15" s="15">
-        <v>0</v>
-      </c>
       <c r="O15" s="15">
         <v>0</v>
       </c>
-      <c r="P15" s="16">
+      <c r="P15" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="16">
         <v>0.77857599597779015</v>
       </c>
-      <c r="Q15" s="16">
-        <v>0</v>
-      </c>
       <c r="R15" s="16">
+        <v>0</v>
+      </c>
+      <c r="S15" s="16">
         <v>0.22142400402220988</v>
       </c>
-      <c r="S15" s="16">
-        <v>0</v>
-      </c>
       <c r="T15" s="16">
         <v>0</v>
       </c>
@@ -11076,11 +11293,17 @@
       <c r="V15" s="16">
         <v>0</v>
       </c>
-      <c r="W15" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W15" s="16">
+        <v>0</v>
+      </c>
+      <c r="X15" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A16" s="10">
         <v>46195</v>
       </c>
@@ -11117,24 +11340,24 @@
       <c r="L16" s="13">
         <v>0</v>
       </c>
-      <c r="M16" s="14">
+      <c r="M16" s="13">
+        <v>0</v>
+      </c>
+      <c r="N16" s="14">
         <v>3586250</v>
       </c>
-      <c r="N16" s="15">
-        <v>0</v>
-      </c>
       <c r="O16" s="15">
         <v>0</v>
       </c>
-      <c r="P16" s="16">
+      <c r="P16" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="16">
         <v>0.12867730916695713</v>
       </c>
-      <c r="Q16" s="16">
+      <c r="R16" s="16">
         <v>0.87132269083304292</v>
       </c>
-      <c r="R16" s="16">
-        <v>0</v>
-      </c>
       <c r="S16" s="16">
         <v>0</v>
       </c>
@@ -11147,11 +11370,17 @@
       <c r="V16" s="16">
         <v>0</v>
       </c>
-      <c r="W16" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W16" s="16">
+        <v>0</v>
+      </c>
+      <c r="X16" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A17" s="10">
         <v>46196</v>
       </c>
@@ -11188,24 +11417,24 @@
       <c r="L17" s="13">
         <v>0</v>
       </c>
-      <c r="M17" s="14">
+      <c r="M17" s="13">
+        <v>0</v>
+      </c>
+      <c r="N17" s="14">
         <v>3586250</v>
       </c>
-      <c r="N17" s="15">
-        <v>0</v>
-      </c>
       <c r="O17" s="15">
         <v>0</v>
       </c>
-      <c r="P17" s="16">
+      <c r="P17" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="16">
         <v>0.12867730916695713</v>
       </c>
-      <c r="Q17" s="16">
+      <c r="R17" s="16">
         <v>0.87132269083304292</v>
       </c>
-      <c r="R17" s="16">
-        <v>0</v>
-      </c>
       <c r="S17" s="16">
         <v>0</v>
       </c>
@@ -11218,11 +11447,17 @@
       <c r="V17" s="16">
         <v>0</v>
       </c>
-      <c r="W17" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W17" s="16">
+        <v>0</v>
+      </c>
+      <c r="X17" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A18" s="10">
         <v>46197</v>
       </c>
@@ -11257,26 +11492,26 @@
         <v>0</v>
       </c>
       <c r="L18" s="13">
+        <v>0</v>
+      </c>
+      <c r="M18" s="13">
         <v>193096</v>
       </c>
-      <c r="M18" s="14">
+      <c r="N18" s="14">
         <v>3779346</v>
       </c>
-      <c r="N18" s="15">
-        <v>0</v>
-      </c>
       <c r="O18" s="15">
         <v>0</v>
       </c>
-      <c r="P18" s="16">
+      <c r="P18" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="16">
         <v>0.12210287176670249</v>
       </c>
-      <c r="Q18" s="16">
+      <c r="R18" s="16">
         <v>0.8268046905469888</v>
       </c>
-      <c r="R18" s="16">
-        <v>0</v>
-      </c>
       <c r="S18" s="16">
         <v>0</v>
       </c>
@@ -11289,11 +11524,17 @@
       <c r="V18" s="16">
         <v>0</v>
       </c>
-      <c r="W18" s="15">
+      <c r="W18" s="16">
+        <v>0</v>
+      </c>
+      <c r="X18" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="15">
         <v>5.1092437686308688E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A19" s="10">
         <v>46198</v>
       </c>
@@ -11328,26 +11569,26 @@
         <v>0</v>
       </c>
       <c r="L19" s="13">
+        <v>0</v>
+      </c>
+      <c r="M19" s="13">
         <v>193096</v>
       </c>
-      <c r="M19" s="14">
+      <c r="N19" s="14">
         <v>3981471</v>
       </c>
-      <c r="N19" s="15">
-        <v>0</v>
-      </c>
       <c r="O19" s="15">
         <v>0</v>
       </c>
-      <c r="P19" s="16">
+      <c r="P19" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="16">
         <v>0.16667055970017111</v>
       </c>
-      <c r="Q19" s="16">
+      <c r="R19" s="16">
         <v>0.78483078239173409</v>
       </c>
-      <c r="R19" s="16">
-        <v>0</v>
-      </c>
       <c r="S19" s="16">
         <v>0</v>
       </c>
@@ -11360,11 +11601,17 @@
       <c r="V19" s="16">
         <v>0</v>
       </c>
-      <c r="W19" s="15">
+      <c r="W19" s="16">
+        <v>0</v>
+      </c>
+      <c r="X19" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="15">
         <v>4.8498657908094774E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A20" s="10">
         <v>46199</v>
       </c>
@@ -11399,26 +11646,26 @@
         <v>0</v>
       </c>
       <c r="L20" s="13">
+        <v>0</v>
+      </c>
+      <c r="M20" s="13">
         <v>193096</v>
       </c>
-      <c r="M20" s="14">
+      <c r="N20" s="14">
         <v>3981471</v>
       </c>
-      <c r="N20" s="15">
-        <v>0</v>
-      </c>
       <c r="O20" s="15">
         <v>0</v>
       </c>
-      <c r="P20" s="16">
+      <c r="P20" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="16">
         <v>0.16667055970017111</v>
       </c>
-      <c r="Q20" s="16">
+      <c r="R20" s="16">
         <v>0.78483078239173409</v>
       </c>
-      <c r="R20" s="16">
-        <v>0</v>
-      </c>
       <c r="S20" s="16">
         <v>0</v>
       </c>
@@ -11431,11 +11678,17 @@
       <c r="V20" s="16">
         <v>0</v>
       </c>
-      <c r="W20" s="15">
+      <c r="W20" s="16">
+        <v>0</v>
+      </c>
+      <c r="X20" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="15">
         <v>4.8498657908094774E-2</v>
       </c>
     </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A21" s="10">
         <v>46202</v>
       </c>
@@ -11470,26 +11723,26 @@
         <v>0</v>
       </c>
       <c r="L21" s="13">
+        <v>0</v>
+      </c>
+      <c r="M21" s="13">
         <v>416939</v>
       </c>
-      <c r="M21" s="14">
+      <c r="N21" s="14">
         <v>4260349</v>
       </c>
-      <c r="N21" s="15">
+      <c r="O21" s="15">
         <v>1.2917955782495754E-2</v>
       </c>
-      <c r="O21" s="15">
-        <v>0</v>
-      </c>
-      <c r="P21" s="16">
+      <c r="P21" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="16">
         <v>0.1557604787776776</v>
       </c>
-      <c r="Q21" s="16">
+      <c r="R21" s="16">
         <v>0.73345657832257405</v>
       </c>
-      <c r="R21" s="16">
-        <v>0</v>
-      </c>
       <c r="S21" s="16">
         <v>0</v>
       </c>
@@ -11502,11 +11755,17 @@
       <c r="V21" s="16">
         <v>0</v>
       </c>
-      <c r="W21" s="15">
+      <c r="W21" s="16">
+        <v>0</v>
+      </c>
+      <c r="X21" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="15">
         <v>9.7864987117252597E-2</v>
       </c>
     </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A22" s="10">
         <v>46203</v>
       </c>
@@ -11541,43 +11800,49 @@
         <v>0</v>
       </c>
       <c r="L22" s="13">
+        <v>0</v>
+      </c>
+      <c r="M22" s="13">
         <v>223843</v>
       </c>
-      <c r="M22" s="14">
+      <c r="N22" s="14">
         <v>3524723</v>
       </c>
-      <c r="N22" s="15">
+      <c r="O22" s="15">
         <v>1.5613992929373457E-2</v>
       </c>
-      <c r="O22" s="15">
-        <v>0</v>
-      </c>
-      <c r="P22" s="16">
+      <c r="P22" s="15">
         <v>0</v>
       </c>
       <c r="Q22" s="16">
+        <v>0</v>
+      </c>
+      <c r="R22" s="16">
         <v>0.88653236013156211</v>
       </c>
-      <c r="R22" s="16">
-        <v>0</v>
-      </c>
       <c r="S22" s="16">
+        <v>0</v>
+      </c>
+      <c r="T22" s="16">
         <v>3.4347096211532084E-2</v>
       </c>
-      <c r="T22" s="16">
-        <v>0</v>
-      </c>
       <c r="U22" s="16">
         <v>0</v>
       </c>
       <c r="V22" s="16">
         <v>0</v>
       </c>
-      <c r="W22" s="15">
+      <c r="W22" s="16">
+        <v>0</v>
+      </c>
+      <c r="X22" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="15">
         <v>6.3506550727532349E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A23" s="10">
         <v>46204</v>
       </c>
@@ -11612,43 +11877,49 @@
         <v>0</v>
       </c>
       <c r="L23" s="13">
+        <v>0</v>
+      </c>
+      <c r="M23" s="13">
         <v>223843</v>
       </c>
-      <c r="M23" s="14">
+      <c r="N23" s="14">
         <v>3469688</v>
       </c>
-      <c r="N23" s="15">
-        <v>0</v>
-      </c>
       <c r="O23" s="15">
         <v>0</v>
       </c>
-      <c r="P23" s="16">
+      <c r="P23" s="15">
         <v>0</v>
       </c>
       <c r="Q23" s="16">
+        <v>0</v>
+      </c>
+      <c r="R23" s="16">
         <v>0.90059423210386635</v>
       </c>
-      <c r="R23" s="16">
-        <v>0</v>
-      </c>
       <c r="S23" s="16">
+        <v>0</v>
+      </c>
+      <c r="T23" s="16">
         <v>3.4891898061151318E-2</v>
       </c>
-      <c r="T23" s="16">
-        <v>0</v>
-      </c>
       <c r="U23" s="16">
         <v>0</v>
       </c>
       <c r="V23" s="16">
         <v>0</v>
       </c>
-      <c r="W23" s="15">
+      <c r="W23" s="16">
+        <v>0</v>
+      </c>
+      <c r="X23" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y23" s="15">
         <v>6.4513869834982279E-2</v>
       </c>
     </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A24" s="10">
         <v>46205</v>
       </c>
@@ -11683,47 +11954,53 @@
         <v>0</v>
       </c>
       <c r="L24" s="13">
+        <v>0</v>
+      </c>
+      <c r="M24" s="13">
         <v>223843</v>
       </c>
-      <c r="M24" s="14">
-        <f>SUM(C24:L24)</f>
+      <c r="N24" s="14">
+        <f>SUM(C24:M24)</f>
         <v>460932</v>
       </c>
-      <c r="N24" s="15">
-        <v>0</v>
-      </c>
       <c r="O24" s="15">
         <v>0</v>
       </c>
-      <c r="P24" s="16">
+      <c r="P24" s="15">
         <v>0</v>
       </c>
       <c r="Q24" s="16">
         <v>0</v>
       </c>
       <c r="R24" s="16">
-        <f>G24/M24</f>
+        <v>0</v>
+      </c>
+      <c r="S24" s="16">
+        <f>G24/N24</f>
         <v>0.25171825779073703</v>
       </c>
-      <c r="S24" s="16">
-        <f>H24/M24</f>
+      <c r="T24" s="16">
+        <f>H24/N24</f>
         <v>0.2626504560325601</v>
       </c>
-      <c r="T24" s="16">
-        <v>0</v>
-      </c>
       <c r="U24" s="16">
         <v>0</v>
       </c>
       <c r="V24" s="16">
         <v>0</v>
       </c>
-      <c r="W24" s="15">
-        <f>L24/M24</f>
+      <c r="W24" s="16">
+        <v>0</v>
+      </c>
+      <c r="X24" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y24" s="15">
+        <f>M24/N24</f>
         <v>0.48563128617670287</v>
       </c>
     </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A25" s="10">
         <v>46206</v>
       </c>
@@ -11758,20 +12035,20 @@
         <v>0</v>
       </c>
       <c r="L25" s="13">
+        <v>0</v>
+      </c>
+      <c r="M25" s="13">
         <v>223843</v>
       </c>
-      <c r="M25" s="14">
+      <c r="N25" s="14">
         <v>374479.39</v>
       </c>
-      <c r="N25" s="15">
-        <v>0</v>
-      </c>
       <c r="O25" s="15">
+        <v>0</v>
+      </c>
+      <c r="P25" s="15">
         <v>7.8969339273918415E-2</v>
       </c>
-      <c r="P25" s="16">
-        <v>0</v>
-      </c>
       <c r="Q25" s="16">
         <v>0</v>
       </c>
@@ -11779,22 +12056,28 @@
         <v>0</v>
       </c>
       <c r="S25" s="16">
+        <v>0</v>
+      </c>
+      <c r="T25" s="16">
         <v>0.32328614933921995</v>
       </c>
-      <c r="T25" s="16">
-        <v>0</v>
-      </c>
       <c r="U25" s="16">
         <v>0</v>
       </c>
       <c r="V25" s="16">
         <v>0</v>
       </c>
-      <c r="W25" s="15">
+      <c r="W25" s="16">
+        <v>0</v>
+      </c>
+      <c r="X25" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y25" s="15">
         <v>0.59774451138686158</v>
       </c>
     </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A26" s="10">
         <v>46209</v>
       </c>
@@ -11829,20 +12112,20 @@
         <v>0</v>
       </c>
       <c r="L26" s="13">
+        <v>0</v>
+      </c>
+      <c r="M26" s="13">
         <v>223843</v>
       </c>
-      <c r="M26" s="14">
+      <c r="N26" s="14">
         <v>372801.92</v>
       </c>
-      <c r="N26" s="15">
-        <v>0</v>
-      </c>
       <c r="O26" s="15">
+        <v>0</v>
+      </c>
+      <c r="P26" s="15">
         <v>7.4825043819516768E-2</v>
       </c>
-      <c r="P26" s="16">
-        <v>0</v>
-      </c>
       <c r="Q26" s="16">
         <v>0</v>
       </c>
@@ -11850,22 +12133,28 @@
         <v>0</v>
       </c>
       <c r="S26" s="16">
+        <v>0</v>
+      </c>
+      <c r="T26" s="16">
         <v>0.32474081678549299</v>
       </c>
-      <c r="T26" s="16">
-        <v>0</v>
-      </c>
       <c r="U26" s="16">
         <v>0</v>
       </c>
       <c r="V26" s="16">
         <v>0</v>
       </c>
-      <c r="W26" s="15">
+      <c r="W26" s="16">
+        <v>0</v>
+      </c>
+      <c r="X26" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y26" s="15">
         <v>0.60043413939499024</v>
       </c>
     </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A27" s="10">
         <v>46210</v>
       </c>
@@ -11900,20 +12189,20 @@
         <v>0</v>
       </c>
       <c r="L27" s="13">
+        <v>0</v>
+      </c>
+      <c r="M27" s="13">
         <v>223843</v>
       </c>
-      <c r="M27" s="14">
+      <c r="N27" s="14">
         <v>375246.11</v>
       </c>
-      <c r="N27" s="15">
-        <v>0</v>
-      </c>
       <c r="O27" s="15">
+        <v>0</v>
+      </c>
+      <c r="P27" s="15">
         <v>8.0851231209298838E-2</v>
       </c>
-      <c r="P27" s="16">
-        <v>0</v>
-      </c>
       <c r="Q27" s="16">
         <v>0</v>
       </c>
@@ -11921,22 +12210,28 @@
         <v>0</v>
       </c>
       <c r="S27" s="16">
+        <v>0</v>
+      </c>
+      <c r="T27" s="16">
         <v>0.32262559630531545</v>
       </c>
-      <c r="T27" s="16">
-        <v>0</v>
-      </c>
       <c r="U27" s="16">
         <v>0</v>
       </c>
       <c r="V27" s="16">
         <v>0</v>
       </c>
-      <c r="W27" s="15">
+      <c r="W27" s="16">
+        <v>0</v>
+      </c>
+      <c r="X27" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y27" s="15">
         <v>0.59652317248538567</v>
       </c>
     </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A28" s="10">
         <v>46211</v>
       </c>
@@ -11971,18 +12266,18 @@
         <v>0</v>
       </c>
       <c r="L28" s="13">
+        <v>0</v>
+      </c>
+      <c r="M28" s="13">
         <v>223843</v>
       </c>
-      <c r="M28" s="14">
+      <c r="N28" s="14">
         <v>435718</v>
       </c>
-      <c r="N28" s="15">
+      <c r="O28" s="15">
         <v>0.20841691185583336</v>
       </c>
-      <c r="O28" s="15">
-        <v>0</v>
-      </c>
-      <c r="P28" s="16">
+      <c r="P28" s="15">
         <v>0</v>
       </c>
       <c r="Q28" s="16">
@@ -11992,22 +12287,28 @@
         <v>0</v>
       </c>
       <c r="S28" s="16">
+        <v>0</v>
+      </c>
+      <c r="T28" s="16">
         <v>0.27784943472613022</v>
       </c>
-      <c r="T28" s="16">
-        <v>0</v>
-      </c>
       <c r="U28" s="16">
         <v>0</v>
       </c>
       <c r="V28" s="16">
         <v>0</v>
       </c>
-      <c r="W28" s="15">
+      <c r="W28" s="16">
+        <v>0</v>
+      </c>
+      <c r="X28" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="15">
         <v>0.51373365341803645</v>
       </c>
     </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A29" s="10">
         <v>46212</v>
       </c>
@@ -12042,18 +12343,18 @@
         <v>0</v>
       </c>
       <c r="L29" s="13">
+        <v>0</v>
+      </c>
+      <c r="M29" s="13">
         <v>223843</v>
       </c>
-      <c r="M29" s="14">
+      <c r="N29" s="14">
         <v>435718</v>
       </c>
-      <c r="N29" s="15">
+      <c r="O29" s="15">
         <v>0.20841691185583336</v>
       </c>
-      <c r="O29" s="15">
-        <v>0</v>
-      </c>
-      <c r="P29" s="16">
+      <c r="P29" s="15">
         <v>0</v>
       </c>
       <c r="Q29" s="16">
@@ -12063,22 +12364,28 @@
         <v>0</v>
       </c>
       <c r="S29" s="16">
+        <v>0</v>
+      </c>
+      <c r="T29" s="16">
         <v>0.27784943472613022</v>
       </c>
-      <c r="T29" s="16">
-        <v>0</v>
-      </c>
       <c r="U29" s="16">
         <v>0</v>
       </c>
       <c r="V29" s="16">
         <v>0</v>
       </c>
-      <c r="W29" s="15">
+      <c r="W29" s="16">
+        <v>0</v>
+      </c>
+      <c r="X29" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="15">
         <v>0.51373365341803645</v>
       </c>
     </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A30" s="10">
         <v>46213</v>
       </c>
@@ -12113,18 +12420,18 @@
         <v>0</v>
       </c>
       <c r="L30" s="13">
+        <v>0</v>
+      </c>
+      <c r="M30" s="13">
         <v>223843</v>
       </c>
-      <c r="M30" s="14">
+      <c r="N30" s="14">
         <v>435718</v>
       </c>
-      <c r="N30" s="15">
+      <c r="O30" s="15">
         <v>0.20841691185583336</v>
       </c>
-      <c r="O30" s="15">
-        <v>0</v>
-      </c>
-      <c r="P30" s="16">
+      <c r="P30" s="15">
         <v>0</v>
       </c>
       <c r="Q30" s="16">
@@ -12134,22 +12441,28 @@
         <v>0</v>
       </c>
       <c r="S30" s="16">
+        <v>0</v>
+      </c>
+      <c r="T30" s="16">
         <v>0.27784943472613022</v>
       </c>
-      <c r="T30" s="16">
-        <v>0</v>
-      </c>
       <c r="U30" s="16">
         <v>0</v>
       </c>
       <c r="V30" s="16">
         <v>0</v>
       </c>
-      <c r="W30" s="15">
+      <c r="W30" s="16">
+        <v>0</v>
+      </c>
+      <c r="X30" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="15">
         <v>0.51373365341803645</v>
       </c>
     </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A31" s="10">
         <v>46216</v>
       </c>
@@ -12184,18 +12497,18 @@
         <v>0</v>
       </c>
       <c r="L31" s="13">
+        <v>0</v>
+      </c>
+      <c r="M31" s="13">
         <v>223843</v>
       </c>
-      <c r="M31" s="14">
+      <c r="N31" s="14">
         <v>435718</v>
       </c>
-      <c r="N31" s="15">
+      <c r="O31" s="15">
         <v>0.20841691185583336</v>
       </c>
-      <c r="O31" s="15">
-        <v>0</v>
-      </c>
-      <c r="P31" s="16">
+      <c r="P31" s="15">
         <v>0</v>
       </c>
       <c r="Q31" s="16">
@@ -12205,22 +12518,28 @@
         <v>0</v>
       </c>
       <c r="S31" s="16">
+        <v>0</v>
+      </c>
+      <c r="T31" s="16">
         <v>0.27784943472613022</v>
       </c>
-      <c r="T31" s="16">
-        <v>0</v>
-      </c>
       <c r="U31" s="16">
         <v>0</v>
       </c>
       <c r="V31" s="16">
         <v>0</v>
       </c>
-      <c r="W31" s="15">
+      <c r="W31" s="16">
+        <v>0</v>
+      </c>
+      <c r="X31" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="15">
         <v>0.51373365341803645</v>
       </c>
     </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A32" s="10">
         <v>46217</v>
       </c>
@@ -12255,20 +12574,20 @@
         <v>0</v>
       </c>
       <c r="L32" s="13">
+        <v>0</v>
+      </c>
+      <c r="M32" s="13">
         <v>223843</v>
       </c>
-      <c r="M32" s="14">
+      <c r="N32" s="14">
         <v>378852.03</v>
       </c>
-      <c r="N32" s="15">
-        <v>0</v>
-      </c>
       <c r="O32" s="15">
+        <v>0</v>
+      </c>
+      <c r="P32" s="15">
         <v>8.9599704665697652E-2</v>
       </c>
-      <c r="P32" s="16">
-        <v>0</v>
-      </c>
       <c r="Q32" s="16">
         <v>0</v>
       </c>
@@ -12276,22 +12595,28 @@
         <v>0</v>
       </c>
       <c r="S32" s="16">
+        <v>0</v>
+      </c>
+      <c r="T32" s="16">
         <v>0.31955484044786558</v>
       </c>
-      <c r="T32" s="16">
-        <v>0</v>
-      </c>
       <c r="U32" s="16">
         <v>0</v>
       </c>
       <c r="V32" s="16">
         <v>0</v>
       </c>
-      <c r="W32" s="15">
+      <c r="W32" s="16">
+        <v>0</v>
+      </c>
+      <c r="X32" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y32" s="15">
         <v>0.5908454548864368</v>
       </c>
     </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A33" s="10">
         <v>46218</v>
       </c>
@@ -12326,20 +12651,20 @@
         <v>0</v>
       </c>
       <c r="L33" s="13">
+        <v>0</v>
+      </c>
+      <c r="M33" s="13">
         <v>223843</v>
       </c>
-      <c r="M33" s="14">
+      <c r="N33" s="14">
         <v>374437.1</v>
       </c>
-      <c r="N33" s="15">
-        <v>0</v>
-      </c>
       <c r="O33" s="15">
+        <v>0</v>
+      </c>
+      <c r="P33" s="15">
         <v>7.8865315429480623E-2</v>
       </c>
-      <c r="P33" s="16">
-        <v>0</v>
-      </c>
       <c r="Q33" s="16">
         <v>0</v>
       </c>
@@ -12347,22 +12672,28 @@
         <v>0</v>
       </c>
       <c r="S33" s="16">
+        <v>0</v>
+      </c>
+      <c r="T33" s="16">
         <v>0.32332266220414591</v>
       </c>
-      <c r="T33" s="16">
-        <v>0</v>
-      </c>
       <c r="U33" s="16">
         <v>0</v>
       </c>
       <c r="V33" s="16">
         <v>0</v>
       </c>
-      <c r="W33" s="15">
+      <c r="W33" s="16">
+        <v>0</v>
+      </c>
+      <c r="X33" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y33" s="15">
         <v>0.59781202236637343</v>
       </c>
     </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A34" s="10">
         <v>46219</v>
       </c>
@@ -12397,20 +12728,20 @@
         <v>0</v>
       </c>
       <c r="L34" s="13">
+        <v>0</v>
+      </c>
+      <c r="M34" s="13">
         <v>223843</v>
       </c>
-      <c r="M34" s="14">
+      <c r="N34" s="14">
         <v>372248.26</v>
       </c>
-      <c r="N34" s="15">
-        <v>0</v>
-      </c>
       <c r="O34" s="15">
+        <v>0</v>
+      </c>
+      <c r="P34" s="15">
         <v>7.3448993421755704E-2</v>
       </c>
-      <c r="P34" s="16">
-        <v>0</v>
-      </c>
       <c r="Q34" s="16">
         <v>0</v>
       </c>
@@ -12418,22 +12749,28 @@
         <v>0</v>
       </c>
       <c r="S34" s="16">
+        <v>0</v>
+      </c>
+      <c r="T34" s="16">
         <v>0.32522381703006481</v>
       </c>
-      <c r="T34" s="16">
-        <v>0</v>
-      </c>
       <c r="U34" s="16">
         <v>0</v>
       </c>
       <c r="V34" s="16">
         <v>0</v>
       </c>
-      <c r="W34" s="15">
+      <c r="W34" s="16">
+        <v>0</v>
+      </c>
+      <c r="X34" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y34" s="15">
         <v>0.60132718954817943</v>
       </c>
     </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A35" s="10">
         <v>46220</v>
       </c>
@@ -12468,20 +12805,20 @@
         <v>0</v>
       </c>
       <c r="L35" s="13">
+        <v>0</v>
+      </c>
+      <c r="M35" s="13">
         <v>223843</v>
       </c>
-      <c r="M35" s="14">
+      <c r="N35" s="14">
         <v>376025.4</v>
       </c>
-      <c r="N35" s="15">
-        <v>0</v>
-      </c>
       <c r="O35" s="15">
+        <v>0</v>
+      </c>
+      <c r="P35" s="15">
         <v>8.2756111688199838E-2</v>
       </c>
-      <c r="P35" s="16">
-        <v>0</v>
-      </c>
       <c r="Q35" s="16">
         <v>0</v>
       </c>
@@ -12489,22 +12826,28 @@
         <v>0</v>
       </c>
       <c r="S35" s="16">
+        <v>0</v>
+      </c>
+      <c r="T35" s="16">
         <v>0.32195697418312696</v>
       </c>
-      <c r="T35" s="16">
-        <v>0</v>
-      </c>
       <c r="U35" s="16">
         <v>0</v>
       </c>
       <c r="V35" s="16">
         <v>0</v>
       </c>
-      <c r="W35" s="15">
+      <c r="W35" s="16">
+        <v>0</v>
+      </c>
+      <c r="X35" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y35" s="15">
         <v>0.59528691412867318</v>
       </c>
     </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A36" s="10">
         <v>46223</v>
       </c>
@@ -12539,20 +12882,20 @@
         <v>0</v>
       </c>
       <c r="L36" s="13">
+        <v>0</v>
+      </c>
+      <c r="M36" s="13">
         <v>223843</v>
       </c>
-      <c r="M36" s="14">
+      <c r="N36" s="14">
         <v>375009.72</v>
       </c>
-      <c r="N36" s="15">
-        <v>0</v>
-      </c>
       <c r="O36" s="15">
+        <v>0</v>
+      </c>
+      <c r="P36" s="15">
         <v>8.0271839353923874E-2</v>
       </c>
-      <c r="P36" s="16">
-        <v>0</v>
-      </c>
       <c r="Q36" s="16">
         <v>0</v>
       </c>
@@ -12560,22 +12903,28 @@
         <v>0</v>
       </c>
       <c r="S36" s="16">
+        <v>0</v>
+      </c>
+      <c r="T36" s="16">
         <v>0.32282896560654484</v>
       </c>
-      <c r="T36" s="16">
-        <v>0</v>
-      </c>
       <c r="U36" s="16">
         <v>0</v>
       </c>
       <c r="V36" s="16">
         <v>0</v>
       </c>
-      <c r="W36" s="15">
+      <c r="W36" s="16">
+        <v>0</v>
+      </c>
+      <c r="X36" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y36" s="15">
         <v>0.59689919503953126</v>
       </c>
     </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A37" s="10">
         <v>46224</v>
       </c>
@@ -12610,20 +12959,20 @@
         <v>0</v>
       </c>
       <c r="L37" s="13">
+        <v>0</v>
+      </c>
+      <c r="M37" s="13">
         <v>223843</v>
       </c>
-      <c r="M37" s="14">
+      <c r="N37" s="14">
         <v>375731.28</v>
       </c>
-      <c r="N37" s="15">
-        <v>0</v>
-      </c>
       <c r="O37" s="15">
+        <v>0</v>
+      </c>
+      <c r="P37" s="15">
         <v>8.2038099143622076E-2</v>
       </c>
-      <c r="P37" s="16">
-        <v>0</v>
-      </c>
       <c r="Q37" s="16">
         <v>0</v>
       </c>
@@ -12631,22 +12980,28 @@
         <v>0</v>
       </c>
       <c r="S37" s="16">
+        <v>0</v>
+      </c>
+      <c r="T37" s="16">
         <v>0.32220900000660047</v>
       </c>
-      <c r="T37" s="16">
-        <v>0</v>
-      </c>
       <c r="U37" s="16">
         <v>0</v>
       </c>
       <c r="V37" s="16">
         <v>0</v>
       </c>
-      <c r="W37" s="15">
+      <c r="W37" s="16">
+        <v>0</v>
+      </c>
+      <c r="X37" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y37" s="15">
         <v>0.5957529008497775</v>
       </c>
     </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A38" s="10">
         <v>46225</v>
       </c>
@@ -12681,20 +13036,20 @@
         <v>0</v>
       </c>
       <c r="L38" s="13">
+        <v>0</v>
+      </c>
+      <c r="M38" s="13">
         <v>223843</v>
       </c>
-      <c r="M38" s="14">
+      <c r="N38" s="14">
         <v>378174.99</v>
       </c>
-      <c r="N38" s="15">
-        <v>0</v>
-      </c>
       <c r="O38" s="15">
+        <v>0</v>
+      </c>
+      <c r="P38" s="15">
         <v>8.79698311091381E-2</v>
       </c>
-      <c r="P38" s="16">
-        <v>0</v>
-      </c>
       <c r="Q38" s="16">
         <v>0</v>
       </c>
@@ -12702,22 +13057,28 @@
         <v>0</v>
       </c>
       <c r="S38" s="16">
+        <v>0</v>
+      </c>
+      <c r="T38" s="16">
         <v>0.32012693383028845</v>
       </c>
-      <c r="T38" s="16">
-        <v>0</v>
-      </c>
       <c r="U38" s="16">
         <v>0</v>
       </c>
       <c r="V38" s="16">
         <v>0</v>
       </c>
-      <c r="W38" s="15">
+      <c r="W38" s="16">
+        <v>0</v>
+      </c>
+      <c r="X38" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y38" s="15">
         <v>0.59190323506057341</v>
       </c>
     </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A39" s="10">
         <v>46226</v>
       </c>
@@ -12752,20 +13113,20 @@
         <v>0</v>
       </c>
       <c r="L39" s="13">
+        <v>0</v>
+      </c>
+      <c r="M39" s="13">
         <v>223843</v>
       </c>
-      <c r="M39" s="14">
+      <c r="N39" s="14">
         <v>380362.45</v>
       </c>
-      <c r="N39" s="15">
-        <v>0</v>
-      </c>
       <c r="O39" s="15">
+        <v>0</v>
+      </c>
+      <c r="P39" s="15">
         <v>9.3214905940373474E-2</v>
       </c>
-      <c r="P39" s="16">
-        <v>0</v>
-      </c>
       <c r="Q39" s="16">
         <v>0</v>
       </c>
@@ -12773,22 +13134,28 @@
         <v>0</v>
       </c>
       <c r="S39" s="16">
+        <v>0</v>
+      </c>
+      <c r="T39" s="16">
         <v>0.31828588757907095</v>
       </c>
-      <c r="T39" s="16">
-        <v>0</v>
-      </c>
       <c r="U39" s="16">
         <v>0</v>
       </c>
       <c r="V39" s="16">
         <v>0</v>
       </c>
-      <c r="W39" s="15">
+      <c r="W39" s="16">
+        <v>0</v>
+      </c>
+      <c r="X39" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y39" s="15">
         <v>0.58849920648055554</v>
       </c>
     </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A40" s="10">
         <v>46227</v>
       </c>
@@ -12824,20 +13191,20 @@
         <v>0</v>
       </c>
       <c r="L40" s="13">
+        <v>0</v>
+      </c>
+      <c r="M40" s="13">
         <v>223843</v>
       </c>
-      <c r="M40" s="14">
+      <c r="N40" s="14">
         <v>377185.45</v>
       </c>
-      <c r="N40" s="15">
-        <v>0</v>
-      </c>
       <c r="O40" s="15">
+        <v>0</v>
+      </c>
+      <c r="P40" s="15">
         <v>8.5577134536870422E-2</v>
       </c>
-      <c r="P40" s="16">
-        <v>0</v>
-      </c>
       <c r="Q40" s="16">
         <v>0</v>
       </c>
@@ -12845,22 +13212,28 @@
         <v>0</v>
       </c>
       <c r="S40" s="16">
+        <v>0</v>
+      </c>
+      <c r="T40" s="16">
         <v>0.32096678172501086</v>
       </c>
-      <c r="T40" s="16">
-        <v>0</v>
-      </c>
       <c r="U40" s="16">
         <v>0</v>
       </c>
       <c r="V40" s="16">
         <v>0</v>
       </c>
-      <c r="W40" s="15">
+      <c r="W40" s="16">
+        <v>0</v>
+      </c>
+      <c r="X40" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y40" s="15">
         <v>0.59345608373811876</v>
       </c>
     </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A41" s="10">
         <v>46230</v>
       </c>
@@ -12896,20 +13269,20 @@
         <v>0</v>
       </c>
       <c r="L41" s="13">
+        <v>0</v>
+      </c>
+      <c r="M41" s="13">
         <v>223843</v>
       </c>
-      <c r="M41" s="14">
+      <c r="N41" s="14">
         <v>378220.45</v>
       </c>
-      <c r="N41" s="15">
-        <v>0</v>
-      </c>
       <c r="O41" s="15">
+        <v>0</v>
+      </c>
+      <c r="P41" s="15">
         <v>8.807945207616355E-2</v>
       </c>
-      <c r="P41" s="16">
-        <v>0</v>
-      </c>
       <c r="Q41" s="16">
         <v>0</v>
       </c>
@@ -12917,22 +13290,28 @@
         <v>0</v>
       </c>
       <c r="S41" s="16">
+        <v>0</v>
+      </c>
+      <c r="T41" s="16">
         <v>0.32008845634867178</v>
       </c>
-      <c r="T41" s="16">
-        <v>0</v>
-      </c>
       <c r="U41" s="16">
         <v>0</v>
       </c>
       <c r="V41" s="16">
         <v>0</v>
       </c>
-      <c r="W41" s="15">
+      <c r="W41" s="16">
+        <v>0</v>
+      </c>
+      <c r="X41" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="15">
         <v>0.5918320915751647</v>
       </c>
     </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A42" s="10">
         <v>46231</v>
       </c>
@@ -12968,18 +13347,18 @@
         <v>0</v>
       </c>
       <c r="L42" s="13">
+        <v>0</v>
+      </c>
+      <c r="M42" s="13">
         <v>223843</v>
       </c>
-      <c r="M42" s="14">
+      <c r="N42" s="14">
         <v>679531</v>
       </c>
-      <c r="N42" s="15">
+      <c r="O42" s="15">
         <v>0.49243375210255308</v>
       </c>
-      <c r="O42" s="15">
-        <v>0</v>
-      </c>
-      <c r="P42" s="16">
+      <c r="P42" s="15">
         <v>0</v>
       </c>
       <c r="Q42" s="16">
@@ -12989,22 +13368,28 @@
         <v>0</v>
       </c>
       <c r="S42" s="16">
+        <v>0</v>
+      </c>
+      <c r="T42" s="16">
         <v>0.17815817085607574</v>
       </c>
-      <c r="T42" s="16">
-        <v>0</v>
-      </c>
       <c r="U42" s="16">
         <v>0</v>
       </c>
       <c r="V42" s="16">
         <v>0</v>
       </c>
-      <c r="W42" s="15">
+      <c r="W42" s="16">
+        <v>0</v>
+      </c>
+      <c r="X42" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y42" s="15">
         <v>0.32940807704137121</v>
       </c>
     </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A43" s="10">
         <v>46232</v>
       </c>
@@ -13040,18 +13425,18 @@
         <v>0</v>
       </c>
       <c r="L43" s="13">
+        <v>0</v>
+      </c>
+      <c r="M43" s="13">
         <v>223843</v>
       </c>
-      <c r="M43" s="14">
+      <c r="N43" s="14">
         <v>679531</v>
       </c>
-      <c r="N43" s="15">
+      <c r="O43" s="15">
         <v>0.49243375210255308</v>
       </c>
-      <c r="O43" s="15">
-        <v>0</v>
-      </c>
-      <c r="P43" s="16">
+      <c r="P43" s="15">
         <v>0</v>
       </c>
       <c r="Q43" s="16">
@@ -13061,22 +13446,28 @@
         <v>0</v>
       </c>
       <c r="S43" s="16">
+        <v>0</v>
+      </c>
+      <c r="T43" s="16">
         <v>0.17815817085607574</v>
       </c>
-      <c r="T43" s="16">
-        <v>0</v>
-      </c>
       <c r="U43" s="16">
         <v>0</v>
       </c>
       <c r="V43" s="16">
         <v>0</v>
       </c>
-      <c r="W43" s="15">
+      <c r="W43" s="16">
+        <v>0</v>
+      </c>
+      <c r="X43" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y43" s="15">
         <v>0.32940807704137121</v>
       </c>
     </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A44" s="10">
         <v>46233</v>
       </c>
@@ -13112,20 +13503,20 @@
         <v>0</v>
       </c>
       <c r="L44" s="13">
+        <v>0</v>
+      </c>
+      <c r="M44" s="13">
         <v>223843</v>
       </c>
-      <c r="M44" s="14">
+      <c r="N44" s="14">
         <v>391793.7</v>
       </c>
-      <c r="N44" s="15">
-        <v>0</v>
-      </c>
       <c r="O44" s="15">
+        <v>0</v>
+      </c>
+      <c r="P44" s="15">
         <v>0.11967190896637697</v>
       </c>
-      <c r="P44" s="16">
-        <v>0</v>
-      </c>
       <c r="Q44" s="16">
         <v>0</v>
       </c>
@@ -13133,22 +13524,28 @@
         <v>0</v>
       </c>
       <c r="S44" s="16">
+        <v>0</v>
+      </c>
+      <c r="T44" s="16">
         <v>0.30899935348628627</v>
       </c>
-      <c r="T44" s="16">
-        <v>0</v>
-      </c>
       <c r="U44" s="16">
         <v>0</v>
       </c>
       <c r="V44" s="16">
         <v>0</v>
       </c>
-      <c r="W44" s="15">
+      <c r="W44" s="16">
+        <v>0</v>
+      </c>
+      <c r="X44" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y44" s="15">
         <v>0.57132873754733671</v>
       </c>
     </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A45" s="10">
         <v>46234</v>
       </c>
@@ -13184,20 +13581,20 @@
         <v>0</v>
       </c>
       <c r="L45" s="13">
+        <v>0</v>
+      </c>
+      <c r="M45" s="13">
         <v>223843</v>
       </c>
-      <c r="M45" s="14">
+      <c r="N45" s="14">
         <v>388741.7</v>
       </c>
-      <c r="N45" s="15">
-        <v>0</v>
-      </c>
       <c r="O45" s="15">
+        <v>0</v>
+      </c>
+      <c r="P45" s="15">
         <v>0.11276047823014616</v>
       </c>
-      <c r="P45" s="16">
-        <v>0</v>
-      </c>
       <c r="Q45" s="16">
         <v>0</v>
       </c>
@@ -13205,22 +13602,28 @@
         <v>0</v>
       </c>
       <c r="S45" s="16">
+        <v>0</v>
+      </c>
+      <c r="T45" s="16">
         <v>0.3114252985980151</v>
       </c>
-      <c r="T45" s="16">
-        <v>0</v>
-      </c>
       <c r="U45" s="16">
         <v>0</v>
       </c>
       <c r="V45" s="16">
         <v>0</v>
       </c>
-      <c r="W45" s="15">
+      <c r="W45" s="16">
+        <v>0</v>
+      </c>
+      <c r="X45" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y45" s="15">
         <v>0.57581422317183872</v>
       </c>
     </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A46" s="10">
         <v>46237</v>
       </c>
@@ -13256,20 +13659,20 @@
         <v>0</v>
       </c>
       <c r="L46" s="13">
+        <v>0</v>
+      </c>
+      <c r="M46" s="13">
         <v>223843</v>
       </c>
-      <c r="M46" s="14">
+      <c r="N46" s="14">
         <v>385314.7</v>
       </c>
-      <c r="N46" s="15">
-        <v>0</v>
-      </c>
       <c r="O46" s="15">
+        <v>0</v>
+      </c>
+      <c r="P46" s="15">
         <v>0.10486934446051503</v>
       </c>
-      <c r="P46" s="16">
-        <v>0</v>
-      </c>
       <c r="Q46" s="16">
         <v>0</v>
       </c>
@@ -13277,22 +13680,28 @@
         <v>0</v>
       </c>
       <c r="S46" s="16">
+        <v>0</v>
+      </c>
+      <c r="T46" s="16">
         <v>0.31419512414138362</v>
       </c>
-      <c r="T46" s="16">
-        <v>0</v>
-      </c>
       <c r="U46" s="16">
         <v>0</v>
       </c>
       <c r="V46" s="16">
         <v>0</v>
       </c>
-      <c r="W46" s="15">
+      <c r="W46" s="16">
+        <v>0</v>
+      </c>
+      <c r="X46" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y46" s="15">
         <v>0.58093553139810128</v>
       </c>
     </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A47" s="10">
         <v>46238</v>
       </c>
@@ -13328,20 +13737,20 @@
         <v>0</v>
       </c>
       <c r="L47" s="13">
+        <v>0</v>
+      </c>
+      <c r="M47" s="13">
         <v>223843</v>
       </c>
-      <c r="M47" s="14">
+      <c r="N47" s="14">
         <v>383427.7</v>
       </c>
-      <c r="N47" s="15">
-        <v>0</v>
-      </c>
       <c r="O47" s="15">
+        <v>0</v>
+      </c>
+      <c r="P47" s="15">
         <v>0.1004640509801457</v>
       </c>
-      <c r="P47" s="16">
-        <v>0</v>
-      </c>
       <c r="Q47" s="16">
         <v>0</v>
       </c>
@@ -13349,22 +13758,28 @@
         <v>0</v>
       </c>
       <c r="S47" s="16">
+        <v>0</v>
+      </c>
+      <c r="T47" s="16">
         <v>0.31574140313806226</v>
       </c>
-      <c r="T47" s="16">
-        <v>0</v>
-      </c>
       <c r="U47" s="16">
         <v>0</v>
       </c>
       <c r="V47" s="16">
         <v>0</v>
       </c>
-      <c r="W47" s="15">
+      <c r="W47" s="16">
+        <v>0</v>
+      </c>
+      <c r="X47" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y47" s="15">
         <v>0.58379454588179203</v>
       </c>
     </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A48" s="10">
         <v>46239</v>
       </c>
@@ -13400,20 +13815,20 @@
         <v>0</v>
       </c>
       <c r="L48" s="13">
+        <v>0</v>
+      </c>
+      <c r="M48" s="13">
         <v>223843</v>
       </c>
-      <c r="M48" s="14">
+      <c r="N48" s="14">
         <v>381652.7</v>
       </c>
-      <c r="N48" s="15">
-        <v>0</v>
-      </c>
       <c r="O48" s="15">
+        <v>0</v>
+      </c>
+      <c r="P48" s="15">
         <v>9.6280466507901064E-2</v>
       </c>
-      <c r="P48" s="16">
-        <v>0</v>
-      </c>
       <c r="Q48" s="16">
         <v>0</v>
       </c>
@@ -13421,22 +13836,28 @@
         <v>0</v>
       </c>
       <c r="S48" s="16">
+        <v>0</v>
+      </c>
+      <c r="T48" s="16">
         <v>0.31720986121675543</v>
       </c>
-      <c r="T48" s="16">
-        <v>0</v>
-      </c>
       <c r="U48" s="16">
         <v>0</v>
       </c>
       <c r="V48" s="16">
         <v>0</v>
       </c>
-      <c r="W48" s="15">
+      <c r="W48" s="16">
+        <v>0</v>
+      </c>
+      <c r="X48" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y48" s="15">
         <v>0.58650967227534356</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A49" s="10">
         <v>46240</v>
       </c>
@@ -13472,20 +13893,20 @@
         <v>0</v>
       </c>
       <c r="L49" s="13">
+        <v>0</v>
+      </c>
+      <c r="M49" s="13">
         <v>223843</v>
       </c>
-      <c r="M49" s="14">
+      <c r="N49" s="14">
         <v>383198.7</v>
       </c>
-      <c r="N49" s="15">
-        <v>0</v>
-      </c>
       <c r="O49" s="15">
+        <v>0</v>
+      </c>
+      <c r="P49" s="15">
         <v>9.9926487224513055E-2</v>
       </c>
-      <c r="P49" s="16">
-        <v>0</v>
-      </c>
       <c r="Q49" s="16">
         <v>0</v>
       </c>
@@ -13493,22 +13914,28 @@
         <v>0</v>
       </c>
       <c r="S49" s="16">
+        <v>0</v>
+      </c>
+      <c r="T49" s="16">
         <v>0.31593009057702959</v>
       </c>
-      <c r="T49" s="16">
-        <v>0</v>
-      </c>
       <c r="U49" s="16">
         <v>0</v>
       </c>
       <c r="V49" s="16">
         <v>0</v>
       </c>
-      <c r="W49" s="15">
+      <c r="W49" s="16">
+        <v>0</v>
+      </c>
+      <c r="X49" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y49" s="15">
         <v>0.58414342219845738</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A50" s="10">
         <v>46241</v>
       </c>
@@ -13544,20 +13971,20 @@
         <v>0</v>
       </c>
       <c r="L50" s="13">
+        <v>0</v>
+      </c>
+      <c r="M50" s="13">
         <v>223843</v>
       </c>
-      <c r="M50" s="14">
+      <c r="N50" s="14">
         <v>384776.7</v>
       </c>
-      <c r="N50" s="15">
-        <v>0</v>
-      </c>
       <c r="O50" s="15">
+        <v>0</v>
+      </c>
+      <c r="P50" s="15">
         <v>0.10361776063883289</v>
       </c>
-      <c r="P50" s="16">
-        <v>0</v>
-      </c>
       <c r="Q50" s="16">
         <v>0</v>
       </c>
@@ -13565,22 +13992,28 @@
         <v>0</v>
       </c>
       <c r="S50" s="16">
+        <v>0</v>
+      </c>
+      <c r="T50" s="16">
         <v>0.31463443602484248</v>
       </c>
-      <c r="T50" s="16">
-        <v>0</v>
-      </c>
       <c r="U50" s="16">
         <v>0</v>
       </c>
       <c r="V50" s="16">
         <v>0</v>
       </c>
-      <c r="W50" s="15">
+      <c r="W50" s="16">
+        <v>0</v>
+      </c>
+      <c r="X50" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y50" s="15">
         <v>0.5817478033363247</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A51" s="10">
         <v>46244</v>
       </c>
@@ -13615,21 +14048,21 @@
       <c r="K51" s="13">
         <v>0</v>
       </c>
-      <c r="L51" s="18">
+      <c r="L51" s="13">
+        <v>0</v>
+      </c>
+      <c r="M51" s="18">
         <v>54051</v>
       </c>
-      <c r="M51" s="14">
+      <c r="N51" s="14">
         <v>384909.7</v>
       </c>
-      <c r="N51" s="15">
-        <v>0</v>
-      </c>
       <c r="O51" s="15">
+        <v>0</v>
+      </c>
+      <c r="P51" s="15">
         <v>6.342448631458239E-2</v>
       </c>
-      <c r="P51" s="16">
-        <v>0</v>
-      </c>
       <c r="Q51" s="16">
         <v>0</v>
       </c>
@@ -13637,22 +14070,28 @@
         <v>0</v>
       </c>
       <c r="S51" s="16">
+        <v>0</v>
+      </c>
+      <c r="T51" s="16">
         <v>0.31452571862959028</v>
       </c>
-      <c r="T51" s="16">
+      <c r="U51" s="16">
         <v>0.48162465118442066</v>
       </c>
-      <c r="U51" s="16">
-        <v>0</v>
-      </c>
       <c r="V51" s="16">
         <v>0</v>
       </c>
-      <c r="W51" s="15">
+      <c r="W51" s="16">
+        <v>0</v>
+      </c>
+      <c r="X51" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y51" s="15">
         <v>0.14042514387140673</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A52" s="10">
         <v>46245</v>
       </c>
@@ -13687,21 +14126,21 @@
       <c r="K52" s="13">
         <v>0</v>
       </c>
-      <c r="L52" s="18">
+      <c r="L52" s="13">
+        <v>0</v>
+      </c>
+      <c r="M52" s="18">
         <v>54051</v>
       </c>
-      <c r="M52" s="14">
+      <c r="N52" s="14">
         <v>379686.7</v>
       </c>
-      <c r="N52" s="15">
-        <v>0</v>
-      </c>
       <c r="O52" s="15">
+        <v>0</v>
+      </c>
+      <c r="P52" s="15">
         <v>5.0540880151977961E-2</v>
       </c>
-      <c r="P52" s="16">
-        <v>0</v>
-      </c>
       <c r="Q52" s="16">
         <v>0</v>
       </c>
@@ -13709,22 +14148,28 @@
         <v>0</v>
       </c>
       <c r="S52" s="16">
+        <v>0</v>
+      </c>
+      <c r="T52" s="16">
         <v>0.31885235906340675</v>
       </c>
-      <c r="T52" s="16">
+      <c r="U52" s="16">
         <v>0.48824991762945608</v>
       </c>
-      <c r="U52" s="16">
-        <v>0</v>
-      </c>
       <c r="V52" s="16">
         <v>0</v>
       </c>
-      <c r="W52" s="15">
+      <c r="W52" s="16">
+        <v>0</v>
+      </c>
+      <c r="X52" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y52" s="15">
         <v>0.14235684315515923</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A53" s="10">
         <v>46246</v>
       </c>
@@ -13759,49 +14204,55 @@
       <c r="K53" s="13">
         <v>0</v>
       </c>
-      <c r="L53" s="18">
+      <c r="L53" s="13">
+        <v>0</v>
+      </c>
+      <c r="M53" s="18">
         <v>218671</v>
       </c>
-      <c r="M53" s="14">
-        <f>SUM(C53:L53)</f>
+      <c r="N53" s="14">
+        <f>SUM(C53:M53)</f>
         <v>676730</v>
       </c>
-      <c r="N53" s="15">
-        <v>0</v>
-      </c>
       <c r="O53" s="15">
         <v>0</v>
       </c>
-      <c r="P53" s="16">
+      <c r="P53" s="15">
         <v>0</v>
       </c>
       <c r="Q53" s="16">
         <v>0</v>
       </c>
       <c r="R53" s="16">
-        <f>G53/M53</f>
+        <v>0</v>
+      </c>
+      <c r="S53" s="16">
+        <f>G53/N53</f>
         <v>0.2699821199001079</v>
       </c>
-      <c r="S53" s="16">
-        <f>H53/M53</f>
+      <c r="T53" s="16">
+        <f>H53/N53</f>
         <v>0.17889557135046474</v>
       </c>
-      <c r="T53" s="16">
-        <f>I53/M53</f>
+      <c r="U53" s="16">
+        <f>I53/N53</f>
         <v>0.22799343903772554</v>
       </c>
-      <c r="U53" s="16">
-        <v>0</v>
-      </c>
       <c r="V53" s="16">
         <v>0</v>
       </c>
-      <c r="W53" s="15">
-        <f>L53/M53</f>
+      <c r="W53" s="16">
+        <v>0</v>
+      </c>
+      <c r="X53" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="15">
+        <f>M53/N53</f>
         <v>0.32312886971170185</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A54" s="10">
         <v>46247</v>
       </c>
@@ -13836,19 +14287,19 @@
       <c r="K54" s="13">
         <v>0</v>
       </c>
-      <c r="L54" s="18">
+      <c r="L54" s="13">
+        <v>0</v>
+      </c>
+      <c r="M54" s="18">
         <v>218671</v>
       </c>
-      <c r="M54" s="14">
+      <c r="N54" s="14">
         <v>494025</v>
       </c>
-      <c r="N54" s="15">
-        <v>0</v>
-      </c>
       <c r="O54" s="15">
         <v>0</v>
       </c>
-      <c r="P54" s="16">
+      <c r="P54" s="15">
         <v>0</v>
       </c>
       <c r="Q54" s="16">
@@ -13858,22 +14309,28 @@
         <v>0</v>
       </c>
       <c r="S54" s="16">
+        <v>0</v>
+      </c>
+      <c r="T54" s="16">
         <v>0.24505642427002683</v>
       </c>
-      <c r="T54" s="16">
+      <c r="U54" s="16">
         <v>0.31231212995293761</v>
       </c>
-      <c r="U54" s="16">
-        <v>0</v>
-      </c>
       <c r="V54" s="16">
         <v>0</v>
       </c>
-      <c r="W54" s="15">
+      <c r="W54" s="16">
+        <v>0</v>
+      </c>
+      <c r="X54" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="15">
         <v>0.44263144577703556</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A55" s="10">
         <v>46248</v>
       </c>
@@ -13908,19 +14365,19 @@
       <c r="K55" s="13">
         <v>0</v>
       </c>
-      <c r="L55" s="18">
+      <c r="L55" s="13">
+        <v>0</v>
+      </c>
+      <c r="M55" s="18">
         <v>218671</v>
       </c>
-      <c r="M55" s="14">
+      <c r="N55" s="14">
         <v>494025</v>
       </c>
-      <c r="N55" s="15">
-        <v>0</v>
-      </c>
       <c r="O55" s="15">
         <v>0</v>
       </c>
-      <c r="P55" s="16">
+      <c r="P55" s="15">
         <v>0</v>
       </c>
       <c r="Q55" s="16">
@@ -13930,22 +14387,28 @@
         <v>0</v>
       </c>
       <c r="S55" s="16">
+        <v>0</v>
+      </c>
+      <c r="T55" s="16">
         <v>0.24505642427002683</v>
       </c>
-      <c r="T55" s="16">
+      <c r="U55" s="16">
         <v>0.31231212995293761</v>
       </c>
-      <c r="U55" s="16">
-        <v>0</v>
-      </c>
       <c r="V55" s="16">
         <v>0</v>
       </c>
-      <c r="W55" s="15">
+      <c r="W55" s="16">
+        <v>0</v>
+      </c>
+      <c r="X55" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y55" s="15">
         <v>0.44263144577703556</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A56" s="10">
         <v>46251</v>
       </c>
@@ -13980,19 +14443,19 @@
       <c r="K56" s="13">
         <v>0</v>
       </c>
-      <c r="L56" s="18">
+      <c r="L56" s="13">
+        <v>0</v>
+      </c>
+      <c r="M56" s="18">
         <v>218671</v>
       </c>
-      <c r="M56" s="14">
+      <c r="N56" s="14">
         <v>494025</v>
       </c>
-      <c r="N56" s="15">
-        <v>0</v>
-      </c>
       <c r="O56" s="15">
         <v>0</v>
       </c>
-      <c r="P56" s="16">
+      <c r="P56" s="15">
         <v>0</v>
       </c>
       <c r="Q56" s="16">
@@ -14002,22 +14465,28 @@
         <v>0</v>
       </c>
       <c r="S56" s="16">
+        <v>0</v>
+      </c>
+      <c r="T56" s="16">
         <v>0.24505642427002683</v>
       </c>
-      <c r="T56" s="16">
+      <c r="U56" s="16">
         <v>0.31231212995293761</v>
       </c>
-      <c r="U56" s="16">
-        <v>0</v>
-      </c>
       <c r="V56" s="16">
         <v>0</v>
       </c>
-      <c r="W56" s="15">
+      <c r="W56" s="16">
+        <v>0</v>
+      </c>
+      <c r="X56" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y56" s="15">
         <v>0.44263144577703556</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A57" s="10">
         <v>46252</v>
       </c>
@@ -14052,19 +14521,19 @@
       <c r="K57" s="13">
         <v>0</v>
       </c>
-      <c r="L57" s="18">
+      <c r="L57" s="13">
+        <v>0</v>
+      </c>
+      <c r="M57" s="18">
         <v>218671</v>
       </c>
-      <c r="M57" s="14">
+      <c r="N57" s="14">
         <v>494025</v>
       </c>
-      <c r="N57" s="15">
-        <v>0</v>
-      </c>
       <c r="O57" s="15">
         <v>0</v>
       </c>
-      <c r="P57" s="16">
+      <c r="P57" s="15">
         <v>0</v>
       </c>
       <c r="Q57" s="16">
@@ -14074,22 +14543,28 @@
         <v>0</v>
       </c>
       <c r="S57" s="16">
+        <v>0</v>
+      </c>
+      <c r="T57" s="16">
         <v>0.24505642427002683</v>
       </c>
-      <c r="T57" s="16">
+      <c r="U57" s="16">
         <v>0.31231212995293761</v>
       </c>
-      <c r="U57" s="16">
-        <v>0</v>
-      </c>
       <c r="V57" s="16">
         <v>0</v>
       </c>
-      <c r="W57" s="15">
+      <c r="W57" s="16">
+        <v>0</v>
+      </c>
+      <c r="X57" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y57" s="15">
         <v>0.44263144577703556</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A58" s="10">
         <v>46253</v>
       </c>
@@ -14124,19 +14599,19 @@
       <c r="K58" s="13">
         <v>0</v>
       </c>
-      <c r="L58" s="18">
+      <c r="L58" s="13">
+        <v>0</v>
+      </c>
+      <c r="M58" s="18">
         <v>218671</v>
       </c>
-      <c r="M58" s="14">
+      <c r="N58" s="14">
         <v>494025</v>
       </c>
-      <c r="N58" s="15">
-        <v>0</v>
-      </c>
       <c r="O58" s="15">
         <v>0</v>
       </c>
-      <c r="P58" s="16">
+      <c r="P58" s="15">
         <v>0</v>
       </c>
       <c r="Q58" s="16">
@@ -14146,22 +14621,28 @@
         <v>0</v>
       </c>
       <c r="S58" s="16">
+        <v>0</v>
+      </c>
+      <c r="T58" s="16">
         <v>0.24505642427002683</v>
       </c>
-      <c r="T58" s="16">
+      <c r="U58" s="16">
         <v>0.31231212995293761</v>
       </c>
-      <c r="U58" s="16">
-        <v>0</v>
-      </c>
       <c r="V58" s="16">
         <v>0</v>
       </c>
-      <c r="W58" s="15">
+      <c r="W58" s="16">
+        <v>0</v>
+      </c>
+      <c r="X58" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y58" s="15">
         <v>0.44263144577703556</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A59" s="10">
         <v>46254</v>
       </c>
@@ -14196,49 +14677,55 @@
       <c r="K59" s="13">
         <v>0</v>
       </c>
-      <c r="L59" s="18">
+      <c r="L59" s="13">
+        <v>0</v>
+      </c>
+      <c r="M59" s="18">
         <v>218671</v>
       </c>
-      <c r="M59" s="14">
-        <f>SUM(C59:L59)</f>
+      <c r="N59" s="14">
+        <f>SUM(C59:M59)</f>
         <v>1945025</v>
       </c>
-      <c r="N59" s="15">
-        <v>0</v>
-      </c>
       <c r="O59" s="15">
         <v>0</v>
       </c>
-      <c r="P59" s="16">
+      <c r="P59" s="15">
         <v>0</v>
       </c>
       <c r="Q59" s="16">
-        <f>E59/M59</f>
+        <v>0</v>
+      </c>
+      <c r="R59" s="16">
+        <f>E59/N59</f>
         <v>0.7460058354005733</v>
       </c>
-      <c r="R59" s="16">
-        <v>0</v>
-      </c>
       <c r="S59" s="16">
-        <f>H59/M59</f>
+        <v>0</v>
+      </c>
+      <c r="T59" s="16">
+        <f>H59/N59</f>
         <v>6.2242901762188149E-2</v>
       </c>
-      <c r="T59" s="16">
-        <f>I59/M59</f>
+      <c r="U59" s="16">
+        <f>I59/N59</f>
         <v>7.9325458541663993E-2</v>
       </c>
-      <c r="U59" s="16">
-        <v>0</v>
-      </c>
       <c r="V59" s="16">
         <v>0</v>
       </c>
-      <c r="W59" s="15">
-        <f>L59/M59</f>
+      <c r="W59" s="16">
+        <v>0</v>
+      </c>
+      <c r="X59" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y59" s="15">
+        <f>M59/N59</f>
         <v>0.11242580429557461</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A60" s="10">
         <v>46255</v>
       </c>
@@ -14273,44 +14760,50 @@
       <c r="K60" s="13">
         <v>0</v>
       </c>
-      <c r="L60" s="18">
+      <c r="L60" s="13">
+        <v>0</v>
+      </c>
+      <c r="M60" s="18">
         <v>218671</v>
       </c>
-      <c r="M60" s="14">
+      <c r="N60" s="14">
         <v>930260</v>
       </c>
-      <c r="N60" s="15">
-        <v>0</v>
-      </c>
       <c r="O60" s="15">
         <v>0</v>
       </c>
-      <c r="P60" s="16">
+      <c r="P60" s="15">
         <v>0</v>
       </c>
       <c r="Q60" s="16">
+        <v>0</v>
+      </c>
+      <c r="R60" s="16">
         <v>0.46893879130565647</v>
       </c>
-      <c r="R60" s="16">
-        <v>0</v>
-      </c>
       <c r="S60" s="16">
+        <v>0</v>
+      </c>
+      <c r="T60" s="16">
         <v>0.13013996087115431</v>
       </c>
-      <c r="T60" s="16">
+      <c r="U60" s="16">
         <v>0.16585685722271193</v>
       </c>
-      <c r="U60" s="16">
-        <v>0</v>
-      </c>
       <c r="V60" s="16">
         <v>0</v>
       </c>
-      <c r="W60" s="15">
+      <c r="W60" s="16">
+        <v>0</v>
+      </c>
+      <c r="X60" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="15">
         <v>0.23506439060047729</v>
       </c>
     </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A61" s="10">
         <v>46258</v>
       </c>
@@ -14345,51 +14838,57 @@
       <c r="K61" s="13">
         <v>0</v>
       </c>
-      <c r="L61" s="18">
+      <c r="L61" s="13">
+        <v>0</v>
+      </c>
+      <c r="M61" s="18">
         <v>218671</v>
       </c>
-      <c r="M61" s="14">
-        <f>SUM(C61:L61)</f>
+      <c r="N61" s="14">
+        <f>SUM(C61:M61)</f>
         <v>1204798</v>
       </c>
-      <c r="N61" s="15">
-        <f>C61/M61</f>
+      <c r="O61" s="15">
+        <f>C61/N61</f>
         <v>0.11067249447625245</v>
       </c>
-      <c r="O61" s="15">
-        <v>0</v>
-      </c>
-      <c r="P61" s="16">
-        <f>F61/M61</f>
+      <c r="P61" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="16">
+        <f>F61/N61</f>
         <v>0.11719806971791122</v>
       </c>
-      <c r="Q61" s="16">
-        <f>E61/M61</f>
+      <c r="R61" s="16">
+        <f>E61/N61</f>
         <v>0.36208144435830736</v>
       </c>
-      <c r="R61" s="16">
-        <v>0</v>
-      </c>
       <c r="S61" s="16">
-        <f>H61/M61</f>
+        <v>0</v>
+      </c>
+      <c r="T61" s="16">
+        <f>H61/N61</f>
         <v>0.10048489456323799</v>
       </c>
-      <c r="T61" s="16">
-        <f>I61/M61</f>
+      <c r="U61" s="16">
+        <f>I61/N61</f>
         <v>0.12806296159190173</v>
       </c>
-      <c r="U61" s="16">
-        <v>0</v>
-      </c>
       <c r="V61" s="16">
         <v>0</v>
       </c>
-      <c r="W61" s="15">
-        <f>L61/M61</f>
+      <c r="W61" s="16">
+        <v>0</v>
+      </c>
+      <c r="X61" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="15">
+        <f>M61/N61</f>
         <v>0.18150013529238926</v>
       </c>
     </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A62" s="10">
         <v>46259</v>
       </c>
@@ -14424,21 +14923,21 @@
       <c r="K62" s="13">
         <v>0</v>
       </c>
-      <c r="L62" s="18">
+      <c r="L62" s="13">
+        <v>0</v>
+      </c>
+      <c r="M62" s="18">
         <v>54671</v>
       </c>
-      <c r="M62" s="14">
+      <c r="N62" s="14">
         <v>396282.31</v>
       </c>
-      <c r="N62" s="15">
-        <v>0</v>
-      </c>
       <c r="O62" s="15">
+        <v>0</v>
+      </c>
+      <c r="P62" s="15">
         <v>0.86204027123996529</v>
       </c>
-      <c r="P62" s="16">
-        <v>0</v>
-      </c>
       <c r="Q62" s="16">
         <v>0</v>
       </c>
@@ -14457,11 +14956,17 @@
       <c r="V62" s="16">
         <v>0</v>
       </c>
-      <c r="W62" s="15">
+      <c r="W62" s="16">
+        <v>0</v>
+      </c>
+      <c r="X62" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y62" s="15">
         <v>0.13795972876003473</v>
       </c>
     </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A63" s="10">
         <v>46260</v>
       </c>
@@ -14496,21 +15001,21 @@
       <c r="K63" s="13">
         <v>0</v>
       </c>
-      <c r="L63" s="18">
+      <c r="L63" s="13">
+        <v>0</v>
+      </c>
+      <c r="M63" s="18">
         <v>54671</v>
       </c>
-      <c r="M63" s="14">
+      <c r="N63" s="14">
         <v>395802.31</v>
       </c>
-      <c r="N63" s="15">
-        <v>0</v>
-      </c>
       <c r="O63" s="15">
+        <v>0</v>
+      </c>
+      <c r="P63" s="15">
         <v>0.86187296380357159</v>
       </c>
-      <c r="P63" s="16">
-        <v>0</v>
-      </c>
       <c r="Q63" s="16">
         <v>0</v>
       </c>
@@ -14529,11 +15034,17 @@
       <c r="V63" s="16">
         <v>0</v>
       </c>
-      <c r="W63" s="15">
+      <c r="W63" s="16">
+        <v>0</v>
+      </c>
+      <c r="X63" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y63" s="15">
         <v>0.13812703619642847</v>
       </c>
     </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A64" s="10">
         <v>46261</v>
       </c>
@@ -14568,21 +15079,21 @@
       <c r="K64" s="13">
         <v>0</v>
       </c>
-      <c r="L64" s="18">
+      <c r="L64" s="13">
+        <v>0</v>
+      </c>
+      <c r="M64" s="18">
         <v>54671</v>
       </c>
-      <c r="M64" s="14">
+      <c r="N64" s="14">
         <v>396617.31</v>
       </c>
-      <c r="N64" s="15">
-        <v>0</v>
-      </c>
       <c r="O64" s="15">
+        <v>0</v>
+      </c>
+      <c r="P64" s="15">
         <v>0.8621567979471193</v>
       </c>
-      <c r="P64" s="16">
-        <v>0</v>
-      </c>
       <c r="Q64" s="16">
         <v>0</v>
       </c>
@@ -14601,11 +15112,17 @@
       <c r="V64" s="16">
         <v>0</v>
       </c>
-      <c r="W64" s="15">
+      <c r="W64" s="16">
+        <v>0</v>
+      </c>
+      <c r="X64" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y64" s="15">
         <v>0.13784320205288064</v>
       </c>
     </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A65" s="10">
         <v>46262</v>
       </c>
@@ -14640,21 +15157,21 @@
       <c r="K65" s="13">
         <v>0</v>
       </c>
-      <c r="L65" s="18">
+      <c r="L65" s="13">
+        <v>0</v>
+      </c>
+      <c r="M65" s="18">
         <v>54671</v>
       </c>
-      <c r="M65" s="14">
+      <c r="N65" s="14">
         <v>396917.31</v>
       </c>
-      <c r="N65" s="15">
-        <v>0</v>
-      </c>
       <c r="O65" s="15">
+        <v>0</v>
+      </c>
+      <c r="P65" s="15">
         <v>0.86226098327634038</v>
       </c>
-      <c r="P65" s="16">
-        <v>0</v>
-      </c>
       <c r="Q65" s="16">
         <v>0</v>
       </c>
@@ -14673,11 +15190,17 @@
       <c r="V65" s="16">
         <v>0</v>
       </c>
-      <c r="W65" s="15">
+      <c r="W65" s="16">
+        <v>0</v>
+      </c>
+      <c r="X65" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y65" s="15">
         <v>0.13773901672365965</v>
       </c>
     </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A66" s="10">
         <v>46265</v>
       </c>
@@ -14712,21 +15235,21 @@
       <c r="K66" s="13">
         <v>0</v>
       </c>
-      <c r="L66" s="18">
+      <c r="L66" s="13">
+        <v>0</v>
+      </c>
+      <c r="M66" s="18">
         <v>54671</v>
       </c>
-      <c r="M66" s="14">
+      <c r="N66" s="14">
         <v>399269.72</v>
       </c>
-      <c r="N66" s="15">
+      <c r="O66" s="15">
         <v>0.14977093679931452</v>
       </c>
-      <c r="O66" s="15">
+      <c r="P66" s="15">
         <v>0.71330157468490218</v>
       </c>
-      <c r="P66" s="16">
-        <v>0</v>
-      </c>
       <c r="Q66" s="16">
         <v>0</v>
       </c>
@@ -14745,11 +15268,17 @@
       <c r="V66" s="16">
         <v>0</v>
       </c>
-      <c r="W66" s="15">
+      <c r="W66" s="16">
+        <v>0</v>
+      </c>
+      <c r="X66" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="15">
         <v>0.13692748851578326</v>
       </c>
     </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A67" s="10">
         <v>46266</v>
       </c>
@@ -14784,19 +15313,19 @@
       <c r="K67" s="13">
         <v>0</v>
       </c>
-      <c r="L67" s="18">
+      <c r="L67" s="13">
+        <v>0</v>
+      </c>
+      <c r="M67" s="18">
         <v>54671</v>
       </c>
-      <c r="M67" s="14">
+      <c r="N67" s="14">
         <v>926093</v>
       </c>
-      <c r="N67" s="15">
+      <c r="O67" s="15">
         <v>0.94096597209999433</v>
       </c>
-      <c r="O67" s="15">
-        <v>0</v>
-      </c>
-      <c r="P67" s="16">
+      <c r="P67" s="15">
         <v>0</v>
       </c>
       <c r="Q67" s="16">
@@ -14817,11 +15346,17 @@
       <c r="V67" s="16">
         <v>0</v>
       </c>
-      <c r="W67" s="15">
+      <c r="W67" s="16">
+        <v>0</v>
+      </c>
+      <c r="X67" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="15">
         <v>5.9034027900005726E-2</v>
       </c>
     </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A68" s="10">
         <v>46267</v>
       </c>
@@ -14856,19 +15391,19 @@
       <c r="K68" s="13">
         <v>0</v>
       </c>
-      <c r="L68" s="18">
+      <c r="L68" s="13">
+        <v>0</v>
+      </c>
+      <c r="M68" s="18">
         <v>54671</v>
       </c>
-      <c r="M68" s="14">
+      <c r="N68" s="14">
         <v>794093</v>
       </c>
-      <c r="N68" s="15">
+      <c r="O68" s="15">
         <v>0.93115290022705144</v>
       </c>
-      <c r="O68" s="15">
-        <v>0</v>
-      </c>
-      <c r="P68" s="16">
+      <c r="P68" s="15">
         <v>0</v>
       </c>
       <c r="Q68" s="16">
@@ -14889,11 +15424,17 @@
       <c r="V68" s="16">
         <v>0</v>
       </c>
-      <c r="W68" s="15">
+      <c r="W68" s="16">
+        <v>0</v>
+      </c>
+      <c r="X68" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y68" s="15">
         <v>6.8847099772948506E-2</v>
       </c>
     </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A69" s="10">
         <v>46268</v>
       </c>
@@ -14928,22 +15469,22 @@
       <c r="K69" s="13">
         <v>0</v>
       </c>
-      <c r="L69" s="18">
-        <v>0</v>
-      </c>
-      <c r="M69" s="14">
-        <f t="shared" ref="M69:M102" si="0">SUM(C69:L69)</f>
+      <c r="L69" s="13">
+        <v>0</v>
+      </c>
+      <c r="M69" s="18">
+        <v>0</v>
+      </c>
+      <c r="N69" s="14">
+        <f t="shared" ref="N69:N103" si="0">SUM(C69:M69)</f>
         <v>407651</v>
       </c>
-      <c r="N69" s="15">
+      <c r="O69" s="15">
         <v>0.25051515991027662</v>
       </c>
-      <c r="O69" s="15">
+      <c r="P69" s="15">
         <v>0.74948484008972338</v>
       </c>
-      <c r="P69" s="16">
-        <v>0</v>
-      </c>
       <c r="Q69" s="16">
         <v>0</v>
       </c>
@@ -14962,11 +15503,17 @@
       <c r="V69" s="16">
         <v>0</v>
       </c>
-      <c r="W69" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W69" s="16">
+        <v>0</v>
+      </c>
+      <c r="X69" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y69" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A70" s="10">
         <v>46269</v>
       </c>
@@ -15001,24 +15548,24 @@
       <c r="K70" s="13">
         <v>0</v>
       </c>
-      <c r="L70" s="18">
-        <v>0</v>
-      </c>
-      <c r="M70" s="14">
+      <c r="L70" s="13">
+        <v>0</v>
+      </c>
+      <c r="M70" s="18">
+        <v>0</v>
+      </c>
+      <c r="N70" s="14">
         <f t="shared" si="0"/>
         <v>408551</v>
       </c>
-      <c r="N70" s="15">
-        <f t="shared" ref="N70:N75" si="1">C70/M70</f>
+      <c r="O70" s="15">
+        <f t="shared" ref="O70:O75" si="1">C70/N70</f>
         <v>0.24736201845057287</v>
       </c>
-      <c r="O70" s="15">
-        <f t="shared" ref="O70:O75" si="2">D70/M70</f>
+      <c r="P70" s="15">
+        <f t="shared" ref="P70:P75" si="2">D70/N70</f>
         <v>0.75263798154942707</v>
       </c>
-      <c r="P70" s="16">
-        <v>0</v>
-      </c>
       <c r="Q70" s="16">
         <v>0</v>
       </c>
@@ -15037,11 +15584,17 @@
       <c r="V70" s="16">
         <v>0</v>
       </c>
-      <c r="W70" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W70" s="16">
+        <v>0</v>
+      </c>
+      <c r="X70" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y70" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A71" s="10">
         <v>46272</v>
       </c>
@@ -15076,24 +15629,24 @@
       <c r="K71" s="13">
         <v>0</v>
       </c>
-      <c r="L71" s="18">
-        <v>0</v>
-      </c>
-      <c r="M71" s="14">
+      <c r="L71" s="13">
+        <v>0</v>
+      </c>
+      <c r="M71" s="18">
+        <v>0</v>
+      </c>
+      <c r="N71" s="14">
         <f t="shared" si="0"/>
         <v>408551</v>
       </c>
-      <c r="N71" s="15">
+      <c r="O71" s="15">
         <f t="shared" si="1"/>
         <v>0.24736201845057287</v>
       </c>
-      <c r="O71" s="15">
+      <c r="P71" s="15">
         <f t="shared" si="2"/>
         <v>0.75263798154942707</v>
       </c>
-      <c r="P71" s="16">
-        <v>0</v>
-      </c>
       <c r="Q71" s="16">
         <v>0</v>
       </c>
@@ -15112,11 +15665,17 @@
       <c r="V71" s="16">
         <v>0</v>
       </c>
-      <c r="W71" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W71" s="16">
+        <v>0</v>
+      </c>
+      <c r="X71" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y71" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A72" s="10">
         <v>46273</v>
       </c>
@@ -15151,24 +15710,24 @@
       <c r="K72" s="13">
         <v>0</v>
       </c>
-      <c r="L72" s="18">
-        <v>0</v>
-      </c>
-      <c r="M72" s="14">
+      <c r="L72" s="13">
+        <v>0</v>
+      </c>
+      <c r="M72" s="18">
+        <v>0</v>
+      </c>
+      <c r="N72" s="14">
         <f t="shared" si="0"/>
         <v>408551</v>
       </c>
-      <c r="N72" s="15">
+      <c r="O72" s="15">
         <f t="shared" si="1"/>
         <v>0.24736201845057287</v>
       </c>
-      <c r="O72" s="15">
+      <c r="P72" s="15">
         <f t="shared" si="2"/>
         <v>0.75263798154942707</v>
       </c>
-      <c r="P72" s="16">
-        <v>0</v>
-      </c>
       <c r="Q72" s="16">
         <v>0</v>
       </c>
@@ -15187,11 +15746,17 @@
       <c r="V72" s="16">
         <v>0</v>
       </c>
-      <c r="W72" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W72" s="16">
+        <v>0</v>
+      </c>
+      <c r="X72" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A73" s="10">
         <v>46274</v>
       </c>
@@ -15226,24 +15791,24 @@
       <c r="K73" s="13">
         <v>0</v>
       </c>
-      <c r="L73" s="18">
-        <v>0</v>
-      </c>
-      <c r="M73" s="14">
+      <c r="L73" s="13">
+        <v>0</v>
+      </c>
+      <c r="M73" s="18">
+        <v>0</v>
+      </c>
+      <c r="N73" s="14">
         <f t="shared" si="0"/>
         <v>409358</v>
       </c>
-      <c r="N73" s="15">
+      <c r="O73" s="15">
         <f t="shared" si="1"/>
         <v>0.45189296410476892</v>
       </c>
-      <c r="O73" s="15">
+      <c r="P73" s="15">
         <f t="shared" si="2"/>
         <v>0.54810703589523102</v>
       </c>
-      <c r="P73" s="16">
-        <v>0</v>
-      </c>
       <c r="Q73" s="16">
         <v>0</v>
       </c>
@@ -15262,11 +15827,17 @@
       <c r="V73" s="16">
         <v>0</v>
       </c>
-      <c r="W73" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W73" s="16">
+        <v>0</v>
+      </c>
+      <c r="X73" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A74" s="10">
         <v>46275</v>
       </c>
@@ -15300,24 +15871,24 @@
       <c r="K74" s="13">
         <v>0</v>
       </c>
-      <c r="L74" s="18">
+      <c r="L74" s="13">
+        <v>0</v>
+      </c>
+      <c r="M74" s="18">
         <v>120370</v>
       </c>
-      <c r="M74" s="14">
+      <c r="N74" s="14">
         <f t="shared" si="0"/>
         <v>563114</v>
       </c>
-      <c r="N74" s="15">
+      <c r="O74" s="15">
         <f t="shared" si="1"/>
         <v>0.74001534325198803</v>
       </c>
-      <c r="O74" s="15">
+      <c r="P74" s="15">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
-      <c r="P74" s="16">
-        <v>0</v>
-      </c>
       <c r="Q74" s="16">
         <v>0</v>
       </c>
@@ -15328,21 +15899,27 @@
         <v>0</v>
       </c>
       <c r="T74" s="16">
-        <f t="shared" ref="T74:T79" si="3">I74/M74</f>
+        <v>0</v>
+      </c>
+      <c r="U74" s="16">
+        <f t="shared" ref="U74:U79" si="3">I74/N74</f>
         <v>4.6226874132058518E-2</v>
       </c>
-      <c r="U74" s="16">
-        <f>L74/M74</f>
+      <c r="V74" s="16">
+        <v>0</v>
+      </c>
+      <c r="W74" s="16">
+        <f>M74/N74</f>
         <v>0.21375778261595343</v>
       </c>
-      <c r="V74" s="16">
-        <v>0</v>
-      </c>
-      <c r="W74" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="X74" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y74" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A75" s="10">
         <v>46276</v>
       </c>
@@ -15381,21 +15958,21 @@
       <c r="L75" s="13">
         <v>0</v>
       </c>
-      <c r="M75" s="14">
+      <c r="M75" s="13">
+        <v>0</v>
+      </c>
+      <c r="N75" s="14">
         <f t="shared" si="0"/>
         <v>412405</v>
       </c>
-      <c r="N75" s="15">
+      <c r="O75" s="15">
         <f t="shared" si="1"/>
         <v>0.52517307016161296</v>
       </c>
-      <c r="O75" s="15">
+      <c r="P75" s="15">
         <f t="shared" si="2"/>
         <v>0.41170693856767016</v>
       </c>
-      <c r="P75" s="16">
-        <v>0</v>
-      </c>
       <c r="Q75" s="16">
         <v>0</v>
       </c>
@@ -15406,21 +15983,27 @@
         <v>0</v>
       </c>
       <c r="T75" s="16">
+        <v>0</v>
+      </c>
+      <c r="U75" s="16">
         <f t="shared" si="3"/>
         <v>6.3119991270716894E-2</v>
       </c>
-      <c r="U75" s="16">
-        <f>L75/M75</f>
-        <v>0</v>
-      </c>
       <c r="V75" s="16">
         <v>0</v>
       </c>
-      <c r="W75" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W75" s="16">
+        <f>M75/N75</f>
+        <v>0</v>
+      </c>
+      <c r="X75" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y75" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A76" s="10">
         <v>46279</v>
       </c>
@@ -15455,24 +16038,24 @@
       <c r="K76" s="13">
         <v>0</v>
       </c>
-      <c r="L76" s="18">
-        <v>0</v>
-      </c>
-      <c r="M76" s="14">
+      <c r="L76" s="13">
+        <v>0</v>
+      </c>
+      <c r="M76" s="18">
+        <v>0</v>
+      </c>
+      <c r="N76" s="14">
         <f t="shared" si="0"/>
         <v>408536</v>
       </c>
-      <c r="N76" s="15">
-        <f t="shared" ref="N76" si="4">C76/M76</f>
+      <c r="O76" s="15">
+        <f t="shared" ref="O76" si="4">C76/N76</f>
         <v>0.74552793389077099</v>
       </c>
-      <c r="O76" s="15">
-        <f t="shared" ref="O76" si="5">D76/M76</f>
+      <c r="P76" s="15">
+        <f t="shared" ref="P76" si="5">D76/N76</f>
         <v>0.25447206610922907</v>
       </c>
-      <c r="P76" s="16">
-        <v>0</v>
-      </c>
       <c r="Q76" s="16">
         <v>0</v>
       </c>
@@ -15483,21 +16066,27 @@
         <v>0</v>
       </c>
       <c r="T76" s="16">
+        <v>0</v>
+      </c>
+      <c r="U76" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U76" s="16">
-        <f>L76/M76</f>
-        <v>0</v>
-      </c>
       <c r="V76" s="16">
         <v>0</v>
       </c>
-      <c r="W76" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W76" s="16">
+        <f>M76/N76</f>
+        <v>0</v>
+      </c>
+      <c r="X76" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y76" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A77" s="10">
         <v>46280</v>
       </c>
@@ -15532,24 +16121,24 @@
       <c r="K77" s="13">
         <v>0</v>
       </c>
-      <c r="L77" s="18">
-        <v>0</v>
-      </c>
-      <c r="M77" s="14">
+      <c r="L77" s="13">
+        <v>0</v>
+      </c>
+      <c r="M77" s="18">
+        <v>0</v>
+      </c>
+      <c r="N77" s="14">
         <f t="shared" si="0"/>
         <v>406109</v>
       </c>
-      <c r="N77" s="15">
-        <f t="shared" ref="N77" si="6">C77/M77</f>
+      <c r="O77" s="15">
+        <f t="shared" ref="O77" si="6">C77/N77</f>
         <v>0.96410569576148275</v>
       </c>
-      <c r="O77" s="15">
-        <f t="shared" ref="O77" si="7">D77/M77</f>
+      <c r="P77" s="15">
+        <f t="shared" ref="P77" si="7">D77/N77</f>
         <v>3.5894304238517243E-2</v>
       </c>
-      <c r="P77" s="16">
-        <v>0</v>
-      </c>
       <c r="Q77" s="16">
         <v>0</v>
       </c>
@@ -15560,21 +16149,27 @@
         <v>0</v>
       </c>
       <c r="T77" s="16">
+        <v>0</v>
+      </c>
+      <c r="U77" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U77" s="16">
-        <f>L77/M77</f>
-        <v>0</v>
-      </c>
       <c r="V77" s="16">
         <v>0</v>
       </c>
-      <c r="W77" s="15">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="W77" s="16">
+        <f>M77/N77</f>
+        <v>0</v>
+      </c>
+      <c r="X77" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="15">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A78" s="10">
         <v>46281</v>
       </c>
@@ -15586,7 +16181,7 @@
         <v>288016</v>
       </c>
       <c r="D78" s="13">
-        <f>B78-C78-L78</f>
+        <f>B78-C78-M78</f>
         <v>35963</v>
       </c>
       <c r="E78" s="13">
@@ -15610,24 +16205,24 @@
       <c r="K78" s="13">
         <v>0</v>
       </c>
-      <c r="L78" s="18">
+      <c r="L78" s="13">
+        <v>0</v>
+      </c>
+      <c r="M78" s="18">
         <v>88000</v>
       </c>
-      <c r="M78" s="14">
+      <c r="N78" s="14">
         <f t="shared" si="0"/>
         <v>411979</v>
       </c>
-      <c r="N78" s="15">
-        <f t="shared" ref="N78" si="8">C78/M78</f>
+      <c r="O78" s="15">
+        <f t="shared" ref="O78" si="8">C78/N78</f>
         <v>0.69910359508615727</v>
       </c>
-      <c r="O78" s="15">
-        <f t="shared" ref="O78" si="9">D78/M78</f>
+      <c r="P78" s="15">
+        <f t="shared" ref="P78" si="9">D78/N78</f>
         <v>8.7293284366436158E-2</v>
       </c>
-      <c r="P78" s="16">
-        <v>0</v>
-      </c>
       <c r="Q78" s="16">
         <v>0</v>
       </c>
@@ -15638,21 +16233,27 @@
         <v>0</v>
       </c>
       <c r="T78" s="16">
+        <v>0</v>
+      </c>
+      <c r="U78" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U78" s="16">
-        <v>0</v>
-      </c>
       <c r="V78" s="16">
         <v>0</v>
       </c>
       <c r="W78" s="16">
-        <f t="shared" ref="W78:W83" si="10">L78/M78</f>
+        <v>0</v>
+      </c>
+      <c r="X78" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="16">
+        <f t="shared" ref="Y78:Y83" si="10">M78/N78</f>
         <v>0.21360312054740654</v>
       </c>
     </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A79" s="10">
         <v>46282</v>
       </c>
@@ -15663,7 +16264,7 @@
         <v>235136</v>
       </c>
       <c r="D79" s="13">
-        <f>B79-C79-L79</f>
+        <f>B79-C79-M79</f>
         <v>136527</v>
       </c>
       <c r="E79" s="13">
@@ -15687,24 +16288,24 @@
       <c r="K79" s="13">
         <v>0</v>
       </c>
-      <c r="L79" s="18">
+      <c r="L79" s="13">
+        <v>0</v>
+      </c>
+      <c r="M79" s="18">
         <v>44000</v>
       </c>
-      <c r="M79" s="14">
+      <c r="N79" s="14">
         <f t="shared" si="0"/>
         <v>415663</v>
       </c>
-      <c r="N79" s="15">
-        <f t="shared" ref="N79" si="11">C79/M79</f>
+      <c r="O79" s="15">
+        <f t="shared" ref="O79" si="11">C79/N79</f>
         <v>0.56568903173965446</v>
       </c>
-      <c r="O79" s="15">
-        <f t="shared" ref="O79" si="12">D79/M79</f>
+      <c r="P79" s="15">
+        <f t="shared" ref="P79" si="12">D79/N79</f>
         <v>0.32845598477612875</v>
       </c>
-      <c r="P79" s="16">
-        <v>0</v>
-      </c>
       <c r="Q79" s="16">
         <v>0</v>
       </c>
@@ -15715,21 +16316,27 @@
         <v>0</v>
       </c>
       <c r="T79" s="16">
+        <v>0</v>
+      </c>
+      <c r="U79" s="16">
         <f t="shared" si="3"/>
         <v>0</v>
       </c>
-      <c r="U79" s="16">
-        <v>0</v>
-      </c>
       <c r="V79" s="16">
         <v>0</v>
       </c>
       <c r="W79" s="16">
+        <v>0</v>
+      </c>
+      <c r="X79" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y79" s="16">
         <f t="shared" si="10"/>
         <v>0.10585498348421678</v>
       </c>
     </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A80" s="10">
         <v>46283</v>
       </c>
@@ -15740,7 +16347,7 @@
         <v>17795</v>
       </c>
       <c r="D80" s="13">
-        <f>B80-C80-L80</f>
+        <f>B80-C80-M80</f>
         <v>352080</v>
       </c>
       <c r="E80" s="13">
@@ -15764,24 +16371,24 @@
       <c r="K80" s="13">
         <v>0</v>
       </c>
-      <c r="L80" s="18">
+      <c r="L80" s="13">
+        <v>0</v>
+      </c>
+      <c r="M80" s="18">
         <v>44000</v>
       </c>
-      <c r="M80" s="14">
+      <c r="N80" s="14">
         <f t="shared" si="0"/>
         <v>413875</v>
       </c>
-      <c r="N80" s="15">
-        <f t="shared" ref="N80" si="13">C80/M80</f>
+      <c r="O80" s="15">
+        <f t="shared" ref="O80" si="13">C80/N80</f>
         <v>4.299607369374811E-2</v>
       </c>
-      <c r="O80" s="15">
-        <f t="shared" ref="O80" si="14">D80/M80</f>
+      <c r="P80" s="15">
+        <f t="shared" ref="P80" si="14">D80/N80</f>
         <v>0.85069163394744796</v>
       </c>
-      <c r="P80" s="16">
-        <v>0</v>
-      </c>
       <c r="Q80" s="16">
         <v>0</v>
       </c>
@@ -15792,21 +16399,27 @@
         <v>0</v>
       </c>
       <c r="T80" s="16">
-        <f t="shared" ref="T80" si="15">I80/M80</f>
         <v>0</v>
       </c>
       <c r="U80" s="16">
+        <f t="shared" ref="U80" si="15">I80/N80</f>
         <v>0</v>
       </c>
       <c r="V80" s="16">
         <v>0</v>
       </c>
       <c r="W80" s="16">
+        <v>0</v>
+      </c>
+      <c r="X80" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y80" s="16">
         <f t="shared" si="10"/>
         <v>0.10631229235880399</v>
       </c>
     </row>
-    <row r="81" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A81" s="10">
         <v>46286</v>
       </c>
@@ -15840,22 +16453,22 @@
       <c r="K81" s="13">
         <v>0</v>
       </c>
-      <c r="L81" s="18">
+      <c r="L81" s="13">
+        <v>0</v>
+      </c>
+      <c r="M81" s="18">
         <v>44000</v>
       </c>
-      <c r="M81" s="14">
+      <c r="N81" s="14">
         <f t="shared" si="0"/>
         <v>504892</v>
       </c>
-      <c r="N81" s="15">
-        <f t="shared" ref="N81" si="16">C81/M81</f>
+      <c r="O81" s="15">
+        <f t="shared" ref="O81" si="16">C81/N81</f>
         <v>0.60245359403595222</v>
       </c>
-      <c r="O81" s="15">
-        <f t="shared" ref="O81" si="17">D81/M81</f>
-        <v>0</v>
-      </c>
-      <c r="P81" s="16">
+      <c r="P81" s="15">
+        <f t="shared" ref="P81" si="17">D81/N81</f>
         <v>0</v>
       </c>
       <c r="Q81" s="16">
@@ -15868,21 +16481,27 @@
         <v>0</v>
       </c>
       <c r="T81" s="16">
-        <f t="shared" ref="T81" si="18">I81/M81</f>
+        <v>0</v>
+      </c>
+      <c r="U81" s="16">
+        <f t="shared" ref="U81" si="18">I81/N81</f>
         <v>0.31039905563962195</v>
       </c>
-      <c r="U81" s="16">
-        <v>0</v>
-      </c>
       <c r="V81" s="16">
         <v>0</v>
       </c>
       <c r="W81" s="16">
+        <v>0</v>
+      </c>
+      <c r="X81" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y81" s="16">
         <f t="shared" si="10"/>
         <v>8.7147350324425818E-2</v>
       </c>
     </row>
-    <row r="82" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A82" s="10">
         <v>46287</v>
       </c>
@@ -15893,7 +16512,7 @@
         <v>292095</v>
       </c>
       <c r="D82" s="13">
-        <f>B82-C82-L82</f>
+        <f>B82-C82-M82</f>
         <v>82294</v>
       </c>
       <c r="E82" s="13">
@@ -15917,24 +16536,24 @@
       <c r="K82" s="13">
         <v>0</v>
       </c>
-      <c r="L82" s="18">
+      <c r="L82" s="13">
+        <v>0</v>
+      </c>
+      <c r="M82" s="18">
         <v>44000</v>
       </c>
-      <c r="M82" s="14">
+      <c r="N82" s="14">
         <f t="shared" si="0"/>
         <v>418389</v>
       </c>
-      <c r="N82" s="15">
-        <f t="shared" ref="N82:N83" si="19">C82/M82</f>
+      <c r="O82" s="15">
+        <f t="shared" ref="O82:O83" si="19">C82/N82</f>
         <v>0.69814215956920478</v>
       </c>
-      <c r="O82" s="15">
-        <f t="shared" ref="O82:O83" si="20">D82/M82</f>
+      <c r="P82" s="15">
+        <f t="shared" ref="P82:P83" si="20">D82/N82</f>
         <v>0.19669255166842339</v>
       </c>
-      <c r="P82" s="16">
-        <v>0</v>
-      </c>
       <c r="Q82" s="16">
         <v>0</v>
       </c>
@@ -15945,21 +16564,27 @@
         <v>0</v>
       </c>
       <c r="T82" s="16">
-        <f t="shared" ref="T82:T83" si="21">I82/M82</f>
         <v>0</v>
       </c>
       <c r="U82" s="16">
+        <f t="shared" ref="U82:U83" si="21">I82/N82</f>
         <v>0</v>
       </c>
       <c r="V82" s="16">
         <v>0</v>
       </c>
       <c r="W82" s="16">
+        <v>0</v>
+      </c>
+      <c r="X82" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y82" s="16">
         <f t="shared" si="10"/>
         <v>0.10516528876237186</v>
       </c>
     </row>
-    <row r="83" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A83" s="10">
         <v>46288</v>
       </c>
@@ -15994,24 +16619,24 @@
       <c r="K83" s="13">
         <v>0</v>
       </c>
-      <c r="L83" s="18">
-        <v>0</v>
-      </c>
-      <c r="M83" s="14">
+      <c r="L83" s="13">
+        <v>0</v>
+      </c>
+      <c r="M83" s="18">
+        <v>0</v>
+      </c>
+      <c r="N83" s="14">
         <f t="shared" si="0"/>
         <v>415890</v>
       </c>
-      <c r="N83" s="15">
+      <c r="O83" s="15">
         <f t="shared" si="19"/>
         <v>0.13702421313328045</v>
       </c>
-      <c r="O83" s="15">
+      <c r="P83" s="15">
         <f t="shared" si="20"/>
         <v>0.77713578109596293</v>
       </c>
-      <c r="P83" s="15">
-        <v>0</v>
-      </c>
       <c r="Q83" s="15">
         <v>0</v>
       </c>
@@ -16019,25 +16644,31 @@
         <v>0</v>
       </c>
       <c r="S83" s="15">
-        <f t="shared" ref="S83:S88" si="22">H83/M83</f>
+        <v>0</v>
+      </c>
+      <c r="T83" s="15">
+        <f t="shared" ref="T83:T88" si="22">H83/N83</f>
         <v>8.5840005770756692E-2</v>
       </c>
-      <c r="T83" s="15">
+      <c r="U83" s="15">
         <f t="shared" si="21"/>
         <v>0</v>
       </c>
-      <c r="U83" s="15">
-        <v>0</v>
-      </c>
       <c r="V83" s="16">
         <v>0</v>
       </c>
       <c r="W83" s="15">
+        <v>0</v>
+      </c>
+      <c r="X83" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y83" s="15">
         <f t="shared" si="10"/>
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A84" s="10">
         <v>46289</v>
       </c>
@@ -16048,7 +16679,7 @@
         <v>72287</v>
       </c>
       <c r="D84" s="13">
-        <f>B84-C84-H84-K84</f>
+        <f>B84-C84-H84-L84</f>
         <v>291870</v>
       </c>
       <c r="E84" s="13">
@@ -16070,26 +16701,26 @@
         <v>0</v>
       </c>
       <c r="K84" s="13">
+        <v>0</v>
+      </c>
+      <c r="L84" s="13">
         <v>16220</v>
       </c>
-      <c r="L84" s="18">
-        <v>0</v>
-      </c>
-      <c r="M84" s="14">
+      <c r="M84" s="18">
+        <v>0</v>
+      </c>
+      <c r="N84" s="14">
         <f t="shared" si="0"/>
         <v>416077</v>
       </c>
-      <c r="N84" s="15">
-        <f t="shared" ref="N84" si="23">C84/M84</f>
+      <c r="O84" s="15">
+        <f t="shared" ref="O84" si="23">C84/N84</f>
         <v>0.17373466930399903</v>
       </c>
-      <c r="O84" s="15">
-        <f t="shared" ref="O84" si="24">D84/M84</f>
+      <c r="P84" s="15">
+        <f t="shared" ref="P84" si="24">D84/N84</f>
         <v>0.70148073553693191</v>
       </c>
-      <c r="P84" s="15">
-        <v>0</v>
-      </c>
       <c r="Q84" s="15">
         <v>0</v>
       </c>
@@ -16097,26 +16728,32 @@
         <v>0</v>
       </c>
       <c r="S84" s="15">
+        <v>0</v>
+      </c>
+      <c r="T84" s="15">
         <f t="shared" si="22"/>
         <v>8.5801426178327575E-2</v>
       </c>
-      <c r="T84" s="15">
-        <f t="shared" ref="T84" si="25">I84/M84</f>
-        <v>0</v>
-      </c>
       <c r="U84" s="15">
+        <f t="shared" ref="U84" si="25">I84/N84</f>
         <v>0</v>
       </c>
       <c r="V84" s="16">
-        <f t="shared" ref="V84:V89" si="26">K84/M84</f>
+        <v>0</v>
+      </c>
+      <c r="W84" s="15">
+        <v>0</v>
+      </c>
+      <c r="X84" s="16">
+        <f t="shared" ref="X84:X89" si="26">L84/N84</f>
         <v>3.8983168980741542E-2</v>
       </c>
-      <c r="W84" s="15">
-        <f t="shared" ref="W84" si="27">L84/M84</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y84" s="15">
+        <f t="shared" ref="Y84" si="27">M84/N84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A85" s="10">
         <v>46290</v>
       </c>
@@ -16127,7 +16764,7 @@
         <v>72287</v>
       </c>
       <c r="D85" s="13">
-        <f>B85-C85-H85-K85</f>
+        <f>B85-C85-H85-L85</f>
         <v>311574</v>
       </c>
       <c r="E85" s="13">
@@ -16151,24 +16788,24 @@
       <c r="K85" s="13">
         <v>0</v>
       </c>
-      <c r="L85" s="18">
-        <v>0</v>
-      </c>
-      <c r="M85" s="14">
+      <c r="L85" s="13">
+        <v>0</v>
+      </c>
+      <c r="M85" s="18">
+        <v>0</v>
+      </c>
+      <c r="N85" s="14">
         <f t="shared" si="0"/>
         <v>419561</v>
       </c>
-      <c r="N85" s="15">
-        <f t="shared" ref="N85" si="28">C85/M85</f>
+      <c r="O85" s="15">
+        <f t="shared" ref="O85" si="28">C85/N85</f>
         <v>0.17229199091431283</v>
       </c>
-      <c r="O85" s="15">
-        <f t="shared" ref="O85:O86" si="29">D85/M85</f>
+      <c r="P85" s="15">
+        <f t="shared" ref="P85:P86" si="29">D85/N85</f>
         <v>0.74261907088599755</v>
       </c>
-      <c r="P85" s="15">
-        <v>0</v>
-      </c>
       <c r="Q85" s="15">
         <v>0</v>
       </c>
@@ -16176,26 +16813,32 @@
         <v>0</v>
       </c>
       <c r="S85" s="15">
+        <v>0</v>
+      </c>
+      <c r="T85" s="15">
         <f t="shared" si="22"/>
         <v>8.508893819968967E-2</v>
       </c>
-      <c r="T85" s="15">
-        <f t="shared" ref="T85" si="30">I85/M85</f>
-        <v>0</v>
-      </c>
       <c r="U85" s="15">
+        <f t="shared" ref="U85" si="30">I85/N85</f>
         <v>0</v>
       </c>
       <c r="V85" s="16">
+        <v>0</v>
+      </c>
+      <c r="W85" s="15">
+        <v>0</v>
+      </c>
+      <c r="X85" s="16">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="W85" s="15">
-        <f t="shared" ref="W85" si="31">L85/M85</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Y85" s="15">
+        <f t="shared" ref="Y85" si="31">M85/N85</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A86" s="10">
         <v>46293</v>
       </c>
@@ -16229,24 +16872,24 @@
       <c r="K86" s="13">
         <v>0</v>
       </c>
-      <c r="L86" s="18">
+      <c r="L86" s="13">
+        <v>0</v>
+      </c>
+      <c r="M86" s="18">
         <v>41648</v>
       </c>
-      <c r="M86" s="14">
+      <c r="N86" s="14">
         <f t="shared" si="0"/>
         <v>427887</v>
       </c>
-      <c r="N86" s="15">
-        <f t="shared" ref="N86" si="32">C86/M86</f>
+      <c r="O86" s="15">
+        <f t="shared" ref="O86" si="32">C86/N86</f>
         <v>0.81923264787198491</v>
       </c>
-      <c r="O86" s="15">
+      <c r="P86" s="15">
         <f t="shared" si="29"/>
         <v>0</v>
       </c>
-      <c r="P86" s="15">
-        <v>0</v>
-      </c>
       <c r="Q86" s="15">
         <v>0</v>
       </c>
@@ -16254,26 +16897,32 @@
         <v>0</v>
       </c>
       <c r="S86" s="15">
+        <v>0</v>
+      </c>
+      <c r="T86" s="15">
         <f t="shared" si="22"/>
         <v>8.3433242888893561E-2</v>
       </c>
-      <c r="T86" s="15">
-        <f t="shared" ref="T86" si="33">I86/M86</f>
-        <v>0</v>
-      </c>
       <c r="U86" s="15">
+        <f t="shared" ref="U86" si="33">I86/N86</f>
         <v>0</v>
       </c>
       <c r="V86" s="16">
+        <v>0</v>
+      </c>
+      <c r="W86" s="15">
+        <v>0</v>
+      </c>
+      <c r="X86" s="16">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="W86" s="15">
-        <f t="shared" ref="W86" si="34">L86/M86</f>
+      <c r="Y86" s="15">
+        <f t="shared" ref="Y86" si="34">M86/N86</f>
         <v>9.7334109239121544E-2</v>
       </c>
     </row>
-    <row r="87" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A87" s="10">
         <v>46294</v>
       </c>
@@ -16307,22 +16956,22 @@
       <c r="K87" s="13">
         <v>0</v>
       </c>
-      <c r="L87" s="18">
+      <c r="L87" s="13">
+        <v>0</v>
+      </c>
+      <c r="M87" s="18">
         <v>208986</v>
       </c>
-      <c r="M87" s="14">
+      <c r="N87" s="14">
         <f t="shared" si="0"/>
         <v>610003</v>
       </c>
-      <c r="N87" s="15">
-        <f t="shared" ref="N87" si="35">C87/M87</f>
+      <c r="O87" s="15">
+        <f t="shared" ref="O87" si="35">C87/N87</f>
         <v>0.57058899710329292</v>
       </c>
-      <c r="O87" s="15">
-        <f t="shared" ref="O87" si="36">D87/M87</f>
-        <v>0</v>
-      </c>
       <c r="P87" s="15">
+        <f t="shared" ref="P87" si="36">D87/N87</f>
         <v>0</v>
       </c>
       <c r="Q87" s="15">
@@ -16332,26 +16981,32 @@
         <v>0</v>
       </c>
       <c r="S87" s="15">
+        <v>0</v>
+      </c>
+      <c r="T87" s="15">
         <f t="shared" si="22"/>
         <v>8.6812687806453417E-2</v>
       </c>
-      <c r="T87" s="15">
-        <f t="shared" ref="T87" si="37">I87/M87</f>
-        <v>0</v>
-      </c>
       <c r="U87" s="15">
+        <f t="shared" ref="U87" si="37">I87/N87</f>
         <v>0</v>
       </c>
       <c r="V87" s="16">
+        <v>0</v>
+      </c>
+      <c r="W87" s="15">
+        <v>0</v>
+      </c>
+      <c r="X87" s="16">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="W87" s="15">
-        <f t="shared" ref="W87" si="38">L87/M87</f>
+      <c r="Y87" s="15">
+        <f t="shared" ref="Y87" si="38">M87/N87</f>
         <v>0.34259831509025368</v>
       </c>
     </row>
-    <row r="88" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A88" s="10">
         <v>46295</v>
       </c>
@@ -16385,22 +17040,22 @@
       <c r="K88" s="13">
         <v>0</v>
       </c>
-      <c r="L88" s="18">
+      <c r="L88" s="13">
+        <v>0</v>
+      </c>
+      <c r="M88" s="18">
         <v>240039</v>
       </c>
-      <c r="M88" s="14">
+      <c r="N88" s="14">
         <f t="shared" si="0"/>
         <v>572683</v>
       </c>
-      <c r="N88" s="15">
-        <f t="shared" ref="N88" si="39">C88/M88</f>
+      <c r="O88" s="15">
+        <f t="shared" ref="O88" si="39">C88/N88</f>
         <v>0.4883818796786355</v>
       </c>
-      <c r="O88" s="15">
-        <f t="shared" ref="O88" si="40">D88/M88</f>
-        <v>0</v>
-      </c>
       <c r="P88" s="15">
+        <f t="shared" ref="P88" si="40">D88/N88</f>
         <v>0</v>
       </c>
       <c r="Q88" s="15">
@@ -16410,26 +17065,32 @@
         <v>0</v>
       </c>
       <c r="S88" s="15">
+        <v>0</v>
+      </c>
+      <c r="T88" s="15">
         <f t="shared" si="22"/>
         <v>9.2470005221038515E-2</v>
       </c>
-      <c r="T88" s="15">
-        <f t="shared" ref="T88" si="41">I88/M88</f>
-        <v>0</v>
-      </c>
       <c r="U88" s="15">
+        <f t="shared" ref="U88" si="41">I88/N88</f>
         <v>0</v>
       </c>
       <c r="V88" s="16">
+        <v>0</v>
+      </c>
+      <c r="W88" s="15">
+        <v>0</v>
+      </c>
+      <c r="X88" s="16">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="W88" s="15">
-        <f t="shared" ref="W88" si="42">L88/M88</f>
+      <c r="Y88" s="15">
+        <f t="shared" ref="Y88" si="42">M88/N88</f>
         <v>0.41914811510032601</v>
       </c>
     </row>
-    <row r="89" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A89" s="10">
         <v>46296</v>
       </c>
@@ -16440,7 +17101,7 @@
         <v>164387</v>
       </c>
       <c r="D89" s="13">
-        <f>B89-C89-H89-L89</f>
+        <f>B89-C89-H89-M89</f>
         <v>13084</v>
       </c>
       <c r="E89" s="13">
@@ -16464,24 +17125,24 @@
       <c r="K89" s="13">
         <v>0</v>
       </c>
-      <c r="L89" s="18">
+      <c r="L89" s="13">
+        <v>0</v>
+      </c>
+      <c r="M89" s="18">
         <v>240039</v>
       </c>
-      <c r="M89" s="14">
+      <c r="N89" s="14">
         <f t="shared" si="0"/>
         <v>417510</v>
       </c>
-      <c r="N89" s="15">
-        <f t="shared" ref="N89" si="43">C89/M89</f>
+      <c r="O89" s="15">
+        <f t="shared" ref="O89" si="43">C89/N89</f>
         <v>0.39373188666139736</v>
       </c>
-      <c r="O89" s="15">
-        <f t="shared" ref="O89" si="44">D89/M89</f>
+      <c r="P89" s="15">
+        <f t="shared" ref="P89" si="44">D89/N89</f>
         <v>3.1338171540801416E-2</v>
       </c>
-      <c r="P89" s="15">
-        <v>0</v>
-      </c>
       <c r="Q89" s="15">
         <v>0</v>
       </c>
@@ -16489,26 +17150,32 @@
         <v>0</v>
       </c>
       <c r="S89" s="15">
-        <f t="shared" ref="S89" si="45">H89/M89</f>
         <v>0</v>
       </c>
       <c r="T89" s="15">
-        <f t="shared" ref="T89" si="46">I89/M89</f>
+        <f t="shared" ref="T89" si="45">H89/N89</f>
         <v>0</v>
       </c>
       <c r="U89" s="15">
+        <f t="shared" ref="U89" si="46">I89/N89</f>
         <v>0</v>
       </c>
       <c r="V89" s="16">
+        <v>0</v>
+      </c>
+      <c r="W89" s="15">
+        <v>0</v>
+      </c>
+      <c r="X89" s="16">
         <f t="shared" si="26"/>
         <v>0</v>
       </c>
-      <c r="W89" s="15">
-        <f t="shared" ref="W89" si="47">L89/M89</f>
+      <c r="Y89" s="15">
+        <f t="shared" ref="Y89" si="47">M89/N89</f>
         <v>0.57492994179780121</v>
       </c>
     </row>
-    <row r="90" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A90" s="10">
         <v>46297</v>
       </c>
@@ -16519,7 +17186,7 @@
         <v>115219</v>
       </c>
       <c r="D90" s="13">
-        <f>B90-C90-H90-L90</f>
+        <f>B90-C90-H90-M90</f>
         <v>41258</v>
       </c>
       <c r="E90" s="13">
@@ -16543,24 +17210,24 @@
       <c r="K90" s="13">
         <v>0</v>
       </c>
-      <c r="L90" s="18">
+      <c r="L90" s="13">
+        <v>0</v>
+      </c>
+      <c r="M90" s="18">
         <v>240039</v>
       </c>
-      <c r="M90" s="14">
+      <c r="N90" s="14">
         <f t="shared" si="0"/>
         <v>414176</v>
       </c>
-      <c r="N90" s="15">
-        <f t="shared" ref="N90" si="48">C90/M90</f>
+      <c r="O90" s="15">
+        <f t="shared" ref="O90" si="48">C90/N90</f>
         <v>0.27818849957505987</v>
       </c>
-      <c r="O90" s="15">
-        <f t="shared" ref="O90" si="49">D90/M90</f>
+      <c r="P90" s="15">
+        <f t="shared" ref="P90" si="49">D90/N90</f>
         <v>9.9614656571119523E-2</v>
       </c>
-      <c r="P90" s="15">
-        <v>0</v>
-      </c>
       <c r="Q90" s="15">
         <v>0</v>
       </c>
@@ -16568,26 +17235,32 @@
         <v>0</v>
       </c>
       <c r="S90" s="15">
-        <f t="shared" ref="S90" si="50">H90/M90</f>
+        <v>0</v>
+      </c>
+      <c r="T90" s="15">
+        <f t="shared" ref="T90" si="50">H90/N90</f>
         <v>4.2638878158077723E-2</v>
       </c>
-      <c r="T90" s="15">
-        <f t="shared" ref="T90" si="51">I90/M90</f>
-        <v>0</v>
-      </c>
       <c r="U90" s="15">
+        <f t="shared" ref="U90" si="51">I90/N90</f>
         <v>0</v>
       </c>
       <c r="V90" s="16">
-        <f t="shared" ref="V90" si="52">K90/M90</f>
         <v>0</v>
       </c>
       <c r="W90" s="15">
-        <f t="shared" ref="W90" si="53">L90/M90</f>
+        <v>0</v>
+      </c>
+      <c r="X90" s="16">
+        <f t="shared" ref="X90" si="52">L90/N90</f>
+        <v>0</v>
+      </c>
+      <c r="Y90" s="15">
+        <f t="shared" ref="Y90" si="53">M90/N90</f>
         <v>0.57955796569574292</v>
       </c>
     </row>
-    <row r="91" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A91" s="10">
         <v>46300</v>
       </c>
@@ -16621,52 +17294,58 @@
       <c r="K91" s="13">
         <v>0</v>
       </c>
-      <c r="L91" s="18">
+      <c r="L91" s="13">
+        <v>0</v>
+      </c>
+      <c r="M91" s="18">
         <v>240039</v>
       </c>
-      <c r="M91" s="14">
+      <c r="N91" s="14">
         <f t="shared" si="0"/>
         <v>1885893</v>
       </c>
-      <c r="N91" s="15">
-        <f t="shared" ref="N91" si="54">C91/M91</f>
+      <c r="O91" s="15">
+        <f t="shared" ref="O91" si="54">C91/N91</f>
         <v>0.11781898548857225</v>
       </c>
-      <c r="O91" s="15">
-        <f t="shared" ref="O91" si="55">D91/M91</f>
-        <v>0</v>
-      </c>
       <c r="P91" s="15">
+        <f t="shared" ref="P91" si="55">D91/N91</f>
         <v>0</v>
       </c>
       <c r="Q91" s="15">
-        <f t="shared" ref="Q91:Q96" si="56">E91/M91</f>
+        <v>0</v>
+      </c>
+      <c r="R91" s="15">
+        <f t="shared" ref="R91:R96" si="56">E91/N91</f>
         <v>0.74553540418252784</v>
       </c>
-      <c r="R91" s="15">
-        <v>0</v>
-      </c>
       <c r="S91" s="15">
-        <f t="shared" ref="S91" si="57">H91/M91</f>
+        <v>0</v>
+      </c>
+      <c r="T91" s="15">
+        <f t="shared" ref="T91" si="57">H91/N91</f>
         <v>9.3642640383097032E-3</v>
       </c>
-      <c r="T91" s="15">
-        <f t="shared" ref="T91" si="58">I91/M91</f>
-        <v>0</v>
-      </c>
       <c r="U91" s="15">
+        <f t="shared" ref="U91" si="58">I91/N91</f>
         <v>0</v>
       </c>
       <c r="V91" s="16">
-        <f t="shared" ref="V91" si="59">K91/M91</f>
         <v>0</v>
       </c>
       <c r="W91" s="15">
-        <f t="shared" ref="W91" si="60">L91/M91</f>
+        <v>0</v>
+      </c>
+      <c r="X91" s="16">
+        <f t="shared" ref="X91" si="59">L91/N91</f>
+        <v>0</v>
+      </c>
+      <c r="Y91" s="15">
+        <f t="shared" ref="Y91" si="60">M91/N91</f>
         <v>0.12728134629059018</v>
       </c>
     </row>
-    <row r="92" spans="1:23" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A92" s="10">
         <v>46301</v>
       </c>
@@ -16677,7 +17356,7 @@
         <v>160440</v>
       </c>
       <c r="D92" s="13">
-        <f>B92-C92-H92-L92</f>
+        <f>B92-C92-H92-M92</f>
         <v>230166</v>
       </c>
       <c r="E92" s="13">
@@ -16701,52 +17380,58 @@
       <c r="K92" s="13">
         <v>0</v>
       </c>
-      <c r="L92" s="18">
-        <v>0</v>
-      </c>
-      <c r="M92" s="14">
+      <c r="L92" s="13">
+        <v>0</v>
+      </c>
+      <c r="M92" s="18">
+        <v>0</v>
+      </c>
+      <c r="N92" s="14">
         <f t="shared" si="0"/>
         <v>408266</v>
       </c>
-      <c r="N92" s="15">
-        <f t="shared" ref="N92" si="61">C92/M92</f>
+      <c r="O92" s="15">
+        <f t="shared" ref="O92" si="61">C92/N92</f>
         <v>0.3929790871637609</v>
       </c>
-      <c r="O92" s="15">
-        <f t="shared" ref="O92" si="62">D92/M92</f>
+      <c r="P92" s="15">
+        <f t="shared" ref="P92" si="62">D92/N92</f>
         <v>0.56376480039973942</v>
       </c>
-      <c r="P92" s="15">
-        <v>0</v>
-      </c>
       <c r="Q92" s="15">
+        <v>0</v>
+      </c>
+      <c r="R92" s="15">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="R92" s="15">
-        <v>0</v>
-      </c>
       <c r="S92" s="15">
-        <f t="shared" ref="S92" si="63">H92/M92</f>
+        <v>0</v>
+      </c>
+      <c r="T92" s="15">
+        <f t="shared" ref="T92" si="63">H92/N92</f>
         <v>4.3256112436499732E-2</v>
       </c>
-      <c r="T92" s="15">
-        <f t="shared" ref="T92" si="64">I92/M92</f>
-        <v>0</v>
-      </c>
       <c r="U92" s="15">
+        <f t="shared" ref="U92" si="64">I92/N92</f>
         <v>0</v>
       </c>
       <c r="V92" s="16">
-        <f t="shared" ref="V92" si="65">K92/M92</f>
         <v>0</v>
       </c>
       <c r="W92" s="15">
-        <f t="shared" ref="W92" si="66">L92/M92</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="X92" s="16">
+        <f t="shared" ref="X92" si="65">L92/N92</f>
+        <v>0</v>
+      </c>
+      <c r="Y92" s="15">
+        <f t="shared" ref="Y92" si="66">M92/N92</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A93" s="10">
         <v>46302</v>
       </c>
@@ -16780,52 +17465,58 @@
       <c r="K93" s="13">
         <v>0</v>
       </c>
-      <c r="L93" s="18">
-        <v>0</v>
-      </c>
-      <c r="M93" s="14">
+      <c r="L93" s="13">
+        <v>0</v>
+      </c>
+      <c r="M93" s="18">
+        <v>0</v>
+      </c>
+      <c r="N93" s="14">
         <f t="shared" si="0"/>
         <v>2279975</v>
       </c>
-      <c r="N93" s="15">
-        <f t="shared" ref="N93" si="67">C93/M93</f>
+      <c r="O93" s="15">
+        <f t="shared" ref="O93" si="67">C93/N93</f>
         <v>7.0369192644656187E-2</v>
       </c>
-      <c r="O93" s="15">
-        <f t="shared" ref="O93" si="68">D93/M93</f>
-        <v>0</v>
-      </c>
       <c r="P93" s="15">
+        <f t="shared" ref="P93" si="68">D93/N93</f>
         <v>0</v>
       </c>
       <c r="Q93" s="15">
+        <v>0</v>
+      </c>
+      <c r="R93" s="15">
         <f t="shared" si="56"/>
         <v>0.92188510838934634</v>
       </c>
-      <c r="R93" s="15">
-        <v>0</v>
-      </c>
       <c r="S93" s="15">
-        <f t="shared" ref="S93" si="69">H93/M93</f>
+        <v>0</v>
+      </c>
+      <c r="T93" s="15">
+        <f t="shared" ref="T93" si="69">H93/N93</f>
         <v>7.7456989659974345E-3</v>
       </c>
-      <c r="T93" s="15">
-        <f t="shared" ref="T93" si="70">I93/M93</f>
-        <v>0</v>
-      </c>
       <c r="U93" s="15">
+        <f t="shared" ref="U93" si="70">I93/N93</f>
         <v>0</v>
       </c>
       <c r="V93" s="16">
-        <f t="shared" ref="V93" si="71">K93/M93</f>
         <v>0</v>
       </c>
       <c r="W93" s="15">
-        <f t="shared" ref="W93" si="72">L93/M93</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="X93" s="16">
+        <f t="shared" ref="X93" si="71">L93/N93</f>
+        <v>0</v>
+      </c>
+      <c r="Y93" s="15">
+        <f t="shared" ref="Y93" si="72">M93/N93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A94" s="10">
         <v>46303</v>
       </c>
@@ -16836,7 +17527,7 @@
         <v>160440</v>
       </c>
       <c r="D94" s="13">
-        <f t="shared" ref="D94:D102" si="73">B94-C94-H94-L94-F94</f>
+        <f t="shared" ref="D94:D102" si="73">B94-C94-H94-M94-F94</f>
         <v>76736</v>
       </c>
       <c r="E94" s="13">
@@ -16860,53 +17551,59 @@
       <c r="K94" s="13">
         <v>0</v>
       </c>
-      <c r="L94" s="18">
-        <v>0</v>
-      </c>
-      <c r="M94" s="14">
+      <c r="L94" s="13">
+        <v>0</v>
+      </c>
+      <c r="M94" s="18">
+        <v>0</v>
+      </c>
+      <c r="N94" s="14">
         <f t="shared" si="0"/>
         <v>420025</v>
       </c>
-      <c r="N94" s="15">
-        <f t="shared" ref="N94" si="74">C94/M94</f>
+      <c r="O94" s="15">
+        <f t="shared" ref="O94" si="74">C94/N94</f>
         <v>0.38197726325813941</v>
       </c>
-      <c r="O94" s="15">
-        <f t="shared" ref="O94" si="75">D94/M94</f>
+      <c r="P94" s="15">
+        <f t="shared" ref="P94" si="75">D94/N94</f>
         <v>0.18269388726861496</v>
       </c>
-      <c r="P94" s="15">
-        <f>F94/M94</f>
+      <c r="Q94" s="15">
+        <f>F94/N94</f>
         <v>0.39328373311112436</v>
       </c>
-      <c r="Q94" s="15">
+      <c r="R94" s="15">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="R94" s="15">
-        <v>0</v>
-      </c>
       <c r="S94" s="15">
-        <f t="shared" ref="S94" si="76">H94/M94</f>
+        <v>0</v>
+      </c>
+      <c r="T94" s="15">
+        <f t="shared" ref="T94" si="76">H94/N94</f>
         <v>4.2045116362121306E-2</v>
       </c>
-      <c r="T94" s="15">
-        <f t="shared" ref="T94" si="77">I94/M94</f>
-        <v>0</v>
-      </c>
       <c r="U94" s="15">
+        <f t="shared" ref="U94" si="77">I94/N94</f>
         <v>0</v>
       </c>
       <c r="V94" s="16">
-        <f t="shared" ref="V94" si="78">K94/M94</f>
         <v>0</v>
       </c>
       <c r="W94" s="15">
-        <f t="shared" ref="W94" si="79">L94/M94</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="X94" s="16">
+        <f t="shared" ref="X94" si="78">L94/N94</f>
+        <v>0</v>
+      </c>
+      <c r="Y94" s="15">
+        <f t="shared" ref="Y94" si="79">M94/N94</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A95" s="10">
         <v>46304</v>
       </c>
@@ -16941,53 +17638,59 @@
       <c r="K95" s="13">
         <v>0</v>
       </c>
-      <c r="L95" s="18">
-        <v>0</v>
-      </c>
-      <c r="M95" s="14">
+      <c r="L95" s="13">
+        <v>0</v>
+      </c>
+      <c r="M95" s="18">
+        <v>0</v>
+      </c>
+      <c r="N95" s="14">
         <f t="shared" si="0"/>
         <v>419639</v>
       </c>
-      <c r="N95" s="15">
-        <f t="shared" ref="N95" si="80">C95/M95</f>
-        <v>0</v>
-      </c>
       <c r="O95" s="15">
-        <f t="shared" ref="O95" si="81">D95/M95</f>
+        <f t="shared" ref="O95" si="80">C95/N95</f>
+        <v>0</v>
+      </c>
+      <c r="P95" s="15">
+        <f t="shared" ref="P95" si="81">D95/N95</f>
         <v>0.56427071840319898</v>
       </c>
-      <c r="P95" s="15">
-        <f>F95/M95</f>
+      <c r="Q95" s="15">
+        <f>F95/N95</f>
         <v>0.39364549052876402</v>
       </c>
-      <c r="Q95" s="15">
+      <c r="R95" s="15">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="R95" s="15">
-        <v>0</v>
-      </c>
       <c r="S95" s="15">
-        <f t="shared" ref="S95" si="82">H95/M95</f>
+        <v>0</v>
+      </c>
+      <c r="T95" s="15">
+        <f t="shared" ref="T95" si="82">H95/N95</f>
         <v>4.2083791068037051E-2</v>
       </c>
-      <c r="T95" s="15">
-        <f t="shared" ref="T95" si="83">I95/M95</f>
-        <v>0</v>
-      </c>
       <c r="U95" s="15">
+        <f t="shared" ref="U95" si="83">I95/N95</f>
         <v>0</v>
       </c>
       <c r="V95" s="16">
-        <f t="shared" ref="V95" si="84">K95/M95</f>
         <v>0</v>
       </c>
       <c r="W95" s="15">
-        <f t="shared" ref="W95" si="85">L95/M95</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="X95" s="16">
+        <f t="shared" ref="X95" si="84">L95/N95</f>
+        <v>0</v>
+      </c>
+      <c r="Y95" s="15">
+        <f t="shared" ref="Y95" si="85">M95/N95</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A96" s="10">
         <v>46307</v>
       </c>
@@ -17022,53 +17725,59 @@
       <c r="K96" s="13">
         <v>0</v>
       </c>
-      <c r="L96" s="18">
-        <v>0</v>
-      </c>
-      <c r="M96" s="14">
+      <c r="L96" s="13">
+        <v>0</v>
+      </c>
+      <c r="M96" s="18">
+        <v>0</v>
+      </c>
+      <c r="N96" s="14">
         <f t="shared" si="0"/>
         <v>418610</v>
       </c>
-      <c r="N96" s="15">
-        <f t="shared" ref="N96" si="86">C96/M96</f>
-        <v>0</v>
-      </c>
       <c r="O96" s="15">
-        <f t="shared" ref="O96" si="87">D96/M96</f>
+        <f t="shared" ref="O96" si="86">C96/N96</f>
+        <v>0</v>
+      </c>
+      <c r="P96" s="15">
+        <f t="shared" ref="P96" si="87">D96/N96</f>
         <v>0.54257184491531496</v>
       </c>
-      <c r="P96" s="15">
-        <f>F96/M96</f>
+      <c r="Q96" s="15">
+        <f>F96/N96</f>
         <v>0.39461312438785506</v>
       </c>
-      <c r="Q96" s="15">
+      <c r="R96" s="15">
         <f t="shared" si="56"/>
         <v>0</v>
       </c>
-      <c r="R96" s="15">
-        <v>0</v>
-      </c>
       <c r="S96" s="15">
-        <f t="shared" ref="S96" si="88">H96/M96</f>
+        <v>0</v>
+      </c>
+      <c r="T96" s="15">
+        <f t="shared" ref="T96" si="88">H96/N96</f>
         <v>6.281503069682999E-2</v>
       </c>
-      <c r="T96" s="15">
-        <f t="shared" ref="T96" si="89">I96/M96</f>
-        <v>0</v>
-      </c>
       <c r="U96" s="15">
+        <f t="shared" ref="U96" si="89">I96/N96</f>
         <v>0</v>
       </c>
       <c r="V96" s="16">
-        <f t="shared" ref="V96" si="90">K96/M96</f>
         <v>0</v>
       </c>
       <c r="W96" s="15">
-        <f t="shared" ref="W96" si="91">L96/M96</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="X96" s="16">
+        <f t="shared" ref="X96" si="90">L96/N96</f>
+        <v>0</v>
+      </c>
+      <c r="Y96" s="15">
+        <f t="shared" ref="Y96" si="91">M96/N96</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A97" s="10">
         <v>46308</v>
       </c>
@@ -17103,53 +17812,59 @@
       <c r="K97" s="13">
         <v>0</v>
       </c>
-      <c r="L97" s="18">
-        <v>0</v>
-      </c>
-      <c r="M97" s="14">
+      <c r="L97" s="13">
+        <v>0</v>
+      </c>
+      <c r="M97" s="18">
+        <v>0</v>
+      </c>
+      <c r="N97" s="14">
         <f t="shared" si="0"/>
         <v>418740</v>
       </c>
-      <c r="N97" s="15">
-        <f t="shared" ref="N97" si="92">C97/M97</f>
-        <v>0</v>
-      </c>
       <c r="O97" s="15">
-        <f t="shared" ref="O97" si="93">D97/M97</f>
+        <f t="shared" ref="O97" si="92">C97/N97</f>
+        <v>0</v>
+      </c>
+      <c r="P97" s="15">
+        <f t="shared" ref="P97" si="93">D97/N97</f>
         <v>0.54271385585327414</v>
       </c>
-      <c r="P97" s="15">
-        <f>F97/M97</f>
+      <c r="Q97" s="15">
+        <f>F97/N97</f>
         <v>0.39449061470124658</v>
       </c>
-      <c r="Q97" s="15">
-        <f t="shared" ref="Q97" si="94">E97/M97</f>
-        <v>0</v>
-      </c>
       <c r="R97" s="15">
+        <f t="shared" ref="R97" si="94">E97/N97</f>
         <v>0</v>
       </c>
       <c r="S97" s="15">
-        <f t="shared" ref="S97" si="95">H97/M97</f>
+        <v>0</v>
+      </c>
+      <c r="T97" s="15">
+        <f t="shared" ref="T97" si="95">H97/N97</f>
         <v>6.2795529445479295E-2</v>
       </c>
-      <c r="T97" s="15">
-        <f t="shared" ref="T97" si="96">I97/M97</f>
-        <v>0</v>
-      </c>
       <c r="U97" s="15">
+        <f t="shared" ref="U97" si="96">I97/N97</f>
         <v>0</v>
       </c>
       <c r="V97" s="16">
-        <f t="shared" ref="V97" si="97">K97/M97</f>
         <v>0</v>
       </c>
       <c r="W97" s="15">
-        <f t="shared" ref="W97" si="98">L97/M97</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="X97" s="16">
+        <f t="shared" ref="X97" si="97">L97/N97</f>
+        <v>0</v>
+      </c>
+      <c r="Y97" s="15">
+        <f t="shared" ref="Y97" si="98">M97/N97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A98" s="10">
         <v>46309</v>
       </c>
@@ -17184,53 +17899,59 @@
       <c r="K98" s="13">
         <v>0</v>
       </c>
-      <c r="L98" s="18">
-        <v>0</v>
-      </c>
-      <c r="M98" s="14">
+      <c r="L98" s="13">
+        <v>0</v>
+      </c>
+      <c r="M98" s="18">
+        <v>0</v>
+      </c>
+      <c r="N98" s="14">
         <f t="shared" si="0"/>
         <v>421826</v>
       </c>
-      <c r="N98" s="15">
-        <f t="shared" ref="N98" si="99">C98/M98</f>
-        <v>0</v>
-      </c>
       <c r="O98" s="15">
-        <f t="shared" ref="O98:O99" si="100">D98/M98</f>
+        <f t="shared" ref="O98" si="99">C98/N98</f>
+        <v>0</v>
+      </c>
+      <c r="P98" s="15">
+        <f t="shared" ref="P98:P99" si="100">D98/N98</f>
         <v>0.32961695106513111</v>
       </c>
-      <c r="P98" s="15">
-        <f>F98/M98</f>
+      <c r="Q98" s="15">
+        <f>F98/N98</f>
         <v>0.60804691982002057</v>
       </c>
-      <c r="Q98" s="15">
-        <f t="shared" ref="Q98" si="101">E98/M98</f>
-        <v>0</v>
-      </c>
       <c r="R98" s="15">
+        <f t="shared" ref="R98" si="101">E98/N98</f>
         <v>0</v>
       </c>
       <c r="S98" s="15">
-        <f t="shared" ref="S98" si="102">H98/M98</f>
+        <v>0</v>
+      </c>
+      <c r="T98" s="15">
+        <f t="shared" ref="T98" si="102">H98/N98</f>
         <v>6.2336129114848302E-2</v>
       </c>
-      <c r="T98" s="15">
-        <f t="shared" ref="T98" si="103">I98/M98</f>
-        <v>0</v>
-      </c>
       <c r="U98" s="15">
+        <f t="shared" ref="U98" si="103">I98/N98</f>
         <v>0</v>
       </c>
       <c r="V98" s="16">
-        <f t="shared" ref="V98" si="104">K98/M98</f>
         <v>0</v>
       </c>
       <c r="W98" s="15">
-        <f t="shared" ref="W98" si="105">L98/M98</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="X98" s="16">
+        <f t="shared" ref="X98" si="104">L98/N98</f>
+        <v>0</v>
+      </c>
+      <c r="Y98" s="15">
+        <f t="shared" ref="Y98" si="105">M98/N98</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A99" s="10">
         <v>46310</v>
       </c>
@@ -17265,52 +17986,58 @@
       <c r="K99" s="13">
         <v>0</v>
       </c>
-      <c r="L99" s="18">
-        <v>0</v>
-      </c>
-      <c r="M99" s="14">
+      <c r="L99" s="13">
+        <v>0</v>
+      </c>
+      <c r="M99" s="18">
+        <v>0</v>
+      </c>
+      <c r="N99" s="14">
         <f t="shared" si="0"/>
         <v>422979</v>
       </c>
-      <c r="N99" s="15">
-        <f t="shared" ref="N99" si="106">C99/M99</f>
+      <c r="O99" s="15">
+        <f t="shared" ref="O99" si="106">C99/N99</f>
         <v>0.33346099924582545</v>
       </c>
-      <c r="O99" s="15">
+      <c r="P99" s="15">
         <f t="shared" si="100"/>
         <v>0.6665390007541746</v>
       </c>
-      <c r="P99" s="15">
-        <f t="shared" ref="P99" si="107">E99/N99</f>
-        <v>0</v>
-      </c>
       <c r="Q99" s="15">
-        <f t="shared" ref="Q99" si="108">E99/M99</f>
+        <f t="shared" ref="Q99" si="107">E99/O99</f>
         <v>0</v>
       </c>
       <c r="R99" s="15">
+        <f t="shared" ref="R99" si="108">E99/N99</f>
         <v>0</v>
       </c>
       <c r="S99" s="15">
         <v>0</v>
       </c>
       <c r="T99" s="15">
-        <f t="shared" ref="T99" si="109">I99/M99</f>
         <v>0</v>
       </c>
       <c r="U99" s="15">
+        <f t="shared" ref="U99" si="109">I99/N99</f>
         <v>0</v>
       </c>
       <c r="V99" s="16">
-        <f t="shared" ref="V99" si="110">K99/M99</f>
         <v>0</v>
       </c>
       <c r="W99" s="15">
-        <f t="shared" ref="W99" si="111">L99/M99</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="X99" s="16">
+        <f t="shared" ref="X99" si="110">L99/N99</f>
+        <v>0</v>
+      </c>
+      <c r="Y99" s="15">
+        <f t="shared" ref="Y99" si="111">M99/N99</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A100" s="10">
         <v>46311</v>
       </c>
@@ -17345,52 +18072,58 @@
       <c r="K100" s="13">
         <v>0</v>
       </c>
-      <c r="L100" s="18">
-        <v>0</v>
-      </c>
-      <c r="M100" s="14">
+      <c r="L100" s="13">
+        <v>0</v>
+      </c>
+      <c r="M100" s="18">
+        <v>0</v>
+      </c>
+      <c r="N100" s="14">
         <f t="shared" si="0"/>
         <v>424623</v>
       </c>
-      <c r="N100" s="15">
-        <f t="shared" ref="N100" si="112">C100/M100</f>
+      <c r="O100" s="15">
+        <f t="shared" ref="O100" si="112">C100/N100</f>
         <v>0.5304587834384854</v>
       </c>
-      <c r="O100" s="15">
-        <f t="shared" ref="O100" si="113">D100/M100</f>
+      <c r="P100" s="15">
+        <f t="shared" ref="P100" si="113">D100/N100</f>
         <v>0.46954121656151454</v>
       </c>
-      <c r="P100" s="15">
-        <f t="shared" ref="P100" si="114">E100/N100</f>
-        <v>0</v>
-      </c>
       <c r="Q100" s="15">
-        <f t="shared" ref="Q100" si="115">E100/M100</f>
+        <f t="shared" ref="Q100" si="114">E100/O100</f>
         <v>0</v>
       </c>
       <c r="R100" s="15">
+        <f t="shared" ref="R100" si="115">E100/N100</f>
         <v>0</v>
       </c>
       <c r="S100" s="15">
         <v>0</v>
       </c>
       <c r="T100" s="15">
-        <f t="shared" ref="T100" si="116">I100/M100</f>
         <v>0</v>
       </c>
       <c r="U100" s="15">
+        <f t="shared" ref="U100" si="116">I100/N100</f>
         <v>0</v>
       </c>
       <c r="V100" s="16">
-        <f t="shared" ref="V100" si="117">K100/M100</f>
         <v>0</v>
       </c>
       <c r="W100" s="15">
-        <f t="shared" ref="W100" si="118">L100/M100</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="X100" s="16">
+        <f t="shared" ref="X100" si="117">L100/N100</f>
+        <v>0</v>
+      </c>
+      <c r="Y100" s="15">
+        <f t="shared" ref="Y100" si="118">M100/N100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A101" s="10">
         <v>46314</v>
       </c>
@@ -17425,52 +18158,58 @@
       <c r="K101" s="13">
         <v>0</v>
       </c>
-      <c r="L101" s="18">
-        <v>0</v>
-      </c>
-      <c r="M101" s="14">
+      <c r="L101" s="13">
+        <v>0</v>
+      </c>
+      <c r="M101" s="18">
+        <v>0</v>
+      </c>
+      <c r="N101" s="14">
         <f t="shared" si="0"/>
         <v>425296</v>
       </c>
-      <c r="N101" s="15">
-        <f t="shared" ref="N101" si="119">C101/M101</f>
+      <c r="O101" s="15">
+        <f t="shared" ref="O101" si="119">C101/N101</f>
         <v>8.1016515556224369E-2</v>
       </c>
-      <c r="O101" s="15">
-        <f t="shared" ref="O101" si="120">D101/M101</f>
+      <c r="P101" s="15">
+        <f t="shared" ref="P101" si="120">D101/N101</f>
         <v>0.91898348444377564</v>
       </c>
-      <c r="P101" s="15">
-        <f t="shared" ref="P101" si="121">E101/N101</f>
-        <v>0</v>
-      </c>
       <c r="Q101" s="15">
-        <f t="shared" ref="Q101" si="122">E101/M101</f>
+        <f t="shared" ref="Q101" si="121">E101/O101</f>
         <v>0</v>
       </c>
       <c r="R101" s="15">
+        <f t="shared" ref="R101" si="122">E101/N101</f>
         <v>0</v>
       </c>
       <c r="S101" s="15">
         <v>0</v>
       </c>
       <c r="T101" s="15">
-        <f t="shared" ref="T101" si="123">I101/M101</f>
         <v>0</v>
       </c>
       <c r="U101" s="15">
+        <f t="shared" ref="U101" si="123">I101/N101</f>
         <v>0</v>
       </c>
       <c r="V101" s="16">
-        <f t="shared" ref="V101" si="124">K101/M101</f>
         <v>0</v>
       </c>
       <c r="W101" s="15">
-        <f t="shared" ref="W101" si="125">L101/M101</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:23" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+      <c r="X101" s="16">
+        <f t="shared" ref="X101" si="124">L101/N101</f>
+        <v>0</v>
+      </c>
+      <c r="Y101" s="15">
+        <f t="shared" ref="Y101" si="125">M101/N101</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
       <c r="A102" s="10">
         <v>46315</v>
       </c>
@@ -17505,60 +18244,154 @@
       <c r="K102" s="13">
         <v>0</v>
       </c>
-      <c r="L102" s="18">
-        <v>0</v>
-      </c>
-      <c r="M102" s="14">
+      <c r="L102" s="13">
+        <v>0</v>
+      </c>
+      <c r="M102" s="18">
+        <v>0</v>
+      </c>
+      <c r="N102" s="14">
         <f t="shared" si="0"/>
         <v>423806</v>
       </c>
-      <c r="N102" s="15">
-        <f t="shared" ref="N102" si="126">C102/M102</f>
+      <c r="O102" s="15">
+        <f t="shared" ref="O102" si="126">C102/N102</f>
         <v>0.50963412504778127</v>
       </c>
-      <c r="O102" s="15">
-        <f t="shared" ref="O102" si="127">D102/M102</f>
+      <c r="P102" s="15">
+        <f t="shared" ref="P102" si="127">D102/N102</f>
         <v>0.49036587495221873</v>
       </c>
-      <c r="P102" s="15">
-        <f t="shared" ref="P102" si="128">E102/N102</f>
-        <v>0</v>
-      </c>
       <c r="Q102" s="15">
-        <f t="shared" ref="Q102" si="129">E102/M102</f>
+        <f t="shared" ref="Q102" si="128">E102/O102</f>
         <v>0</v>
       </c>
       <c r="R102" s="15">
+        <f t="shared" ref="R102" si="129">E102/N102</f>
         <v>0</v>
       </c>
       <c r="S102" s="15">
         <v>0</v>
       </c>
       <c r="T102" s="15">
-        <f t="shared" ref="T102" si="130">I102/M102</f>
         <v>0</v>
       </c>
       <c r="U102" s="15">
+        <f t="shared" ref="U102" si="130">I102/N102</f>
         <v>0</v>
       </c>
       <c r="V102" s="16">
-        <f t="shared" ref="V102" si="131">K102/M102</f>
         <v>0</v>
       </c>
       <c r="W102" s="15">
-        <f t="shared" ref="W102" si="132">L102/M102</f>
+        <v>0</v>
+      </c>
+      <c r="X102" s="16">
+        <f t="shared" ref="X102" si="131">L102/N102</f>
+        <v>0</v>
+      </c>
+      <c r="Y102" s="15">
+        <f t="shared" ref="Y102" si="132">M102/N102</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A103" s="10">
+        <v>46316</v>
+      </c>
+      <c r="B103" s="11">
+        <v>424792</v>
+      </c>
+      <c r="C103" s="19">
+        <v>118964</v>
+      </c>
+      <c r="D103" s="13">
+        <f>B103-C103-J103-M103-F103</f>
+        <v>293328</v>
+      </c>
+      <c r="E103" s="13">
+        <v>0</v>
+      </c>
+      <c r="F103" s="13">
+        <v>0</v>
+      </c>
+      <c r="G103" s="13">
+        <v>0</v>
+      </c>
+      <c r="H103" s="13">
+        <v>0</v>
+      </c>
+      <c r="I103" s="13">
+        <v>0</v>
+      </c>
+      <c r="J103" s="13">
+        <v>12500</v>
+      </c>
+      <c r="K103" s="13">
+        <v>0</v>
+      </c>
+      <c r="L103" s="13">
+        <v>0</v>
+      </c>
+      <c r="M103" s="18">
+        <v>0</v>
+      </c>
+      <c r="N103" s="14">
+        <f t="shared" si="0"/>
+        <v>424792</v>
+      </c>
+      <c r="O103" s="15">
+        <f t="shared" ref="O103" si="133">C103/N103</f>
+        <v>0.28005235503493475</v>
+      </c>
+      <c r="P103" s="15">
+        <f t="shared" ref="P103" si="134">D103/N103</f>
+        <v>0.69052147874724568</v>
+      </c>
+      <c r="Q103" s="15">
+        <f t="shared" ref="Q103" si="135">E103/O103</f>
+        <v>0</v>
+      </c>
+      <c r="R103" s="15">
+        <f t="shared" ref="R103" si="136">E103/N103</f>
+        <v>0</v>
+      </c>
+      <c r="S103" s="15">
+        <v>0</v>
+      </c>
+      <c r="T103" s="15">
+        <v>0</v>
+      </c>
+      <c r="U103" s="15">
+        <f t="shared" ref="U103" si="137">I103/N103</f>
+        <v>0</v>
+      </c>
+      <c r="V103" s="16">
+        <f>J103/N103</f>
+        <v>2.9426166217819544E-2</v>
+      </c>
+      <c r="W103" s="15">
+        <v>0</v>
+      </c>
+      <c r="X103" s="16">
+        <f t="shared" ref="X103" si="138">L103/N103</f>
+        <v>0</v>
+      </c>
+      <c r="Y103" s="15">
+        <f t="shared" ref="Y103" si="139">M103/N103</f>
         <v>0</v>
       </c>
     </row>
     <row r="1048543" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1048543" s="10"/>
     </row>
-    <row r="1048576" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1048576" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1048576" s="10"/>
-      <c r="M1048576" s="14"/>
+      <c r="D1048576" s="13"/>
+      <c r="N1048576" s="14"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="N2:W1048576">
+  <conditionalFormatting sqref="O2:Y1048576">
     <cfRule type="cellIs" dxfId="0" priority="1" operator="greaterThan">
       <formula>0</formula>
     </cfRule>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B42079BE-908C-0045-8E16-9DE54A54C089}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{B38C7DAB-9DB5-4F46-9AEA-1308F28CAAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1720" yWindow="-27160" windowWidth="43440" windowHeight="23120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2100" yWindow="-26980" windowWidth="43440" windowHeight="23120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1101" uniqueCount="764">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="760">
   <si>
     <t>Trade ID</t>
   </si>
@@ -264,9 +264,6 @@
     <t>iShares MSCI Mid-Cap Developed Mkt Equities ETF</t>
   </si>
   <si>
-    <t>OPEN</t>
-  </si>
-  <si>
     <t>XAI</t>
   </si>
   <si>
@@ -2343,19 +2340,10 @@
     <t>Toronto Dominion Bank</t>
   </si>
   <si>
-    <t>YW</t>
-  </si>
-  <si>
-    <t>wheat</t>
-  </si>
-  <si>
-    <t>Wheat Futures</t>
-  </si>
-  <si>
-    <t>Wheat (+)</t>
-  </si>
-  <si>
     <t>Agricultural_Exposure</t>
+  </si>
+  <si>
+    <t>Gold (+)</t>
   </si>
 </sst>
 </file>
@@ -2443,7 +2431,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2465,12 +2453,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="1"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2505,85 +2487,85 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="59">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="3" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="3" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="5" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="5" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="3" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="3" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="4" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="6" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="3" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="10" fontId="0" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="14" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="10" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2593,34 +2575,34 @@
     <xf numFmtId="1" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="3" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="10" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="3" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="3" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="3" fontId="10" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -2632,43 +2614,25 @@
     <xf numFmtId="3" fontId="11" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="1" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="10" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="9" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="10" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="7" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -2997,7 +2961,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="21" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="14" style="50" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="14" style="47" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="16.5" style="46" customWidth="1"/>
     <col min="5" max="5" width="9" style="33" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="11.1640625" style="33" bestFit="1" customWidth="1"/>
@@ -3017,7 +2981,7 @@
     <col min="23" max="23" width="14.83203125" style="33" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="6" style="33" bestFit="1" customWidth="1"/>
     <col min="25" max="25" width="18.5" style="33" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="23.33203125" style="58" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="23.33203125" style="52" bestFit="1" customWidth="1"/>
     <col min="27" max="16384" width="9.1640625" style="33"/>
   </cols>
   <sheetData>
@@ -3038,7 +3002,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="30" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G1" s="30" t="s">
         <v>5</v>
@@ -3047,7 +3011,7 @@
         <v>6</v>
       </c>
       <c r="I1" s="30" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="J1" s="30" t="s">
         <v>7</v>
@@ -3092,10 +3056,10 @@
         <v>19</v>
       </c>
       <c r="Y1" s="30" t="s">
+        <v>749</v>
+      </c>
+      <c r="Z1" s="51" t="s">
         <v>750</v>
-      </c>
-      <c r="Z1" s="57" t="s">
-        <v>751</v>
       </c>
     </row>
     <row r="2" spans="1:26" x14ac:dyDescent="0.25">
@@ -3116,7 +3080,7 @@
         <v>20</v>
       </c>
       <c r="F2" s="33" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G2" s="36" t="s">
         <v>21</v>
@@ -3125,7 +3089,7 @@
         <v>22</v>
       </c>
       <c r="I2" s="38" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="J2" s="37" t="s">
         <v>23</v>
@@ -3191,7 +3155,7 @@
         <v>24</v>
       </c>
       <c r="F3" s="37" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G3" s="38" t="s">
         <v>25</v>
@@ -3200,7 +3164,7 @@
         <v>22</v>
       </c>
       <c r="I3" s="38" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="J3" s="37" t="s">
         <v>23</v>
@@ -3265,7 +3229,7 @@
         <v>26</v>
       </c>
       <c r="F4" s="33" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G4" s="36" t="s">
         <v>27</v>
@@ -3274,13 +3238,13 @@
         <v>28</v>
       </c>
       <c r="I4" s="36" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="J4" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K4" s="33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L4" s="33" t="s">
         <v>30</v>
@@ -3340,7 +3304,7 @@
         <v>31</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G5" s="36" t="s">
         <v>32</v>
@@ -3349,13 +3313,13 @@
         <v>22</v>
       </c>
       <c r="I5" s="38" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J5" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K5" s="33" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L5" s="33" t="s">
         <v>31</v>
@@ -3414,7 +3378,7 @@
         <v>33</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G6" s="36" t="s">
         <v>34</v>
@@ -3423,13 +3387,13 @@
         <v>28</v>
       </c>
       <c r="I6" s="36" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="J6" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K6" s="33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L6" s="33" t="s">
         <v>35</v>
@@ -3489,7 +3453,7 @@
         <v>36</v>
       </c>
       <c r="F7" s="33" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="G7" s="36" t="s">
         <v>37</v>
@@ -3498,13 +3462,13 @@
         <v>22</v>
       </c>
       <c r="I7" s="38" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="J7" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K7" s="33" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L7" s="33" t="s">
         <v>38</v>
@@ -3561,10 +3525,10 @@
         <v>11</v>
       </c>
       <c r="E8" s="33" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="F8" s="33" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="G8" s="36" t="s">
         <v>39</v>
@@ -3573,13 +3537,13 @@
         <v>22</v>
       </c>
       <c r="I8" s="38" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="J8" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K8" s="33" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L8" s="33" t="s">
         <v>40</v>
@@ -3639,7 +3603,7 @@
         <v>41</v>
       </c>
       <c r="F9" s="37" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="G9" s="38" t="s">
         <v>42</v>
@@ -3648,7 +3612,7 @@
         <v>28</v>
       </c>
       <c r="I9" s="38" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="J9" s="37" t="s">
         <v>43</v>
@@ -3713,7 +3677,7 @@
         <v>44</v>
       </c>
       <c r="F10" s="37" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="G10" s="38" t="s">
         <v>45</v>
@@ -3722,7 +3686,7 @@
         <v>28</v>
       </c>
       <c r="I10" s="38" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="J10" s="37" t="s">
         <v>43</v>
@@ -3787,7 +3751,7 @@
         <v>46</v>
       </c>
       <c r="F11" s="33" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G11" s="36" t="s">
         <v>47</v>
@@ -3796,13 +3760,13 @@
         <v>28</v>
       </c>
       <c r="I11" s="36" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="J11" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K11" s="33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L11" s="33" t="s">
         <v>48</v>
@@ -3862,7 +3826,7 @@
         <v>49</v>
       </c>
       <c r="F12" s="37" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="G12" s="38" t="s">
         <v>50</v>
@@ -3871,7 +3835,7 @@
         <v>22</v>
       </c>
       <c r="I12" s="38" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="J12" s="37" t="s">
         <v>43</v>
@@ -3936,7 +3900,7 @@
         <v>51</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G13" s="38" t="s">
         <v>52</v>
@@ -3945,7 +3909,7 @@
         <v>22</v>
       </c>
       <c r="I13" s="38" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="J13" s="37" t="s">
         <v>23</v>
@@ -4011,22 +3975,22 @@
         <v>53</v>
       </c>
       <c r="F14" s="33" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G14" s="36" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H14" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I14" s="38" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="J14" s="37" t="s">
         <v>29</v>
       </c>
       <c r="K14" s="37" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L14" s="33" t="s">
         <v>54</v>
@@ -4085,7 +4049,7 @@
         <v>55</v>
       </c>
       <c r="F15" s="33" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="G15" s="36" t="s">
         <v>56</v>
@@ -4094,13 +4058,13 @@
         <v>22</v>
       </c>
       <c r="I15" s="38" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="J15" s="37" t="s">
         <v>29</v>
       </c>
       <c r="K15" s="37" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L15" s="33" t="s">
         <v>57</v>
@@ -4160,7 +4124,7 @@
         <v>58</v>
       </c>
       <c r="F16" s="37" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="G16" s="38" t="s">
         <v>59</v>
@@ -4169,7 +4133,7 @@
         <v>22</v>
       </c>
       <c r="I16" s="38" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="J16" s="37" t="s">
         <v>23</v>
@@ -4235,7 +4199,7 @@
         <v>60</v>
       </c>
       <c r="F17" s="33" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="G17" s="36" t="s">
         <v>61</v>
@@ -4244,7 +4208,7 @@
         <v>22</v>
       </c>
       <c r="I17" s="36" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="J17" s="33" t="s">
         <v>23</v>
@@ -4310,7 +4274,7 @@
         <v>62</v>
       </c>
       <c r="F18" s="33" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="G18" s="36" t="s">
         <v>63</v>
@@ -4319,7 +4283,7 @@
         <v>22</v>
       </c>
       <c r="I18" s="36" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="J18" s="33" t="s">
         <v>23</v>
@@ -4385,7 +4349,7 @@
         <v>64</v>
       </c>
       <c r="F19" s="33" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="G19" s="36" t="s">
         <v>65</v>
@@ -4394,7 +4358,7 @@
         <v>22</v>
       </c>
       <c r="I19" s="36" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="J19" s="33" t="s">
         <v>43</v>
@@ -4456,28 +4420,28 @@
         <v>10</v>
       </c>
       <c r="E20" s="33" t="s">
+        <v>66</v>
+      </c>
+      <c r="F20" s="33" t="s">
+        <v>705</v>
+      </c>
+      <c r="G20" s="36" t="s">
         <v>67</v>
-      </c>
-      <c r="F20" s="33" t="s">
-        <v>706</v>
-      </c>
-      <c r="G20" s="36" t="s">
-        <v>68</v>
       </c>
       <c r="H20" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I20" s="36" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="J20" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K20" s="33" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="L20" s="33" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="M20" s="33">
         <v>-5</v>
@@ -4530,19 +4494,19 @@
         <v>13</v>
       </c>
       <c r="E21" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>706</v>
+      </c>
+      <c r="G21" s="36" t="s">
         <v>70</v>
-      </c>
-      <c r="F21" s="33" t="s">
-        <v>707</v>
-      </c>
-      <c r="G21" s="36" t="s">
-        <v>71</v>
       </c>
       <c r="H21" s="33" t="s">
         <v>28</v>
       </c>
       <c r="I21" s="36" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="J21" s="33" t="s">
         <v>43</v>
@@ -4551,7 +4515,7 @@
         <v>43</v>
       </c>
       <c r="L21" s="33" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="M21" s="33">
         <v>2000</v>
@@ -4604,28 +4568,28 @@
         <v>13</v>
       </c>
       <c r="E22" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F22" s="33" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="G22" s="36" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H22" s="33" t="s">
         <v>28</v>
       </c>
       <c r="I22" s="36" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="J22" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K22" s="33" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L22" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M22" s="33">
         <v>-4</v>
@@ -4678,28 +4642,28 @@
         <v>0</v>
       </c>
       <c r="E23" s="33" t="s">
+        <v>72</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>708</v>
+      </c>
+      <c r="G23" s="36" t="s">
         <v>73</v>
-      </c>
-      <c r="F23" s="33" t="s">
-        <v>709</v>
-      </c>
-      <c r="G23" s="36" t="s">
-        <v>74</v>
       </c>
       <c r="H23" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I23" s="36" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="J23" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K23" s="33" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="L23" s="33" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="M23" s="33">
         <v>-10</v>
@@ -4755,7 +4719,7 @@
         <v>31</v>
       </c>
       <c r="F24" s="33" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G24" s="36" t="s">
         <v>32</v>
@@ -4764,16 +4728,16 @@
         <v>22</v>
       </c>
       <c r="I24" s="36" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="J24" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K24" s="33" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L24" s="33" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="M24" s="33">
         <v>-10</v>
@@ -4825,28 +4789,28 @@
         <v>2</v>
       </c>
       <c r="E25" s="33" t="s">
+        <v>76</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>709</v>
+      </c>
+      <c r="G25" s="36" t="s">
         <v>77</v>
-      </c>
-      <c r="F25" s="33" t="s">
-        <v>710</v>
-      </c>
-      <c r="G25" s="36" t="s">
-        <v>78</v>
       </c>
       <c r="H25" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I25" s="36" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="J25" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K25" s="33" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L25" s="33" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="M25" s="33">
         <v>-6</v>
@@ -4899,10 +4863,10 @@
         <v>1</v>
       </c>
       <c r="E26" s="33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F26" s="33" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G26" s="36" t="s">
         <v>47</v>
@@ -4911,16 +4875,16 @@
         <v>22</v>
       </c>
       <c r="I26" s="36" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="J26" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K26" s="33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L26" s="33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M26" s="33">
         <v>-3</v>
@@ -4972,19 +4936,19 @@
         <v>0</v>
       </c>
       <c r="E27" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>710</v>
+      </c>
+      <c r="G27" s="36" t="s">
         <v>82</v>
-      </c>
-      <c r="F27" s="33" t="s">
-        <v>711</v>
-      </c>
-      <c r="G27" s="36" t="s">
-        <v>83</v>
       </c>
       <c r="H27" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I27" s="36" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="J27" s="33" t="s">
         <v>23</v>
@@ -4993,7 +4957,7 @@
         <v>23</v>
       </c>
       <c r="L27" s="33" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="M27" s="33">
         <v>-1000</v>
@@ -5046,19 +5010,19 @@
         <v>1</v>
       </c>
       <c r="E28" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" s="33" t="s">
+        <v>711</v>
+      </c>
+      <c r="G28" s="36" t="s">
         <v>84</v>
-      </c>
-      <c r="F28" s="33" t="s">
-        <v>712</v>
-      </c>
-      <c r="G28" s="36" t="s">
-        <v>85</v>
       </c>
       <c r="H28" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I28" s="36" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="J28" s="33" t="s">
         <v>23</v>
@@ -5067,7 +5031,7 @@
         <v>23</v>
       </c>
       <c r="L28" s="33" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M28" s="33">
         <v>-1000</v>
@@ -5120,19 +5084,19 @@
         <v>2</v>
       </c>
       <c r="E29" s="33" t="s">
+        <v>85</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>712</v>
+      </c>
+      <c r="G29" s="36" t="s">
         <v>86</v>
-      </c>
-      <c r="F29" s="33" t="s">
-        <v>713</v>
-      </c>
-      <c r="G29" s="36" t="s">
-        <v>87</v>
       </c>
       <c r="H29" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I29" s="36" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="J29" s="33" t="s">
         <v>23</v>
@@ -5141,7 +5105,7 @@
         <v>23</v>
       </c>
       <c r="L29" s="33" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="M29" s="33">
         <v>900</v>
@@ -5194,19 +5158,19 @@
         <v>2</v>
       </c>
       <c r="E30" s="33" t="s">
+        <v>87</v>
+      </c>
+      <c r="F30" s="33" t="s">
+        <v>713</v>
+      </c>
+      <c r="G30" s="36" t="s">
         <v>88</v>
-      </c>
-      <c r="F30" s="33" t="s">
-        <v>714</v>
-      </c>
-      <c r="G30" s="36" t="s">
-        <v>89</v>
       </c>
       <c r="H30" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I30" s="36" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="J30" s="33" t="s">
         <v>23</v>
@@ -5215,7 +5179,7 @@
         <v>23</v>
       </c>
       <c r="L30" s="33" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M30" s="33">
         <v>310</v>
@@ -5268,19 +5232,19 @@
         <v>1</v>
       </c>
       <c r="E31" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>714</v>
+      </c>
+      <c r="G31" s="36" t="s">
         <v>90</v>
-      </c>
-      <c r="F31" s="33" t="s">
-        <v>715</v>
-      </c>
-      <c r="G31" s="36" t="s">
-        <v>91</v>
       </c>
       <c r="H31" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I31" s="36" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="J31" s="33" t="s">
         <v>23</v>
@@ -5289,7 +5253,7 @@
         <v>23</v>
       </c>
       <c r="L31" s="33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M31" s="33">
         <v>400</v>
@@ -5342,19 +5306,19 @@
         <v>17</v>
       </c>
       <c r="E32" s="33" t="s">
+        <v>91</v>
+      </c>
+      <c r="F32" s="33" t="s">
+        <v>715</v>
+      </c>
+      <c r="G32" s="36" t="s">
         <v>92</v>
-      </c>
-      <c r="F32" s="33" t="s">
-        <v>716</v>
-      </c>
-      <c r="G32" s="36" t="s">
-        <v>93</v>
       </c>
       <c r="H32" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I32" s="36" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="J32" s="33" t="s">
         <v>23</v>
@@ -5363,7 +5327,7 @@
         <v>23</v>
       </c>
       <c r="L32" s="33" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="M32" s="33">
         <v>-8000</v>
@@ -5416,19 +5380,19 @@
         <v>2</v>
       </c>
       <c r="E33" s="33" t="s">
+        <v>571</v>
+      </c>
+      <c r="F33" s="33" t="s">
+        <v>716</v>
+      </c>
+      <c r="G33" s="36" t="s">
         <v>572</v>
-      </c>
-      <c r="F33" s="33" t="s">
-        <v>717</v>
-      </c>
-      <c r="G33" s="36" t="s">
-        <v>573</v>
       </c>
       <c r="H33" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I33" s="36" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="J33" s="33" t="s">
         <v>23</v>
@@ -5437,7 +5401,7 @@
         <v>23</v>
       </c>
       <c r="L33" s="33" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="M33" s="33">
         <v>13000</v>
@@ -5490,19 +5454,19 @@
         <v>2</v>
       </c>
       <c r="E34" s="33" t="s">
+        <v>89</v>
+      </c>
+      <c r="F34" s="33" t="s">
+        <v>714</v>
+      </c>
+      <c r="G34" s="36" t="s">
         <v>90</v>
-      </c>
-      <c r="F34" s="33" t="s">
-        <v>715</v>
-      </c>
-      <c r="G34" s="36" t="s">
-        <v>91</v>
       </c>
       <c r="H34" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I34" s="36" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="J34" s="33" t="s">
         <v>23</v>
@@ -5511,7 +5475,7 @@
         <v>23</v>
       </c>
       <c r="L34" s="33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M34" s="33">
         <v>400</v>
@@ -5564,28 +5528,28 @@
         <v>4</v>
       </c>
       <c r="E35" s="33" t="s">
+        <v>573</v>
+      </c>
+      <c r="F35" s="33" t="s">
+        <v>717</v>
+      </c>
+      <c r="G35" s="36" t="s">
         <v>574</v>
-      </c>
-      <c r="F35" s="33" t="s">
-        <v>718</v>
-      </c>
-      <c r="G35" s="36" t="s">
-        <v>575</v>
       </c>
       <c r="H35" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I35" s="36" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="J35" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K35" s="33" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L35" s="33" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="M35" s="33">
         <v>1</v>
@@ -5641,16 +5605,16 @@
         <v>51</v>
       </c>
       <c r="F36" s="33" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="G36" s="36" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H36" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I36" s="36" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="J36" s="33" t="s">
         <v>23</v>
@@ -5712,19 +5676,19 @@
         <v>1</v>
       </c>
       <c r="E37" s="33" t="s">
+        <v>576</v>
+      </c>
+      <c r="F37" s="33" t="s">
+        <v>718</v>
+      </c>
+      <c r="G37" s="36" t="s">
         <v>577</v>
-      </c>
-      <c r="F37" s="33" t="s">
-        <v>719</v>
-      </c>
-      <c r="G37" s="36" t="s">
-        <v>578</v>
       </c>
       <c r="H37" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I37" s="36" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="J37" s="33" t="s">
         <v>23</v>
@@ -5733,7 +5697,7 @@
         <v>23</v>
       </c>
       <c r="L37" s="33" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="M37" s="33">
         <v>250</v>
@@ -5786,28 +5750,28 @@
         <v>1</v>
       </c>
       <c r="E38" s="33" t="s">
+        <v>578</v>
+      </c>
+      <c r="F38" s="33" t="s">
+        <v>719</v>
+      </c>
+      <c r="G38" s="36" t="s">
         <v>579</v>
-      </c>
-      <c r="F38" s="33" t="s">
-        <v>720</v>
-      </c>
-      <c r="G38" s="36" t="s">
-        <v>580</v>
       </c>
       <c r="H38" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I38" s="36" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="J38" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K38" s="33" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="L38" s="33" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="M38" s="33">
         <v>1</v>
@@ -5860,19 +5824,19 @@
         <v>7</v>
       </c>
       <c r="E39" s="33" t="s">
+        <v>581</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>720</v>
+      </c>
+      <c r="G39" s="36" t="s">
         <v>582</v>
-      </c>
-      <c r="F39" s="33" t="s">
-        <v>721</v>
-      </c>
-      <c r="G39" s="36" t="s">
-        <v>583</v>
       </c>
       <c r="H39" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I39" s="36" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="J39" s="33" t="s">
         <v>43</v>
@@ -5881,7 +5845,7 @@
         <v>43</v>
       </c>
       <c r="L39" s="33" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="M39" s="33">
         <v>2000</v>
@@ -5935,19 +5899,19 @@
         <v>5</v>
       </c>
       <c r="E40" s="33" t="s">
+        <v>583</v>
+      </c>
+      <c r="F40" s="33" t="s">
+        <v>721</v>
+      </c>
+      <c r="G40" s="36" t="s">
         <v>584</v>
-      </c>
-      <c r="F40" s="33" t="s">
-        <v>722</v>
-      </c>
-      <c r="G40" s="36" t="s">
-        <v>585</v>
       </c>
       <c r="H40" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I40" s="36" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="J40" s="33" t="s">
         <v>23</v>
@@ -5956,7 +5920,7 @@
         <v>23</v>
       </c>
       <c r="L40" s="33" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="M40" s="33">
         <v>1000</v>
@@ -6010,19 +5974,19 @@
         <v>2</v>
       </c>
       <c r="E41" s="33" t="s">
+        <v>585</v>
+      </c>
+      <c r="F41" s="33" t="s">
+        <v>722</v>
+      </c>
+      <c r="G41" s="36" t="s">
         <v>586</v>
-      </c>
-      <c r="F41" s="33" t="s">
-        <v>723</v>
-      </c>
-      <c r="G41" s="36" t="s">
-        <v>587</v>
       </c>
       <c r="H41" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I41" s="36" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="J41" s="33" t="s">
         <v>23</v>
@@ -6031,7 +5995,7 @@
         <v>23</v>
       </c>
       <c r="L41" s="33" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="M41" s="33">
         <v>700</v>
@@ -6084,19 +6048,19 @@
         <v>2</v>
       </c>
       <c r="E42" s="33" t="s">
+        <v>587</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>723</v>
+      </c>
+      <c r="G42" s="36" t="s">
         <v>588</v>
-      </c>
-      <c r="F42" s="33" t="s">
-        <v>724</v>
-      </c>
-      <c r="G42" s="36" t="s">
-        <v>589</v>
       </c>
       <c r="H42" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I42" s="36" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="J42" s="33" t="s">
         <v>23</v>
@@ -6105,7 +6069,7 @@
         <v>23</v>
       </c>
       <c r="L42" s="33" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M42" s="33">
         <v>300</v>
@@ -6159,19 +6123,19 @@
         <v>15</v>
       </c>
       <c r="E43" s="33" t="s">
+        <v>589</v>
+      </c>
+      <c r="F43" s="33" t="s">
+        <v>724</v>
+      </c>
+      <c r="G43" s="36" t="s">
         <v>590</v>
-      </c>
-      <c r="F43" s="33" t="s">
-        <v>725</v>
-      </c>
-      <c r="G43" s="36" t="s">
-        <v>591</v>
       </c>
       <c r="H43" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I43" s="36" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="J43" s="33" t="s">
         <v>23</v>
@@ -6180,7 +6144,7 @@
         <v>23</v>
       </c>
       <c r="L43" s="33" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="M43" s="33">
         <v>-700</v>
@@ -6234,19 +6198,19 @@
         <v>2</v>
       </c>
       <c r="E44" s="33" t="s">
+        <v>591</v>
+      </c>
+      <c r="F44" s="33" t="s">
+        <v>725</v>
+      </c>
+      <c r="G44" s="36" t="s">
         <v>592</v>
-      </c>
-      <c r="F44" s="33" t="s">
-        <v>726</v>
-      </c>
-      <c r="G44" s="36" t="s">
-        <v>593</v>
       </c>
       <c r="H44" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I44" s="36" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="J44" s="33" t="s">
         <v>23</v>
@@ -6255,7 +6219,7 @@
         <v>23</v>
       </c>
       <c r="L44" s="33" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="M44" s="33">
         <v>400</v>
@@ -6309,28 +6273,28 @@
         <v>0</v>
       </c>
       <c r="E45" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F45" s="33" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="G45" s="36" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H45" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I45" s="36" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="J45" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K45" s="33" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="L45" s="33" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M45" s="33">
         <v>-4</v>
@@ -6383,19 +6347,19 @@
         <v>1</v>
       </c>
       <c r="E46" s="33" t="s">
+        <v>594</v>
+      </c>
+      <c r="F46" s="33" t="s">
+        <v>726</v>
+      </c>
+      <c r="G46" s="36" t="s">
         <v>595</v>
-      </c>
-      <c r="F46" s="33" t="s">
-        <v>727</v>
-      </c>
-      <c r="G46" s="36" t="s">
-        <v>596</v>
       </c>
       <c r="H46" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I46" s="36" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="J46" s="33" t="s">
         <v>23</v>
@@ -6404,7 +6368,7 @@
         <v>23</v>
       </c>
       <c r="L46" s="33" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="M46" s="33">
         <v>2000</v>
@@ -6458,19 +6422,19 @@
         <v>15</v>
       </c>
       <c r="E47" s="33" t="s">
+        <v>596</v>
+      </c>
+      <c r="F47" s="33" t="s">
+        <v>727</v>
+      </c>
+      <c r="G47" s="36" t="s">
         <v>597</v>
-      </c>
-      <c r="F47" s="33" t="s">
-        <v>728</v>
-      </c>
-      <c r="G47" s="36" t="s">
-        <v>598</v>
       </c>
       <c r="H47" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I47" s="36" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="J47" s="33" t="s">
         <v>23</v>
@@ -6479,7 +6443,7 @@
         <v>23</v>
       </c>
       <c r="L47" s="33" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="M47" s="33">
         <v>-600</v>
@@ -6536,25 +6500,25 @@
         <v>53</v>
       </c>
       <c r="F48" s="33" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G48" s="36" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H48" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I48" s="36" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="J48" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K48" s="33" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L48" s="33" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="M48" s="33">
         <v>30</v>
@@ -6608,28 +6572,28 @@
         <v>1</v>
       </c>
       <c r="E49" s="33" t="s">
+        <v>599</v>
+      </c>
+      <c r="F49" s="33" t="s">
+        <v>728</v>
+      </c>
+      <c r="G49" s="36" t="s">
         <v>600</v>
-      </c>
-      <c r="F49" s="33" t="s">
-        <v>729</v>
-      </c>
-      <c r="G49" s="36" t="s">
-        <v>601</v>
       </c>
       <c r="H49" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I49" s="36" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="J49" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K49" s="33" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L49" s="33" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="M49" s="33">
         <v>-2</v>
@@ -6682,19 +6646,19 @@
         <v>0</v>
       </c>
       <c r="E50" s="33" t="s">
+        <v>603</v>
+      </c>
+      <c r="F50" s="33" t="s">
+        <v>729</v>
+      </c>
+      <c r="G50" s="36" t="s">
         <v>604</v>
-      </c>
-      <c r="F50" s="33" t="s">
-        <v>730</v>
-      </c>
-      <c r="G50" s="36" t="s">
-        <v>605</v>
       </c>
       <c r="H50" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I50" s="36" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="J50" s="33" t="s">
         <v>23</v>
@@ -6703,7 +6667,7 @@
         <v>23</v>
       </c>
       <c r="L50" s="33" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="M50" s="33">
         <v>-750</v>
@@ -6756,19 +6720,19 @@
         <v>3</v>
       </c>
       <c r="E51" s="33" t="s">
+        <v>605</v>
+      </c>
+      <c r="F51" s="33" t="s">
+        <v>730</v>
+      </c>
+      <c r="G51" s="36" t="s">
         <v>606</v>
-      </c>
-      <c r="F51" s="33" t="s">
-        <v>731</v>
-      </c>
-      <c r="G51" s="36" t="s">
-        <v>607</v>
       </c>
       <c r="H51" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I51" s="36" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="J51" s="33" t="s">
         <v>23</v>
@@ -6777,7 +6741,7 @@
         <v>23</v>
       </c>
       <c r="L51" s="33" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="M51" s="33">
         <v>700</v>
@@ -6831,19 +6795,19 @@
         <v>4</v>
       </c>
       <c r="E52" s="33" t="s">
+        <v>607</v>
+      </c>
+      <c r="F52" s="33" t="s">
+        <v>731</v>
+      </c>
+      <c r="G52" s="36" t="s">
         <v>608</v>
-      </c>
-      <c r="F52" s="33" t="s">
-        <v>732</v>
-      </c>
-      <c r="G52" s="36" t="s">
-        <v>609</v>
       </c>
       <c r="H52" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I52" s="36" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="J52" s="33" t="s">
         <v>23</v>
@@ -6852,7 +6816,7 @@
         <v>23</v>
       </c>
       <c r="L52" s="33" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="M52" s="33">
         <v>-110</v>
@@ -6906,19 +6870,19 @@
         <v>2</v>
       </c>
       <c r="E53" s="33" t="s">
+        <v>609</v>
+      </c>
+      <c r="F53" s="33" t="s">
+        <v>732</v>
+      </c>
+      <c r="G53" s="36" t="s">
         <v>610</v>
-      </c>
-      <c r="F53" s="33" t="s">
-        <v>733</v>
-      </c>
-      <c r="G53" s="36" t="s">
-        <v>611</v>
       </c>
       <c r="H53" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I53" s="36" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="J53" s="33" t="s">
         <v>23</v>
@@ -6927,7 +6891,7 @@
         <v>23</v>
       </c>
       <c r="L53" s="33" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="M53" s="33">
         <v>4000</v>
@@ -6981,19 +6945,19 @@
         <v>7</v>
       </c>
       <c r="E54" s="33" t="s">
+        <v>611</v>
+      </c>
+      <c r="F54" s="33" t="s">
+        <v>733</v>
+      </c>
+      <c r="G54" s="36" t="s">
         <v>612</v>
-      </c>
-      <c r="F54" s="33" t="s">
-        <v>734</v>
-      </c>
-      <c r="G54" s="36" t="s">
-        <v>613</v>
       </c>
       <c r="H54" s="33" t="s">
         <v>28</v>
       </c>
       <c r="I54" s="36" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="J54" s="33" t="s">
         <v>43</v>
@@ -7002,7 +6966,7 @@
         <v>43</v>
       </c>
       <c r="L54" s="33" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="M54" s="33">
         <v>400</v>
@@ -7056,19 +7020,19 @@
         <v>7</v>
       </c>
       <c r="E55" s="33" t="s">
+        <v>613</v>
+      </c>
+      <c r="F55" s="33" t="s">
+        <v>734</v>
+      </c>
+      <c r="G55" s="36" t="s">
         <v>614</v>
-      </c>
-      <c r="F55" s="33" t="s">
-        <v>735</v>
-      </c>
-      <c r="G55" s="36" t="s">
-        <v>615</v>
       </c>
       <c r="H55" s="33" t="s">
         <v>28</v>
       </c>
       <c r="I55" s="36" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="J55" s="33" t="s">
         <v>43</v>
@@ -7077,7 +7041,7 @@
         <v>43</v>
       </c>
       <c r="L55" s="33" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="M55" s="33">
         <v>-140</v>
@@ -7131,19 +7095,19 @@
         <v>1</v>
       </c>
       <c r="E56" s="33" t="s">
+        <v>615</v>
+      </c>
+      <c r="F56" s="33" t="s">
+        <v>735</v>
+      </c>
+      <c r="G56" s="36" t="s">
         <v>616</v>
-      </c>
-      <c r="F56" s="33" t="s">
-        <v>736</v>
-      </c>
-      <c r="G56" s="36" t="s">
-        <v>617</v>
       </c>
       <c r="H56" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I56" s="36" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="J56" s="33" t="s">
         <v>23</v>
@@ -7152,7 +7116,7 @@
         <v>23</v>
       </c>
       <c r="L56" s="33" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="M56" s="33">
         <v>-100</v>
@@ -7177,7 +7141,7 @@
         <v>1</v>
       </c>
       <c r="T56" s="40">
-        <f t="shared" ref="T56:T63" si="14">IF(S56=1, ABS(O56-N56)/N56, 0)</f>
+        <f t="shared" ref="T56:T64" si="14">IF(S56=1, ABS(O56-N56)/N56, 0)</f>
         <v>2.7360178970917266E-2</v>
       </c>
       <c r="U56" s="39">
@@ -7206,19 +7170,19 @@
         <v>1</v>
       </c>
       <c r="E57" s="33" t="s">
+        <v>617</v>
+      </c>
+      <c r="F57" s="33" t="s">
+        <v>736</v>
+      </c>
+      <c r="G57" s="36" t="s">
         <v>618</v>
-      </c>
-      <c r="F57" s="33" t="s">
-        <v>737</v>
-      </c>
-      <c r="G57" s="36" t="s">
-        <v>619</v>
       </c>
       <c r="H57" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I57" s="36" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="J57" s="33" t="s">
         <v>23</v>
@@ -7227,7 +7191,7 @@
         <v>23</v>
       </c>
       <c r="L57" s="33" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="M57" s="33">
         <v>-100</v>
@@ -7284,7 +7248,7 @@
         <v>24</v>
       </c>
       <c r="F58" s="33" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G58" s="36" t="s">
         <v>25</v>
@@ -7293,7 +7257,7 @@
         <v>22</v>
       </c>
       <c r="I58" s="36" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="J58" s="33" t="s">
         <v>23</v>
@@ -7359,25 +7323,25 @@
         <v>53</v>
       </c>
       <c r="F59" s="33" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="G59" s="36" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H59" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I59" s="36" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="J59" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K59" s="33" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="L59" s="33" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="M59" s="33">
         <v>15</v>
@@ -7434,7 +7398,7 @@
         <v>31</v>
       </c>
       <c r="F60" s="33" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G60" s="36" t="s">
         <v>32</v>
@@ -7443,16 +7407,16 @@
         <v>22</v>
       </c>
       <c r="I60" s="36" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J60" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K60" s="33" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L60" s="33" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="M60" s="33">
         <v>10</v>
@@ -7509,7 +7473,7 @@
         <v>31</v>
       </c>
       <c r="F61" s="33" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="G61" s="36" t="s">
         <v>32</v>
@@ -7518,16 +7482,16 @@
         <v>22</v>
       </c>
       <c r="I61" s="36" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="J61" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K61" s="33" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="L61" s="33" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="M61" s="33">
         <v>15</v>
@@ -7581,10 +7545,10 @@
         <v>7</v>
       </c>
       <c r="E62" s="33" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F62" s="33" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="G62" s="36" t="s">
         <v>47</v>
@@ -7593,16 +7557,16 @@
         <v>28</v>
       </c>
       <c r="I62" s="36" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="J62" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K62" s="33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L62" s="33" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="M62" s="33">
         <v>5</v>
@@ -7656,28 +7620,28 @@
         <v>7</v>
       </c>
       <c r="E63" s="33" t="s">
+        <v>620</v>
+      </c>
+      <c r="F63" s="33" t="s">
+        <v>737</v>
+      </c>
+      <c r="G63" s="36" t="s">
         <v>621</v>
-      </c>
-      <c r="F63" s="33" t="s">
-        <v>738</v>
-      </c>
-      <c r="G63" s="36" t="s">
-        <v>622</v>
       </c>
       <c r="H63" s="33" t="s">
         <v>28</v>
       </c>
       <c r="I63" s="36" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="J63" s="33" t="s">
         <v>29</v>
       </c>
       <c r="K63" s="33" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="L63" s="33" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="M63" s="33">
         <v>-14</v>
@@ -7722,73 +7686,71 @@
       <c r="B64" s="34">
         <v>46310</v>
       </c>
-      <c r="C64" s="54">
-        <v>46317</v>
-      </c>
-      <c r="D64" s="55">
+      <c r="C64" s="34">
+        <v>46318</v>
+      </c>
+      <c r="D64" s="35">
         <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="E64" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="E64" s="33" t="s">
+        <v>623</v>
+      </c>
+      <c r="F64" s="33" t="s">
+        <v>738</v>
+      </c>
+      <c r="G64" s="36" t="s">
         <v>624</v>
       </c>
-      <c r="F64" s="47" t="s">
-        <v>739</v>
-      </c>
-      <c r="G64" s="48" t="s">
-        <v>625</v>
-      </c>
-      <c r="H64" s="47" t="s">
+      <c r="H64" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="I64" s="48" t="s">
-        <v>638</v>
-      </c>
-      <c r="J64" s="47" t="s">
+      <c r="I64" s="36" t="s">
+        <v>637</v>
+      </c>
+      <c r="J64" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="K64" s="47" t="s">
+      <c r="K64" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="L64" s="47" t="s">
-        <v>624</v>
-      </c>
-      <c r="M64" s="47">
+      <c r="L64" s="33" t="s">
+        <v>623</v>
+      </c>
+      <c r="M64" s="33">
         <v>1820</v>
       </c>
-      <c r="N64" s="47">
-        <v>7.82</v>
-      </c>
-      <c r="O64" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="P64" s="47">
-        <v>7.9</v>
-      </c>
-      <c r="Q64" s="49">
-        <v>14487</v>
-      </c>
-      <c r="R64" s="47">
-        <v>3.03</v>
-      </c>
-      <c r="S64" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="T64" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="U64" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="V64" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="W64" s="33">
-        <v>146</v>
+      <c r="N64" s="33">
+        <v>7.819</v>
+      </c>
+      <c r="O64" s="33">
+        <v>7.35</v>
+      </c>
+      <c r="P64" s="33">
+        <v>7.35</v>
+      </c>
+      <c r="Q64" s="39">
+        <v>13377</v>
+      </c>
+      <c r="R64" s="33">
+        <v>23.69</v>
+      </c>
+      <c r="S64" s="33">
+        <v>0</v>
+      </c>
+      <c r="T64" s="40">
+        <f t="shared" si="14"/>
+        <v>0</v>
+      </c>
+      <c r="U64" s="33">
+        <v>-853</v>
+      </c>
+      <c r="V64" s="45">
+        <v>-853</v>
       </c>
       <c r="Y64" s="39">
         <f t="shared" si="5"/>
-        <v>19377798.130000003</v>
+        <v>19376688.130000003</v>
       </c>
     </row>
     <row r="65" spans="1:26" x14ac:dyDescent="0.25">
@@ -7798,73 +7760,71 @@
       <c r="B65" s="34">
         <v>46310</v>
       </c>
-      <c r="C65" s="54">
-        <v>46317</v>
-      </c>
-      <c r="D65" s="55">
+      <c r="C65" s="34">
+        <v>46318</v>
+      </c>
+      <c r="D65" s="35">
         <f t="shared" si="7"/>
-        <v>7</v>
-      </c>
-      <c r="E65" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="E65" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="F65" s="33" t="s">
+        <v>739</v>
+      </c>
+      <c r="G65" s="36" t="s">
         <v>626</v>
       </c>
-      <c r="F65" s="47" t="s">
-        <v>740</v>
-      </c>
-      <c r="G65" s="48" t="s">
-        <v>627</v>
-      </c>
-      <c r="H65" s="47" t="s">
+      <c r="H65" s="33" t="s">
         <v>22</v>
       </c>
-      <c r="I65" s="48" t="s">
-        <v>637</v>
-      </c>
-      <c r="J65" s="47" t="s">
+      <c r="I65" s="36" t="s">
+        <v>636</v>
+      </c>
+      <c r="J65" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="K65" s="47" t="s">
+      <c r="K65" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="L65" s="47" t="s">
-        <v>626</v>
-      </c>
-      <c r="M65" s="47">
-        <v>-2242</v>
-      </c>
-      <c r="N65" s="47">
-        <v>28.315999999999999</v>
-      </c>
-      <c r="O65" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="P65" s="47">
-        <v>28.5</v>
-      </c>
-      <c r="Q65" s="49">
-        <v>64480</v>
-      </c>
-      <c r="R65" s="47">
-        <v>2.33</v>
-      </c>
-      <c r="S65" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="T65" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="U65" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="V65" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="W65" s="33">
-        <v>-412</v>
+      <c r="L65" s="33" t="s">
+        <v>625</v>
+      </c>
+      <c r="M65" s="33">
+        <v>-3605</v>
+      </c>
+      <c r="N65" s="33">
+        <v>28.847999999999999</v>
+      </c>
+      <c r="O65" s="33">
+        <v>29.456</v>
+      </c>
+      <c r="P65" s="33">
+        <v>29.456</v>
+      </c>
+      <c r="Q65" s="39">
+        <v>103999</v>
+      </c>
+      <c r="R65" s="33">
+        <v>42.02</v>
+      </c>
+      <c r="S65" s="33">
+        <v>0</v>
+      </c>
+      <c r="T65" s="40">
+        <f t="shared" ref="T65:T66" si="15">IF(S65=1, ABS(O65-N65)/N65, 0)</f>
+        <v>0</v>
+      </c>
+      <c r="U65" s="33">
+        <v>-2191</v>
+      </c>
+      <c r="V65" s="45">
+        <v>-2191</v>
       </c>
       <c r="Y65" s="39">
         <f t="shared" si="5"/>
-        <v>19442278.130000003</v>
+        <v>19480687.130000003</v>
       </c>
     </row>
     <row r="66" spans="1:26" x14ac:dyDescent="0.25">
@@ -7882,19 +7842,19 @@
         <v>4</v>
       </c>
       <c r="E66" s="33" t="s">
+        <v>627</v>
+      </c>
+      <c r="F66" s="33" t="s">
+        <v>740</v>
+      </c>
+      <c r="G66" s="36" t="s">
         <v>628</v>
-      </c>
-      <c r="F66" s="33" t="s">
-        <v>741</v>
-      </c>
-      <c r="G66" s="36" t="s">
-        <v>629</v>
       </c>
       <c r="H66" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I66" s="36" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="J66" s="33" t="s">
         <v>23</v>
@@ -7903,7 +7863,7 @@
         <v>23</v>
       </c>
       <c r="L66" s="33" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="M66" s="33">
         <v>-1956</v>
@@ -7927,7 +7887,7 @@
         <v>1</v>
       </c>
       <c r="T66" s="40">
-        <f t="shared" ref="T66" si="15">IF(S66=1, ABS(O66-N66)/N66, 0)</f>
+        <f t="shared" si="15"/>
         <v>7.9314040728829653E-4</v>
       </c>
       <c r="U66" s="33">
@@ -7938,7 +7898,7 @@
       </c>
       <c r="Y66" s="39">
         <f t="shared" si="5"/>
-        <v>19533232.130000003</v>
+        <v>19571641.130000003</v>
       </c>
     </row>
     <row r="67" spans="1:26" x14ac:dyDescent="0.25">
@@ -7956,19 +7916,19 @@
         <v>4</v>
       </c>
       <c r="E67" s="33" t="s">
+        <v>629</v>
+      </c>
+      <c r="F67" s="33" t="s">
+        <v>741</v>
+      </c>
+      <c r="G67" s="36" t="s">
         <v>630</v>
-      </c>
-      <c r="F67" s="33" t="s">
-        <v>742</v>
-      </c>
-      <c r="G67" s="36" t="s">
-        <v>631</v>
       </c>
       <c r="H67" s="33" t="s">
         <v>22</v>
       </c>
       <c r="I67" s="36" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="J67" s="33" t="s">
         <v>23</v>
@@ -7977,7 +7937,7 @@
         <v>23</v>
       </c>
       <c r="L67" s="33" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="M67" s="33">
         <v>-700</v>
@@ -8001,7 +7961,7 @@
         <v>1</v>
       </c>
       <c r="T67" s="40">
-        <f t="shared" ref="T67:T70" si="16">IF(S67=1, ABS(O67-N67)/N67, 0)</f>
+        <f t="shared" ref="T67:T71" si="16">IF(S67=1, ABS(O67-N67)/N67, 0)</f>
         <v>5.3806348634246369E-3</v>
       </c>
       <c r="U67" s="33">
@@ -8012,7 +7972,7 @@
       </c>
       <c r="Y67" s="39">
         <f t="shared" si="5"/>
-        <v>19805145.130000003</v>
+        <v>19843554.130000003</v>
       </c>
     </row>
     <row r="68" spans="1:26" x14ac:dyDescent="0.25">
@@ -8022,77 +7982,75 @@
       <c r="B68" s="34">
         <v>46314</v>
       </c>
-      <c r="C68" s="54">
-        <v>46317</v>
-      </c>
-      <c r="D68" s="55">
+      <c r="C68" s="34">
+        <v>46318</v>
+      </c>
+      <c r="D68" s="35">
         <f t="shared" si="7"/>
-        <v>3</v>
-      </c>
-      <c r="E68" s="47" t="s">
+        <v>4</v>
+      </c>
+      <c r="E68" s="33" t="s">
+        <v>745</v>
+      </c>
+      <c r="F68" s="33" t="s">
         <v>746</v>
       </c>
-      <c r="F68" s="47" t="s">
+      <c r="G68" s="36" t="s">
         <v>747</v>
       </c>
-      <c r="G68" s="48" t="s">
+      <c r="H68" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I68" s="36" t="s">
         <v>748</v>
       </c>
-      <c r="H68" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="I68" s="48" t="s">
-        <v>749</v>
-      </c>
-      <c r="J68" s="47" t="s">
+      <c r="J68" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="K68" s="47" t="s">
+      <c r="K68" s="33" t="s">
         <v>23</v>
       </c>
-      <c r="L68" s="47" t="s">
-        <v>746</v>
-      </c>
-      <c r="M68" s="47">
-        <v>-851</v>
-      </c>
-      <c r="N68" s="47">
-        <v>47.387999999999998</v>
-      </c>
-      <c r="O68" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="P68" s="47">
-        <v>46.63</v>
-      </c>
-      <c r="Q68" s="49">
-        <v>39997</v>
-      </c>
-      <c r="R68" s="47">
+      <c r="L68" s="33" t="s">
+        <v>745</v>
+      </c>
+      <c r="M68" s="33">
+        <v>-2810</v>
+      </c>
+      <c r="N68" s="33">
+        <v>47.01</v>
+      </c>
+      <c r="O68" s="33">
+        <v>46.89</v>
+      </c>
+      <c r="P68" s="33">
+        <v>46.89</v>
+      </c>
+      <c r="Q68" s="39">
+        <v>108010</v>
+      </c>
+      <c r="R68" s="33">
         <v>2.12</v>
       </c>
-      <c r="S68" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="T68" s="56" t="s">
-        <v>66</v>
-      </c>
-      <c r="U68" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="V68" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="W68" s="33">
-        <v>645</v>
+      <c r="S68" s="33">
+        <v>1</v>
+      </c>
+      <c r="T68" s="40">
+        <f t="shared" si="16"/>
+        <v>2.5526483726866079E-3</v>
+      </c>
+      <c r="U68" s="33">
+        <v>1278</v>
+      </c>
+      <c r="V68" s="41">
+        <v>1278</v>
       </c>
       <c r="Y68" s="39">
         <f t="shared" si="5"/>
-        <v>19845142.130000003</v>
-      </c>
-      <c r="Z68" s="58">
+        <v>19951564.130000003</v>
+      </c>
+      <c r="Z68" s="52">
         <f>Y68/424000</f>
-        <v>46.804580495283027</v>
+        <v>47.055575778301893</v>
       </c>
     </row>
     <row r="69" spans="1:26" x14ac:dyDescent="0.25">
@@ -8110,19 +8068,19 @@
         <v>1</v>
       </c>
       <c r="E69" s="33" t="s">
+        <v>751</v>
+      </c>
+      <c r="F69" s="33" t="s">
         <v>752</v>
       </c>
-      <c r="F69" s="33" t="s">
+      <c r="G69" s="36" t="s">
         <v>753</v>
-      </c>
-      <c r="G69" s="36" t="s">
-        <v>754</v>
       </c>
       <c r="H69" s="33" t="s">
         <v>28</v>
       </c>
       <c r="I69" s="36" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="J69" s="33" t="s">
         <v>23</v>
@@ -8131,7 +8089,7 @@
         <v>23</v>
       </c>
       <c r="L69" s="33" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="M69" s="33">
         <v>242</v>
@@ -8181,19 +8139,19 @@
         <v>1</v>
       </c>
       <c r="E70" s="33" t="s">
+        <v>755</v>
+      </c>
+      <c r="F70" s="33" t="s">
         <v>756</v>
       </c>
-      <c r="F70" s="33" t="s">
+      <c r="G70" s="36" t="s">
         <v>757</v>
-      </c>
-      <c r="G70" s="36" t="s">
-        <v>758</v>
       </c>
       <c r="H70" s="33" t="s">
         <v>28</v>
       </c>
       <c r="I70" s="36" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="J70" s="33" t="s">
         <v>23</v>
@@ -8202,7 +8160,7 @@
         <v>23</v>
       </c>
       <c r="L70" s="33" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="M70" s="33">
         <v>-400</v>
@@ -8242,71 +8200,69 @@
         <v>63</v>
       </c>
       <c r="B71" s="34">
-        <v>46316</v>
-      </c>
-      <c r="C71" s="54">
-        <v>46317</v>
-      </c>
-      <c r="D71" s="55">
+        <v>46318</v>
+      </c>
+      <c r="C71" s="34">
+        <v>46322</v>
+      </c>
+      <c r="D71" s="35">
         <f t="shared" si="7"/>
+        <v>4</v>
+      </c>
+      <c r="E71" s="33" t="s">
+        <v>79</v>
+      </c>
+      <c r="F71" s="33" t="s">
+        <v>696</v>
+      </c>
+      <c r="G71" s="36" t="s">
+        <v>47</v>
+      </c>
+      <c r="H71" s="33" t="s">
+        <v>22</v>
+      </c>
+      <c r="I71" s="36" t="s">
+        <v>759</v>
+      </c>
+      <c r="J71" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="K71" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="L71" s="33" t="s">
+        <v>80</v>
+      </c>
+      <c r="M71" s="33">
+        <v>4</v>
+      </c>
+      <c r="N71" s="33">
+        <v>4005.1</v>
+      </c>
+      <c r="O71" s="33">
+        <v>4066.33</v>
+      </c>
+      <c r="P71" s="33">
+        <v>4066.33</v>
+      </c>
+      <c r="Q71" s="39">
+        <v>162105</v>
+      </c>
+      <c r="R71" s="33">
+        <v>7.4</v>
+      </c>
+      <c r="S71" s="33">
         <v>1</v>
       </c>
-      <c r="E71" s="47" t="s">
-        <v>759</v>
-      </c>
-      <c r="F71" s="47" t="s">
-        <v>760</v>
-      </c>
-      <c r="G71" s="48" t="s">
-        <v>761</v>
-      </c>
-      <c r="H71" s="47" t="s">
-        <v>22</v>
-      </c>
-      <c r="I71" s="48" t="s">
-        <v>762</v>
-      </c>
-      <c r="J71" s="47" t="s">
-        <v>29</v>
-      </c>
-      <c r="K71" s="47" t="s">
-        <v>115</v>
-      </c>
-      <c r="L71" s="47" t="s">
-        <v>759</v>
-      </c>
-      <c r="M71" s="47">
-        <v>2</v>
-      </c>
-      <c r="N71" s="47">
-        <v>622.80999999999995</v>
-      </c>
-      <c r="O71" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="P71" s="47">
-        <v>628</v>
-      </c>
-      <c r="Q71" s="49">
-        <v>12568</v>
-      </c>
-      <c r="R71" s="47">
-        <v>1.0900000000000001</v>
-      </c>
-      <c r="S71" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="T71" s="56" t="s">
-        <v>66</v>
-      </c>
-      <c r="U71" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="V71" s="47" t="s">
-        <v>66</v>
-      </c>
-      <c r="W71" s="33">
-        <v>111</v>
+      <c r="T71" s="40">
+        <f t="shared" si="16"/>
+        <v>1.5288007790067669E-2</v>
+      </c>
+      <c r="U71" s="33">
+        <v>3108</v>
+      </c>
+      <c r="V71" s="41">
+        <v>3108</v>
       </c>
       <c r="Y71" s="39"/>
     </row>
@@ -8345,8 +8301,8 @@
       <c r="I75" s="36"/>
     </row>
     <row r="76" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D76" s="51" t="s">
-        <v>94</v>
+      <c r="D76" s="48" t="s">
+        <v>93</v>
       </c>
       <c r="E76" s="46">
         <f>AVERAGE(D2:D63)</f>
@@ -8356,12 +8312,12 @@
       <c r="G76" s="36"/>
       <c r="I76" s="36"/>
       <c r="V76" s="39">
-        <f>SUM(V2:V70)</f>
-        <v>89294.47</v>
+        <f>SUM(V2:V74)</f>
+        <v>90636.47</v>
       </c>
       <c r="W76" s="39">
         <f>SUM(W2:W71)</f>
-        <v>490</v>
+        <v>0</v>
       </c>
       <c r="X76" s="39">
         <f>SUM(X2:X70)</f>
@@ -8370,8 +8326,8 @@
       <c r="Y76" s="39"/>
     </row>
     <row r="77" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="D77" s="51" t="s">
-        <v>95</v>
+      <c r="D77" s="48" t="s">
+        <v>94</v>
       </c>
       <c r="E77" s="46">
         <f>AVERAGE(D2:D11,D13,D15:D63)</f>
@@ -8379,24 +8335,24 @@
       </c>
       <c r="F77" s="46"/>
       <c r="G77" s="36"/>
-      <c r="V77" s="52" t="s">
+      <c r="V77" s="49" t="s">
+        <v>95</v>
+      </c>
+      <c r="W77" s="36" t="s">
         <v>96</v>
-      </c>
-      <c r="W77" s="36" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="78" spans="1:26" x14ac:dyDescent="0.25">
       <c r="G78" s="36"/>
       <c r="V78" s="33" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="79" spans="1:26" x14ac:dyDescent="0.25">
       <c r="G79" s="36"/>
       <c r="V79" s="39">
         <f>V76+W76</f>
-        <v>89784.47</v>
+        <v>90636.47</v>
       </c>
     </row>
     <row r="80" spans="1:26" x14ac:dyDescent="0.25">
@@ -8405,7 +8361,7 @@
     <row r="81" spans="7:22" x14ac:dyDescent="0.25">
       <c r="G81" s="36"/>
       <c r="V81" s="36" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="82" spans="7:22" x14ac:dyDescent="0.25">
@@ -8416,13 +8372,13 @@
     </row>
     <row r="84" spans="7:22" x14ac:dyDescent="0.25">
       <c r="V84" s="33" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="85" spans="7:22" x14ac:dyDescent="0.25">
-      <c r="V85" s="53">
+      <c r="V85" s="50">
         <f>V79/V82</f>
-        <v>0.26962303303303303</v>
+        <v>0.27218159159159161</v>
       </c>
     </row>
   </sheetData>
@@ -8435,7 +8391,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:I96"/>
+  <dimension ref="A1:I100"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -8450,16 +8406,16 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A1" s="22" t="s">
+        <v>100</v>
+      </c>
+      <c r="B1" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="C1" s="22" t="s">
         <v>102</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="D1" s="23" t="s">
         <v>103</v>
-      </c>
-      <c r="D1" s="23" t="s">
-        <v>104</v>
       </c>
       <c r="G1" s="25"/>
     </row>
@@ -8501,11 +8457,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C96" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C100" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D96" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D100" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -9678,14 +9634,14 @@
         <v>1.3941407429779523E-3</v>
       </c>
       <c r="F74" s="25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G74" s="27">
         <f>AVERAGE(C3:C960)</f>
-        <v>971.66053191489323</v>
+        <v>945.7458163265303</v>
       </c>
       <c r="I74" s="27">
-        <v>971.50634408602116</v>
+        <v>910.5062105263155</v>
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
@@ -9705,14 +9661,14 @@
         <v>9.4992906295542062E-3</v>
       </c>
       <c r="F75" s="25" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="G75" s="27">
         <f>_xlfn.STDEV.S(C3:C960)</f>
-        <v>3984.5198053783611</v>
+        <v>3951.4887179831735</v>
       </c>
       <c r="I75" s="27">
-        <v>4006.1159949205462</v>
+        <v>4007.840575031722</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
@@ -9732,14 +9688,14 @@
         <v>-5.9729103776628928E-3</v>
       </c>
       <c r="F76" s="25" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
-        <v>3.871139688280854</v>
+        <v>3.7993906783925544</v>
       </c>
       <c r="I76" s="28">
-        <v>3.8496601498791141</v>
+        <v>3.6063904566064999</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
@@ -9759,14 +9715,14 @@
         <v>4.4963812546586836E-4</v>
       </c>
       <c r="F77" s="25" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G77" s="29">
         <f>_xlfn.STDEV.S(D2:D960)*SQRT(252)</f>
-        <v>0.17051315116727933</v>
+        <v>0.16864973925541754</v>
       </c>
       <c r="I77" s="29">
-        <v>0.17142680382144651</v>
+        <v>0.17112271724924777</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
@@ -9786,14 +9742,14 @@
         <v>8.3734501065908466E-3</v>
       </c>
       <c r="F78" s="25" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G78" s="29" cm="1">
         <f t="array" ref="G78">PRODUCT(1+D3:D960)-1</f>
-        <v>0.27390774259606276</v>
+        <v>0.27794725776884577</v>
       </c>
       <c r="I78" s="29">
-        <v>0.27095082948517613</v>
+        <v>0.25939907562804132</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
@@ -9813,14 +9769,14 @@
         <v>9.6529467705530299E-4</v>
       </c>
       <c r="F79" s="25" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="G79" s="29" cm="1">
         <f t="array" ref="G79">PRODUCT(1+D2:D960)^(252/COUNT(D2:D960))-1</f>
-        <v>0.90060697367872566</v>
+        <v>0.86691189510860522</v>
       </c>
       <c r="I79" s="29">
-        <v>0.90175106123334814</v>
+        <v>0.83201424728177864</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
@@ -10110,6 +10066,74 @@
       <c r="D96" s="23">
         <f t="shared" si="1"/>
         <v>2.3265361981661421E-3</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A97" s="26">
+        <v>46317</v>
+      </c>
+      <c r="B97" s="5">
+        <f>B96-570-3431-764-73</f>
+        <v>419954</v>
+      </c>
+      <c r="C97" s="5">
+        <f t="shared" si="0"/>
+        <v>-4838</v>
+      </c>
+      <c r="D97" s="23">
+        <f t="shared" si="1"/>
+        <v>-1.1389103372944876E-2</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A98" s="26">
+        <v>46318</v>
+      </c>
+      <c r="B98" s="5">
+        <f>B97+1325+1609-249</f>
+        <v>422639</v>
+      </c>
+      <c r="C98" s="5">
+        <f t="shared" si="0"/>
+        <v>2685</v>
+      </c>
+      <c r="D98" s="23">
+        <f t="shared" si="1"/>
+        <v>6.3935573896188634E-3</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A99" s="26">
+        <v>46321</v>
+      </c>
+      <c r="B99" s="5">
+        <f>B98+1400</f>
+        <v>424039</v>
+      </c>
+      <c r="C99" s="5">
+        <f t="shared" si="0"/>
+        <v>1400</v>
+      </c>
+      <c r="D99" s="23">
+        <f t="shared" si="1"/>
+        <v>3.3125196680855291E-3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A100" s="26">
+        <v>46322</v>
+      </c>
+      <c r="B100" s="5">
+        <f>B99+2100</f>
+        <v>426139</v>
+      </c>
+      <c r="C100" s="5">
+        <f t="shared" si="0"/>
+        <v>2100</v>
+      </c>
+      <c r="D100" s="23">
+        <f t="shared" si="1"/>
+        <v>4.9523746636512206E-3</v>
       </c>
     </row>
   </sheetData>
@@ -10150,79 +10174,79 @@
   <sheetData>
     <row r="1" spans="1:25" s="8" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B1" s="6" t="s">
+        <v>513</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="D1" s="8" t="s">
         <v>515</v>
       </c>
-      <c r="D1" s="8" t="s">
-        <v>516</v>
-      </c>
       <c r="E1" s="8" t="s">
+        <v>520</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G1" s="8" t="s">
         <v>521</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="H1" s="8" t="s">
+        <v>522</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="J1" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="G1" s="8" t="s">
-        <v>522</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>523</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>525</v>
-      </c>
-      <c r="J1" s="8" t="s">
+      <c r="K1" s="8" t="s">
+        <v>111</v>
+      </c>
+      <c r="L1" s="8" t="s">
         <v>115</v>
-      </c>
-      <c r="K1" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="L1" s="8" t="s">
-        <v>116</v>
       </c>
       <c r="M1" s="8" t="s">
         <v>43</v>
       </c>
       <c r="N1" s="9" t="s">
+        <v>516</v>
+      </c>
+      <c r="O1" s="8" t="s">
         <v>517</v>
       </c>
-      <c r="O1" s="8" t="s">
+      <c r="P1" s="8" t="s">
         <v>518</v>
       </c>
-      <c r="P1" s="8" t="s">
+      <c r="Q1" s="8" t="s">
+        <v>526</v>
+      </c>
+      <c r="R1" s="8" t="s">
+        <v>527</v>
+      </c>
+      <c r="S1" s="8" t="s">
+        <v>528</v>
+      </c>
+      <c r="T1" s="8" t="s">
+        <v>529</v>
+      </c>
+      <c r="U1" s="8" t="s">
+        <v>530</v>
+      </c>
+      <c r="V1" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="W1" s="8" t="s">
+        <v>580</v>
+      </c>
+      <c r="X1" s="8" t="s">
+        <v>602</v>
+      </c>
+      <c r="Y1" s="8" t="s">
         <v>519</v>
-      </c>
-      <c r="Q1" s="8" t="s">
-        <v>527</v>
-      </c>
-      <c r="R1" s="8" t="s">
-        <v>528</v>
-      </c>
-      <c r="S1" s="8" t="s">
-        <v>529</v>
-      </c>
-      <c r="T1" s="8" t="s">
-        <v>530</v>
-      </c>
-      <c r="U1" s="8" t="s">
-        <v>531</v>
-      </c>
-      <c r="V1" s="8" t="s">
-        <v>763</v>
-      </c>
-      <c r="W1" s="8" t="s">
-        <v>581</v>
-      </c>
-      <c r="X1" s="8" t="s">
-        <v>603</v>
-      </c>
-      <c r="Y1" s="8" t="s">
-        <v>520</v>
       </c>
     </row>
     <row r="2" spans="1:25" x14ac:dyDescent="0.25">
@@ -15476,7 +15500,7 @@
         <v>0</v>
       </c>
       <c r="N69" s="14">
-        <f t="shared" ref="N69:N103" si="0">SUM(C69:M69)</f>
+        <f t="shared" ref="N69:N107" si="0">SUM(C69:M69)</f>
         <v>407651</v>
       </c>
       <c r="O69" s="15">
@@ -18307,7 +18331,7 @@
       </c>
       <c r="D103" s="13">
         <f>B103-C103-J103-M103-F103</f>
-        <v>293328</v>
+        <v>305828</v>
       </c>
       <c r="E103" s="13">
         <v>0</v>
@@ -18325,7 +18349,7 @@
         <v>0</v>
       </c>
       <c r="J103" s="13">
-        <v>12500</v>
+        <v>0</v>
       </c>
       <c r="K103" s="13">
         <v>0</v>
@@ -18346,7 +18370,7 @@
       </c>
       <c r="P103" s="15">
         <f t="shared" ref="P103" si="134">D103/N103</f>
-        <v>0.69052147874724568</v>
+        <v>0.71994764496506525</v>
       </c>
       <c r="Q103" s="15">
         <f t="shared" ref="Q103" si="135">E103/O103</f>
@@ -18368,7 +18392,7 @@
       </c>
       <c r="V103" s="16">
         <f>J103/N103</f>
-        <v>2.9426166217819544E-2</v>
+        <v>0</v>
       </c>
       <c r="W103" s="15">
         <v>0</v>
@@ -18379,6 +18403,354 @@
       </c>
       <c r="Y103" s="15">
         <f t="shared" ref="Y103" si="139">M103/N103</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A104" s="10">
+        <v>46317</v>
+      </c>
+      <c r="B104" s="11">
+        <v>419954</v>
+      </c>
+      <c r="C104" s="19">
+        <v>225386</v>
+      </c>
+      <c r="D104" s="13">
+        <f>B104-C104-J104-M104-F104</f>
+        <v>194568</v>
+      </c>
+      <c r="E104" s="13">
+        <v>0</v>
+      </c>
+      <c r="F104" s="13">
+        <v>0</v>
+      </c>
+      <c r="G104" s="13">
+        <v>0</v>
+      </c>
+      <c r="H104" s="13">
+        <v>0</v>
+      </c>
+      <c r="I104" s="13">
+        <v>0</v>
+      </c>
+      <c r="J104" s="13">
+        <v>0</v>
+      </c>
+      <c r="K104" s="13">
+        <v>0</v>
+      </c>
+      <c r="L104" s="13">
+        <v>0</v>
+      </c>
+      <c r="M104" s="18">
+        <v>0</v>
+      </c>
+      <c r="N104" s="14">
+        <f t="shared" si="0"/>
+        <v>419954</v>
+      </c>
+      <c r="O104" s="15">
+        <f t="shared" ref="O104" si="140">C104/N104</f>
+        <v>0.53669211389818883</v>
+      </c>
+      <c r="P104" s="15">
+        <f t="shared" ref="P104" si="141">D104/N104</f>
+        <v>0.46330788610181117</v>
+      </c>
+      <c r="Q104" s="15">
+        <f t="shared" ref="Q104" si="142">E104/O104</f>
+        <v>0</v>
+      </c>
+      <c r="R104" s="15">
+        <f t="shared" ref="R104" si="143">E104/N104</f>
+        <v>0</v>
+      </c>
+      <c r="S104" s="15">
+        <v>0</v>
+      </c>
+      <c r="T104" s="15">
+        <v>0</v>
+      </c>
+      <c r="U104" s="15">
+        <f t="shared" ref="U104" si="144">I104/N104</f>
+        <v>0</v>
+      </c>
+      <c r="V104" s="16">
+        <f>J104/N104</f>
+        <v>0</v>
+      </c>
+      <c r="W104" s="15">
+        <v>0</v>
+      </c>
+      <c r="X104" s="16">
+        <f t="shared" ref="X104" si="145">L104/N104</f>
+        <v>0</v>
+      </c>
+      <c r="Y104" s="15">
+        <f t="shared" ref="Y104" si="146">M104/N104</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A105" s="10">
+        <v>46318</v>
+      </c>
+      <c r="B105" s="11">
+        <v>422639</v>
+      </c>
+      <c r="C105" s="19">
+        <v>0</v>
+      </c>
+      <c r="D105" s="13">
+        <f>B105-C105-J105-M105-F105</f>
+        <v>260534</v>
+      </c>
+      <c r="E105" s="13">
+        <v>0</v>
+      </c>
+      <c r="F105" s="13">
+        <v>162105</v>
+      </c>
+      <c r="G105" s="13">
+        <v>0</v>
+      </c>
+      <c r="H105" s="13">
+        <v>0</v>
+      </c>
+      <c r="I105" s="13">
+        <v>0</v>
+      </c>
+      <c r="J105" s="13">
+        <v>0</v>
+      </c>
+      <c r="K105" s="13">
+        <v>0</v>
+      </c>
+      <c r="L105" s="13">
+        <v>0</v>
+      </c>
+      <c r="M105" s="18">
+        <v>0</v>
+      </c>
+      <c r="N105" s="14">
+        <f t="shared" si="0"/>
+        <v>422639</v>
+      </c>
+      <c r="O105" s="15">
+        <f t="shared" ref="O105" si="147">C105/N105</f>
+        <v>0</v>
+      </c>
+      <c r="P105" s="15">
+        <f t="shared" ref="P105" si="148">D105/N105</f>
+        <v>0.61644571371785373</v>
+      </c>
+      <c r="Q105" s="15">
+        <f>F105/N105</f>
+        <v>0.38355428628214622</v>
+      </c>
+      <c r="R105" s="15">
+        <f t="shared" ref="R105" si="149">E105/N105</f>
+        <v>0</v>
+      </c>
+      <c r="S105" s="15">
+        <v>0</v>
+      </c>
+      <c r="T105" s="15">
+        <v>0</v>
+      </c>
+      <c r="U105" s="15">
+        <f t="shared" ref="U105" si="150">I105/N105</f>
+        <v>0</v>
+      </c>
+      <c r="V105" s="16">
+        <f>J105/N105</f>
+        <v>0</v>
+      </c>
+      <c r="W105" s="15">
+        <v>0</v>
+      </c>
+      <c r="X105" s="16">
+        <f t="shared" ref="X105" si="151">L105/N105</f>
+        <v>0</v>
+      </c>
+      <c r="Y105" s="15">
+        <f t="shared" ref="Y105" si="152">M105/N105</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A106" s="10">
+        <v>46321</v>
+      </c>
+      <c r="B106" s="11">
+        <v>424039</v>
+      </c>
+      <c r="C106" s="19">
+        <v>0</v>
+      </c>
+      <c r="D106" s="13">
+        <f>B106-C106-J106-M106-F106</f>
+        <v>261934</v>
+      </c>
+      <c r="E106" s="13">
+        <v>0</v>
+      </c>
+      <c r="F106" s="13">
+        <v>162105</v>
+      </c>
+      <c r="G106" s="13">
+        <v>0</v>
+      </c>
+      <c r="H106" s="13">
+        <v>0</v>
+      </c>
+      <c r="I106" s="13">
+        <v>0</v>
+      </c>
+      <c r="J106" s="13">
+        <v>0</v>
+      </c>
+      <c r="K106" s="13">
+        <v>0</v>
+      </c>
+      <c r="L106" s="13">
+        <v>0</v>
+      </c>
+      <c r="M106" s="18">
+        <v>0</v>
+      </c>
+      <c r="N106" s="14">
+        <f t="shared" si="0"/>
+        <v>424039</v>
+      </c>
+      <c r="O106" s="15">
+        <f t="shared" ref="O106" si="153">C106/N106</f>
+        <v>0</v>
+      </c>
+      <c r="P106" s="15">
+        <f t="shared" ref="P106" si="154">D106/N106</f>
+        <v>0.61771205007086616</v>
+      </c>
+      <c r="Q106" s="15">
+        <f>F106/N106</f>
+        <v>0.3822879499291339</v>
+      </c>
+      <c r="R106" s="15">
+        <f t="shared" ref="R106" si="155">E106/N106</f>
+        <v>0</v>
+      </c>
+      <c r="S106" s="15">
+        <v>0</v>
+      </c>
+      <c r="T106" s="15">
+        <v>0</v>
+      </c>
+      <c r="U106" s="15">
+        <f t="shared" ref="U106" si="156">I106/N106</f>
+        <v>0</v>
+      </c>
+      <c r="V106" s="16">
+        <f>J106/N106</f>
+        <v>0</v>
+      </c>
+      <c r="W106" s="15">
+        <v>0</v>
+      </c>
+      <c r="X106" s="16">
+        <f t="shared" ref="X106" si="157">L106/N106</f>
+        <v>0</v>
+      </c>
+      <c r="Y106" s="15">
+        <f t="shared" ref="Y106" si="158">M106/N106</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A107" s="10">
+        <v>46322</v>
+      </c>
+      <c r="B107" s="11">
+        <v>426139</v>
+      </c>
+      <c r="C107" s="19">
+        <v>0</v>
+      </c>
+      <c r="D107" s="13">
+        <f>B107-C107-J107-M107-F107</f>
+        <v>426139</v>
+      </c>
+      <c r="E107" s="13">
+        <v>0</v>
+      </c>
+      <c r="F107" s="13">
+        <v>0</v>
+      </c>
+      <c r="G107" s="13">
+        <v>0</v>
+      </c>
+      <c r="H107" s="13">
+        <v>0</v>
+      </c>
+      <c r="I107" s="13">
+        <v>0</v>
+      </c>
+      <c r="J107" s="13">
+        <v>0</v>
+      </c>
+      <c r="K107" s="13">
+        <v>0</v>
+      </c>
+      <c r="L107" s="13">
+        <v>0</v>
+      </c>
+      <c r="M107" s="18">
+        <v>0</v>
+      </c>
+      <c r="N107" s="14">
+        <f t="shared" si="0"/>
+        <v>426139</v>
+      </c>
+      <c r="O107" s="15">
+        <f t="shared" ref="O107" si="159">C107/N107</f>
+        <v>0</v>
+      </c>
+      <c r="P107" s="15">
+        <f t="shared" ref="P107" si="160">D107/N107</f>
+        <v>1</v>
+      </c>
+      <c r="Q107" s="15">
+        <f>F107/N107</f>
+        <v>0</v>
+      </c>
+      <c r="R107" s="15">
+        <f t="shared" ref="R107" si="161">E107/N107</f>
+        <v>0</v>
+      </c>
+      <c r="S107" s="15">
+        <v>0</v>
+      </c>
+      <c r="T107" s="15">
+        <v>0</v>
+      </c>
+      <c r="U107" s="15">
+        <f t="shared" ref="U107" si="162">I107/N107</f>
+        <v>0</v>
+      </c>
+      <c r="V107" s="16">
+        <f>J107/N107</f>
+        <v>0</v>
+      </c>
+      <c r="W107" s="15">
+        <v>0</v>
+      </c>
+      <c r="X107" s="16">
+        <f t="shared" ref="X107" si="163">L107/N107</f>
+        <v>0</v>
+      </c>
+      <c r="Y107" s="15">
+        <f t="shared" ref="Y107" si="164">M107/N107</f>
         <v>0</v>
       </c>
     </row>
@@ -18422,386 +18794,386 @@
   <sheetData>
     <row r="1" spans="1:12" s="4" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B1" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="C1" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="D1" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="D1" s="4" t="s">
+      <c r="E1" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="F1" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="G1" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="H1" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="I1" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="J1" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="K1" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="K1" s="4" t="s">
+      <c r="L1" s="4" t="s">
         <v>121</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="2" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="C2" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="D2" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="E2" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="F2" s="3" t="s">
-        <v>128</v>
-      </c>
       <c r="G2" s="3" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H2" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="I2" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>133</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="3" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="B3" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="C3" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="D3" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="E3" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="G3" s="3" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H3" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>143</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="K3" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="B4" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="C4" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="D4" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="E4" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="F4" s="2"/>
       <c r="G4" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H4" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="I4" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="J4" s="3" t="s">
+      <c r="K4" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="K4" s="3" t="s">
+      <c r="L4" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="5" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
+        <v>157</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="D5" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="F5" s="2"/>
       <c r="G5" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H5" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="I5" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="J5" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="J5" s="3" t="s">
+      <c r="K5" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="K5" s="3" t="s">
+      <c r="L5" s="3" t="s">
         <v>167</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="6" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B6" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="C6" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="D6" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>172</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>173</v>
       </c>
       <c r="F6" s="2"/>
       <c r="G6" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="J6" s="3" t="s">
+      <c r="K6" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="K6" s="3" t="s">
+      <c r="L6" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="7" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="C7" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="D7" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>183</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>184</v>
       </c>
       <c r="F7" s="2"/>
       <c r="G7" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H7" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="I7" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="J7" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="J7" s="3" t="s">
+      <c r="K7" s="3" t="s">
         <v>188</v>
       </c>
-      <c r="K7" s="3" t="s">
+      <c r="L7" s="3" t="s">
         <v>189</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="8" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="C8" s="3" t="s">
         <v>192</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>193</v>
       </c>
       <c r="D8" s="2"/>
       <c r="E8" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="F8" s="2"/>
       <c r="G8" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H8" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="I8" s="3" t="s">
         <v>196</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="J8" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="J8" s="3" t="s">
+      <c r="K8" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="K8" s="3" t="s">
+      <c r="L8" s="3" t="s">
         <v>199</v>
-      </c>
-      <c r="L8" s="3" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="9" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A9" s="3"/>
       <c r="B9" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="D9" s="2"/>
       <c r="E9" s="3" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F9" s="2"/>
       <c r="G9" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H9" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="I9" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="J9" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="J9" s="3" t="s">
+      <c r="K9" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="K9" s="3" t="s">
+      <c r="L9" s="3" t="s">
         <v>208</v>
-      </c>
-      <c r="L9" s="3" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="10" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A10" s="3"/>
       <c r="B10" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="C10" s="3" t="s">
         <v>210</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>211</v>
       </c>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
       <c r="F10" s="2"/>
       <c r="G10" s="3" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H10" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="I10" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="J10" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="J10" s="3" t="s">
+      <c r="K10" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="K10" s="3" t="s">
+      <c r="L10" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="11" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A11" s="3"/>
       <c r="B11" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C11" s="3" t="s">
         <v>218</v>
-      </c>
-      <c r="C11" s="3" t="s">
-        <v>219</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
       <c r="F11" s="2"/>
       <c r="G11" s="3" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H11" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="I11" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="J11" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="J11" s="3" t="s">
+      <c r="K11" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="K11" s="3" t="s">
+      <c r="L11" s="3" t="s">
         <v>224</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="12" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -18812,22 +19184,22 @@
       <c r="E12" s="2"/>
       <c r="F12" s="2"/>
       <c r="G12" s="3" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="I12" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="J12" s="3" t="s">
         <v>228</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>229</v>
-      </c>
       <c r="K12" s="3" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -18838,20 +19210,20 @@
       <c r="E13" s="2"/>
       <c r="F13" s="2"/>
       <c r="G13" s="3" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="J13" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>234</v>
-      </c>
       <c r="K13" s="3" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="L13" s="3" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
     </row>
     <row r="14" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -18862,20 +19234,20 @@
       <c r="E14" s="2"/>
       <c r="F14" s="2"/>
       <c r="G14" s="3" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>239</v>
-      </c>
       <c r="K14" s="3" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="L14" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="15" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -18886,20 +19258,20 @@
       <c r="E15" s="2"/>
       <c r="F15" s="2"/>
       <c r="G15" s="3" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>244</v>
-      </c>
       <c r="K15" s="3" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="L15" s="3" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="16" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
@@ -18910,25 +19282,25 @@
       <c r="E16" s="2"/>
       <c r="F16" s="2"/>
       <c r="G16" s="3" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>249</v>
-      </c>
       <c r="K16" s="3" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="L16" s="3" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="17" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A17" s="3" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="B17" s="3">
         <v>7</v>
@@ -18938,25 +19310,25 @@
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
       <c r="G17" s="3" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>254</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>255</v>
-      </c>
       <c r="K17" s="3" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="L17" s="3" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="18" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A18" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B18" s="3">
         <v>10</v>
@@ -18966,25 +19338,25 @@
       <c r="E18" s="2"/>
       <c r="F18" s="2"/>
       <c r="G18" s="3" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H18" s="3"/>
       <c r="I18" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="J18" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="J18" s="3" t="s">
-        <v>260</v>
-      </c>
       <c r="K18" s="3" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="L18" s="3" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
     </row>
     <row r="19" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A19" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B19" s="3">
         <v>10</v>
@@ -18994,25 +19366,25 @@
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
       <c r="G19" s="3" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H19" s="3"/>
       <c r="I19" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="J19" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="J19" s="3" t="s">
-        <v>265</v>
-      </c>
       <c r="K19" s="3" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="L19" s="3" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
     </row>
     <row r="20" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A20" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B20" s="3">
         <v>6</v>
@@ -19022,25 +19394,25 @@
       <c r="E20" s="2"/>
       <c r="F20" s="2"/>
       <c r="G20" s="3" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H20" s="3"/>
       <c r="I20" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="J20" s="3" t="s">
         <v>269</v>
       </c>
-      <c r="J20" s="3" t="s">
-        <v>270</v>
-      </c>
       <c r="K20" s="3" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="L20" s="3" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="21" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B21" s="3">
         <v>8</v>
@@ -19050,25 +19422,25 @@
       <c r="E21" s="2"/>
       <c r="F21" s="2"/>
       <c r="G21" s="3" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H21" s="3"/>
       <c r="I21" s="3" t="s">
+        <v>273</v>
+      </c>
+      <c r="J21" s="3" t="s">
         <v>274</v>
       </c>
-      <c r="J21" s="3" t="s">
-        <v>275</v>
-      </c>
       <c r="K21" s="3" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="L21" s="3" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="22" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A22" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B22" s="3">
         <v>2</v>
@@ -19078,25 +19450,25 @@
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="3" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H22" s="3"/>
       <c r="I22" s="3" t="s">
+        <v>278</v>
+      </c>
+      <c r="J22" s="3" t="s">
         <v>279</v>
       </c>
-      <c r="J22" s="3" t="s">
+      <c r="K22" s="3" t="s">
+        <v>275</v>
+      </c>
+      <c r="L22" s="3" t="s">
         <v>280</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>276</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="23" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A23" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B23" s="3">
         <v>149</v>
@@ -19106,23 +19478,23 @@
       <c r="E23" s="2"/>
       <c r="F23" s="2"/>
       <c r="G23" s="3" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H23" s="3"/>
       <c r="I23" s="3" t="s">
+        <v>282</v>
+      </c>
+      <c r="J23" s="3" t="s">
         <v>283</v>
-      </c>
-      <c r="J23" s="3" t="s">
-        <v>284</v>
       </c>
       <c r="K23" s="3"/>
       <c r="L23" s="3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A24" s="3" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="B24" s="3">
         <v>11</v>
@@ -19132,21 +19504,21 @@
       <c r="E24" s="2"/>
       <c r="F24" s="2"/>
       <c r="G24" s="3" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H24" s="3"/>
       <c r="I24" s="3" t="s">
+        <v>287</v>
+      </c>
+      <c r="J24" s="3" t="s">
         <v>288</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>289</v>
       </c>
       <c r="K24" s="3"/>
       <c r="L24" s="3"/>
     </row>
     <row r="25" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A25" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B25" s="3">
         <v>97</v>
@@ -19156,21 +19528,21 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="3" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H25" s="3"/>
       <c r="I25" s="3" t="s">
+        <v>290</v>
+      </c>
+      <c r="J25" s="3" t="s">
         <v>291</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>292</v>
       </c>
       <c r="K25" s="3"/>
       <c r="L25" s="3"/>
     </row>
     <row r="26" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A26" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B26" s="3">
         <v>32</v>
@@ -19180,14 +19552,14 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="3" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H26" s="3"/>
       <c r="I26" s="3" t="s">
+        <v>293</v>
+      </c>
+      <c r="J26" s="3" t="s">
         <v>294</v>
-      </c>
-      <c r="J26" s="3" t="s">
-        <v>295</v>
       </c>
       <c r="K26" s="3"/>
       <c r="L26" s="3"/>
@@ -19204,21 +19576,21 @@
       <c r="E27" s="2"/>
       <c r="F27" s="2"/>
       <c r="G27" s="3" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3" t="s">
+        <v>296</v>
+      </c>
+      <c r="J27" s="3" t="s">
         <v>297</v>
-      </c>
-      <c r="J27" s="3" t="s">
-        <v>298</v>
       </c>
       <c r="K27" s="3"/>
       <c r="L27" s="3"/>
     </row>
     <row r="28" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A28" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B28" s="3">
         <v>22</v>
@@ -19228,21 +19600,21 @@
       <c r="E28" s="2"/>
       <c r="F28" s="2"/>
       <c r="G28" s="3" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3" t="s">
+        <v>299</v>
+      </c>
+      <c r="J28" s="3" t="s">
         <v>300</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>301</v>
       </c>
       <c r="K28" s="3"/>
       <c r="L28" s="3"/>
     </row>
     <row r="29" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A29" s="3" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="B29" s="3">
         <f>SUM(B17:B28)</f>
@@ -19253,14 +19625,14 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="3" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3" t="s">
+        <v>303</v>
+      </c>
+      <c r="J29" s="3" t="s">
         <v>304</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>305</v>
       </c>
       <c r="K29" s="3"/>
       <c r="L29" s="3"/>
@@ -19273,14 +19645,14 @@
       <c r="E30" s="2"/>
       <c r="F30" s="2"/>
       <c r="G30" s="3" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3" t="s">
+        <v>306</v>
+      </c>
+      <c r="J30" s="3" t="s">
         <v>307</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>308</v>
       </c>
       <c r="K30" s="3"/>
       <c r="L30" s="2"/>
@@ -19293,14 +19665,14 @@
       <c r="E31" s="2"/>
       <c r="F31" s="2"/>
       <c r="G31" s="3" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H31" s="3"/>
       <c r="I31" s="3" t="s">
+        <v>309</v>
+      </c>
+      <c r="J31" s="3" t="s">
         <v>310</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>311</v>
       </c>
       <c r="K31" s="3"/>
       <c r="L31" s="2"/>
@@ -19313,14 +19685,14 @@
       <c r="E32" s="2"/>
       <c r="F32" s="2"/>
       <c r="G32" s="3" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H32" s="3"/>
       <c r="I32" s="3" t="s">
+        <v>312</v>
+      </c>
+      <c r="J32" s="3" t="s">
         <v>313</v>
-      </c>
-      <c r="J32" s="3" t="s">
-        <v>314</v>
       </c>
       <c r="K32" s="3"/>
       <c r="L32" s="2"/>
@@ -19333,14 +19705,14 @@
       <c r="E33" s="2"/>
       <c r="F33" s="2"/>
       <c r="G33" s="3" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H33" s="3"/>
       <c r="I33" s="3" t="s">
+        <v>315</v>
+      </c>
+      <c r="J33" s="3" t="s">
         <v>316</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>317</v>
       </c>
       <c r="K33" s="3"/>
       <c r="L33" s="2"/>
@@ -19353,11 +19725,11 @@
       <c r="E34" s="2"/>
       <c r="F34" s="2"/>
       <c r="G34" s="3" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H34" s="3"/>
       <c r="I34" s="3" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="2"/>
@@ -19371,11 +19743,11 @@
       <c r="E35" s="2"/>
       <c r="F35" s="2"/>
       <c r="G35" s="3" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H35" s="3"/>
       <c r="I35" s="3" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="2"/>
@@ -19383,1037 +19755,1037 @@
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G36" s="3" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H36" s="3"/>
       <c r="I36" s="3" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="37" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G37" s="3" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G38" s="3" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G39" s="3" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G40" s="3" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G41" s="3" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G42" s="3" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="I42" s="3" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G43" s="3" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="I43" s="3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G44" s="3" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="I44" s="3" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G45" s="3" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="I45" s="3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G46" s="3" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="I46" s="3" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G47" s="3" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="I47" s="3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="G48" s="3" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="I48" s="3" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="49" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G49" s="3" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="I49" s="3" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="50" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G50" s="3" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="I50" s="3" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="51" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G51" s="3" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I51" s="3" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
     </row>
     <row r="52" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G52" s="3" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I52" s="3" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
     </row>
     <row r="53" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G53" s="3" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="I53" s="3" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
     </row>
     <row r="54" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G54" s="3" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="I54" s="3" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
     </row>
     <row r="55" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G55" s="3" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="I55" s="3" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="56" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G56" s="3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="I56" s="3" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="57" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G57" s="3" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="I57" s="3" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="58" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G58" s="3" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I58" s="3" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="59" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G59" s="3" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I59" s="3" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="60" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G60" s="3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="I60" s="3" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="61" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G61" s="3" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="I61" s="3" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="62" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G62" s="3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="I62" s="3" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
     </row>
     <row r="63" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G63" s="3" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I63" s="3" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="64" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G64" s="3" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I64" s="3" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
     </row>
     <row r="65" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G65" s="3" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I65" s="3" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
     </row>
     <row r="66" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G66" s="3" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="I66" s="3" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
     </row>
     <row r="67" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G67" s="3" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="I67" s="3" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
     </row>
     <row r="68" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G68" s="3" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="I68" s="3" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
     </row>
     <row r="69" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G69" s="3" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="I69" s="3" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
     </row>
     <row r="70" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G70" s="3" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="I70" s="3" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
     </row>
     <row r="71" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G71" s="3" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="I71" s="3" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
     </row>
     <row r="72" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G72" s="3" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="I72" s="3" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
     </row>
     <row r="73" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G73" s="3" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="I73" s="3" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
     </row>
     <row r="74" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G74" s="3" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="I74" s="3" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
     </row>
     <row r="75" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G75" s="3" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="I75" s="3" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="76" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G76" s="3" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="I76" s="3" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="77" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G77" s="3" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="I77" s="3" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
     </row>
     <row r="78" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G78" s="3" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="I78" s="3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="79" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G79" s="3" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="I79" s="3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="80" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G80" s="3" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="I80" s="3" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="81" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G81" s="3" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="I81" s="3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
     </row>
     <row r="82" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G82" s="3" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I82" s="3" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
     </row>
     <row r="83" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G83" s="3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="I83" s="3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
     </row>
     <row r="84" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G84" s="3" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="I84" s="3" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
     </row>
     <row r="85" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G85" s="3" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="I85" s="3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
     </row>
     <row r="86" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G86" s="3" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="I86" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="87" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G87" s="3" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="I87" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
     </row>
     <row r="88" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G88" s="3" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="I88" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
     </row>
     <row r="89" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G89" s="3" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="I89" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
     </row>
     <row r="90" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G90" s="3" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="I90" s="3" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="91" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G91" s="3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="I91" s="3" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
     </row>
     <row r="92" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G92" s="3" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="I92" s="3" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
     </row>
     <row r="93" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G93" s="3" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="I93" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="94" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G94" s="3" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I94" s="3" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
     </row>
     <row r="95" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G95" s="3" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I95" s="3" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
     </row>
     <row r="96" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G96" s="3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="I96" s="3" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
     </row>
     <row r="97" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G97" s="3" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I97" s="3" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
     </row>
     <row r="98" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G98" s="3" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="I98" s="3" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
     </row>
     <row r="99" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G99" s="3" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
     </row>
     <row r="100" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G100" s="3" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
     </row>
     <row r="101" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G101" s="3" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
     </row>
     <row r="102" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G102" s="3" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
     </row>
     <row r="103" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G103" s="3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
     </row>
     <row r="104" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G104" s="3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
     </row>
     <row r="105" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G105" s="3" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
     </row>
     <row r="106" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G106" s="3" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
     </row>
     <row r="107" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G107" s="3" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
     </row>
     <row r="108" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G108" s="3" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
     </row>
     <row r="109" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G109" s="3" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
     </row>
     <row r="110" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G110" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
     </row>
     <row r="111" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G111" s="3" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
     </row>
     <row r="112" spans="7:9" x14ac:dyDescent="0.2">
       <c r="G112" s="3" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
     </row>
     <row r="113" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G113" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
     </row>
     <row r="114" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G114" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
     </row>
     <row r="115" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G115" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
     </row>
     <row r="116" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G116" s="3" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
     </row>
     <row r="117" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G117" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
     </row>
     <row r="118" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G118" s="3" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
     </row>
     <row r="119" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G119" s="3" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
     </row>
     <row r="120" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G120" s="3" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
     </row>
     <row r="121" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G121" s="3" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="122" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G122" s="3" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
     </row>
     <row r="123" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G123" s="3" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
     </row>
     <row r="124" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G124" s="3" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="125" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G125" s="3" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
     </row>
     <row r="126" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G126" s="3" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
     </row>
     <row r="127" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G127" s="3" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
     </row>
     <row r="128" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G128" s="3" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
     </row>
     <row r="129" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G129" s="3" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
     </row>
     <row r="130" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G130" s="3" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="131" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G131" s="3" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
     </row>
     <row r="132" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G132" s="3" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
     </row>
     <row r="133" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G133" s="3" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="134" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G134" s="3" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
     </row>
     <row r="135" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G135" s="3" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
     </row>
     <row r="136" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G136" s="3" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
     </row>
     <row r="137" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G137" s="3" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="138" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G138" s="3" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
     </row>
     <row r="139" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G139" s="3" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
     </row>
     <row r="140" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G140" s="3" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
     </row>
     <row r="141" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G141" s="3" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
     </row>
     <row r="142" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G142" s="3" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
     </row>
     <row r="143" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G143" s="3" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
     </row>
     <row r="144" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G144" s="3" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
     </row>
     <row r="145" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G145" s="3" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="146" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G146" s="3" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
     </row>
     <row r="147" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G147" s="3" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
     </row>
     <row r="148" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G148" s="3" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
     </row>
     <row r="149" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G149" s="3" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
     </row>
     <row r="150" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G150" s="3" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
     </row>
     <row r="151" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G151" s="3" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
     </row>
     <row r="152" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G152" s="3" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
     </row>
     <row r="153" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G153" s="3" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
     </row>
     <row r="154" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G154" s="3" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
     </row>
     <row r="155" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G155" s="3" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="156" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G156" s="3" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
     </row>
     <row r="157" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G157" s="3" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
     </row>
     <row r="158" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G158" s="3" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
     </row>
     <row r="159" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G159" s="3" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
     </row>
     <row r="160" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G160" s="3" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
     </row>
     <row r="161" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G161" s="3" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
     </row>
     <row r="162" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G162" s="3" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
     </row>
     <row r="163" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G163" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
     </row>
     <row r="164" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G164" s="3" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
     </row>
     <row r="165" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G165" s="3" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
     </row>
     <row r="166" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G166" s="3" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="167" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G167" s="3" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
     </row>
     <row r="168" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G168" s="3" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
     </row>
     <row r="169" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G169" s="3" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
     </row>
     <row r="170" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G170" s="3" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
     </row>
     <row r="171" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G171" s="3" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
     </row>
     <row r="172" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G172" s="3" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
     </row>
     <row r="173" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G173" s="3" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
     </row>
     <row r="174" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G174" s="3" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
     </row>
     <row r="175" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G175" s="3" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
     </row>
     <row r="176" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G176" s="3" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
     </row>
     <row r="177" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G177" s="3" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
     <row r="178" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G178" s="3" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
     </row>
     <row r="179" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G179" s="3" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
     </row>
     <row r="180" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G180" s="3" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
     </row>
     <row r="181" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G181" s="3" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
     <row r="182" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G182" s="3" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
     </row>
     <row r="183" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G183" s="3" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
     </row>
     <row r="184" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G184" s="3" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="185" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G185" s="3" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
     </row>
     <row r="186" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G186" s="3" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="187" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G187" s="3" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
     </row>
     <row r="188" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G188" s="3" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
     </row>
     <row r="189" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G189" s="3" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
     </row>
     <row r="190" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G190" s="3" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
     </row>
     <row r="191" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G191" s="3" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
     </row>
     <row r="192" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G192" s="3" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
     </row>
     <row r="193" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G193" s="3" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
     </row>
     <row r="194" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G194" s="3" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
     </row>
     <row r="195" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G195" s="3" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
     </row>
     <row r="196" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G196" s="3" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
     </row>
     <row r="197" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G197" s="3" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="198" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G198" s="3" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
     </row>
     <row r="199" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G199" s="3" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
     </row>
     <row r="200" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G200" s="3" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
     </row>
     <row r="201" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G201" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
     </row>
     <row r="202" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G202" s="3" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
     </row>
     <row r="203" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G203" s="3" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
     </row>
     <row r="204" spans="7:7" x14ac:dyDescent="0.2">
       <c r="G204" s="3" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
     </row>
   </sheetData>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B38C7DAB-9DB5-4F46-9AEA-1308F28CAAB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{32D858FD-D958-9544-AF6A-F647DAA4049C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="2100" yWindow="-26980" windowWidth="43440" windowHeight="23120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -64,7 +64,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="760">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1094" uniqueCount="766">
   <si>
     <t>Trade ID</t>
   </si>
@@ -2344,6 +2344,24 @@
   </si>
   <si>
     <t>Gold (+)</t>
+  </si>
+  <si>
+    <t>ZW</t>
+  </si>
+  <si>
+    <t>wheat</t>
+  </si>
+  <si>
+    <t>Wheat Futures</t>
+  </si>
+  <si>
+    <t>Wheat (+)</t>
+  </si>
+  <si>
+    <t>ZWZ6</t>
+  </si>
+  <si>
+    <t>OPEN</t>
   </si>
 </sst>
 </file>
@@ -2431,7 +2449,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -2474,6 +2492,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -2487,7 +2511,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="59">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2633,6 +2657,24 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="9" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -5006,7 +5048,7 @@
         <v>46266</v>
       </c>
       <c r="D28" s="35">
-        <f t="shared" ref="D28:D71" si="7">C28-B28</f>
+        <f t="shared" ref="D28:D72" si="7">C28-B28</f>
         <v>1</v>
       </c>
       <c r="E28" s="33" t="s">
@@ -8267,13 +8309,76 @@
       <c r="Y71" s="39"/>
     </row>
     <row r="72" spans="1:26" x14ac:dyDescent="0.25">
-      <c r="B72" s="34"/>
-      <c r="C72" s="34"/>
-      <c r="D72" s="35"/>
-      <c r="G72" s="36"/>
-      <c r="I72" s="36"/>
-      <c r="Q72" s="39"/>
-      <c r="T72" s="40"/>
+      <c r="A72" s="33">
+        <v>64</v>
+      </c>
+      <c r="B72" s="34">
+        <v>46323</v>
+      </c>
+      <c r="C72" s="53">
+        <v>46324</v>
+      </c>
+      <c r="D72" s="54">
+        <f t="shared" si="7"/>
+        <v>1</v>
+      </c>
+      <c r="E72" s="55" t="s">
+        <v>760</v>
+      </c>
+      <c r="F72" s="55" t="s">
+        <v>761</v>
+      </c>
+      <c r="G72" s="56" t="s">
+        <v>762</v>
+      </c>
+      <c r="H72" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="I72" s="56" t="s">
+        <v>763</v>
+      </c>
+      <c r="J72" s="55" t="s">
+        <v>29</v>
+      </c>
+      <c r="K72" s="55" t="s">
+        <v>114</v>
+      </c>
+      <c r="L72" s="55" t="s">
+        <v>764</v>
+      </c>
+      <c r="M72" s="55">
+        <v>4</v>
+      </c>
+      <c r="N72" s="55">
+        <v>599.70000000000005</v>
+      </c>
+      <c r="O72" s="55" t="s">
+        <v>765</v>
+      </c>
+      <c r="P72" s="55">
+        <v>603.25</v>
+      </c>
+      <c r="Q72" s="57">
+        <v>120650</v>
+      </c>
+      <c r="R72" s="55">
+        <v>8.5</v>
+      </c>
+      <c r="S72" s="55" t="s">
+        <v>765</v>
+      </c>
+      <c r="T72" s="58" t="s">
+        <v>765</v>
+      </c>
+      <c r="U72" s="55" t="s">
+        <v>765</v>
+      </c>
+      <c r="V72" s="55" t="s">
+        <v>765</v>
+      </c>
+      <c r="W72" s="33">
+        <v>713</v>
+      </c>
       <c r="Y72" s="39"/>
     </row>
     <row r="73" spans="1:26" x14ac:dyDescent="0.25">
@@ -8305,8 +8410,8 @@
         <v>93</v>
       </c>
       <c r="E76" s="46">
-        <f>AVERAGE(D2:D63)</f>
-        <v>6.4838709677419351</v>
+        <f>AVERAGE(D2:D71)</f>
+        <v>6.2285714285714286</v>
       </c>
       <c r="F76" s="46"/>
       <c r="G76" s="36"/>
@@ -8316,8 +8421,8 @@
         <v>90636.47</v>
       </c>
       <c r="W76" s="39">
-        <f>SUM(W2:W71)</f>
-        <v>0</v>
+        <f>SUM(W2:W74)</f>
+        <v>713</v>
       </c>
       <c r="X76" s="39">
         <f>SUM(X2:X70)</f>
@@ -8330,8 +8435,8 @@
         <v>94</v>
       </c>
       <c r="E77" s="46">
-        <f>AVERAGE(D2:D11,D13,D15:D63)</f>
-        <v>4.7666666666666666</v>
+        <f>AVERAGE(D2:D11,D13,D15:D71)</f>
+        <v>4.7058823529411766</v>
       </c>
       <c r="F77" s="46"/>
       <c r="G77" s="36"/>
@@ -8352,7 +8457,7 @@
       <c r="G79" s="36"/>
       <c r="V79" s="39">
         <f>V76+W76</f>
-        <v>90636.47</v>
+        <v>91349.47</v>
       </c>
     </row>
     <row r="80" spans="1:26" x14ac:dyDescent="0.25">
@@ -8378,7 +8483,7 @@
     <row r="85" spans="7:22" x14ac:dyDescent="0.25">
       <c r="V85" s="50">
         <f>V79/V82</f>
-        <v>0.27218159159159161</v>
+        <v>0.27432273273273272</v>
       </c>
     </row>
   </sheetData>
@@ -8391,7 +8496,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:I100"/>
+  <dimension ref="A1:I101"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -8457,11 +8562,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C100" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C101" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D100" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D101" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -9638,7 +9743,7 @@
       </c>
       <c r="G74" s="27">
         <f>AVERAGE(C3:C960)</f>
-        <v>945.7458163265303</v>
+        <v>936.00090909090875</v>
       </c>
       <c r="I74" s="27">
         <v>910.5062105263155</v>
@@ -9665,7 +9770,7 @@
       </c>
       <c r="G75" s="27">
         <f>_xlfn.STDEV.S(C3:C960)</f>
-        <v>3951.4887179831735</v>
+        <v>3932.4718983925536</v>
       </c>
       <c r="I75" s="27">
         <v>4007.840575031722</v>
@@ -9692,7 +9797,7 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
-        <v>3.7993906783925544</v>
+        <v>3.7784259311256974</v>
       </c>
       <c r="I76" s="28">
         <v>3.6063904566064999</v>
@@ -9719,7 +9824,7 @@
       </c>
       <c r="G77" s="29">
         <f>_xlfn.STDEV.S(D2:D960)*SQRT(252)</f>
-        <v>0.16864973925541754</v>
+        <v>0.16784580275408542</v>
       </c>
       <c r="I77" s="29">
         <v>0.17112271724924777</v>
@@ -9746,7 +9851,7 @@
       </c>
       <c r="G78" s="29" cm="1">
         <f t="array" ref="G78">PRODUCT(1+D3:D960)-1</f>
-        <v>0.27794725776884577</v>
+        <v>0.27789027871295646</v>
       </c>
       <c r="I78" s="29">
         <v>0.25939907562804132</v>
@@ -9773,7 +9878,7 @@
       </c>
       <c r="G79" s="29" cm="1">
         <f t="array" ref="G79">PRODUCT(1+D2:D960)^(252/COUNT(D2:D960))-1</f>
-        <v>0.86691189510860522</v>
+        <v>0.8550848864205276</v>
       </c>
       <c r="I79" s="29">
         <v>0.83201424728177864</v>
@@ -10134,6 +10239,23 @@
       <c r="D100" s="23">
         <f t="shared" si="1"/>
         <v>4.9523746636512206E-3</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A101" s="26">
+        <v>46323</v>
+      </c>
+      <c r="B101" s="5">
+        <f>B100-19</f>
+        <v>426120</v>
+      </c>
+      <c r="C101" s="5">
+        <f t="shared" si="0"/>
+        <v>-19</v>
+      </c>
+      <c r="D101" s="23">
+        <f t="shared" si="1"/>
+        <v>-4.4586390825528763E-5</v>
       </c>
     </row>
   </sheetData>
@@ -15500,7 +15622,7 @@
         <v>0</v>
       </c>
       <c r="N69" s="14">
-        <f t="shared" ref="N69:N107" si="0">SUM(C69:M69)</f>
+        <f t="shared" ref="N69:N108" si="0">SUM(C69:M69)</f>
         <v>407651</v>
       </c>
       <c r="O69" s="15">
@@ -18751,6 +18873,93 @@
       </c>
       <c r="Y107" s="15">
         <f t="shared" ref="Y107" si="164">M107/N107</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A108" s="10">
+        <v>46323</v>
+      </c>
+      <c r="B108" s="11">
+        <v>426120</v>
+      </c>
+      <c r="C108" s="19">
+        <v>0</v>
+      </c>
+      <c r="D108" s="13">
+        <f>B108-C108-J108-M108-F108</f>
+        <v>305470</v>
+      </c>
+      <c r="E108" s="13">
+        <v>0</v>
+      </c>
+      <c r="F108" s="13">
+        <v>0</v>
+      </c>
+      <c r="G108" s="13">
+        <v>0</v>
+      </c>
+      <c r="H108" s="13">
+        <v>0</v>
+      </c>
+      <c r="I108" s="13">
+        <v>0</v>
+      </c>
+      <c r="J108" s="13">
+        <v>120650</v>
+      </c>
+      <c r="K108" s="13">
+        <v>0</v>
+      </c>
+      <c r="L108" s="13">
+        <v>0</v>
+      </c>
+      <c r="M108" s="18">
+        <v>0</v>
+      </c>
+      <c r="N108" s="14">
+        <f t="shared" si="0"/>
+        <v>426120</v>
+      </c>
+      <c r="O108" s="15">
+        <f t="shared" ref="O108" si="165">C108/N108</f>
+        <v>0</v>
+      </c>
+      <c r="P108" s="15">
+        <f t="shared" ref="P108" si="166">D108/N108</f>
+        <v>0.71686379423636537</v>
+      </c>
+      <c r="Q108" s="15">
+        <f>F108/N108</f>
+        <v>0</v>
+      </c>
+      <c r="R108" s="15">
+        <f t="shared" ref="R108" si="167">E108/N108</f>
+        <v>0</v>
+      </c>
+      <c r="S108" s="15">
+        <v>0</v>
+      </c>
+      <c r="T108" s="15">
+        <v>0</v>
+      </c>
+      <c r="U108" s="15">
+        <f t="shared" ref="U108" si="168">I108/N108</f>
+        <v>0</v>
+      </c>
+      <c r="V108" s="16">
+        <f>J108/N108</f>
+        <v>0.28313620576363463</v>
+      </c>
+      <c r="W108" s="15">
+        <v>0</v>
+      </c>
+      <c r="X108" s="16">
+        <f t="shared" ref="X108" si="169">L108/N108</f>
+        <v>0</v>
+      </c>
+      <c r="Y108" s="15">
+        <f t="shared" ref="Y108" si="170">M108/N108</f>
         <v>0</v>
       </c>
     </row>

--- a/track_record.xlsx
+++ b/track_record.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bariskaya/Desktop/_bookmonitor_serve/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{32D858FD-D958-9544-AF6A-F647DAA4049C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{813D75F2-E433-FF4A-B787-AE893735332C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2100" yWindow="-26980" windowWidth="43440" windowHeight="23120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="740" yWindow="-25080" windowWidth="43440" windowHeight="23120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Trades" sheetId="1" r:id="rId1"/>
@@ -8316,11 +8316,11 @@
         <v>46323</v>
       </c>
       <c r="C72" s="53">
-        <v>46324</v>
+        <v>46325</v>
       </c>
       <c r="D72" s="54">
         <f t="shared" si="7"/>
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E72" s="55" t="s">
         <v>760</v>
@@ -8356,7 +8356,7 @@
         <v>765</v>
       </c>
       <c r="P72" s="55">
-        <v>603.25</v>
+        <v>606</v>
       </c>
       <c r="Q72" s="57">
         <v>120650</v>
@@ -8377,7 +8377,7 @@
         <v>765</v>
       </c>
       <c r="W72" s="33">
-        <v>713</v>
+        <v>1263</v>
       </c>
       <c r="Y72" s="39"/>
     </row>
@@ -8422,7 +8422,7 @@
       </c>
       <c r="W76" s="39">
         <f>SUM(W2:W74)</f>
-        <v>713</v>
+        <v>1263</v>
       </c>
       <c r="X76" s="39">
         <f>SUM(X2:X70)</f>
@@ -8457,7 +8457,7 @@
       <c r="G79" s="36"/>
       <c r="V79" s="39">
         <f>V76+W76</f>
-        <v>91349.47</v>
+        <v>91899.47</v>
       </c>
     </row>
     <row r="80" spans="1:26" x14ac:dyDescent="0.25">
@@ -8483,7 +8483,7 @@
     <row r="85" spans="7:22" x14ac:dyDescent="0.25">
       <c r="V85" s="50">
         <f>V79/V82</f>
-        <v>0.27432273273273272</v>
+        <v>0.27597438438438437</v>
       </c>
     </row>
   </sheetData>
@@ -8496,7 +8496,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1FF7184-1B22-B24C-9622-F17CF8130416}">
-  <dimension ref="A1:I101"/>
+  <dimension ref="A1:I102"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.1640625" style="24" bestFit="1" customWidth="1"/>
@@ -8562,11 +8562,11 @@
         <v>356930.64</v>
       </c>
       <c r="C4" s="5">
-        <f t="shared" ref="C4:C101" si="0">B4-B3</f>
+        <f t="shared" ref="C4:C102" si="0">B4-B3</f>
         <v>6713.6600000000326</v>
       </c>
       <c r="D4" s="23">
-        <f t="shared" ref="D4:D101" si="1">C4/B3</f>
+        <f t="shared" ref="D4:D102" si="1">C4/B3</f>
         <v>1.9170001408840977E-2</v>
       </c>
     </row>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="G74" s="27">
         <f>AVERAGE(C3:C960)</f>
-        <v>936.00090909090875</v>
+        <v>934.57089999999971</v>
       </c>
       <c r="I74" s="27">
         <v>910.5062105263155</v>
@@ -9770,7 +9770,7 @@
       </c>
       <c r="G75" s="27">
         <f>_xlfn.STDEV.S(C3:C960)</f>
-        <v>3932.4718983925536</v>
+        <v>3912.5866530809089</v>
       </c>
       <c r="I75" s="27">
         <v>4007.840575031722</v>
@@ -9797,7 +9797,7 @@
       </c>
       <c r="G76" s="28">
         <f>(G74/G75)*SQRT(252)</f>
-        <v>3.7784259311256974</v>
+        <v>3.7918273559678499</v>
       </c>
       <c r="I76" s="28">
         <v>3.6063904566064999</v>
@@ -9824,7 +9824,7 @@
       </c>
       <c r="G77" s="29">
         <f>_xlfn.STDEV.S(D2:D960)*SQRT(252)</f>
-        <v>0.16784580275408542</v>
+        <v>0.16700761174026066</v>
       </c>
       <c r="I77" s="29">
         <v>0.17112271724924777</v>
@@ -9851,7 +9851,7 @@
       </c>
       <c r="G78" s="29" cm="1">
         <f t="array" ref="G78">PRODUCT(1+D3:D960)-1</f>
-        <v>0.27789027871295646</v>
+        <v>0.28026840457191504</v>
       </c>
       <c r="I78" s="29">
         <v>0.25939907562804132</v>
@@ -9878,7 +9878,7 @@
       </c>
       <c r="G79" s="29" cm="1">
         <f t="array" ref="G79">PRODUCT(1+D2:D960)^(252/COUNT(D2:D960))-1</f>
-        <v>0.8550848864205276</v>
+        <v>0.85234286243457613</v>
       </c>
       <c r="I79" s="29">
         <v>0.83201424728177864</v>
@@ -10256,6 +10256,23 @@
       <c r="D101" s="23">
         <f t="shared" si="1"/>
         <v>-4.4586390825528763E-5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A102" s="26">
+        <v>46324</v>
+      </c>
+      <c r="B102" s="5">
+        <f>B101+793</f>
+        <v>426913</v>
+      </c>
+      <c r="C102" s="5">
+        <f t="shared" si="0"/>
+        <v>793</v>
+      </c>
+      <c r="D102" s="23">
+        <f t="shared" si="1"/>
+        <v>1.8609781282267906E-3</v>
       </c>
     </row>
   </sheetData>
@@ -15622,7 +15639,7 @@
         <v>0</v>
       </c>
       <c r="N69" s="14">
-        <f t="shared" ref="N69:N108" si="0">SUM(C69:M69)</f>
+        <f t="shared" ref="N69:N109" si="0">SUM(C69:M69)</f>
         <v>407651</v>
       </c>
       <c r="O69" s="15">
@@ -18452,7 +18469,7 @@
         <v>118964</v>
       </c>
       <c r="D103" s="13">
-        <f>B103-C103-J103-M103-F103</f>
+        <f t="shared" ref="D103:D109" si="133">B103-C103-J103-M103-F103</f>
         <v>305828</v>
       </c>
       <c r="E103" s="13">
@@ -18487,19 +18504,19 @@
         <v>424792</v>
       </c>
       <c r="O103" s="15">
-        <f t="shared" ref="O103" si="133">C103/N103</f>
+        <f t="shared" ref="O103" si="134">C103/N103</f>
         <v>0.28005235503493475</v>
       </c>
       <c r="P103" s="15">
-        <f t="shared" ref="P103" si="134">D103/N103</f>
+        <f t="shared" ref="P103" si="135">D103/N103</f>
         <v>0.71994764496506525</v>
       </c>
       <c r="Q103" s="15">
-        <f t="shared" ref="Q103" si="135">E103/O103</f>
+        <f t="shared" ref="Q103" si="136">E103/O103</f>
         <v>0</v>
       </c>
       <c r="R103" s="15">
-        <f t="shared" ref="R103" si="136">E103/N103</f>
+        <f t="shared" ref="R103" si="137">E103/N103</f>
         <v>0</v>
       </c>
       <c r="S103" s="15">
@@ -18509,22 +18526,22 @@
         <v>0</v>
       </c>
       <c r="U103" s="15">
-        <f t="shared" ref="U103" si="137">I103/N103</f>
+        <f t="shared" ref="U103" si="138">I103/N103</f>
         <v>0</v>
       </c>
       <c r="V103" s="16">
-        <f>J103/N103</f>
+        <f t="shared" ref="V103:V108" si="139">J103/N103</f>
         <v>0</v>
       </c>
       <c r="W103" s="15">
         <v>0</v>
       </c>
       <c r="X103" s="16">
-        <f t="shared" ref="X103" si="138">L103/N103</f>
+        <f t="shared" ref="X103" si="140">L103/N103</f>
         <v>0</v>
       </c>
       <c r="Y103" s="15">
-        <f t="shared" ref="Y103" si="139">M103/N103</f>
+        <f t="shared" ref="Y103" si="141">M103/N103</f>
         <v>0</v>
       </c>
     </row>
@@ -18539,7 +18556,7 @@
         <v>225386</v>
       </c>
       <c r="D104" s="13">
-        <f>B104-C104-J104-M104-F104</f>
+        <f t="shared" si="133"/>
         <v>194568</v>
       </c>
       <c r="E104" s="13">
@@ -18574,19 +18591,19 @@
         <v>419954</v>
       </c>
       <c r="O104" s="15">
-        <f t="shared" ref="O104" si="140">C104/N104</f>
+        <f t="shared" ref="O104" si="142">C104/N104</f>
         <v>0.53669211389818883</v>
       </c>
       <c r="P104" s="15">
-        <f t="shared" ref="P104" si="141">D104/N104</f>
+        <f t="shared" ref="P104" si="143">D104/N104</f>
         <v>0.46330788610181117</v>
       </c>
       <c r="Q104" s="15">
-        <f t="shared" ref="Q104" si="142">E104/O104</f>
+        <f t="shared" ref="Q104" si="144">E104/O104</f>
         <v>0</v>
       </c>
       <c r="R104" s="15">
-        <f t="shared" ref="R104" si="143">E104/N104</f>
+        <f t="shared" ref="R104" si="145">E104/N104</f>
         <v>0</v>
       </c>
       <c r="S104" s="15">
@@ -18596,22 +18613,22 @@
         <v>0</v>
       </c>
       <c r="U104" s="15">
-        <f t="shared" ref="U104" si="144">I104/N104</f>
+        <f t="shared" ref="U104" si="146">I104/N104</f>
         <v>0</v>
       </c>
       <c r="V104" s="16">
-        <f>J104/N104</f>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="W104" s="15">
         <v>0</v>
       </c>
       <c r="X104" s="16">
-        <f t="shared" ref="X104" si="145">L104/N104</f>
+        <f t="shared" ref="X104" si="147">L104/N104</f>
         <v>0</v>
       </c>
       <c r="Y104" s="15">
-        <f t="shared" ref="Y104" si="146">M104/N104</f>
+        <f t="shared" ref="Y104" si="148">M104/N104</f>
         <v>0</v>
       </c>
     </row>
@@ -18626,7 +18643,7 @@
         <v>0</v>
       </c>
       <c r="D105" s="13">
-        <f>B105-C105-J105-M105-F105</f>
+        <f t="shared" si="133"/>
         <v>260534</v>
       </c>
       <c r="E105" s="13">
@@ -18661,11 +18678,11 @@
         <v>422639</v>
       </c>
       <c r="O105" s="15">
-        <f t="shared" ref="O105" si="147">C105/N105</f>
+        <f t="shared" ref="O105" si="149">C105/N105</f>
         <v>0</v>
       </c>
       <c r="P105" s="15">
-        <f t="shared" ref="P105" si="148">D105/N105</f>
+        <f t="shared" ref="P105" si="150">D105/N105</f>
         <v>0.61644571371785373</v>
       </c>
       <c r="Q105" s="15">
@@ -18673,7 +18690,7 @@
         <v>0.38355428628214622</v>
       </c>
       <c r="R105" s="15">
-        <f t="shared" ref="R105" si="149">E105/N105</f>
+        <f t="shared" ref="R105" si="151">E105/N105</f>
         <v>0</v>
       </c>
       <c r="S105" s="15">
@@ -18683,22 +18700,22 @@
         <v>0</v>
       </c>
       <c r="U105" s="15">
-        <f t="shared" ref="U105" si="150">I105/N105</f>
+        <f t="shared" ref="U105" si="152">I105/N105</f>
         <v>0</v>
       </c>
       <c r="V105" s="16">
-        <f>J105/N105</f>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="W105" s="15">
         <v>0</v>
       </c>
       <c r="X105" s="16">
-        <f t="shared" ref="X105" si="151">L105/N105</f>
+        <f t="shared" ref="X105" si="153">L105/N105</f>
         <v>0</v>
       </c>
       <c r="Y105" s="15">
-        <f t="shared" ref="Y105" si="152">M105/N105</f>
+        <f t="shared" ref="Y105" si="154">M105/N105</f>
         <v>0</v>
       </c>
     </row>
@@ -18713,7 +18730,7 @@
         <v>0</v>
       </c>
       <c r="D106" s="13">
-        <f>B106-C106-J106-M106-F106</f>
+        <f t="shared" si="133"/>
         <v>261934</v>
       </c>
       <c r="E106" s="13">
@@ -18748,11 +18765,11 @@
         <v>424039</v>
       </c>
       <c r="O106" s="15">
-        <f t="shared" ref="O106" si="153">C106/N106</f>
+        <f t="shared" ref="O106" si="155">C106/N106</f>
         <v>0</v>
       </c>
       <c r="P106" s="15">
-        <f t="shared" ref="P106" si="154">D106/N106</f>
+        <f t="shared" ref="P106" si="156">D106/N106</f>
         <v>0.61771205007086616</v>
       </c>
       <c r="Q106" s="15">
@@ -18760,7 +18777,7 @@
         <v>0.3822879499291339</v>
       </c>
       <c r="R106" s="15">
-        <f t="shared" ref="R106" si="155">E106/N106</f>
+        <f t="shared" ref="R106" si="157">E106/N106</f>
         <v>0</v>
       </c>
       <c r="S106" s="15">
@@ -18770,22 +18787,22 @@
         <v>0</v>
       </c>
       <c r="U106" s="15">
-        <f t="shared" ref="U106" si="156">I106/N106</f>
+        <f t="shared" ref="U106" si="158">I106/N106</f>
         <v>0</v>
       </c>
       <c r="V106" s="16">
-        <f>J106/N106</f>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="W106" s="15">
         <v>0</v>
       </c>
       <c r="X106" s="16">
-        <f t="shared" ref="X106" si="157">L106/N106</f>
+        <f t="shared" ref="X106" si="159">L106/N106</f>
         <v>0</v>
       </c>
       <c r="Y106" s="15">
-        <f t="shared" ref="Y106" si="158">M106/N106</f>
+        <f t="shared" ref="Y106" si="160">M106/N106</f>
         <v>0</v>
       </c>
     </row>
@@ -18800,7 +18817,7 @@
         <v>0</v>
       </c>
       <c r="D107" s="13">
-        <f>B107-C107-J107-M107-F107</f>
+        <f t="shared" si="133"/>
         <v>426139</v>
       </c>
       <c r="E107" s="13">
@@ -18835,11 +18852,11 @@
         <v>426139</v>
       </c>
       <c r="O107" s="15">
-        <f t="shared" ref="O107" si="159">C107/N107</f>
+        <f t="shared" ref="O107" si="161">C107/N107</f>
         <v>0</v>
       </c>
       <c r="P107" s="15">
-        <f t="shared" ref="P107" si="160">D107/N107</f>
+        <f t="shared" ref="P107" si="162">D107/N107</f>
         <v>1</v>
       </c>
       <c r="Q107" s="15">
@@ -18847,7 +18864,7 @@
         <v>0</v>
       </c>
       <c r="R107" s="15">
-        <f t="shared" ref="R107" si="161">E107/N107</f>
+        <f t="shared" ref="R107" si="163">E107/N107</f>
         <v>0</v>
       </c>
       <c r="S107" s="15">
@@ -18857,22 +18874,22 @@
         <v>0</v>
       </c>
       <c r="U107" s="15">
-        <f t="shared" ref="U107" si="162">I107/N107</f>
+        <f t="shared" ref="U107" si="164">I107/N107</f>
         <v>0</v>
       </c>
       <c r="V107" s="16">
-        <f>J107/N107</f>
+        <f t="shared" si="139"/>
         <v>0</v>
       </c>
       <c r="W107" s="15">
         <v>0</v>
       </c>
       <c r="X107" s="16">
-        <f t="shared" ref="X107" si="163">L107/N107</f>
+        <f t="shared" ref="X107" si="165">L107/N107</f>
         <v>0</v>
       </c>
       <c r="Y107" s="15">
-        <f t="shared" ref="Y107" si="164">M107/N107</f>
+        <f t="shared" ref="Y107" si="166">M107/N107</f>
         <v>0</v>
       </c>
     </row>
@@ -18887,7 +18904,7 @@
         <v>0</v>
       </c>
       <c r="D108" s="13">
-        <f>B108-C108-J108-M108-F108</f>
+        <f t="shared" si="133"/>
         <v>305470</v>
       </c>
       <c r="E108" s="13">
@@ -18922,11 +18939,11 @@
         <v>426120</v>
       </c>
       <c r="O108" s="15">
-        <f t="shared" ref="O108" si="165">C108/N108</f>
+        <f t="shared" ref="O108" si="167">C108/N108</f>
         <v>0</v>
       </c>
       <c r="P108" s="15">
-        <f t="shared" ref="P108" si="166">D108/N108</f>
+        <f t="shared" ref="P108" si="168">D108/N108</f>
         <v>0.71686379423636537</v>
       </c>
       <c r="Q108" s="15">
@@ -18934,7 +18951,7 @@
         <v>0</v>
       </c>
       <c r="R108" s="15">
-        <f t="shared" ref="R108" si="167">E108/N108</f>
+        <f t="shared" ref="R108" si="169">E108/N108</f>
         <v>0</v>
       </c>
       <c r="S108" s="15">
@@ -18944,22 +18961,109 @@
         <v>0</v>
       </c>
       <c r="U108" s="15">
-        <f t="shared" ref="U108" si="168">I108/N108</f>
+        <f t="shared" ref="U108" si="170">I108/N108</f>
         <v>0</v>
       </c>
       <c r="V108" s="16">
-        <f>J108/N108</f>
+        <f t="shared" si="139"/>
         <v>0.28313620576363463</v>
       </c>
       <c r="W108" s="15">
         <v>0</v>
       </c>
       <c r="X108" s="16">
-        <f t="shared" ref="X108" si="169">L108/N108</f>
+        <f t="shared" ref="X108" si="171">L108/N108</f>
         <v>0</v>
       </c>
       <c r="Y108" s="15">
-        <f t="shared" ref="Y108" si="170">M108/N108</f>
+        <f t="shared" ref="Y108" si="172">M108/N108</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
+      <c r="A109" s="10">
+        <v>46324</v>
+      </c>
+      <c r="B109" s="11">
+        <v>426913</v>
+      </c>
+      <c r="C109" s="19">
+        <v>0</v>
+      </c>
+      <c r="D109" s="13">
+        <f t="shared" si="133"/>
+        <v>306263</v>
+      </c>
+      <c r="E109" s="13">
+        <v>0</v>
+      </c>
+      <c r="F109" s="13">
+        <v>0</v>
+      </c>
+      <c r="G109" s="13">
+        <v>0</v>
+      </c>
+      <c r="H109" s="13">
+        <v>0</v>
+      </c>
+      <c r="I109" s="13">
+        <v>0</v>
+      </c>
+      <c r="J109" s="13">
+        <v>120650</v>
+      </c>
+      <c r="K109" s="13">
+        <v>0</v>
+      </c>
+      <c r="L109" s="13">
+        <v>0</v>
+      </c>
+      <c r="M109" s="18">
+        <v>0</v>
+      </c>
+      <c r="N109" s="14">
+        <f t="shared" si="0"/>
+        <v>426913</v>
+      </c>
+      <c r="O109" s="15">
+        <f t="shared" ref="O109" si="173">C109/N109</f>
+        <v>0</v>
+      </c>
+      <c r="P109" s="15">
+        <f t="shared" ref="P109" si="174">D109/N109</f>
+        <v>0.7173897257755093</v>
+      </c>
+      <c r="Q109" s="15">
+        <f>F109/N109</f>
+        <v>0</v>
+      </c>
+      <c r="R109" s="15">
+        <f t="shared" ref="R109" si="175">E109/N109</f>
+        <v>0</v>
+      </c>
+      <c r="S109" s="15">
+        <v>0</v>
+      </c>
+      <c r="T109" s="15">
+        <v>0</v>
+      </c>
+      <c r="U109" s="15">
+        <f t="shared" ref="U109" si="176">I109/N109</f>
+        <v>0</v>
+      </c>
+      <c r="V109" s="16">
+        <f t="shared" ref="V109" si="177">J109/N109</f>
+        <v>0.2826102742244907</v>
+      </c>
+      <c r="W109" s="15">
+        <v>0</v>
+      </c>
+      <c r="X109" s="16">
+        <f t="shared" ref="X109" si="178">L109/N109</f>
+        <v>0</v>
+      </c>
+      <c r="Y109" s="15">
+        <f t="shared" ref="Y109" si="179">M109/N109</f>
         <v>0</v>
       </c>
     </row>
